--- a/data.xlsx
+++ b/data.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="190">
   <si>
     <t>순번</t>
   </si>
@@ -608,17 +608,97 @@
   </si>
   <si>
     <t>서울 노원구</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서면동일파크스위트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차아파트</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에이치제이건설</t>
+    </r>
+  </si>
+  <si>
+    <t>특허료</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="182" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -681,6 +761,33 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -696,7 +803,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -747,11 +854,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -833,11 +981,78 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="11">
+    <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
+    <cellStyle name="백분율 2" xfId="2"/>
+    <cellStyle name="백분율 3" xfId="10"/>
+    <cellStyle name="쉼표 [0] 118 2 7 16" xfId="3"/>
+    <cellStyle name="쉼표 [0] 2" xfId="4"/>
+    <cellStyle name="쉼표 [0] 3" xfId="9"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 118 2 7 16" xfId="5"/>
+    <cellStyle name="표준 125" xfId="6"/>
+    <cellStyle name="표준 2" xfId="7"/>
+    <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1317,7 +1532,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S408"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="5" style="2" customWidth="1"/>
@@ -1341,7 +1556,7 @@
     <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="A1" s="7">
         <v>0.71111111111167702</v>
       </c>
@@ -1400,7 +1615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B2" s="10">
         <v>1</v>
       </c>
@@ -1425,7 +1640,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I55" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -1463,7 +1678,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B3" s="10">
         <f>IF(C3="","",COUNTA($C$2:C3))</f>
         <v>2</v>
@@ -1489,7 +1704,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J58" ca="1" si="2">IF(I3="","",
@@ -1522,7 +1737,7 @@
       </c>
       <c r="S3" s="10"/>
     </row>
-    <row r="4" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B4" s="10">
         <f>IF(C4="","",COUNTA($C$2:C4))</f>
         <v>3</v>
@@ -1548,7 +1763,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1574,7 +1789,7 @@
       </c>
       <c r="S4" s="10"/>
     </row>
-    <row r="5" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B5" s="10">
         <f>IF(C5="","",COUNTA($C$2:C5))</f>
         <v>4</v>
@@ -1620,7 +1835,7 @@
       <c r="R5" s="14"/>
       <c r="S5" s="10"/>
     </row>
-    <row r="6" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B6" s="10">
         <f>IF(C6="","",COUNTA($C$2:C6))</f>
         <v>5</v>
@@ -1646,7 +1861,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1676,7 +1891,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B7" s="10">
         <f>IF(C7="","",COUNTA($C$2:C7))</f>
         <v>6</v>
@@ -1702,7 +1917,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1725,7 +1940,7 @@
       </c>
       <c r="S7" s="10"/>
     </row>
-    <row r="8" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B8" s="10">
         <f>IF(C8="","",COUNTA($C$2:C8))</f>
         <v>7</v>
@@ -1751,7 +1966,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1776,7 +1991,7 @@
       </c>
       <c r="S8" s="10"/>
     </row>
-    <row r="9" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B9" s="10">
         <f>IF(C9="","",COUNTA($C$2:C9))</f>
         <v>8</v>
@@ -1802,7 +2017,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1828,7 +2043,7 @@
       </c>
       <c r="S9" s="10"/>
     </row>
-    <row r="10" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B10" s="10">
         <f>IF(C10="","",COUNTA($C$2:C10))</f>
         <v>9</v>
@@ -1854,7 +2069,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1872,7 +2087,7 @@
       <c r="R10" s="14"/>
       <c r="S10" s="10"/>
     </row>
-    <row r="11" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B11" s="10">
         <f>IF(C11="","",COUNTA($C$2:C11))</f>
         <v>10</v>
@@ -1898,7 +2113,7 @@
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J11" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1919,7 +2134,7 @@
       <c r="R11" s="14"/>
       <c r="S11" s="10"/>
     </row>
-    <row r="12" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B12" s="10">
         <f>IF(C12="","",COUNTA($C$2:C12))</f>
         <v>11</v>
@@ -1965,7 +2180,7 @@
       <c r="R12" s="14"/>
       <c r="S12" s="10"/>
     </row>
-    <row r="13" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B13" s="10">
         <f>IF(C13="","",COUNTA($C$2:C13))</f>
         <v>12</v>
@@ -1991,7 +2206,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2021,7 +2236,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B14" s="10">
         <f>IF(C14="","",COUNTA($C$2:C14))</f>
         <v>13</v>
@@ -2047,7 +2262,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2070,7 +2285,7 @@
       </c>
       <c r="S14" s="10"/>
     </row>
-    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B15" s="10">
         <f>IF(C15="","",COUNTA($C$2:C15))</f>
         <v>14</v>
@@ -2096,7 +2311,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2119,7 +2334,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B16" s="10">
         <f>IF(C16="","",COUNTA($C$2:C16))</f>
         <v>15</v>
@@ -2145,7 +2360,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2166,7 +2381,7 @@
       <c r="R16" s="14"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B17" s="10">
         <f>IF(C17="","",COUNTA($C$2:C17))</f>
         <v>16</v>
@@ -2192,7 +2407,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2213,7 +2428,7 @@
       <c r="R17" s="14"/>
       <c r="S17" s="10"/>
     </row>
-    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B18" s="10">
         <f>IF(C18="","",COUNTA($C$2:C18))</f>
         <v>17</v>
@@ -2239,7 +2454,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2260,7 +2475,7 @@
       <c r="R18" s="14"/>
       <c r="S18" s="10"/>
     </row>
-    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B19" s="10">
         <f>IF(C19="","",COUNTA($C$2:C19))</f>
         <v>18</v>
@@ -2286,7 +2501,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2307,7 +2522,7 @@
       <c r="R19" s="14"/>
       <c r="S19" s="10"/>
     </row>
-    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B20" s="10">
         <f>IF(C20="","",COUNTA($C$2:C20))</f>
         <v>19</v>
@@ -2333,7 +2548,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2354,7 +2569,7 @@
       <c r="R20" s="14"/>
       <c r="S20" s="10"/>
     </row>
-    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B21" s="10">
         <f>IF(C21="","",COUNTA($C$2:C21))</f>
         <v>20</v>
@@ -2380,7 +2595,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2403,7 +2618,7 @@
       </c>
       <c r="S21" s="10"/>
     </row>
-    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B22" s="10">
         <f>IF(C22="","",COUNTA($C$2:C22))</f>
         <v>21</v>
@@ -2429,7 +2644,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2452,7 +2667,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B23" s="10">
         <f>IF(C23="","",COUNTA($C$2:C23))</f>
         <v>22</v>
@@ -2478,7 +2693,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2501,7 +2716,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B24" s="10">
         <f>IF(C24="","",COUNTA($C$2:C24))</f>
         <v>23</v>
@@ -2527,7 +2742,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2550,7 +2765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B25" s="10">
         <f>IF(C25="","",COUNTA($C$2:C25))</f>
         <v>24</v>
@@ -2576,7 +2791,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2599,7 +2814,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B26" s="10">
         <f>IF(C26="","",COUNTA($C$2:C26))</f>
         <v>25</v>
@@ -2625,7 +2840,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2648,7 +2863,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B27" s="10">
         <f>IF(C27="","",COUNTA($C$2:C27))</f>
         <v>26</v>
@@ -2674,7 +2889,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2697,7 +2912,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B28" s="10">
         <f>IF(C28="","",COUNTA($C$2:C28))</f>
         <v>27</v>
@@ -2723,7 +2938,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2746,7 +2961,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B29" s="10">
         <f>IF(C29="","",COUNTA($C$2:C29))</f>
         <v>28</v>
@@ -2772,7 +2987,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2795,7 +3010,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B30" s="10">
         <f>IF(C30="","",COUNTA($C$2:C30))</f>
         <v>29</v>
@@ -2821,7 +3036,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2844,7 +3059,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B31" s="10">
         <f>IF(C31="","",COUNTA($C$2:C31))</f>
         <v>30</v>
@@ -2870,7 +3085,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2893,7 +3108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B32" s="10">
         <f>IF(C32="","",COUNTA($C$2:C32))</f>
         <v>31</v>
@@ -2919,7 +3134,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2942,7 +3157,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B33" s="10">
         <f>IF(C33="","",COUNTA($C$2:C33))</f>
         <v>32</v>
@@ -2968,7 +3183,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2991,7 +3206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B34" s="10">
         <f>IF(C34="","",COUNTA($C$2:C34))</f>
         <v>33</v>
@@ -3017,7 +3232,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3040,7 +3255,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B35" s="10">
         <f>IF(C35="","",COUNTA($C$2:C35))</f>
         <v>34</v>
@@ -3066,7 +3281,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3089,7 +3304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B36" s="10">
         <f>IF(C36="","",COUNTA($C$2:C36))</f>
         <v>35</v>
@@ -3115,7 +3330,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3134,7 +3349,7 @@
       <c r="R36" s="14"/>
       <c r="S36" s="10"/>
     </row>
-    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B37" s="10">
         <f>IF(C37="","",COUNTA($C$2:C37))</f>
         <v>36</v>
@@ -3160,7 +3375,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3188,7 +3403,7 @@
       </c>
       <c r="S37" s="10"/>
     </row>
-    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B38" s="10">
         <f>IF(C38="","",COUNTA($C$2:C38))</f>
         <v>37</v>
@@ -3214,7 +3429,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3244,7 +3459,7 @@
       </c>
       <c r="S38" s="10"/>
     </row>
-    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B39" s="10">
         <f>IF(C39="","",COUNTA($C$2:C39))</f>
         <v>38</v>
@@ -3270,7 +3485,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3297,7 +3512,7 @@
       </c>
       <c r="S39" s="10"/>
     </row>
-    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B40" s="10">
         <f>IF(C40="","",COUNTA($C$2:C40))</f>
         <v>39</v>
@@ -3323,7 +3538,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3344,7 +3559,7 @@
       <c r="R40" s="11"/>
       <c r="S40" s="10"/>
     </row>
-    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B41" s="10">
         <f>IF(C41="","",COUNTA($C$2:C41))</f>
         <v>40</v>
@@ -3370,7 +3585,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3398,7 +3613,7 @@
       </c>
       <c r="S41" s="10"/>
     </row>
-    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B42" s="10">
         <f>IF(C42="","",COUNTA($C$2:C42))</f>
         <v>41</v>
@@ -3424,7 +3639,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3451,7 +3666,7 @@
       </c>
       <c r="S42" s="10"/>
     </row>
-    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B43" s="10">
         <f>IF(C43="","",COUNTA($C$2:C43))</f>
         <v>42</v>
@@ -3503,7 +3718,7 @@
       <c r="R43" s="11"/>
       <c r="S43" s="10"/>
     </row>
-    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B44" s="10">
         <f>IF(C44="","",COUNTA($C$2:C44))</f>
         <v>43</v>
@@ -3529,7 +3744,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3554,7 +3769,7 @@
       </c>
       <c r="S44" s="10"/>
     </row>
-    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B45" s="10">
         <f>IF(C45="","",COUNTA($C$2:C45))</f>
         <v>44</v>
@@ -3580,7 +3795,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3598,7 +3813,7 @@
       <c r="R45" s="11"/>
       <c r="S45" s="10"/>
     </row>
-    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B46" s="10">
         <f>IF(C46="","",COUNTA($C$2:C46))</f>
         <v>45</v>
@@ -3624,7 +3839,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3642,7 +3857,7 @@
       <c r="R46" s="11"/>
       <c r="S46" s="10"/>
     </row>
-    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B47" s="10">
         <f>IF(C47="","",COUNTA($C$2:C47))</f>
         <v>46</v>
@@ -3668,7 +3883,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3689,7 +3904,7 @@
       <c r="R47" s="11"/>
       <c r="S47" s="10"/>
     </row>
-    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B48" s="10">
         <f>IF(C48="","",COUNTA($C$2:C48))</f>
         <v>47</v>
@@ -3715,7 +3930,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3736,7 +3951,7 @@
       <c r="R48" s="11"/>
       <c r="S48" s="10"/>
     </row>
-    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B49" s="10">
         <f>IF(C49="","",COUNTA($C$2:C49))</f>
         <v>48</v>
@@ -3762,7 +3977,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3783,7 +3998,7 @@
       <c r="R49" s="11"/>
       <c r="S49" s="10"/>
     </row>
-    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B50" s="10">
         <f>IF(C50="","",COUNTA($C$2:C50))</f>
         <v>49</v>
@@ -3809,7 +4024,7 @@
       </c>
       <c r="I50" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J50" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3827,7 +4042,7 @@
       <c r="R50" s="11"/>
       <c r="S50" s="10"/>
     </row>
-    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B51" s="10">
         <f>IF(C51="","",COUNTA($C$2:C51))</f>
         <v>50</v>
@@ -3853,7 +4068,7 @@
       </c>
       <c r="I51" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J51" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3871,7 +4086,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="10"/>
     </row>
-    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B52" s="10">
         <f>IF(C52="","",COUNTA($C$2:C52))</f>
         <v>51</v>
@@ -3897,7 +4112,7 @@
       </c>
       <c r="I52" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J52" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3918,7 +4133,7 @@
       <c r="R52" s="11"/>
       <c r="S52" s="10"/>
     </row>
-    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B53" s="10">
         <f>IF(C53="","",COUNTA($C$2:C53))</f>
         <v>52</v>
@@ -3944,7 +4159,7 @@
       </c>
       <c r="I53" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J53" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3970,7 +4185,7 @@
       </c>
       <c r="S53" s="10"/>
     </row>
-    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B54" s="10">
         <f>IF(C54="","",COUNTA($C$2:C54))</f>
         <v>53</v>
@@ -4014,7 +4229,7 @@
       <c r="R54" s="11"/>
       <c r="S54" s="10"/>
     </row>
-    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B55" s="10">
         <f>IF(C55="","",COUNTA($C$2:C55))</f>
         <v>54</v>
@@ -4040,7 +4255,7 @@
       </c>
       <c r="I55" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J55" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4061,7 +4276,7 @@
       <c r="R55" s="11"/>
       <c r="S55" s="10"/>
     </row>
-    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B56" s="10">
         <f>IF(C56="","",COUNTA($C$2:C56))</f>
         <v>55</v>
@@ -4087,7 +4302,7 @@
       </c>
       <c r="I56" s="12">
         <f t="shared" ref="I56:I65" ca="1" si="4">IF(C56="","",IF(L56="",TODAY()-C56,L56-C56))</f>
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="J56" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4108,7 +4323,7 @@
       <c r="R56" s="14"/>
       <c r="S56" s="10"/>
     </row>
-    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B57" s="10">
         <f>IF(C57="","",COUNTA($C$2:C57))</f>
         <v>56</v>
@@ -4134,7 +4349,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4155,7 +4370,7 @@
       <c r="R57" s="14"/>
       <c r="S57" s="10"/>
     </row>
-    <row r="58" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B58" s="10">
         <f>IF(C58="","",COUNTA($C$2:C58))</f>
         <v>57</v>
@@ -4181,7 +4396,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4202,7 +4417,7 @@
       <c r="R58" s="14"/>
       <c r="S58" s="10"/>
     </row>
-    <row r="59" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B59" s="10">
         <f>IF(C59="","",COUNTA($C$2:C59))</f>
         <v>58</v>
@@ -4228,7 +4443,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ref="J59:J113" ca="1" si="5">IF(I59="","",
@@ -4257,7 +4472,7 @@
       <c r="R59" s="14"/>
       <c r="S59" s="10"/>
     </row>
-    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B60" s="10">
         <f>IF(C60="","",COUNTA($C$2:C60))</f>
         <v>59</v>
@@ -4292,7 +4507,9 @@
       <c r="K60" s="11">
         <v>46066</v>
       </c>
-      <c r="L60" s="11"/>
+      <c r="L60" s="11">
+        <v>46066</v>
+      </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10" t="s">
         <v>33</v>
@@ -4301,7 +4518,7 @@
       <c r="R60" s="14"/>
       <c r="S60" s="10"/>
     </row>
-    <row r="61" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B61" s="10">
         <f>IF(C61="","",COUNTA($C$2:C61))</f>
         <v>60</v>
@@ -4336,7 +4553,9 @@
       <c r="K61" s="11">
         <v>46066</v>
       </c>
-      <c r="L61" s="11"/>
+      <c r="L61" s="11">
+        <v>46066</v>
+      </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10" t="s">
         <v>33</v>
@@ -4345,7 +4564,7 @@
       <c r="R61" s="14"/>
       <c r="S61" s="10"/>
     </row>
-    <row r="62" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B62" s="10">
         <f>IF(C62="","",COUNTA($C$2:C62))</f>
         <v>61</v>
@@ -4371,7 +4590,7 @@
       </c>
       <c r="I62" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J62" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4389,7 +4608,7 @@
       <c r="R62" s="14"/>
       <c r="S62" s="10"/>
     </row>
-    <row r="63" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B63" s="10">
         <f>IF(C63="","",COUNTA($C$2:C63))</f>
         <v>62</v>
@@ -4415,7 +4634,7 @@
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J63" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4433,7 +4652,7 @@
       <c r="R63" s="14"/>
       <c r="S63" s="10"/>
     </row>
-    <row r="64" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B64" s="10">
         <f>IF(C64="","",COUNTA($C$2:C64))</f>
         <v>63</v>
@@ -4479,7 +4698,7 @@
       <c r="R64" s="14"/>
       <c r="S64" s="10"/>
     </row>
-    <row r="65" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B65" s="10">
         <f>IF(C65="","",COUNTA($C$2:C65))</f>
         <v>64</v>
@@ -4505,7 +4724,7 @@
       </c>
       <c r="I65" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J65" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4523,7 +4742,7 @@
       <c r="R65" s="14"/>
       <c r="S65" s="10"/>
     </row>
-    <row r="66" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B66" s="10">
         <f>IF(C66="","",COUNTA($C$2:C66))</f>
         <v>65</v>
@@ -4549,7 +4768,7 @@
       </c>
       <c r="I66" s="6">
         <f t="shared" ref="I66:I71" ca="1" si="7">IF(C66="","",IF(L66="",TODAY()-C66,L66-C66))</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4565,7 +4784,7 @@
       <c r="R66" s="11"/>
       <c r="S66" s="10"/>
     </row>
-    <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B67" s="10">
         <f>IF(C67="","",COUNTA($C$2:C67))</f>
         <v>66</v>
@@ -4591,7 +4810,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4607,7 +4826,7 @@
       <c r="R67" s="11"/>
       <c r="S67" s="10"/>
     </row>
-    <row r="68" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B68" s="10">
         <f>IF(C68="","",COUNTA($C$2:C68))</f>
         <v>67</v>
@@ -4633,7 +4852,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4649,7 +4868,7 @@
       <c r="R68" s="11"/>
       <c r="S68" s="10"/>
     </row>
-    <row r="69" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B69" s="10">
         <f>IF(C69="","",COUNTA($C$2:C69))</f>
         <v>68</v>
@@ -4675,7 +4894,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4694,7 +4913,7 @@
       <c r="R69" s="11"/>
       <c r="S69" s="10"/>
     </row>
-    <row r="70" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B70" s="10">
         <f>IF(C70="","",COUNTA($C$2:C70))</f>
         <v>69</v>
@@ -4746,7 +4965,7 @@
       <c r="R70" s="11"/>
       <c r="S70" s="10"/>
     </row>
-    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B71" s="10">
         <f>IF(C71="","",COUNTA($C$2:C71))</f>
         <v>70</v>
@@ -4772,11 +4991,11 @@
       </c>
       <c r="I71" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J71" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K71" s="11"/>
       <c r="L71" s="11"/>
@@ -4798,7 +5017,7 @@
       </c>
       <c r="S71" s="10"/>
     </row>
-    <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B72" s="10">
         <f>IF(C72="","",COUNTA($C$2:C72))</f>
         <v>71</v>
@@ -4824,11 +5043,11 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ref="I72:I75" ca="1" si="8">IF(C72="","",IF(L72="",TODAY()-C72,L72-C72))</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K72" s="11">
         <v>46112</v>
@@ -4845,7 +5064,7 @@
       <c r="R72" s="11"/>
       <c r="S72" s="10"/>
     </row>
-    <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B73" s="10">
         <f>IF(C73="","",COUNTA($C$2:C73))</f>
         <v>72</v>
@@ -4899,7 +5118,7 @@
       </c>
       <c r="S73" s="10"/>
     </row>
-    <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B74" s="10">
         <f>IF(C74="","",COUNTA($C$2:C74))</f>
         <v>73</v>
@@ -4943,7 +5162,7 @@
       <c r="R74" s="11"/>
       <c r="S74" s="10"/>
     </row>
-    <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B75" s="10">
         <f>IF(C75="","",COUNTA($C$2:C75))</f>
         <v>74</v>
@@ -4969,11 +5188,11 @@
       </c>
       <c r="I75" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J75" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K75" s="11"/>
       <c r="L75" s="11"/>
@@ -4985,7 +5204,7 @@
       <c r="R75" s="11"/>
       <c r="S75" s="10"/>
     </row>
-    <row r="76" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B76" s="10">
         <f>IF(C76="","",COUNTA($C$2:C76))</f>
         <v>75</v>
@@ -5039,7 +5258,7 @@
       </c>
       <c r="S76" s="10"/>
     </row>
-    <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B77" s="10">
         <f>IF(C77="","",COUNTA($C$2:C77))</f>
         <v>76</v>
@@ -5093,7 +5312,7 @@
       </c>
       <c r="S77" s="10"/>
     </row>
-    <row r="78" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B78" s="10">
         <f>IF(C78="","",COUNTA($C$2:C78))</f>
         <v>77</v>
@@ -5137,7 +5356,7 @@
       <c r="R78" s="11"/>
       <c r="S78" s="10"/>
     </row>
-    <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B79" s="10">
         <f>IF(C79="","",COUNTA($C$2:C79))</f>
         <v>78</v>
@@ -5181,7 +5400,7 @@
       <c r="R79" s="11"/>
       <c r="S79" s="10"/>
     </row>
-    <row r="80" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B80" s="10">
         <f>IF(C80="","",COUNTA($C$2:C80))</f>
         <v>79</v>
@@ -5207,7 +5426,7 @@
       </c>
       <c r="I80" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J80" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5223,7 +5442,7 @@
       <c r="R80" s="11"/>
       <c r="S80" s="10"/>
     </row>
-    <row r="81" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B81" s="10">
         <f>IF(C81="","",COUNTA($C$2:C81))</f>
         <v>80</v>
@@ -5267,7 +5486,7 @@
       <c r="R81" s="11"/>
       <c r="S81" s="10"/>
     </row>
-    <row r="82" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B82" s="10">
         <f>IF(C82="","",COUNTA($C$2:C82))</f>
         <v>81</v>
@@ -5293,7 +5512,7 @@
       </c>
       <c r="I82" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J82" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5319,7 +5538,7 @@
       </c>
       <c r="S82" s="10"/>
     </row>
-    <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B83" s="10">
         <f>IF(C83="","",COUNTA($C$2:C83))</f>
         <v>82</v>
@@ -5345,7 +5564,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5371,7 +5590,7 @@
       </c>
       <c r="S83" s="10"/>
     </row>
-    <row r="84" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B84" s="10">
         <f>IF(C84="","",COUNTA($C$2:C84))</f>
         <v>83</v>
@@ -5397,7 +5616,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5423,7 +5642,7 @@
       </c>
       <c r="S84" s="10"/>
     </row>
-    <row r="85" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B85" s="10">
         <f>IF(C85="","",COUNTA($C$2:C85))</f>
         <v>84</v>
@@ -5449,7 +5668,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5465,7 +5684,7 @@
       <c r="R85" s="11"/>
       <c r="S85" s="10"/>
     </row>
-    <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B86" s="10">
         <f>IF(C86="","",COUNTA($C$2:C86))</f>
         <v>85</v>
@@ -5491,7 +5710,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5517,7 +5736,7 @@
       </c>
       <c r="S86" s="10"/>
     </row>
-    <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B87" s="10">
         <f>IF(C87="","",COUNTA($C$2:C87))</f>
         <v>86</v>
@@ -5561,7 +5780,7 @@
       <c r="R87" s="11"/>
       <c r="S87" s="10"/>
     </row>
-    <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B88" s="10">
         <f>IF(C88="","",COUNTA($C$2:C88))</f>
         <v>87</v>
@@ -5587,7 +5806,7 @@
       </c>
       <c r="I88" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J88" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5613,7 +5832,7 @@
       </c>
       <c r="S88" s="10"/>
     </row>
-    <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B89" s="10">
         <f>IF(C89="","",COUNTA($C$2:C89))</f>
         <v>88</v>
@@ -5639,7 +5858,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5665,7 +5884,7 @@
       </c>
       <c r="S89" s="10"/>
     </row>
-    <row r="90" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B90" s="10">
         <f>IF(C90="","",COUNTA($C$2:C90))</f>
         <v>89</v>
@@ -5709,7 +5928,7 @@
       <c r="R90" s="11"/>
       <c r="S90" s="10"/>
     </row>
-    <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B91" s="10">
         <f>IF(C91="","",COUNTA($C$2:C91))</f>
         <v>90</v>
@@ -5735,7 +5954,7 @@
       </c>
       <c r="I91" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J91" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5751,7 +5970,7 @@
       <c r="R91" s="11"/>
       <c r="S91" s="10"/>
     </row>
-    <row r="92" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B92" s="10">
         <f>IF(C92="","",COUNTA($C$2:C92))</f>
         <v>91</v>
@@ -5795,7 +6014,7 @@
       <c r="R92" s="11"/>
       <c r="S92" s="10"/>
     </row>
-    <row r="93" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B93" s="10">
         <f>IF(C93="","",COUNTA($C$2:C93))</f>
         <v>92</v>
@@ -5839,7 +6058,7 @@
       <c r="R93" s="11"/>
       <c r="S93" s="10"/>
     </row>
-    <row r="94" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B94" s="10">
         <f>IF(C94="","",COUNTA($C$2:C94))</f>
         <v>93</v>
@@ -5865,7 +6084,7 @@
       </c>
       <c r="I94" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J94" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5881,7 +6100,7 @@
       <c r="R94" s="11"/>
       <c r="S94" s="10"/>
     </row>
-    <row r="95" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B95" s="10">
         <f>IF(C95="","",COUNTA($C$2:C95))</f>
         <v>94</v>
@@ -5907,7 +6126,7 @@
       </c>
       <c r="I95" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J95" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5923,7 +6142,7 @@
       <c r="R95" s="11"/>
       <c r="S95" s="10"/>
     </row>
-    <row r="96" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B96" s="10">
         <f>IF(C96="","",COUNTA($C$2:C96))</f>
         <v>95</v>
@@ -5967,7 +6186,7 @@
       <c r="R96" s="11"/>
       <c r="S96" s="10"/>
     </row>
-    <row r="97" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B97" s="10">
         <f>IF(C97="","",COUNTA($C$2:C97))</f>
         <v>96</v>
@@ -5993,7 +6212,7 @@
       </c>
       <c r="I97" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6009,7 +6228,7 @@
       <c r="R97" s="11"/>
       <c r="S97" s="10"/>
     </row>
-    <row r="98" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B98" s="10">
         <f>IF(C98="","",COUNTA($C$2:C98))</f>
         <v>97</v>
@@ -6035,7 +6254,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6051,7 +6270,7 @@
       <c r="R98" s="11"/>
       <c r="S98" s="10"/>
     </row>
-    <row r="99" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B99" s="10">
         <f>IF(C99="","",COUNTA($C$2:C99))</f>
         <v>98</v>
@@ -6076,7 +6295,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6092,7 +6311,7 @@
       <c r="R99" s="11"/>
       <c r="S99" s="10"/>
     </row>
-    <row r="100" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B100" s="10">
         <f>IF(C100="","",COUNTA($C$2:C100))</f>
         <v>99</v>
@@ -6135,7 +6354,7 @@
       <c r="R100" s="11"/>
       <c r="S100" s="10"/>
     </row>
-    <row r="101" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B101" s="10">
         <f>IF(C101="","",COUNTA($C$2:C101))</f>
         <v>100</v>
@@ -6179,7 +6398,7 @@
       <c r="R101" s="11"/>
       <c r="S101" s="10"/>
     </row>
-    <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B102" s="26">
         <f>IF(C102="","",COUNTA($C$2:C102))</f>
         <v>101</v>
@@ -6212,14 +6431,18 @@
         <v>정상</v>
       </c>
       <c r="K102" s="27"/>
-      <c r="L102" s="27"/>
+      <c r="L102" s="27">
+        <v>46066</v>
+      </c>
       <c r="M102" s="26"/>
-      <c r="N102" s="26"/>
+      <c r="N102" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q102" s="11"/>
       <c r="R102" s="11"/>
       <c r="S102" s="10"/>
     </row>
-    <row r="103" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B103" s="10">
         <f>IF(C103="","",COUNTA($C$2:C103))</f>
         <v>102</v>
@@ -6245,7 +6468,7 @@
       </c>
       <c r="I103" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J103" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6254,12 +6477,14 @@
       <c r="K103" s="11"/>
       <c r="L103" s="11"/>
       <c r="M103" s="10"/>
-      <c r="N103" s="10"/>
+      <c r="N103" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q103" s="11"/>
       <c r="R103" s="11"/>
       <c r="S103" s="10"/>
     </row>
-    <row r="104" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B104" s="10">
         <f>IF(C104="","",COUNTA($C$2:C104))</f>
         <v>103</v>
@@ -6285,7 +6510,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6294,12 +6519,14 @@
       <c r="K104" s="11"/>
       <c r="L104" s="11"/>
       <c r="M104" s="10"/>
-      <c r="N104" s="10"/>
+      <c r="N104" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q104" s="11"/>
       <c r="R104" s="11"/>
       <c r="S104" s="10"/>
     </row>
-    <row r="105" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B105" s="10">
         <f>IF(C105="","",COUNTA($C$2:C105))</f>
         <v>104</v>
@@ -6324,7 +6551,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6333,12 +6560,17 @@
       <c r="K105" s="11"/>
       <c r="L105" s="11"/>
       <c r="M105" s="10"/>
-      <c r="N105" s="10"/>
+      <c r="N105" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P105" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="Q105" s="11"/>
       <c r="R105" s="11"/>
       <c r="S105" s="10"/>
     </row>
-    <row r="106" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B106" s="10">
         <f>IF(C106="","",COUNTA($C$2:C106))</f>
         <v>105</v>
@@ -6363,7 +6595,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6372,12 +6604,14 @@
       <c r="K106" s="11"/>
       <c r="L106" s="11"/>
       <c r="M106" s="10"/>
-      <c r="N106" s="10"/>
+      <c r="N106" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q106" s="11"/>
       <c r="R106" s="11"/>
       <c r="S106" s="10"/>
     </row>
-    <row r="107" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B107" s="10">
         <f>IF(C107="","",COUNTA($C$2:C107))</f>
         <v>106</v>
@@ -6402,7 +6636,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6411,66 +6645,99 @@
       <c r="K107" s="11"/>
       <c r="L107" s="11"/>
       <c r="M107" s="10"/>
-      <c r="N107" s="10"/>
+      <c r="N107" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q107" s="11"/>
       <c r="R107" s="11"/>
       <c r="S107" s="10"/>
     </row>
-    <row r="108" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="10" t="str">
+    <row r="108" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B108" s="10">
         <f>IF(C108="","",COUNTA($C$2:C108))</f>
-        <v/>
-      </c>
-      <c r="C108" s="11"/>
-      <c r="D108" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H108" s="4"/>
-      <c r="I108" s="6" t="str">
+        <v>107</v>
+      </c>
+      <c r="C108" s="11">
+        <v>46066</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E108" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F108" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H108" s="33">
+        <v>11000000</v>
+      </c>
+      <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K108" s="11"/>
       <c r="L108" s="11"/>
       <c r="M108" s="10"/>
-      <c r="N108" s="10"/>
+      <c r="N108" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q108" s="11"/>
       <c r="R108" s="11"/>
       <c r="S108" s="10"/>
     </row>
-    <row r="109" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="10" t="str">
+    <row r="109" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B109" s="10">
         <f>IF(C109="","",COUNTA($C$2:C109))</f>
-        <v/>
-      </c>
-      <c r="C109" s="11"/>
-      <c r="D109" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H109" s="4"/>
-      <c r="I109" s="6" t="str">
+        <v>108</v>
+      </c>
+      <c r="C109" s="11">
+        <v>46067</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E109" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F109" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H109" s="34">
+        <v>35304000</v>
+      </c>
+      <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K109" s="11"/>
       <c r="L109" s="11"/>
       <c r="M109" s="10"/>
-      <c r="N109" s="10"/>
+      <c r="N109" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P109" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="Q109" s="11"/>
       <c r="R109" s="11"/>
       <c r="S109" s="10"/>
     </row>
-    <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B110" s="10" t="str">
         <f>IF(C110="","",COUNTA($C$2:C110))</f>
         <v/>
@@ -6497,7 +6764,7 @@
       <c r="R110" s="11"/>
       <c r="S110" s="10"/>
     </row>
-    <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B111" s="10" t="str">
         <f>IF(C111="","",COUNTA($C$2:C111))</f>
         <v/>
@@ -6524,7 +6791,7 @@
       <c r="R111" s="11"/>
       <c r="S111" s="10"/>
     </row>
-    <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B112" s="10" t="str">
         <f>IF(C112="","",COUNTA($C$2:C112))</f>
         <v/>
@@ -6551,7 +6818,7 @@
       <c r="R112" s="11"/>
       <c r="S112" s="10"/>
     </row>
-    <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B113" s="10" t="str">
         <f>IF(C113="","",COUNTA($C$2:C113))</f>
         <v/>
@@ -6578,7 +6845,7 @@
       <c r="R113" s="11"/>
       <c r="S113" s="10"/>
     </row>
-    <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B114" s="10" t="str">
         <f>IF(C114="","",COUNTA($C$2:C114))</f>
         <v/>
@@ -6613,7 +6880,7 @@
       <c r="R114" s="11"/>
       <c r="S114" s="10"/>
     </row>
-    <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B115" s="10" t="str">
         <f>IF(C115="","",COUNTA($C$2:C115))</f>
         <v/>
@@ -6640,7 +6907,7 @@
       <c r="R115" s="11"/>
       <c r="S115" s="10"/>
     </row>
-    <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B116" s="10" t="str">
         <f>IF(C116="","",COUNTA($C$2:C116))</f>
         <v/>
@@ -6667,7 +6934,7 @@
       <c r="R116" s="11"/>
       <c r="S116" s="10"/>
     </row>
-    <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B117" s="10" t="str">
         <f>IF(C117="","",COUNTA($C$2:C117))</f>
         <v/>
@@ -6694,7 +6961,7 @@
       <c r="R117" s="11"/>
       <c r="S117" s="10"/>
     </row>
-    <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B118" s="10" t="str">
         <f>IF(C118="","",COUNTA($C$2:C118))</f>
         <v/>
@@ -6721,7 +6988,7 @@
       <c r="R118" s="11"/>
       <c r="S118" s="10"/>
     </row>
-    <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B119" s="10" t="str">
         <f>IF(C119="","",COUNTA($C$2:C119))</f>
         <v/>
@@ -6748,7 +7015,7 @@
       <c r="R119" s="11"/>
       <c r="S119" s="10"/>
     </row>
-    <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B120" s="10" t="str">
         <f>IF(C120="","",COUNTA($C$2:C120))</f>
         <v/>
@@ -6775,7 +7042,7 @@
       <c r="R120" s="11"/>
       <c r="S120" s="10"/>
     </row>
-    <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B121" s="10" t="str">
         <f>IF(C121="","",COUNTA($C$2:C121))</f>
         <v/>
@@ -6802,7 +7069,7 @@
       <c r="R121" s="11"/>
       <c r="S121" s="10"/>
     </row>
-    <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B122" s="10" t="str">
         <f>IF(C122="","",COUNTA($C$2:C122))</f>
         <v/>
@@ -6829,7 +7096,7 @@
       <c r="R122" s="11"/>
       <c r="S122" s="10"/>
     </row>
-    <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B123" s="10" t="str">
         <f>IF(C123="","",COUNTA($C$2:C123))</f>
         <v/>
@@ -6856,7 +7123,7 @@
       <c r="R123" s="11"/>
       <c r="S123" s="10"/>
     </row>
-    <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B124" s="10" t="str">
         <f>IF(C124="","",COUNTA($C$2:C124))</f>
         <v/>
@@ -6883,7 +7150,7 @@
       <c r="R124" s="11"/>
       <c r="S124" s="10"/>
     </row>
-    <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B125" s="10" t="str">
         <f>IF(C125="","",COUNTA($C$2:C125))</f>
         <v/>
@@ -6910,7 +7177,7 @@
       <c r="R125" s="11"/>
       <c r="S125" s="10"/>
     </row>
-    <row r="126" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B126" s="10" t="str">
         <f>IF(C126="","",COUNTA($C$2:C126))</f>
         <v/>
@@ -6937,7 +7204,7 @@
       <c r="R126" s="11"/>
       <c r="S126" s="10"/>
     </row>
-    <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B127" s="10" t="str">
         <f>IF(C127="","",COUNTA($C$2:C127))</f>
         <v/>
@@ -6964,7 +7231,7 @@
       <c r="R127" s="11"/>
       <c r="S127" s="10"/>
     </row>
-    <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B128" s="10" t="str">
         <f>IF(C128="","",COUNTA($C$2:C128))</f>
         <v/>
@@ -6991,7 +7258,7 @@
       <c r="R128" s="11"/>
       <c r="S128" s="10"/>
     </row>
-    <row r="129" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B129" s="10" t="str">
         <f>IF(C129="","",COUNTA($C$2:C129))</f>
         <v/>
@@ -7018,7 +7285,7 @@
       <c r="R129" s="11"/>
       <c r="S129" s="10"/>
     </row>
-    <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B130" s="10" t="str">
         <f>IF(C130="","",COUNTA($C$2:C130))</f>
         <v/>
@@ -7045,7 +7312,7 @@
       <c r="R130" s="11"/>
       <c r="S130" s="10"/>
     </row>
-    <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B131" s="10" t="str">
         <f>IF(C131="","",COUNTA($C$2:C131))</f>
         <v/>
@@ -7069,7 +7336,7 @@
       <c r="R131" s="11"/>
       <c r="S131" s="10"/>
     </row>
-    <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B132" s="10" t="str">
         <f>IF(C132="","",COUNTA($C$2:C132))</f>
         <v/>
@@ -7093,7 +7360,7 @@
       <c r="R132" s="11"/>
       <c r="S132" s="10"/>
     </row>
-    <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B133" s="10" t="str">
         <f>IF(C133="","",COUNTA($C$2:C133))</f>
         <v/>
@@ -7117,7 +7384,7 @@
       <c r="R133" s="11"/>
       <c r="S133" s="10"/>
     </row>
-    <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B134" s="10" t="str">
         <f>IF(C134="","",COUNTA($C$2:C134))</f>
         <v/>
@@ -7141,7 +7408,7 @@
       <c r="R134" s="11"/>
       <c r="S134" s="10"/>
     </row>
-    <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B135" s="10" t="str">
         <f>IF(C135="","",COUNTA($C$2:C135))</f>
         <v/>
@@ -7165,7 +7432,7 @@
       <c r="R135" s="11"/>
       <c r="S135" s="10"/>
     </row>
-    <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B136" s="10" t="str">
         <f>IF(C136="","",COUNTA($C$2:C136))</f>
         <v/>
@@ -7189,7 +7456,7 @@
       <c r="R136" s="11"/>
       <c r="S136" s="10"/>
     </row>
-    <row r="137" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B137" s="10" t="str">
         <f>IF(C137="","",COUNTA($C$2:C137))</f>
         <v/>
@@ -7213,7 +7480,7 @@
       <c r="R137" s="11"/>
       <c r="S137" s="10"/>
     </row>
-    <row r="138" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B138" s="10" t="str">
         <f>IF(C138="","",COUNTA($C$2:C138))</f>
         <v/>
@@ -7237,7 +7504,7 @@
       <c r="R138" s="11"/>
       <c r="S138" s="10"/>
     </row>
-    <row r="139" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B139" s="10" t="str">
         <f>IF(C139="","",COUNTA($C$2:C139))</f>
         <v/>
@@ -7261,7 +7528,7 @@
       <c r="R139" s="11"/>
       <c r="S139" s="10"/>
     </row>
-    <row r="140" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B140" s="10" t="str">
         <f>IF(C140="","",COUNTA($C$2:C140))</f>
         <v/>
@@ -7285,7 +7552,7 @@
       <c r="R140" s="11"/>
       <c r="S140" s="10"/>
     </row>
-    <row r="141" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B141" s="10" t="str">
         <f>IF(C141="","",COUNTA($C$2:C141))</f>
         <v/>
@@ -7309,7 +7576,7 @@
       <c r="R141" s="11"/>
       <c r="S141" s="10"/>
     </row>
-    <row r="142" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B142" s="10" t="str">
         <f>IF(C142="","",COUNTA($C$2:C142))</f>
         <v/>
@@ -7333,7 +7600,7 @@
       <c r="R142" s="11"/>
       <c r="S142" s="10"/>
     </row>
-    <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B143" s="10" t="str">
         <f>IF(C143="","",COUNTA($C$2:C143))</f>
         <v/>
@@ -7357,7 +7624,7 @@
       <c r="R143" s="11"/>
       <c r="S143" s="10"/>
     </row>
-    <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B144" s="10" t="str">
         <f>IF(C144="","",COUNTA($C$2:C144))</f>
         <v/>
@@ -7381,7 +7648,7 @@
       <c r="R144" s="11"/>
       <c r="S144" s="10"/>
     </row>
-    <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B145" s="10" t="str">
         <f>IF(C145="","",COUNTA($C$2:C145))</f>
         <v/>
@@ -7405,7 +7672,7 @@
       <c r="R145" s="11"/>
       <c r="S145" s="10"/>
     </row>
-    <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B146" s="10" t="str">
         <f>IF(C146="","",COUNTA($C$2:C146))</f>
         <v/>
@@ -7429,7 +7696,7 @@
       <c r="R146" s="11"/>
       <c r="S146" s="10"/>
     </row>
-    <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B147" s="10" t="str">
         <f>IF(C147="","",COUNTA($C$2:C147))</f>
         <v/>
@@ -7453,7 +7720,7 @@
       <c r="R147" s="11"/>
       <c r="S147" s="10"/>
     </row>
-    <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B148" s="10" t="str">
         <f>IF(C148="","",COUNTA($C$2:C148))</f>
         <v/>
@@ -7477,7 +7744,7 @@
       <c r="R148" s="11"/>
       <c r="S148" s="10"/>
     </row>
-    <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B149" s="10" t="str">
         <f>IF(C149="","",COUNTA($C$2:C149))</f>
         <v/>
@@ -7501,7 +7768,7 @@
       <c r="R149" s="11"/>
       <c r="S149" s="10"/>
     </row>
-    <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B150" s="10" t="str">
         <f>IF(C150="","",COUNTA($C$2:C150))</f>
         <v/>
@@ -7525,7 +7792,7 @@
       <c r="R150" s="11"/>
       <c r="S150" s="10"/>
     </row>
-    <row r="151" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B151" s="10" t="str">
         <f>IF(C151="","",COUNTA($C$2:C151))</f>
         <v/>
@@ -7549,7 +7816,7 @@
       <c r="R151" s="11"/>
       <c r="S151" s="10"/>
     </row>
-    <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B152" s="10" t="str">
         <f>IF(C152="","",COUNTA($C$2:C152))</f>
         <v/>
@@ -7573,7 +7840,7 @@
       <c r="R152" s="11"/>
       <c r="S152" s="10"/>
     </row>
-    <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B153" s="10" t="str">
         <f>IF(C153="","",COUNTA($C$2:C153))</f>
         <v/>
@@ -7597,7 +7864,7 @@
       <c r="R153" s="11"/>
       <c r="S153" s="10"/>
     </row>
-    <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B154" s="10" t="str">
         <f>IF(C154="","",COUNTA($C$2:C154))</f>
         <v/>
@@ -7621,7 +7888,7 @@
       <c r="R154" s="11"/>
       <c r="S154" s="10"/>
     </row>
-    <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B155" s="10" t="str">
         <f>IF(C155="","",COUNTA($C$2:C155))</f>
         <v/>
@@ -7645,7 +7912,7 @@
       <c r="R155" s="11"/>
       <c r="S155" s="10"/>
     </row>
-    <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B156" s="10" t="str">
         <f>IF(C156="","",COUNTA($C$2:C156))</f>
         <v/>
@@ -7669,7 +7936,7 @@
       <c r="R156" s="11"/>
       <c r="S156" s="10"/>
     </row>
-    <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B157" s="10" t="str">
         <f>IF(C157="","",COUNTA($C$2:C157))</f>
         <v/>
@@ -7693,7 +7960,7 @@
       <c r="R157" s="11"/>
       <c r="S157" s="10"/>
     </row>
-    <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B158" s="10" t="str">
         <f>IF(C158="","",COUNTA($C$2:C158))</f>
         <v/>
@@ -7717,7 +7984,7 @@
       <c r="R158" s="11"/>
       <c r="S158" s="10"/>
     </row>
-    <row r="159" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B159" s="10" t="str">
         <f>IF(C159="","",COUNTA($C$2:C159))</f>
         <v/>
@@ -7741,7 +8008,7 @@
       <c r="R159" s="11"/>
       <c r="S159" s="10"/>
     </row>
-    <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B160" s="10" t="str">
         <f>IF(C160="","",COUNTA($C$2:C160))</f>
         <v/>
@@ -7765,7 +8032,7 @@
       <c r="R160" s="11"/>
       <c r="S160" s="10"/>
     </row>
-    <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B161" s="10" t="str">
         <f>IF(C161="","",COUNTA($C$2:C161))</f>
         <v/>
@@ -7789,7 +8056,7 @@
       <c r="R161" s="11"/>
       <c r="S161" s="10"/>
     </row>
-    <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B162" s="10" t="str">
         <f>IF(C162="","",COUNTA($C$2:C162))</f>
         <v/>
@@ -7813,7 +8080,7 @@
       <c r="R162" s="11"/>
       <c r="S162" s="10"/>
     </row>
-    <row r="163" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B163" s="10" t="str">
         <f>IF(C163="","",COUNTA($C$2:C163))</f>
         <v/>
@@ -7837,7 +8104,7 @@
       <c r="R163" s="11"/>
       <c r="S163" s="10"/>
     </row>
-    <row r="164" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B164" s="10" t="str">
         <f>IF(C164="","",COUNTA($C$2:C164))</f>
         <v/>
@@ -7861,7 +8128,7 @@
       <c r="R164" s="11"/>
       <c r="S164" s="10"/>
     </row>
-    <row r="165" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B165" s="10" t="str">
         <f>IF(C165="","",COUNTA($C$2:C165))</f>
         <v/>
@@ -7885,7 +8152,7 @@
       <c r="R165" s="11"/>
       <c r="S165" s="10"/>
     </row>
-    <row r="166" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B166" s="10" t="str">
         <f>IF(C166="","",COUNTA($C$2:C166))</f>
         <v/>
@@ -7909,7 +8176,7 @@
       <c r="R166" s="11"/>
       <c r="S166" s="10"/>
     </row>
-    <row r="167" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B167" s="10" t="str">
         <f>IF(C167="","",COUNTA($C$2:C167))</f>
         <v/>
@@ -7933,7 +8200,7 @@
       <c r="R167" s="11"/>
       <c r="S167" s="10"/>
     </row>
-    <row r="168" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B168" s="10" t="str">
         <f>IF(C168="","",COUNTA($C$2:C168))</f>
         <v/>
@@ -7957,7 +8224,7 @@
       <c r="R168" s="11"/>
       <c r="S168" s="10"/>
     </row>
-    <row r="169" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B169" s="10" t="str">
         <f>IF(C169="","",COUNTA($C$2:C169))</f>
         <v/>
@@ -7981,7 +8248,7 @@
       <c r="R169" s="11"/>
       <c r="S169" s="10"/>
     </row>
-    <row r="170" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B170" s="10" t="str">
         <f>IF(C170="","",COUNTA($C$2:C170))</f>
         <v/>
@@ -8005,7 +8272,7 @@
       <c r="R170" s="11"/>
       <c r="S170" s="10"/>
     </row>
-    <row r="171" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B171" s="10" t="str">
         <f>IF(C171="","",COUNTA($C$2:C171))</f>
         <v/>
@@ -8029,7 +8296,7 @@
       <c r="R171" s="11"/>
       <c r="S171" s="10"/>
     </row>
-    <row r="172" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B172" s="10" t="str">
         <f>IF(C172="","",COUNTA($C$2:C172))</f>
         <v/>
@@ -8053,7 +8320,7 @@
       <c r="R172" s="11"/>
       <c r="S172" s="10"/>
     </row>
-    <row r="173" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B173" s="10" t="str">
         <f>IF(C173="","",COUNTA($C$2:C173))</f>
         <v/>
@@ -8077,7 +8344,7 @@
       <c r="R173" s="11"/>
       <c r="S173" s="10"/>
     </row>
-    <row r="174" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B174" s="10" t="str">
         <f>IF(C174="","",COUNTA($C$2:C174))</f>
         <v/>
@@ -8101,7 +8368,7 @@
       <c r="R174" s="11"/>
       <c r="S174" s="10"/>
     </row>
-    <row r="175" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B175" s="10" t="str">
         <f>IF(C175="","",COUNTA($C$2:C175))</f>
         <v/>
@@ -8125,7 +8392,7 @@
       <c r="R175" s="11"/>
       <c r="S175" s="10"/>
     </row>
-    <row r="176" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B176" s="10" t="str">
         <f>IF(C176="","",COUNTA($C$2:C176))</f>
         <v/>
@@ -8149,7 +8416,7 @@
       <c r="R176" s="11"/>
       <c r="S176" s="10"/>
     </row>
-    <row r="177" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B177" s="10" t="str">
         <f>IF(C177="","",COUNTA($C$2:C177))</f>
         <v/>
@@ -8173,7 +8440,7 @@
       <c r="R177" s="11"/>
       <c r="S177" s="10"/>
     </row>
-    <row r="178" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B178" s="10" t="str">
         <f>IF(C178="","",COUNTA($C$2:C178))</f>
         <v/>
@@ -8197,7 +8464,7 @@
       <c r="R178" s="11"/>
       <c r="S178" s="10"/>
     </row>
-    <row r="179" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B179" s="10" t="str">
         <f>IF(C179="","",COUNTA($C$2:C179))</f>
         <v/>
@@ -8221,7 +8488,7 @@
       <c r="R179" s="11"/>
       <c r="S179" s="10"/>
     </row>
-    <row r="180" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B180" s="10" t="str">
         <f>IF(C180="","",COUNTA($C$2:C180))</f>
         <v/>
@@ -8245,7 +8512,7 @@
       <c r="R180" s="11"/>
       <c r="S180" s="10"/>
     </row>
-    <row r="181" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B181" s="10" t="str">
         <f>IF(C181="","",COUNTA($C$2:C181))</f>
         <v/>
@@ -8269,7 +8536,7 @@
       <c r="R181" s="11"/>
       <c r="S181" s="10"/>
     </row>
-    <row r="182" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B182" s="10" t="str">
         <f>IF(C182="","",COUNTA($C$2:C182))</f>
         <v/>
@@ -8293,7 +8560,7 @@
       <c r="R182" s="11"/>
       <c r="S182" s="10"/>
     </row>
-    <row r="183" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B183" s="10" t="str">
         <f>IF(C183="","",COUNTA($C$2:C183))</f>
         <v/>
@@ -8317,7 +8584,7 @@
       <c r="R183" s="11"/>
       <c r="S183" s="10"/>
     </row>
-    <row r="184" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B184" s="10" t="str">
         <f>IF(C184="","",COUNTA($C$2:C184))</f>
         <v/>
@@ -8341,7 +8608,7 @@
       <c r="R184" s="11"/>
       <c r="S184" s="10"/>
     </row>
-    <row r="185" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B185" s="10" t="str">
         <f>IF(C185="","",COUNTA($C$2:C185))</f>
         <v/>
@@ -8365,7 +8632,7 @@
       <c r="R185" s="11"/>
       <c r="S185" s="10"/>
     </row>
-    <row r="186" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B186" s="10" t="str">
         <f>IF(C186="","",COUNTA($C$2:C186))</f>
         <v/>
@@ -8389,7 +8656,7 @@
       <c r="R186" s="11"/>
       <c r="S186" s="10"/>
     </row>
-    <row r="187" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B187" s="10" t="str">
         <f>IF(C187="","",COUNTA($C$2:C187))</f>
         <v/>
@@ -8413,7 +8680,7 @@
       <c r="R187" s="11"/>
       <c r="S187" s="10"/>
     </row>
-    <row r="188" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B188" s="10" t="str">
         <f>IF(C188="","",COUNTA($C$2:C188))</f>
         <v/>
@@ -8437,7 +8704,7 @@
       <c r="R188" s="11"/>
       <c r="S188" s="10"/>
     </row>
-    <row r="189" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B189" s="10" t="str">
         <f>IF(C189="","",COUNTA($C$2:C189))</f>
         <v/>
@@ -8461,7 +8728,7 @@
       <c r="R189" s="11"/>
       <c r="S189" s="10"/>
     </row>
-    <row r="190" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B190" s="10" t="str">
         <f>IF(C190="","",COUNTA($C$2:C190))</f>
         <v/>
@@ -8485,7 +8752,7 @@
       <c r="R190" s="11"/>
       <c r="S190" s="10"/>
     </row>
-    <row r="191" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B191" s="10" t="str">
         <f>IF(C191="","",COUNTA($C$2:C191))</f>
         <v/>
@@ -8509,7 +8776,7 @@
       <c r="R191" s="11"/>
       <c r="S191" s="10"/>
     </row>
-    <row r="192" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B192" s="10" t="str">
         <f>IF(C192="","",COUNTA($C$2:C192))</f>
         <v/>
@@ -8533,7 +8800,7 @@
       <c r="R192" s="11"/>
       <c r="S192" s="10"/>
     </row>
-    <row r="193" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B193" s="10" t="str">
         <f>IF(C193="","",COUNTA($C$2:C193))</f>
         <v/>
@@ -8557,7 +8824,7 @@
       <c r="R193" s="11"/>
       <c r="S193" s="10"/>
     </row>
-    <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B194" s="10" t="str">
         <f>IF(C194="","",COUNTA($C$2:C194))</f>
         <v/>
@@ -8581,7 +8848,7 @@
       <c r="R194" s="11"/>
       <c r="S194" s="10"/>
     </row>
-    <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B195" s="10" t="str">
         <f>IF(C195="","",COUNTA($C$2:C195))</f>
         <v/>
@@ -8605,7 +8872,7 @@
       <c r="R195" s="11"/>
       <c r="S195" s="10"/>
     </row>
-    <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B196" s="10" t="str">
         <f>IF(C196="","",COUNTA($C$2:C196))</f>
         <v/>
@@ -8629,7 +8896,7 @@
       <c r="R196" s="11"/>
       <c r="S196" s="10"/>
     </row>
-    <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B197" s="10" t="str">
         <f>IF(C197="","",COUNTA($C$2:C197))</f>
         <v/>
@@ -8653,7 +8920,7 @@
       <c r="R197" s="11"/>
       <c r="S197" s="10"/>
     </row>
-    <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B198" s="10" t="str">
         <f>IF(C198="","",COUNTA($C$2:C198))</f>
         <v/>
@@ -8677,7 +8944,7 @@
       <c r="R198" s="11"/>
       <c r="S198" s="10"/>
     </row>
-    <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B199" s="10" t="str">
         <f>IF(C199="","",COUNTA($C$2:C199))</f>
         <v/>
@@ -8701,7 +8968,7 @@
       <c r="R199" s="11"/>
       <c r="S199" s="10"/>
     </row>
-    <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B200" s="10" t="str">
         <f>IF(C200="","",COUNTA($C$2:C200))</f>
         <v/>
@@ -8725,7 +8992,7 @@
       <c r="R200" s="11"/>
       <c r="S200" s="10"/>
     </row>
-    <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B201" s="10" t="str">
         <f>IF(C201="","",COUNTA($C$2:C201))</f>
         <v/>
@@ -8749,7 +9016,7 @@
       <c r="R201" s="11"/>
       <c r="S201" s="10"/>
     </row>
-    <row r="202" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B202" s="10" t="str">
         <f>IF(C202="","",COUNTA($C$2:C202))</f>
         <v/>
@@ -8773,7 +9040,7 @@
       <c r="R202" s="11"/>
       <c r="S202" s="10"/>
     </row>
-    <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B203" s="10" t="str">
         <f>IF(C203="","",COUNTA($C$2:C203))</f>
         <v/>
@@ -8797,7 +9064,7 @@
       <c r="R203" s="11"/>
       <c r="S203" s="10"/>
     </row>
-    <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B204" s="10" t="str">
         <f>IF(C204="","",COUNTA($C$2:C204))</f>
         <v/>
@@ -8821,7 +9088,7 @@
       <c r="R204" s="11"/>
       <c r="S204" s="10"/>
     </row>
-    <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B205" s="10" t="str">
         <f>IF(C205="","",COUNTA($C$2:C205))</f>
         <v/>
@@ -8845,7 +9112,7 @@
       <c r="R205" s="11"/>
       <c r="S205" s="10"/>
     </row>
-    <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B206" s="10" t="str">
         <f>IF(C206="","",COUNTA($C$2:C206))</f>
         <v/>
@@ -8869,7 +9136,7 @@
       <c r="R206" s="11"/>
       <c r="S206" s="10"/>
     </row>
-    <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B207" s="10" t="str">
         <f>IF(C207="","",COUNTA($C$2:C207))</f>
         <v/>
@@ -8893,7 +9160,7 @@
       <c r="R207" s="11"/>
       <c r="S207" s="10"/>
     </row>
-    <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B208" s="10" t="str">
         <f>IF(C208="","",COUNTA($C$2:C208))</f>
         <v/>
@@ -8917,7 +9184,7 @@
       <c r="R208" s="11"/>
       <c r="S208" s="10"/>
     </row>
-    <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B209" s="10" t="str">
         <f>IF(C209="","",COUNTA($C$2:C209))</f>
         <v/>
@@ -8941,7 +9208,7 @@
       <c r="R209" s="11"/>
       <c r="S209" s="10"/>
     </row>
-    <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B210" s="10" t="str">
         <f>IF(C210="","",COUNTA($C$2:C210))</f>
         <v/>
@@ -8965,7 +9232,7 @@
       <c r="R210" s="11"/>
       <c r="S210" s="10"/>
     </row>
-    <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B211" s="10" t="str">
         <f>IF(C211="","",COUNTA($C$2:C211))</f>
         <v/>
@@ -8989,7 +9256,7 @@
       <c r="R211" s="11"/>
       <c r="S211" s="10"/>
     </row>
-    <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B212" s="10"/>
       <c r="C212" s="11"/>
       <c r="D212" s="10" t="str">
@@ -9010,7 +9277,7 @@
       <c r="R212" s="11"/>
       <c r="S212" s="10"/>
     </row>
-    <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B213" s="10"/>
       <c r="C213" s="11"/>
       <c r="D213" s="10" t="str">
@@ -9031,7 +9298,7 @@
       <c r="R213" s="11"/>
       <c r="S213" s="10"/>
     </row>
-    <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B214" s="10"/>
       <c r="C214" s="11"/>
       <c r="D214" s="10" t="str">
@@ -9052,7 +9319,7 @@
       <c r="R214" s="11"/>
       <c r="S214" s="10"/>
     </row>
-    <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B215" s="10"/>
       <c r="C215" s="11"/>
       <c r="D215" s="10" t="str">
@@ -9073,7 +9340,7 @@
       <c r="R215" s="11"/>
       <c r="S215" s="10"/>
     </row>
-    <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B216" s="10"/>
       <c r="C216" s="11"/>
       <c r="D216" s="10" t="str">
@@ -9094,7 +9361,7 @@
       <c r="R216" s="11"/>
       <c r="S216" s="10"/>
     </row>
-    <row r="217" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B217" s="10"/>
       <c r="C217" s="11"/>
       <c r="D217" s="10" t="str">
@@ -9115,7 +9382,7 @@
       <c r="R217" s="11"/>
       <c r="S217" s="10"/>
     </row>
-    <row r="218" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B218" s="10"/>
       <c r="C218" s="11"/>
       <c r="D218" s="10" t="str">
@@ -9136,7 +9403,7 @@
       <c r="R218" s="11"/>
       <c r="S218" s="10"/>
     </row>
-    <row r="219" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B219" s="10"/>
       <c r="C219" s="11"/>
       <c r="D219" s="10" t="str">
@@ -9157,7 +9424,7 @@
       <c r="R219" s="11"/>
       <c r="S219" s="10"/>
     </row>
-    <row r="220" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B220" s="10"/>
       <c r="C220" s="11"/>
       <c r="D220" s="10" t="str">
@@ -9178,7 +9445,7 @@
       <c r="R220" s="11"/>
       <c r="S220" s="10"/>
     </row>
-    <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B221" s="10"/>
       <c r="C221" s="11"/>
       <c r="D221" s="10" t="str">
@@ -9199,7 +9466,7 @@
       <c r="R221" s="11"/>
       <c r="S221" s="10"/>
     </row>
-    <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B222" s="10"/>
       <c r="C222" s="11"/>
       <c r="D222" s="10" t="str">
@@ -9220,7 +9487,7 @@
       <c r="R222" s="11"/>
       <c r="S222" s="10"/>
     </row>
-    <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B223" s="10"/>
       <c r="C223" s="11"/>
       <c r="D223" s="10" t="str">
@@ -9241,7 +9508,7 @@
       <c r="R223" s="11"/>
       <c r="S223" s="10"/>
     </row>
-    <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B224" s="10"/>
       <c r="C224" s="11"/>
       <c r="D224" s="10" t="str">
@@ -9262,7 +9529,7 @@
       <c r="R224" s="11"/>
       <c r="S224" s="10"/>
     </row>
-    <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B225" s="10"/>
       <c r="C225" s="11"/>
       <c r="D225" s="10" t="str">
@@ -9283,7 +9550,7 @@
       <c r="R225" s="11"/>
       <c r="S225" s="10"/>
     </row>
-    <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B226" s="10"/>
       <c r="C226" s="11"/>
       <c r="D226" s="10" t="str">
@@ -9304,7 +9571,7 @@
       <c r="R226" s="11"/>
       <c r="S226" s="10"/>
     </row>
-    <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B227" s="10"/>
       <c r="C227" s="11"/>
       <c r="D227" s="10" t="str">
@@ -9325,7 +9592,7 @@
       <c r="R227" s="11"/>
       <c r="S227" s="10"/>
     </row>
-    <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B228" s="10"/>
       <c r="C228" s="11"/>
       <c r="D228" s="10" t="str">
@@ -9346,7 +9613,7 @@
       <c r="R228" s="11"/>
       <c r="S228" s="10"/>
     </row>
-    <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B229" s="10"/>
       <c r="C229" s="11"/>
       <c r="D229" s="10" t="str">
@@ -9367,7 +9634,7 @@
       <c r="R229" s="11"/>
       <c r="S229" s="10"/>
     </row>
-    <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B230" s="10"/>
       <c r="C230" s="11"/>
       <c r="D230" s="10" t="str">
@@ -9388,7 +9655,7 @@
       <c r="R230" s="11"/>
       <c r="S230" s="10"/>
     </row>
-    <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B231" s="10"/>
       <c r="C231" s="11"/>
       <c r="D231" s="10" t="str">
@@ -9409,7 +9676,7 @@
       <c r="R231" s="11"/>
       <c r="S231" s="10"/>
     </row>
-    <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B232" s="10"/>
       <c r="C232" s="11"/>
       <c r="D232" s="10" t="str">
@@ -9430,7 +9697,7 @@
       <c r="R232" s="11"/>
       <c r="S232" s="10"/>
     </row>
-    <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B233" s="10"/>
       <c r="C233" s="11"/>
       <c r="D233" s="10" t="str">
@@ -9451,7 +9718,7 @@
       <c r="R233" s="11"/>
       <c r="S233" s="10"/>
     </row>
-    <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B234" s="10"/>
       <c r="C234" s="11"/>
       <c r="D234" s="10" t="str">
@@ -9472,7 +9739,7 @@
       <c r="R234" s="11"/>
       <c r="S234" s="10"/>
     </row>
-    <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B235" s="10"/>
       <c r="C235" s="11"/>
       <c r="D235" s="10" t="str">
@@ -9493,7 +9760,7 @@
       <c r="R235" s="11"/>
       <c r="S235" s="10"/>
     </row>
-    <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B236" s="10"/>
       <c r="C236" s="11"/>
       <c r="D236" s="10" t="str">
@@ -9514,7 +9781,7 @@
       <c r="R236" s="11"/>
       <c r="S236" s="10"/>
     </row>
-    <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B237" s="10"/>
       <c r="C237" s="11"/>
       <c r="D237" s="10" t="str">
@@ -9535,7 +9802,7 @@
       <c r="R237" s="11"/>
       <c r="S237" s="10"/>
     </row>
-    <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B238" s="10"/>
       <c r="C238" s="11"/>
       <c r="D238" s="10" t="str">
@@ -9556,7 +9823,7 @@
       <c r="R238" s="11"/>
       <c r="S238" s="10"/>
     </row>
-    <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B239" s="10"/>
       <c r="C239" s="11"/>
       <c r="D239" s="10" t="str">
@@ -9577,7 +9844,7 @@
       <c r="R239" s="11"/>
       <c r="S239" s="10"/>
     </row>
-    <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B240" s="10"/>
       <c r="C240" s="11"/>
       <c r="D240" s="10" t="str">
@@ -9598,7 +9865,7 @@
       <c r="R240" s="11"/>
       <c r="S240" s="10"/>
     </row>
-    <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B241" s="10"/>
       <c r="C241" s="11"/>
       <c r="D241" s="10" t="str">
@@ -9619,7 +9886,7 @@
       <c r="R241" s="11"/>
       <c r="S241" s="10"/>
     </row>
-    <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B242" s="10"/>
       <c r="C242" s="11"/>
       <c r="D242" s="10" t="str">
@@ -9640,7 +9907,7 @@
       <c r="R242" s="11"/>
       <c r="S242" s="10"/>
     </row>
-    <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B243" s="10"/>
       <c r="C243" s="11"/>
       <c r="D243" s="10" t="str">
@@ -9661,7 +9928,7 @@
       <c r="R243" s="11"/>
       <c r="S243" s="10"/>
     </row>
-    <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B244" s="10"/>
       <c r="C244" s="11"/>
       <c r="D244" s="10" t="str">
@@ -9682,7 +9949,7 @@
       <c r="R244" s="11"/>
       <c r="S244" s="10"/>
     </row>
-    <row r="245" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B245" s="10"/>
       <c r="C245" s="11"/>
       <c r="D245" s="10" t="str">
@@ -9703,7 +9970,7 @@
       <c r="R245" s="11"/>
       <c r="S245" s="10"/>
     </row>
-    <row r="246" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B246" s="10"/>
       <c r="C246" s="11"/>
       <c r="D246" s="10" t="str">
@@ -9724,7 +9991,7 @@
       <c r="R246" s="11"/>
       <c r="S246" s="10"/>
     </row>
-    <row r="247" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B247" s="10"/>
       <c r="C247" s="11"/>
       <c r="D247" s="10" t="str">
@@ -9745,7 +10012,7 @@
       <c r="R247" s="11"/>
       <c r="S247" s="10"/>
     </row>
-    <row r="248" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B248" s="10"/>
       <c r="C248" s="11"/>
       <c r="D248" s="10" t="str">
@@ -9766,7 +10033,7 @@
       <c r="R248" s="11"/>
       <c r="S248" s="10"/>
     </row>
-    <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B249" s="10"/>
       <c r="C249" s="11"/>
       <c r="D249" s="10" t="str">
@@ -9787,7 +10054,7 @@
       <c r="R249" s="11"/>
       <c r="S249" s="10"/>
     </row>
-    <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B250" s="10"/>
       <c r="C250" s="11"/>
       <c r="D250" s="10" t="str">
@@ -9808,7 +10075,7 @@
       <c r="R250" s="11"/>
       <c r="S250" s="10"/>
     </row>
-    <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B251" s="10"/>
       <c r="C251" s="11"/>
       <c r="D251" s="10" t="str">
@@ -9829,7 +10096,7 @@
       <c r="R251" s="11"/>
       <c r="S251" s="10"/>
     </row>
-    <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B252" s="10"/>
       <c r="C252" s="11"/>
       <c r="D252" s="10" t="str">
@@ -9850,7 +10117,7 @@
       <c r="R252" s="11"/>
       <c r="S252" s="10"/>
     </row>
-    <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B253" s="10"/>
       <c r="C253" s="11"/>
       <c r="D253" s="10" t="str">
@@ -9871,7 +10138,7 @@
       <c r="R253" s="11"/>
       <c r="S253" s="10"/>
     </row>
-    <row r="254" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B254" s="10"/>
       <c r="C254" s="11"/>
       <c r="D254" s="10" t="str">
@@ -9892,7 +10159,7 @@
       <c r="R254" s="11"/>
       <c r="S254" s="10"/>
     </row>
-    <row r="255" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B255" s="10"/>
       <c r="C255" s="11"/>
       <c r="D255" s="10" t="str">
@@ -9913,7 +10180,7 @@
       <c r="R255" s="11"/>
       <c r="S255" s="10"/>
     </row>
-    <row r="256" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B256" s="10"/>
       <c r="C256" s="11"/>
       <c r="D256" s="10" t="str">
@@ -9934,7 +10201,7 @@
       <c r="R256" s="11"/>
       <c r="S256" s="10"/>
     </row>
-    <row r="257" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B257" s="10"/>
       <c r="C257" s="11"/>
       <c r="D257" s="10" t="str">
@@ -9955,7 +10222,7 @@
       <c r="R257" s="11"/>
       <c r="S257" s="10"/>
     </row>
-    <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B258" s="10"/>
       <c r="C258" s="11"/>
       <c r="D258" s="10" t="str">
@@ -9976,7 +10243,7 @@
       <c r="R258" s="11"/>
       <c r="S258" s="10"/>
     </row>
-    <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B259" s="10"/>
       <c r="C259" s="11"/>
       <c r="D259" s="10" t="str">
@@ -9997,7 +10264,7 @@
       <c r="R259" s="11"/>
       <c r="S259" s="10"/>
     </row>
-    <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B260" s="10"/>
       <c r="C260" s="11"/>
       <c r="D260" s="10" t="str">
@@ -10018,7 +10285,7 @@
       <c r="R260" s="11"/>
       <c r="S260" s="10"/>
     </row>
-    <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B261" s="10"/>
       <c r="C261" s="11"/>
       <c r="D261" s="10" t="str">
@@ -10039,7 +10306,7 @@
       <c r="R261" s="11"/>
       <c r="S261" s="10"/>
     </row>
-    <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B262" s="10"/>
       <c r="C262" s="11"/>
       <c r="D262" s="10" t="str">
@@ -10060,7 +10327,7 @@
       <c r="R262" s="11"/>
       <c r="S262" s="10"/>
     </row>
-    <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B263" s="10"/>
       <c r="C263" s="11"/>
       <c r="D263" s="10" t="str">
@@ -10081,7 +10348,7 @@
       <c r="R263" s="11"/>
       <c r="S263" s="10"/>
     </row>
-    <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B264" s="10"/>
       <c r="C264" s="11"/>
       <c r="D264" s="10" t="str">
@@ -10102,7 +10369,7 @@
       <c r="R264" s="11"/>
       <c r="S264" s="10"/>
     </row>
-    <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B265" s="10"/>
       <c r="C265" s="11"/>
       <c r="D265" s="10" t="str">
@@ -10123,7 +10390,7 @@
       <c r="R265" s="11"/>
       <c r="S265" s="10"/>
     </row>
-    <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B266" s="10"/>
       <c r="C266" s="11"/>
       <c r="D266" s="10" t="str">
@@ -10144,7 +10411,7 @@
       <c r="R266" s="11"/>
       <c r="S266" s="10"/>
     </row>
-    <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B267" s="10"/>
       <c r="C267" s="11"/>
       <c r="D267" s="10" t="str">
@@ -10165,7 +10432,7 @@
       <c r="R267" s="11"/>
       <c r="S267" s="10"/>
     </row>
-    <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
       <c r="D268" s="10" t="str">
@@ -10186,7 +10453,7 @@
       <c r="R268" s="11"/>
       <c r="S268" s="10"/>
     </row>
-    <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B269" s="10"/>
       <c r="C269" s="11"/>
       <c r="D269" s="10" t="str">
@@ -10207,7 +10474,7 @@
       <c r="R269" s="11"/>
       <c r="S269" s="10"/>
     </row>
-    <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B270" s="10"/>
       <c r="C270" s="11"/>
       <c r="D270" s="10" t="str">
@@ -10228,7 +10495,7 @@
       <c r="R270" s="11"/>
       <c r="S270" s="10"/>
     </row>
-    <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B271" s="10"/>
       <c r="C271" s="11"/>
       <c r="D271" s="10" t="str">
@@ -10249,7 +10516,7 @@
       <c r="R271" s="11"/>
       <c r="S271" s="10"/>
     </row>
-    <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B272" s="10"/>
       <c r="C272" s="11"/>
       <c r="D272" s="10" t="str">
@@ -10270,7 +10537,7 @@
       <c r="R272" s="11"/>
       <c r="S272" s="10"/>
     </row>
-    <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B273" s="10"/>
       <c r="C273" s="11"/>
       <c r="D273" s="10" t="str">
@@ -10291,7 +10558,7 @@
       <c r="R273" s="11"/>
       <c r="S273" s="10"/>
     </row>
-    <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B274" s="10"/>
       <c r="C274" s="11"/>
       <c r="D274" s="10" t="str">
@@ -10312,7 +10579,7 @@
       <c r="R274" s="11"/>
       <c r="S274" s="10"/>
     </row>
-    <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B275" s="10"/>
       <c r="C275" s="11"/>
       <c r="D275" s="10" t="str">
@@ -10333,7 +10600,7 @@
       <c r="R275" s="11"/>
       <c r="S275" s="10"/>
     </row>
-    <row r="276" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B276" s="10"/>
       <c r="C276" s="11"/>
       <c r="D276" s="10" t="str">
@@ -10354,7 +10621,7 @@
       <c r="R276" s="11"/>
       <c r="S276" s="10"/>
     </row>
-    <row r="277" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B277" s="10"/>
       <c r="C277" s="11"/>
       <c r="D277" s="10" t="str">
@@ -10375,7 +10642,7 @@
       <c r="R277" s="11"/>
       <c r="S277" s="10"/>
     </row>
-    <row r="278" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B278" s="10"/>
       <c r="C278" s="11"/>
       <c r="D278" s="10" t="str">
@@ -10396,7 +10663,7 @@
       <c r="R278" s="11"/>
       <c r="S278" s="10"/>
     </row>
-    <row r="279" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B279" s="10"/>
       <c r="C279" s="11"/>
       <c r="D279" s="10" t="str">
@@ -10417,7 +10684,7 @@
       <c r="R279" s="11"/>
       <c r="S279" s="10"/>
     </row>
-    <row r="280" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B280" s="10"/>
       <c r="C280" s="11"/>
       <c r="D280" s="10" t="str">
@@ -10438,7 +10705,7 @@
       <c r="R280" s="11"/>
       <c r="S280" s="10"/>
     </row>
-    <row r="281" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B281" s="10"/>
       <c r="C281" s="11"/>
       <c r="D281" s="10" t="str">
@@ -10459,7 +10726,7 @@
       <c r="R281" s="11"/>
       <c r="S281" s="10"/>
     </row>
-    <row r="282" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B282" s="10"/>
       <c r="C282" s="11"/>
       <c r="D282" s="10" t="str">
@@ -10480,7 +10747,7 @@
       <c r="R282" s="11"/>
       <c r="S282" s="10"/>
     </row>
-    <row r="283" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B283" s="10"/>
       <c r="C283" s="11"/>
       <c r="D283" s="10" t="str">
@@ -10501,7 +10768,7 @@
       <c r="R283" s="11"/>
       <c r="S283" s="10"/>
     </row>
-    <row r="284" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B284" s="10"/>
       <c r="C284" s="11"/>
       <c r="D284" s="10" t="str">
@@ -10522,7 +10789,7 @@
       <c r="R284" s="11"/>
       <c r="S284" s="10"/>
     </row>
-    <row r="285" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B285" s="10"/>
       <c r="C285" s="11"/>
       <c r="D285" s="10" t="str">
@@ -10543,7 +10810,7 @@
       <c r="R285" s="11"/>
       <c r="S285" s="10"/>
     </row>
-    <row r="286" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B286" s="10"/>
       <c r="C286" s="11"/>
       <c r="D286" s="10" t="str">
@@ -10564,7 +10831,7 @@
       <c r="R286" s="11"/>
       <c r="S286" s="10"/>
     </row>
-    <row r="287" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B287" s="10"/>
       <c r="C287" s="11"/>
       <c r="D287" s="10" t="str">
@@ -10585,7 +10852,7 @@
       <c r="R287" s="11"/>
       <c r="S287" s="10"/>
     </row>
-    <row r="288" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B288" s="10"/>
       <c r="C288" s="11"/>
       <c r="D288" s="10" t="str">
@@ -10606,7 +10873,7 @@
       <c r="R288" s="11"/>
       <c r="S288" s="10"/>
     </row>
-    <row r="289" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B289" s="10"/>
       <c r="C289" s="11"/>
       <c r="D289" s="10" t="str">
@@ -10627,7 +10894,7 @@
       <c r="R289" s="11"/>
       <c r="S289" s="10"/>
     </row>
-    <row r="290" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B290" s="10"/>
       <c r="C290" s="11"/>
       <c r="D290" s="10" t="str">
@@ -10648,7 +10915,7 @@
       <c r="R290" s="11"/>
       <c r="S290" s="10"/>
     </row>
-    <row r="291" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B291" s="10"/>
       <c r="C291" s="11"/>
       <c r="D291" s="10" t="str">
@@ -10669,7 +10936,7 @@
       <c r="R291" s="11"/>
       <c r="S291" s="10"/>
     </row>
-    <row r="292" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B292" s="10"/>
       <c r="C292" s="11"/>
       <c r="D292" s="10" t="str">
@@ -10690,7 +10957,7 @@
       <c r="R292" s="11"/>
       <c r="S292" s="10"/>
     </row>
-    <row r="293" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B293" s="10"/>
       <c r="C293" s="11"/>
       <c r="D293" s="10" t="str">
@@ -10711,7 +10978,7 @@
       <c r="R293" s="11"/>
       <c r="S293" s="10"/>
     </row>
-    <row r="294" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B294" s="10"/>
       <c r="C294" s="11"/>
       <c r="D294" s="10" t="str">
@@ -10732,7 +10999,7 @@
       <c r="R294" s="11"/>
       <c r="S294" s="10"/>
     </row>
-    <row r="295" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B295" s="10"/>
       <c r="C295" s="11"/>
       <c r="D295" s="10" t="str">
@@ -10753,7 +11020,7 @@
       <c r="R295" s="11"/>
       <c r="S295" s="10"/>
     </row>
-    <row r="296" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B296" s="10"/>
       <c r="C296" s="11"/>
       <c r="D296" s="10" t="str">
@@ -10774,7 +11041,7 @@
       <c r="R296" s="11"/>
       <c r="S296" s="10"/>
     </row>
-    <row r="297" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B297" s="10"/>
       <c r="C297" s="11"/>
       <c r="D297" s="10" t="str">
@@ -10795,7 +11062,7 @@
       <c r="R297" s="11"/>
       <c r="S297" s="10"/>
     </row>
-    <row r="298" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B298" s="10"/>
       <c r="C298" s="11"/>
       <c r="D298" s="10" t="str">
@@ -10816,7 +11083,7 @@
       <c r="R298" s="11"/>
       <c r="S298" s="10"/>
     </row>
-    <row r="299" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B299" s="10"/>
       <c r="C299" s="11"/>
       <c r="D299" s="10" t="str">
@@ -10837,7 +11104,7 @@
       <c r="R299" s="11"/>
       <c r="S299" s="10"/>
     </row>
-    <row r="300" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B300" s="10"/>
       <c r="C300" s="11"/>
       <c r="D300" s="10" t="str">
@@ -10858,7 +11125,7 @@
       <c r="R300" s="11"/>
       <c r="S300" s="10"/>
     </row>
-    <row r="301" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B301" s="10"/>
       <c r="C301" s="11"/>
       <c r="D301" s="10" t="str">
@@ -10879,7 +11146,7 @@
       <c r="R301" s="11"/>
       <c r="S301" s="10"/>
     </row>
-    <row r="302" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B302" s="10"/>
       <c r="C302" s="11"/>
       <c r="D302" s="10" t="str">
@@ -10900,7 +11167,7 @@
       <c r="R302" s="11"/>
       <c r="S302" s="10"/>
     </row>
-    <row r="303" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B303" s="10"/>
       <c r="C303" s="11"/>
       <c r="D303" s="10" t="str">
@@ -10921,7 +11188,7 @@
       <c r="R303" s="11"/>
       <c r="S303" s="10"/>
     </row>
-    <row r="304" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B304" s="10"/>
       <c r="C304" s="11"/>
       <c r="D304" s="10" t="str">
@@ -10942,7 +11209,7 @@
       <c r="R304" s="11"/>
       <c r="S304" s="10"/>
     </row>
-    <row r="305" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B305" s="10"/>
       <c r="C305" s="11"/>
       <c r="D305" s="10" t="str">
@@ -10963,7 +11230,7 @@
       <c r="R305" s="11"/>
       <c r="S305" s="10"/>
     </row>
-    <row r="306" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B306" s="10"/>
       <c r="C306" s="11"/>
       <c r="D306" s="10" t="str">
@@ -10984,7 +11251,7 @@
       <c r="R306" s="11"/>
       <c r="S306" s="10"/>
     </row>
-    <row r="307" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B307" s="10"/>
       <c r="C307" s="11"/>
       <c r="D307" s="10" t="str">
@@ -11005,7 +11272,7 @@
       <c r="R307" s="11"/>
       <c r="S307" s="10"/>
     </row>
-    <row r="308" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B308" s="10"/>
       <c r="C308" s="11"/>
       <c r="D308" s="10" t="str">
@@ -11026,7 +11293,7 @@
       <c r="R308" s="11"/>
       <c r="S308" s="10"/>
     </row>
-    <row r="309" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B309" s="10"/>
       <c r="C309" s="11"/>
       <c r="D309" s="10" t="str">
@@ -11047,7 +11314,7 @@
       <c r="R309" s="11"/>
       <c r="S309" s="10"/>
     </row>
-    <row r="310" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B310" s="10"/>
       <c r="C310" s="11"/>
       <c r="D310" s="10" t="str">
@@ -11068,7 +11335,7 @@
       <c r="R310" s="11"/>
       <c r="S310" s="10"/>
     </row>
-    <row r="311" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B311" s="10"/>
       <c r="C311" s="11"/>
       <c r="D311" s="10" t="str">
@@ -11089,7 +11356,7 @@
       <c r="R311" s="11"/>
       <c r="S311" s="10"/>
     </row>
-    <row r="312" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B312" s="10"/>
       <c r="C312" s="11"/>
       <c r="D312" s="10" t="str">
@@ -11110,7 +11377,7 @@
       <c r="R312" s="11"/>
       <c r="S312" s="10"/>
     </row>
-    <row r="313" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B313" s="10"/>
       <c r="C313" s="11"/>
       <c r="D313" s="10" t="str">
@@ -11131,7 +11398,7 @@
       <c r="R313" s="11"/>
       <c r="S313" s="10"/>
     </row>
-    <row r="314" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B314" s="10"/>
       <c r="C314" s="11"/>
       <c r="D314" s="10" t="str">
@@ -11152,7 +11419,7 @@
       <c r="R314" s="11"/>
       <c r="S314" s="10"/>
     </row>
-    <row r="315" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B315" s="10"/>
       <c r="C315" s="11"/>
       <c r="D315" s="10" t="str">
@@ -11173,7 +11440,7 @@
       <c r="R315" s="11"/>
       <c r="S315" s="10"/>
     </row>
-    <row r="316" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B316" s="10"/>
       <c r="C316" s="11"/>
       <c r="D316" s="10" t="str">
@@ -11194,7 +11461,7 @@
       <c r="R316" s="11"/>
       <c r="S316" s="10"/>
     </row>
-    <row r="317" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B317" s="10"/>
       <c r="C317" s="11"/>
       <c r="D317" s="10" t="str">
@@ -11215,7 +11482,7 @@
       <c r="R317" s="11"/>
       <c r="S317" s="10"/>
     </row>
-    <row r="318" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B318" s="10"/>
       <c r="C318" s="11"/>
       <c r="D318" s="10" t="str">
@@ -11236,7 +11503,7 @@
       <c r="R318" s="11"/>
       <c r="S318" s="10"/>
     </row>
-    <row r="319" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B319" s="10"/>
       <c r="C319" s="11"/>
       <c r="D319" s="10" t="str">
@@ -11257,7 +11524,7 @@
       <c r="R319" s="11"/>
       <c r="S319" s="10"/>
     </row>
-    <row r="320" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B320" s="10"/>
       <c r="C320" s="11"/>
       <c r="D320" s="10" t="str">
@@ -11278,7 +11545,7 @@
       <c r="R320" s="11"/>
       <c r="S320" s="10"/>
     </row>
-    <row r="321" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B321" s="10"/>
       <c r="C321" s="11"/>
       <c r="D321" s="10" t="str">
@@ -11299,7 +11566,7 @@
       <c r="R321" s="11"/>
       <c r="S321" s="10"/>
     </row>
-    <row r="322" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B322" s="10"/>
       <c r="C322" s="11"/>
       <c r="D322" s="10" t="str">
@@ -11320,7 +11587,7 @@
       <c r="R322" s="11"/>
       <c r="S322" s="10"/>
     </row>
-    <row r="323" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B323" s="10"/>
       <c r="C323" s="11"/>
       <c r="D323" s="10" t="str">
@@ -11341,7 +11608,7 @@
       <c r="R323" s="11"/>
       <c r="S323" s="10"/>
     </row>
-    <row r="324" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B324" s="10"/>
       <c r="C324" s="11"/>
       <c r="D324" s="10" t="str">
@@ -11362,7 +11629,7 @@
       <c r="R324" s="11"/>
       <c r="S324" s="10"/>
     </row>
-    <row r="325" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B325" s="10"/>
       <c r="C325" s="11"/>
       <c r="D325" s="10" t="str">
@@ -11383,7 +11650,7 @@
       <c r="R325" s="11"/>
       <c r="S325" s="10"/>
     </row>
-    <row r="326" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B326" s="10"/>
       <c r="C326" s="11"/>
       <c r="D326" s="10" t="str">
@@ -11404,7 +11671,7 @@
       <c r="R326" s="11"/>
       <c r="S326" s="10"/>
     </row>
-    <row r="327" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B327" s="10"/>
       <c r="C327" s="11"/>
       <c r="D327" s="10" t="str">
@@ -11425,7 +11692,7 @@
       <c r="R327" s="11"/>
       <c r="S327" s="10"/>
     </row>
-    <row r="328" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B328" s="10"/>
       <c r="C328" s="11"/>
       <c r="D328" s="10" t="str">
@@ -11446,7 +11713,7 @@
       <c r="R328" s="11"/>
       <c r="S328" s="10"/>
     </row>
-    <row r="329" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B329" s="10"/>
       <c r="C329" s="11"/>
       <c r="D329" s="10" t="str">
@@ -11467,7 +11734,7 @@
       <c r="R329" s="11"/>
       <c r="S329" s="10"/>
     </row>
-    <row r="330" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B330" s="10"/>
       <c r="C330" s="11"/>
       <c r="D330" s="10" t="str">
@@ -11488,7 +11755,7 @@
       <c r="R330" s="11"/>
       <c r="S330" s="10"/>
     </row>
-    <row r="331" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
       <c r="D331" s="10" t="str">
@@ -11509,7 +11776,7 @@
       <c r="R331" s="11"/>
       <c r="S331" s="10"/>
     </row>
-    <row r="332" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
@@ -11530,7 +11797,7 @@
       <c r="R332" s="11"/>
       <c r="S332" s="10"/>
     </row>
-    <row r="333" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B333" s="10"/>
       <c r="C333" s="11"/>
       <c r="D333" s="10" t="str">
@@ -11551,7 +11818,7 @@
       <c r="R333" s="11"/>
       <c r="S333" s="10"/>
     </row>
-    <row r="334" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B334" s="10"/>
       <c r="C334" s="11"/>
       <c r="D334" s="10" t="str">
@@ -11572,7 +11839,7 @@
       <c r="R334" s="11"/>
       <c r="S334" s="10"/>
     </row>
-    <row r="335" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B335" s="10"/>
       <c r="C335" s="11"/>
       <c r="D335" s="10" t="str">
@@ -11593,7 +11860,7 @@
       <c r="R335" s="11"/>
       <c r="S335" s="10"/>
     </row>
-    <row r="336" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B336" s="10"/>
       <c r="C336" s="11"/>
       <c r="D336" s="10" t="str">
@@ -11614,7 +11881,7 @@
       <c r="R336" s="11"/>
       <c r="S336" s="10"/>
     </row>
-    <row r="337" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B337" s="10"/>
       <c r="C337" s="11"/>
       <c r="D337" s="10" t="str">
@@ -11635,7 +11902,7 @@
       <c r="R337" s="11"/>
       <c r="S337" s="10"/>
     </row>
-    <row r="338" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B338" s="10"/>
       <c r="C338" s="11"/>
       <c r="D338" s="10" t="str">
@@ -11656,7 +11923,7 @@
       <c r="R338" s="11"/>
       <c r="S338" s="10"/>
     </row>
-    <row r="339" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B339" s="10"/>
       <c r="C339" s="11"/>
       <c r="D339" s="10" t="str">
@@ -11677,7 +11944,7 @@
       <c r="R339" s="11"/>
       <c r="S339" s="10"/>
     </row>
-    <row r="340" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B340" s="10"/>
       <c r="C340" s="11"/>
       <c r="D340" s="10" t="str">
@@ -11698,7 +11965,7 @@
       <c r="R340" s="11"/>
       <c r="S340" s="10"/>
     </row>
-    <row r="341" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B341" s="10"/>
       <c r="C341" s="11"/>
       <c r="D341" s="10" t="str">
@@ -11719,7 +11986,7 @@
       <c r="R341" s="11"/>
       <c r="S341" s="10"/>
     </row>
-    <row r="342" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B342" s="10"/>
       <c r="C342" s="11"/>
       <c r="D342" s="10" t="str">
@@ -11740,7 +12007,7 @@
       <c r="R342" s="11"/>
       <c r="S342" s="10"/>
     </row>
-    <row r="343" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B343" s="10"/>
       <c r="C343" s="11"/>
       <c r="D343" s="10" t="str">
@@ -11761,7 +12028,7 @@
       <c r="R343" s="11"/>
       <c r="S343" s="10"/>
     </row>
-    <row r="344" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B344" s="10"/>
       <c r="C344" s="11"/>
       <c r="D344" s="10" t="str">
@@ -11782,7 +12049,7 @@
       <c r="R344" s="11"/>
       <c r="S344" s="10"/>
     </row>
-    <row r="345" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B345" s="10"/>
       <c r="C345" s="11"/>
       <c r="D345" s="10" t="str">
@@ -11803,7 +12070,7 @@
       <c r="R345" s="11"/>
       <c r="S345" s="10"/>
     </row>
-    <row r="346" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B346" s="10"/>
       <c r="C346" s="11"/>
       <c r="D346" s="10" t="str">
@@ -11824,7 +12091,7 @@
       <c r="R346" s="11"/>
       <c r="S346" s="10"/>
     </row>
-    <row r="347" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B347" s="10"/>
       <c r="C347" s="11"/>
       <c r="D347" s="10" t="str">
@@ -11845,7 +12112,7 @@
       <c r="R347" s="11"/>
       <c r="S347" s="10"/>
     </row>
-    <row r="348" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B348" s="10"/>
       <c r="C348" s="11"/>
       <c r="D348" s="10" t="str">
@@ -11866,7 +12133,7 @@
       <c r="R348" s="11"/>
       <c r="S348" s="10"/>
     </row>
-    <row r="349" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B349" s="10"/>
       <c r="C349" s="11"/>
       <c r="D349" s="10" t="str">
@@ -11887,7 +12154,7 @@
       <c r="R349" s="11"/>
       <c r="S349" s="10"/>
     </row>
-    <row r="350" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B350" s="10"/>
       <c r="C350" s="11"/>
       <c r="D350" s="10" t="str">
@@ -11908,7 +12175,7 @@
       <c r="R350" s="11"/>
       <c r="S350" s="10"/>
     </row>
-    <row r="351" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B351" s="10"/>
       <c r="C351" s="11"/>
       <c r="D351" s="10" t="str">
@@ -11929,7 +12196,7 @@
       <c r="R351" s="11"/>
       <c r="S351" s="10"/>
     </row>
-    <row r="352" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B352" s="10"/>
       <c r="C352" s="11"/>
       <c r="D352" s="10" t="str">
@@ -11950,7 +12217,7 @@
       <c r="R352" s="11"/>
       <c r="S352" s="10"/>
     </row>
-    <row r="353" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B353" s="10"/>
       <c r="C353" s="11"/>
       <c r="D353" s="10" t="str">
@@ -11971,7 +12238,7 @@
       <c r="R353" s="11"/>
       <c r="S353" s="10"/>
     </row>
-    <row r="354" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B354" s="10"/>
       <c r="C354" s="11"/>
       <c r="D354" s="10" t="str">
@@ -11992,7 +12259,7 @@
       <c r="R354" s="11"/>
       <c r="S354" s="10"/>
     </row>
-    <row r="355" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B355" s="10"/>
       <c r="C355" s="11"/>
       <c r="D355" s="10" t="str">
@@ -12013,7 +12280,7 @@
       <c r="R355" s="11"/>
       <c r="S355" s="10"/>
     </row>
-    <row r="356" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B356" s="10"/>
       <c r="C356" s="11"/>
       <c r="D356" s="10" t="str">
@@ -12034,7 +12301,7 @@
       <c r="R356" s="11"/>
       <c r="S356" s="10"/>
     </row>
-    <row r="357" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B357" s="10"/>
       <c r="C357" s="11"/>
       <c r="D357" s="10" t="str">
@@ -12055,7 +12322,7 @@
       <c r="R357" s="11"/>
       <c r="S357" s="10"/>
     </row>
-    <row r="358" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B358" s="10"/>
       <c r="C358" s="11"/>
       <c r="D358" s="10" t="str">
@@ -12076,7 +12343,7 @@
       <c r="R358" s="11"/>
       <c r="S358" s="10"/>
     </row>
-    <row r="359" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B359" s="10"/>
       <c r="C359" s="11"/>
       <c r="D359" s="10" t="str">
@@ -12097,7 +12364,7 @@
       <c r="R359" s="11"/>
       <c r="S359" s="10"/>
     </row>
-    <row r="360" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B360" s="10"/>
       <c r="C360" s="11"/>
       <c r="D360" s="10" t="str">
@@ -12118,7 +12385,7 @@
       <c r="R360" s="11"/>
       <c r="S360" s="10"/>
     </row>
-    <row r="361" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B361" s="10"/>
       <c r="C361" s="11"/>
       <c r="D361" s="10" t="str">
@@ -12139,7 +12406,7 @@
       <c r="R361" s="11"/>
       <c r="S361" s="10"/>
     </row>
-    <row r="362" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B362" s="10"/>
       <c r="C362" s="11"/>
       <c r="D362" s="10" t="str">
@@ -12160,7 +12427,7 @@
       <c r="R362" s="11"/>
       <c r="S362" s="10"/>
     </row>
-    <row r="363" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B363" s="10"/>
       <c r="C363" s="11"/>
       <c r="D363" s="10" t="str">
@@ -12181,7 +12448,7 @@
       <c r="R363" s="11"/>
       <c r="S363" s="10"/>
     </row>
-    <row r="364" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B364" s="10"/>
       <c r="C364" s="11"/>
       <c r="D364" s="10" t="str">
@@ -12202,7 +12469,7 @@
       <c r="R364" s="11"/>
       <c r="S364" s="10"/>
     </row>
-    <row r="365" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B365" s="10"/>
       <c r="C365" s="11"/>
       <c r="D365" s="10" t="str">
@@ -12223,7 +12490,7 @@
       <c r="R365" s="11"/>
       <c r="S365" s="10"/>
     </row>
-    <row r="366" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B366" s="10"/>
       <c r="C366" s="11"/>
       <c r="D366" s="10" t="str">
@@ -12244,7 +12511,7 @@
       <c r="R366" s="11"/>
       <c r="S366" s="10"/>
     </row>
-    <row r="367" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B367" s="10"/>
       <c r="C367" s="11"/>
       <c r="D367" s="10" t="str">
@@ -12265,7 +12532,7 @@
       <c r="R367" s="11"/>
       <c r="S367" s="10"/>
     </row>
-    <row r="368" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B368" s="10"/>
       <c r="C368" s="11"/>
       <c r="D368" s="10" t="str">
@@ -12286,7 +12553,7 @@
       <c r="R368" s="11"/>
       <c r="S368" s="10"/>
     </row>
-    <row r="369" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B369" s="10"/>
       <c r="C369" s="11"/>
       <c r="D369" s="10" t="str">
@@ -12307,7 +12574,7 @@
       <c r="R369" s="11"/>
       <c r="S369" s="10"/>
     </row>
-    <row r="370" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B370" s="10"/>
       <c r="C370" s="11"/>
       <c r="D370" s="10" t="str">
@@ -12328,7 +12595,7 @@
       <c r="R370" s="11"/>
       <c r="S370" s="10"/>
     </row>
-    <row r="371" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B371" s="10"/>
       <c r="C371" s="11"/>
       <c r="D371" s="10" t="str">
@@ -12349,7 +12616,7 @@
       <c r="R371" s="11"/>
       <c r="S371" s="10"/>
     </row>
-    <row r="372" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B372" s="10"/>
       <c r="C372" s="11"/>
       <c r="D372" s="10" t="str">
@@ -12370,7 +12637,7 @@
       <c r="R372" s="11"/>
       <c r="S372" s="10"/>
     </row>
-    <row r="373" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B373" s="10"/>
       <c r="C373" s="11"/>
       <c r="D373" s="10" t="str">
@@ -12391,7 +12658,7 @@
       <c r="R373" s="11"/>
       <c r="S373" s="10"/>
     </row>
-    <row r="374" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B374" s="10"/>
       <c r="C374" s="11"/>
       <c r="D374" s="10" t="str">
@@ -12412,7 +12679,7 @@
       <c r="R374" s="11"/>
       <c r="S374" s="10"/>
     </row>
-    <row r="375" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B375" s="10"/>
       <c r="C375" s="11"/>
       <c r="D375" s="10" t="str">
@@ -12433,7 +12700,7 @@
       <c r="R375" s="11"/>
       <c r="S375" s="10"/>
     </row>
-    <row r="376" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B376" s="10"/>
       <c r="C376" s="11"/>
       <c r="D376" s="10" t="str">
@@ -12454,7 +12721,7 @@
       <c r="R376" s="11"/>
       <c r="S376" s="10"/>
     </row>
-    <row r="377" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B377" s="10"/>
       <c r="C377" s="11"/>
       <c r="D377" s="10" t="str">
@@ -12475,7 +12742,7 @@
       <c r="R377" s="11"/>
       <c r="S377" s="10"/>
     </row>
-    <row r="378" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B378" s="10"/>
       <c r="C378" s="11"/>
       <c r="D378" s="10" t="str">
@@ -12496,7 +12763,7 @@
       <c r="R378" s="11"/>
       <c r="S378" s="10"/>
     </row>
-    <row r="379" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B379" s="10"/>
       <c r="C379" s="11"/>
       <c r="D379" s="10" t="str">
@@ -12517,7 +12784,7 @@
       <c r="R379" s="11"/>
       <c r="S379" s="10"/>
     </row>
-    <row r="380" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B380" s="10"/>
       <c r="C380" s="11"/>
       <c r="D380" s="10" t="str">
@@ -12538,7 +12805,7 @@
       <c r="R380" s="11"/>
       <c r="S380" s="10"/>
     </row>
-    <row r="381" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B381" s="10"/>
       <c r="C381" s="11"/>
       <c r="D381" s="10" t="str">
@@ -12559,7 +12826,7 @@
       <c r="R381" s="11"/>
       <c r="S381" s="10"/>
     </row>
-    <row r="382" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B382" s="10"/>
       <c r="C382" s="11"/>
       <c r="D382" s="10" t="str">
@@ -12580,7 +12847,7 @@
       <c r="R382" s="11"/>
       <c r="S382" s="10"/>
     </row>
-    <row r="383" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B383" s="10"/>
       <c r="C383" s="11"/>
       <c r="D383" s="10" t="str">
@@ -12601,7 +12868,7 @@
       <c r="R383" s="11"/>
       <c r="S383" s="10"/>
     </row>
-    <row r="384" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B384" s="10"/>
       <c r="C384" s="11"/>
       <c r="D384" s="10" t="str">
@@ -12622,7 +12889,7 @@
       <c r="R384" s="11"/>
       <c r="S384" s="10"/>
     </row>
-    <row r="385" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B385" s="10"/>
       <c r="C385" s="11"/>
       <c r="D385" s="10" t="str">
@@ -12643,7 +12910,7 @@
       <c r="R385" s="11"/>
       <c r="S385" s="10"/>
     </row>
-    <row r="386" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B386" s="10"/>
       <c r="C386" s="11"/>
       <c r="D386" s="10" t="str">
@@ -12664,7 +12931,7 @@
       <c r="R386" s="11"/>
       <c r="S386" s="10"/>
     </row>
-    <row r="387" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B387" s="10"/>
       <c r="C387" s="11"/>
       <c r="D387" s="10" t="str">
@@ -12685,7 +12952,7 @@
       <c r="R387" s="11"/>
       <c r="S387" s="10"/>
     </row>
-    <row r="388" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B388" s="10"/>
       <c r="C388" s="11"/>
       <c r="D388" s="10" t="str">
@@ -12706,7 +12973,7 @@
       <c r="R388" s="11"/>
       <c r="S388" s="10"/>
     </row>
-    <row r="389" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B389" s="10"/>
       <c r="C389" s="11"/>
       <c r="D389" s="10" t="str">
@@ -12727,7 +12994,7 @@
       <c r="R389" s="11"/>
       <c r="S389" s="10"/>
     </row>
-    <row r="390" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B390" s="10"/>
       <c r="C390" s="11"/>
       <c r="D390" s="10" t="str">
@@ -12748,7 +13015,7 @@
       <c r="R390" s="11"/>
       <c r="S390" s="10"/>
     </row>
-    <row r="391" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B391" s="10"/>
       <c r="C391" s="11"/>
       <c r="D391" s="10" t="str">
@@ -12769,7 +13036,7 @@
       <c r="R391" s="11"/>
       <c r="S391" s="10"/>
     </row>
-    <row r="392" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B392" s="10"/>
       <c r="C392" s="11"/>
       <c r="D392" s="10" t="str">
@@ -12790,7 +13057,7 @@
       <c r="R392" s="11"/>
       <c r="S392" s="10"/>
     </row>
-    <row r="393" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B393" s="10"/>
       <c r="C393" s="11"/>
       <c r="D393" s="10" t="str">
@@ -12811,7 +13078,7 @@
       <c r="R393" s="11"/>
       <c r="S393" s="10"/>
     </row>
-    <row r="394" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B394" s="10"/>
       <c r="C394" s="11"/>
       <c r="D394" s="10" t="str">
@@ -12832,7 +13099,7 @@
       <c r="R394" s="11"/>
       <c r="S394" s="10"/>
     </row>
-    <row r="395" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
       <c r="D395" s="10" t="str">
@@ -12853,7 +13120,7 @@
       <c r="R395" s="11"/>
       <c r="S395" s="10"/>
     </row>
-    <row r="396" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
@@ -12874,7 +13141,7 @@
       <c r="R396" s="11"/>
       <c r="S396" s="10"/>
     </row>
-    <row r="397" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B397" s="10"/>
       <c r="C397" s="11"/>
       <c r="D397" s="10" t="str">
@@ -12895,7 +13162,7 @@
       <c r="R397" s="11"/>
       <c r="S397" s="10"/>
     </row>
-    <row r="398" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B398" s="10"/>
       <c r="C398" s="11"/>
       <c r="D398" s="10" t="str">
@@ -12916,7 +13183,7 @@
       <c r="R398" s="11"/>
       <c r="S398" s="10"/>
     </row>
-    <row r="399" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B399" s="10"/>
       <c r="C399" s="11"/>
       <c r="D399" s="10" t="str">
@@ -12937,7 +13204,7 @@
       <c r="R399" s="11"/>
       <c r="S399" s="10"/>
     </row>
-    <row r="400" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B400" s="10"/>
       <c r="C400" s="11"/>
       <c r="D400" s="10" t="str">
@@ -12958,7 +13225,7 @@
       <c r="R400" s="11"/>
       <c r="S400" s="10"/>
     </row>
-    <row r="401" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B401" s="10"/>
       <c r="C401" s="11"/>
       <c r="D401" s="10" t="str">
@@ -12979,7 +13246,7 @@
       <c r="R401" s="11"/>
       <c r="S401" s="10"/>
     </row>
-    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
       <c r="D402" s="10" t="str">
@@ -13000,7 +13267,7 @@
       <c r="R402" s="11"/>
       <c r="S402" s="10"/>
     </row>
-    <row r="403" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:19">
       <c r="B403" s="10"/>
       <c r="C403" s="11"/>
       <c r="D403" s="1" t="str">
@@ -13016,7 +13283,7 @@
       <c r="Q403" s="11"/>
       <c r="R403" s="11"/>
     </row>
-    <row r="404" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:19">
       <c r="B404" s="10"/>
       <c r="C404" s="11"/>
       <c r="D404" s="1" t="str">
@@ -13032,7 +13299,7 @@
       <c r="Q404" s="11"/>
       <c r="R404" s="11"/>
     </row>
-    <row r="405" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:19">
       <c r="B405" s="10"/>
       <c r="C405" s="11"/>
       <c r="D405" s="1" t="str">
@@ -13046,7 +13313,7 @@
       <c r="Q405" s="11"/>
       <c r="R405" s="11"/>
     </row>
-    <row r="406" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:19">
       <c r="B406" s="10"/>
       <c r="C406" s="11"/>
       <c r="D406" s="1" t="str">
@@ -13060,7 +13327,7 @@
       <c r="Q406" s="11"/>
       <c r="R406" s="11"/>
     </row>
-    <row r="407" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:19">
       <c r="B407" s="10"/>
       <c r="C407" s="11"/>
       <c r="D407" s="1" t="str">
@@ -13070,7 +13337,7 @@
       <c r="Q407" s="11"/>
       <c r="R407" s="11"/>
     </row>
-    <row r="408" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:19">
       <c r="B408" s="10"/>
       <c r="C408" s="11"/>
       <c r="D408" s="1" t="str">
@@ -13084,63 +13351,73 @@
   <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F56:F59">
-    <cfRule type="expression" dxfId="11" priority="26">
+    <cfRule type="expression" dxfId="14" priority="28">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="10" priority="25">
+    <cfRule type="expression" dxfId="13" priority="27">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="9" priority="24">
+    <cfRule type="expression" dxfId="12" priority="26">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="8" priority="23">
+    <cfRule type="expression" dxfId="11" priority="25">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="7" priority="18">
+    <cfRule type="expression" dxfId="10" priority="20">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E97:E98">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$J97="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97:F98">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$J97="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103:F104">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$J103="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H103:H104">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>$J103="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E105:E107">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$J105="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:F107">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>$J105="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H105:H107">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$J105="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E109">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$J109="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F109">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J105="잔금"</formula>
+      <formula>$J109="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -13150,7 +13427,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G2:G70">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N101">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N109">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13162,7 +13439,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C22"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.375" style="18" customWidth="1"/>
     <col min="2" max="2" width="26.75" style="18" bestFit="1" customWidth="1"/>
@@ -13170,12 +13447,12 @@
     <col min="4" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="16.5" customHeight="1">
       <c r="B2" s="18" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" ht="16.5" customHeight="1">
       <c r="B3" s="22" t="s">
         <v>132</v>
       </c>
@@ -13183,7 +13460,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" ht="16.5" customHeight="1">
       <c r="B4" s="16" t="s">
         <v>141</v>
       </c>
@@ -13191,7 +13468,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" ht="16.5" customHeight="1">
       <c r="B5" s="16" t="s">
         <v>148</v>
       </c>
@@ -13199,7 +13476,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" ht="16.5" customHeight="1">
       <c r="B6" s="16" t="s">
         <v>149</v>
       </c>
@@ -13207,7 +13484,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" ht="13.5">
       <c r="B7" s="20" t="s">
         <v>142</v>
       </c>
@@ -13215,7 +13492,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" ht="16.5" customHeight="1">
       <c r="B8" s="16" t="s">
         <v>143</v>
       </c>
@@ -13223,7 +13500,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" ht="16.5" customHeight="1">
       <c r="B9" s="16" t="s">
         <v>144</v>
       </c>
@@ -13231,37 +13508,37 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" ht="16.5" customHeight="1">
       <c r="B12" s="19"/>
     </row>
-    <row r="13" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" ht="16.5" customHeight="1">
       <c r="B13"/>
     </row>
-    <row r="14" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" ht="16.5" customHeight="1">
       <c r="B14" s="19"/>
     </row>
-    <row r="15" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" ht="16.5" customHeight="1">
       <c r="B15"/>
     </row>
-    <row r="16" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" ht="16.5" customHeight="1">
       <c r="B16" s="19"/>
     </row>
-    <row r="17" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" ht="16.5" customHeight="1">
       <c r="B17"/>
     </row>
-    <row r="18" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" ht="16.5" customHeight="1">
       <c r="B18" s="19"/>
     </row>
-    <row r="19" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" ht="16.5" customHeight="1">
       <c r="B19"/>
     </row>
-    <row r="20" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" ht="16.5" customHeight="1">
       <c r="B20" s="19"/>
     </row>
-    <row r="21" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" ht="16.5" customHeight="1">
       <c r="B21"/>
     </row>
-    <row r="22" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" ht="16.5" customHeight="1">
       <c r="B22" s="19"/>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="197">
   <si>
     <t>순번</t>
   </si>
@@ -687,6 +687,28 @@
     <t>자재</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>청록개발</t>
+  </si>
+  <si>
+    <t>(주)태영건설</t>
+  </si>
+  <si>
+    <t>경기도광주</t>
+  </si>
+  <si>
+    <t>잠실리센츠</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>풍납현대리버빌1차</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
 </sst>
 </file>
 
@@ -695,10 +717,10 @@
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="182" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -788,6 +810,12 @@
       <family val="3"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -876,10 +904,10 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -891,15 +919,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -993,6 +1021,9 @@
     <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
@@ -1007,7 +1038,82 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="20">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1640,7 +1746,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I55" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -1704,7 +1810,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J58" ca="1" si="2">IF(I3="","",
@@ -1763,7 +1869,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1861,7 +1967,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1917,7 +2023,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1966,7 +2072,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2017,7 +2123,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2069,7 +2175,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2113,7 +2219,7 @@
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J11" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2206,7 +2312,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2262,7 +2368,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2311,7 +2417,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2360,7 +2466,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2407,7 +2513,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2454,7 +2560,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2501,7 +2607,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2548,7 +2654,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2595,7 +2701,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2644,7 +2750,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2693,7 +2799,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2742,7 +2848,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2791,7 +2897,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2840,7 +2946,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2889,7 +2995,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2938,7 +3044,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2987,7 +3093,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3036,7 +3142,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3085,7 +3191,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3134,7 +3240,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3183,7 +3289,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3232,7 +3338,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3281,7 +3387,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3330,7 +3436,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3375,7 +3481,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3429,7 +3535,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3485,7 +3591,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3538,7 +3644,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3585,7 +3691,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3639,7 +3745,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3744,7 +3850,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3795,7 +3901,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3839,7 +3945,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3883,7 +3989,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3930,7 +4036,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3977,7 +4083,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4024,7 +4130,7 @@
       </c>
       <c r="I50" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J50" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4068,7 +4174,7 @@
       </c>
       <c r="I51" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J51" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4112,7 +4218,7 @@
       </c>
       <c r="I52" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J52" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4159,7 +4265,7 @@
       </c>
       <c r="I53" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J53" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4255,7 +4361,7 @@
       </c>
       <c r="I55" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J55" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4302,7 +4408,7 @@
       </c>
       <c r="I56" s="12">
         <f t="shared" ref="I56:I65" ca="1" si="4">IF(C56="","",IF(L56="",TODAY()-C56,L56-C56))</f>
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J56" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4349,7 +4455,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4396,7 +4502,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4443,7 +4549,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ref="J59:J113" ca="1" si="5">IF(I59="","",
@@ -4590,7 +4696,7 @@
       </c>
       <c r="I62" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J62" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4634,7 +4740,7 @@
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J63" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4724,7 +4830,7 @@
       </c>
       <c r="I65" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J65" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4768,7 +4874,7 @@
       </c>
       <c r="I66" s="6">
         <f t="shared" ref="I66:I71" ca="1" si="7">IF(C66="","",IF(L66="",TODAY()-C66,L66-C66))</f>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4810,7 +4916,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4852,7 +4958,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4894,14 +5000,16 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
       <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
+      <c r="L69" s="11">
+        <v>46073</v>
+      </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10" t="s">
         <v>20</v>
@@ -4991,7 +5099,7 @@
       </c>
       <c r="I71" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J71" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5043,7 +5151,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ref="I72:I75" ca="1" si="8">IF(C72="","",IF(L72="",TODAY()-C72,L72-C72))</f>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5188,7 +5296,7 @@
       </c>
       <c r="I75" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J75" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5426,7 +5534,7 @@
       </c>
       <c r="I80" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J80" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5512,7 +5620,7 @@
       </c>
       <c r="I82" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J82" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5564,7 +5672,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5616,7 +5724,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5668,7 +5776,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5710,7 +5818,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5806,7 +5914,7 @@
       </c>
       <c r="I88" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J88" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5858,7 +5966,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5954,7 +6062,7 @@
       </c>
       <c r="I91" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J91" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6084,7 +6192,7 @@
       </c>
       <c r="I94" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J94" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6126,7 +6234,7 @@
       </c>
       <c r="I95" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J95" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6212,7 +6320,7 @@
       </c>
       <c r="I97" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6254,7 +6362,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6295,7 +6403,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6468,7 +6576,7 @@
       </c>
       <c r="I103" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J103" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6510,7 +6618,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6551,7 +6659,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6595,7 +6703,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6636,7 +6744,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6677,7 +6785,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6718,7 +6826,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6738,82 +6846,132 @@
       <c r="S109" s="10"/>
     </row>
     <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B110" s="10" t="str">
+      <c r="B110" s="10">
         <f>IF(C110="","",COUNTA($C$2:C110))</f>
-        <v/>
-      </c>
-      <c r="C110" s="11"/>
+        <v>109</v>
+      </c>
+      <c r="C110" s="35" t="s">
+        <v>195</v>
+      </c>
       <c r="D110" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H110" s="4"/>
-      <c r="I110" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E110" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F110" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H110" s="25">
+        <v>5436700</v>
+      </c>
+      <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K110" s="11"/>
-      <c r="L110" s="11"/>
+      <c r="L110" s="11">
+        <v>46073</v>
+      </c>
       <c r="M110" s="10"/>
-      <c r="N110" s="10"/>
+      <c r="N110" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q110" s="11"/>
       <c r="R110" s="11"/>
       <c r="S110" s="10"/>
     </row>
     <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B111" s="10" t="str">
+      <c r="B111" s="10">
         <f>IF(C111="","",COUNTA($C$2:C111))</f>
-        <v/>
-      </c>
-      <c r="C111" s="11"/>
+        <v>110</v>
+      </c>
+      <c r="C111" s="35" t="s">
+        <v>195</v>
+      </c>
       <c r="D111" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H111" s="4"/>
-      <c r="I111" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E111" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F111" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H111" s="25">
+        <v>37600000</v>
+      </c>
+      <c r="I111" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J111" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K111" s="11"/>
       <c r="L111" s="11"/>
       <c r="M111" s="10"/>
-      <c r="N111" s="10"/>
+      <c r="N111" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P111" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="Q111" s="11"/>
       <c r="R111" s="11"/>
       <c r="S111" s="10"/>
     </row>
     <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B112" s="10" t="str">
+      <c r="B112" s="10">
         <f>IF(C112="","",COUNTA($C$2:C112))</f>
-        <v/>
-      </c>
-      <c r="C112" s="11"/>
+        <v>111</v>
+      </c>
+      <c r="C112" s="35" t="s">
+        <v>196</v>
+      </c>
       <c r="D112" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H112" s="4"/>
-      <c r="I112" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E112" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="F112" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H112" s="25">
+        <v>2706000</v>
+      </c>
+      <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K112" s="11"/>
       <c r="L112" s="11"/>
       <c r="M112" s="10"/>
-      <c r="N112" s="10"/>
+      <c r="N112" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q112" s="11"/>
       <c r="R112" s="11"/>
       <c r="S112" s="10"/>
@@ -13351,73 +13509,98 @@
   <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F56:F59">
-    <cfRule type="expression" dxfId="14" priority="28">
+    <cfRule type="expression" dxfId="19" priority="33">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="13" priority="27">
+    <cfRule type="expression" dxfId="18" priority="32">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="12" priority="26">
+    <cfRule type="expression" dxfId="17" priority="31">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="11" priority="25">
+    <cfRule type="expression" dxfId="16" priority="30">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="10" priority="20">
+    <cfRule type="expression" dxfId="15" priority="25">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E97:E98">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>$J97="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97:F98">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>$J97="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103:F104">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$J103="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H103:H104">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>$J103="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E105:E107">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$J105="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:F107">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>$J105="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H105:H107">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$J105="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E109">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$J109="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109">
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>$J109="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E110:E112">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>$J110="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F110 F112">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>$J110="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F111">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H110:H112">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J110="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C110:C112">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J109="잔금"</formula>
+      <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -13427,7 +13610,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G2:G70">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N109">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N112">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -927,7 +927,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1024,6 +1024,9 @@
     <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
@@ -1038,22 +1041,7 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill>
@@ -6857,7 +6845,7 @@
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="E110" s="23" t="s">
+      <c r="E110" s="36" t="s">
         <v>190</v>
       </c>
       <c r="F110" s="23" t="s">
@@ -13509,87 +13497,87 @@
   <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F56:F59">
-    <cfRule type="expression" dxfId="19" priority="33">
+    <cfRule type="expression" dxfId="18" priority="33">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="18" priority="32">
+    <cfRule type="expression" dxfId="17" priority="32">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="17" priority="31">
+    <cfRule type="expression" dxfId="16" priority="31">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="16" priority="30">
+    <cfRule type="expression" dxfId="15" priority="30">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="15" priority="25">
+    <cfRule type="expression" dxfId="14" priority="25">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E97:E98">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>$J97="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97:F98">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="12" priority="14">
       <formula>$J97="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F103:F104">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>$J103="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H103:H104">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$J103="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E105:E107">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$J105="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F105:F107">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$J105="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H105:H107">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>$J105="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E109">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$J109="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F109">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$J109="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110:E112">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110 F112">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="198">
   <si>
     <t>순번</t>
   </si>
@@ -709,16 +709,20 @@
   <si>
     <t>2026-02-23</t>
   </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="181" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -896,7 +900,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -926,8 +930,11 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1027,14 +1034,27 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="11">
+  <cellStyles count="12">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
     <cellStyle name="백분율 2" xfId="2"/>
     <cellStyle name="백분율 3" xfId="10"/>
     <cellStyle name="쉼표 [0] 118 2 7 16" xfId="3"/>
     <cellStyle name="쉼표 [0] 2" xfId="4"/>
     <cellStyle name="쉼표 [0] 3" xfId="9"/>
+    <cellStyle name="쉼표 [0] 4" xfId="11"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 118 2 7 16" xfId="5"/>
     <cellStyle name="표준 125" xfId="6"/>
@@ -1734,7 +1754,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I55" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -1798,7 +1818,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J58" ca="1" si="2">IF(I3="","",
@@ -1857,7 +1877,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1955,7 +1975,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2011,7 +2031,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2060,7 +2080,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2111,7 +2131,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2163,7 +2183,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2207,7 +2227,7 @@
       </c>
       <c r="I11" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J11" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2300,7 +2320,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2356,7 +2376,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2405,7 +2425,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2454,7 +2474,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2501,7 +2521,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2548,7 +2568,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2595,7 +2615,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2642,7 +2662,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2689,7 +2709,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2738,7 +2758,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2787,7 +2807,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2836,7 +2856,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2885,7 +2905,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2934,7 +2954,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2983,7 +3003,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3032,7 +3052,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3081,7 +3101,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3130,7 +3150,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3179,7 +3199,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3228,7 +3248,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3277,7 +3297,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3326,7 +3346,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3375,7 +3395,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3424,7 +3444,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3469,7 +3489,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3523,7 +3543,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3579,7 +3599,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3632,7 +3652,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3679,7 +3699,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3733,7 +3753,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3838,7 +3858,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3889,7 +3909,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3933,7 +3953,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3977,7 +3997,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4024,7 +4044,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4071,7 +4091,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4118,7 +4138,7 @@
       </c>
       <c r="I50" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J50" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4162,7 +4182,7 @@
       </c>
       <c r="I51" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J51" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4206,7 +4226,7 @@
       </c>
       <c r="I52" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J52" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4253,7 +4273,7 @@
       </c>
       <c r="I53" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J53" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4349,7 +4369,7 @@
       </c>
       <c r="I55" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J55" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4396,7 +4416,7 @@
       </c>
       <c r="I56" s="12">
         <f t="shared" ref="I56:I65" ca="1" si="4">IF(C56="","",IF(L56="",TODAY()-C56,L56-C56))</f>
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J56" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4443,7 +4463,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4490,7 +4510,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4537,7 +4557,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ref="J59:J113" ca="1" si="5">IF(I59="","",
@@ -4684,7 +4704,7 @@
       </c>
       <c r="I62" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J62" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4728,7 +4748,7 @@
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J63" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4818,7 +4838,7 @@
       </c>
       <c r="I65" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J65" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4862,7 +4882,7 @@
       </c>
       <c r="I66" s="6">
         <f t="shared" ref="I66:I71" ca="1" si="7">IF(C66="","",IF(L66="",TODAY()-C66,L66-C66))</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4904,7 +4924,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4946,7 +4966,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5087,7 +5107,7 @@
       </c>
       <c r="I71" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J71" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5139,7 +5159,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ref="I72:I75" ca="1" si="8">IF(C72="","",IF(L72="",TODAY()-C72,L72-C72))</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5284,7 +5304,7 @@
       </c>
       <c r="I75" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J75" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5522,7 +5542,7 @@
       </c>
       <c r="I80" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J80" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5608,7 +5628,7 @@
       </c>
       <c r="I82" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J82" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5660,7 +5680,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5712,7 +5732,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5764,7 +5784,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5806,7 +5826,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5902,7 +5922,7 @@
       </c>
       <c r="I88" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J88" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5954,7 +5974,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6050,7 +6070,7 @@
       </c>
       <c r="I91" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J91" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6180,7 +6200,7 @@
       </c>
       <c r="I94" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J94" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6222,7 +6242,7 @@
       </c>
       <c r="I95" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J95" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6308,7 +6328,7 @@
       </c>
       <c r="I97" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6350,7 +6370,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6391,7 +6411,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6564,7 +6584,7 @@
       </c>
       <c r="I103" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J103" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6606,7 +6626,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6647,7 +6667,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6691,7 +6711,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6732,7 +6752,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6773,7 +6793,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6814,7 +6834,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6903,7 +6923,7 @@
       </c>
       <c r="I111" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J111" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6955,7 +6975,9 @@
         <v>정상</v>
       </c>
       <c r="K112" s="11"/>
-      <c r="L112" s="11"/>
+      <c r="L112" s="11">
+        <v>46076</v>
+      </c>
       <c r="M112" s="10"/>
       <c r="N112" s="10" t="s">
         <v>33</v>
@@ -6965,46 +6987,77 @@
       <c r="S112" s="10"/>
     </row>
     <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B113" s="10" t="str">
+      <c r="B113" s="10">
         <f>IF(C113="","",COUNTA($C$2:C113))</f>
-        <v/>
-      </c>
-      <c r="C113" s="11"/>
+        <v>112</v>
+      </c>
+      <c r="C113" s="39" t="s">
+        <v>196</v>
+      </c>
       <c r="D113" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H113" s="4"/>
-      <c r="I113" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E113" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F113" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H113" s="40">
+        <v>11500000</v>
+      </c>
+      <c r="I113" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J113" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K113" s="11"/>
       <c r="L113" s="11"/>
       <c r="M113" s="10"/>
-      <c r="N113" s="10"/>
+      <c r="N113" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P113" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="Q113" s="11"/>
       <c r="R113" s="11"/>
       <c r="S113" s="10"/>
     </row>
     <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B114" s="10" t="str">
+      <c r="B114" s="10">
         <f>IF(C114="","",COUNTA($C$2:C114))</f>
-        <v/>
-      </c>
-      <c r="C114" s="11"/>
+        <v>113</v>
+      </c>
+      <c r="C114" s="39" t="s">
+        <v>196</v>
+      </c>
       <c r="D114" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H114" s="4"/>
-      <c r="I114" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E114" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F114" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H114" s="40">
+        <v>3438000</v>
+      </c>
+      <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ref="J114:J130" ca="1" si="11">IF(I114="","",
@@ -7016,39 +7069,59 @@
   )
  )
 )</f>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K114" s="11"/>
       <c r="L114" s="11"/>
       <c r="M114" s="10"/>
-      <c r="N114" s="10"/>
+      <c r="N114" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="Q114" s="11"/>
       <c r="R114" s="11"/>
       <c r="S114" s="10"/>
     </row>
     <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B115" s="10" t="str">
+      <c r="B115" s="10">
         <f>IF(C115="","",COUNTA($C$2:C115))</f>
-        <v/>
-      </c>
-      <c r="C115" s="11"/>
+        <v>114</v>
+      </c>
+      <c r="C115" s="39" t="s">
+        <v>197</v>
+      </c>
       <c r="D115" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H115" s="4"/>
-      <c r="I115" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E115" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="F115" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H115" s="40">
+        <v>502300</v>
+      </c>
+      <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K115" s="11"/>
       <c r="L115" s="11"/>
       <c r="M115" s="10"/>
-      <c r="N115" s="10"/>
+      <c r="N115" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q115" s="11"/>
       <c r="R115" s="11"/>
       <c r="S115" s="10"/>
@@ -13598,7 +13671,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G2:G70">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N112">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N115">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,15 +11,15 @@
     <sheet name="프로세스현황" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$408</definedName>
-    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$408</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$409</definedName>
+    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$409</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="202">
   <si>
     <t>순번</t>
   </si>
@@ -712,17 +712,32 @@
   <si>
     <t>2026-02-24</t>
   </si>
+  <si>
+    <t>대표건설㈜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>금당그리안</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="181" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -930,7 +945,7 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1645,7 +1660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S408"/>
+  <dimension ref="A1:S409"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
@@ -1737,7 +1752,7 @@
         <v>45797</v>
       </c>
       <c r="D2" s="10" t="str">
-        <f t="shared" ref="D2:D55" si="0">IF(G2="","",IF(OR(G2="선급금",G2="중도금",G2="잔금"),"A",IF(G2="자재","B",IF(G2="특허료","C",""))))</f>
+        <f t="shared" ref="D2:D56" si="0">IF(G2="","",IF(OR(G2="선급금",G2="중도금",G2="잔금"),"A",IF(G2="자재","B",IF(G2="특허료","C",""))))</f>
         <v>A</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -1753,7 +1768,7 @@
         <v>23770800</v>
       </c>
       <c r="I2" s="12">
-        <f t="shared" ref="I2:I55" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
+        <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
         <v>280</v>
       </c>
       <c r="J2" s="13" t="str">
@@ -1821,7 +1836,7 @@
         <v>130</v>
       </c>
       <c r="J3" s="13" t="str">
-        <f t="shared" ref="J3:J58" ca="1" si="2">IF(I3="","",
+        <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
  IF(G3="선급금",
    IF(I3&lt;=20,"정상",IF(I3&lt;=90,"관리","장기미수")),
  IF(G3="자재",
@@ -4071,42 +4086,37 @@
         <v>48</v>
       </c>
       <c r="C49" s="11">
-        <v>45993</v>
+        <v>46345</v>
       </c>
       <c r="D49" s="10" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>26</v>
+        <v>198</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="H49" s="4">
-        <v>7920000</v>
+        <v>645000</v>
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>84</v>
+        <v>-268</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>관리</v>
-      </c>
-      <c r="K49" s="11">
-        <v>46080</v>
-      </c>
+        <v>정상</v>
+      </c>
+      <c r="K49" s="11"/>
       <c r="L49" s="11"/>
       <c r="M49" s="10"/>
       <c r="N49" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="P49" s="6" t="s">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
@@ -4118,27 +4128,27 @@
         <v>49</v>
       </c>
       <c r="C50" s="11">
-        <v>45999</v>
+        <v>45993</v>
       </c>
       <c r="D50" s="10" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H50" s="4">
-        <v>5253000</v>
+        <v>7920000</v>
       </c>
       <c r="I50" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J50" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4152,6 +4162,9 @@
       <c r="N50" s="10" t="s">
         <v>33</v>
       </c>
+      <c r="P50" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="Q50" s="11"/>
       <c r="R50" s="11"/>
       <c r="S50" s="10"/>
@@ -4162,7 +4175,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11">
-        <v>46006</v>
+        <v>45999</v>
       </c>
       <c r="D51" s="10" t="str">
         <f t="shared" si="0"/>
@@ -4178,11 +4191,11 @@
         <v>48</v>
       </c>
       <c r="H51" s="4">
-        <v>1120000</v>
+        <v>5253000</v>
       </c>
       <c r="I51" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J51" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4206,27 +4219,27 @@
         <v>51</v>
       </c>
       <c r="C52" s="11">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="D52" s="10" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H52" s="4">
-        <v>1969400</v>
+        <v>1120000</v>
       </c>
       <c r="I52" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J52" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4240,9 +4253,6 @@
       <c r="N52" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P52" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="Q52" s="11"/>
       <c r="R52" s="11"/>
       <c r="S52" s="10"/>
@@ -4253,50 +4263,45 @@
         <v>52</v>
       </c>
       <c r="C53" s="11">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="D53" s="10" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H53" s="4">
-        <v>54744000</v>
+        <v>1969400</v>
       </c>
       <c r="I53" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J53" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>관리</v>
       </c>
-      <c r="K53" s="11"/>
+      <c r="K53" s="11">
+        <v>46080</v>
+      </c>
       <c r="L53" s="11"/>
       <c r="M53" s="10"/>
       <c r="N53" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O53" s="6" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q53" s="11">
-        <v>46036</v>
-      </c>
-      <c r="R53" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="Q53" s="11"/>
+      <c r="R53" s="11"/>
       <c r="S53" s="10"/>
     </row>
     <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -4312,35 +4317,43 @@
         <v>B</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H54" s="4">
-        <v>321000</v>
+        <v>54744000</v>
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>관리</v>
       </c>
       <c r="K54" s="11"/>
-      <c r="L54" s="11">
-        <v>46063</v>
-      </c>
+      <c r="L54" s="11"/>
       <c r="M54" s="10"/>
       <c r="N54" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q54" s="11"/>
-      <c r="R54" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q54" s="11">
+        <v>46036</v>
+      </c>
+      <c r="R54" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="S54" s="10"/>
     </row>
     <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -4349,42 +4362,39 @@
         <v>54</v>
       </c>
       <c r="C55" s="11">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="D55" s="10" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H55" s="4">
-        <v>15840000</v>
+        <v>321000</v>
       </c>
       <c r="I55" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="J55" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>관리</v>
       </c>
-      <c r="K55" s="11">
-        <v>46080</v>
-      </c>
-      <c r="L55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11">
+        <v>46063</v>
+      </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="P55" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="Q55" s="11"/>
       <c r="R55" s="11"/>
@@ -4396,45 +4406,45 @@
         <v>55</v>
       </c>
       <c r="C56" s="11">
-        <v>45705</v>
+        <v>46013</v>
       </c>
       <c r="D56" s="10" t="str">
-        <f t="shared" ref="D56:D65" si="3">IF(G56="","",IF(OR(G56="선급금",G56="중도금",G56="잔금"),"A",IF(G56="자재","B",IF(G56="특허료","C",""))))</f>
-        <v>C</v>
+        <f t="shared" si="0"/>
+        <v>B</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H56" s="4">
-        <v>1632000</v>
+        <v>15840000</v>
       </c>
       <c r="I56" s="12">
-        <f t="shared" ref="I56:I65" ca="1" si="4">IF(C56="","",IF(L56="",TODAY()-C56,L56-C56))</f>
-        <v>372</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>64</v>
       </c>
       <c r="J56" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>장기미수</v>
-      </c>
-      <c r="K56" s="11"/>
+        <v>관리</v>
+      </c>
+      <c r="K56" s="11">
+        <v>46080</v>
+      </c>
       <c r="L56" s="11"/>
-      <c r="M56" s="10" t="s">
-        <v>153</v>
-      </c>
+      <c r="M56" s="10"/>
       <c r="N56" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q56" s="14"/>
-      <c r="R56" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q56" s="11"/>
+      <c r="R56" s="11"/>
       <c r="S56" s="10"/>
     </row>
     <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -4443,27 +4453,27 @@
         <v>56</v>
       </c>
       <c r="C57" s="11">
-        <v>45840</v>
+        <v>45705</v>
       </c>
       <c r="D57" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D57:D66" si="3">IF(G57="","",IF(OR(G57="선급금",G57="중도금",G57="잔금"),"A",IF(G57="자재","B",IF(G57="특허료","C",""))))</f>
         <v>C</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>46</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H57" s="4">
-        <v>5380000</v>
+        <v>1632000</v>
       </c>
       <c r="I57" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>237</v>
+        <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
+        <v>372</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4500,13 +4510,13 @@
         <v>46</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H58" s="4">
-        <v>765000</v>
+        <v>5380000</v>
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
@@ -4537,7 +4547,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11">
-        <v>45889</v>
+        <v>45840</v>
       </c>
       <c r="D59" s="10" t="str">
         <f t="shared" si="3"/>
@@ -4547,86 +4557,87 @@
         <v>46</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H59" s="4">
-        <v>2738900</v>
+        <v>765000</v>
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
+        <v>237</v>
+      </c>
+      <c r="J59" s="13" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>장기미수</v>
+      </c>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="O59" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q59" s="14"/>
+      <c r="R59" s="14"/>
+      <c r="S59" s="10"/>
+    </row>
+    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B60" s="10">
+        <f>IF(C60="","",COUNTA($C$2:C60))</f>
+        <v>59</v>
+      </c>
+      <c r="C60" s="11">
+        <v>45889</v>
+      </c>
+      <c r="D60" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>C</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H60" s="4">
+        <v>2738900</v>
+      </c>
+      <c r="I60" s="12">
+        <f t="shared" ca="1" si="4"/>
         <v>188</v>
       </c>
-      <c r="J59" s="13" t="str">
-        <f t="shared" ref="J59:J113" ca="1" si="5">IF(I59="","",
- IF(G59="선급금",
-   IF(I59&lt;=20,"정상",IF(I59&lt;=90,"관리","장기미수")),
- IF(G59="자재",
-   IF(I59&lt;=40,"정상",IF(I59&lt;=90,"관리","장기미수")),
-   IF(I59&lt;=30,"정상",IF(I59&lt;=90,"관리","장기미수"))
+      <c r="J60" s="13" t="str">
+        <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
+ IF(G60="선급금",
+   IF(I60&lt;=20,"정상",IF(I60&lt;=90,"관리","장기미수")),
+ IF(G60="자재",
+   IF(I60&lt;=40,"정상",IF(I60&lt;=90,"관리","장기미수")),
+   IF(I60&lt;=30,"정상",IF(I60&lt;=90,"관리","장기미수"))
   )
  )
 )</f>
         <v>장기미수</v>
       </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="10" t="s">
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="N59" s="10" t="s">
+      <c r="N60" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="O59" s="6" t="s">
+      <c r="O60" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="Q59" s="14"/>
-      <c r="R59" s="14"/>
-      <c r="S59" s="10"/>
-    </row>
-    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B60" s="10">
-        <f>IF(C60="","",COUNTA($C$2:C60))</f>
-        <v>59</v>
-      </c>
-      <c r="C60" s="11">
-        <v>46006</v>
-      </c>
-      <c r="D60" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>C</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H60" s="4">
-        <v>1648500</v>
-      </c>
-      <c r="I60" s="12">
-        <f t="shared" ca="1" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="J60" s="13" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>관리</v>
-      </c>
-      <c r="K60" s="11">
-        <v>46066</v>
-      </c>
-      <c r="L60" s="11">
-        <v>46066</v>
-      </c>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10" t="s">
-        <v>33</v>
       </c>
       <c r="Q60" s="14"/>
       <c r="R60" s="14"/>
@@ -4648,13 +4659,13 @@
         <v>62</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H61" s="4">
-        <v>2625000</v>
+        <v>1648500</v>
       </c>
       <c r="I61" s="12">
         <f t="shared" ca="1" si="4"/>
@@ -4691,29 +4702,31 @@
         <v>C</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H62" s="4">
-        <v>495000</v>
+        <v>2625000</v>
       </c>
       <c r="I62" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="J62" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
       <c r="K62" s="11">
-        <v>46087</v>
-      </c>
-      <c r="L62" s="11"/>
+        <v>46066</v>
+      </c>
+      <c r="L62" s="11">
+        <v>46066</v>
+      </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10" t="s">
         <v>33</v>
@@ -4738,13 +4751,13 @@
         <v>92</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H63" s="4">
-        <v>485000</v>
+        <v>495000</v>
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
@@ -4772,38 +4785,36 @@
         <v>63</v>
       </c>
       <c r="C64" s="11">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="D64" s="10" t="str">
         <f t="shared" si="3"/>
         <v>C</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H64" s="4">
-        <v>662500</v>
+        <v>485000</v>
       </c>
       <c r="I64" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="J64" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
       <c r="K64" s="11">
-        <v>46066</v>
-      </c>
-      <c r="L64" s="11">
-        <v>46064</v>
-      </c>
+        <v>46087</v>
+      </c>
+      <c r="L64" s="11"/>
       <c r="M64" s="10"/>
       <c r="N64" s="10" t="s">
         <v>33</v>
@@ -4825,29 +4836,31 @@
         <v>C</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H65" s="4">
-        <v>3537700</v>
+        <v>662500</v>
       </c>
       <c r="I65" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="J65" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
       <c r="K65" s="11">
-        <v>46052</v>
-      </c>
-      <c r="L65" s="11"/>
+        <v>46066</v>
+      </c>
+      <c r="L65" s="11">
+        <v>46064</v>
+      </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10" t="s">
         <v>33</v>
@@ -4862,40 +4875,42 @@
         <v>65</v>
       </c>
       <c r="C66" s="11">
-        <v>46027</v>
+        <v>46009</v>
       </c>
       <c r="D66" s="10" t="str">
-        <f t="shared" ref="D66:D75" si="6">IF(G66="","",IF(OR(G66="선급금",G66="중도금",G66="잔금"),"A",IF(G66="자재","B",IF(G66="특허료","C",""))))</f>
+        <f t="shared" si="3"/>
         <v>C</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="4">
-        <v>3802500</v>
-      </c>
-      <c r="I66" s="6">
-        <f t="shared" ref="I66:I71" ca="1" si="7">IF(C66="","",IF(L66="",TODAY()-C66,L66-C66))</f>
-        <v>50</v>
+        <v>3537700</v>
+      </c>
+      <c r="I66" s="12">
+        <f t="shared" ca="1" si="4"/>
+        <v>68</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
-      <c r="K66" s="11"/>
+      <c r="K66" s="11">
+        <v>46052</v>
+      </c>
       <c r="L66" s="11"/>
       <c r="M66" s="10"/>
       <c r="N66" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Q66" s="11"/>
-      <c r="R66" s="11"/>
+      <c r="Q66" s="14"/>
+      <c r="R66" s="14"/>
       <c r="S66" s="10"/>
     </row>
     <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -4904,27 +4919,27 @@
         <v>66</v>
       </c>
       <c r="C67" s="11">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="D67" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D67:D76" si="6">IF(G67="","",IF(OR(G67="선급금",G67="중도금",G67="잔금"),"A",IF(G67="자재","B",IF(G67="특허료","C",""))))</f>
         <v>C</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H67" s="4">
-        <v>138050</v>
+        <v>3802500</v>
       </c>
       <c r="I67" s="6">
-        <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
+        <v>50</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4956,13 +4971,13 @@
         <v>101</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H68" s="4">
-        <v>6675050</v>
+        <v>138050</v>
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
@@ -4995,35 +5010,30 @@
         <v>C</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H69" s="4">
-        <v>7500000</v>
+        <v>6675050</v>
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
       <c r="K69" s="11"/>
-      <c r="L69" s="11">
-        <v>46073</v>
-      </c>
+      <c r="L69" s="11"/>
       <c r="M69" s="10"/>
       <c r="N69" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O69" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="Q69" s="11"/>
       <c r="R69" s="11"/>
@@ -5035,102 +5045,97 @@
         <v>69</v>
       </c>
       <c r="C70" s="11">
-        <v>46034</v>
+        <v>46028</v>
       </c>
       <c r="D70" s="10" t="str">
         <f t="shared" si="6"/>
         <v>C</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H70" s="4">
-        <v>179500</v>
+        <v>7500000</v>
       </c>
       <c r="I70" s="6">
         <f t="shared" ca="1" si="7"/>
+        <v>45</v>
+      </c>
+      <c r="J70" s="13" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>관리</v>
+      </c>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11">
+        <v>46073</v>
+      </c>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="10"/>
+    </row>
+    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B71" s="10">
+        <f>IF(C71="","",COUNTA($C$2:C71))</f>
+        <v>70</v>
+      </c>
+      <c r="C71" s="11">
+        <v>46034</v>
+      </c>
+      <c r="D71" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>C</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H71" s="4">
+        <v>179500</v>
+      </c>
+      <c r="I71" s="6">
+        <f t="shared" ca="1" si="7"/>
         <v>3</v>
       </c>
-      <c r="J70" s="13" t="str">
-        <f ca="1">IF(I70="","",
- IF(G70="선급금",
-   IF(I70&lt;=20,"정상",IF(I70&lt;=90,"관리","장기미수")),
- IF(G70="자재",
-   IF(I70&lt;=40,"정상",IF(I70&lt;=90,"관리","장기미수")),
-   IF(I70&lt;=30,"정상",IF(I70&lt;=90,"관리","장기미수"))
+      <c r="J71" s="13" t="str">
+        <f ca="1">IF(I71="","",
+ IF(G71="선급금",
+   IF(I71&lt;=20,"정상",IF(I71&lt;=90,"관리","장기미수")),
+ IF(G71="자재",
+   IF(I71&lt;=40,"정상",IF(I71&lt;=90,"관리","장기미수")),
+   IF(I71&lt;=30,"정상",IF(I71&lt;=90,"관리","장기미수"))
   )
  )
 )</f>
         <v>정상</v>
       </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11">
+      <c r="K71" s="11"/>
+      <c r="L71" s="11">
         <v>46037</v>
       </c>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q70" s="11"/>
-      <c r="R70" s="11"/>
-      <c r="S70" s="10"/>
-    </row>
-    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B71" s="10">
-        <f>IF(C71="","",COUNTA($C$2:C71))</f>
-        <v>70</v>
-      </c>
-      <c r="C71" s="11">
-        <v>46027</v>
-      </c>
-      <c r="D71" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v>B</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H71" s="4">
-        <v>26182000</v>
-      </c>
-      <c r="I71" s="6">
-        <f t="shared" ca="1" si="7"/>
-        <v>50</v>
-      </c>
-      <c r="J71" s="13" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v>관리</v>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
       <c r="M71" s="10"/>
       <c r="N71" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O71" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="P71" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q71" s="11">
-        <v>46036</v>
-      </c>
-      <c r="R71" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Q71" s="11"/>
+      <c r="R71" s="11"/>
       <c r="S71" s="10"/>
     </row>
     <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5146,38 +5151,43 @@
         <v>B</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H72" s="4">
-        <v>1100000</v>
+        <v>26182000</v>
       </c>
       <c r="I72" s="6">
-        <f t="shared" ref="I72:I75" ca="1" si="8">IF(C72="","",IF(L72="",TODAY()-C72,L72-C72))</f>
+        <f t="shared" ca="1" si="7"/>
         <v>50</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
-      <c r="K72" s="11">
-        <v>46112</v>
-      </c>
+      <c r="K72" s="11"/>
       <c r="L72" s="11"/>
       <c r="M72" s="10"/>
       <c r="N72" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q72" s="11"/>
-      <c r="R72" s="11"/>
+        <v>156</v>
+      </c>
+      <c r="Q72" s="11">
+        <v>46036</v>
+      </c>
+      <c r="R72" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="S72" s="10"/>
     </row>
     <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5186,52 +5196,45 @@
         <v>72</v>
       </c>
       <c r="C73" s="11">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="D73" s="10" t="str">
         <f t="shared" si="6"/>
         <v>B</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H73" s="4">
-        <v>799000</v>
+        <v>1100000</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" ca="1" si="8"/>
-        <v>17</v>
+        <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
+        <v>50</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11">
-        <v>46045</v>
-      </c>
+        <v>관리</v>
+      </c>
+      <c r="K73" s="11">
+        <v>46112</v>
+      </c>
+      <c r="L73" s="11"/>
       <c r="M73" s="10"/>
       <c r="N73" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O73" s="6" t="s">
-        <v>154</v>
+        <v>33</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q73" s="11">
-        <v>46036</v>
-      </c>
-      <c r="R73" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="Q73" s="11"/>
+      <c r="R73" s="11"/>
       <c r="S73" s="10"/>
     </row>
     <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5247,20 +5250,20 @@
         <v>B</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H74" s="4">
-        <v>3430000</v>
+        <v>799000</v>
       </c>
       <c r="I74" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J74" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5268,14 +5271,24 @@
       </c>
       <c r="K74" s="11"/>
       <c r="L74" s="11">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q74" s="11"/>
-      <c r="R74" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q74" s="11">
+        <v>46036</v>
+      </c>
+      <c r="R74" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="S74" s="10"/>
     </row>
     <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5284,34 +5297,36 @@
         <v>74</v>
       </c>
       <c r="C75" s="11">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="D75" s="10" t="str">
         <f t="shared" si="6"/>
         <v>B</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H75" s="4">
-        <v>528000</v>
+        <v>3430000</v>
       </c>
       <c r="I75" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="J75" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>관리</v>
+        <v>정상</v>
       </c>
       <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
+      <c r="L75" s="11">
+        <v>46052</v>
+      </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10" t="s">
         <v>33</v>
@@ -5326,52 +5341,40 @@
         <v>75</v>
       </c>
       <c r="C76" s="11">
-        <v>46034</v>
+        <v>46030</v>
       </c>
       <c r="D76" s="10" t="str">
-        <f t="shared" ref="D76:D139" si="9">IF(G76="","",IF(OR(G76="선급금",G76="중도금",G76="잔금"),"A",IF(G76="자재","B",IF(G76="특허료","C",""))))</f>
+        <f t="shared" si="6"/>
         <v>B</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H76" s="4">
-        <v>2200000</v>
+        <v>528000</v>
       </c>
       <c r="I76" s="6">
-        <f t="shared" ref="I76:I139" ca="1" si="10">IF(C76="","",IF(L76="",TODAY()-C76,L76-C76))</f>
-        <v>11</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>47</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K76" s="11"/>
-      <c r="L76" s="11">
-        <v>46045</v>
-      </c>
+      <c r="L76" s="11"/>
       <c r="M76" s="10"/>
       <c r="N76" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q76" s="11">
-        <v>46036</v>
-      </c>
-      <c r="R76" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Q76" s="11"/>
+      <c r="R76" s="11"/>
       <c r="S76" s="10"/>
     </row>
     <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5383,7 +5386,7 @@
         <v>46034</v>
       </c>
       <c r="D77" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="D77:D140" si="9">IF(G77="","",IF(OR(G77="선급금",G77="중도금",G77="잔금"),"A",IF(G77="자재","B",IF(G77="특허료","C",""))))</f>
         <v>B</v>
       </c>
       <c r="E77" s="6" t="s">
@@ -5396,10 +5399,10 @@
         <v>48</v>
       </c>
       <c r="H77" s="4">
-        <v>580000</v>
+        <v>2200000</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ref="I77:I140" ca="1" si="10">IF(C77="","",IF(L77="",TODAY()-C77,L77-C77))</f>
         <v>11</v>
       </c>
       <c r="J77" s="13" t="str">
@@ -5441,20 +5444,20 @@
         <v>B</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H78" s="4">
-        <v>3418000</v>
+        <v>580000</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J78" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5462,14 +5465,24 @@
       </c>
       <c r="K78" s="11"/>
       <c r="L78" s="11">
-        <v>46034</v>
+        <v>46045</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q78" s="11"/>
-      <c r="R78" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q78" s="11">
+        <v>46036</v>
+      </c>
+      <c r="R78" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="S78" s="10"/>
     </row>
     <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5478,23 +5491,23 @@
         <v>78</v>
       </c>
       <c r="C79" s="11">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="D79" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H79" s="4">
-        <v>496500</v>
+        <v>3418000</v>
       </c>
       <c r="I79" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -5506,7 +5519,7 @@
       </c>
       <c r="K79" s="11"/>
       <c r="L79" s="11">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10" t="s">
@@ -5522,34 +5535,36 @@
         <v>79</v>
       </c>
       <c r="C80" s="11">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="D80" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H80" s="4">
-        <v>280000</v>
+        <v>496500</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J80" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
+      <c r="L80" s="11">
+        <v>46036</v>
+      </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10" t="s">
         <v>33</v>
@@ -5571,29 +5586,27 @@
         <v>B</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H81" s="4">
-        <v>380000</v>
+        <v>280000</v>
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K81" s="11"/>
-      <c r="L81" s="11">
-        <v>46038</v>
-      </c>
+      <c r="L81" s="11"/>
       <c r="M81" s="10"/>
       <c r="N81" s="10" t="s">
         <v>33</v>
@@ -5608,50 +5621,42 @@
         <v>81</v>
       </c>
       <c r="C82" s="11">
-        <v>46042</v>
+        <v>46038</v>
       </c>
       <c r="D82" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H82" s="4">
-        <v>36816000</v>
+        <v>380000</v>
       </c>
       <c r="I82" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J82" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
+      <c r="L82" s="11">
+        <v>46038</v>
+      </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q82" s="11">
-        <v>46036</v>
-      </c>
-      <c r="R82" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Q82" s="11"/>
+      <c r="R82" s="11"/>
       <c r="S82" s="10"/>
     </row>
     <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5676,7 +5681,7 @@
         <v>48</v>
       </c>
       <c r="H83" s="4">
-        <v>7390000</v>
+        <v>36816000</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -5712,7 +5717,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="11">
-        <v>46044</v>
+        <v>46042</v>
       </c>
       <c r="D84" s="10" t="str">
         <f t="shared" si="9"/>
@@ -5728,11 +5733,11 @@
         <v>48</v>
       </c>
       <c r="H84" s="4">
-        <v>56770000</v>
+        <v>7390000</v>
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5771,16 +5776,16 @@
         <v>B</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H85" s="4">
-        <v>321000</v>
+        <v>56770000</v>
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -5794,10 +5799,20 @@
       <c r="L85" s="11"/>
       <c r="M85" s="10"/>
       <c r="N85" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q85" s="11"/>
-      <c r="R85" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q85" s="11">
+        <v>46036</v>
+      </c>
+      <c r="R85" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="S85" s="10"/>
     </row>
     <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5806,27 +5821,27 @@
         <v>85</v>
       </c>
       <c r="C86" s="11">
-        <v>46048</v>
+        <v>46044</v>
       </c>
       <c r="D86" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H86" s="4">
-        <v>4784000</v>
+        <v>321000</v>
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5836,20 +5851,10 @@
       <c r="L86" s="11"/>
       <c r="M86" s="10"/>
       <c r="N86" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q86" s="11">
-        <v>46036</v>
-      </c>
-      <c r="R86" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Q86" s="11"/>
+      <c r="R86" s="11"/>
       <c r="S86" s="10"/>
     </row>
     <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5865,35 +5870,43 @@
         <v>B</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H87" s="4">
-        <v>15356500</v>
+        <v>4784000</v>
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K87" s="11"/>
-      <c r="L87" s="11">
-        <v>46063</v>
-      </c>
+      <c r="L87" s="11"/>
       <c r="M87" s="10"/>
       <c r="N87" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q87" s="11"/>
-      <c r="R87" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q87" s="11">
+        <v>46036</v>
+      </c>
+      <c r="R87" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="S87" s="10"/>
     </row>
     <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5902,50 +5915,42 @@
         <v>87</v>
       </c>
       <c r="C88" s="11">
-        <v>46051</v>
+        <v>46048</v>
       </c>
       <c r="D88" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H88" s="4">
-        <v>17250000</v>
+        <v>15356500</v>
       </c>
       <c r="I88" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J88" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K88" s="11"/>
-      <c r="L88" s="11"/>
+      <c r="L88" s="11">
+        <v>46063</v>
+      </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q88" s="11">
-        <v>46036</v>
-      </c>
-      <c r="R88" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="Q88" s="11"/>
+      <c r="R88" s="11"/>
       <c r="S88" s="10"/>
     </row>
     <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -5970,7 +5975,7 @@
         <v>48</v>
       </c>
       <c r="H89" s="4">
-        <v>5750000</v>
+        <v>17250000</v>
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -6006,42 +6011,50 @@
         <v>89</v>
       </c>
       <c r="C90" s="11">
-        <v>46055</v>
+        <v>46051</v>
       </c>
       <c r="D90" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H90" s="4">
-        <v>231000</v>
+        <v>5750000</v>
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K90" s="11"/>
-      <c r="L90" s="11">
-        <v>46055</v>
-      </c>
+      <c r="L90" s="11"/>
       <c r="M90" s="10"/>
       <c r="N90" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q90" s="11"/>
-      <c r="R90" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q90" s="11">
+        <v>46036</v>
+      </c>
+      <c r="R90" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="S90" s="10"/>
     </row>
     <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
@@ -6057,27 +6070,29 @@
         <v>B</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G91" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H91" s="4">
-        <v>219000</v>
+        <v>231000</v>
       </c>
       <c r="I91" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J91" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K91" s="11"/>
-      <c r="L91" s="11"/>
+      <c r="L91" s="11">
+        <v>46055</v>
+      </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10" t="s">
         <v>33</v>
@@ -6092,36 +6107,34 @@
         <v>91</v>
       </c>
       <c r="C92" s="11">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="D92" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H92" s="4">
-        <v>432000</v>
+        <v>219000</v>
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K92" s="11"/>
-      <c r="L92" s="11">
-        <v>46057</v>
-      </c>
+      <c r="L92" s="11"/>
       <c r="M92" s="10"/>
       <c r="N92" s="10" t="s">
         <v>33</v>
@@ -6136,27 +6149,27 @@
         <v>92</v>
       </c>
       <c r="C93" s="11">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="D93" s="10" t="str">
         <f t="shared" si="9"/>
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="H93" s="4">
-        <v>478000</v>
+        <v>432000</v>
       </c>
       <c r="I93" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J93" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6164,7 +6177,7 @@
       </c>
       <c r="K93" s="11"/>
       <c r="L93" s="11">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10" t="s">
@@ -6180,34 +6193,36 @@
         <v>93</v>
       </c>
       <c r="C94" s="11">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="D94" s="10" t="str">
         <f t="shared" si="9"/>
         <v>C</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>140</v>
       </c>
       <c r="H94" s="4">
-        <v>1206700</v>
+        <v>478000</v>
       </c>
       <c r="I94" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J94" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K94" s="11"/>
-      <c r="L94" s="11"/>
+      <c r="L94" s="11">
+        <v>46059</v>
+      </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10" t="s">
         <v>33</v>
@@ -6221,28 +6236,28 @@
         <f>IF(C95="","",COUNTA($C$2:C95))</f>
         <v>94</v>
       </c>
-      <c r="C95" s="11" t="s">
-        <v>160</v>
+      <c r="C95" s="11">
+        <v>46058</v>
       </c>
       <c r="D95" s="10" t="str">
         <f t="shared" si="9"/>
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="H95" s="4">
-        <v>2627900</v>
+        <v>1206700</v>
       </c>
       <c r="I95" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J95" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6271,29 +6286,27 @@
         <v>B</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H96" s="4">
-        <v>1210000</v>
+        <v>2627900</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K96" s="11"/>
-      <c r="L96" s="11">
-        <v>46062</v>
-      </c>
+      <c r="L96" s="11"/>
       <c r="M96" s="10"/>
       <c r="N96" s="10" t="s">
         <v>33</v>
@@ -6308,34 +6321,36 @@
         <v>96</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D97" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="E97" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="F97" s="23" t="s">
-        <v>111</v>
+      <c r="E97" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H97" s="4">
-        <v>216000</v>
+        <v>1210000</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J97" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K97" s="11"/>
-      <c r="L97" s="11"/>
+      <c r="L97" s="11">
+        <v>46062</v>
+      </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10" t="s">
         <v>33</v>
@@ -6349,24 +6364,24 @@
         <f>IF(C98="","",COUNTA($C$2:C98))</f>
         <v>97</v>
       </c>
-      <c r="C98" s="11">
-        <v>46063</v>
+      <c r="C98" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="D98" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="F98" s="23" t="s">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>48</v>
       </c>
       <c r="H98" s="4">
-        <v>154300</v>
+        <v>216000</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -6392,30 +6407,31 @@
         <v>98</v>
       </c>
       <c r="C99" s="11">
-        <v>46027</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="E99" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="F99" s="24" t="s">
-        <v>169</v>
+        <v>46063</v>
+      </c>
+      <c r="D99" s="10" t="str">
+        <f t="shared" si="9"/>
+        <v>B</v>
+      </c>
+      <c r="E99" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="F99" s="23" t="s">
+        <v>167</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>173</v>
+        <v>48</v>
       </c>
       <c r="H99" s="4">
-        <v>16130000</v>
+        <v>154300</v>
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>관리</v>
+        <v>정상</v>
       </c>
       <c r="K99" s="11"/>
       <c r="L99" s="11"/>
@@ -6433,35 +6449,33 @@
         <v>99</v>
       </c>
       <c r="C100" s="11">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>172</v>
       </c>
       <c r="E100" s="24" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="F100" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G100" s="6" t="s">
         <v>173</v>
       </c>
       <c r="H100" s="4">
-        <v>-883400</v>
+        <v>16130000</v>
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K100" s="11"/>
-      <c r="L100" s="11">
-        <v>46052</v>
-      </c>
+      <c r="L100" s="11"/>
       <c r="M100" s="10"/>
       <c r="N100" s="10" t="s">
         <v>33</v>
@@ -6476,27 +6490,26 @@
         <v>100</v>
       </c>
       <c r="C101" s="11">
-        <v>46052</v>
-      </c>
-      <c r="D101" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>175</v>
+        <v>46023</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E101" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F101" s="24" t="s">
+        <v>171</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H101" s="4">
-        <v>-3943480</v>
+        <v>-883400</v>
       </c>
       <c r="I101" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="J101" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6504,7 +6517,7 @@
       </c>
       <c r="K101" s="11"/>
       <c r="L101" s="11">
-        <v>46064</v>
+        <v>46052</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10" t="s">
@@ -6515,42 +6528,42 @@
       <c r="S101" s="10"/>
     </row>
     <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B102" s="26">
+      <c r="B102" s="10">
         <f>IF(C102="","",COUNTA($C$2:C102))</f>
         <v>101</v>
       </c>
-      <c r="C102" s="27">
-        <v>46038</v>
-      </c>
-      <c r="D102" s="26" t="str">
+      <c r="C102" s="11">
+        <v>46052</v>
+      </c>
+      <c r="D102" s="10" t="str">
         <f t="shared" si="9"/>
-        <v>A</v>
-      </c>
-      <c r="E102" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="F102" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="G102" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="H102" s="29">
-        <v>59635000</v>
-      </c>
-      <c r="I102" s="28">
+        <v>B</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H102" s="4">
+        <v>-3943480</v>
+      </c>
+      <c r="I102" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
-      </c>
-      <c r="J102" s="30" t="str">
+        <v>12</v>
+      </c>
+      <c r="J102" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
-      <c r="K102" s="27"/>
-      <c r="L102" s="27">
-        <v>46066</v>
-      </c>
-      <c r="M102" s="26"/>
+      <c r="K102" s="11"/>
+      <c r="L102" s="11">
+        <v>46064</v>
+      </c>
+      <c r="M102" s="10"/>
       <c r="N102" s="10" t="s">
         <v>33</v>
       </c>
@@ -6559,40 +6572,42 @@
       <c r="S102" s="10"/>
     </row>
     <row r="103" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B103" s="10">
+      <c r="B103" s="26">
         <f>IF(C103="","",COUNTA($C$2:C103))</f>
         <v>102</v>
       </c>
-      <c r="C103" s="11">
-        <v>46064</v>
-      </c>
-      <c r="D103" s="10" t="str">
+      <c r="C103" s="27">
+        <v>46038</v>
+      </c>
+      <c r="D103" s="26" t="str">
         <f t="shared" si="9"/>
-        <v>B</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F103" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="H103" s="25">
-        <v>1138000</v>
-      </c>
-      <c r="I103" s="6">
+        <v>A</v>
+      </c>
+      <c r="E103" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F103" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G103" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H103" s="29">
+        <v>59635000</v>
+      </c>
+      <c r="I103" s="28">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
-      </c>
-      <c r="J103" s="13" t="str">
+        <v>28</v>
+      </c>
+      <c r="J103" s="30" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
-      <c r="K103" s="11"/>
-      <c r="L103" s="11"/>
-      <c r="M103" s="10"/>
+      <c r="K103" s="27"/>
+      <c r="L103" s="27">
+        <v>46066</v>
+      </c>
+      <c r="M103" s="26"/>
       <c r="N103" s="10" t="s">
         <v>33</v>
       </c>
@@ -6616,13 +6631,13 @@
         <v>110</v>
       </c>
       <c r="F104" s="23" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>181</v>
       </c>
       <c r="H104" s="25">
-        <v>11632500</v>
+        <v>1138000</v>
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -6648,26 +6663,27 @@
         <v>104</v>
       </c>
       <c r="C105" s="11">
-        <v>46065</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E105" s="23" t="s">
-        <v>24</v>
+        <v>46064</v>
+      </c>
+      <c r="D105" s="10" t="str">
+        <f t="shared" si="9"/>
+        <v>B</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="F105" s="23" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>181</v>
       </c>
       <c r="H105" s="25">
-        <v>7390000</v>
+        <v>11632500</v>
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6677,10 +6693,7 @@
       <c r="L105" s="11"/>
       <c r="M105" s="10"/>
       <c r="N105" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="P105" s="6" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="Q105" s="11"/>
       <c r="R105" s="11"/>
@@ -6698,16 +6711,16 @@
         <v>182</v>
       </c>
       <c r="E106" s="23" t="s">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="F106" s="23" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>181</v>
       </c>
       <c r="H106" s="25">
-        <v>651400</v>
+        <v>7390000</v>
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -6721,7 +6734,10 @@
       <c r="L106" s="11"/>
       <c r="M106" s="10"/>
       <c r="N106" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="P106" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="Q106" s="11"/>
       <c r="R106" s="11"/>
@@ -6739,16 +6755,16 @@
         <v>182</v>
       </c>
       <c r="E107" s="23" t="s">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="F107" s="23" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="G107" s="6" t="s">
         <v>181</v>
       </c>
       <c r="H107" s="25">
-        <v>1997773</v>
+        <v>651400</v>
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -6774,26 +6790,26 @@
         <v>107</v>
       </c>
       <c r="C108" s="11">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="E108" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F108" s="31" t="s">
-        <v>186</v>
+        <v>182</v>
+      </c>
+      <c r="E108" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F108" s="23" t="s">
+        <v>158</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H108" s="33">
-        <v>11000000</v>
+        <v>181</v>
+      </c>
+      <c r="H108" s="25">
+        <v>1997773</v>
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6815,26 +6831,26 @@
         <v>108</v>
       </c>
       <c r="C109" s="11">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E109" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="F109" s="23" t="s">
-        <v>108</v>
+        <v>185</v>
+      </c>
+      <c r="E109" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F109" s="31" t="s">
+        <v>186</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H109" s="34">
-        <v>35304000</v>
+        <v>188</v>
+      </c>
+      <c r="H109" s="33">
+        <v>11000000</v>
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6844,10 +6860,7 @@
       <c r="L109" s="11"/>
       <c r="M109" s="10"/>
       <c r="N109" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="P109" s="6" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="Q109" s="11"/>
       <c r="R109" s="11"/>
@@ -6858,40 +6871,40 @@
         <f>IF(C110="","",COUNTA($C$2:C110))</f>
         <v>109</v>
       </c>
-      <c r="C110" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="D110" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
-      </c>
-      <c r="E110" s="36" t="s">
-        <v>190</v>
+      <c r="C110" s="11">
+        <v>46067</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E110" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="F110" s="23" t="s">
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H110" s="25">
-        <v>5436700</v>
+        <v>189</v>
+      </c>
+      <c r="H110" s="34">
+        <v>35304000</v>
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K110" s="11"/>
-      <c r="L110" s="11">
-        <v>46073</v>
-      </c>
+      <c r="L110" s="11"/>
       <c r="M110" s="10"/>
       <c r="N110" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="P110" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="Q110" s="11"/>
       <c r="R110" s="11"/>
@@ -6909,34 +6922,33 @@
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="E111" s="23" t="s">
-        <v>24</v>
+      <c r="E111" s="36" t="s">
+        <v>190</v>
       </c>
       <c r="F111" s="23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G111" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H111" s="25">
-        <v>37600000</v>
+        <v>5436700</v>
       </c>
       <c r="I111" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J111" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K111" s="11"/>
-      <c r="L111" s="11"/>
+      <c r="L111" s="11">
+        <v>46073</v>
+      </c>
       <c r="M111" s="10"/>
       <c r="N111" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="P111" s="6" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="Q111" s="11"/>
       <c r="R111" s="11"/>
@@ -6948,39 +6960,40 @@
         <v>111</v>
       </c>
       <c r="C112" s="35" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D112" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E112" s="23" t="s">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="F112" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G112" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H112" s="25">
-        <v>2706000</v>
+        <v>37600000</v>
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K112" s="11"/>
-      <c r="L112" s="11">
-        <v>46076</v>
-      </c>
+      <c r="L112" s="11"/>
       <c r="M112" s="10"/>
       <c r="N112" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="P112" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="Q112" s="11"/>
       <c r="R112" s="11"/>
@@ -6991,41 +7004,40 @@
         <f>IF(C113="","",COUNTA($C$2:C113))</f>
         <v>112</v>
       </c>
-      <c r="C113" s="39" t="s">
+      <c r="C113" s="35" t="s">
         <v>196</v>
       </c>
       <c r="D113" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="E113" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="F113" s="38" t="s">
-        <v>108</v>
+      <c r="E113" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="F113" s="23" t="s">
+        <v>194</v>
       </c>
       <c r="G113" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H113" s="40">
-        <v>11500000</v>
+      <c r="H113" s="25">
+        <v>2706000</v>
       </c>
       <c r="I113" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K113" s="11"/>
-      <c r="L113" s="11"/>
+      <c r="L113" s="11">
+        <v>46076</v>
+      </c>
       <c r="M113" s="10"/>
       <c r="N113" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="P113" s="6" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="Q113" s="11"/>
       <c r="R113" s="11"/>
@@ -7053,22 +7065,14 @@
         <v>176</v>
       </c>
       <c r="H114" s="40">
-        <v>3438000</v>
+        <v>11500000</v>
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
         <v>1</v>
       </c>
       <c r="J114" s="13" t="str">
-        <f t="shared" ref="J114:J130" ca="1" si="11">IF(I114="","",
- IF(G114="선급금",
-   IF(I114&lt;=20,"정상",IF(I114&lt;=90,"관리","장기미수")),
- IF(G114="자재",
-   IF(I114&lt;=40,"정상",IF(I114&lt;=90,"관리","장기미수")),
-   IF(I114&lt;=30,"정상",IF(I114&lt;=90,"관리","장기미수"))
-  )
- )
-)</f>
+        <f t="shared" ca="1" si="5"/>
         <v>정상</v>
       </c>
       <c r="K114" s="11"/>
@@ -7090,65 +7094,91 @@
         <v>114</v>
       </c>
       <c r="C115" s="39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D115" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
       <c r="E115" s="37" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="F115" s="38" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H115" s="40">
-        <v>502300</v>
+        <v>3438000</v>
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" ref="J115:J131" ca="1" si="11">IF(I115="","",
+ IF(G115="선급금",
+   IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
+ IF(G115="자재",
+   IF(I115&lt;=40,"정상",IF(I115&lt;=90,"관리","장기미수")),
+   IF(I115&lt;=30,"정상",IF(I115&lt;=90,"관리","장기미수"))
+  )
+ )
+)</f>
         <v>정상</v>
       </c>
       <c r="K115" s="11"/>
       <c r="L115" s="11"/>
       <c r="M115" s="10"/>
       <c r="N115" s="10" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="P115" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="Q115" s="11"/>
       <c r="R115" s="11"/>
       <c r="S115" s="10"/>
     </row>
     <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B116" s="10" t="str">
+      <c r="B116" s="10">
         <f>IF(C116="","",COUNTA($C$2:C116))</f>
-        <v/>
-      </c>
-      <c r="C116" s="11"/>
+        <v>115</v>
+      </c>
+      <c r="C116" s="39" t="s">
+        <v>197</v>
+      </c>
       <c r="D116" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H116" s="4"/>
-      <c r="I116" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E116" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="F116" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H116" s="40">
+        <v>502300</v>
+      </c>
+      <c r="I116" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J116" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K116" s="11"/>
       <c r="L116" s="11"/>
       <c r="M116" s="10"/>
-      <c r="N116" s="10"/>
+      <c r="N116" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q116" s="11"/>
       <c r="R116" s="11"/>
       <c r="S116" s="10"/>
@@ -7546,7 +7576,10 @@
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="J131" s="13"/>
+      <c r="J131" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
       <c r="K131" s="11"/>
       <c r="L131" s="11"/>
       <c r="M131" s="10"/>
@@ -7754,12 +7787,12 @@
       </c>
       <c r="C140" s="11"/>
       <c r="D140" s="10" t="str">
-        <f t="shared" ref="D140:D203" si="12">IF(G140="","",IF(OR(G140="선급금",G140="중도금",G140="잔금"),"A",IF(G140="자재","B",IF(G140="특허료","C",""))))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="H140" s="4"/>
       <c r="I140" s="6" t="str">
-        <f t="shared" ref="I140:I203" ca="1" si="13">IF(C140="","",IF(L140="",TODAY()-C140,L140-C140))</f>
+        <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
       <c r="J140" s="13"/>
@@ -7778,12 +7811,12 @@
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D141:D204" si="12">IF(G141="","",IF(OR(G141="선급금",G141="중도금",G141="잔금"),"A",IF(G141="자재","B",IF(G141="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H141" s="4"/>
       <c r="I141" s="6" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ref="I141:I204" ca="1" si="13">IF(C141="","",IF(L141="",TODAY()-C141,L141-C141))</f>
         <v/>
       </c>
       <c r="J141" s="13"/>
@@ -9290,12 +9323,12 @@
       </c>
       <c r="C204" s="11"/>
       <c r="D204" s="10" t="str">
-        <f t="shared" ref="D204:D267" si="14">IF(G204="","",IF(OR(G204="선급금",G204="중도금",G204="잔금"),"A",IF(G204="자재","B",IF(G204="특허료","C",""))))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" s="6" t="str">
-        <f t="shared" ref="I204:I267" ca="1" si="15">IF(C204="","",IF(L204="",TODAY()-C204,L204-C204))</f>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="J204" s="13"/>
@@ -9314,12 +9347,12 @@
       </c>
       <c r="C205" s="11"/>
       <c r="D205" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="D205:D268" si="14">IF(G205="","",IF(OR(G205="선급금",G205="중도금",G205="잔금"),"A",IF(G205="자재","B",IF(G205="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H205" s="4"/>
       <c r="I205" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ref="I205:I268" ca="1" si="15">IF(C205="","",IF(L205="",TODAY()-C205,L205-C205))</f>
         <v/>
       </c>
       <c r="J205" s="13"/>
@@ -9476,7 +9509,10 @@
       <c r="S211" s="10"/>
     </row>
     <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B212" s="10"/>
+      <c r="B212" s="10" t="str">
+        <f>IF(C212="","",COUNTA($C$2:C212))</f>
+        <v/>
+      </c>
       <c r="C212" s="11"/>
       <c r="D212" s="10" t="str">
         <f t="shared" si="14"/>
@@ -10655,12 +10691,12 @@
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
       <c r="D268" s="10" t="str">
-        <f t="shared" ref="D268:D331" si="16">IF(G268="","",IF(OR(G268="선급금",G268="중도금",G268="잔금"),"A",IF(G268="자재","B",IF(G268="특허료","C",""))))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" s="6" t="str">
-        <f t="shared" ref="I268:I331" ca="1" si="17">IF(C268="","",IF(L268="",TODAY()-C268,L268-C268))</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="J268" s="13"/>
@@ -10676,12 +10712,12 @@
       <c r="B269" s="10"/>
       <c r="C269" s="11"/>
       <c r="D269" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="D269:D332" si="16">IF(G269="","",IF(OR(G269="선급금",G269="중도금",G269="잔금"),"A",IF(G269="자재","B",IF(G269="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H269" s="4"/>
       <c r="I269" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ref="I269:I332" ca="1" si="17">IF(C269="","",IF(L269="",TODAY()-C269,L269-C269))</f>
         <v/>
       </c>
       <c r="J269" s="13"/>
@@ -11999,12 +12035,12 @@
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
-        <f t="shared" ref="D332:D395" si="18">IF(G332="","",IF(OR(G332="선급금",G332="중도금",G332="잔금"),"A",IF(G332="자재","B",IF(G332="특허료","C",""))))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="6" t="str">
-        <f t="shared" ref="I332:I395" ca="1" si="19">IF(C332="","",IF(L332="",TODAY()-C332,L332-C332))</f>
+        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="J332" s="13"/>
@@ -12020,12 +12056,12 @@
       <c r="B333" s="10"/>
       <c r="C333" s="11"/>
       <c r="D333" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="D333:D396" si="18">IF(G333="","",IF(OR(G333="선급금",G333="중도금",G333="잔금"),"A",IF(G333="자재","B",IF(G333="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H333" s="4"/>
       <c r="I333" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ref="I333:I396" ca="1" si="19">IF(C333="","",IF(L333="",TODAY()-C333,L333-C333))</f>
         <v/>
       </c>
       <c r="J333" s="13"/>
@@ -13343,12 +13379,12 @@
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
-        <f t="shared" ref="D396:D408" si="20">IF(G396="","",IF(OR(G396="선급금",G396="중도금",G396="잔금"),"A",IF(G396="자재","B",IF(G396="특허료","C",""))))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H396" s="4"/>
       <c r="I396" s="6" t="str">
-        <f t="shared" ref="I396:I406" ca="1" si="21">IF(C396="","",IF(L396="",TODAY()-C396,L396-C396))</f>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J396" s="13"/>
@@ -13364,12 +13400,12 @@
       <c r="B397" s="10"/>
       <c r="C397" s="11"/>
       <c r="D397" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D397:D409" si="20">IF(G397="","",IF(OR(G397="선급금",G397="중도금",G397="잔금"),"A",IF(G397="자재","B",IF(G397="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H397" s="4"/>
       <c r="I397" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ref="I397:I407" ca="1" si="21">IF(C397="","",IF(L397="",TODAY()-C397,L397-C397))</f>
         <v/>
       </c>
       <c r="J397" s="13"/>
@@ -13486,21 +13522,26 @@
       <c r="R402" s="11"/>
       <c r="S402" s="10"/>
     </row>
-    <row r="403" spans="2:19">
+    <row r="403" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B403" s="10"/>
       <c r="C403" s="11"/>
-      <c r="D403" s="1" t="str">
+      <c r="D403" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I403" s="1" t="str">
+      <c r="H403" s="4"/>
+      <c r="I403" s="6" t="str">
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
+      <c r="J403" s="13"/>
       <c r="K403" s="11"/>
       <c r="L403" s="11"/>
+      <c r="M403" s="10"/>
+      <c r="N403" s="10"/>
       <c r="Q403" s="11"/>
       <c r="R403" s="11"/>
+      <c r="S403" s="10"/>
     </row>
     <row r="404" spans="2:19">
       <c r="B404" s="10"/>
@@ -13529,6 +13570,8 @@
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
+      <c r="K405" s="11"/>
+      <c r="L405" s="11"/>
       <c r="Q405" s="11"/>
       <c r="R405" s="11"/>
     </row>
@@ -13553,6 +13596,10 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
+      <c r="I407" s="1" t="str">
+        <f t="shared" ca="1" si="21"/>
+        <v/>
+      </c>
       <c r="Q407" s="11"/>
       <c r="R407" s="11"/>
     </row>
@@ -13566,10 +13613,20 @@
       <c r="Q408" s="11"/>
       <c r="R408" s="11"/>
     </row>
+    <row r="409" spans="2:19">
+      <c r="B409" s="10"/>
+      <c r="C409" s="11"/>
+      <c r="D409" s="1" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="Q409" s="11"/>
+      <c r="R409" s="11"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S408"/>
+  <autoFilter ref="A1:S409"/>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="E3 F56:F59">
+  <conditionalFormatting sqref="E3 F57:F60">
     <cfRule type="expression" dxfId="18" priority="33">
       <formula>$J3="잔금"</formula>
     </cfRule>
@@ -13594,84 +13651,84 @@
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E97:E98">
+  <conditionalFormatting sqref="E98:E99">
     <cfRule type="expression" dxfId="13" priority="15">
-      <formula>$J97="잔금"</formula>
+      <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F97:F98">
+  <conditionalFormatting sqref="F98:F99">
     <cfRule type="expression" dxfId="12" priority="14">
-      <formula>$J97="잔금"</formula>
+      <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F103:F104">
+  <conditionalFormatting sqref="F104:F105">
     <cfRule type="expression" dxfId="11" priority="12">
-      <formula>$J103="잔금"</formula>
+      <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H103:H104">
+  <conditionalFormatting sqref="H104:H105">
     <cfRule type="expression" dxfId="10" priority="11">
-      <formula>$J103="잔금"</formula>
+      <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E105:E107">
+  <conditionalFormatting sqref="E106:E108">
     <cfRule type="expression" dxfId="9" priority="10">
-      <formula>$J105="잔금"</formula>
+      <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F105:F107">
+  <conditionalFormatting sqref="F106:F108">
     <cfRule type="expression" dxfId="8" priority="9">
-      <formula>$J105="잔금"</formula>
+      <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H105:H107">
+  <conditionalFormatting sqref="H106:H108">
     <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$J105="잔금"</formula>
+      <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E109">
+  <conditionalFormatting sqref="E110">
     <cfRule type="expression" dxfId="6" priority="7">
-      <formula>$J109="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F109">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>$J109="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E110:E112">
-    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F110 F112">
-    <cfRule type="expression" dxfId="3" priority="4">
+  <conditionalFormatting sqref="F110">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F111">
-    <cfRule type="expression" dxfId="2" priority="3">
+  <conditionalFormatting sqref="E111:E113">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H110:H112">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$J110="잔금"</formula>
+  <conditionalFormatting sqref="F111 F113">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C110:C112">
+  <conditionalFormatting sqref="F112">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$J112="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H111:H113">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C111:C113">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J110="잔금"</formula>
+      <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D408">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D409">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G70">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N115">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N116">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -6775,7 +6775,9 @@
         <v>정상</v>
       </c>
       <c r="K107" s="11"/>
-      <c r="L107" s="11"/>
+      <c r="L107" s="11">
+        <v>46077</v>
+      </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10" t="s">
         <v>33</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -6775,9 +6775,7 @@
         <v>정상</v>
       </c>
       <c r="K107" s="11"/>
-      <c r="L107" s="11">
-        <v>46077</v>
-      </c>
+      <c r="L107" s="11"/>
       <c r="M107" s="10"/>
       <c r="N107" s="10" t="s">
         <v>33</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="203">
   <si>
     <t>순번</t>
   </si>
@@ -727,6 +727,10 @@
   <si>
     <t>N</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>본사 사무실</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1076,7 +1080,52 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1769,7 +1818,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -1833,7 +1882,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -1892,7 +1941,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1990,7 +2039,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2046,7 +2095,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2095,7 +2144,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2146,7 +2195,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2198,7 +2247,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2251,7 +2300,9 @@
       <c r="K11" s="11">
         <v>46066</v>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="11">
+        <v>46077</v>
+      </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10" t="s">
         <v>33</v>
@@ -2335,7 +2386,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2391,7 +2442,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2440,7 +2491,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2489,7 +2540,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2536,7 +2587,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2583,7 +2634,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2630,7 +2681,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2677,7 +2728,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2724,7 +2775,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2773,7 +2824,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2822,7 +2873,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2871,7 +2922,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2920,7 +2971,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2969,7 +3020,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3018,7 +3069,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3067,7 +3118,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3116,7 +3167,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3165,7 +3216,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3214,7 +3265,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3263,7 +3314,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3312,7 +3363,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3361,7 +3412,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3410,7 +3461,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3459,7 +3510,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3504,7 +3555,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3558,7 +3609,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3614,7 +3665,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3667,7 +3718,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3714,7 +3765,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3768,7 +3819,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3873,7 +3924,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3924,7 +3975,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3968,7 +4019,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4012,7 +4063,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4059,7 +4110,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4106,7 +4157,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-268</v>
+        <v>-267</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4148,7 +4199,7 @@
       </c>
       <c r="I50" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J50" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4195,7 +4246,7 @@
       </c>
       <c r="I51" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J51" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4239,7 +4290,7 @@
       </c>
       <c r="I52" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J52" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4283,7 +4334,7 @@
       </c>
       <c r="I53" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J53" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4330,7 +4381,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4426,7 +4477,7 @@
       </c>
       <c r="I56" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J56" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4473,7 +4524,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4520,7 +4571,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4567,7 +4618,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4614,7 +4665,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -4761,7 +4812,7 @@
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J63" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4805,7 +4856,7 @@
       </c>
       <c r="I64" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J64" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4895,7 +4946,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4939,7 +4990,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4981,7 +5032,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5023,7 +5074,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5164,7 +5215,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5216,7 +5267,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5361,7 +5412,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5599,7 +5650,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5685,7 +5736,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5737,7 +5788,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5789,7 +5840,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5841,7 +5892,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5883,7 +5934,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5979,7 +6030,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6031,7 +6082,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6127,7 +6178,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6257,7 +6308,7 @@
       </c>
       <c r="I95" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J95" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6299,7 +6350,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6385,7 +6436,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6427,7 +6478,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6468,7 +6519,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6641,7 +6692,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6683,7 +6734,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6724,7 +6775,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6768,7 +6819,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6809,7 +6860,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6850,7 +6901,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6891,7 +6942,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6980,7 +7031,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7069,7 +7120,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7114,7 +7165,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J131" ca="1" si="11">IF(I115="","",
@@ -7167,7 +7218,7 @@
       </c>
       <c r="I116" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7184,28 +7235,43 @@
       <c r="S116" s="10"/>
     </row>
     <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B117" s="10" t="str">
+      <c r="B117" s="10">
         <f>IF(C117="","",COUNTA($C$2:C117))</f>
-        <v/>
-      </c>
-      <c r="C117" s="11"/>
+        <v>116</v>
+      </c>
+      <c r="C117" s="39">
+        <v>46077</v>
+      </c>
       <c r="D117" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H117" s="4"/>
-      <c r="I117" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E117" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F117" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H117" s="4">
+        <v>106200</v>
+      </c>
+      <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K117" s="11"/>
       <c r="L117" s="11"/>
       <c r="M117" s="10"/>
-      <c r="N117" s="10"/>
+      <c r="N117" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q117" s="11"/>
       <c r="R117" s="11"/>
       <c r="S117" s="10"/>
@@ -13627,98 +13693,108 @@
   <autoFilter ref="A1:S409"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="18" priority="33">
+    <cfRule type="expression" dxfId="21" priority="35">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="17" priority="32">
+    <cfRule type="expression" dxfId="20" priority="34">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="16" priority="31">
+    <cfRule type="expression" dxfId="19" priority="33">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="15" priority="30">
+    <cfRule type="expression" dxfId="18" priority="32">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="14" priority="25">
+    <cfRule type="expression" dxfId="17" priority="27">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="16" priority="17">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="12" priority="14">
+    <cfRule type="expression" dxfId="15" priority="16">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="14" priority="14">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="13" priority="13">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E117">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J117="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F117">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J111="잔금"</formula>
+      <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -13728,7 +13804,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N116">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N117">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="206">
   <si>
     <t>순번</t>
   </si>
@@ -732,16 +732,27 @@
     <t>본사 사무실</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
+  <si>
+    <t>삼정ING건설</t>
+  </si>
+  <si>
+    <t>삼익세라믹1,2차</t>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="181" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -919,7 +930,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -952,8 +963,11 @@
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1065,8 +1079,20 @@
     <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="13">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
     <cellStyle name="백분율 2" xfId="2"/>
     <cellStyle name="백분율 3" xfId="10"/>
@@ -1074,28 +1100,14 @@
     <cellStyle name="쉼표 [0] 2" xfId="4"/>
     <cellStyle name="쉼표 [0] 3" xfId="9"/>
     <cellStyle name="쉼표 [0] 4" xfId="11"/>
+    <cellStyle name="쉼표 [0] 5" xfId="12"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 118 2 7 16" xfId="5"/>
     <cellStyle name="표준 125" xfId="6"/>
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -1818,7 +1830,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -1882,7 +1894,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -1941,7 +1953,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2039,7 +2051,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2095,7 +2107,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2144,7 +2156,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2195,7 +2207,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2247,7 +2259,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2386,7 +2398,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2442,7 +2454,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2491,7 +2503,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2540,7 +2552,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2587,7 +2599,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2634,7 +2646,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2681,7 +2693,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2728,7 +2740,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2775,7 +2787,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2824,7 +2836,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2873,7 +2885,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2922,7 +2934,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2971,7 +2983,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3020,7 +3032,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3069,7 +3081,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3118,7 +3130,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3167,7 +3179,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3216,7 +3228,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3265,7 +3277,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3314,7 +3326,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3363,7 +3375,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3412,7 +3424,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3461,7 +3473,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3510,7 +3522,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3555,7 +3567,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3609,7 +3621,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3665,7 +3677,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3718,7 +3730,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3765,7 +3777,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3819,7 +3831,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3924,7 +3936,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3975,7 +3987,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4019,7 +4031,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4063,7 +4075,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4110,7 +4122,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4157,7 +4169,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-267</v>
+        <v>-266</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4199,7 +4211,7 @@
       </c>
       <c r="I50" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J50" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4255,7 +4267,9 @@
       <c r="K51" s="11">
         <v>46080</v>
       </c>
-      <c r="L51" s="11"/>
+      <c r="L51" s="11">
+        <v>46078</v>
+      </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10" t="s">
         <v>33</v>
@@ -4299,7 +4313,9 @@
       <c r="K52" s="11">
         <v>46080</v>
       </c>
-      <c r="L52" s="11"/>
+      <c r="L52" s="11">
+        <v>46078</v>
+      </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10" t="s">
         <v>33</v>
@@ -4334,7 +4350,7 @@
       </c>
       <c r="I53" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J53" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4381,7 +4397,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4477,7 +4493,7 @@
       </c>
       <c r="I56" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J56" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4524,7 +4540,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4571,7 +4587,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4618,7 +4634,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4665,7 +4681,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -4812,7 +4828,7 @@
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J63" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4856,7 +4872,7 @@
       </c>
       <c r="I64" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J64" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4946,7 +4962,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4990,7 +5006,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5032,7 +5048,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5074,7 +5090,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5215,7 +5231,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5267,7 +5283,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5412,7 +5428,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5650,11 +5666,11 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K81" s="11"/>
       <c r="L81" s="11"/>
@@ -5736,7 +5752,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5788,7 +5804,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5840,7 +5856,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5892,7 +5908,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5934,7 +5950,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6030,7 +6046,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6082,7 +6098,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6178,7 +6194,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6308,7 +6324,7 @@
       </c>
       <c r="I95" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J95" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6350,7 +6366,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6436,7 +6452,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6478,7 +6494,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6519,7 +6535,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6692,7 +6708,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6734,7 +6750,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6775,7 +6791,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6819,7 +6835,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6860,7 +6876,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6901,7 +6917,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6942,7 +6958,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7031,7 +7047,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7120,7 +7136,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7165,7 +7181,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J131" ca="1" si="11">IF(I115="","",
@@ -7218,7 +7234,7 @@
       </c>
       <c r="I116" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7260,7 +7276,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7277,55 +7293,88 @@
       <c r="S117" s="10"/>
     </row>
     <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B118" s="10" t="str">
+      <c r="B118" s="10">
         <f>IF(C118="","",COUNTA($C$2:C118))</f>
-        <v/>
-      </c>
-      <c r="C118" s="11"/>
+        <v>117</v>
+      </c>
+      <c r="C118" s="44">
+        <v>46079</v>
+      </c>
       <c r="D118" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H118" s="4"/>
-      <c r="I118" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E118" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F118" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H118" s="43">
+        <v>13858000</v>
+      </c>
+      <c r="I118" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J118" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K118" s="11"/>
       <c r="L118" s="11"/>
       <c r="M118" s="10"/>
-      <c r="N118" s="10"/>
+      <c r="N118" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q118" s="11"/>
       <c r="R118" s="11"/>
       <c r="S118" s="10"/>
     </row>
     <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B119" s="10" t="str">
+      <c r="B119" s="10">
         <f>IF(C119="","",COUNTA($C$2:C119))</f>
-        <v/>
-      </c>
-      <c r="C119" s="11"/>
+        <v>118</v>
+      </c>
+      <c r="C119" s="44">
+        <v>46078</v>
+      </c>
       <c r="D119" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H119" s="4"/>
-      <c r="I119" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E119" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F119" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H119" s="43">
+        <v>4787500</v>
+      </c>
+      <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K119" s="11"/>
       <c r="L119" s="11"/>
       <c r="M119" s="10"/>
-      <c r="N119" s="10"/>
+      <c r="N119" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="P119" s="6" t="s">
+        <v>155</v>
+      </c>
       <c r="Q119" s="11"/>
       <c r="R119" s="11"/>
       <c r="S119" s="10"/>
@@ -13693,97 +13742,97 @@
   <autoFilter ref="A1:S409"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="21" priority="35">
+    <cfRule type="expression" dxfId="20" priority="35">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="20" priority="34">
+    <cfRule type="expression" dxfId="19" priority="34">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="19" priority="33">
+    <cfRule type="expression" dxfId="18" priority="33">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="18" priority="32">
+    <cfRule type="expression" dxfId="17" priority="32">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="17" priority="27">
+    <cfRule type="expression" dxfId="16" priority="27">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="14" priority="16">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="12" priority="13">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13804,7 +13853,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N117">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="208">
   <si>
     <t>순번</t>
   </si>
@@ -741,6 +741,12 @@
   <si>
     <t>Y</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>은하마을주공1단지</t>
+  </si>
+  <si>
+    <t>(주)대승이앤씨</t>
   </si>
 </sst>
 </file>
@@ -930,7 +936,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="13">
+  <cellStyleXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -963,11 +969,14 @@
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1091,8 +1100,20 @@
     <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="13">
+  <cellStyles count="14">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
     <cellStyle name="백분율 2" xfId="2"/>
     <cellStyle name="백분율 3" xfId="10"/>
@@ -1101,6 +1122,7 @@
     <cellStyle name="쉼표 [0] 3" xfId="9"/>
     <cellStyle name="쉼표 [0] 4" xfId="11"/>
     <cellStyle name="쉼표 [0] 5" xfId="12"/>
+    <cellStyle name="쉼표 [0] 6" xfId="13"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 118 2 7 16" xfId="5"/>
     <cellStyle name="표준 125" xfId="6"/>
@@ -1830,7 +1852,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -1894,7 +1916,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -1953,7 +1975,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2051,7 +2073,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2107,7 +2129,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2156,7 +2178,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2207,7 +2229,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2259,7 +2281,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2398,7 +2420,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2454,7 +2476,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2503,7 +2525,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2552,7 +2574,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2599,7 +2621,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2646,7 +2668,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2693,7 +2715,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2740,7 +2762,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2787,7 +2809,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2836,7 +2858,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2885,7 +2907,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2934,7 +2956,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2983,7 +3005,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3032,7 +3054,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3081,7 +3103,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3130,7 +3152,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3179,7 +3201,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3228,7 +3250,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3277,7 +3299,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3326,7 +3348,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3375,7 +3397,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3424,7 +3446,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3473,7 +3495,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3522,7 +3544,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3567,7 +3589,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3621,7 +3643,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3677,7 +3699,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3730,7 +3752,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3777,7 +3799,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3831,7 +3853,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3936,7 +3958,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3987,7 +4009,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4031,7 +4053,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4075,7 +4097,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4122,7 +4144,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4169,7 +4191,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-266</v>
+        <v>-265</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4211,7 +4233,7 @@
       </c>
       <c r="I50" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J50" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4350,7 +4372,7 @@
       </c>
       <c r="I53" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J53" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4397,7 +4419,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4493,7 +4515,7 @@
       </c>
       <c r="I56" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J56" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4540,7 +4562,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4587,7 +4609,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4634,7 +4656,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4681,7 +4703,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -4828,7 +4850,7 @@
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J63" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4872,7 +4894,7 @@
       </c>
       <c r="I64" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J64" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4962,7 +4984,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5006,7 +5028,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5048,7 +5070,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5090,7 +5112,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5231,7 +5253,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5283,7 +5305,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5428,7 +5450,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5666,7 +5688,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5752,7 +5774,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5804,7 +5826,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5856,7 +5878,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5908,7 +5930,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5950,7 +5972,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6046,7 +6068,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6098,7 +6120,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6194,7 +6216,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6324,7 +6346,7 @@
       </c>
       <c r="I95" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J95" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6366,7 +6388,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6452,7 +6474,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6494,7 +6516,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6535,7 +6557,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6708,7 +6730,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6750,7 +6772,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6791,7 +6813,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6835,7 +6857,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6876,7 +6898,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6917,7 +6939,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6958,7 +6980,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7047,7 +7069,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7136,7 +7158,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7181,7 +7203,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J131" ca="1" si="11">IF(I115="","",
@@ -7241,7 +7263,9 @@
         <v>정상</v>
       </c>
       <c r="K116" s="11"/>
-      <c r="L116" s="11"/>
+      <c r="L116" s="11">
+        <v>46079</v>
+      </c>
       <c r="M116" s="10"/>
       <c r="N116" s="10" t="s">
         <v>33</v>
@@ -7276,7 +7300,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7318,7 +7342,7 @@
       </c>
       <c r="I118" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7360,7 +7384,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7380,55 +7404,87 @@
       <c r="S119" s="10"/>
     </row>
     <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B120" s="10" t="str">
+      <c r="B120" s="10">
         <f>IF(C120="","",COUNTA($C$2:C120))</f>
-        <v/>
-      </c>
-      <c r="C120" s="11"/>
+        <v>119</v>
+      </c>
+      <c r="C120" s="48">
+        <v>46079</v>
+      </c>
       <c r="D120" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H120" s="4"/>
-      <c r="I120" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E120" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="F120" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H120" s="47">
+        <v>4470000</v>
+      </c>
+      <c r="I120" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J120" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K120" s="11"/>
-      <c r="L120" s="11"/>
+      <c r="L120" s="11">
+        <v>46079</v>
+      </c>
       <c r="M120" s="10"/>
-      <c r="N120" s="10"/>
+      <c r="N120" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q120" s="11"/>
       <c r="R120" s="11"/>
       <c r="S120" s="10"/>
     </row>
     <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B121" s="10" t="str">
+      <c r="B121" s="10">
         <f>IF(C121="","",COUNTA($C$2:C121))</f>
-        <v/>
-      </c>
-      <c r="C121" s="11"/>
+        <v>120</v>
+      </c>
+      <c r="C121" s="48">
+        <v>46080</v>
+      </c>
       <c r="D121" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H121" s="4"/>
-      <c r="I121" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E121" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="F121" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H121" s="47">
+        <v>13858000</v>
+      </c>
+      <c r="I121" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J121" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K121" s="11"/>
       <c r="L121" s="11"/>
       <c r="M121" s="10"/>
-      <c r="N121" s="10"/>
+      <c r="N121" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q121" s="11"/>
       <c r="R121" s="11"/>
       <c r="S121" s="10"/>
@@ -13853,7 +13909,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N121">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,15 +11,15 @@
     <sheet name="프로세스현황" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$409</definedName>
-    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$409</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$407</definedName>
+    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$407</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="219">
   <si>
     <t>순번</t>
   </si>
@@ -747,6 +747,39 @@
   </si>
   <si>
     <t>(주)대승이앤씨</t>
+  </si>
+  <si>
+    <t>던에드워드페인트</t>
+  </si>
+  <si>
+    <t>포항북구죽도644영업소</t>
+  </si>
+  <si>
+    <t>수지동보1차</t>
+  </si>
+  <si>
+    <t>두정마을우남1단지</t>
+  </si>
+  <si>
+    <t>등촌임광그린</t>
+  </si>
+  <si>
+    <t>오산한라그린타운</t>
+  </si>
+  <si>
+    <t>랜반</t>
+  </si>
+  <si>
+    <t>(주)모아씨앤에스</t>
+  </si>
+  <si>
+    <t>(주)기림이앤씨</t>
+  </si>
+  <si>
+    <t>여름건설(주)</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
   </si>
 </sst>
 </file>
@@ -936,7 +969,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="14">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -972,11 +1005,14 @@
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1112,8 +1148,20 @@
     <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="14">
+  <cellStyles count="15">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
     <cellStyle name="백분율 2" xfId="2"/>
     <cellStyle name="백분율 3" xfId="10"/>
@@ -1123,6 +1171,7 @@
     <cellStyle name="쉼표 [0] 4" xfId="11"/>
     <cellStyle name="쉼표 [0] 5" xfId="12"/>
     <cellStyle name="쉼표 [0] 6" xfId="13"/>
+    <cellStyle name="쉼표 [0] 7" xfId="14"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 118 2 7 16" xfId="5"/>
     <cellStyle name="표준 125" xfId="6"/>
@@ -1743,7 +1792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S409"/>
+  <dimension ref="A1:S407"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
@@ -1852,7 +1901,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -1916,7 +1965,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -1975,7 +2024,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2073,7 +2122,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2129,7 +2178,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2178,7 +2227,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2229,7 +2278,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2281,7 +2330,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2420,7 +2469,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2476,7 +2525,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2525,7 +2574,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2574,7 +2623,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2621,7 +2670,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2668,7 +2717,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2715,7 +2764,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2762,7 +2811,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2809,7 +2858,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2858,7 +2907,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2907,7 +2956,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2956,7 +3005,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3005,7 +3054,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3054,7 +3103,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3103,7 +3152,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3152,7 +3201,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3201,7 +3250,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3250,7 +3299,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3299,7 +3348,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3348,7 +3397,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3397,7 +3446,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3446,7 +3495,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3495,7 +3544,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3544,7 +3593,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3589,7 +3638,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3643,7 +3692,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3699,7 +3748,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3752,7 +3801,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3799,7 +3848,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3853,7 +3902,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3958,7 +4007,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4009,7 +4058,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4053,7 +4102,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4097,7 +4146,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4144,7 +4193,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4191,7 +4240,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-265</v>
+        <v>-261</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4242,7 +4291,9 @@
       <c r="K50" s="11">
         <v>46080</v>
       </c>
-      <c r="L50" s="11"/>
+      <c r="L50" s="11">
+        <v>46080</v>
+      </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10" t="s">
         <v>33</v>
@@ -4381,7 +4432,9 @@
       <c r="K53" s="11">
         <v>46080</v>
       </c>
-      <c r="L53" s="11"/>
+      <c r="L53" s="11">
+        <v>46080</v>
+      </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10" t="s">
         <v>33</v>
@@ -4419,7 +4472,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4524,7 +4577,9 @@
       <c r="K56" s="11">
         <v>46080</v>
       </c>
-      <c r="L56" s="11"/>
+      <c r="L56" s="11">
+        <v>46080</v>
+      </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10" t="s">
         <v>33</v>
@@ -4562,7 +4617,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4609,7 +4664,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4656,7 +4711,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4703,7 +4758,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -4850,7 +4905,7 @@
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J63" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4894,7 +4949,7 @@
       </c>
       <c r="I64" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J64" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4984,7 +5039,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5028,7 +5083,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5070,7 +5125,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5112,7 +5167,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5253,7 +5308,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5305,7 +5360,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5450,7 +5505,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5475,7 +5530,7 @@
         <v>46034</v>
       </c>
       <c r="D77" s="10" t="str">
-        <f t="shared" ref="D77:D140" si="9">IF(G77="","",IF(OR(G77="선급금",G77="중도금",G77="잔금"),"A",IF(G77="자재","B",IF(G77="특허료","C",""))))</f>
+        <f t="shared" ref="D77:D138" si="9">IF(G77="","",IF(OR(G77="선급금",G77="중도금",G77="잔금"),"A",IF(G77="자재","B",IF(G77="특허료","C",""))))</f>
         <v>B</v>
       </c>
       <c r="E77" s="6" t="s">
@@ -5491,7 +5546,7 @@
         <v>2200000</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" ref="I77:I140" ca="1" si="10">IF(C77="","",IF(L77="",TODAY()-C77,L77-C77))</f>
+        <f t="shared" ref="I77:I138" ca="1" si="10">IF(C77="","",IF(L77="",TODAY()-C77,L77-C77))</f>
         <v>11</v>
       </c>
       <c r="J77" s="13" t="str">
@@ -5688,7 +5743,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5774,11 +5829,11 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K83" s="11"/>
       <c r="L83" s="11"/>
@@ -5826,11 +5881,11 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K84" s="11"/>
       <c r="L84" s="11"/>
@@ -5878,7 +5933,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5930,7 +5985,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5972,7 +6027,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6068,7 +6123,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6120,7 +6175,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6216,7 +6271,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6353,7 +6408,9 @@
         <v>정상</v>
       </c>
       <c r="K95" s="11"/>
-      <c r="L95" s="11"/>
+      <c r="L95" s="11">
+        <v>46080</v>
+      </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10" t="s">
         <v>33</v>
@@ -6388,7 +6445,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6474,7 +6531,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6516,7 +6573,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6557,7 +6614,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6730,7 +6787,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6772,7 +6829,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6813,7 +6870,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6857,7 +6914,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6898,7 +6955,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6939,7 +6996,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6980,7 +7037,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7069,7 +7126,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7158,7 +7215,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7203,10 +7260,10 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ref="J115:J131" ca="1" si="11">IF(I115="","",
+        <f t="shared" ref="J115:J129" ca="1" si="11">IF(I115="","",
  IF(G115="선급금",
    IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
  IF(G115="자재",
@@ -7300,7 +7357,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7349,7 +7406,9 @@
         <v>정상</v>
       </c>
       <c r="K118" s="11"/>
-      <c r="L118" s="11"/>
+      <c r="L118" s="11">
+        <v>46080</v>
+      </c>
       <c r="M118" s="10"/>
       <c r="N118" s="10" t="s">
         <v>33</v>
@@ -7384,7 +7443,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7452,24 +7511,24 @@
         <f>IF(C121="","",COUNTA($C$2:C121))</f>
         <v>120</v>
       </c>
-      <c r="C121" s="48">
-        <v>46080</v>
+      <c r="C121" s="52" t="s">
+        <v>218</v>
       </c>
       <c r="D121" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="E121" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="F121" s="45" t="s">
-        <v>204</v>
+      <c r="E121" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="F121" s="49" t="s">
+        <v>208</v>
       </c>
       <c r="G121" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H121" s="47">
-        <v>13858000</v>
+      <c r="H121" s="50">
+        <v>210000</v>
       </c>
       <c r="I121" s="6">
         <f t="shared" ca="1" si="10"/>
@@ -7480,7 +7539,9 @@
         <v>정상</v>
       </c>
       <c r="K121" s="11"/>
-      <c r="L121" s="11"/>
+      <c r="L121" s="11">
+        <v>46080</v>
+      </c>
       <c r="M121" s="10"/>
       <c r="N121" s="10" t="s">
         <v>33</v>
@@ -7490,136 +7551,211 @@
       <c r="S121" s="10"/>
     </row>
     <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B122" s="10" t="str">
+      <c r="B122" s="10">
         <f>IF(C122="","",COUNTA($C$2:C122))</f>
-        <v/>
-      </c>
-      <c r="C122" s="11"/>
+        <v>121</v>
+      </c>
+      <c r="C122" s="52" t="s">
+        <v>218</v>
+      </c>
       <c r="D122" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H122" s="4"/>
-      <c r="I122" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E122" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="F122" s="49" t="s">
+        <v>209</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H122" s="50">
+        <v>893000</v>
+      </c>
+      <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K122" s="11"/>
       <c r="L122" s="11"/>
       <c r="M122" s="10"/>
-      <c r="N122" s="10"/>
+      <c r="N122" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q122" s="11"/>
       <c r="R122" s="11"/>
       <c r="S122" s="10"/>
     </row>
     <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B123" s="10" t="str">
+      <c r="B123" s="10">
         <f>IF(C123="","",COUNTA($C$2:C123))</f>
-        <v/>
-      </c>
-      <c r="C123" s="11"/>
+        <v>122</v>
+      </c>
+      <c r="C123" s="52" t="s">
+        <v>218</v>
+      </c>
       <c r="D123" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H123" s="4"/>
-      <c r="I123" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E123" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="F123" s="49" t="s">
+        <v>210</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H123" s="50">
+        <v>4490000</v>
+      </c>
+      <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K123" s="11"/>
       <c r="L123" s="11"/>
       <c r="M123" s="10"/>
-      <c r="N123" s="10"/>
+      <c r="N123" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q123" s="11"/>
       <c r="R123" s="11"/>
       <c r="S123" s="10"/>
     </row>
     <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B124" s="10" t="str">
+      <c r="B124" s="10">
         <f>IF(C124="","",COUNTA($C$2:C124))</f>
-        <v/>
-      </c>
-      <c r="C124" s="11"/>
+        <v>123</v>
+      </c>
+      <c r="C124" s="52" t="s">
+        <v>218</v>
+      </c>
       <c r="D124" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H124" s="4"/>
-      <c r="I124" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E124" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="F124" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H124" s="50">
+        <v>1516000</v>
+      </c>
+      <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K124" s="11"/>
       <c r="L124" s="11"/>
       <c r="M124" s="10"/>
-      <c r="N124" s="10"/>
+      <c r="N124" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q124" s="11"/>
       <c r="R124" s="11"/>
       <c r="S124" s="10"/>
     </row>
     <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B125" s="10" t="str">
+      <c r="B125" s="10">
         <f>IF(C125="","",COUNTA($C$2:C125))</f>
-        <v/>
-      </c>
-      <c r="C125" s="11"/>
+        <v>124</v>
+      </c>
+      <c r="C125" s="52" t="s">
+        <v>218</v>
+      </c>
       <c r="D125" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H125" s="4"/>
-      <c r="I125" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E125" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="F125" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H125" s="50">
+        <v>521000</v>
+      </c>
+      <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K125" s="11"/>
       <c r="L125" s="11"/>
       <c r="M125" s="10"/>
-      <c r="N125" s="10"/>
+      <c r="N125" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q125" s="11"/>
       <c r="R125" s="11"/>
       <c r="S125" s="10"/>
     </row>
     <row r="126" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B126" s="10" t="str">
+      <c r="B126" s="10">
         <f>IF(C126="","",COUNTA($C$2:C126))</f>
-        <v/>
-      </c>
-      <c r="C126" s="11"/>
+        <v>125</v>
+      </c>
+      <c r="C126" s="52" t="s">
+        <v>218</v>
+      </c>
       <c r="D126" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H126" s="4"/>
-      <c r="I126" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E126" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="F126" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H126" s="50">
+        <v>6520600</v>
+      </c>
+      <c r="I126" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="J126" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K126" s="11"/>
       <c r="L126" s="11"/>
       <c r="M126" s="10"/>
-      <c r="N126" s="10"/>
+      <c r="N126" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q126" s="11"/>
       <c r="R126" s="11"/>
       <c r="S126" s="10"/>
@@ -7720,10 +7856,7 @@
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="J130" s="13" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
+      <c r="J130" s="13"/>
       <c r="K130" s="11"/>
       <c r="L130" s="11"/>
       <c r="M130" s="10"/>
@@ -7747,10 +7880,7 @@
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="J131" s="13" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
+      <c r="J131" s="13"/>
       <c r="K131" s="11"/>
       <c r="L131" s="11"/>
       <c r="M131" s="10"/>
@@ -7934,12 +8064,12 @@
       </c>
       <c r="C139" s="11"/>
       <c r="D139" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="D139:D202" si="12">IF(G139="","",IF(OR(G139="선급금",G139="중도금",G139="잔금"),"A",IF(G139="자재","B",IF(G139="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H139" s="4"/>
       <c r="I139" s="6" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ref="I139:I202" ca="1" si="13">IF(C139="","",IF(L139="",TODAY()-C139,L139-C139))</f>
         <v/>
       </c>
       <c r="J139" s="13"/>
@@ -7958,12 +8088,12 @@
       </c>
       <c r="C140" s="11"/>
       <c r="D140" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H140" s="4"/>
       <c r="I140" s="6" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="J140" s="13"/>
@@ -7982,12 +8112,12 @@
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="10" t="str">
-        <f t="shared" ref="D141:D204" si="12">IF(G141="","",IF(OR(G141="선급금",G141="중도금",G141="잔금"),"A",IF(G141="자재","B",IF(G141="특허료","C",""))))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H141" s="4"/>
       <c r="I141" s="6" t="str">
-        <f t="shared" ref="I141:I204" ca="1" si="13">IF(C141="","",IF(L141="",TODAY()-C141,L141-C141))</f>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="J141" s="13"/>
@@ -9470,12 +9600,12 @@
       </c>
       <c r="C203" s="11"/>
       <c r="D203" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D203:D266" si="14">IF(G203="","",IF(OR(G203="선급금",G203="중도금",G203="잔금"),"A",IF(G203="자재","B",IF(G203="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H203" s="4"/>
       <c r="I203" s="6" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ref="I203:I266" ca="1" si="15">IF(C203="","",IF(L203="",TODAY()-C203,L203-C203))</f>
         <v/>
       </c>
       <c r="J203" s="13"/>
@@ -9494,12 +9624,12 @@
       </c>
       <c r="C204" s="11"/>
       <c r="D204" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" s="6" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="J204" s="13"/>
@@ -9518,12 +9648,12 @@
       </c>
       <c r="C205" s="11"/>
       <c r="D205" s="10" t="str">
-        <f t="shared" ref="D205:D268" si="14">IF(G205="","",IF(OR(G205="선급금",G205="중도금",G205="잔금"),"A",IF(G205="자재","B",IF(G205="특허료","C",""))))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H205" s="4"/>
       <c r="I205" s="6" t="str">
-        <f t="shared" ref="I205:I268" ca="1" si="15">IF(C205="","",IF(L205="",TODAY()-C205,L205-C205))</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="J205" s="13"/>
@@ -9656,10 +9786,7 @@
       <c r="S210" s="10"/>
     </row>
     <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B211" s="10" t="str">
-        <f>IF(C211="","",COUNTA($C$2:C211))</f>
-        <v/>
-      </c>
+      <c r="B211" s="10"/>
       <c r="C211" s="11"/>
       <c r="D211" s="10" t="str">
         <f t="shared" si="14"/>
@@ -9680,10 +9807,7 @@
       <c r="S211" s="10"/>
     </row>
     <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B212" s="10" t="str">
-        <f>IF(C212="","",COUNTA($C$2:C212))</f>
-        <v/>
-      </c>
+      <c r="B212" s="10"/>
       <c r="C212" s="11"/>
       <c r="D212" s="10" t="str">
         <f t="shared" si="14"/>
@@ -10841,12 +10965,12 @@
       <c r="B267" s="10"/>
       <c r="C267" s="11"/>
       <c r="D267" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="D267:D330" si="16">IF(G267="","",IF(OR(G267="선급금",G267="중도금",G267="잔금"),"A",IF(G267="자재","B",IF(G267="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H267" s="4"/>
       <c r="I267" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ref="I267:I330" ca="1" si="17">IF(C267="","",IF(L267="",TODAY()-C267,L267-C267))</f>
         <v/>
       </c>
       <c r="J267" s="13"/>
@@ -10862,12 +10986,12 @@
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
       <c r="D268" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="J268" s="13"/>
@@ -10883,12 +11007,12 @@
       <c r="B269" s="10"/>
       <c r="C269" s="11"/>
       <c r="D269" s="10" t="str">
-        <f t="shared" ref="D269:D332" si="16">IF(G269="","",IF(OR(G269="선급금",G269="중도금",G269="잔금"),"A",IF(G269="자재","B",IF(G269="특허료","C",""))))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H269" s="4"/>
       <c r="I269" s="6" t="str">
-        <f t="shared" ref="I269:I332" ca="1" si="17">IF(C269="","",IF(L269="",TODAY()-C269,L269-C269))</f>
+        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="J269" s="13"/>
@@ -12185,12 +12309,12 @@
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
       <c r="D331" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="D331:D394" si="18">IF(G331="","",IF(OR(G331="선급금",G331="중도금",G331="잔금"),"A",IF(G331="자재","B",IF(G331="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H331" s="4"/>
       <c r="I331" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ref="I331:I394" ca="1" si="19">IF(C331="","",IF(L331="",TODAY()-C331,L331-C331))</f>
         <v/>
       </c>
       <c r="J331" s="13"/>
@@ -12206,12 +12330,12 @@
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J332" s="13"/>
@@ -12227,12 +12351,12 @@
       <c r="B333" s="10"/>
       <c r="C333" s="11"/>
       <c r="D333" s="10" t="str">
-        <f t="shared" ref="D333:D396" si="18">IF(G333="","",IF(OR(G333="선급금",G333="중도금",G333="잔금"),"A",IF(G333="자재","B",IF(G333="특허료","C",""))))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H333" s="4"/>
       <c r="I333" s="6" t="str">
-        <f t="shared" ref="I333:I396" ca="1" si="19">IF(C333="","",IF(L333="",TODAY()-C333,L333-C333))</f>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J333" s="13"/>
@@ -13529,12 +13653,12 @@
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
       <c r="D395" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="D395:D407" si="20">IF(G395="","",IF(OR(G395="선급금",G395="중도금",G395="잔금"),"A",IF(G395="자재","B",IF(G395="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H395" s="4"/>
       <c r="I395" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ref="I395:I405" ca="1" si="21">IF(C395="","",IF(L395="",TODAY()-C395,L395-C395))</f>
         <v/>
       </c>
       <c r="J395" s="13"/>
@@ -13550,12 +13674,12 @@
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H396" s="4"/>
       <c r="I396" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J396" s="13"/>
@@ -13571,12 +13695,12 @@
       <c r="B397" s="10"/>
       <c r="C397" s="11"/>
       <c r="D397" s="10" t="str">
-        <f t="shared" ref="D397:D409" si="20">IF(G397="","",IF(OR(G397="선급금",G397="중도금",G397="잔금"),"A",IF(G397="자재","B",IF(G397="특허료","C",""))))</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H397" s="4"/>
       <c r="I397" s="6" t="str">
-        <f t="shared" ref="I397:I407" ca="1" si="21">IF(C397="","",IF(L397="",TODAY()-C397,L397-C397))</f>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J397" s="13"/>
@@ -13672,47 +13796,37 @@
       <c r="R401" s="11"/>
       <c r="S401" s="10"/>
     </row>
-    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="402" spans="2:19">
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
-      <c r="D402" s="10" t="str">
+      <c r="D402" s="1" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="H402" s="4"/>
-      <c r="I402" s="6" t="str">
+      <c r="I402" s="1" t="str">
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
-      <c r="J402" s="13"/>
       <c r="K402" s="11"/>
       <c r="L402" s="11"/>
-      <c r="M402" s="10"/>
-      <c r="N402" s="10"/>
       <c r="Q402" s="11"/>
       <c r="R402" s="11"/>
-      <c r="S402" s="10"/>
-    </row>
-    <row r="403" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    </row>
+    <row r="403" spans="2:19">
       <c r="B403" s="10"/>
       <c r="C403" s="11"/>
-      <c r="D403" s="10" t="str">
+      <c r="D403" s="1" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="H403" s="4"/>
-      <c r="I403" s="6" t="str">
+      <c r="I403" s="1" t="str">
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
-      <c r="J403" s="13"/>
       <c r="K403" s="11"/>
       <c r="L403" s="11"/>
-      <c r="M403" s="10"/>
-      <c r="N403" s="10"/>
       <c r="Q403" s="11"/>
       <c r="R403" s="11"/>
-      <c r="S403" s="10"/>
     </row>
     <row r="404" spans="2:19">
       <c r="B404" s="10"/>
@@ -13725,8 +13839,6 @@
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
-      <c r="K404" s="11"/>
-      <c r="L404" s="11"/>
       <c r="Q404" s="11"/>
       <c r="R404" s="11"/>
     </row>
@@ -13741,8 +13853,6 @@
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
-      <c r="K405" s="11"/>
-      <c r="L405" s="11"/>
       <c r="Q405" s="11"/>
       <c r="R405" s="11"/>
     </row>
@@ -13753,10 +13863,6 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I406" s="1" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
       <c r="Q406" s="11"/>
       <c r="R406" s="11"/>
     </row>
@@ -13767,35 +13873,11 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I407" s="1" t="str">
-        <f t="shared" ca="1" si="21"/>
-        <v/>
-      </c>
       <c r="Q407" s="11"/>
       <c r="R407" s="11"/>
     </row>
-    <row r="408" spans="2:19">
-      <c r="B408" s="10"/>
-      <c r="C408" s="11"/>
-      <c r="D408" s="1" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Q408" s="11"/>
-      <c r="R408" s="11"/>
-    </row>
-    <row r="409" spans="2:19">
-      <c r="B409" s="10"/>
-      <c r="C409" s="11"/>
-      <c r="D409" s="1" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Q409" s="11"/>
-      <c r="R409" s="11"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S409"/>
+  <autoFilter ref="A1:S407"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
     <cfRule type="expression" dxfId="20" priority="35">
@@ -13903,14 +13985,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D409">
-      <formula1>"A,B,C"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N121">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N126">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D407">
+      <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="233">
   <si>
     <t>순번</t>
   </si>
@@ -781,6 +781,48 @@
   <si>
     <t>2026-02-27</t>
   </si>
+  <si>
+    <t>불암현대</t>
+  </si>
+  <si>
+    <t>사무실택배</t>
+  </si>
+  <si>
+    <t>중산11단지현대</t>
+  </si>
+  <si>
+    <t>소촌동대성베르힐</t>
+  </si>
+  <si>
+    <t>동백역벽산블루밍</t>
+  </si>
+  <si>
+    <t>중동역2차푸르지오</t>
+  </si>
+  <si>
+    <t>서울역센트럴자이</t>
+  </si>
+  <si>
+    <t>시흥참이슬아파트</t>
+  </si>
+  <si>
+    <t>(주)진성이앤지</t>
+  </si>
+  <si>
+    <t>대명이엔씨(주)</t>
+  </si>
+  <si>
+    <t>(주)국일구조</t>
+  </si>
+  <si>
+    <t>(주)피앤텍이엔지</t>
+  </si>
+  <si>
+    <t>가온알앤씨</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
 </sst>
 </file>
 
@@ -791,7 +833,7 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="181" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -969,7 +1011,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="15">
+  <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -1008,11 +1050,14 @@
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1160,8 +1205,20 @@
     <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="15">
+  <cellStyles count="16">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
     <cellStyle name="백분율 2" xfId="2"/>
     <cellStyle name="백분율 3" xfId="10"/>
@@ -1172,6 +1229,7 @@
     <cellStyle name="쉼표 [0] 5" xfId="12"/>
     <cellStyle name="쉼표 [0] 6" xfId="13"/>
     <cellStyle name="쉼표 [0] 7" xfId="14"/>
+    <cellStyle name="쉼표 [0] 8" xfId="15"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 118 2 7 16" xfId="5"/>
     <cellStyle name="표준 125" xfId="6"/>
@@ -1901,7 +1959,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -1965,7 +2023,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -2024,7 +2082,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2122,7 +2180,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2178,7 +2236,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2227,7 +2285,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2278,7 +2336,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2330,7 +2388,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2469,7 +2527,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2525,7 +2583,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2574,7 +2632,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2623,7 +2681,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2670,7 +2728,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2717,7 +2775,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2764,7 +2822,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2811,7 +2869,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2858,7 +2916,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2907,7 +2965,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2956,7 +3014,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3005,7 +3063,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3054,7 +3112,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3103,7 +3161,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3152,7 +3210,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3201,7 +3259,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3250,7 +3308,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3299,7 +3357,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3348,7 +3406,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3397,7 +3455,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3446,7 +3504,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3495,7 +3553,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3544,7 +3602,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3593,7 +3651,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3638,7 +3696,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3692,7 +3750,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3748,7 +3806,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3801,7 +3859,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3848,7 +3906,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3902,7 +3960,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4007,7 +4065,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4058,7 +4116,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4102,7 +4160,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4146,7 +4204,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4193,7 +4251,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4240,7 +4298,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-261</v>
+        <v>-260</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4472,7 +4530,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4617,7 +4675,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4664,7 +4722,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4711,7 +4769,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4758,7 +4816,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -4905,7 +4963,7 @@
       </c>
       <c r="I63" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J63" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -4949,7 +5007,7 @@
       </c>
       <c r="I64" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J64" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5039,7 +5097,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5083,7 +5141,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5125,7 +5183,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5167,7 +5225,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5308,7 +5366,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5360,7 +5418,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5505,7 +5563,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5743,7 +5801,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5829,7 +5887,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5881,7 +5939,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5933,11 +5991,11 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K85" s="11"/>
       <c r="L85" s="11"/>
@@ -5985,11 +6043,11 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K86" s="11"/>
       <c r="L86" s="11"/>
@@ -6027,7 +6085,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6123,7 +6181,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6175,7 +6233,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6271,7 +6329,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6445,7 +6503,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6531,7 +6589,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6573,7 +6631,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6614,7 +6672,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6787,7 +6845,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6829,7 +6887,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6870,7 +6928,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6914,7 +6972,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6955,7 +7013,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6996,7 +7054,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7037,7 +7095,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7126,7 +7184,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7215,7 +7273,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7260,10 +7318,10 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ref="J115:J129" ca="1" si="11">IF(I115="","",
+        <f t="shared" ref="J115:J135" ca="1" si="11">IF(I115="","",
  IF(G115="선급금",
    IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
  IF(G115="자재",
@@ -7357,7 +7415,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7443,7 +7501,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7576,7 +7634,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7618,7 +7676,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7660,7 +7718,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7702,7 +7760,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7744,7 +7802,7 @@
       </c>
       <c r="I126" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J126" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7761,226 +7819,379 @@
       <c r="S126" s="10"/>
     </row>
     <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B127" s="10" t="str">
+      <c r="B127" s="10">
         <f>IF(C127="","",COUNTA($C$2:C127))</f>
-        <v/>
-      </c>
-      <c r="C127" s="11"/>
+        <v>126</v>
+      </c>
+      <c r="C127" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D127" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H127" s="4"/>
-      <c r="I127" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E127" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="F127" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H127" s="54">
+        <v>2330000</v>
+      </c>
+      <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K127" s="11"/>
       <c r="L127" s="11"/>
       <c r="M127" s="10"/>
-      <c r="N127" s="10"/>
+      <c r="N127" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q127" s="11"/>
       <c r="R127" s="11"/>
       <c r="S127" s="10"/>
     </row>
     <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B128" s="10" t="str">
+      <c r="B128" s="10">
         <f>IF(C128="","",COUNTA($C$2:C128))</f>
-        <v/>
-      </c>
-      <c r="C128" s="11"/>
+        <v>127</v>
+      </c>
+      <c r="C128" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D128" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H128" s="4"/>
-      <c r="I128" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E128" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="F128" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="G128" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H128" s="54">
+        <v>52200</v>
+      </c>
+      <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K128" s="11"/>
       <c r="L128" s="11"/>
       <c r="M128" s="10"/>
-      <c r="N128" s="10"/>
+      <c r="N128" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q128" s="11"/>
       <c r="R128" s="11"/>
       <c r="S128" s="10"/>
     </row>
     <row r="129" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B129" s="10" t="str">
+      <c r="B129" s="10">
         <f>IF(C129="","",COUNTA($C$2:C129))</f>
-        <v/>
-      </c>
-      <c r="C129" s="11"/>
+        <v>128</v>
+      </c>
+      <c r="C129" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D129" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H129" s="4"/>
-      <c r="I129" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E129" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="F129" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H129" s="54">
+        <v>7624000</v>
+      </c>
+      <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v/>
+        <v>정상</v>
       </c>
       <c r="K129" s="11"/>
       <c r="L129" s="11"/>
       <c r="M129" s="10"/>
-      <c r="N129" s="10"/>
+      <c r="N129" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q129" s="11"/>
       <c r="R129" s="11"/>
       <c r="S129" s="10"/>
     </row>
     <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B130" s="10" t="str">
+      <c r="B130" s="10">
         <f>IF(C130="","",COUNTA($C$2:C130))</f>
-        <v/>
-      </c>
-      <c r="C130" s="11"/>
+        <v>129</v>
+      </c>
+      <c r="C130" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D130" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H130" s="4"/>
-      <c r="I130" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E130" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="F130" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="G130" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H130" s="54">
+        <v>4010000</v>
+      </c>
+      <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J130" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J130" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K130" s="11"/>
       <c r="L130" s="11"/>
       <c r="M130" s="10"/>
-      <c r="N130" s="10"/>
+      <c r="N130" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q130" s="11"/>
       <c r="R130" s="11"/>
       <c r="S130" s="10"/>
     </row>
     <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B131" s="10" t="str">
+      <c r="B131" s="10">
         <f>IF(C131="","",COUNTA($C$2:C131))</f>
-        <v/>
-      </c>
-      <c r="C131" s="11"/>
+        <v>130</v>
+      </c>
+      <c r="C131" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D131" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H131" s="4"/>
-      <c r="I131" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E131" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="F131" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H131" s="54">
+        <v>889500</v>
+      </c>
+      <c r="I131" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J131" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J131" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K131" s="11"/>
       <c r="L131" s="11"/>
       <c r="M131" s="10"/>
-      <c r="N131" s="10"/>
+      <c r="N131" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q131" s="11"/>
       <c r="R131" s="11"/>
       <c r="S131" s="10"/>
     </row>
     <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B132" s="10" t="str">
+      <c r="B132" s="10">
         <f>IF(C132="","",COUNTA($C$2:C132))</f>
-        <v/>
-      </c>
-      <c r="C132" s="11"/>
+        <v>131</v>
+      </c>
+      <c r="C132" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D132" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H132" s="4"/>
-      <c r="I132" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E132" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="F132" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H132" s="54">
+        <v>2470000</v>
+      </c>
+      <c r="I132" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J132" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J132" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K132" s="11"/>
       <c r="L132" s="11"/>
       <c r="M132" s="10"/>
-      <c r="N132" s="10"/>
+      <c r="N132" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q132" s="11"/>
       <c r="R132" s="11"/>
       <c r="S132" s="10"/>
     </row>
     <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B133" s="10" t="str">
+      <c r="B133" s="10">
         <f>IF(C133="","",COUNTA($C$2:C133))</f>
-        <v/>
-      </c>
-      <c r="C133" s="11"/>
+        <v>132</v>
+      </c>
+      <c r="C133" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D133" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H133" s="4"/>
-      <c r="I133" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E133" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="F133" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H133" s="54">
+        <v>72937600</v>
+      </c>
+      <c r="I133" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J133" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J133" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K133" s="11"/>
       <c r="L133" s="11"/>
       <c r="M133" s="10"/>
-      <c r="N133" s="10"/>
+      <c r="N133" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q133" s="11"/>
       <c r="R133" s="11"/>
       <c r="S133" s="10"/>
     </row>
     <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B134" s="10" t="str">
+      <c r="B134" s="10">
         <f>IF(C134="","",COUNTA($C$2:C134))</f>
-        <v/>
-      </c>
-      <c r="C134" s="11"/>
+        <v>133</v>
+      </c>
+      <c r="C134" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D134" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H134" s="4"/>
-      <c r="I134" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E134" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F134" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="G134" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H134" s="54">
+        <v>5427900</v>
+      </c>
+      <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J134" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J134" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K134" s="11"/>
       <c r="L134" s="11"/>
       <c r="M134" s="10"/>
-      <c r="N134" s="10"/>
+      <c r="N134" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q134" s="11"/>
       <c r="R134" s="11"/>
       <c r="S134" s="10"/>
     </row>
     <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B135" s="10" t="str">
+      <c r="B135" s="10">
         <f>IF(C135="","",COUNTA($C$2:C135))</f>
-        <v/>
-      </c>
-      <c r="C135" s="11"/>
+        <v>134</v>
+      </c>
+      <c r="C135" s="56" t="s">
+        <v>232</v>
+      </c>
       <c r="D135" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H135" s="4"/>
-      <c r="I135" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E135" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="F135" s="53" t="s">
+        <v>206</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H135" s="54">
+        <v>4470000</v>
+      </c>
+      <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J135" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J135" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K135" s="11"/>
       <c r="L135" s="11"/>
       <c r="M135" s="10"/>
-      <c r="N135" s="10"/>
+      <c r="N135" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q135" s="11"/>
       <c r="R135" s="11"/>
       <c r="S135" s="10"/>
@@ -13988,7 +14199,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N126">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N135">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D407">

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="240">
   <si>
     <t>순번</t>
   </si>
@@ -823,6 +823,28 @@
   <si>
     <t>2026-03-03</t>
   </si>
+  <si>
+    <t>건진개발㈜</t>
+  </si>
+  <si>
+    <t>덕천동롯데</t>
+  </si>
+  <si>
+    <t>토당금강KCC</t>
+  </si>
+  <si>
+    <t>영산대학교</t>
+  </si>
+  <si>
+    <t>선급금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>색채산업개발㈜</t>
+  </si>
+  <si>
+    <t>주식회사 대신하우징</t>
+  </si>
 </sst>
 </file>
 
@@ -833,9 +855,9 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,6 +953,20 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1011,7 +1047,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="16">
+  <cellStyleXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -1053,11 +1089,14 @@
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1217,8 +1256,17 @@
     <xf numFmtId="178" fontId="7" fillId="2" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="2" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="16">
+  <cellStyles count="17">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
     <cellStyle name="백분율 2" xfId="2"/>
     <cellStyle name="백분율 3" xfId="10"/>
@@ -1230,6 +1278,7 @@
     <cellStyle name="쉼표 [0] 6" xfId="13"/>
     <cellStyle name="쉼표 [0] 7" xfId="14"/>
     <cellStyle name="쉼표 [0] 8" xfId="15"/>
+    <cellStyle name="쉼표 [0] 9" xfId="16"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 118 2 7 16" xfId="5"/>
     <cellStyle name="표준 125" xfId="6"/>
@@ -1959,7 +2008,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2023,7 +2072,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -2082,7 +2131,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2180,7 +2229,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2236,7 +2285,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2285,7 +2334,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2336,7 +2385,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2388,7 +2437,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2527,7 +2576,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2583,7 +2632,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2632,7 +2681,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2681,7 +2730,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2728,7 +2777,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2775,7 +2824,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2822,7 +2871,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2869,7 +2918,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2916,7 +2965,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2965,7 +3014,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3014,7 +3063,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3063,7 +3112,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3112,7 +3161,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3161,7 +3210,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3210,7 +3259,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3259,7 +3308,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3308,7 +3357,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3357,7 +3406,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3406,7 +3455,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3455,7 +3504,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3504,7 +3553,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3553,7 +3602,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3602,7 +3651,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3651,7 +3700,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3696,7 +3745,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3750,7 +3799,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3806,7 +3855,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3859,7 +3908,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3906,7 +3955,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3960,7 +4009,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4065,7 +4114,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4116,7 +4165,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4160,7 +4209,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4204,7 +4253,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4251,7 +4300,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4298,7 +4347,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-260</v>
+        <v>-259</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4530,7 +4579,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4675,7 +4724,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4722,7 +4771,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4769,7 +4818,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4816,7 +4865,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -4972,7 +5021,9 @@
       <c r="K63" s="11">
         <v>46087</v>
       </c>
-      <c r="L63" s="11"/>
+      <c r="L63" s="11">
+        <v>46085</v>
+      </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10" t="s">
         <v>33</v>
@@ -5016,7 +5067,9 @@
       <c r="K64" s="11">
         <v>46087</v>
       </c>
-      <c r="L64" s="11"/>
+      <c r="L64" s="11">
+        <v>46085</v>
+      </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10" t="s">
         <v>33</v>
@@ -5097,7 +5150,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5141,7 +5194,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5183,7 +5236,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5225,7 +5278,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5366,7 +5419,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5418,7 +5471,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5563,7 +5616,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5801,7 +5854,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5887,7 +5940,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5939,7 +5992,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5991,7 +6044,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6043,7 +6096,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6085,7 +6138,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6181,7 +6234,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6233,7 +6286,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6329,7 +6382,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6503,7 +6556,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6589,7 +6642,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6631,7 +6684,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6672,7 +6725,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6845,7 +6898,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6887,7 +6940,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6928,7 +6981,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6972,7 +7025,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7013,7 +7066,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7054,7 +7107,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7095,7 +7148,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7184,7 +7237,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7273,7 +7326,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7318,10 +7371,10 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ref="J115:J135" ca="1" si="11">IF(I115="","",
+        <f t="shared" ref="J115:J138" ca="1" si="11">IF(I115="","",
  IF(G115="선급금",
    IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
  IF(G115="자재",
@@ -7415,7 +7468,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7501,7 +7554,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7634,7 +7687,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7676,7 +7729,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7718,7 +7771,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7760,7 +7813,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7802,7 +7855,7 @@
       </c>
       <c r="I126" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J126" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7844,7 +7897,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7886,7 +7939,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7928,7 +7981,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7970,7 +8023,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8012,7 +8065,7 @@
       </c>
       <c r="I131" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J131" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8054,7 +8107,7 @@
       </c>
       <c r="I132" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J132" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8096,7 +8149,7 @@
       </c>
       <c r="I133" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J133" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8138,7 +8191,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8180,7 +8233,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8197,73 +8250,129 @@
       <c r="S135" s="10"/>
     </row>
     <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B136" s="10" t="str">
+      <c r="B136" s="10">
         <f>IF(C136="","",COUNTA($C$2:C136))</f>
-        <v/>
-      </c>
-      <c r="C136" s="11"/>
+        <v>135</v>
+      </c>
+      <c r="C136" s="58">
+        <v>46085</v>
+      </c>
       <c r="D136" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H136" s="4"/>
-      <c r="I136" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E136" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="F136" s="57" t="s">
+        <v>234</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H136" s="4">
+        <v>12360000</v>
+      </c>
+      <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J136" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J136" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K136" s="11"/>
       <c r="L136" s="11"/>
       <c r="M136" s="10"/>
-      <c r="N136" s="10"/>
+      <c r="N136" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q136" s="11"/>
       <c r="R136" s="11"/>
       <c r="S136" s="10"/>
     </row>
     <row r="137" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B137" s="10" t="str">
+      <c r="B137" s="10">
         <f>IF(C137="","",COUNTA($C$2:C137))</f>
-        <v/>
-      </c>
-      <c r="C137" s="11"/>
+        <v>136</v>
+      </c>
+      <c r="C137" s="58">
+        <v>46085</v>
+      </c>
       <c r="D137" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H137" s="4"/>
-      <c r="I137" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E137" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="F137" s="57" t="s">
+        <v>235</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H137" s="59">
+        <v>10474600</v>
+      </c>
+      <c r="I137" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J137" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J137" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K137" s="11"/>
       <c r="L137" s="11"/>
       <c r="M137" s="10"/>
-      <c r="N137" s="10"/>
+      <c r="N137" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q137" s="11"/>
       <c r="R137" s="11"/>
       <c r="S137" s="10"/>
     </row>
     <row r="138" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B138" s="10" t="str">
+      <c r="B138" s="10">
         <f>IF(C138="","",COUNTA($C$2:C138))</f>
-        <v/>
-      </c>
-      <c r="C138" s="11"/>
+        <v>137</v>
+      </c>
+      <c r="C138" s="58">
+        <v>46085</v>
+      </c>
       <c r="D138" s="10" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="H138" s="4"/>
-      <c r="I138" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E138" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="F138" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H138" s="59">
+        <v>9772000</v>
+      </c>
+      <c r="I138" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="J138" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J138" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K138" s="11"/>
-      <c r="L138" s="11"/>
+      <c r="L138" s="11">
+        <v>46085</v>
+      </c>
       <c r="M138" s="10"/>
-      <c r="N138" s="10"/>
+      <c r="N138" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q138" s="11"/>
       <c r="R138" s="11"/>
       <c r="S138" s="10"/>
@@ -14199,7 +14308,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N135">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N138">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D407">

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="253">
   <si>
     <t>순번</t>
   </si>
@@ -844,6 +844,54 @@
   </si>
   <si>
     <t>주식회사 대신하우징</t>
+  </si>
+  <si>
+    <t>중도금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>영산대학교</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 20,124,400 
+</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E편한세상한강신도시2차 아파트</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선급금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로이건설㈜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>해운대센텀트루엘1단지직영건</t>
+  </si>
+  <si>
+    <t>상무모아제일아파트</t>
+  </si>
+  <si>
+    <t>동수원월드메르디앙</t>
+  </si>
+  <si>
+    <t>수원로얄팰리스</t>
+  </si>
+  <si>
+    <t>(주)이두건설</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1047,7 +1095,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="17">
+  <cellStyleXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -1092,11 +1140,14 @@
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1265,11 +1316,18 @@
     <xf numFmtId="176" fontId="13" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="17">
+  <cellStyles count="18">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
     <cellStyle name="백분율 2" xfId="2"/>
     <cellStyle name="백분율 3" xfId="10"/>
+    <cellStyle name="쉼표 [0] 10" xfId="17"/>
     <cellStyle name="쉼표 [0] 118 2 7 16" xfId="3"/>
     <cellStyle name="쉼표 [0] 2" xfId="4"/>
     <cellStyle name="쉼표 [0] 3" xfId="9"/>
@@ -1285,7 +1343,82 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="26">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2008,7 +2141,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2072,7 +2205,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -2131,7 +2264,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2229,7 +2362,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2285,7 +2418,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2334,7 +2467,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2385,7 +2518,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2437,7 +2570,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2576,7 +2709,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2632,7 +2765,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2681,7 +2814,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2730,7 +2863,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2777,7 +2910,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2824,7 +2957,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2871,7 +3004,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2918,7 +3051,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2965,7 +3098,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3014,7 +3147,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3063,7 +3196,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3112,7 +3245,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3161,7 +3294,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3210,7 +3343,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3259,7 +3392,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3308,7 +3441,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3357,7 +3490,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3406,7 +3539,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3455,7 +3588,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3504,7 +3637,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3553,7 +3686,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3602,7 +3735,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3651,7 +3784,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3700,7 +3833,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3745,7 +3878,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3799,7 +3932,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3855,7 +3988,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3908,7 +4041,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3955,7 +4088,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4009,7 +4142,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4114,7 +4247,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4165,7 +4298,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4209,7 +4342,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4253,7 +4386,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4300,7 +4433,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4347,7 +4480,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-259</v>
+        <v>-258</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4579,7 +4712,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4724,7 +4857,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4771,7 +4904,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4818,7 +4951,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4865,7 +4998,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -5150,7 +5283,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5194,7 +5327,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5236,7 +5369,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5278,7 +5411,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5419,7 +5552,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5471,7 +5604,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5616,7 +5749,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5854,7 +5987,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5940,7 +6073,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5992,7 +6125,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6044,7 +6177,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6096,7 +6229,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6138,7 +6271,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6234,7 +6367,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6286,7 +6419,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6382,7 +6515,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6556,7 +6689,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6642,7 +6775,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6684,7 +6817,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6725,7 +6858,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6898,7 +7031,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6940,7 +7073,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6981,7 +7114,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7025,7 +7158,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7066,7 +7199,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7107,7 +7240,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7148,7 +7281,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7237,7 +7370,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7326,7 +7459,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7371,10 +7504,10 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ref="J115:J138" ca="1" si="11">IF(I115="","",
+        <f t="shared" ref="J115:J148" ca="1" si="11">IF(I115="","",
  IF(G115="선급금",
    IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
  IF(G115="자재",
@@ -7468,7 +7601,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7554,7 +7687,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7687,7 +7820,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7729,7 +7862,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7771,7 +7904,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7813,7 +7946,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7855,7 +7988,7 @@
       </c>
       <c r="I126" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J126" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7897,7 +8030,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7939,7 +8072,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7981,7 +8114,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8023,7 +8156,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8065,7 +8198,7 @@
       </c>
       <c r="I131" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J131" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8107,7 +8240,7 @@
       </c>
       <c r="I132" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J132" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8149,7 +8282,7 @@
       </c>
       <c r="I133" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J133" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8191,7 +8324,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8233,7 +8366,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8282,7 +8415,9 @@
         <v>정상</v>
       </c>
       <c r="K136" s="11"/>
-      <c r="L136" s="11"/>
+      <c r="L136" s="11">
+        <v>46086</v>
+      </c>
       <c r="M136" s="10"/>
       <c r="N136" s="10" t="s">
         <v>33</v>
@@ -8317,7 +8452,7 @@
       </c>
       <c r="I137" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J137" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8348,8 +8483,8 @@
       <c r="E138" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="F138" s="57" t="s">
-        <v>236</v>
+      <c r="F138" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="G138" s="6" t="s">
         <v>237</v>
@@ -8378,241 +8513,413 @@
       <c r="S138" s="10"/>
     </row>
     <row r="139" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B139" s="10" t="str">
+      <c r="B139" s="10">
         <f>IF(C139="","",COUNTA($C$2:C139))</f>
-        <v/>
-      </c>
-      <c r="C139" s="11"/>
+        <v>138</v>
+      </c>
+      <c r="C139" s="58">
+        <v>46086</v>
+      </c>
       <c r="D139" s="10" t="str">
         <f t="shared" ref="D139:D202" si="12">IF(G139="","",IF(OR(G139="선급금",G139="중도금",G139="잔금"),"A",IF(G139="자재","B",IF(G139="특허료","C",""))))</f>
-        <v/>
-      </c>
-      <c r="H139" s="4"/>
-      <c r="I139" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E139" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="F139" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H139" s="61">
+        <v>19544000</v>
+      </c>
+      <c r="I139" s="6">
         <f t="shared" ref="I139:I202" ca="1" si="13">IF(C139="","",IF(L139="",TODAY()-C139,L139-C139))</f>
-        <v/>
-      </c>
-      <c r="J139" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J139" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K139" s="11"/>
       <c r="L139" s="11"/>
       <c r="M139" s="10"/>
-      <c r="N139" s="10"/>
+      <c r="N139" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q139" s="11"/>
       <c r="R139" s="11"/>
       <c r="S139" s="10"/>
     </row>
     <row r="140" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B140" s="10" t="str">
+      <c r="B140" s="10">
         <f>IF(C140="","",COUNTA($C$2:C140))</f>
-        <v/>
-      </c>
-      <c r="C140" s="11"/>
+        <v>139</v>
+      </c>
+      <c r="C140" s="58">
+        <v>46086</v>
+      </c>
       <c r="D140" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H140" s="4"/>
-      <c r="I140" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H140" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="I140" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J140" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J140" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K140" s="11"/>
       <c r="L140" s="11"/>
       <c r="M140" s="10"/>
-      <c r="N140" s="10"/>
+      <c r="N140" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q140" s="11"/>
       <c r="R140" s="11"/>
       <c r="S140" s="10"/>
     </row>
     <row r="141" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B141" s="10" t="str">
+      <c r="B141" s="10">
         <f>IF(C141="","",COUNTA($C$2:C141))</f>
-        <v/>
-      </c>
-      <c r="C141" s="11"/>
-      <c r="D141" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H141" s="4"/>
-      <c r="I141" s="6" t="str">
+        <v>140</v>
+      </c>
+      <c r="C141" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E141" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="F141" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H141" s="25">
+        <v>577500</v>
+      </c>
+      <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J141" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J141" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K141" s="11"/>
       <c r="L141" s="11"/>
       <c r="M141" s="10"/>
-      <c r="N141" s="10"/>
+      <c r="N141" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q141" s="11"/>
       <c r="R141" s="11"/>
       <c r="S141" s="10"/>
     </row>
     <row r="142" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B142" s="10" t="str">
+      <c r="B142" s="10">
         <f>IF(C142="","",COUNTA($C$2:C142))</f>
-        <v/>
-      </c>
-      <c r="C142" s="11"/>
-      <c r="D142" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H142" s="4"/>
-      <c r="I142" s="6" t="str">
+        <v>141</v>
+      </c>
+      <c r="C142" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E142" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F142" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H142" s="25">
+        <v>226000</v>
+      </c>
+      <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J142" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J142" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K142" s="11"/>
       <c r="L142" s="11"/>
       <c r="M142" s="10"/>
-      <c r="N142" s="10"/>
+      <c r="N142" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q142" s="11"/>
       <c r="R142" s="11"/>
       <c r="S142" s="10"/>
     </row>
     <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B143" s="10" t="str">
+      <c r="B143" s="10">
         <f>IF(C143="","",COUNTA($C$2:C143))</f>
-        <v/>
-      </c>
-      <c r="C143" s="11"/>
-      <c r="D143" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H143" s="4"/>
-      <c r="I143" s="6" t="str">
+        <v>142</v>
+      </c>
+      <c r="C143" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E143" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F143" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H143" s="25">
+        <v>23700</v>
+      </c>
+      <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J143" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J143" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K143" s="11"/>
       <c r="L143" s="11"/>
       <c r="M143" s="10"/>
-      <c r="N143" s="10"/>
+      <c r="N143" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q143" s="11"/>
       <c r="R143" s="11"/>
       <c r="S143" s="10"/>
     </row>
     <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B144" s="10" t="str">
+      <c r="B144" s="10">
         <f>IF(C144="","",COUNTA($C$2:C144))</f>
-        <v/>
-      </c>
-      <c r="C144" s="11"/>
-      <c r="D144" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H144" s="4"/>
-      <c r="I144" s="6" t="str">
+        <v>143</v>
+      </c>
+      <c r="C144" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E144" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="F144" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H144" s="25">
+        <v>16750</v>
+      </c>
+      <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J144" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J144" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K144" s="11"/>
       <c r="L144" s="11"/>
       <c r="M144" s="10"/>
-      <c r="N144" s="10"/>
+      <c r="N144" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q144" s="11"/>
       <c r="R144" s="11"/>
       <c r="S144" s="10"/>
     </row>
     <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B145" s="10" t="str">
+      <c r="B145" s="10">
         <f>IF(C145="","",COUNTA($C$2:C145))</f>
-        <v/>
-      </c>
-      <c r="C145" s="11"/>
-      <c r="D145" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H145" s="4"/>
-      <c r="I145" s="6" t="str">
+        <v>144</v>
+      </c>
+      <c r="C145" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E145" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F145" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H145" s="25">
+        <v>317960</v>
+      </c>
+      <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J145" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J145" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K145" s="11"/>
       <c r="L145" s="11"/>
       <c r="M145" s="10"/>
-      <c r="N145" s="10"/>
+      <c r="N145" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q145" s="11"/>
       <c r="R145" s="11"/>
       <c r="S145" s="10"/>
     </row>
     <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B146" s="10" t="str">
+      <c r="B146" s="10">
         <f>IF(C146="","",COUNTA($C$2:C146))</f>
-        <v/>
-      </c>
-      <c r="C146" s="11"/>
-      <c r="D146" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H146" s="4"/>
-      <c r="I146" s="6" t="str">
+        <v>145</v>
+      </c>
+      <c r="C146" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E146" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F146" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H146" s="25">
+        <v>550000</v>
+      </c>
+      <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J146" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J146" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K146" s="11"/>
       <c r="L146" s="11"/>
       <c r="M146" s="10"/>
-      <c r="N146" s="10"/>
+      <c r="N146" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q146" s="11"/>
       <c r="R146" s="11"/>
       <c r="S146" s="10"/>
     </row>
     <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B147" s="10" t="str">
+      <c r="B147" s="10">
         <f>IF(C147="","",COUNTA($C$2:C147))</f>
-        <v/>
-      </c>
-      <c r="C147" s="11"/>
-      <c r="D147" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H147" s="4"/>
-      <c r="I147" s="6" t="str">
+        <v>146</v>
+      </c>
+      <c r="C147" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E147" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F147" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H147" s="25">
+        <v>180100</v>
+      </c>
+      <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J147" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J147" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K147" s="11"/>
       <c r="L147" s="11"/>
       <c r="M147" s="10"/>
-      <c r="N147" s="10"/>
+      <c r="N147" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q147" s="11"/>
       <c r="R147" s="11"/>
       <c r="S147" s="10"/>
     </row>
     <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B148" s="10" t="str">
+      <c r="B148" s="10">
         <f>IF(C148="","",COUNTA($C$2:C148))</f>
-        <v/>
-      </c>
-      <c r="C148" s="11"/>
-      <c r="D148" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H148" s="4"/>
-      <c r="I148" s="6" t="str">
+        <v>147</v>
+      </c>
+      <c r="C148" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="E148" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F148" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H148" s="25">
+        <v>640050</v>
+      </c>
+      <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J148" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J148" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K148" s="11"/>
       <c r="L148" s="11"/>
       <c r="M148" s="10"/>
-      <c r="N148" s="10"/>
+      <c r="N148" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q148" s="11"/>
       <c r="R148" s="11"/>
       <c r="S148" s="10"/>
@@ -14200,115 +14507,130 @@
   <autoFilter ref="A1:S407"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="20" priority="35">
+    <cfRule type="expression" dxfId="25" priority="38">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="19" priority="34">
+    <cfRule type="expression" dxfId="24" priority="37">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="18" priority="33">
+    <cfRule type="expression" dxfId="23" priority="36">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="17" priority="32">
+    <cfRule type="expression" dxfId="22" priority="35">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="16" priority="27">
+    <cfRule type="expression" dxfId="21" priority="30">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="15" priority="17">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="17" priority="16">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="16" priority="15">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="15" priority="14">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="13" priority="12">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="12" priority="11">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="9" priority="8">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="7" priority="6">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>$J117="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F141:F148">
+    <cfRule type="expression" dxfId="4" priority="3">
+      <formula>$J141="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E141:E148">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>$J141="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H141:H148">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J117="잔금"</formula>
+      <formula>$J141="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N138">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N148">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D407">

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,15 +11,15 @@
     <sheet name="프로세스현황" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$407</definedName>
-    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$408</definedName>
+    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$408</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="268">
   <si>
     <t>순번</t>
   </si>
@@ -871,9 +871,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>해운대센텀트루엘1단지직영건</t>
-  </si>
-  <si>
     <t>상무모아제일아파트</t>
   </si>
   <si>
@@ -888,6 +885,66 @@
   <si>
     <t>B</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>신화건설㈜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>광명노온수장</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>잔금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>성균관대역서희스타힐스 1,2단지아파트</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)모아씨앤에스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>해운대센텀트루엘1단지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>두레이앤씨(주)</t>
+  </si>
+  <si>
+    <t>월암창고</t>
+  </si>
+  <si>
+    <t>삼익세라믹1,2차</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>월산마을7단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>헬리오시티</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>조치원자이</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-06</t>
   </si>
   <si>
     <t>자재</t>
@@ -898,12 +955,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="181" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -1143,11 +1199,11 @@
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1322,6 +1378,9 @@
     <xf numFmtId="176" fontId="13" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="18">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
@@ -1343,7 +1402,52 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2032,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S407"/>
+  <dimension ref="A1:S409"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
@@ -2141,7 +2245,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2205,7 +2309,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -2264,7 +2368,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2362,7 +2466,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2418,7 +2522,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2467,7 +2571,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2518,7 +2622,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2570,7 +2674,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2709,7 +2813,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2765,7 +2869,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2814,7 +2918,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2863,7 +2967,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2910,7 +3014,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2957,7 +3061,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3004,7 +3108,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3051,7 +3155,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3098,7 +3202,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3147,7 +3251,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3196,7 +3300,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3245,7 +3349,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3294,7 +3398,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3343,7 +3447,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3392,7 +3496,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3441,7 +3545,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3490,7 +3594,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3539,7 +3643,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3588,7 +3692,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3637,7 +3741,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3686,7 +3790,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3735,7 +3839,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3784,7 +3888,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3833,7 +3937,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3878,7 +3982,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3932,7 +4036,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3988,7 +4092,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4041,7 +4145,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4088,7 +4192,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4142,7 +4246,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4247,7 +4351,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4298,7 +4402,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4342,7 +4446,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4386,7 +4490,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4433,7 +4537,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4480,7 +4584,7 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-258</v>
+        <v>-255</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4712,7 +4816,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4857,7 +4961,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4904,7 +5008,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4951,7 +5055,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4998,7 +5102,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -5283,7 +5387,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5327,7 +5431,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5369,7 +5473,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5411,7 +5515,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5552,7 +5656,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5604,7 +5708,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5749,7 +5853,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5774,7 +5878,7 @@
         <v>46034</v>
       </c>
       <c r="D77" s="10" t="str">
-        <f t="shared" ref="D77:D138" si="9">IF(G77="","",IF(OR(G77="선급금",G77="중도금",G77="잔금"),"A",IF(G77="자재","B",IF(G77="특허료","C",""))))</f>
+        <f t="shared" ref="D77:D139" si="9">IF(G77="","",IF(OR(G77="선급금",G77="중도금",G77="잔금"),"A",IF(G77="자재","B",IF(G77="특허료","C",""))))</f>
         <v>B</v>
       </c>
       <c r="E77" s="6" t="s">
@@ -5790,7 +5894,7 @@
         <v>2200000</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" ref="I77:I138" ca="1" si="10">IF(C77="","",IF(L77="",TODAY()-C77,L77-C77))</f>
+        <f t="shared" ref="I77:I139" ca="1" si="10">IF(C77="","",IF(L77="",TODAY()-C77,L77-C77))</f>
         <v>11</v>
       </c>
       <c r="J77" s="13" t="str">
@@ -5987,7 +6091,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6073,7 +6177,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6125,7 +6229,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6177,7 +6281,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6229,7 +6333,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6271,11 +6375,11 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K87" s="11"/>
       <c r="L87" s="11"/>
@@ -6367,7 +6471,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6419,7 +6523,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6515,7 +6619,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6689,7 +6793,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6775,7 +6879,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6817,7 +6921,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6858,7 +6962,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7031,7 +7135,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7073,7 +7177,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7114,7 +7218,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7158,7 +7262,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7199,7 +7303,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7240,7 +7344,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7281,7 +7385,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7370,7 +7474,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7459,7 +7563,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7504,10 +7608,10 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ref="J115:J148" ca="1" si="11">IF(I115="","",
+        <f t="shared" ref="J115:J157" ca="1" si="11">IF(I115="","",
  IF(G115="선급금",
    IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
  IF(G115="자재",
@@ -7601,7 +7705,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7687,7 +7791,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7820,7 +7924,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7862,7 +7966,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7904,7 +8008,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7946,7 +8050,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7964,35 +8068,28 @@
     </row>
     <row r="126" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B126" s="10">
-        <f>IF(C126="","",COUNTA($C$2:C126))</f>
         <v>125</v>
       </c>
-      <c r="C126" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="D126" s="10" t="str">
-        <f t="shared" si="9"/>
-        <v>B</v>
-      </c>
-      <c r="E126" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="F126" s="49" t="s">
-        <v>213</v>
+      <c r="C126" s="56">
+        <v>46080</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="E126" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="F126" s="55" t="s">
+        <v>253</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H126" s="50">
-        <v>6520600</v>
-      </c>
-      <c r="I126" s="6">
-        <f t="shared" ca="1" si="10"/>
-        <v>7</v>
-      </c>
-      <c r="J126" s="13" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v>정상</v>
+        <v>255</v>
+      </c>
+      <c r="H126" s="54">
+        <v>9036000</v>
+      </c>
+      <c r="J126" s="13" t="s">
+        <v>256</v>
       </c>
       <c r="K126" s="11"/>
       <c r="L126" s="11"/>
@@ -8009,28 +8106,28 @@
         <f>IF(C127="","",COUNTA($C$2:C127))</f>
         <v>126</v>
       </c>
-      <c r="C127" s="56" t="s">
-        <v>232</v>
+      <c r="C127" s="52" t="s">
+        <v>218</v>
       </c>
       <c r="D127" s="10" t="str">
         <f t="shared" si="9"/>
         <v>B</v>
       </c>
-      <c r="E127" s="55" t="s">
-        <v>227</v>
-      </c>
-      <c r="F127" s="53" t="s">
-        <v>219</v>
+      <c r="E127" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="F127" s="49" t="s">
+        <v>213</v>
       </c>
       <c r="G127" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H127" s="54">
-        <v>2330000</v>
+      <c r="H127" s="50">
+        <v>6520600</v>
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8059,20 +8156,20 @@
         <v>B</v>
       </c>
       <c r="E128" s="55" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="F128" s="53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G128" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H128" s="54">
-        <v>52200</v>
+        <v>2330000</v>
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8101,20 +8198,20 @@
         <v>B</v>
       </c>
       <c r="E129" s="55" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="F129" s="53" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G129" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H129" s="54">
-        <v>7624000</v>
+        <v>52200</v>
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8143,20 +8240,20 @@
         <v>B</v>
       </c>
       <c r="E130" s="55" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F130" s="53" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G130" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H130" s="54">
-        <v>4010000</v>
+        <v>7624000</v>
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8185,20 +8282,20 @@
         <v>B</v>
       </c>
       <c r="E131" s="55" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="F131" s="53" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G131" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H131" s="54">
-        <v>889500</v>
+        <v>4010000</v>
       </c>
       <c r="I131" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J131" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8227,20 +8324,20 @@
         <v>B</v>
       </c>
       <c r="E132" s="55" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="F132" s="53" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G132" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H132" s="54">
-        <v>2470000</v>
+        <v>889500</v>
       </c>
       <c r="I132" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J132" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8269,20 +8366,20 @@
         <v>B</v>
       </c>
       <c r="E133" s="55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F133" s="53" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G133" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H133" s="54">
-        <v>72937600</v>
+        <v>2470000</v>
       </c>
       <c r="I133" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J133" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8311,20 +8408,20 @@
         <v>B</v>
       </c>
       <c r="E134" s="55" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F134" s="53" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G134" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H134" s="54">
-        <v>5427900</v>
+        <v>72937600</v>
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8353,20 +8450,20 @@
         <v>B</v>
       </c>
       <c r="E135" s="55" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="F135" s="53" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="G135" s="6" t="s">
         <v>176</v>
       </c>
       <c r="H135" s="54">
-        <v>4470000</v>
+        <v>5427900</v>
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8387,37 +8484,35 @@
         <f>IF(C136="","",COUNTA($C$2:C136))</f>
         <v>135</v>
       </c>
-      <c r="C136" s="58">
-        <v>46085</v>
+      <c r="C136" s="56" t="s">
+        <v>232</v>
       </c>
       <c r="D136" s="10" t="str">
         <f t="shared" si="9"/>
-        <v>A</v>
-      </c>
-      <c r="E136" s="57" t="s">
-        <v>233</v>
-      </c>
-      <c r="F136" s="57" t="s">
-        <v>234</v>
+        <v>B</v>
+      </c>
+      <c r="E136" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="F136" s="53" t="s">
+        <v>206</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="H136" s="4">
-        <v>12360000</v>
+        <v>176</v>
+      </c>
+      <c r="H136" s="54">
+        <v>4470000</v>
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K136" s="11"/>
-      <c r="L136" s="11">
-        <v>46086</v>
-      </c>
+      <c r="L136" s="11"/>
       <c r="M136" s="10"/>
       <c r="N136" s="10" t="s">
         <v>33</v>
@@ -8439,27 +8534,29 @@
         <v>A</v>
       </c>
       <c r="E137" s="57" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F137" s="57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G137" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="H137" s="59">
-        <v>10474600</v>
+      <c r="H137" s="4">
+        <v>12360000</v>
       </c>
       <c r="I137" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J137" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K137" s="11"/>
-      <c r="L137" s="11"/>
+      <c r="L137" s="11">
+        <v>46086</v>
+      </c>
       <c r="M137" s="10"/>
       <c r="N137" s="10" t="s">
         <v>33</v>
@@ -8481,29 +8578,27 @@
         <v>A</v>
       </c>
       <c r="E138" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
+      </c>
+      <c r="F138" s="57" t="s">
+        <v>235</v>
       </c>
       <c r="G138" s="6" t="s">
         <v>237</v>
       </c>
       <c r="H138" s="59">
-        <v>9772000</v>
+        <v>10474600</v>
       </c>
       <c r="I138" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J138" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K138" s="11"/>
-      <c r="L138" s="11">
-        <v>46085</v>
-      </c>
+      <c r="L138" s="11"/>
       <c r="M138" s="10"/>
       <c r="N138" s="10" t="s">
         <v>33</v>
@@ -8518,34 +8613,36 @@
         <v>138</v>
       </c>
       <c r="C139" s="58">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="D139" s="10" t="str">
-        <f t="shared" ref="D139:D202" si="12">IF(G139="","",IF(OR(G139="선급금",G139="중도금",G139="잔금"),"A",IF(G139="자재","B",IF(G139="특허료","C",""))))</f>
+        <f t="shared" si="9"/>
         <v>A</v>
       </c>
       <c r="E139" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="F139" s="57" t="s">
-        <v>236</v>
+      <c r="F139" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="H139" s="61">
-        <v>19544000</v>
+        <v>237</v>
+      </c>
+      <c r="H139" s="59">
+        <v>9772000</v>
       </c>
       <c r="I139" s="6">
-        <f t="shared" ref="I139:I202" ca="1" si="13">IF(C139="","",IF(L139="",TODAY()-C139,L139-C139))</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
       </c>
       <c r="J139" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K139" s="11"/>
-      <c r="L139" s="11"/>
+      <c r="L139" s="11">
+        <v>46085</v>
+      </c>
       <c r="M139" s="10"/>
       <c r="N139" s="10" t="s">
         <v>33</v>
@@ -8563,24 +8660,24 @@
         <v>46086</v>
       </c>
       <c r="D140" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D140:D203" si="12">IF(G140="","",IF(OR(G140="선급금",G140="중도금",G140="잔금"),"A",IF(G140="자재","B",IF(G140="특허료","C",""))))</f>
         <v>A</v>
       </c>
-      <c r="E140" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>243</v>
+      <c r="E140" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="F140" s="57" t="s">
+        <v>236</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="H140" s="60" t="s">
-        <v>242</v>
+        <v>240</v>
+      </c>
+      <c r="H140" s="61">
+        <v>19544000</v>
       </c>
       <c r="I140" s="6">
-        <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <f t="shared" ref="I140:I203" ca="1" si="13">IF(C140="","",IF(L140="",TODAY()-C140,L140-C140))</f>
+        <v>4</v>
       </c>
       <c r="J140" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8604,24 +8701,25 @@
       <c r="C141" s="58">
         <v>46086</v>
       </c>
-      <c r="D141" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="E141" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="F141" s="23" t="s">
-        <v>204</v>
+      <c r="D141" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v>A</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>243</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="H141" s="25">
-        <v>577500</v>
+        <v>244</v>
+      </c>
+      <c r="H141" s="60" t="s">
+        <v>242</v>
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8646,23 +8744,23 @@
         <v>46086</v>
       </c>
       <c r="D142" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E142" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="F142" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="G142" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E142" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="F142" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="G142" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="H142" s="25">
-        <v>226000</v>
+        <v>577500</v>
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8687,23 +8785,23 @@
         <v>46086</v>
       </c>
       <c r="D143" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E143" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F143" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="G143" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E143" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F143" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="H143" s="25">
-        <v>23700</v>
+        <v>226000</v>
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8728,23 +8826,23 @@
         <v>46086</v>
       </c>
       <c r="D144" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E144" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F144" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="G144" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E144" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="F144" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="H144" s="25">
-        <v>16750</v>
+        <v>237000</v>
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8769,23 +8867,23 @@
         <v>46086</v>
       </c>
       <c r="D145" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E145" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="F145" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="G145" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E145" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="F145" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="H145" s="25">
-        <v>317960</v>
+        <v>167500</v>
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8810,23 +8908,23 @@
         <v>46086</v>
       </c>
       <c r="D146" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E146" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F146" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="G146" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E146" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="F146" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="G146" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="H146" s="25">
-        <v>550000</v>
+        <v>3179600</v>
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8851,7 +8949,7 @@
         <v>46086</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E147" s="23" t="s">
         <v>227</v>
@@ -8860,14 +8958,14 @@
         <v>219</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H147" s="25">
-        <v>180100</v>
+        <v>5500000</v>
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8892,23 +8990,23 @@
         <v>46086</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E148" s="23" t="s">
         <v>227</v>
       </c>
       <c r="F148" s="23" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H148" s="25">
-        <v>640050</v>
+        <v>1801000</v>
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8925,217 +9023,374 @@
       <c r="S148" s="10"/>
     </row>
     <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B149" s="10" t="str">
+      <c r="B149" s="10">
         <f>IF(C149="","",COUNTA($C$2:C149))</f>
-        <v/>
-      </c>
-      <c r="C149" s="11"/>
-      <c r="D149" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H149" s="4"/>
-      <c r="I149" s="6" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J149" s="13"/>
+        <v>148</v>
+      </c>
+      <c r="C149" s="58">
+        <v>46086</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E149" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F149" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H149" s="25">
+        <v>6400500</v>
+      </c>
+      <c r="I149" s="6">
+        <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
+        <v>4</v>
+      </c>
+      <c r="J149" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K149" s="11"/>
       <c r="L149" s="11"/>
       <c r="M149" s="10"/>
-      <c r="N149" s="10"/>
+      <c r="N149" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q149" s="11"/>
       <c r="R149" s="11"/>
       <c r="S149" s="10"/>
     </row>
     <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B150" s="10" t="str">
+      <c r="B150" s="10">
         <f>IF(C150="","",COUNTA($C$2:C150))</f>
-        <v/>
-      </c>
-      <c r="C150" s="11"/>
-      <c r="D150" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H150" s="4"/>
-      <c r="I150" s="6" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J150" s="13"/>
+        <v>149</v>
+      </c>
+      <c r="C150" s="58">
+        <v>46087</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H150" s="4">
+        <v>5358400</v>
+      </c>
+      <c r="I150" s="6">
+        <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
+        <v>3</v>
+      </c>
+      <c r="J150" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K150" s="11"/>
       <c r="L150" s="11"/>
       <c r="M150" s="10"/>
-      <c r="N150" s="10"/>
+      <c r="N150" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q150" s="11"/>
       <c r="R150" s="11"/>
       <c r="S150" s="10"/>
     </row>
     <row r="151" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B151" s="10" t="str">
+      <c r="B151" s="10">
         <f>IF(C151="","",COUNTA($C$2:C151))</f>
-        <v/>
-      </c>
-      <c r="C151" s="11"/>
-      <c r="D151" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H151" s="4"/>
-      <c r="I151" s="6" t="str">
+        <v>150</v>
+      </c>
+      <c r="C151" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E151" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F151" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H151" s="25">
+        <v>753000</v>
+      </c>
+      <c r="I151" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J151" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J151" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K151" s="11"/>
-      <c r="L151" s="11"/>
+      <c r="L151" s="11">
+        <v>46087</v>
+      </c>
       <c r="M151" s="10"/>
-      <c r="N151" s="10"/>
+      <c r="N151" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q151" s="11"/>
       <c r="R151" s="11"/>
       <c r="S151" s="10"/>
     </row>
     <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B152" s="10" t="str">
+      <c r="B152" s="10">
         <f>IF(C152="","",COUNTA($C$2:C152))</f>
-        <v/>
-      </c>
-      <c r="C152" s="11"/>
-      <c r="D152" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H152" s="4"/>
-      <c r="I152" s="6" t="str">
+        <v>151</v>
+      </c>
+      <c r="C152" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E152" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="F152" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H152" s="25">
+        <v>3230000</v>
+      </c>
+      <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J152" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J152" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K152" s="11"/>
       <c r="L152" s="11"/>
       <c r="M152" s="10"/>
-      <c r="N152" s="10"/>
+      <c r="N152" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q152" s="11"/>
       <c r="R152" s="11"/>
       <c r="S152" s="10"/>
     </row>
     <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B153" s="10" t="str">
+      <c r="B153" s="10">
         <f>IF(C153="","",COUNTA($C$2:C153))</f>
-        <v/>
-      </c>
-      <c r="C153" s="11"/>
-      <c r="D153" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H153" s="4"/>
-      <c r="I153" s="6" t="str">
+        <v>152</v>
+      </c>
+      <c r="C153" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E153" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F153" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H153" s="25">
+        <v>5030650</v>
+      </c>
+      <c r="I153" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J153" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J153" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K153" s="11"/>
-      <c r="L153" s="11"/>
+      <c r="L153" s="11">
+        <v>46087</v>
+      </c>
       <c r="M153" s="10"/>
-      <c r="N153" s="10"/>
+      <c r="N153" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q153" s="11"/>
       <c r="R153" s="11"/>
       <c r="S153" s="10"/>
     </row>
     <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B154" s="10" t="str">
+      <c r="B154" s="10">
         <f>IF(C154="","",COUNTA($C$2:C154))</f>
-        <v/>
-      </c>
-      <c r="C154" s="11"/>
-      <c r="D154" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H154" s="4"/>
-      <c r="I154" s="6" t="str">
+        <v>153</v>
+      </c>
+      <c r="C154" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="D154" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E154" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="F154" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H154" s="25">
+        <v>9140500</v>
+      </c>
+      <c r="I154" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J154" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J154" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K154" s="11"/>
       <c r="L154" s="11"/>
       <c r="M154" s="10"/>
-      <c r="N154" s="10"/>
+      <c r="N154" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q154" s="11"/>
       <c r="R154" s="11"/>
       <c r="S154" s="10"/>
     </row>
     <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B155" s="10" t="str">
+      <c r="B155" s="10">
         <f>IF(C155="","",COUNTA($C$2:C155))</f>
-        <v/>
-      </c>
-      <c r="C155" s="11"/>
-      <c r="D155" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H155" s="4"/>
-      <c r="I155" s="6" t="str">
+        <v>154</v>
+      </c>
+      <c r="C155" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E155" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="F155" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="G155" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H155" s="25">
+        <v>16695000</v>
+      </c>
+      <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J155" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J155" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K155" s="11"/>
       <c r="L155" s="11"/>
       <c r="M155" s="10"/>
-      <c r="N155" s="10"/>
+      <c r="N155" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q155" s="11"/>
       <c r="R155" s="11"/>
       <c r="S155" s="10"/>
     </row>
     <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B156" s="10" t="str">
+      <c r="B156" s="10">
         <f>IF(C156="","",COUNTA($C$2:C156))</f>
-        <v/>
-      </c>
-      <c r="C156" s="11"/>
-      <c r="D156" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H156" s="4"/>
-      <c r="I156" s="6" t="str">
+        <v>155</v>
+      </c>
+      <c r="C156" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E156" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="F156" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H156" s="25">
+        <v>1870000</v>
+      </c>
+      <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J156" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J156" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K156" s="11"/>
       <c r="L156" s="11"/>
       <c r="M156" s="10"/>
-      <c r="N156" s="10"/>
+      <c r="N156" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q156" s="11"/>
       <c r="R156" s="11"/>
       <c r="S156" s="10"/>
     </row>
     <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B157" s="10" t="str">
+      <c r="B157" s="10">
         <f>IF(C157="","",COUNTA($C$2:C157))</f>
-        <v/>
-      </c>
-      <c r="C157" s="11"/>
-      <c r="D157" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H157" s="4"/>
-      <c r="I157" s="6" t="str">
+        <v>156</v>
+      </c>
+      <c r="C157" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E157" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F157" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H157" s="25">
+        <v>12478000</v>
+      </c>
+      <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J157" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J157" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K157" s="11"/>
       <c r="L157" s="11"/>
       <c r="M157" s="10"/>
-      <c r="N157" s="10"/>
+      <c r="N157" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q157" s="11"/>
       <c r="R157" s="11"/>
       <c r="S157" s="10"/>
@@ -10227,12 +10482,12 @@
       </c>
       <c r="C203" s="11"/>
       <c r="D203" s="10" t="str">
-        <f t="shared" ref="D203:D266" si="14">IF(G203="","",IF(OR(G203="선급금",G203="중도금",G203="잔금"),"A",IF(G203="자재","B",IF(G203="특허료","C",""))))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="H203" s="4"/>
       <c r="I203" s="6" t="str">
-        <f t="shared" ref="I203:I266" ca="1" si="15">IF(C203="","",IF(L203="",TODAY()-C203,L203-C203))</f>
+        <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
       <c r="J203" s="13"/>
@@ -10251,12 +10506,12 @@
       </c>
       <c r="C204" s="11"/>
       <c r="D204" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="D204:D267" si="14">IF(G204="","",IF(OR(G204="선급금",G204="중도금",G204="잔금"),"A",IF(G204="자재","B",IF(G204="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ref="I204:I267" ca="1" si="15">IF(C204="","",IF(L204="",TODAY()-C204,L204-C204))</f>
         <v/>
       </c>
       <c r="J204" s="13"/>
@@ -10413,7 +10668,10 @@
       <c r="S210" s="10"/>
     </row>
     <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B211" s="10"/>
+      <c r="B211" s="10" t="str">
+        <f>IF(C211="","",COUNTA($C$2:C211))</f>
+        <v/>
+      </c>
       <c r="C211" s="11"/>
       <c r="D211" s="10" t="str">
         <f t="shared" si="14"/>
@@ -11592,12 +11850,12 @@
       <c r="B267" s="10"/>
       <c r="C267" s="11"/>
       <c r="D267" s="10" t="str">
-        <f t="shared" ref="D267:D330" si="16">IF(G267="","",IF(OR(G267="선급금",G267="중도금",G267="잔금"),"A",IF(G267="자재","B",IF(G267="특허료","C",""))))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H267" s="4"/>
       <c r="I267" s="6" t="str">
-        <f t="shared" ref="I267:I330" ca="1" si="17">IF(C267="","",IF(L267="",TODAY()-C267,L267-C267))</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="J267" s="13"/>
@@ -11613,12 +11871,12 @@
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
       <c r="D268" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="D268:D331" si="16">IF(G268="","",IF(OR(G268="선급금",G268="중도금",G268="잔금"),"A",IF(G268="자재","B",IF(G268="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ref="I268:I331" ca="1" si="17">IF(C268="","",IF(L268="",TODAY()-C268,L268-C268))</f>
         <v/>
       </c>
       <c r="J268" s="13"/>
@@ -12936,12 +13194,12 @@
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
       <c r="D331" s="10" t="str">
-        <f t="shared" ref="D331:D394" si="18">IF(G331="","",IF(OR(G331="선급금",G331="중도금",G331="잔금"),"A",IF(G331="자재","B",IF(G331="특허료","C",""))))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H331" s="4"/>
       <c r="I331" s="6" t="str">
-        <f t="shared" ref="I331:I394" ca="1" si="19">IF(C331="","",IF(L331="",TODAY()-C331,L331-C331))</f>
+        <f t="shared" ca="1" si="17"/>
         <v/>
       </c>
       <c r="J331" s="13"/>
@@ -12957,12 +13215,12 @@
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="D332:D395" si="18">IF(G332="","",IF(OR(G332="선급금",G332="중도금",G332="잔금"),"A",IF(G332="자재","B",IF(G332="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ref="I332:I395" ca="1" si="19">IF(C332="","",IF(L332="",TODAY()-C332,L332-C332))</f>
         <v/>
       </c>
       <c r="J332" s="13"/>
@@ -14280,12 +14538,12 @@
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
       <c r="D395" s="10" t="str">
-        <f t="shared" ref="D395:D407" si="20">IF(G395="","",IF(OR(G395="선급금",G395="중도금",G395="잔금"),"A",IF(G395="자재","B",IF(G395="특허료","C",""))))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H395" s="4"/>
       <c r="I395" s="6" t="str">
-        <f t="shared" ref="I395:I405" ca="1" si="21">IF(C395="","",IF(L395="",TODAY()-C395,L395-C395))</f>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J395" s="13"/>
@@ -14301,12 +14559,12 @@
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D396:D408" si="20">IF(G396="","",IF(OR(G396="선급금",G396="중도금",G396="잔금"),"A",IF(G396="자재","B",IF(G396="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H396" s="4"/>
       <c r="I396" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ref="I396:I406" ca="1" si="21">IF(C396="","",IF(L396="",TODAY()-C396,L396-C396))</f>
         <v/>
       </c>
       <c r="J396" s="13"/>
@@ -14423,21 +14681,26 @@
       <c r="R401" s="11"/>
       <c r="S401" s="10"/>
     </row>
-    <row r="402" spans="2:19">
+    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
-      <c r="D402" s="1" t="str">
+      <c r="D402" s="10" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I402" s="1" t="str">
+      <c r="H402" s="4"/>
+      <c r="I402" s="6" t="str">
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
+      <c r="J402" s="13"/>
       <c r="K402" s="11"/>
       <c r="L402" s="11"/>
+      <c r="M402" s="10"/>
+      <c r="N402" s="10"/>
       <c r="Q402" s="11"/>
       <c r="R402" s="11"/>
+      <c r="S402" s="10"/>
     </row>
     <row r="403" spans="2:19">
       <c r="B403" s="10"/>
@@ -14466,6 +14729,8 @@
         <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
+      <c r="K404" s="11"/>
+      <c r="L404" s="11"/>
       <c r="Q404" s="11"/>
       <c r="R404" s="11"/>
     </row>
@@ -14490,6 +14755,10 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
+      <c r="I406" s="1" t="str">
+        <f t="shared" ca="1" si="21"/>
+        <v/>
+      </c>
       <c r="Q406" s="11"/>
       <c r="R406" s="11"/>
     </row>
@@ -14503,137 +14772,171 @@
       <c r="Q407" s="11"/>
       <c r="R407" s="11"/>
     </row>
+    <row r="408" spans="2:19">
+      <c r="B408" s="10"/>
+      <c r="C408" s="11"/>
+      <c r="D408" s="1" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="Q408" s="11"/>
+      <c r="R408" s="11"/>
+    </row>
+    <row r="409" spans="2:19" ht="16.5" customHeight="1">
+      <c r="C409" s="58"/>
+      <c r="F409" s="62"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S407"/>
+  <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="25" priority="38">
+    <cfRule type="expression" dxfId="28" priority="43">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="24" priority="37">
+    <cfRule type="expression" dxfId="27" priority="42">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="23" priority="36">
+    <cfRule type="expression" dxfId="26" priority="41">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="22" priority="35">
+    <cfRule type="expression" dxfId="25" priority="40">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="21" priority="30">
+    <cfRule type="expression" dxfId="24" priority="35">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="23" priority="25">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="22" priority="24">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="18" priority="17">
+    <cfRule type="expression" dxfId="21" priority="22">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="17" priority="16">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="16" priority="15">
+    <cfRule type="expression" dxfId="19" priority="20">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="15" priority="14">
+    <cfRule type="expression" dxfId="18" priority="19">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="14" priority="13">
+    <cfRule type="expression" dxfId="17" priority="18">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="13" priority="12">
+    <cfRule type="expression" dxfId="16" priority="17">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="12" priority="11">
+    <cfRule type="expression" dxfId="15" priority="16">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="12" priority="13">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F141:F148">
-    <cfRule type="expression" dxfId="4" priority="3">
-      <formula>$J141="잔금"</formula>
+  <conditionalFormatting sqref="F142:F149">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E141:E148">
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>$J141="잔금"</formula>
+  <conditionalFormatting sqref="E142:E149">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H141:H148">
+  <conditionalFormatting sqref="H142:H149">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$J142="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E151:E157">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$J151="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F151:F157">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$J151="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C151:C157">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J151="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H151:H157">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J141="잔금"</formula>
+      <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N148">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N157">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D407">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D408">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="270">
   <si>
     <t>순번</t>
   </si>
@@ -854,11 +854,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 20,124,400 
-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>E편한세상한강신도시2차 아파트</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -948,6 +943,18 @@
   </si>
   <si>
     <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">계산서 발급 기록 누락으로 미수확인 늦음 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>발주처 정산지연</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>내부 시스템 오류로 업무정상화 복구기간소요</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1402,22 +1409,7 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="29">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <fill>
         <patternFill>
@@ -4416,6 +4408,9 @@
       <c r="N45" s="10" t="s">
         <v>33</v>
       </c>
+      <c r="P45" s="6" t="s">
+        <v>268</v>
+      </c>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
       <c r="S45" s="10"/>
@@ -4459,6 +4454,9 @@
       <c r="M46" s="10"/>
       <c r="N46" s="10" t="s">
         <v>33</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>268</v>
       </c>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
@@ -4595,6 +4593,9 @@
       <c r="M49" s="10"/>
       <c r="N49" s="10" t="s">
         <v>201</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="Q49" s="11"/>
       <c r="R49" s="11"/>
@@ -5265,6 +5266,9 @@
       <c r="N63" s="10" t="s">
         <v>33</v>
       </c>
+      <c r="P63" s="6" t="s">
+        <v>269</v>
+      </c>
       <c r="Q63" s="14"/>
       <c r="R63" s="14"/>
       <c r="S63" s="10"/>
@@ -5310,6 +5314,9 @@
       <c r="M64" s="10"/>
       <c r="N64" s="10" t="s">
         <v>33</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>269</v>
       </c>
       <c r="Q64" s="14"/>
       <c r="R64" s="14"/>
@@ -8074,22 +8081,22 @@
         <v>46080</v>
       </c>
       <c r="D126" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E126" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="F126" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="G126" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="E126" s="55" t="s">
-        <v>252</v>
-      </c>
-      <c r="F126" s="55" t="s">
-        <v>253</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="H126" s="54">
         <v>9036000</v>
       </c>
       <c r="J126" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K126" s="11"/>
       <c r="L126" s="11"/>
@@ -8706,16 +8713,16 @@
         <v>A</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F141" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G141" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="G141" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="H141" s="60" t="s">
-        <v>242</v>
+      <c r="H141" s="60">
+        <v>20124400</v>
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -8744,7 +8751,7 @@
         <v>46086</v>
       </c>
       <c r="D142" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E142" s="23" t="s">
         <v>203</v>
@@ -8753,7 +8760,7 @@
         <v>204</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H142" s="25">
         <v>577500</v>
@@ -8785,7 +8792,7 @@
         <v>46086</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E143" s="23" t="s">
         <v>215</v>
@@ -8794,7 +8801,7 @@
         <v>210</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H143" s="25">
         <v>226000</v>
@@ -8826,16 +8833,16 @@
         <v>46086</v>
       </c>
       <c r="D144" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E144" s="23" t="s">
         <v>26</v>
       </c>
       <c r="F144" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H144" s="25">
         <v>237000</v>
@@ -8867,16 +8874,16 @@
         <v>46086</v>
       </c>
       <c r="D145" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="E145" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="F145" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="G145" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="E145" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="F145" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="H145" s="25">
         <v>167500</v>
@@ -8908,16 +8915,16 @@
         <v>46086</v>
       </c>
       <c r="D146" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E146" s="23" t="s">
         <v>128</v>
       </c>
       <c r="F146" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H146" s="25">
         <v>3179600</v>
@@ -8949,7 +8956,7 @@
         <v>46086</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E147" s="23" t="s">
         <v>227</v>
@@ -8958,7 +8965,7 @@
         <v>219</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H147" s="25">
         <v>5500000</v>
@@ -8990,7 +8997,7 @@
         <v>46086</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E148" s="23" t="s">
         <v>227</v>
@@ -8999,7 +9006,7 @@
         <v>219</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H148" s="25">
         <v>1801000</v>
@@ -9031,16 +9038,16 @@
         <v>46086</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E149" s="23" t="s">
         <v>227</v>
       </c>
       <c r="F149" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H149" s="25">
         <v>6400500</v>
@@ -9072,13 +9079,13 @@
         <v>46087</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G150" s="6" t="s">
         <v>237</v>
@@ -9110,7 +9117,7 @@
         <v>150</v>
       </c>
       <c r="C151" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D151" s="10" t="s">
         <v>182</v>
@@ -9119,10 +9126,10 @@
         <v>126</v>
       </c>
       <c r="F151" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H151" s="25">
         <v>753000</v>
@@ -9153,7 +9160,7 @@
         <v>151</v>
       </c>
       <c r="C152" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D152" s="10" t="s">
         <v>182</v>
@@ -9162,10 +9169,10 @@
         <v>203</v>
       </c>
       <c r="F152" s="23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H152" s="25">
         <v>3230000</v>
@@ -9194,7 +9201,7 @@
         <v>152</v>
       </c>
       <c r="C153" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D153" s="10" t="s">
         <v>182</v>
@@ -9203,10 +9210,10 @@
         <v>130</v>
       </c>
       <c r="F153" s="23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H153" s="25">
         <v>5030650</v>
@@ -9237,19 +9244,19 @@
         <v>153</v>
       </c>
       <c r="C154" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D154" s="10" t="s">
         <v>182</v>
       </c>
       <c r="E154" s="23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F154" s="23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H154" s="25">
         <v>9140500</v>
@@ -9278,7 +9285,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>182</v>
@@ -9290,7 +9297,7 @@
         <v>222</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H155" s="25">
         <v>16695000</v>
@@ -9319,7 +9326,7 @@
         <v>155</v>
       </c>
       <c r="C156" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D156" s="10" t="s">
         <v>182</v>
@@ -9331,7 +9338,7 @@
         <v>222</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H156" s="25">
         <v>1870000</v>
@@ -9360,7 +9367,7 @@
         <v>156</v>
       </c>
       <c r="C157" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D157" s="10" t="s">
         <v>182</v>
@@ -9369,10 +9376,10 @@
         <v>82</v>
       </c>
       <c r="F157" s="23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H157" s="25">
         <v>12478000</v>
@@ -14790,122 +14797,122 @@
   <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="28" priority="43">
+    <cfRule type="expression" dxfId="27" priority="43">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="27" priority="42">
+    <cfRule type="expression" dxfId="26" priority="42">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="26" priority="41">
+    <cfRule type="expression" dxfId="25" priority="41">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="25" priority="40">
+    <cfRule type="expression" dxfId="24" priority="40">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="24" priority="35">
+    <cfRule type="expression" dxfId="23" priority="35">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="23" priority="25">
+    <cfRule type="expression" dxfId="22" priority="25">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="22" priority="24">
+    <cfRule type="expression" dxfId="21" priority="24">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="20" priority="22">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="20" priority="21">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="18" priority="20">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="14" priority="16">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="12" priority="14">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="11" priority="13">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="281">
   <si>
     <t>순번</t>
   </si>
@@ -955,6 +955,47 @@
   </si>
   <si>
     <t>내부 시스템 오류로 업무정상화 복구기간소요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>성원아파트2단지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>주식회사 유광씨앤씨</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선급금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>은하마을주공1단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>헬리오시티</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>검단우방아이유쉘</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>무등산광신프로그레스</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)정민씨앤씨</t>
+  </si>
+  <si>
+    <t>(주)수안건설</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>자재</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1210,7 +1251,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1388,6 +1429,9 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="13" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="18">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
@@ -1409,7 +1453,82 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="33">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2237,7 +2356,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2301,7 +2420,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -2360,7 +2479,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2458,7 +2577,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2514,7 +2633,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2563,7 +2682,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2614,7 +2733,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2666,7 +2785,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2805,7 +2924,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2861,7 +2980,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2910,7 +3029,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2959,7 +3078,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3006,7 +3125,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3053,7 +3172,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3100,7 +3219,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3147,7 +3266,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3194,7 +3313,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3243,7 +3362,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3292,7 +3411,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3341,7 +3460,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3390,7 +3509,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3439,7 +3558,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3488,7 +3607,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3537,7 +3656,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3586,7 +3705,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3635,7 +3754,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3684,7 +3803,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3733,7 +3852,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3782,7 +3901,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3831,7 +3950,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3880,7 +3999,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3929,7 +4048,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3974,7 +4093,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4028,7 +4147,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4084,7 +4203,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4137,7 +4256,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4184,7 +4303,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4238,7 +4357,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4343,7 +4462,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4394,7 +4513,7 @@
       </c>
       <c r="I45" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J45" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4441,7 +4560,7 @@
       </c>
       <c r="I46" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J46" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4488,7 +4607,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4535,7 +4654,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4562,7 +4681,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="11">
-        <v>46345</v>
+        <v>45980</v>
       </c>
       <c r="D49" s="10" t="str">
         <f t="shared" si="0"/>
@@ -4582,13 +4701,15 @@
       </c>
       <c r="I49" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>-255</v>
+        <v>111</v>
       </c>
       <c r="J49" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>정상</v>
-      </c>
-      <c r="K49" s="11"/>
+        <v>장기미수</v>
+      </c>
+      <c r="K49" s="11">
+        <v>46112</v>
+      </c>
       <c r="L49" s="11"/>
       <c r="M49" s="10"/>
       <c r="N49" s="10" t="s">
@@ -4817,7 +4938,7 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4962,7 +5083,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5009,7 +5130,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5056,7 +5177,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5103,7 +5224,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -5394,7 +5515,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5438,7 +5559,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5480,7 +5601,7 @@
       </c>
       <c r="I68" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J68" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5522,7 +5643,7 @@
       </c>
       <c r="I69" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J69" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5663,7 +5784,7 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5715,7 +5836,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5860,7 +5981,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6098,7 +6219,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6184,7 +6305,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6236,7 +6357,7 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6288,7 +6409,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6340,7 +6461,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6382,7 +6503,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6478,7 +6599,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6530,7 +6651,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6626,7 +6747,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6800,7 +6921,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6886,7 +7007,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6928,7 +7049,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6969,7 +7090,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7142,7 +7263,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7184,7 +7305,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7225,7 +7346,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7269,7 +7390,7 @@
       </c>
       <c r="I107" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J107" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7310,7 +7431,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7351,7 +7472,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7392,7 +7513,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7481,7 +7602,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7570,7 +7691,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7615,10 +7736,10 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ref="J115:J157" ca="1" si="11">IF(I115="","",
+        <f t="shared" ref="J115:J162" ca="1" si="11">IF(I115="","",
  IF(G115="선급금",
    IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
  IF(G115="자재",
@@ -7712,7 +7833,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7798,7 +7919,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7931,7 +8052,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7973,7 +8094,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8015,7 +8136,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8057,7 +8178,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8134,7 +8255,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8176,7 +8297,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8218,7 +8339,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8260,7 +8381,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8302,7 +8423,7 @@
       </c>
       <c r="I131" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J131" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8344,7 +8465,7 @@
       </c>
       <c r="I132" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J132" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8386,7 +8507,7 @@
       </c>
       <c r="I133" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J133" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8428,7 +8549,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8470,7 +8591,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8512,7 +8633,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8598,7 +8719,7 @@
       </c>
       <c r="I138" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J138" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8691,7 +8812,9 @@
         <v>정상</v>
       </c>
       <c r="K140" s="11"/>
-      <c r="L140" s="11"/>
+      <c r="L140" s="11">
+        <v>46090</v>
+      </c>
       <c r="M140" s="10"/>
       <c r="N140" s="10" t="s">
         <v>33</v>
@@ -8726,7 +8849,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8767,7 +8890,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8808,7 +8931,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8849,7 +8972,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8890,7 +9013,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8931,7 +9054,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8972,7 +9095,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9013,7 +9136,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9054,7 +9177,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9095,7 +9218,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9179,7 +9302,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9263,7 +9386,7 @@
       </c>
       <c r="I154" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J154" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9304,7 +9427,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9345,7 +9468,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9386,7 +9509,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9403,121 +9526,211 @@
       <c r="S157" s="10"/>
     </row>
     <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B158" s="10" t="str">
+      <c r="B158" s="10">
         <f>IF(C158="","",COUNTA($C$2:C158))</f>
-        <v/>
-      </c>
-      <c r="C158" s="11"/>
+        <v>157</v>
+      </c>
+      <c r="C158" s="63">
+        <v>46090</v>
+      </c>
       <c r="D158" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H158" s="4"/>
-      <c r="I158" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H158" s="4">
+        <v>29070400</v>
+      </c>
+      <c r="I158" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J158" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J158" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K158" s="11"/>
       <c r="L158" s="11"/>
       <c r="M158" s="10"/>
-      <c r="N158" s="10"/>
+      <c r="N158" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q158" s="11"/>
       <c r="R158" s="11"/>
       <c r="S158" s="10"/>
     </row>
     <row r="159" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B159" s="10" t="str">
+      <c r="B159" s="10">
         <f>IF(C159="","",COUNTA($C$2:C159))</f>
-        <v/>
-      </c>
-      <c r="C159" s="11"/>
+        <v>158</v>
+      </c>
+      <c r="C159" s="35" t="s">
+        <v>279</v>
+      </c>
       <c r="D159" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H159" s="4"/>
-      <c r="I159" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E159" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="F159" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H159" s="25">
+        <v>3390000</v>
+      </c>
+      <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J159" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J159" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K159" s="11"/>
       <c r="L159" s="11"/>
       <c r="M159" s="10"/>
-      <c r="N159" s="10"/>
+      <c r="N159" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q159" s="11"/>
       <c r="R159" s="11"/>
       <c r="S159" s="10"/>
     </row>
     <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B160" s="10" t="str">
+      <c r="B160" s="10">
         <f>IF(C160="","",COUNTA($C$2:C160))</f>
-        <v/>
-      </c>
-      <c r="C160" s="11"/>
+        <v>159</v>
+      </c>
+      <c r="C160" s="35" t="s">
+        <v>279</v>
+      </c>
       <c r="D160" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H160" s="4"/>
-      <c r="I160" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E160" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="F160" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H160" s="25">
+        <v>9140500</v>
+      </c>
+      <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J160" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J160" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K160" s="11"/>
       <c r="L160" s="11"/>
       <c r="M160" s="10"/>
-      <c r="N160" s="10"/>
+      <c r="N160" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q160" s="11"/>
       <c r="R160" s="11"/>
       <c r="S160" s="10"/>
     </row>
     <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B161" s="10" t="str">
+      <c r="B161" s="10">
         <f>IF(C161="","",COUNTA($C$2:C161))</f>
-        <v/>
-      </c>
-      <c r="C161" s="11"/>
+        <v>160</v>
+      </c>
+      <c r="C161" s="35" t="s">
+        <v>279</v>
+      </c>
       <c r="D161" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H161" s="4"/>
-      <c r="I161" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E161" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F161" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H161" s="25">
+        <v>4719500</v>
+      </c>
+      <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J161" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J161" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K161" s="11"/>
       <c r="L161" s="11"/>
       <c r="M161" s="10"/>
-      <c r="N161" s="10"/>
+      <c r="N161" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q161" s="11"/>
       <c r="R161" s="11"/>
       <c r="S161" s="10"/>
     </row>
     <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B162" s="10" t="str">
+      <c r="B162" s="10">
         <f>IF(C162="","",COUNTA($C$2:C162))</f>
-        <v/>
-      </c>
-      <c r="C162" s="11"/>
+        <v>161</v>
+      </c>
+      <c r="C162" s="35" t="s">
+        <v>279</v>
+      </c>
       <c r="D162" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H162" s="4"/>
-      <c r="I162" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E162" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="F162" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H162" s="25">
+        <v>38534600</v>
+      </c>
+      <c r="I162" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J162" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J162" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K162" s="11"/>
       <c r="L162" s="11"/>
       <c r="M162" s="10"/>
-      <c r="N162" s="10"/>
+      <c r="N162" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q162" s="11"/>
       <c r="R162" s="11"/>
       <c r="S162" s="10"/>
@@ -14797,150 +15010,175 @@
   <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="27" priority="43">
+    <cfRule type="expression" dxfId="32" priority="48">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="26" priority="42">
+    <cfRule type="expression" dxfId="31" priority="47">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="25" priority="41">
+    <cfRule type="expression" dxfId="30" priority="46">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="24" priority="40">
+    <cfRule type="expression" dxfId="29" priority="45">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="23" priority="35">
+    <cfRule type="expression" dxfId="28" priority="40">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="22" priority="25">
+    <cfRule type="expression" dxfId="27" priority="30">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="21" priority="24">
+    <cfRule type="expression" dxfId="26" priority="29">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="20" priority="22">
+    <cfRule type="expression" dxfId="25" priority="27">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="24" priority="26">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="18" priority="20">
+    <cfRule type="expression" dxfId="23" priority="25">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="22" priority="24">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="16" priority="18">
+    <cfRule type="expression" dxfId="21" priority="23">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="15" priority="17">
+    <cfRule type="expression" dxfId="20" priority="22">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="18" priority="20">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="12" priority="14">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="11" priority="13">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="14" priority="16">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="12" priority="14">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="11" priority="13">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$J151="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C158">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$I158="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F159:F162">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$J159="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E159:E162">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$J159="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C159:C162">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J159="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H159:H162">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J151="잔금"</formula>
+      <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N157">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N162">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D408">

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="311">
   <si>
     <t>순번</t>
   </si>
@@ -993,6 +993,118 @@
   </si>
   <si>
     <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>동탄역시범한화꿈에그린프레스티지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)석민이앤씨</t>
+  </si>
+  <si>
+    <t>선급금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>갈매스타힐스아파트</t>
+  </si>
+  <si>
+    <t>이루미건설㈜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>선급금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현마을8단지아파트</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>동일산건㈜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>수원로얄팰리스</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>오창2지구대원칸타빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>효천1중흥S클래스에코시티</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>헬리오시티</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>시흥참이슬아파트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>무지개마을신한건영</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠실리센츠</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>월산마을7단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>수지동보1차</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>오성빌라</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>주택</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>도경오벨리스</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>본사사무실</t>
+  </si>
+  <si>
+    <t>등촌임광그린</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>오양힐타운</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>해운대센텀트루엘1단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>주식회사 이산이씨에프</t>
+  </si>
+  <si>
+    <t>(주)세원산업개발</t>
+  </si>
+  <si>
+    <t>(주)청람건설</t>
   </si>
   <si>
     <t>자재</t>
@@ -1453,7 +1565,172 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="44">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2247,6 +2524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S409"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
@@ -2331,7 +2609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B2" s="10">
         <v>1</v>
       </c>
@@ -2356,7 +2634,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2394,7 +2672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="3" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B3" s="10">
         <f>IF(C3="","",COUNTA($C$2:C3))</f>
         <v>2</v>
@@ -2420,7 +2698,7 @@
       </c>
       <c r="I3" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J3" s="13" t="str">
         <f t="shared" ref="J3:J59" ca="1" si="2">IF(I3="","",
@@ -2437,7 +2715,9 @@
       <c r="K3" s="11">
         <v>46111</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="11">
+        <v>46092</v>
+      </c>
       <c r="M3" s="10" t="s">
         <v>153</v>
       </c>
@@ -2453,7 +2733,7 @@
       </c>
       <c r="S3" s="10"/>
     </row>
-    <row r="4" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="4" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B4" s="10">
         <f>IF(C4="","",COUNTA($C$2:C4))</f>
         <v>3</v>
@@ -2479,7 +2759,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2505,7 +2785,7 @@
       </c>
       <c r="S4" s="10"/>
     </row>
-    <row r="5" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="5" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B5" s="10">
         <f>IF(C5="","",COUNTA($C$2:C5))</f>
         <v>4</v>
@@ -2551,7 +2831,7 @@
       <c r="R5" s="14"/>
       <c r="S5" s="10"/>
     </row>
-    <row r="6" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="6" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B6" s="10">
         <f>IF(C6="","",COUNTA($C$2:C6))</f>
         <v>5</v>
@@ -2577,7 +2857,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2607,7 +2887,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="7" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B7" s="10">
         <f>IF(C7="","",COUNTA($C$2:C7))</f>
         <v>6</v>
@@ -2633,7 +2913,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2656,7 +2936,7 @@
       </c>
       <c r="S7" s="10"/>
     </row>
-    <row r="8" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="8" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B8" s="10">
         <f>IF(C8="","",COUNTA($C$2:C8))</f>
         <v>7</v>
@@ -2682,7 +2962,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2707,7 +2987,7 @@
       </c>
       <c r="S8" s="10"/>
     </row>
-    <row r="9" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="9" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B9" s="10">
         <f>IF(C9="","",COUNTA($C$2:C9))</f>
         <v>8</v>
@@ -2733,7 +3013,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2759,7 +3039,7 @@
       </c>
       <c r="S9" s="10"/>
     </row>
-    <row r="10" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="10" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B10" s="10">
         <f>IF(C10="","",COUNTA($C$2:C10))</f>
         <v>9</v>
@@ -2785,7 +3065,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2803,7 +3083,7 @@
       <c r="R10" s="14"/>
       <c r="S10" s="10"/>
     </row>
-    <row r="11" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="11" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B11" s="10">
         <f>IF(C11="","",COUNTA($C$2:C11))</f>
         <v>10</v>
@@ -2852,7 +3132,7 @@
       <c r="R11" s="14"/>
       <c r="S11" s="10"/>
     </row>
-    <row r="12" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="12" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B12" s="10">
         <f>IF(C12="","",COUNTA($C$2:C12))</f>
         <v>11</v>
@@ -2898,7 +3178,7 @@
       <c r="R12" s="14"/>
       <c r="S12" s="10"/>
     </row>
-    <row r="13" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="13" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B13" s="10">
         <f>IF(C13="","",COUNTA($C$2:C13))</f>
         <v>12</v>
@@ -2924,7 +3204,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2954,7 +3234,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="14" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B14" s="10">
         <f>IF(C14="","",COUNTA($C$2:C14))</f>
         <v>13</v>
@@ -2980,7 +3260,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3003,7 +3283,7 @@
       </c>
       <c r="S14" s="10"/>
     </row>
-    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B15" s="10">
         <f>IF(C15="","",COUNTA($C$2:C15))</f>
         <v>14</v>
@@ -3029,7 +3309,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3052,7 +3332,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B16" s="10">
         <f>IF(C16="","",COUNTA($C$2:C16))</f>
         <v>15</v>
@@ -3078,7 +3358,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3099,7 +3379,7 @@
       <c r="R16" s="14"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B17" s="10">
         <f>IF(C17="","",COUNTA($C$2:C17))</f>
         <v>16</v>
@@ -3125,7 +3405,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3146,7 +3426,7 @@
       <c r="R17" s="14"/>
       <c r="S17" s="10"/>
     </row>
-    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B18" s="10">
         <f>IF(C18="","",COUNTA($C$2:C18))</f>
         <v>17</v>
@@ -3172,7 +3452,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3193,7 +3473,7 @@
       <c r="R18" s="14"/>
       <c r="S18" s="10"/>
     </row>
-    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B19" s="10">
         <f>IF(C19="","",COUNTA($C$2:C19))</f>
         <v>18</v>
@@ -3219,7 +3499,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3240,7 +3520,7 @@
       <c r="R19" s="14"/>
       <c r="S19" s="10"/>
     </row>
-    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B20" s="10">
         <f>IF(C20="","",COUNTA($C$2:C20))</f>
         <v>19</v>
@@ -3266,7 +3546,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3287,7 +3567,7 @@
       <c r="R20" s="14"/>
       <c r="S20" s="10"/>
     </row>
-    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B21" s="10">
         <f>IF(C21="","",COUNTA($C$2:C21))</f>
         <v>20</v>
@@ -3313,7 +3593,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3336,7 +3616,7 @@
       </c>
       <c r="S21" s="10"/>
     </row>
-    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B22" s="10">
         <f>IF(C22="","",COUNTA($C$2:C22))</f>
         <v>21</v>
@@ -3362,7 +3642,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3385,7 +3665,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B23" s="10">
         <f>IF(C23="","",COUNTA($C$2:C23))</f>
         <v>22</v>
@@ -3411,7 +3691,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3434,7 +3714,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B24" s="10">
         <f>IF(C24="","",COUNTA($C$2:C24))</f>
         <v>23</v>
@@ -3460,7 +3740,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3483,7 +3763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B25" s="10">
         <f>IF(C25="","",COUNTA($C$2:C25))</f>
         <v>24</v>
@@ -3509,7 +3789,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3532,7 +3812,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B26" s="10">
         <f>IF(C26="","",COUNTA($C$2:C26))</f>
         <v>25</v>
@@ -3558,7 +3838,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3581,7 +3861,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B27" s="10">
         <f>IF(C27="","",COUNTA($C$2:C27))</f>
         <v>26</v>
@@ -3607,7 +3887,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3630,7 +3910,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B28" s="10">
         <f>IF(C28="","",COUNTA($C$2:C28))</f>
         <v>27</v>
@@ -3656,7 +3936,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3679,7 +3959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B29" s="10">
         <f>IF(C29="","",COUNTA($C$2:C29))</f>
         <v>28</v>
@@ -3705,7 +3985,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3728,7 +4008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B30" s="10">
         <f>IF(C30="","",COUNTA($C$2:C30))</f>
         <v>29</v>
@@ -3754,7 +4034,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3777,7 +4057,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B31" s="10">
         <f>IF(C31="","",COUNTA($C$2:C31))</f>
         <v>30</v>
@@ -3803,7 +4083,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3826,7 +4106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B32" s="10">
         <f>IF(C32="","",COUNTA($C$2:C32))</f>
         <v>31</v>
@@ -3852,7 +4132,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3875,7 +4155,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B33" s="10">
         <f>IF(C33="","",COUNTA($C$2:C33))</f>
         <v>32</v>
@@ -3901,7 +4181,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3924,7 +4204,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B34" s="10">
         <f>IF(C34="","",COUNTA($C$2:C34))</f>
         <v>33</v>
@@ -3950,7 +4230,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3973,7 +4253,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B35" s="10">
         <f>IF(C35="","",COUNTA($C$2:C35))</f>
         <v>34</v>
@@ -3999,7 +4279,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4022,7 +4302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B36" s="10">
         <f>IF(C36="","",COUNTA($C$2:C36))</f>
         <v>35</v>
@@ -4048,7 +4328,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4067,7 +4347,7 @@
       <c r="R36" s="14"/>
       <c r="S36" s="10"/>
     </row>
-    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B37" s="10">
         <f>IF(C37="","",COUNTA($C$2:C37))</f>
         <v>36</v>
@@ -4093,7 +4373,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4121,7 +4401,7 @@
       </c>
       <c r="S37" s="10"/>
     </row>
-    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B38" s="10">
         <f>IF(C38="","",COUNTA($C$2:C38))</f>
         <v>37</v>
@@ -4147,7 +4427,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4177,7 +4457,7 @@
       </c>
       <c r="S38" s="10"/>
     </row>
-    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B39" s="10">
         <f>IF(C39="","",COUNTA($C$2:C39))</f>
         <v>38</v>
@@ -4203,7 +4483,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4230,7 +4510,7 @@
       </c>
       <c r="S39" s="10"/>
     </row>
-    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B40" s="10">
         <f>IF(C40="","",COUNTA($C$2:C40))</f>
         <v>39</v>
@@ -4256,7 +4536,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4277,7 +4557,7 @@
       <c r="R40" s="11"/>
       <c r="S40" s="10"/>
     </row>
-    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B41" s="10">
         <f>IF(C41="","",COUNTA($C$2:C41))</f>
         <v>40</v>
@@ -4303,7 +4583,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4331,7 +4611,7 @@
       </c>
       <c r="S41" s="10"/>
     </row>
-    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B42" s="10">
         <f>IF(C42="","",COUNTA($C$2:C42))</f>
         <v>41</v>
@@ -4357,7 +4637,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4384,7 +4664,7 @@
       </c>
       <c r="S42" s="10"/>
     </row>
-    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B43" s="10">
         <f>IF(C43="","",COUNTA($C$2:C43))</f>
         <v>42</v>
@@ -4436,7 +4716,7 @@
       <c r="R43" s="11"/>
       <c r="S43" s="10"/>
     </row>
-    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B44" s="10">
         <f>IF(C44="","",COUNTA($C$2:C44))</f>
         <v>43</v>
@@ -4462,7 +4742,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4487,7 +4767,7 @@
       </c>
       <c r="S44" s="10"/>
     </row>
-    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B45" s="10">
         <f>IF(C45="","",COUNTA($C$2:C45))</f>
         <v>44</v>
@@ -4522,7 +4802,9 @@
       <c r="K45" s="11">
         <v>46066</v>
       </c>
-      <c r="L45" s="11"/>
+      <c r="L45" s="11">
+        <v>46091</v>
+      </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10" t="s">
         <v>33</v>
@@ -4534,7 +4816,7 @@
       <c r="R45" s="11"/>
       <c r="S45" s="10"/>
     </row>
-    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B46" s="10">
         <f>IF(C46="","",COUNTA($C$2:C46))</f>
         <v>45</v>
@@ -4569,7 +4851,9 @@
       <c r="K46" s="11">
         <v>46066</v>
       </c>
-      <c r="L46" s="11"/>
+      <c r="L46" s="11">
+        <v>46091</v>
+      </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10" t="s">
         <v>33</v>
@@ -4581,7 +4865,7 @@
       <c r="R46" s="11"/>
       <c r="S46" s="10"/>
     </row>
-    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B47" s="10">
         <f>IF(C47="","",COUNTA($C$2:C47))</f>
         <v>46</v>
@@ -4607,7 +4891,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4628,7 +4912,7 @@
       <c r="R47" s="11"/>
       <c r="S47" s="10"/>
     </row>
-    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B48" s="10">
         <f>IF(C48="","",COUNTA($C$2:C48))</f>
         <v>47</v>
@@ -4654,7 +4938,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4675,7 +4959,7 @@
       <c r="R48" s="11"/>
       <c r="S48" s="10"/>
     </row>
-    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B49" s="10">
         <f>IF(C49="","",COUNTA($C$2:C49))</f>
         <v>48</v>
@@ -4710,7 +4994,9 @@
       <c r="K49" s="11">
         <v>46112</v>
       </c>
-      <c r="L49" s="11"/>
+      <c r="L49" s="11">
+        <v>46091</v>
+      </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10" t="s">
         <v>201</v>
@@ -4722,7 +5008,7 @@
       <c r="R49" s="11"/>
       <c r="S49" s="10"/>
     </row>
-    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B50" s="10">
         <f>IF(C50="","",COUNTA($C$2:C50))</f>
         <v>49</v>
@@ -4771,7 +5057,7 @@
       <c r="R50" s="11"/>
       <c r="S50" s="10"/>
     </row>
-    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B51" s="10">
         <f>IF(C51="","",COUNTA($C$2:C51))</f>
         <v>50</v>
@@ -4817,7 +5103,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="10"/>
     </row>
-    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B52" s="10">
         <f>IF(C52="","",COUNTA($C$2:C52))</f>
         <v>51</v>
@@ -4863,7 +5149,7 @@
       <c r="R52" s="11"/>
       <c r="S52" s="10"/>
     </row>
-    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B53" s="10">
         <f>IF(C53="","",COUNTA($C$2:C53))</f>
         <v>52</v>
@@ -4912,7 +5198,7 @@
       <c r="R53" s="11"/>
       <c r="S53" s="10"/>
     </row>
-    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B54" s="10">
         <f>IF(C54="","",COUNTA($C$2:C54))</f>
         <v>53</v>
@@ -4938,14 +5224,16 @@
       </c>
       <c r="I54" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J54" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>관리</v>
       </c>
       <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
+      <c r="L54" s="11">
+        <v>46092</v>
+      </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10" t="s">
         <v>20</v>
@@ -4964,7 +5252,7 @@
       </c>
       <c r="S54" s="10"/>
     </row>
-    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B55" s="10">
         <f>IF(C55="","",COUNTA($C$2:C55))</f>
         <v>54</v>
@@ -5008,7 +5296,7 @@
       <c r="R55" s="11"/>
       <c r="S55" s="10"/>
     </row>
-    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B56" s="10">
         <f>IF(C56="","",COUNTA($C$2:C56))</f>
         <v>55</v>
@@ -5057,7 +5345,7 @@
       <c r="R56" s="11"/>
       <c r="S56" s="10"/>
     </row>
-    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B57" s="10">
         <f>IF(C57="","",COUNTA($C$2:C57))</f>
         <v>56</v>
@@ -5083,7 +5371,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5104,7 +5392,7 @@
       <c r="R57" s="14"/>
       <c r="S57" s="10"/>
     </row>
-    <row r="58" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="58" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B58" s="10">
         <f>IF(C58="","",COUNTA($C$2:C58))</f>
         <v>57</v>
@@ -5130,7 +5418,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5151,7 +5439,7 @@
       <c r="R58" s="14"/>
       <c r="S58" s="10"/>
     </row>
-    <row r="59" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="59" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B59" s="10">
         <f>IF(C59="","",COUNTA($C$2:C59))</f>
         <v>58</v>
@@ -5177,7 +5465,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5198,7 +5486,7 @@
       <c r="R59" s="14"/>
       <c r="S59" s="10"/>
     </row>
-    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B60" s="10">
         <f>IF(C60="","",COUNTA($C$2:C60))</f>
         <v>59</v>
@@ -5224,7 +5512,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -5253,7 +5541,7 @@
       <c r="R60" s="14"/>
       <c r="S60" s="10"/>
     </row>
-    <row r="61" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="61" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B61" s="10">
         <f>IF(C61="","",COUNTA($C$2:C61))</f>
         <v>60</v>
@@ -5299,7 +5587,7 @@
       <c r="R61" s="14"/>
       <c r="S61" s="10"/>
     </row>
-    <row r="62" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="62" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B62" s="10">
         <f>IF(C62="","",COUNTA($C$2:C62))</f>
         <v>61</v>
@@ -5345,7 +5633,7 @@
       <c r="R62" s="14"/>
       <c r="S62" s="10"/>
     </row>
-    <row r="63" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="63" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B63" s="10">
         <f>IF(C63="","",COUNTA($C$2:C63))</f>
         <v>62</v>
@@ -5394,7 +5682,7 @@
       <c r="R63" s="14"/>
       <c r="S63" s="10"/>
     </row>
-    <row r="64" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="64" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B64" s="10">
         <f>IF(C64="","",COUNTA($C$2:C64))</f>
         <v>63</v>
@@ -5443,7 +5731,7 @@
       <c r="R64" s="14"/>
       <c r="S64" s="10"/>
     </row>
-    <row r="65" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="65" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B65" s="10">
         <f>IF(C65="","",COUNTA($C$2:C65))</f>
         <v>64</v>
@@ -5489,7 +5777,7 @@
       <c r="R65" s="14"/>
       <c r="S65" s="10"/>
     </row>
-    <row r="66" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="66" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B66" s="10">
         <f>IF(C66="","",COUNTA($C$2:C66))</f>
         <v>65</v>
@@ -5515,7 +5803,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5533,7 +5821,7 @@
       <c r="R66" s="14"/>
       <c r="S66" s="10"/>
     </row>
-    <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B67" s="10">
         <f>IF(C67="","",COUNTA($C$2:C67))</f>
         <v>66</v>
@@ -5559,7 +5847,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5575,7 +5863,7 @@
       <c r="R67" s="11"/>
       <c r="S67" s="10"/>
     </row>
-    <row r="68" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="68" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B68" s="10">
         <f>IF(C68="","",COUNTA($C$2:C68))</f>
         <v>67</v>
@@ -5608,7 +5896,9 @@
         <v>관리</v>
       </c>
       <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
+      <c r="L68" s="11">
+        <v>46091</v>
+      </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10" t="s">
         <v>33</v>
@@ -5617,7 +5907,7 @@
       <c r="R68" s="11"/>
       <c r="S68" s="10"/>
     </row>
-    <row r="69" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="69" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B69" s="10">
         <f>IF(C69="","",COUNTA($C$2:C69))</f>
         <v>68</v>
@@ -5650,7 +5940,9 @@
         <v>관리</v>
       </c>
       <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
+      <c r="L69" s="11">
+        <v>46091</v>
+      </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10" t="s">
         <v>33</v>
@@ -5659,7 +5951,7 @@
       <c r="R69" s="11"/>
       <c r="S69" s="10"/>
     </row>
-    <row r="70" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="70" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B70" s="10">
         <f>IF(C70="","",COUNTA($C$2:C70))</f>
         <v>69</v>
@@ -5706,7 +5998,7 @@
       <c r="R70" s="11"/>
       <c r="S70" s="10"/>
     </row>
-    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B71" s="10">
         <f>IF(C71="","",COUNTA($C$2:C71))</f>
         <v>70</v>
@@ -5758,7 +6050,7 @@
       <c r="R71" s="11"/>
       <c r="S71" s="10"/>
     </row>
-    <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B72" s="10">
         <f>IF(C72="","",COUNTA($C$2:C72))</f>
         <v>71</v>
@@ -5784,14 +6076,16 @@
       </c>
       <c r="I72" s="6">
         <f t="shared" ca="1" si="7"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J72" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
       <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
+      <c r="L72" s="11">
+        <v>46092</v>
+      </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10" t="s">
         <v>20</v>
@@ -5810,7 +6104,7 @@
       </c>
       <c r="S72" s="10"/>
     </row>
-    <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B73" s="10">
         <f>IF(C73="","",COUNTA($C$2:C73))</f>
         <v>72</v>
@@ -5836,7 +6130,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5857,7 +6151,7 @@
       <c r="R73" s="11"/>
       <c r="S73" s="10"/>
     </row>
-    <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B74" s="10">
         <f>IF(C74="","",COUNTA($C$2:C74))</f>
         <v>73</v>
@@ -5911,7 +6205,7 @@
       </c>
       <c r="S74" s="10"/>
     </row>
-    <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B75" s="10">
         <f>IF(C75="","",COUNTA($C$2:C75))</f>
         <v>74</v>
@@ -5955,7 +6249,7 @@
       <c r="R75" s="11"/>
       <c r="S75" s="10"/>
     </row>
-    <row r="76" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="76" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B76" s="10">
         <f>IF(C76="","",COUNTA($C$2:C76))</f>
         <v>75</v>
@@ -5981,7 +6275,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5997,7 +6291,7 @@
       <c r="R76" s="11"/>
       <c r="S76" s="10"/>
     </row>
-    <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B77" s="10">
         <f>IF(C77="","",COUNTA($C$2:C77))</f>
         <v>76</v>
@@ -6051,7 +6345,7 @@
       </c>
       <c r="S77" s="10"/>
     </row>
-    <row r="78" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="78" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B78" s="10">
         <f>IF(C78="","",COUNTA($C$2:C78))</f>
         <v>77</v>
@@ -6105,7 +6399,7 @@
       </c>
       <c r="S78" s="10"/>
     </row>
-    <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B79" s="10">
         <f>IF(C79="","",COUNTA($C$2:C79))</f>
         <v>78</v>
@@ -6149,7 +6443,7 @@
       <c r="R79" s="11"/>
       <c r="S79" s="10"/>
     </row>
-    <row r="80" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="80" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B80" s="10">
         <f>IF(C80="","",COUNTA($C$2:C80))</f>
         <v>79</v>
@@ -6193,7 +6487,7 @@
       <c r="R80" s="11"/>
       <c r="S80" s="10"/>
     </row>
-    <row r="81" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="81" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B81" s="10">
         <f>IF(C81="","",COUNTA($C$2:C81))</f>
         <v>80</v>
@@ -6219,7 +6513,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6235,7 +6529,7 @@
       <c r="R81" s="11"/>
       <c r="S81" s="10"/>
     </row>
-    <row r="82" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="82" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B82" s="10">
         <f>IF(C82="","",COUNTA($C$2:C82))</f>
         <v>81</v>
@@ -6279,7 +6573,7 @@
       <c r="R82" s="11"/>
       <c r="S82" s="10"/>
     </row>
-    <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B83" s="10">
         <f>IF(C83="","",COUNTA($C$2:C83))</f>
         <v>82</v>
@@ -6305,7 +6599,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6331,7 +6625,7 @@
       </c>
       <c r="S83" s="10"/>
     </row>
-    <row r="84" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="84" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B84" s="10">
         <f>IF(C84="","",COUNTA($C$2:C84))</f>
         <v>83</v>
@@ -6357,14 +6651,16 @@
       </c>
       <c r="I84" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J84" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
       <c r="K84" s="11"/>
-      <c r="L84" s="11"/>
+      <c r="L84" s="11">
+        <v>46092</v>
+      </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10" t="s">
         <v>20</v>
@@ -6383,7 +6679,7 @@
       </c>
       <c r="S84" s="10"/>
     </row>
-    <row r="85" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="85" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B85" s="10">
         <f>IF(C85="","",COUNTA($C$2:C85))</f>
         <v>84</v>
@@ -6409,7 +6705,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6435,7 +6731,7 @@
       </c>
       <c r="S85" s="10"/>
     </row>
-    <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B86" s="10">
         <f>IF(C86="","",COUNTA($C$2:C86))</f>
         <v>85</v>
@@ -6461,7 +6757,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6477,7 +6773,7 @@
       <c r="R86" s="11"/>
       <c r="S86" s="10"/>
     </row>
-    <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B87" s="10">
         <f>IF(C87="","",COUNTA($C$2:C87))</f>
         <v>86</v>
@@ -6503,7 +6799,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6529,7 +6825,7 @@
       </c>
       <c r="S87" s="10"/>
     </row>
-    <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B88" s="10">
         <f>IF(C88="","",COUNTA($C$2:C88))</f>
         <v>87</v>
@@ -6573,7 +6869,7 @@
       <c r="R88" s="11"/>
       <c r="S88" s="10"/>
     </row>
-    <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B89" s="10">
         <f>IF(C89="","",COUNTA($C$2:C89))</f>
         <v>88</v>
@@ -6599,11 +6895,11 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K89" s="11"/>
       <c r="L89" s="11"/>
@@ -6625,7 +6921,7 @@
       </c>
       <c r="S89" s="10"/>
     </row>
-    <row r="90" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="90" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B90" s="10">
         <f>IF(C90="","",COUNTA($C$2:C90))</f>
         <v>89</v>
@@ -6651,11 +6947,11 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K90" s="11"/>
       <c r="L90" s="11"/>
@@ -6677,7 +6973,7 @@
       </c>
       <c r="S90" s="10"/>
     </row>
-    <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B91" s="10">
         <f>IF(C91="","",COUNTA($C$2:C91))</f>
         <v>90</v>
@@ -6721,7 +7017,7 @@
       <c r="R91" s="11"/>
       <c r="S91" s="10"/>
     </row>
-    <row r="92" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="92" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B92" s="10">
         <f>IF(C92="","",COUNTA($C$2:C92))</f>
         <v>91</v>
@@ -6747,7 +7043,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6763,7 +7059,7 @@
       <c r="R92" s="11"/>
       <c r="S92" s="10"/>
     </row>
-    <row r="93" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="93" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B93" s="10">
         <f>IF(C93="","",COUNTA($C$2:C93))</f>
         <v>92</v>
@@ -6807,7 +7103,7 @@
       <c r="R93" s="11"/>
       <c r="S93" s="10"/>
     </row>
-    <row r="94" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="94" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B94" s="10">
         <f>IF(C94="","",COUNTA($C$2:C94))</f>
         <v>93</v>
@@ -6851,7 +7147,7 @@
       <c r="R94" s="11"/>
       <c r="S94" s="10"/>
     </row>
-    <row r="95" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="95" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B95" s="10">
         <f>IF(C95="","",COUNTA($C$2:C95))</f>
         <v>94</v>
@@ -6895,7 +7191,7 @@
       <c r="R95" s="11"/>
       <c r="S95" s="10"/>
     </row>
-    <row r="96" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="96" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B96" s="10">
         <f>IF(C96="","",COUNTA($C$2:C96))</f>
         <v>95</v>
@@ -6921,7 +7217,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6937,7 +7233,7 @@
       <c r="R96" s="11"/>
       <c r="S96" s="10"/>
     </row>
-    <row r="97" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="97" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B97" s="10">
         <f>IF(C97="","",COUNTA($C$2:C97))</f>
         <v>96</v>
@@ -6981,7 +7277,7 @@
       <c r="R97" s="11"/>
       <c r="S97" s="10"/>
     </row>
-    <row r="98" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="98" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B98" s="10">
         <f>IF(C98="","",COUNTA($C$2:C98))</f>
         <v>97</v>
@@ -7007,7 +7303,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7023,7 +7319,7 @@
       <c r="R98" s="11"/>
       <c r="S98" s="10"/>
     </row>
-    <row r="99" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="99" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B99" s="10">
         <f>IF(C99="","",COUNTA($C$2:C99))</f>
         <v>98</v>
@@ -7049,7 +7345,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7065,7 +7361,7 @@
       <c r="R99" s="11"/>
       <c r="S99" s="10"/>
     </row>
-    <row r="100" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="100" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B100" s="10">
         <f>IF(C100="","",COUNTA($C$2:C100))</f>
         <v>99</v>
@@ -7090,7 +7386,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7106,7 +7402,7 @@
       <c r="R100" s="11"/>
       <c r="S100" s="10"/>
     </row>
-    <row r="101" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="101" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B101" s="10">
         <f>IF(C101="","",COUNTA($C$2:C101))</f>
         <v>100</v>
@@ -7149,7 +7445,7 @@
       <c r="R101" s="11"/>
       <c r="S101" s="10"/>
     </row>
-    <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B102" s="10">
         <f>IF(C102="","",COUNTA($C$2:C102))</f>
         <v>101</v>
@@ -7193,7 +7489,7 @@
       <c r="R102" s="11"/>
       <c r="S102" s="10"/>
     </row>
-    <row r="103" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="103" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B103" s="26">
         <f>IF(C103="","",COUNTA($C$2:C103))</f>
         <v>102</v>
@@ -7237,7 +7533,7 @@
       <c r="R103" s="11"/>
       <c r="S103" s="10"/>
     </row>
-    <row r="104" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="104" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B104" s="10">
         <f>IF(C104="","",COUNTA($C$2:C104))</f>
         <v>103</v>
@@ -7263,7 +7559,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7279,7 +7575,7 @@
       <c r="R104" s="11"/>
       <c r="S104" s="10"/>
     </row>
-    <row r="105" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="105" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B105" s="10">
         <f>IF(C105="","",COUNTA($C$2:C105))</f>
         <v>104</v>
@@ -7305,7 +7601,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7321,7 +7617,7 @@
       <c r="R105" s="11"/>
       <c r="S105" s="10"/>
     </row>
-    <row r="106" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="106" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B106" s="10">
         <f>IF(C106="","",COUNTA($C$2:C106))</f>
         <v>105</v>
@@ -7346,7 +7642,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7397,7 +7693,9 @@
         <v>정상</v>
       </c>
       <c r="K107" s="11"/>
-      <c r="L107" s="11"/>
+      <c r="L107" s="11">
+        <v>46091</v>
+      </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10" t="s">
         <v>33</v>
@@ -7406,7 +7704,7 @@
       <c r="R107" s="11"/>
       <c r="S107" s="10"/>
     </row>
-    <row r="108" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="108" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B108" s="10">
         <f>IF(C108="","",COUNTA($C$2:C108))</f>
         <v>107</v>
@@ -7431,7 +7729,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7447,7 +7745,7 @@
       <c r="R108" s="11"/>
       <c r="S108" s="10"/>
     </row>
-    <row r="109" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="109" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B109" s="10">
         <f>IF(C109="","",COUNTA($C$2:C109))</f>
         <v>108</v>
@@ -7472,7 +7770,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7488,7 +7786,7 @@
       <c r="R109" s="11"/>
       <c r="S109" s="10"/>
     </row>
-    <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B110" s="10">
         <f>IF(C110="","",COUNTA($C$2:C110))</f>
         <v>109</v>
@@ -7513,7 +7811,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7532,7 +7830,7 @@
       <c r="R110" s="11"/>
       <c r="S110" s="10"/>
     </row>
-    <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B111" s="10">
         <f>IF(C111="","",COUNTA($C$2:C111))</f>
         <v>110</v>
@@ -7576,7 +7874,7 @@
       <c r="R111" s="11"/>
       <c r="S111" s="10"/>
     </row>
-    <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B112" s="10">
         <f>IF(C112="","",COUNTA($C$2:C112))</f>
         <v>111</v>
@@ -7602,7 +7900,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7621,7 +7919,7 @@
       <c r="R112" s="11"/>
       <c r="S112" s="10"/>
     </row>
-    <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B113" s="10">
         <f>IF(C113="","",COUNTA($C$2:C113))</f>
         <v>112</v>
@@ -7665,7 +7963,7 @@
       <c r="R113" s="11"/>
       <c r="S113" s="10"/>
     </row>
-    <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B114" s="10">
         <f>IF(C114="","",COUNTA($C$2:C114))</f>
         <v>113</v>
@@ -7691,7 +7989,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7710,7 +8008,7 @@
       <c r="R114" s="11"/>
       <c r="S114" s="10"/>
     </row>
-    <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B115" s="10">
         <f>IF(C115="","",COUNTA($C$2:C115))</f>
         <v>114</v>
@@ -7736,10 +8034,10 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ref="J115:J162" ca="1" si="11">IF(I115="","",
+        <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
  IF(G115="선급금",
    IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
  IF(G115="자재",
@@ -7763,7 +8061,7 @@
       <c r="R115" s="11"/>
       <c r="S115" s="10"/>
     </row>
-    <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B116" s="10">
         <f>IF(C116="","",COUNTA($C$2:C116))</f>
         <v>115</v>
@@ -7807,7 +8105,7 @@
       <c r="R116" s="11"/>
       <c r="S116" s="10"/>
     </row>
-    <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B117" s="10">
         <f>IF(C117="","",COUNTA($C$2:C117))</f>
         <v>116</v>
@@ -7833,7 +8131,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7849,7 +8147,7 @@
       <c r="R117" s="11"/>
       <c r="S117" s="10"/>
     </row>
-    <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B118" s="10">
         <f>IF(C118="","",COUNTA($C$2:C118))</f>
         <v>117</v>
@@ -7893,7 +8191,7 @@
       <c r="R118" s="11"/>
       <c r="S118" s="10"/>
     </row>
-    <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B119" s="10">
         <f>IF(C119="","",COUNTA($C$2:C119))</f>
         <v>118</v>
@@ -7919,7 +8217,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7938,7 +8236,7 @@
       <c r="R119" s="11"/>
       <c r="S119" s="10"/>
     </row>
-    <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B120" s="10">
         <f>IF(C120="","",COUNTA($C$2:C120))</f>
         <v>119</v>
@@ -7982,7 +8280,7 @@
       <c r="R120" s="11"/>
       <c r="S120" s="10"/>
     </row>
-    <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B121" s="10">
         <f>IF(C121="","",COUNTA($C$2:C121))</f>
         <v>120</v>
@@ -8026,7 +8324,7 @@
       <c r="R121" s="11"/>
       <c r="S121" s="10"/>
     </row>
-    <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B122" s="10">
         <f>IF(C122="","",COUNTA($C$2:C122))</f>
         <v>121</v>
@@ -8052,7 +8350,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8068,7 +8366,7 @@
       <c r="R122" s="11"/>
       <c r="S122" s="10"/>
     </row>
-    <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B123" s="10">
         <f>IF(C123="","",COUNTA($C$2:C123))</f>
         <v>122</v>
@@ -8094,7 +8392,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8110,7 +8408,7 @@
       <c r="R123" s="11"/>
       <c r="S123" s="10"/>
     </row>
-    <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B124" s="10">
         <f>IF(C124="","",COUNTA($C$2:C124))</f>
         <v>123</v>
@@ -8136,7 +8434,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8152,7 +8450,7 @@
       <c r="R124" s="11"/>
       <c r="S124" s="10"/>
     </row>
-    <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B125" s="10">
         <f>IF(C125="","",COUNTA($C$2:C125))</f>
         <v>124</v>
@@ -8178,7 +8476,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8194,7 +8492,7 @@
       <c r="R125" s="11"/>
       <c r="S125" s="10"/>
     </row>
-    <row r="126" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="126" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B126" s="10">
         <v>125</v>
       </c>
@@ -8229,7 +8527,7 @@
       <c r="R126" s="11"/>
       <c r="S126" s="10"/>
     </row>
-    <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B127" s="10">
         <f>IF(C127="","",COUNTA($C$2:C127))</f>
         <v>126</v>
@@ -8255,7 +8553,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8271,7 +8569,7 @@
       <c r="R127" s="11"/>
       <c r="S127" s="10"/>
     </row>
-    <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B128" s="10">
         <f>IF(C128="","",COUNTA($C$2:C128))</f>
         <v>127</v>
@@ -8297,7 +8595,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8339,7 +8637,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8355,7 +8653,7 @@
       <c r="R129" s="11"/>
       <c r="S129" s="10"/>
     </row>
-    <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B130" s="10">
         <f>IF(C130="","",COUNTA($C$2:C130))</f>
         <v>129</v>
@@ -8381,7 +8679,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8397,7 +8695,7 @@
       <c r="R130" s="11"/>
       <c r="S130" s="10"/>
     </row>
-    <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B131" s="10">
         <f>IF(C131="","",COUNTA($C$2:C131))</f>
         <v>130</v>
@@ -8430,7 +8728,9 @@
         <v>정상</v>
       </c>
       <c r="K131" s="11"/>
-      <c r="L131" s="11"/>
+      <c r="L131" s="11">
+        <v>46091</v>
+      </c>
       <c r="M131" s="10"/>
       <c r="N131" s="10" t="s">
         <v>33</v>
@@ -8439,7 +8739,7 @@
       <c r="R131" s="11"/>
       <c r="S131" s="10"/>
     </row>
-    <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B132" s="10">
         <f>IF(C132="","",COUNTA($C$2:C132))</f>
         <v>131</v>
@@ -8472,7 +8772,9 @@
         <v>정상</v>
       </c>
       <c r="K132" s="11"/>
-      <c r="L132" s="11"/>
+      <c r="L132" s="11">
+        <v>46091</v>
+      </c>
       <c r="M132" s="10"/>
       <c r="N132" s="10" t="s">
         <v>33</v>
@@ -8481,7 +8783,7 @@
       <c r="R132" s="11"/>
       <c r="S132" s="10"/>
     </row>
-    <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B133" s="10">
         <f>IF(C133="","",COUNTA($C$2:C133))</f>
         <v>132</v>
@@ -8514,7 +8816,9 @@
         <v>정상</v>
       </c>
       <c r="K133" s="11"/>
-      <c r="L133" s="11"/>
+      <c r="L133" s="11">
+        <v>46091</v>
+      </c>
       <c r="M133" s="10"/>
       <c r="N133" s="10" t="s">
         <v>33</v>
@@ -8523,7 +8827,7 @@
       <c r="R133" s="11"/>
       <c r="S133" s="10"/>
     </row>
-    <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B134" s="10">
         <f>IF(C134="","",COUNTA($C$2:C134))</f>
         <v>133</v>
@@ -8549,7 +8853,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8565,7 +8869,7 @@
       <c r="R134" s="11"/>
       <c r="S134" s="10"/>
     </row>
-    <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B135" s="10">
         <f>IF(C135="","",COUNTA($C$2:C135))</f>
         <v>134</v>
@@ -8591,7 +8895,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8607,7 +8911,7 @@
       <c r="R135" s="11"/>
       <c r="S135" s="10"/>
     </row>
-    <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B136" s="10">
         <f>IF(C136="","",COUNTA($C$2:C136))</f>
         <v>135</v>
@@ -8633,7 +8937,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8649,7 +8953,7 @@
       <c r="R136" s="11"/>
       <c r="S136" s="10"/>
     </row>
-    <row r="137" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="137" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B137" s="10">
         <f>IF(C137="","",COUNTA($C$2:C137))</f>
         <v>136</v>
@@ -8693,7 +8997,7 @@
       <c r="R137" s="11"/>
       <c r="S137" s="10"/>
     </row>
-    <row r="138" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="138" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B138" s="10">
         <f>IF(C138="","",COUNTA($C$2:C138))</f>
         <v>137</v>
@@ -8719,7 +9023,7 @@
       </c>
       <c r="I138" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J138" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8735,7 +9039,7 @@
       <c r="R138" s="11"/>
       <c r="S138" s="10"/>
     </row>
-    <row r="139" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="139" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B139" s="10">
         <f>IF(C139="","",COUNTA($C$2:C139))</f>
         <v>138</v>
@@ -8779,7 +9083,7 @@
       <c r="R139" s="11"/>
       <c r="S139" s="10"/>
     </row>
-    <row r="140" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="140" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B140" s="10">
         <f>IF(C140="","",COUNTA($C$2:C140))</f>
         <v>139</v>
@@ -8823,7 +9127,7 @@
       <c r="R140" s="11"/>
       <c r="S140" s="10"/>
     </row>
-    <row r="141" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="141" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B141" s="10">
         <f>IF(C141="","",COUNTA($C$2:C141))</f>
         <v>140</v>
@@ -8849,7 +9153,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8865,7 +9169,7 @@
       <c r="R141" s="11"/>
       <c r="S141" s="10"/>
     </row>
-    <row r="142" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="142" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B142" s="10">
         <f>IF(C142="","",COUNTA($C$2:C142))</f>
         <v>141</v>
@@ -8890,7 +9194,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8906,7 +9210,7 @@
       <c r="R142" s="11"/>
       <c r="S142" s="10"/>
     </row>
-    <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B143" s="10">
         <f>IF(C143="","",COUNTA($C$2:C143))</f>
         <v>142</v>
@@ -8931,7 +9235,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8947,7 +9251,7 @@
       <c r="R143" s="11"/>
       <c r="S143" s="10"/>
     </row>
-    <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B144" s="10">
         <f>IF(C144="","",COUNTA($C$2:C144))</f>
         <v>143</v>
@@ -8972,7 +9276,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8988,7 +9292,7 @@
       <c r="R144" s="11"/>
       <c r="S144" s="10"/>
     </row>
-    <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B145" s="10">
         <f>IF(C145="","",COUNTA($C$2:C145))</f>
         <v>144</v>
@@ -9013,7 +9317,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9029,7 +9333,7 @@
       <c r="R145" s="11"/>
       <c r="S145" s="10"/>
     </row>
-    <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B146" s="10">
         <f>IF(C146="","",COUNTA($C$2:C146))</f>
         <v>145</v>
@@ -9054,7 +9358,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9070,7 +9374,7 @@
       <c r="R146" s="11"/>
       <c r="S146" s="10"/>
     </row>
-    <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B147" s="10">
         <f>IF(C147="","",COUNTA($C$2:C147))</f>
         <v>146</v>
@@ -9095,7 +9399,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9111,7 +9415,7 @@
       <c r="R147" s="11"/>
       <c r="S147" s="10"/>
     </row>
-    <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B148" s="10">
         <f>IF(C148="","",COUNTA($C$2:C148))</f>
         <v>147</v>
@@ -9136,7 +9440,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9152,7 +9456,7 @@
       <c r="R148" s="11"/>
       <c r="S148" s="10"/>
     </row>
-    <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B149" s="10">
         <f>IF(C149="","",COUNTA($C$2:C149))</f>
         <v>148</v>
@@ -9177,7 +9481,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9193,7 +9497,7 @@
       <c r="R149" s="11"/>
       <c r="S149" s="10"/>
     </row>
-    <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B150" s="10">
         <f>IF(C150="","",COUNTA($C$2:C150))</f>
         <v>149</v>
@@ -9218,7 +9522,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9234,7 +9538,7 @@
       <c r="R150" s="11"/>
       <c r="S150" s="10"/>
     </row>
-    <row r="151" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="151" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B151" s="10">
         <f>IF(C151="","",COUNTA($C$2:C151))</f>
         <v>150</v>
@@ -9277,7 +9581,7 @@
       <c r="R151" s="11"/>
       <c r="S151" s="10"/>
     </row>
-    <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B152" s="10">
         <f>IF(C152="","",COUNTA($C$2:C152))</f>
         <v>151</v>
@@ -9302,7 +9606,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9318,7 +9622,7 @@
       <c r="R152" s="11"/>
       <c r="S152" s="10"/>
     </row>
-    <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B153" s="10">
         <f>IF(C153="","",COUNTA($C$2:C153))</f>
         <v>152</v>
@@ -9361,7 +9665,7 @@
       <c r="R153" s="11"/>
       <c r="S153" s="10"/>
     </row>
-    <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B154" s="10">
         <f>IF(C154="","",COUNTA($C$2:C154))</f>
         <v>153</v>
@@ -9386,7 +9690,7 @@
       </c>
       <c r="I154" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J154" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9402,7 +9706,7 @@
       <c r="R154" s="11"/>
       <c r="S154" s="10"/>
     </row>
-    <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B155" s="10">
         <f>IF(C155="","",COUNTA($C$2:C155))</f>
         <v>154</v>
@@ -9427,7 +9731,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9443,7 +9747,7 @@
       <c r="R155" s="11"/>
       <c r="S155" s="10"/>
     </row>
-    <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B156" s="10">
         <f>IF(C156="","",COUNTA($C$2:C156))</f>
         <v>155</v>
@@ -9468,7 +9772,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9484,7 +9788,7 @@
       <c r="R156" s="11"/>
       <c r="S156" s="10"/>
     </row>
-    <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B157" s="10">
         <f>IF(C157="","",COUNTA($C$2:C157))</f>
         <v>156</v>
@@ -9509,7 +9813,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9525,7 +9829,7 @@
       <c r="R157" s="11"/>
       <c r="S157" s="10"/>
     </row>
-    <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B158" s="10">
         <f>IF(C158="","",COUNTA($C$2:C158))</f>
         <v>157</v>
@@ -9551,7 +9855,7 @@
       </c>
       <c r="I158" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J158" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9567,7 +9871,7 @@
       <c r="R158" s="11"/>
       <c r="S158" s="10"/>
     </row>
-    <row r="159" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="159" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B159" s="10">
         <f>IF(C159="","",COUNTA($C$2:C159))</f>
         <v>158</v>
@@ -9593,7 +9897,7 @@
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9609,7 +9913,7 @@
       <c r="R159" s="11"/>
       <c r="S159" s="10"/>
     </row>
-    <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B160" s="10">
         <f>IF(C160="","",COUNTA($C$2:C160))</f>
         <v>159</v>
@@ -9635,7 +9939,7 @@
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J160" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9651,7 +9955,7 @@
       <c r="R160" s="11"/>
       <c r="S160" s="10"/>
     </row>
-    <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B161" s="10">
         <f>IF(C161="","",COUNTA($C$2:C161))</f>
         <v>160</v>
@@ -9677,7 +9981,7 @@
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J161" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9693,7 +9997,7 @@
       <c r="R161" s="11"/>
       <c r="S161" s="10"/>
     </row>
-    <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B162" s="10">
         <f>IF(C162="","",COUNTA($C$2:C162))</f>
         <v>161</v>
@@ -9726,7 +10030,9 @@
         <v>정상</v>
       </c>
       <c r="K162" s="11"/>
-      <c r="L162" s="11"/>
+      <c r="L162" s="11">
+        <v>46091</v>
+      </c>
       <c r="M162" s="10"/>
       <c r="N162" s="10" t="s">
         <v>33</v>
@@ -9735,559 +10041,985 @@
       <c r="R162" s="11"/>
       <c r="S162" s="10"/>
     </row>
-    <row r="163" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B163" s="10" t="str">
+    <row r="163" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B163" s="10">
         <f>IF(C163="","",COUNTA($C$2:C163))</f>
-        <v/>
-      </c>
-      <c r="C163" s="11"/>
-      <c r="D163" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H163" s="4"/>
-      <c r="I163" s="6" t="str">
+        <v>162</v>
+      </c>
+      <c r="C163" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="H163" s="4">
+        <v>13694000</v>
+      </c>
+      <c r="I163" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J163" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J163" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K163" s="11"/>
       <c r="L163" s="11"/>
       <c r="M163" s="10"/>
-      <c r="N163" s="10"/>
+      <c r="N163" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q163" s="11"/>
       <c r="R163" s="11"/>
       <c r="S163" s="10"/>
     </row>
-    <row r="164" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B164" s="10" t="str">
+    <row r="164" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B164" s="10">
         <f>IF(C164="","",COUNTA($C$2:C164))</f>
-        <v/>
-      </c>
-      <c r="C164" s="11"/>
+        <v>163</v>
+      </c>
+      <c r="C164" s="35">
+        <v>46091</v>
+      </c>
       <c r="D164" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H164" s="4"/>
-      <c r="I164" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H164" s="4">
+        <v>59166000</v>
+      </c>
+      <c r="I164" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J164" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J164" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K164" s="11"/>
       <c r="L164" s="11"/>
       <c r="M164" s="10"/>
-      <c r="N164" s="10"/>
+      <c r="N164" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q164" s="11"/>
       <c r="R164" s="11"/>
       <c r="S164" s="10"/>
     </row>
-    <row r="165" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B165" s="10" t="str">
+    <row r="165" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B165" s="10">
         <f>IF(C165="","",COUNTA($C$2:C165))</f>
-        <v/>
-      </c>
-      <c r="C165" s="11"/>
-      <c r="D165" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H165" s="4"/>
-      <c r="I165" s="6" t="str">
+        <v>164</v>
+      </c>
+      <c r="C165" s="35">
+        <v>46092</v>
+      </c>
+      <c r="D165" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G165" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H165" s="4">
+        <v>4500000</v>
+      </c>
+      <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J165" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J165" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K165" s="11"/>
       <c r="L165" s="11"/>
       <c r="M165" s="10"/>
-      <c r="N165" s="10"/>
+      <c r="N165" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q165" s="11"/>
       <c r="R165" s="11"/>
       <c r="S165" s="10"/>
     </row>
-    <row r="166" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B166" s="10" t="str">
+    <row r="166" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B166" s="10">
         <f>IF(C166="","",COUNTA($C$2:C166))</f>
-        <v/>
-      </c>
-      <c r="C166" s="11"/>
+        <v>165</v>
+      </c>
+      <c r="C166" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D166" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H166" s="4"/>
-      <c r="I166" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E166" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F166" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H166" s="25">
+        <v>8400000</v>
+      </c>
+      <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J166" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J166" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K166" s="11"/>
       <c r="L166" s="11"/>
       <c r="M166" s="10"/>
-      <c r="N166" s="10"/>
+      <c r="N166" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q166" s="11"/>
       <c r="R166" s="11"/>
       <c r="S166" s="10"/>
     </row>
-    <row r="167" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B167" s="10" t="str">
+    <row r="167" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B167" s="10">
         <f>IF(C167="","",COUNTA($C$2:C167))</f>
-        <v/>
-      </c>
-      <c r="C167" s="11"/>
+        <v>166</v>
+      </c>
+      <c r="C167" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D167" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H167" s="4"/>
-      <c r="I167" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E167" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F167" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H167" s="25">
+        <v>46282000</v>
+      </c>
+      <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J167" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J167" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K167" s="11"/>
       <c r="L167" s="11"/>
       <c r="M167" s="10"/>
-      <c r="N167" s="10"/>
+      <c r="N167" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q167" s="11"/>
       <c r="R167" s="11"/>
       <c r="S167" s="10"/>
     </row>
-    <row r="168" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B168" s="10" t="str">
+    <row r="168" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B168" s="10">
         <f>IF(C168="","",COUNTA($C$2:C168))</f>
-        <v/>
-      </c>
-      <c r="C168" s="11"/>
+        <v>167</v>
+      </c>
+      <c r="C168" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D168" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H168" s="4"/>
-      <c r="I168" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E168" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F168" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="G168" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H168" s="25">
+        <v>1832500</v>
+      </c>
+      <c r="I168" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J168" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J168" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K168" s="11"/>
-      <c r="L168" s="11"/>
+      <c r="L168" s="11">
+        <v>46091</v>
+      </c>
       <c r="M168" s="10"/>
-      <c r="N168" s="10"/>
+      <c r="N168" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q168" s="11"/>
       <c r="R168" s="11"/>
       <c r="S168" s="10"/>
     </row>
-    <row r="169" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B169" s="10" t="str">
+    <row r="169" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B169" s="10">
         <f>IF(C169="","",COUNTA($C$2:C169))</f>
-        <v/>
-      </c>
-      <c r="C169" s="11"/>
+        <v>168</v>
+      </c>
+      <c r="C169" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D169" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H169" s="4"/>
-      <c r="I169" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E169" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="F169" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="G169" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H169" s="25">
+        <v>222000</v>
+      </c>
+      <c r="I169" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J169" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J169" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K169" s="11"/>
       <c r="L169" s="11"/>
       <c r="M169" s="10"/>
-      <c r="N169" s="10"/>
+      <c r="N169" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q169" s="11"/>
       <c r="R169" s="11"/>
       <c r="S169" s="10"/>
     </row>
-    <row r="170" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B170" s="10" t="str">
+    <row r="170" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B170" s="10">
         <f>IF(C170="","",COUNTA($C$2:C170))</f>
-        <v/>
-      </c>
-      <c r="C170" s="11"/>
+        <v>169</v>
+      </c>
+      <c r="C170" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D170" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H170" s="4"/>
-      <c r="I170" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E170" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="F170" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="G170" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H170" s="25">
+        <v>14080000</v>
+      </c>
+      <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J170" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J170" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K170" s="11"/>
       <c r="L170" s="11"/>
       <c r="M170" s="10"/>
-      <c r="N170" s="10"/>
+      <c r="N170" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q170" s="11"/>
       <c r="R170" s="11"/>
       <c r="S170" s="10"/>
     </row>
-    <row r="171" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B171" s="10" t="str">
+    <row r="171" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B171" s="10">
         <f>IF(C171="","",COUNTA($C$2:C171))</f>
-        <v/>
-      </c>
-      <c r="C171" s="11"/>
+        <v>170</v>
+      </c>
+      <c r="C171" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D171" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H171" s="4"/>
-      <c r="I171" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E171" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F171" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="G171" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H171" s="25">
+        <v>14080000</v>
+      </c>
+      <c r="I171" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J171" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J171" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K171" s="11"/>
       <c r="L171" s="11"/>
       <c r="M171" s="10"/>
-      <c r="N171" s="10"/>
+      <c r="N171" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q171" s="11"/>
       <c r="R171" s="11"/>
       <c r="S171" s="10"/>
     </row>
-    <row r="172" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B172" s="10" t="str">
+    <row r="172" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B172" s="10">
         <f>IF(C172="","",COUNTA($C$2:C172))</f>
-        <v/>
-      </c>
-      <c r="C172" s="11"/>
+        <v>171</v>
+      </c>
+      <c r="C172" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D172" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H172" s="4"/>
-      <c r="I172" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E172" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="F172" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="G172" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H172" s="25">
+        <v>1186600</v>
+      </c>
+      <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J172" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J172" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K172" s="11"/>
       <c r="L172" s="11"/>
       <c r="M172" s="10"/>
-      <c r="N172" s="10"/>
+      <c r="N172" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q172" s="11"/>
       <c r="R172" s="11"/>
       <c r="S172" s="10"/>
     </row>
-    <row r="173" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B173" s="10" t="str">
+    <row r="173" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B173" s="10">
         <f>IF(C173="","",COUNTA($C$2:C173))</f>
-        <v/>
-      </c>
-      <c r="C173" s="11"/>
+        <v>172</v>
+      </c>
+      <c r="C173" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D173" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H173" s="4"/>
-      <c r="I173" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E173" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="F173" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H173" s="25">
+        <v>270000</v>
+      </c>
+      <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J173" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J173" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K173" s="11"/>
       <c r="L173" s="11"/>
       <c r="M173" s="10"/>
-      <c r="N173" s="10"/>
+      <c r="N173" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q173" s="11"/>
       <c r="R173" s="11"/>
       <c r="S173" s="10"/>
     </row>
-    <row r="174" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B174" s="10" t="str">
+    <row r="174" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B174" s="10">
         <f>IF(C174="","",COUNTA($C$2:C174))</f>
-        <v/>
-      </c>
-      <c r="C174" s="11"/>
+        <v>173</v>
+      </c>
+      <c r="C174" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D174" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H174" s="4"/>
-      <c r="I174" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E174" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F174" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="G174" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H174" s="25">
+        <v>5912000</v>
+      </c>
+      <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J174" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J174" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K174" s="11"/>
       <c r="L174" s="11"/>
       <c r="M174" s="10"/>
-      <c r="N174" s="10"/>
+      <c r="N174" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q174" s="11"/>
       <c r="R174" s="11"/>
       <c r="S174" s="10"/>
     </row>
-    <row r="175" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B175" s="10" t="str">
+    <row r="175" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B175" s="10">
         <f>IF(C175="","",COUNTA($C$2:C175))</f>
-        <v/>
-      </c>
-      <c r="C175" s="11"/>
+        <v>174</v>
+      </c>
+      <c r="C175" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D175" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H175" s="4"/>
-      <c r="I175" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E175" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F175" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H175" s="25">
+        <v>4992000</v>
+      </c>
+      <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J175" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J175" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K175" s="11"/>
       <c r="L175" s="11"/>
       <c r="M175" s="10"/>
-      <c r="N175" s="10"/>
+      <c r="N175" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q175" s="11"/>
       <c r="R175" s="11"/>
       <c r="S175" s="10"/>
     </row>
-    <row r="176" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B176" s="10" t="str">
+    <row r="176" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B176" s="10">
         <f>IF(C176="","",COUNTA($C$2:C176))</f>
-        <v/>
-      </c>
-      <c r="C176" s="11"/>
+        <v>175</v>
+      </c>
+      <c r="C176" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D176" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H176" s="4"/>
-      <c r="I176" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E176" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F176" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="G176" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H176" s="25">
+        <v>950350</v>
+      </c>
+      <c r="I176" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J176" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J176" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K176" s="11"/>
-      <c r="L176" s="11"/>
+      <c r="L176" s="11">
+        <v>46091</v>
+      </c>
       <c r="M176" s="10"/>
-      <c r="N176" s="10"/>
+      <c r="N176" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q176" s="11"/>
       <c r="R176" s="11"/>
       <c r="S176" s="10"/>
     </row>
-    <row r="177" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B177" s="10" t="str">
+    <row r="177" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B177" s="10">
         <f>IF(C177="","",COUNTA($C$2:C177))</f>
-        <v/>
-      </c>
-      <c r="C177" s="11"/>
+        <v>176</v>
+      </c>
+      <c r="C177" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D177" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H177" s="4"/>
-      <c r="I177" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E177" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F177" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H177" s="25">
+        <v>770400</v>
+      </c>
+      <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J177" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J177" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K177" s="11"/>
       <c r="L177" s="11"/>
       <c r="M177" s="10"/>
-      <c r="N177" s="10"/>
+      <c r="N177" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q177" s="11"/>
       <c r="R177" s="11"/>
       <c r="S177" s="10"/>
     </row>
-    <row r="178" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B178" s="10" t="str">
+    <row r="178" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B178" s="10">
         <f>IF(C178="","",COUNTA($C$2:C178))</f>
-        <v/>
-      </c>
-      <c r="C178" s="11"/>
+        <v>177</v>
+      </c>
+      <c r="C178" s="35" t="s">
+        <v>281</v>
+      </c>
       <c r="D178" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H178" s="4"/>
-      <c r="I178" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E178" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="F178" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H178" s="25">
+        <v>473600</v>
+      </c>
+      <c r="I178" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J178" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J178" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
       <c r="K178" s="11"/>
-      <c r="L178" s="11"/>
+      <c r="L178" s="11">
+        <v>46091</v>
+      </c>
       <c r="M178" s="10"/>
-      <c r="N178" s="10"/>
+      <c r="N178" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q178" s="11"/>
       <c r="R178" s="11"/>
       <c r="S178" s="10"/>
     </row>
-    <row r="179" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B179" s="10" t="str">
+    <row r="179" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B179" s="10">
         <f>IF(C179="","",COUNTA($C$2:C179))</f>
-        <v/>
-      </c>
-      <c r="C179" s="11"/>
+        <v>178</v>
+      </c>
+      <c r="C179" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="D179" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H179" s="4"/>
-      <c r="I179" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E179" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="F179" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H179" s="25">
+        <v>121500</v>
+      </c>
+      <c r="I179" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J179" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J179" s="13" t="str">
+        <f t="shared" ref="J179:J185" ca="1" si="14">IF(I179="","",
+ IF(G179="선급금",
+   IF(I179&lt;=20,"정상",IF(I179&lt;=90,"관리","장기미수")),
+ IF(G179="자재",
+   IF(I179&lt;=40,"정상",IF(I179&lt;=90,"관리","장기미수")),
+   IF(I179&lt;=30,"정상",IF(I179&lt;=90,"관리","장기미수"))
+  )
+ )
+)</f>
+        <v>정상</v>
+      </c>
       <c r="K179" s="11"/>
       <c r="L179" s="11"/>
       <c r="M179" s="10"/>
-      <c r="N179" s="10"/>
+      <c r="N179" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q179" s="11"/>
       <c r="R179" s="11"/>
       <c r="S179" s="10"/>
     </row>
-    <row r="180" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B180" s="10" t="str">
+    <row r="180" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B180" s="10">
         <f>IF(C180="","",COUNTA($C$2:C180))</f>
-        <v/>
-      </c>
-      <c r="C180" s="11"/>
+        <v>179</v>
+      </c>
+      <c r="C180" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="D180" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H180" s="4"/>
-      <c r="I180" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E180" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F180" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="G180" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H180" s="25">
+        <v>16818900</v>
+      </c>
+      <c r="I180" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J180" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J180" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K180" s="11"/>
       <c r="L180" s="11"/>
       <c r="M180" s="10"/>
-      <c r="N180" s="10"/>
+      <c r="N180" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q180" s="11"/>
       <c r="R180" s="11"/>
       <c r="S180" s="10"/>
     </row>
-    <row r="181" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B181" s="10" t="str">
+    <row r="181" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B181" s="10">
         <f>IF(C181="","",COUNTA($C$2:C181))</f>
-        <v/>
-      </c>
-      <c r="C181" s="11"/>
+        <v>180</v>
+      </c>
+      <c r="C181" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="D181" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H181" s="4"/>
-      <c r="I181" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E181" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="G181" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H181" s="25">
+        <v>294800</v>
+      </c>
+      <c r="I181" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J181" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J181" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K181" s="11"/>
       <c r="L181" s="11"/>
       <c r="M181" s="10"/>
-      <c r="N181" s="10"/>
+      <c r="N181" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q181" s="11"/>
       <c r="R181" s="11"/>
       <c r="S181" s="10"/>
     </row>
-    <row r="182" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B182" s="10" t="str">
+    <row r="182" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B182" s="10">
         <f>IF(C182="","",COUNTA($C$2:C182))</f>
-        <v/>
-      </c>
-      <c r="C182" s="11"/>
+        <v>181</v>
+      </c>
+      <c r="C182" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="D182" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H182" s="4"/>
-      <c r="I182" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E182" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F182" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H182" s="25">
+        <v>321000</v>
+      </c>
+      <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J182" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J182" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K182" s="11"/>
       <c r="L182" s="11"/>
       <c r="M182" s="10"/>
-      <c r="N182" s="10"/>
+      <c r="N182" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q182" s="11"/>
       <c r="R182" s="11"/>
       <c r="S182" s="10"/>
     </row>
-    <row r="183" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B183" s="10" t="str">
+    <row r="183" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B183" s="10">
         <f>IF(C183="","",COUNTA($C$2:C183))</f>
-        <v/>
-      </c>
-      <c r="C183" s="11"/>
+        <v>182</v>
+      </c>
+      <c r="C183" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="D183" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H183" s="4"/>
-      <c r="I183" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E183" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="F183" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="G183" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H183" s="25">
+        <v>1275400</v>
+      </c>
+      <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J183" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J183" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K183" s="11"/>
       <c r="L183" s="11"/>
       <c r="M183" s="10"/>
-      <c r="N183" s="10"/>
+      <c r="N183" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q183" s="11"/>
       <c r="R183" s="11"/>
       <c r="S183" s="10"/>
     </row>
-    <row r="184" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B184" s="10" t="str">
+    <row r="184" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B184" s="10">
         <f>IF(C184="","",COUNTA($C$2:C184))</f>
-        <v/>
-      </c>
-      <c r="C184" s="11"/>
+        <v>183</v>
+      </c>
+      <c r="C184" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="D184" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H184" s="4"/>
-      <c r="I184" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E184" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F184" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G184" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H184" s="25">
+        <v>11000000</v>
+      </c>
+      <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J184" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J184" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K184" s="11"/>
       <c r="L184" s="11"/>
       <c r="M184" s="10"/>
-      <c r="N184" s="10"/>
+      <c r="N184" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q184" s="11"/>
       <c r="R184" s="11"/>
       <c r="S184" s="10"/>
     </row>
-    <row r="185" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B185" s="10" t="str">
+    <row r="185" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B185" s="10">
         <f>IF(C185="","",COUNTA($C$2:C185))</f>
-        <v/>
-      </c>
-      <c r="C185" s="11"/>
+        <v>184</v>
+      </c>
+      <c r="C185" s="35" t="s">
+        <v>287</v>
+      </c>
       <c r="D185" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H185" s="4"/>
-      <c r="I185" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E185" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F185" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H185" s="25">
+        <v>5475500</v>
+      </c>
+      <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J185" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J185" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K185" s="11"/>
       <c r="L185" s="11"/>
       <c r="M185" s="10"/>
-      <c r="N185" s="10"/>
+      <c r="N185" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q185" s="11"/>
       <c r="R185" s="11"/>
       <c r="S185" s="10"/>
     </row>
-    <row r="186" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="186" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B186" s="10" t="str">
         <f>IF(C186="","",COUNTA($C$2:C186))</f>
         <v/>
@@ -10311,7 +11043,7 @@
       <c r="R186" s="11"/>
       <c r="S186" s="10"/>
     </row>
-    <row r="187" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="187" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B187" s="10" t="str">
         <f>IF(C187="","",COUNTA($C$2:C187))</f>
         <v/>
@@ -10335,7 +11067,7 @@
       <c r="R187" s="11"/>
       <c r="S187" s="10"/>
     </row>
-    <row r="188" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="188" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B188" s="10" t="str">
         <f>IF(C188="","",COUNTA($C$2:C188))</f>
         <v/>
@@ -10359,7 +11091,7 @@
       <c r="R188" s="11"/>
       <c r="S188" s="10"/>
     </row>
-    <row r="189" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="189" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B189" s="10" t="str">
         <f>IF(C189="","",COUNTA($C$2:C189))</f>
         <v/>
@@ -10383,7 +11115,7 @@
       <c r="R189" s="11"/>
       <c r="S189" s="10"/>
     </row>
-    <row r="190" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="190" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B190" s="10" t="str">
         <f>IF(C190="","",COUNTA($C$2:C190))</f>
         <v/>
@@ -10407,7 +11139,7 @@
       <c r="R190" s="11"/>
       <c r="S190" s="10"/>
     </row>
-    <row r="191" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="191" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B191" s="10" t="str">
         <f>IF(C191="","",COUNTA($C$2:C191))</f>
         <v/>
@@ -10431,7 +11163,7 @@
       <c r="R191" s="11"/>
       <c r="S191" s="10"/>
     </row>
-    <row r="192" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="192" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B192" s="10" t="str">
         <f>IF(C192="","",COUNTA($C$2:C192))</f>
         <v/>
@@ -10455,7 +11187,7 @@
       <c r="R192" s="11"/>
       <c r="S192" s="10"/>
     </row>
-    <row r="193" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="193" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B193" s="10" t="str">
         <f>IF(C193="","",COUNTA($C$2:C193))</f>
         <v/>
@@ -10479,7 +11211,7 @@
       <c r="R193" s="11"/>
       <c r="S193" s="10"/>
     </row>
-    <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B194" s="10" t="str">
         <f>IF(C194="","",COUNTA($C$2:C194))</f>
         <v/>
@@ -10503,7 +11235,7 @@
       <c r="R194" s="11"/>
       <c r="S194" s="10"/>
     </row>
-    <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B195" s="10" t="str">
         <f>IF(C195="","",COUNTA($C$2:C195))</f>
         <v/>
@@ -10527,7 +11259,7 @@
       <c r="R195" s="11"/>
       <c r="S195" s="10"/>
     </row>
-    <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B196" s="10" t="str">
         <f>IF(C196="","",COUNTA($C$2:C196))</f>
         <v/>
@@ -10551,7 +11283,7 @@
       <c r="R196" s="11"/>
       <c r="S196" s="10"/>
     </row>
-    <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B197" s="10" t="str">
         <f>IF(C197="","",COUNTA($C$2:C197))</f>
         <v/>
@@ -10575,7 +11307,7 @@
       <c r="R197" s="11"/>
       <c r="S197" s="10"/>
     </row>
-    <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B198" s="10" t="str">
         <f>IF(C198="","",COUNTA($C$2:C198))</f>
         <v/>
@@ -10599,7 +11331,7 @@
       <c r="R198" s="11"/>
       <c r="S198" s="10"/>
     </row>
-    <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B199" s="10" t="str">
         <f>IF(C199="","",COUNTA($C$2:C199))</f>
         <v/>
@@ -10623,7 +11355,7 @@
       <c r="R199" s="11"/>
       <c r="S199" s="10"/>
     </row>
-    <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B200" s="10" t="str">
         <f>IF(C200="","",COUNTA($C$2:C200))</f>
         <v/>
@@ -10647,7 +11379,7 @@
       <c r="R200" s="11"/>
       <c r="S200" s="10"/>
     </row>
-    <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B201" s="10" t="str">
         <f>IF(C201="","",COUNTA($C$2:C201))</f>
         <v/>
@@ -10671,7 +11403,7 @@
       <c r="R201" s="11"/>
       <c r="S201" s="10"/>
     </row>
-    <row r="202" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="202" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B202" s="10" t="str">
         <f>IF(C202="","",COUNTA($C$2:C202))</f>
         <v/>
@@ -10695,7 +11427,7 @@
       <c r="R202" s="11"/>
       <c r="S202" s="10"/>
     </row>
-    <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B203" s="10" t="str">
         <f>IF(C203="","",COUNTA($C$2:C203))</f>
         <v/>
@@ -10719,19 +11451,19 @@
       <c r="R203" s="11"/>
       <c r="S203" s="10"/>
     </row>
-    <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B204" s="10" t="str">
         <f>IF(C204="","",COUNTA($C$2:C204))</f>
         <v/>
       </c>
       <c r="C204" s="11"/>
       <c r="D204" s="10" t="str">
-        <f t="shared" ref="D204:D267" si="14">IF(G204="","",IF(OR(G204="선급금",G204="중도금",G204="잔금"),"A",IF(G204="자재","B",IF(G204="특허료","C",""))))</f>
+        <f t="shared" ref="D204:D267" si="15">IF(G204="","",IF(OR(G204="선급금",G204="중도금",G204="잔금"),"A",IF(G204="자재","B",IF(G204="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" s="6" t="str">
-        <f t="shared" ref="I204:I267" ca="1" si="15">IF(C204="","",IF(L204="",TODAY()-C204,L204-C204))</f>
+        <f t="shared" ref="I204:I267" ca="1" si="16">IF(C204="","",IF(L204="",TODAY()-C204,L204-C204))</f>
         <v/>
       </c>
       <c r="J204" s="13"/>
@@ -10743,19 +11475,19 @@
       <c r="R204" s="11"/>
       <c r="S204" s="10"/>
     </row>
-    <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B205" s="10" t="str">
         <f>IF(C205="","",COUNTA($C$2:C205))</f>
         <v/>
       </c>
       <c r="C205" s="11"/>
       <c r="D205" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H205" s="4"/>
       <c r="I205" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J205" s="13"/>
@@ -10767,19 +11499,19 @@
       <c r="R205" s="11"/>
       <c r="S205" s="10"/>
     </row>
-    <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B206" s="10" t="str">
         <f>IF(C206="","",COUNTA($C$2:C206))</f>
         <v/>
       </c>
       <c r="C206" s="11"/>
       <c r="D206" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H206" s="4"/>
       <c r="I206" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J206" s="13"/>
@@ -10791,19 +11523,19 @@
       <c r="R206" s="11"/>
       <c r="S206" s="10"/>
     </row>
-    <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B207" s="10" t="str">
         <f>IF(C207="","",COUNTA($C$2:C207))</f>
         <v/>
       </c>
       <c r="C207" s="11"/>
       <c r="D207" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H207" s="4"/>
       <c r="I207" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J207" s="13"/>
@@ -10815,19 +11547,19 @@
       <c r="R207" s="11"/>
       <c r="S207" s="10"/>
     </row>
-    <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B208" s="10" t="str">
         <f>IF(C208="","",COUNTA($C$2:C208))</f>
         <v/>
       </c>
       <c r="C208" s="11"/>
       <c r="D208" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H208" s="4"/>
       <c r="I208" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J208" s="13"/>
@@ -10839,19 +11571,19 @@
       <c r="R208" s="11"/>
       <c r="S208" s="10"/>
     </row>
-    <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B209" s="10" t="str">
         <f>IF(C209="","",COUNTA($C$2:C209))</f>
         <v/>
       </c>
       <c r="C209" s="11"/>
       <c r="D209" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H209" s="4"/>
       <c r="I209" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J209" s="13"/>
@@ -10863,19 +11595,19 @@
       <c r="R209" s="11"/>
       <c r="S209" s="10"/>
     </row>
-    <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B210" s="10" t="str">
         <f>IF(C210="","",COUNTA($C$2:C210))</f>
         <v/>
       </c>
       <c r="C210" s="11"/>
       <c r="D210" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H210" s="4"/>
       <c r="I210" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J210" s="13"/>
@@ -10887,19 +11619,19 @@
       <c r="R210" s="11"/>
       <c r="S210" s="10"/>
     </row>
-    <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B211" s="10" t="str">
         <f>IF(C211="","",COUNTA($C$2:C211))</f>
         <v/>
       </c>
       <c r="C211" s="11"/>
       <c r="D211" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H211" s="4"/>
       <c r="I211" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J211" s="13"/>
@@ -10911,16 +11643,16 @@
       <c r="R211" s="11"/>
       <c r="S211" s="10"/>
     </row>
-    <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B212" s="10"/>
       <c r="C212" s="11"/>
       <c r="D212" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H212" s="4"/>
       <c r="I212" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J212" s="13"/>
@@ -10932,16 +11664,16 @@
       <c r="R212" s="11"/>
       <c r="S212" s="10"/>
     </row>
-    <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B213" s="10"/>
       <c r="C213" s="11"/>
       <c r="D213" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H213" s="4"/>
       <c r="I213" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J213" s="13"/>
@@ -10953,16 +11685,16 @@
       <c r="R213" s="11"/>
       <c r="S213" s="10"/>
     </row>
-    <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B214" s="10"/>
       <c r="C214" s="11"/>
       <c r="D214" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H214" s="4"/>
       <c r="I214" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J214" s="13"/>
@@ -10974,16 +11706,16 @@
       <c r="R214" s="11"/>
       <c r="S214" s="10"/>
     </row>
-    <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B215" s="10"/>
       <c r="C215" s="11"/>
       <c r="D215" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H215" s="4"/>
       <c r="I215" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J215" s="13"/>
@@ -10995,16 +11727,16 @@
       <c r="R215" s="11"/>
       <c r="S215" s="10"/>
     </row>
-    <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B216" s="10"/>
       <c r="C216" s="11"/>
       <c r="D216" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H216" s="4"/>
       <c r="I216" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J216" s="13"/>
@@ -11016,16 +11748,16 @@
       <c r="R216" s="11"/>
       <c r="S216" s="10"/>
     </row>
-    <row r="217" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="217" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B217" s="10"/>
       <c r="C217" s="11"/>
       <c r="D217" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H217" s="4"/>
       <c r="I217" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J217" s="13"/>
@@ -11037,16 +11769,16 @@
       <c r="R217" s="11"/>
       <c r="S217" s="10"/>
     </row>
-    <row r="218" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="218" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B218" s="10"/>
       <c r="C218" s="11"/>
       <c r="D218" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H218" s="4"/>
       <c r="I218" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J218" s="13"/>
@@ -11058,16 +11790,16 @@
       <c r="R218" s="11"/>
       <c r="S218" s="10"/>
     </row>
-    <row r="219" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="219" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B219" s="10"/>
       <c r="C219" s="11"/>
       <c r="D219" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H219" s="4"/>
       <c r="I219" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J219" s="13"/>
@@ -11079,16 +11811,16 @@
       <c r="R219" s="11"/>
       <c r="S219" s="10"/>
     </row>
-    <row r="220" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="220" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B220" s="10"/>
       <c r="C220" s="11"/>
       <c r="D220" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H220" s="4"/>
       <c r="I220" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J220" s="13"/>
@@ -11100,16 +11832,16 @@
       <c r="R220" s="11"/>
       <c r="S220" s="10"/>
     </row>
-    <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B221" s="10"/>
       <c r="C221" s="11"/>
       <c r="D221" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H221" s="4"/>
       <c r="I221" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J221" s="13"/>
@@ -11121,16 +11853,16 @@
       <c r="R221" s="11"/>
       <c r="S221" s="10"/>
     </row>
-    <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B222" s="10"/>
       <c r="C222" s="11"/>
       <c r="D222" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H222" s="4"/>
       <c r="I222" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J222" s="13"/>
@@ -11142,16 +11874,16 @@
       <c r="R222" s="11"/>
       <c r="S222" s="10"/>
     </row>
-    <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B223" s="10"/>
       <c r="C223" s="11"/>
       <c r="D223" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H223" s="4"/>
       <c r="I223" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J223" s="13"/>
@@ -11163,16 +11895,16 @@
       <c r="R223" s="11"/>
       <c r="S223" s="10"/>
     </row>
-    <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B224" s="10"/>
       <c r="C224" s="11"/>
       <c r="D224" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H224" s="4"/>
       <c r="I224" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J224" s="13"/>
@@ -11184,16 +11916,16 @@
       <c r="R224" s="11"/>
       <c r="S224" s="10"/>
     </row>
-    <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B225" s="10"/>
       <c r="C225" s="11"/>
       <c r="D225" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H225" s="4"/>
       <c r="I225" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J225" s="13"/>
@@ -11205,16 +11937,16 @@
       <c r="R225" s="11"/>
       <c r="S225" s="10"/>
     </row>
-    <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B226" s="10"/>
       <c r="C226" s="11"/>
       <c r="D226" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H226" s="4"/>
       <c r="I226" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J226" s="13"/>
@@ -11226,16 +11958,16 @@
       <c r="R226" s="11"/>
       <c r="S226" s="10"/>
     </row>
-    <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B227" s="10"/>
       <c r="C227" s="11"/>
       <c r="D227" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H227" s="4"/>
       <c r="I227" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J227" s="13"/>
@@ -11247,16 +11979,16 @@
       <c r="R227" s="11"/>
       <c r="S227" s="10"/>
     </row>
-    <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B228" s="10"/>
       <c r="C228" s="11"/>
       <c r="D228" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H228" s="4"/>
       <c r="I228" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J228" s="13"/>
@@ -11268,16 +12000,16 @@
       <c r="R228" s="11"/>
       <c r="S228" s="10"/>
     </row>
-    <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B229" s="10"/>
       <c r="C229" s="11"/>
       <c r="D229" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H229" s="4"/>
       <c r="I229" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J229" s="13"/>
@@ -11289,16 +12021,16 @@
       <c r="R229" s="11"/>
       <c r="S229" s="10"/>
     </row>
-    <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B230" s="10"/>
       <c r="C230" s="11"/>
       <c r="D230" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H230" s="4"/>
       <c r="I230" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J230" s="13"/>
@@ -11310,16 +12042,16 @@
       <c r="R230" s="11"/>
       <c r="S230" s="10"/>
     </row>
-    <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B231" s="10"/>
       <c r="C231" s="11"/>
       <c r="D231" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H231" s="4"/>
       <c r="I231" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J231" s="13"/>
@@ -11331,16 +12063,16 @@
       <c r="R231" s="11"/>
       <c r="S231" s="10"/>
     </row>
-    <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B232" s="10"/>
       <c r="C232" s="11"/>
       <c r="D232" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H232" s="4"/>
       <c r="I232" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J232" s="13"/>
@@ -11352,16 +12084,16 @@
       <c r="R232" s="11"/>
       <c r="S232" s="10"/>
     </row>
-    <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B233" s="10"/>
       <c r="C233" s="11"/>
       <c r="D233" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H233" s="4"/>
       <c r="I233" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J233" s="13"/>
@@ -11373,16 +12105,16 @@
       <c r="R233" s="11"/>
       <c r="S233" s="10"/>
     </row>
-    <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B234" s="10"/>
       <c r="C234" s="11"/>
       <c r="D234" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H234" s="4"/>
       <c r="I234" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J234" s="13"/>
@@ -11394,16 +12126,16 @@
       <c r="R234" s="11"/>
       <c r="S234" s="10"/>
     </row>
-    <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B235" s="10"/>
       <c r="C235" s="11"/>
       <c r="D235" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H235" s="4"/>
       <c r="I235" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J235" s="13"/>
@@ -11415,16 +12147,16 @@
       <c r="R235" s="11"/>
       <c r="S235" s="10"/>
     </row>
-    <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B236" s="10"/>
       <c r="C236" s="11"/>
       <c r="D236" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H236" s="4"/>
       <c r="I236" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J236" s="13"/>
@@ -11436,16 +12168,16 @@
       <c r="R236" s="11"/>
       <c r="S236" s="10"/>
     </row>
-    <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B237" s="10"/>
       <c r="C237" s="11"/>
       <c r="D237" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H237" s="4"/>
       <c r="I237" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J237" s="13"/>
@@ -11457,16 +12189,16 @@
       <c r="R237" s="11"/>
       <c r="S237" s="10"/>
     </row>
-    <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B238" s="10"/>
       <c r="C238" s="11"/>
       <c r="D238" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H238" s="4"/>
       <c r="I238" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J238" s="13"/>
@@ -11478,16 +12210,16 @@
       <c r="R238" s="11"/>
       <c r="S238" s="10"/>
     </row>
-    <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B239" s="10"/>
       <c r="C239" s="11"/>
       <c r="D239" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H239" s="4"/>
       <c r="I239" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J239" s="13"/>
@@ -11499,16 +12231,16 @@
       <c r="R239" s="11"/>
       <c r="S239" s="10"/>
     </row>
-    <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B240" s="10"/>
       <c r="C240" s="11"/>
       <c r="D240" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H240" s="4"/>
       <c r="I240" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J240" s="13"/>
@@ -11520,16 +12252,16 @@
       <c r="R240" s="11"/>
       <c r="S240" s="10"/>
     </row>
-    <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B241" s="10"/>
       <c r="C241" s="11"/>
       <c r="D241" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H241" s="4"/>
       <c r="I241" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J241" s="13"/>
@@ -11541,16 +12273,16 @@
       <c r="R241" s="11"/>
       <c r="S241" s="10"/>
     </row>
-    <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B242" s="10"/>
       <c r="C242" s="11"/>
       <c r="D242" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H242" s="4"/>
       <c r="I242" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J242" s="13"/>
@@ -11562,16 +12294,16 @@
       <c r="R242" s="11"/>
       <c r="S242" s="10"/>
     </row>
-    <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B243" s="10"/>
       <c r="C243" s="11"/>
       <c r="D243" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H243" s="4"/>
       <c r="I243" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J243" s="13"/>
@@ -11583,16 +12315,16 @@
       <c r="R243" s="11"/>
       <c r="S243" s="10"/>
     </row>
-    <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B244" s="10"/>
       <c r="C244" s="11"/>
       <c r="D244" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H244" s="4"/>
       <c r="I244" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J244" s="13"/>
@@ -11604,16 +12336,16 @@
       <c r="R244" s="11"/>
       <c r="S244" s="10"/>
     </row>
-    <row r="245" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="245" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B245" s="10"/>
       <c r="C245" s="11"/>
       <c r="D245" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H245" s="4"/>
       <c r="I245" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J245" s="13"/>
@@ -11625,16 +12357,16 @@
       <c r="R245" s="11"/>
       <c r="S245" s="10"/>
     </row>
-    <row r="246" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="246" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B246" s="10"/>
       <c r="C246" s="11"/>
       <c r="D246" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H246" s="4"/>
       <c r="I246" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J246" s="13"/>
@@ -11646,16 +12378,16 @@
       <c r="R246" s="11"/>
       <c r="S246" s="10"/>
     </row>
-    <row r="247" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="247" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B247" s="10"/>
       <c r="C247" s="11"/>
       <c r="D247" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H247" s="4"/>
       <c r="I247" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J247" s="13"/>
@@ -11667,16 +12399,16 @@
       <c r="R247" s="11"/>
       <c r="S247" s="10"/>
     </row>
-    <row r="248" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="248" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B248" s="10"/>
       <c r="C248" s="11"/>
       <c r="D248" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H248" s="4"/>
       <c r="I248" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J248" s="13"/>
@@ -11688,16 +12420,16 @@
       <c r="R248" s="11"/>
       <c r="S248" s="10"/>
     </row>
-    <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B249" s="10"/>
       <c r="C249" s="11"/>
       <c r="D249" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H249" s="4"/>
       <c r="I249" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J249" s="13"/>
@@ -11709,16 +12441,16 @@
       <c r="R249" s="11"/>
       <c r="S249" s="10"/>
     </row>
-    <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B250" s="10"/>
       <c r="C250" s="11"/>
       <c r="D250" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H250" s="4"/>
       <c r="I250" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J250" s="13"/>
@@ -11730,16 +12462,16 @@
       <c r="R250" s="11"/>
       <c r="S250" s="10"/>
     </row>
-    <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B251" s="10"/>
       <c r="C251" s="11"/>
       <c r="D251" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H251" s="4"/>
       <c r="I251" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J251" s="13"/>
@@ -11751,16 +12483,16 @@
       <c r="R251" s="11"/>
       <c r="S251" s="10"/>
     </row>
-    <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B252" s="10"/>
       <c r="C252" s="11"/>
       <c r="D252" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H252" s="4"/>
       <c r="I252" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J252" s="13"/>
@@ -11772,16 +12504,16 @@
       <c r="R252" s="11"/>
       <c r="S252" s="10"/>
     </row>
-    <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B253" s="10"/>
       <c r="C253" s="11"/>
       <c r="D253" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H253" s="4"/>
       <c r="I253" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J253" s="13"/>
@@ -11793,16 +12525,16 @@
       <c r="R253" s="11"/>
       <c r="S253" s="10"/>
     </row>
-    <row r="254" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="254" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B254" s="10"/>
       <c r="C254" s="11"/>
       <c r="D254" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H254" s="4"/>
       <c r="I254" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J254" s="13"/>
@@ -11814,16 +12546,16 @@
       <c r="R254" s="11"/>
       <c r="S254" s="10"/>
     </row>
-    <row r="255" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="255" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B255" s="10"/>
       <c r="C255" s="11"/>
       <c r="D255" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H255" s="4"/>
       <c r="I255" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J255" s="13"/>
@@ -11835,16 +12567,16 @@
       <c r="R255" s="11"/>
       <c r="S255" s="10"/>
     </row>
-    <row r="256" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="256" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B256" s="10"/>
       <c r="C256" s="11"/>
       <c r="D256" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H256" s="4"/>
       <c r="I256" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J256" s="13"/>
@@ -11856,16 +12588,16 @@
       <c r="R256" s="11"/>
       <c r="S256" s="10"/>
     </row>
-    <row r="257" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="257" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B257" s="10"/>
       <c r="C257" s="11"/>
       <c r="D257" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H257" s="4"/>
       <c r="I257" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J257" s="13"/>
@@ -11877,16 +12609,16 @@
       <c r="R257" s="11"/>
       <c r="S257" s="10"/>
     </row>
-    <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B258" s="10"/>
       <c r="C258" s="11"/>
       <c r="D258" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H258" s="4"/>
       <c r="I258" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J258" s="13"/>
@@ -11898,16 +12630,16 @@
       <c r="R258" s="11"/>
       <c r="S258" s="10"/>
     </row>
-    <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B259" s="10"/>
       <c r="C259" s="11"/>
       <c r="D259" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H259" s="4"/>
       <c r="I259" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J259" s="13"/>
@@ -11919,16 +12651,16 @@
       <c r="R259" s="11"/>
       <c r="S259" s="10"/>
     </row>
-    <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B260" s="10"/>
       <c r="C260" s="11"/>
       <c r="D260" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H260" s="4"/>
       <c r="I260" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J260" s="13"/>
@@ -11940,16 +12672,16 @@
       <c r="R260" s="11"/>
       <c r="S260" s="10"/>
     </row>
-    <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B261" s="10"/>
       <c r="C261" s="11"/>
       <c r="D261" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H261" s="4"/>
       <c r="I261" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J261" s="13"/>
@@ -11961,16 +12693,16 @@
       <c r="R261" s="11"/>
       <c r="S261" s="10"/>
     </row>
-    <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B262" s="10"/>
       <c r="C262" s="11"/>
       <c r="D262" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H262" s="4"/>
       <c r="I262" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J262" s="13"/>
@@ -11982,16 +12714,16 @@
       <c r="R262" s="11"/>
       <c r="S262" s="10"/>
     </row>
-    <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B263" s="10"/>
       <c r="C263" s="11"/>
       <c r="D263" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H263" s="4"/>
       <c r="I263" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J263" s="13"/>
@@ -12003,16 +12735,16 @@
       <c r="R263" s="11"/>
       <c r="S263" s="10"/>
     </row>
-    <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B264" s="10"/>
       <c r="C264" s="11"/>
       <c r="D264" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H264" s="4"/>
       <c r="I264" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J264" s="13"/>
@@ -12024,16 +12756,16 @@
       <c r="R264" s="11"/>
       <c r="S264" s="10"/>
     </row>
-    <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B265" s="10"/>
       <c r="C265" s="11"/>
       <c r="D265" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H265" s="4"/>
       <c r="I265" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J265" s="13"/>
@@ -12045,16 +12777,16 @@
       <c r="R265" s="11"/>
       <c r="S265" s="10"/>
     </row>
-    <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B266" s="10"/>
       <c r="C266" s="11"/>
       <c r="D266" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H266" s="4"/>
       <c r="I266" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J266" s="13"/>
@@ -12066,16 +12798,16 @@
       <c r="R266" s="11"/>
       <c r="S266" s="10"/>
     </row>
-    <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B267" s="10"/>
       <c r="C267" s="11"/>
       <c r="D267" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H267" s="4"/>
       <c r="I267" s="6" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J267" s="13"/>
@@ -12087,16 +12819,16 @@
       <c r="R267" s="11"/>
       <c r="S267" s="10"/>
     </row>
-    <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
       <c r="D268" s="10" t="str">
-        <f t="shared" ref="D268:D331" si="16">IF(G268="","",IF(OR(G268="선급금",G268="중도금",G268="잔금"),"A",IF(G268="자재","B",IF(G268="특허료","C",""))))</f>
+        <f t="shared" ref="D268:D331" si="17">IF(G268="","",IF(OR(G268="선급금",G268="중도금",G268="잔금"),"A",IF(G268="자재","B",IF(G268="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" s="6" t="str">
-        <f t="shared" ref="I268:I331" ca="1" si="17">IF(C268="","",IF(L268="",TODAY()-C268,L268-C268))</f>
+        <f t="shared" ref="I268:I331" ca="1" si="18">IF(C268="","",IF(L268="",TODAY()-C268,L268-C268))</f>
         <v/>
       </c>
       <c r="J268" s="13"/>
@@ -12108,16 +12840,16 @@
       <c r="R268" s="11"/>
       <c r="S268" s="10"/>
     </row>
-    <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B269" s="10"/>
       <c r="C269" s="11"/>
       <c r="D269" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H269" s="4"/>
       <c r="I269" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J269" s="13"/>
@@ -12129,16 +12861,16 @@
       <c r="R269" s="11"/>
       <c r="S269" s="10"/>
     </row>
-    <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B270" s="10"/>
       <c r="C270" s="11"/>
       <c r="D270" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H270" s="4"/>
       <c r="I270" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J270" s="13"/>
@@ -12150,16 +12882,16 @@
       <c r="R270" s="11"/>
       <c r="S270" s="10"/>
     </row>
-    <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B271" s="10"/>
       <c r="C271" s="11"/>
       <c r="D271" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H271" s="4"/>
       <c r="I271" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J271" s="13"/>
@@ -12171,16 +12903,16 @@
       <c r="R271" s="11"/>
       <c r="S271" s="10"/>
     </row>
-    <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B272" s="10"/>
       <c r="C272" s="11"/>
       <c r="D272" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H272" s="4"/>
       <c r="I272" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J272" s="13"/>
@@ -12192,16 +12924,16 @@
       <c r="R272" s="11"/>
       <c r="S272" s="10"/>
     </row>
-    <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B273" s="10"/>
       <c r="C273" s="11"/>
       <c r="D273" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H273" s="4"/>
       <c r="I273" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J273" s="13"/>
@@ -12213,16 +12945,16 @@
       <c r="R273" s="11"/>
       <c r="S273" s="10"/>
     </row>
-    <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B274" s="10"/>
       <c r="C274" s="11"/>
       <c r="D274" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H274" s="4"/>
       <c r="I274" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J274" s="13"/>
@@ -12234,16 +12966,16 @@
       <c r="R274" s="11"/>
       <c r="S274" s="10"/>
     </row>
-    <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B275" s="10"/>
       <c r="C275" s="11"/>
       <c r="D275" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H275" s="4"/>
       <c r="I275" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J275" s="13"/>
@@ -12255,16 +12987,16 @@
       <c r="R275" s="11"/>
       <c r="S275" s="10"/>
     </row>
-    <row r="276" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="276" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B276" s="10"/>
       <c r="C276" s="11"/>
       <c r="D276" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H276" s="4"/>
       <c r="I276" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J276" s="13"/>
@@ -12276,16 +13008,16 @@
       <c r="R276" s="11"/>
       <c r="S276" s="10"/>
     </row>
-    <row r="277" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="277" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B277" s="10"/>
       <c r="C277" s="11"/>
       <c r="D277" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H277" s="4"/>
       <c r="I277" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J277" s="13"/>
@@ -12297,16 +13029,16 @@
       <c r="R277" s="11"/>
       <c r="S277" s="10"/>
     </row>
-    <row r="278" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="278" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B278" s="10"/>
       <c r="C278" s="11"/>
       <c r="D278" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H278" s="4"/>
       <c r="I278" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J278" s="13"/>
@@ -12318,16 +13050,16 @@
       <c r="R278" s="11"/>
       <c r="S278" s="10"/>
     </row>
-    <row r="279" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="279" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B279" s="10"/>
       <c r="C279" s="11"/>
       <c r="D279" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H279" s="4"/>
       <c r="I279" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J279" s="13"/>
@@ -12339,16 +13071,16 @@
       <c r="R279" s="11"/>
       <c r="S279" s="10"/>
     </row>
-    <row r="280" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="280" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B280" s="10"/>
       <c r="C280" s="11"/>
       <c r="D280" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H280" s="4"/>
       <c r="I280" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J280" s="13"/>
@@ -12360,16 +13092,16 @@
       <c r="R280" s="11"/>
       <c r="S280" s="10"/>
     </row>
-    <row r="281" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="281" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B281" s="10"/>
       <c r="C281" s="11"/>
       <c r="D281" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H281" s="4"/>
       <c r="I281" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J281" s="13"/>
@@ -12381,16 +13113,16 @@
       <c r="R281" s="11"/>
       <c r="S281" s="10"/>
     </row>
-    <row r="282" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="282" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B282" s="10"/>
       <c r="C282" s="11"/>
       <c r="D282" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H282" s="4"/>
       <c r="I282" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J282" s="13"/>
@@ -12402,16 +13134,16 @@
       <c r="R282" s="11"/>
       <c r="S282" s="10"/>
     </row>
-    <row r="283" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="283" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B283" s="10"/>
       <c r="C283" s="11"/>
       <c r="D283" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H283" s="4"/>
       <c r="I283" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J283" s="13"/>
@@ -12423,16 +13155,16 @@
       <c r="R283" s="11"/>
       <c r="S283" s="10"/>
     </row>
-    <row r="284" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="284" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B284" s="10"/>
       <c r="C284" s="11"/>
       <c r="D284" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H284" s="4"/>
       <c r="I284" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J284" s="13"/>
@@ -12444,16 +13176,16 @@
       <c r="R284" s="11"/>
       <c r="S284" s="10"/>
     </row>
-    <row r="285" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="285" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B285" s="10"/>
       <c r="C285" s="11"/>
       <c r="D285" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H285" s="4"/>
       <c r="I285" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J285" s="13"/>
@@ -12465,16 +13197,16 @@
       <c r="R285" s="11"/>
       <c r="S285" s="10"/>
     </row>
-    <row r="286" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="286" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B286" s="10"/>
       <c r="C286" s="11"/>
       <c r="D286" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H286" s="4"/>
       <c r="I286" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J286" s="13"/>
@@ -12486,16 +13218,16 @@
       <c r="R286" s="11"/>
       <c r="S286" s="10"/>
     </row>
-    <row r="287" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="287" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B287" s="10"/>
       <c r="C287" s="11"/>
       <c r="D287" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H287" s="4"/>
       <c r="I287" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J287" s="13"/>
@@ -12507,16 +13239,16 @@
       <c r="R287" s="11"/>
       <c r="S287" s="10"/>
     </row>
-    <row r="288" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="288" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B288" s="10"/>
       <c r="C288" s="11"/>
       <c r="D288" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H288" s="4"/>
       <c r="I288" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J288" s="13"/>
@@ -12528,16 +13260,16 @@
       <c r="R288" s="11"/>
       <c r="S288" s="10"/>
     </row>
-    <row r="289" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="289" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B289" s="10"/>
       <c r="C289" s="11"/>
       <c r="D289" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H289" s="4"/>
       <c r="I289" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J289" s="13"/>
@@ -12549,16 +13281,16 @@
       <c r="R289" s="11"/>
       <c r="S289" s="10"/>
     </row>
-    <row r="290" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="290" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B290" s="10"/>
       <c r="C290" s="11"/>
       <c r="D290" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H290" s="4"/>
       <c r="I290" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J290" s="13"/>
@@ -12570,16 +13302,16 @@
       <c r="R290" s="11"/>
       <c r="S290" s="10"/>
     </row>
-    <row r="291" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="291" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B291" s="10"/>
       <c r="C291" s="11"/>
       <c r="D291" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H291" s="4"/>
       <c r="I291" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J291" s="13"/>
@@ -12591,16 +13323,16 @@
       <c r="R291" s="11"/>
       <c r="S291" s="10"/>
     </row>
-    <row r="292" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="292" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B292" s="10"/>
       <c r="C292" s="11"/>
       <c r="D292" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H292" s="4"/>
       <c r="I292" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J292" s="13"/>
@@ -12612,16 +13344,16 @@
       <c r="R292" s="11"/>
       <c r="S292" s="10"/>
     </row>
-    <row r="293" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="293" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B293" s="10"/>
       <c r="C293" s="11"/>
       <c r="D293" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H293" s="4"/>
       <c r="I293" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J293" s="13"/>
@@ -12633,16 +13365,16 @@
       <c r="R293" s="11"/>
       <c r="S293" s="10"/>
     </row>
-    <row r="294" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="294" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B294" s="10"/>
       <c r="C294" s="11"/>
       <c r="D294" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H294" s="4"/>
       <c r="I294" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J294" s="13"/>
@@ -12654,16 +13386,16 @@
       <c r="R294" s="11"/>
       <c r="S294" s="10"/>
     </row>
-    <row r="295" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="295" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B295" s="10"/>
       <c r="C295" s="11"/>
       <c r="D295" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H295" s="4"/>
       <c r="I295" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J295" s="13"/>
@@ -12675,16 +13407,16 @@
       <c r="R295" s="11"/>
       <c r="S295" s="10"/>
     </row>
-    <row r="296" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="296" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B296" s="10"/>
       <c r="C296" s="11"/>
       <c r="D296" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H296" s="4"/>
       <c r="I296" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J296" s="13"/>
@@ -12696,16 +13428,16 @@
       <c r="R296" s="11"/>
       <c r="S296" s="10"/>
     </row>
-    <row r="297" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="297" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B297" s="10"/>
       <c r="C297" s="11"/>
       <c r="D297" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H297" s="4"/>
       <c r="I297" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J297" s="13"/>
@@ -12717,16 +13449,16 @@
       <c r="R297" s="11"/>
       <c r="S297" s="10"/>
     </row>
-    <row r="298" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="298" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B298" s="10"/>
       <c r="C298" s="11"/>
       <c r="D298" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H298" s="4"/>
       <c r="I298" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J298" s="13"/>
@@ -12738,16 +13470,16 @@
       <c r="R298" s="11"/>
       <c r="S298" s="10"/>
     </row>
-    <row r="299" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="299" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B299" s="10"/>
       <c r="C299" s="11"/>
       <c r="D299" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H299" s="4"/>
       <c r="I299" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J299" s="13"/>
@@ -12759,16 +13491,16 @@
       <c r="R299" s="11"/>
       <c r="S299" s="10"/>
     </row>
-    <row r="300" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="300" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B300" s="10"/>
       <c r="C300" s="11"/>
       <c r="D300" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H300" s="4"/>
       <c r="I300" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J300" s="13"/>
@@ -12780,16 +13512,16 @@
       <c r="R300" s="11"/>
       <c r="S300" s="10"/>
     </row>
-    <row r="301" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="301" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B301" s="10"/>
       <c r="C301" s="11"/>
       <c r="D301" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H301" s="4"/>
       <c r="I301" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J301" s="13"/>
@@ -12801,16 +13533,16 @@
       <c r="R301" s="11"/>
       <c r="S301" s="10"/>
     </row>
-    <row r="302" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="302" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B302" s="10"/>
       <c r="C302" s="11"/>
       <c r="D302" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H302" s="4"/>
       <c r="I302" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J302" s="13"/>
@@ -12822,16 +13554,16 @@
       <c r="R302" s="11"/>
       <c r="S302" s="10"/>
     </row>
-    <row r="303" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="303" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B303" s="10"/>
       <c r="C303" s="11"/>
       <c r="D303" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H303" s="4"/>
       <c r="I303" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J303" s="13"/>
@@ -12843,16 +13575,16 @@
       <c r="R303" s="11"/>
       <c r="S303" s="10"/>
     </row>
-    <row r="304" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="304" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B304" s="10"/>
       <c r="C304" s="11"/>
       <c r="D304" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H304" s="4"/>
       <c r="I304" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J304" s="13"/>
@@ -12864,16 +13596,16 @@
       <c r="R304" s="11"/>
       <c r="S304" s="10"/>
     </row>
-    <row r="305" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="305" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B305" s="10"/>
       <c r="C305" s="11"/>
       <c r="D305" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H305" s="4"/>
       <c r="I305" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J305" s="13"/>
@@ -12885,16 +13617,16 @@
       <c r="R305" s="11"/>
       <c r="S305" s="10"/>
     </row>
-    <row r="306" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="306" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B306" s="10"/>
       <c r="C306" s="11"/>
       <c r="D306" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H306" s="4"/>
       <c r="I306" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J306" s="13"/>
@@ -12906,16 +13638,16 @@
       <c r="R306" s="11"/>
       <c r="S306" s="10"/>
     </row>
-    <row r="307" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="307" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B307" s="10"/>
       <c r="C307" s="11"/>
       <c r="D307" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H307" s="4"/>
       <c r="I307" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J307" s="13"/>
@@ -12927,16 +13659,16 @@
       <c r="R307" s="11"/>
       <c r="S307" s="10"/>
     </row>
-    <row r="308" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="308" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B308" s="10"/>
       <c r="C308" s="11"/>
       <c r="D308" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H308" s="4"/>
       <c r="I308" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J308" s="13"/>
@@ -12948,16 +13680,16 @@
       <c r="R308" s="11"/>
       <c r="S308" s="10"/>
     </row>
-    <row r="309" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="309" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B309" s="10"/>
       <c r="C309" s="11"/>
       <c r="D309" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H309" s="4"/>
       <c r="I309" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J309" s="13"/>
@@ -12969,16 +13701,16 @@
       <c r="R309" s="11"/>
       <c r="S309" s="10"/>
     </row>
-    <row r="310" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="310" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B310" s="10"/>
       <c r="C310" s="11"/>
       <c r="D310" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H310" s="4"/>
       <c r="I310" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J310" s="13"/>
@@ -12990,16 +13722,16 @@
       <c r="R310" s="11"/>
       <c r="S310" s="10"/>
     </row>
-    <row r="311" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="311" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B311" s="10"/>
       <c r="C311" s="11"/>
       <c r="D311" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H311" s="4"/>
       <c r="I311" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J311" s="13"/>
@@ -13011,16 +13743,16 @@
       <c r="R311" s="11"/>
       <c r="S311" s="10"/>
     </row>
-    <row r="312" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="312" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B312" s="10"/>
       <c r="C312" s="11"/>
       <c r="D312" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H312" s="4"/>
       <c r="I312" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J312" s="13"/>
@@ -13032,16 +13764,16 @@
       <c r="R312" s="11"/>
       <c r="S312" s="10"/>
     </row>
-    <row r="313" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="313" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B313" s="10"/>
       <c r="C313" s="11"/>
       <c r="D313" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H313" s="4"/>
       <c r="I313" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J313" s="13"/>
@@ -13053,16 +13785,16 @@
       <c r="R313" s="11"/>
       <c r="S313" s="10"/>
     </row>
-    <row r="314" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="314" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B314" s="10"/>
       <c r="C314" s="11"/>
       <c r="D314" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H314" s="4"/>
       <c r="I314" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J314" s="13"/>
@@ -13074,16 +13806,16 @@
       <c r="R314" s="11"/>
       <c r="S314" s="10"/>
     </row>
-    <row r="315" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="315" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B315" s="10"/>
       <c r="C315" s="11"/>
       <c r="D315" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H315" s="4"/>
       <c r="I315" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J315" s="13"/>
@@ -13095,16 +13827,16 @@
       <c r="R315" s="11"/>
       <c r="S315" s="10"/>
     </row>
-    <row r="316" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="316" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B316" s="10"/>
       <c r="C316" s="11"/>
       <c r="D316" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H316" s="4"/>
       <c r="I316" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J316" s="13"/>
@@ -13116,16 +13848,16 @@
       <c r="R316" s="11"/>
       <c r="S316" s="10"/>
     </row>
-    <row r="317" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="317" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B317" s="10"/>
       <c r="C317" s="11"/>
       <c r="D317" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H317" s="4"/>
       <c r="I317" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J317" s="13"/>
@@ -13137,16 +13869,16 @@
       <c r="R317" s="11"/>
       <c r="S317" s="10"/>
     </row>
-    <row r="318" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="318" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B318" s="10"/>
       <c r="C318" s="11"/>
       <c r="D318" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H318" s="4"/>
       <c r="I318" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J318" s="13"/>
@@ -13158,16 +13890,16 @@
       <c r="R318" s="11"/>
       <c r="S318" s="10"/>
     </row>
-    <row r="319" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="319" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B319" s="10"/>
       <c r="C319" s="11"/>
       <c r="D319" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H319" s="4"/>
       <c r="I319" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J319" s="13"/>
@@ -13179,16 +13911,16 @@
       <c r="R319" s="11"/>
       <c r="S319" s="10"/>
     </row>
-    <row r="320" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="320" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B320" s="10"/>
       <c r="C320" s="11"/>
       <c r="D320" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H320" s="4"/>
       <c r="I320" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J320" s="13"/>
@@ -13200,16 +13932,16 @@
       <c r="R320" s="11"/>
       <c r="S320" s="10"/>
     </row>
-    <row r="321" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="321" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B321" s="10"/>
       <c r="C321" s="11"/>
       <c r="D321" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H321" s="4"/>
       <c r="I321" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J321" s="13"/>
@@ -13221,16 +13953,16 @@
       <c r="R321" s="11"/>
       <c r="S321" s="10"/>
     </row>
-    <row r="322" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="322" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B322" s="10"/>
       <c r="C322" s="11"/>
       <c r="D322" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H322" s="4"/>
       <c r="I322" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J322" s="13"/>
@@ -13242,16 +13974,16 @@
       <c r="R322" s="11"/>
       <c r="S322" s="10"/>
     </row>
-    <row r="323" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="323" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B323" s="10"/>
       <c r="C323" s="11"/>
       <c r="D323" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H323" s="4"/>
       <c r="I323" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J323" s="13"/>
@@ -13263,16 +13995,16 @@
       <c r="R323" s="11"/>
       <c r="S323" s="10"/>
     </row>
-    <row r="324" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="324" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B324" s="10"/>
       <c r="C324" s="11"/>
       <c r="D324" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H324" s="4"/>
       <c r="I324" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J324" s="13"/>
@@ -13284,16 +14016,16 @@
       <c r="R324" s="11"/>
       <c r="S324" s="10"/>
     </row>
-    <row r="325" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="325" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B325" s="10"/>
       <c r="C325" s="11"/>
       <c r="D325" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H325" s="4"/>
       <c r="I325" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J325" s="13"/>
@@ -13305,16 +14037,16 @@
       <c r="R325" s="11"/>
       <c r="S325" s="10"/>
     </row>
-    <row r="326" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="326" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B326" s="10"/>
       <c r="C326" s="11"/>
       <c r="D326" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H326" s="4"/>
       <c r="I326" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J326" s="13"/>
@@ -13326,16 +14058,16 @@
       <c r="R326" s="11"/>
       <c r="S326" s="10"/>
     </row>
-    <row r="327" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="327" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B327" s="10"/>
       <c r="C327" s="11"/>
       <c r="D327" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H327" s="4"/>
       <c r="I327" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J327" s="13"/>
@@ -13347,16 +14079,16 @@
       <c r="R327" s="11"/>
       <c r="S327" s="10"/>
     </row>
-    <row r="328" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="328" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B328" s="10"/>
       <c r="C328" s="11"/>
       <c r="D328" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H328" s="4"/>
       <c r="I328" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J328" s="13"/>
@@ -13368,16 +14100,16 @@
       <c r="R328" s="11"/>
       <c r="S328" s="10"/>
     </row>
-    <row r="329" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="329" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B329" s="10"/>
       <c r="C329" s="11"/>
       <c r="D329" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H329" s="4"/>
       <c r="I329" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J329" s="13"/>
@@ -13389,16 +14121,16 @@
       <c r="R329" s="11"/>
       <c r="S329" s="10"/>
     </row>
-    <row r="330" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="330" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B330" s="10"/>
       <c r="C330" s="11"/>
       <c r="D330" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H330" s="4"/>
       <c r="I330" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J330" s="13"/>
@@ -13410,16 +14142,16 @@
       <c r="R330" s="11"/>
       <c r="S330" s="10"/>
     </row>
-    <row r="331" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="331" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
       <c r="D331" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H331" s="4"/>
       <c r="I331" s="6" t="str">
-        <f t="shared" ca="1" si="17"/>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J331" s="13"/>
@@ -13431,16 +14163,16 @@
       <c r="R331" s="11"/>
       <c r="S331" s="10"/>
     </row>
-    <row r="332" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="332" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
-        <f t="shared" ref="D332:D395" si="18">IF(G332="","",IF(OR(G332="선급금",G332="중도금",G332="잔금"),"A",IF(G332="자재","B",IF(G332="특허료","C",""))))</f>
+        <f t="shared" ref="D332:D395" si="19">IF(G332="","",IF(OR(G332="선급금",G332="중도금",G332="잔금"),"A",IF(G332="자재","B",IF(G332="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="6" t="str">
-        <f t="shared" ref="I332:I395" ca="1" si="19">IF(C332="","",IF(L332="",TODAY()-C332,L332-C332))</f>
+        <f t="shared" ref="I332:I395" ca="1" si="20">IF(C332="","",IF(L332="",TODAY()-C332,L332-C332))</f>
         <v/>
       </c>
       <c r="J332" s="13"/>
@@ -13452,16 +14184,16 @@
       <c r="R332" s="11"/>
       <c r="S332" s="10"/>
     </row>
-    <row r="333" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="333" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B333" s="10"/>
       <c r="C333" s="11"/>
       <c r="D333" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H333" s="4"/>
       <c r="I333" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J333" s="13"/>
@@ -13473,16 +14205,16 @@
       <c r="R333" s="11"/>
       <c r="S333" s="10"/>
     </row>
-    <row r="334" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="334" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B334" s="10"/>
       <c r="C334" s="11"/>
       <c r="D334" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H334" s="4"/>
       <c r="I334" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J334" s="13"/>
@@ -13494,16 +14226,16 @@
       <c r="R334" s="11"/>
       <c r="S334" s="10"/>
     </row>
-    <row r="335" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="335" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B335" s="10"/>
       <c r="C335" s="11"/>
       <c r="D335" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H335" s="4"/>
       <c r="I335" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J335" s="13"/>
@@ -13515,16 +14247,16 @@
       <c r="R335" s="11"/>
       <c r="S335" s="10"/>
     </row>
-    <row r="336" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="336" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B336" s="10"/>
       <c r="C336" s="11"/>
       <c r="D336" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H336" s="4"/>
       <c r="I336" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J336" s="13"/>
@@ -13536,16 +14268,16 @@
       <c r="R336" s="11"/>
       <c r="S336" s="10"/>
     </row>
-    <row r="337" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="337" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B337" s="10"/>
       <c r="C337" s="11"/>
       <c r="D337" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H337" s="4"/>
       <c r="I337" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J337" s="13"/>
@@ -13557,16 +14289,16 @@
       <c r="R337" s="11"/>
       <c r="S337" s="10"/>
     </row>
-    <row r="338" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="338" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B338" s="10"/>
       <c r="C338" s="11"/>
       <c r="D338" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H338" s="4"/>
       <c r="I338" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J338" s="13"/>
@@ -13578,16 +14310,16 @@
       <c r="R338" s="11"/>
       <c r="S338" s="10"/>
     </row>
-    <row r="339" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="339" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B339" s="10"/>
       <c r="C339" s="11"/>
       <c r="D339" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H339" s="4"/>
       <c r="I339" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J339" s="13"/>
@@ -13599,16 +14331,16 @@
       <c r="R339" s="11"/>
       <c r="S339" s="10"/>
     </row>
-    <row r="340" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="340" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B340" s="10"/>
       <c r="C340" s="11"/>
       <c r="D340" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H340" s="4"/>
       <c r="I340" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J340" s="13"/>
@@ -13620,16 +14352,16 @@
       <c r="R340" s="11"/>
       <c r="S340" s="10"/>
     </row>
-    <row r="341" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="341" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B341" s="10"/>
       <c r="C341" s="11"/>
       <c r="D341" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H341" s="4"/>
       <c r="I341" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J341" s="13"/>
@@ -13641,16 +14373,16 @@
       <c r="R341" s="11"/>
       <c r="S341" s="10"/>
     </row>
-    <row r="342" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="342" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B342" s="10"/>
       <c r="C342" s="11"/>
       <c r="D342" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H342" s="4"/>
       <c r="I342" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J342" s="13"/>
@@ -13662,16 +14394,16 @@
       <c r="R342" s="11"/>
       <c r="S342" s="10"/>
     </row>
-    <row r="343" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="343" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B343" s="10"/>
       <c r="C343" s="11"/>
       <c r="D343" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H343" s="4"/>
       <c r="I343" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J343" s="13"/>
@@ -13683,16 +14415,16 @@
       <c r="R343" s="11"/>
       <c r="S343" s="10"/>
     </row>
-    <row r="344" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="344" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B344" s="10"/>
       <c r="C344" s="11"/>
       <c r="D344" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H344" s="4"/>
       <c r="I344" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J344" s="13"/>
@@ -13704,16 +14436,16 @@
       <c r="R344" s="11"/>
       <c r="S344" s="10"/>
     </row>
-    <row r="345" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="345" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B345" s="10"/>
       <c r="C345" s="11"/>
       <c r="D345" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H345" s="4"/>
       <c r="I345" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J345" s="13"/>
@@ -13725,16 +14457,16 @@
       <c r="R345" s="11"/>
       <c r="S345" s="10"/>
     </row>
-    <row r="346" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="346" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B346" s="10"/>
       <c r="C346" s="11"/>
       <c r="D346" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H346" s="4"/>
       <c r="I346" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J346" s="13"/>
@@ -13746,16 +14478,16 @@
       <c r="R346" s="11"/>
       <c r="S346" s="10"/>
     </row>
-    <row r="347" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="347" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B347" s="10"/>
       <c r="C347" s="11"/>
       <c r="D347" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H347" s="4"/>
       <c r="I347" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J347" s="13"/>
@@ -13767,16 +14499,16 @@
       <c r="R347" s="11"/>
       <c r="S347" s="10"/>
     </row>
-    <row r="348" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="348" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B348" s="10"/>
       <c r="C348" s="11"/>
       <c r="D348" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H348" s="4"/>
       <c r="I348" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J348" s="13"/>
@@ -13788,16 +14520,16 @@
       <c r="R348" s="11"/>
       <c r="S348" s="10"/>
     </row>
-    <row r="349" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="349" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B349" s="10"/>
       <c r="C349" s="11"/>
       <c r="D349" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H349" s="4"/>
       <c r="I349" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J349" s="13"/>
@@ -13809,16 +14541,16 @@
       <c r="R349" s="11"/>
       <c r="S349" s="10"/>
     </row>
-    <row r="350" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="350" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B350" s="10"/>
       <c r="C350" s="11"/>
       <c r="D350" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H350" s="4"/>
       <c r="I350" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J350" s="13"/>
@@ -13830,16 +14562,16 @@
       <c r="R350" s="11"/>
       <c r="S350" s="10"/>
     </row>
-    <row r="351" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="351" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B351" s="10"/>
       <c r="C351" s="11"/>
       <c r="D351" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H351" s="4"/>
       <c r="I351" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J351" s="13"/>
@@ -13851,16 +14583,16 @@
       <c r="R351" s="11"/>
       <c r="S351" s="10"/>
     </row>
-    <row r="352" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="352" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B352" s="10"/>
       <c r="C352" s="11"/>
       <c r="D352" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H352" s="4"/>
       <c r="I352" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J352" s="13"/>
@@ -13872,16 +14604,16 @@
       <c r="R352" s="11"/>
       <c r="S352" s="10"/>
     </row>
-    <row r="353" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="353" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B353" s="10"/>
       <c r="C353" s="11"/>
       <c r="D353" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H353" s="4"/>
       <c r="I353" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J353" s="13"/>
@@ -13893,16 +14625,16 @@
       <c r="R353" s="11"/>
       <c r="S353" s="10"/>
     </row>
-    <row r="354" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="354" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B354" s="10"/>
       <c r="C354" s="11"/>
       <c r="D354" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H354" s="4"/>
       <c r="I354" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J354" s="13"/>
@@ -13914,16 +14646,16 @@
       <c r="R354" s="11"/>
       <c r="S354" s="10"/>
     </row>
-    <row r="355" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="355" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B355" s="10"/>
       <c r="C355" s="11"/>
       <c r="D355" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H355" s="4"/>
       <c r="I355" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J355" s="13"/>
@@ -13935,16 +14667,16 @@
       <c r="R355" s="11"/>
       <c r="S355" s="10"/>
     </row>
-    <row r="356" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="356" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B356" s="10"/>
       <c r="C356" s="11"/>
       <c r="D356" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H356" s="4"/>
       <c r="I356" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J356" s="13"/>
@@ -13956,16 +14688,16 @@
       <c r="R356" s="11"/>
       <c r="S356" s="10"/>
     </row>
-    <row r="357" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="357" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B357" s="10"/>
       <c r="C357" s="11"/>
       <c r="D357" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H357" s="4"/>
       <c r="I357" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J357" s="13"/>
@@ -13977,16 +14709,16 @@
       <c r="R357" s="11"/>
       <c r="S357" s="10"/>
     </row>
-    <row r="358" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="358" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B358" s="10"/>
       <c r="C358" s="11"/>
       <c r="D358" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H358" s="4"/>
       <c r="I358" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J358" s="13"/>
@@ -13998,16 +14730,16 @@
       <c r="R358" s="11"/>
       <c r="S358" s="10"/>
     </row>
-    <row r="359" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="359" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B359" s="10"/>
       <c r="C359" s="11"/>
       <c r="D359" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H359" s="4"/>
       <c r="I359" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J359" s="13"/>
@@ -14019,16 +14751,16 @@
       <c r="R359" s="11"/>
       <c r="S359" s="10"/>
     </row>
-    <row r="360" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="360" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B360" s="10"/>
       <c r="C360" s="11"/>
       <c r="D360" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H360" s="4"/>
       <c r="I360" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J360" s="13"/>
@@ -14040,16 +14772,16 @@
       <c r="R360" s="11"/>
       <c r="S360" s="10"/>
     </row>
-    <row r="361" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="361" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B361" s="10"/>
       <c r="C361" s="11"/>
       <c r="D361" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H361" s="4"/>
       <c r="I361" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J361" s="13"/>
@@ -14061,16 +14793,16 @@
       <c r="R361" s="11"/>
       <c r="S361" s="10"/>
     </row>
-    <row r="362" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="362" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B362" s="10"/>
       <c r="C362" s="11"/>
       <c r="D362" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H362" s="4"/>
       <c r="I362" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J362" s="13"/>
@@ -14082,16 +14814,16 @@
       <c r="R362" s="11"/>
       <c r="S362" s="10"/>
     </row>
-    <row r="363" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="363" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B363" s="10"/>
       <c r="C363" s="11"/>
       <c r="D363" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H363" s="4"/>
       <c r="I363" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J363" s="13"/>
@@ -14103,16 +14835,16 @@
       <c r="R363" s="11"/>
       <c r="S363" s="10"/>
     </row>
-    <row r="364" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="364" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B364" s="10"/>
       <c r="C364" s="11"/>
       <c r="D364" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H364" s="4"/>
       <c r="I364" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J364" s="13"/>
@@ -14124,16 +14856,16 @@
       <c r="R364" s="11"/>
       <c r="S364" s="10"/>
     </row>
-    <row r="365" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="365" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B365" s="10"/>
       <c r="C365" s="11"/>
       <c r="D365" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H365" s="4"/>
       <c r="I365" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J365" s="13"/>
@@ -14145,16 +14877,16 @@
       <c r="R365" s="11"/>
       <c r="S365" s="10"/>
     </row>
-    <row r="366" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="366" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B366" s="10"/>
       <c r="C366" s="11"/>
       <c r="D366" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H366" s="4"/>
       <c r="I366" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J366" s="13"/>
@@ -14166,16 +14898,16 @@
       <c r="R366" s="11"/>
       <c r="S366" s="10"/>
     </row>
-    <row r="367" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="367" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B367" s="10"/>
       <c r="C367" s="11"/>
       <c r="D367" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H367" s="4"/>
       <c r="I367" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J367" s="13"/>
@@ -14187,16 +14919,16 @@
       <c r="R367" s="11"/>
       <c r="S367" s="10"/>
     </row>
-    <row r="368" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="368" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B368" s="10"/>
       <c r="C368" s="11"/>
       <c r="D368" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H368" s="4"/>
       <c r="I368" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J368" s="13"/>
@@ -14208,16 +14940,16 @@
       <c r="R368" s="11"/>
       <c r="S368" s="10"/>
     </row>
-    <row r="369" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="369" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B369" s="10"/>
       <c r="C369" s="11"/>
       <c r="D369" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H369" s="4"/>
       <c r="I369" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J369" s="13"/>
@@ -14229,16 +14961,16 @@
       <c r="R369" s="11"/>
       <c r="S369" s="10"/>
     </row>
-    <row r="370" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="370" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B370" s="10"/>
       <c r="C370" s="11"/>
       <c r="D370" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H370" s="4"/>
       <c r="I370" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J370" s="13"/>
@@ -14250,16 +14982,16 @@
       <c r="R370" s="11"/>
       <c r="S370" s="10"/>
     </row>
-    <row r="371" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="371" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B371" s="10"/>
       <c r="C371" s="11"/>
       <c r="D371" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H371" s="4"/>
       <c r="I371" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J371" s="13"/>
@@ -14271,16 +15003,16 @@
       <c r="R371" s="11"/>
       <c r="S371" s="10"/>
     </row>
-    <row r="372" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="372" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B372" s="10"/>
       <c r="C372" s="11"/>
       <c r="D372" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H372" s="4"/>
       <c r="I372" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J372" s="13"/>
@@ -14292,16 +15024,16 @@
       <c r="R372" s="11"/>
       <c r="S372" s="10"/>
     </row>
-    <row r="373" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="373" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B373" s="10"/>
       <c r="C373" s="11"/>
       <c r="D373" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H373" s="4"/>
       <c r="I373" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J373" s="13"/>
@@ -14313,16 +15045,16 @@
       <c r="R373" s="11"/>
       <c r="S373" s="10"/>
     </row>
-    <row r="374" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="374" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B374" s="10"/>
       <c r="C374" s="11"/>
       <c r="D374" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H374" s="4"/>
       <c r="I374" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J374" s="13"/>
@@ -14334,16 +15066,16 @@
       <c r="R374" s="11"/>
       <c r="S374" s="10"/>
     </row>
-    <row r="375" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="375" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B375" s="10"/>
       <c r="C375" s="11"/>
       <c r="D375" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H375" s="4"/>
       <c r="I375" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J375" s="13"/>
@@ -14355,16 +15087,16 @@
       <c r="R375" s="11"/>
       <c r="S375" s="10"/>
     </row>
-    <row r="376" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="376" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B376" s="10"/>
       <c r="C376" s="11"/>
       <c r="D376" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H376" s="4"/>
       <c r="I376" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J376" s="13"/>
@@ -14376,16 +15108,16 @@
       <c r="R376" s="11"/>
       <c r="S376" s="10"/>
     </row>
-    <row r="377" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="377" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B377" s="10"/>
       <c r="C377" s="11"/>
       <c r="D377" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H377" s="4"/>
       <c r="I377" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J377" s="13"/>
@@ -14397,16 +15129,16 @@
       <c r="R377" s="11"/>
       <c r="S377" s="10"/>
     </row>
-    <row r="378" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="378" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B378" s="10"/>
       <c r="C378" s="11"/>
       <c r="D378" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H378" s="4"/>
       <c r="I378" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J378" s="13"/>
@@ -14418,16 +15150,16 @@
       <c r="R378" s="11"/>
       <c r="S378" s="10"/>
     </row>
-    <row r="379" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="379" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B379" s="10"/>
       <c r="C379" s="11"/>
       <c r="D379" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H379" s="4"/>
       <c r="I379" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J379" s="13"/>
@@ -14439,16 +15171,16 @@
       <c r="R379" s="11"/>
       <c r="S379" s="10"/>
     </row>
-    <row r="380" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="380" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B380" s="10"/>
       <c r="C380" s="11"/>
       <c r="D380" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H380" s="4"/>
       <c r="I380" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J380" s="13"/>
@@ -14460,16 +15192,16 @@
       <c r="R380" s="11"/>
       <c r="S380" s="10"/>
     </row>
-    <row r="381" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="381" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B381" s="10"/>
       <c r="C381" s="11"/>
       <c r="D381" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H381" s="4"/>
       <c r="I381" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J381" s="13"/>
@@ -14481,16 +15213,16 @@
       <c r="R381" s="11"/>
       <c r="S381" s="10"/>
     </row>
-    <row r="382" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="382" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B382" s="10"/>
       <c r="C382" s="11"/>
       <c r="D382" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H382" s="4"/>
       <c r="I382" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J382" s="13"/>
@@ -14502,16 +15234,16 @@
       <c r="R382" s="11"/>
       <c r="S382" s="10"/>
     </row>
-    <row r="383" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="383" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B383" s="10"/>
       <c r="C383" s="11"/>
       <c r="D383" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H383" s="4"/>
       <c r="I383" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J383" s="13"/>
@@ -14523,16 +15255,16 @@
       <c r="R383" s="11"/>
       <c r="S383" s="10"/>
     </row>
-    <row r="384" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="384" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B384" s="10"/>
       <c r="C384" s="11"/>
       <c r="D384" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H384" s="4"/>
       <c r="I384" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J384" s="13"/>
@@ -14544,16 +15276,16 @@
       <c r="R384" s="11"/>
       <c r="S384" s="10"/>
     </row>
-    <row r="385" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="385" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B385" s="10"/>
       <c r="C385" s="11"/>
       <c r="D385" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H385" s="4"/>
       <c r="I385" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J385" s="13"/>
@@ -14565,16 +15297,16 @@
       <c r="R385" s="11"/>
       <c r="S385" s="10"/>
     </row>
-    <row r="386" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="386" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B386" s="10"/>
       <c r="C386" s="11"/>
       <c r="D386" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H386" s="4"/>
       <c r="I386" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J386" s="13"/>
@@ -14586,16 +15318,16 @@
       <c r="R386" s="11"/>
       <c r="S386" s="10"/>
     </row>
-    <row r="387" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="387" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B387" s="10"/>
       <c r="C387" s="11"/>
       <c r="D387" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H387" s="4"/>
       <c r="I387" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J387" s="13"/>
@@ -14607,16 +15339,16 @@
       <c r="R387" s="11"/>
       <c r="S387" s="10"/>
     </row>
-    <row r="388" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="388" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B388" s="10"/>
       <c r="C388" s="11"/>
       <c r="D388" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H388" s="4"/>
       <c r="I388" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J388" s="13"/>
@@ -14628,16 +15360,16 @@
       <c r="R388" s="11"/>
       <c r="S388" s="10"/>
     </row>
-    <row r="389" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="389" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B389" s="10"/>
       <c r="C389" s="11"/>
       <c r="D389" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H389" s="4"/>
       <c r="I389" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J389" s="13"/>
@@ -14649,16 +15381,16 @@
       <c r="R389" s="11"/>
       <c r="S389" s="10"/>
     </row>
-    <row r="390" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="390" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B390" s="10"/>
       <c r="C390" s="11"/>
       <c r="D390" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H390" s="4"/>
       <c r="I390" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J390" s="13"/>
@@ -14670,16 +15402,16 @@
       <c r="R390" s="11"/>
       <c r="S390" s="10"/>
     </row>
-    <row r="391" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="391" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B391" s="10"/>
       <c r="C391" s="11"/>
       <c r="D391" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H391" s="4"/>
       <c r="I391" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J391" s="13"/>
@@ -14691,16 +15423,16 @@
       <c r="R391" s="11"/>
       <c r="S391" s="10"/>
     </row>
-    <row r="392" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="392" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B392" s="10"/>
       <c r="C392" s="11"/>
       <c r="D392" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H392" s="4"/>
       <c r="I392" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J392" s="13"/>
@@ -14712,16 +15444,16 @@
       <c r="R392" s="11"/>
       <c r="S392" s="10"/>
     </row>
-    <row r="393" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="393" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B393" s="10"/>
       <c r="C393" s="11"/>
       <c r="D393" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H393" s="4"/>
       <c r="I393" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J393" s="13"/>
@@ -14733,16 +15465,16 @@
       <c r="R393" s="11"/>
       <c r="S393" s="10"/>
     </row>
-    <row r="394" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="394" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B394" s="10"/>
       <c r="C394" s="11"/>
       <c r="D394" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H394" s="4"/>
       <c r="I394" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J394" s="13"/>
@@ -14754,16 +15486,16 @@
       <c r="R394" s="11"/>
       <c r="S394" s="10"/>
     </row>
-    <row r="395" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="395" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
       <c r="D395" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H395" s="4"/>
       <c r="I395" s="6" t="str">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J395" s="13"/>
@@ -14775,16 +15507,16 @@
       <c r="R395" s="11"/>
       <c r="S395" s="10"/>
     </row>
-    <row r="396" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="396" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
-        <f t="shared" ref="D396:D408" si="20">IF(G396="","",IF(OR(G396="선급금",G396="중도금",G396="잔금"),"A",IF(G396="자재","B",IF(G396="특허료","C",""))))</f>
+        <f t="shared" ref="D396:D408" si="21">IF(G396="","",IF(OR(G396="선급금",G396="중도금",G396="잔금"),"A",IF(G396="자재","B",IF(G396="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H396" s="4"/>
       <c r="I396" s="6" t="str">
-        <f t="shared" ref="I396:I406" ca="1" si="21">IF(C396="","",IF(L396="",TODAY()-C396,L396-C396))</f>
+        <f t="shared" ref="I396:I406" ca="1" si="22">IF(C396="","",IF(L396="",TODAY()-C396,L396-C396))</f>
         <v/>
       </c>
       <c r="J396" s="13"/>
@@ -14796,16 +15528,16 @@
       <c r="R396" s="11"/>
       <c r="S396" s="10"/>
     </row>
-    <row r="397" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="397" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B397" s="10"/>
       <c r="C397" s="11"/>
       <c r="D397" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H397" s="4"/>
       <c r="I397" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="J397" s="13"/>
@@ -14817,16 +15549,16 @@
       <c r="R397" s="11"/>
       <c r="S397" s="10"/>
     </row>
-    <row r="398" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="398" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B398" s="10"/>
       <c r="C398" s="11"/>
       <c r="D398" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H398" s="4"/>
       <c r="I398" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="J398" s="13"/>
@@ -14838,16 +15570,16 @@
       <c r="R398" s="11"/>
       <c r="S398" s="10"/>
     </row>
-    <row r="399" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="399" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B399" s="10"/>
       <c r="C399" s="11"/>
       <c r="D399" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H399" s="4"/>
       <c r="I399" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="J399" s="13"/>
@@ -14859,16 +15591,16 @@
       <c r="R399" s="11"/>
       <c r="S399" s="10"/>
     </row>
-    <row r="400" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="400" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B400" s="10"/>
       <c r="C400" s="11"/>
       <c r="D400" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H400" s="4"/>
       <c r="I400" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="J400" s="13"/>
@@ -14880,16 +15612,16 @@
       <c r="R400" s="11"/>
       <c r="S400" s="10"/>
     </row>
-    <row r="401" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="401" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B401" s="10"/>
       <c r="C401" s="11"/>
       <c r="D401" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H401" s="4"/>
       <c r="I401" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="J401" s="13"/>
@@ -14901,16 +15633,16 @@
       <c r="R401" s="11"/>
       <c r="S401" s="10"/>
     </row>
-    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
       <c r="D402" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H402" s="4"/>
       <c r="I402" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="J402" s="13"/>
@@ -14922,15 +15654,15 @@
       <c r="R402" s="11"/>
       <c r="S402" s="10"/>
     </row>
-    <row r="403" spans="2:19">
+    <row r="403" spans="2:19" hidden="1">
       <c r="B403" s="10"/>
       <c r="C403" s="11"/>
       <c r="D403" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I403" s="1" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="K403" s="11"/>
@@ -14938,15 +15670,15 @@
       <c r="Q403" s="11"/>
       <c r="R403" s="11"/>
     </row>
-    <row r="404" spans="2:19">
+    <row r="404" spans="2:19" hidden="1">
       <c r="B404" s="10"/>
       <c r="C404" s="11"/>
       <c r="D404" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I404" s="1" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="K404" s="11"/>
@@ -14954,49 +15686,49 @@
       <c r="Q404" s="11"/>
       <c r="R404" s="11"/>
     </row>
-    <row r="405" spans="2:19">
+    <row r="405" spans="2:19" hidden="1">
       <c r="B405" s="10"/>
       <c r="C405" s="11"/>
       <c r="D405" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I405" s="1" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="Q405" s="11"/>
       <c r="R405" s="11"/>
     </row>
-    <row r="406" spans="2:19">
+    <row r="406" spans="2:19" hidden="1">
       <c r="B406" s="10"/>
       <c r="C406" s="11"/>
       <c r="D406" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I406" s="1" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="Q406" s="11"/>
       <c r="R406" s="11"/>
     </row>
-    <row r="407" spans="2:19">
+    <row r="407" spans="2:19" hidden="1">
       <c r="B407" s="10"/>
       <c r="C407" s="11"/>
       <c r="D407" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q407" s="11"/>
       <c r="R407" s="11"/>
     </row>
-    <row r="408" spans="2:19">
+    <row r="408" spans="2:19" hidden="1">
       <c r="B408" s="10"/>
       <c r="C408" s="11"/>
       <c r="D408" s="1" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q408" s="11"/>
@@ -15007,178 +15739,224 @@
       <c r="F409" s="62"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S408"/>
+  <autoFilter ref="A1:S408">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="(주)다수건설"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="32" priority="48">
+    <cfRule type="expression" dxfId="43" priority="56">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="31" priority="47">
+    <cfRule type="expression" dxfId="42" priority="55">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="30" priority="46">
+    <cfRule type="expression" dxfId="41" priority="54">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="29" priority="45">
+    <cfRule type="expression" dxfId="40" priority="53">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="28" priority="40">
+    <cfRule type="expression" dxfId="39" priority="48">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="27" priority="30">
+    <cfRule type="expression" dxfId="38" priority="38">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="26" priority="29">
+    <cfRule type="expression" dxfId="37" priority="37">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="25" priority="27">
+    <cfRule type="expression" dxfId="36" priority="35">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="24" priority="26">
+    <cfRule type="expression" dxfId="35" priority="34">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="23" priority="25">
+    <cfRule type="expression" dxfId="34" priority="33">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="22" priority="24">
+    <cfRule type="expression" dxfId="33" priority="32">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="21" priority="23">
+    <cfRule type="expression" dxfId="32" priority="31">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="20" priority="22">
+    <cfRule type="expression" dxfId="31" priority="30">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="30" priority="29">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="18" priority="20">
+    <cfRule type="expression" dxfId="29" priority="28">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="28" priority="27">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="16" priority="18">
+    <cfRule type="expression" dxfId="27" priority="26">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="15" priority="17">
+    <cfRule type="expression" dxfId="26" priority="25">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="25" priority="24">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="24" priority="23">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="12" priority="14">
+    <cfRule type="expression" dxfId="23" priority="22">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="11" priority="13">
+    <cfRule type="expression" dxfId="22" priority="21">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="19" priority="17">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="18" priority="16">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="17" priority="15">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="16" priority="14">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="14" priority="12">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C159:C162">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="C159:C165">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
+    <cfRule type="expression" dxfId="11" priority="9">
+      <formula>$J159="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F166:F178">
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>$J166="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F179:F185">
+    <cfRule type="expression" dxfId="9" priority="7">
+      <formula>$J179="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E166:E178">
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>$J166="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E179:E185">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>$J179="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C166:C178">
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>$J166="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C179:C185">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>$J179="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H166:H178">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J166="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H179:H185">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J159="잔금"</formula>
+      <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N162">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N185">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D408">

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="321">
   <si>
     <t>순번</t>
   </si>
@@ -1105,6 +1105,45 @@
   </si>
   <si>
     <t>(주)청람건설</t>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>주택</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>문촌마을10단지동부</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>은하마을주공1단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>중산11단지현대</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>광양금광1차</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁전빌라파트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼익세라믹1,2차</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>철산두산위브</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>자재</t>
@@ -1565,7 +1604,37 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2524,7 +2593,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S409"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
@@ -2609,7 +2677,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="2" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B2" s="10">
         <v>1</v>
       </c>
@@ -2634,7 +2702,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2672,7 +2740,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="3" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B3" s="10">
         <f>IF(C3="","",COUNTA($C$2:C3))</f>
         <v>2</v>
@@ -2733,7 +2801,7 @@
       </c>
       <c r="S3" s="10"/>
     </row>
-    <row r="4" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="4" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B4" s="10">
         <f>IF(C4="","",COUNTA($C$2:C4))</f>
         <v>3</v>
@@ -2759,7 +2827,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2785,7 +2853,7 @@
       </c>
       <c r="S4" s="10"/>
     </row>
-    <row r="5" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B5" s="10">
         <f>IF(C5="","",COUNTA($C$2:C5))</f>
         <v>4</v>
@@ -2831,7 +2899,7 @@
       <c r="R5" s="14"/>
       <c r="S5" s="10"/>
     </row>
-    <row r="6" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="6" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B6" s="10">
         <f>IF(C6="","",COUNTA($C$2:C6))</f>
         <v>5</v>
@@ -2857,7 +2925,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2887,7 +2955,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="7" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B7" s="10">
         <f>IF(C7="","",COUNTA($C$2:C7))</f>
         <v>6</v>
@@ -2913,7 +2981,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2936,7 +3004,7 @@
       </c>
       <c r="S7" s="10"/>
     </row>
-    <row r="8" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="8" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B8" s="10">
         <f>IF(C8="","",COUNTA($C$2:C8))</f>
         <v>7</v>
@@ -2962,7 +3030,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2987,7 +3055,7 @@
       </c>
       <c r="S8" s="10"/>
     </row>
-    <row r="9" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="9" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B9" s="10">
         <f>IF(C9="","",COUNTA($C$2:C9))</f>
         <v>8</v>
@@ -3013,7 +3081,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3039,7 +3107,7 @@
       </c>
       <c r="S9" s="10"/>
     </row>
-    <row r="10" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B10" s="10">
         <f>IF(C10="","",COUNTA($C$2:C10))</f>
         <v>9</v>
@@ -3065,7 +3133,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3083,7 +3151,7 @@
       <c r="R10" s="14"/>
       <c r="S10" s="10"/>
     </row>
-    <row r="11" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="11" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B11" s="10">
         <f>IF(C11="","",COUNTA($C$2:C11))</f>
         <v>10</v>
@@ -3132,7 +3200,7 @@
       <c r="R11" s="14"/>
       <c r="S11" s="10"/>
     </row>
-    <row r="12" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="12" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B12" s="10">
         <f>IF(C12="","",COUNTA($C$2:C12))</f>
         <v>11</v>
@@ -3178,7 +3246,7 @@
       <c r="R12" s="14"/>
       <c r="S12" s="10"/>
     </row>
-    <row r="13" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="13" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B13" s="10">
         <f>IF(C13="","",COUNTA($C$2:C13))</f>
         <v>12</v>
@@ -3204,7 +3272,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3234,7 +3302,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B14" s="10">
         <f>IF(C14="","",COUNTA($C$2:C14))</f>
         <v>13</v>
@@ -3260,7 +3328,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3283,7 +3351,7 @@
       </c>
       <c r="S14" s="10"/>
     </row>
-    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B15" s="10">
         <f>IF(C15="","",COUNTA($C$2:C15))</f>
         <v>14</v>
@@ -3309,7 +3377,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3332,7 +3400,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B16" s="10">
         <f>IF(C16="","",COUNTA($C$2:C16))</f>
         <v>15</v>
@@ -3358,7 +3426,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3379,7 +3447,7 @@
       <c r="R16" s="14"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B17" s="10">
         <f>IF(C17="","",COUNTA($C$2:C17))</f>
         <v>16</v>
@@ -3405,7 +3473,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3426,7 +3494,7 @@
       <c r="R17" s="14"/>
       <c r="S17" s="10"/>
     </row>
-    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B18" s="10">
         <f>IF(C18="","",COUNTA($C$2:C18))</f>
         <v>17</v>
@@ -3452,7 +3520,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3473,7 +3541,7 @@
       <c r="R18" s="14"/>
       <c r="S18" s="10"/>
     </row>
-    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B19" s="10">
         <f>IF(C19="","",COUNTA($C$2:C19))</f>
         <v>18</v>
@@ -3499,7 +3567,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3520,7 +3588,7 @@
       <c r="R19" s="14"/>
       <c r="S19" s="10"/>
     </row>
-    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B20" s="10">
         <f>IF(C20="","",COUNTA($C$2:C20))</f>
         <v>19</v>
@@ -3546,7 +3614,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3567,7 +3635,7 @@
       <c r="R20" s="14"/>
       <c r="S20" s="10"/>
     </row>
-    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B21" s="10">
         <f>IF(C21="","",COUNTA($C$2:C21))</f>
         <v>20</v>
@@ -3593,7 +3661,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3616,7 +3684,7 @@
       </c>
       <c r="S21" s="10"/>
     </row>
-    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B22" s="10">
         <f>IF(C22="","",COUNTA($C$2:C22))</f>
         <v>21</v>
@@ -3642,7 +3710,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3665,7 +3733,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B23" s="10">
         <f>IF(C23="","",COUNTA($C$2:C23))</f>
         <v>22</v>
@@ -3691,7 +3759,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3714,7 +3782,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B24" s="10">
         <f>IF(C24="","",COUNTA($C$2:C24))</f>
         <v>23</v>
@@ -3740,7 +3808,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3763,7 +3831,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B25" s="10">
         <f>IF(C25="","",COUNTA($C$2:C25))</f>
         <v>24</v>
@@ -3789,7 +3857,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3812,7 +3880,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B26" s="10">
         <f>IF(C26="","",COUNTA($C$2:C26))</f>
         <v>25</v>
@@ -3838,7 +3906,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3861,7 +3929,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B27" s="10">
         <f>IF(C27="","",COUNTA($C$2:C27))</f>
         <v>26</v>
@@ -3887,7 +3955,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3910,7 +3978,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B28" s="10">
         <f>IF(C28="","",COUNTA($C$2:C28))</f>
         <v>27</v>
@@ -3936,7 +4004,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3959,7 +4027,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B29" s="10">
         <f>IF(C29="","",COUNTA($C$2:C29))</f>
         <v>28</v>
@@ -3985,7 +4053,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4008,7 +4076,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B30" s="10">
         <f>IF(C30="","",COUNTA($C$2:C30))</f>
         <v>29</v>
@@ -4034,7 +4102,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4057,7 +4125,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B31" s="10">
         <f>IF(C31="","",COUNTA($C$2:C31))</f>
         <v>30</v>
@@ -4083,7 +4151,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4106,7 +4174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B32" s="10">
         <f>IF(C32="","",COUNTA($C$2:C32))</f>
         <v>31</v>
@@ -4132,7 +4200,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4155,7 +4223,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B33" s="10">
         <f>IF(C33="","",COUNTA($C$2:C33))</f>
         <v>32</v>
@@ -4181,7 +4249,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4204,7 +4272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B34" s="10">
         <f>IF(C34="","",COUNTA($C$2:C34))</f>
         <v>33</v>
@@ -4230,7 +4298,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4253,7 +4321,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B35" s="10">
         <f>IF(C35="","",COUNTA($C$2:C35))</f>
         <v>34</v>
@@ -4279,7 +4347,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4302,7 +4370,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B36" s="10">
         <f>IF(C36="","",COUNTA($C$2:C36))</f>
         <v>35</v>
@@ -4328,7 +4396,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4347,7 +4415,7 @@
       <c r="R36" s="14"/>
       <c r="S36" s="10"/>
     </row>
-    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B37" s="10">
         <f>IF(C37="","",COUNTA($C$2:C37))</f>
         <v>36</v>
@@ -4373,7 +4441,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4401,7 +4469,7 @@
       </c>
       <c r="S37" s="10"/>
     </row>
-    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B38" s="10">
         <f>IF(C38="","",COUNTA($C$2:C38))</f>
         <v>37</v>
@@ -4427,7 +4495,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4457,7 +4525,7 @@
       </c>
       <c r="S38" s="10"/>
     </row>
-    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B39" s="10">
         <f>IF(C39="","",COUNTA($C$2:C39))</f>
         <v>38</v>
@@ -4483,7 +4551,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4510,7 +4578,7 @@
       </c>
       <c r="S39" s="10"/>
     </row>
-    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B40" s="10">
         <f>IF(C40="","",COUNTA($C$2:C40))</f>
         <v>39</v>
@@ -4536,7 +4604,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4557,7 +4625,7 @@
       <c r="R40" s="11"/>
       <c r="S40" s="10"/>
     </row>
-    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B41" s="10">
         <f>IF(C41="","",COUNTA($C$2:C41))</f>
         <v>40</v>
@@ -4583,7 +4651,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4611,7 +4679,7 @@
       </c>
       <c r="S41" s="10"/>
     </row>
-    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B42" s="10">
         <f>IF(C42="","",COUNTA($C$2:C42))</f>
         <v>41</v>
@@ -4637,7 +4705,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4664,7 +4732,7 @@
       </c>
       <c r="S42" s="10"/>
     </row>
-    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B43" s="10">
         <f>IF(C43="","",COUNTA($C$2:C43))</f>
         <v>42</v>
@@ -4716,7 +4784,7 @@
       <c r="R43" s="11"/>
       <c r="S43" s="10"/>
     </row>
-    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B44" s="10">
         <f>IF(C44="","",COUNTA($C$2:C44))</f>
         <v>43</v>
@@ -4742,7 +4810,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4767,7 +4835,7 @@
       </c>
       <c r="S44" s="10"/>
     </row>
-    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B45" s="10">
         <f>IF(C45="","",COUNTA($C$2:C45))</f>
         <v>44</v>
@@ -4816,7 +4884,7 @@
       <c r="R45" s="11"/>
       <c r="S45" s="10"/>
     </row>
-    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B46" s="10">
         <f>IF(C46="","",COUNTA($C$2:C46))</f>
         <v>45</v>
@@ -4865,7 +4933,7 @@
       <c r="R46" s="11"/>
       <c r="S46" s="10"/>
     </row>
-    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B47" s="10">
         <f>IF(C47="","",COUNTA($C$2:C47))</f>
         <v>46</v>
@@ -4891,7 +4959,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4912,7 +4980,7 @@
       <c r="R47" s="11"/>
       <c r="S47" s="10"/>
     </row>
-    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B48" s="10">
         <f>IF(C48="","",COUNTA($C$2:C48))</f>
         <v>47</v>
@@ -4938,7 +5006,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4959,7 +5027,7 @@
       <c r="R48" s="11"/>
       <c r="S48" s="10"/>
     </row>
-    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B49" s="10">
         <f>IF(C49="","",COUNTA($C$2:C49))</f>
         <v>48</v>
@@ -5008,7 +5076,7 @@
       <c r="R49" s="11"/>
       <c r="S49" s="10"/>
     </row>
-    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B50" s="10">
         <f>IF(C50="","",COUNTA($C$2:C50))</f>
         <v>49</v>
@@ -5057,7 +5125,7 @@
       <c r="R50" s="11"/>
       <c r="S50" s="10"/>
     </row>
-    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B51" s="10">
         <f>IF(C51="","",COUNTA($C$2:C51))</f>
         <v>50</v>
@@ -5103,7 +5171,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="10"/>
     </row>
-    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B52" s="10">
         <f>IF(C52="","",COUNTA($C$2:C52))</f>
         <v>51</v>
@@ -5149,7 +5217,7 @@
       <c r="R52" s="11"/>
       <c r="S52" s="10"/>
     </row>
-    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B53" s="10">
         <f>IF(C53="","",COUNTA($C$2:C53))</f>
         <v>52</v>
@@ -5198,7 +5266,7 @@
       <c r="R53" s="11"/>
       <c r="S53" s="10"/>
     </row>
-    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B54" s="10">
         <f>IF(C54="","",COUNTA($C$2:C54))</f>
         <v>53</v>
@@ -5252,7 +5320,7 @@
       </c>
       <c r="S54" s="10"/>
     </row>
-    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B55" s="10">
         <f>IF(C55="","",COUNTA($C$2:C55))</f>
         <v>54</v>
@@ -5296,7 +5364,7 @@
       <c r="R55" s="11"/>
       <c r="S55" s="10"/>
     </row>
-    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B56" s="10">
         <f>IF(C56="","",COUNTA($C$2:C56))</f>
         <v>55</v>
@@ -5345,7 +5413,7 @@
       <c r="R56" s="11"/>
       <c r="S56" s="10"/>
     </row>
-    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B57" s="10">
         <f>IF(C57="","",COUNTA($C$2:C57))</f>
         <v>56</v>
@@ -5371,7 +5439,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5392,7 +5460,7 @@
       <c r="R57" s="14"/>
       <c r="S57" s="10"/>
     </row>
-    <row r="58" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="58" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B58" s="10">
         <f>IF(C58="","",COUNTA($C$2:C58))</f>
         <v>57</v>
@@ -5418,7 +5486,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5439,7 +5507,7 @@
       <c r="R58" s="14"/>
       <c r="S58" s="10"/>
     </row>
-    <row r="59" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="59" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B59" s="10">
         <f>IF(C59="","",COUNTA($C$2:C59))</f>
         <v>58</v>
@@ -5465,7 +5533,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5486,7 +5554,7 @@
       <c r="R59" s="14"/>
       <c r="S59" s="10"/>
     </row>
-    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B60" s="10">
         <f>IF(C60="","",COUNTA($C$2:C60))</f>
         <v>59</v>
@@ -5512,7 +5580,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -5541,7 +5609,7 @@
       <c r="R60" s="14"/>
       <c r="S60" s="10"/>
     </row>
-    <row r="61" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="61" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B61" s="10">
         <f>IF(C61="","",COUNTA($C$2:C61))</f>
         <v>60</v>
@@ -5587,7 +5655,7 @@
       <c r="R61" s="14"/>
       <c r="S61" s="10"/>
     </row>
-    <row r="62" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="62" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B62" s="10">
         <f>IF(C62="","",COUNTA($C$2:C62))</f>
         <v>61</v>
@@ -5633,7 +5701,7 @@
       <c r="R62" s="14"/>
       <c r="S62" s="10"/>
     </row>
-    <row r="63" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="63" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B63" s="10">
         <f>IF(C63="","",COUNTA($C$2:C63))</f>
         <v>62</v>
@@ -5682,7 +5750,7 @@
       <c r="R63" s="14"/>
       <c r="S63" s="10"/>
     </row>
-    <row r="64" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="64" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B64" s="10">
         <f>IF(C64="","",COUNTA($C$2:C64))</f>
         <v>63</v>
@@ -5731,7 +5799,7 @@
       <c r="R64" s="14"/>
       <c r="S64" s="10"/>
     </row>
-    <row r="65" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="65" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B65" s="10">
         <f>IF(C65="","",COUNTA($C$2:C65))</f>
         <v>64</v>
@@ -5777,7 +5845,7 @@
       <c r="R65" s="14"/>
       <c r="S65" s="10"/>
     </row>
-    <row r="66" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="66" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B66" s="10">
         <f>IF(C66="","",COUNTA($C$2:C66))</f>
         <v>65</v>
@@ -5803,7 +5871,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5821,7 +5889,7 @@
       <c r="R66" s="14"/>
       <c r="S66" s="10"/>
     </row>
-    <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B67" s="10">
         <f>IF(C67="","",COUNTA($C$2:C67))</f>
         <v>66</v>
@@ -5847,13 +5915,15 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>관리</v>
       </c>
-      <c r="K67" s="11"/>
+      <c r="K67" s="11">
+        <v>46112</v>
+      </c>
       <c r="L67" s="11"/>
       <c r="M67" s="10"/>
       <c r="N67" s="10" t="s">
@@ -5863,7 +5933,7 @@
       <c r="R67" s="11"/>
       <c r="S67" s="10"/>
     </row>
-    <row r="68" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="68" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B68" s="10">
         <f>IF(C68="","",COUNTA($C$2:C68))</f>
         <v>67</v>
@@ -5907,7 +5977,7 @@
       <c r="R68" s="11"/>
       <c r="S68" s="10"/>
     </row>
-    <row r="69" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="69" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B69" s="10">
         <f>IF(C69="","",COUNTA($C$2:C69))</f>
         <v>68</v>
@@ -5951,7 +6021,7 @@
       <c r="R69" s="11"/>
       <c r="S69" s="10"/>
     </row>
-    <row r="70" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="70" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B70" s="10">
         <f>IF(C70="","",COUNTA($C$2:C70))</f>
         <v>69</v>
@@ -5998,7 +6068,7 @@
       <c r="R70" s="11"/>
       <c r="S70" s="10"/>
     </row>
-    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B71" s="10">
         <f>IF(C71="","",COUNTA($C$2:C71))</f>
         <v>70</v>
@@ -6050,7 +6120,7 @@
       <c r="R71" s="11"/>
       <c r="S71" s="10"/>
     </row>
-    <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B72" s="10">
         <f>IF(C72="","",COUNTA($C$2:C72))</f>
         <v>71</v>
@@ -6104,7 +6174,7 @@
       </c>
       <c r="S72" s="10"/>
     </row>
-    <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B73" s="10">
         <f>IF(C73="","",COUNTA($C$2:C73))</f>
         <v>72</v>
@@ -6130,7 +6200,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6151,7 +6221,7 @@
       <c r="R73" s="11"/>
       <c r="S73" s="10"/>
     </row>
-    <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B74" s="10">
         <f>IF(C74="","",COUNTA($C$2:C74))</f>
         <v>73</v>
@@ -6205,7 +6275,7 @@
       </c>
       <c r="S74" s="10"/>
     </row>
-    <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B75" s="10">
         <f>IF(C75="","",COUNTA($C$2:C75))</f>
         <v>74</v>
@@ -6249,7 +6319,7 @@
       <c r="R75" s="11"/>
       <c r="S75" s="10"/>
     </row>
-    <row r="76" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="76" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B76" s="10">
         <f>IF(C76="","",COUNTA($C$2:C76))</f>
         <v>75</v>
@@ -6275,7 +6345,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6291,7 +6361,7 @@
       <c r="R76" s="11"/>
       <c r="S76" s="10"/>
     </row>
-    <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B77" s="10">
         <f>IF(C77="","",COUNTA($C$2:C77))</f>
         <v>76</v>
@@ -6345,7 +6415,7 @@
       </c>
       <c r="S77" s="10"/>
     </row>
-    <row r="78" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="78" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B78" s="10">
         <f>IF(C78="","",COUNTA($C$2:C78))</f>
         <v>77</v>
@@ -6399,7 +6469,7 @@
       </c>
       <c r="S78" s="10"/>
     </row>
-    <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B79" s="10">
         <f>IF(C79="","",COUNTA($C$2:C79))</f>
         <v>78</v>
@@ -6443,7 +6513,7 @@
       <c r="R79" s="11"/>
       <c r="S79" s="10"/>
     </row>
-    <row r="80" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="80" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B80" s="10">
         <f>IF(C80="","",COUNTA($C$2:C80))</f>
         <v>79</v>
@@ -6487,7 +6557,7 @@
       <c r="R80" s="11"/>
       <c r="S80" s="10"/>
     </row>
-    <row r="81" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="81" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B81" s="10">
         <f>IF(C81="","",COUNTA($C$2:C81))</f>
         <v>80</v>
@@ -6513,7 +6583,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6529,7 +6599,7 @@
       <c r="R81" s="11"/>
       <c r="S81" s="10"/>
     </row>
-    <row r="82" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="82" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B82" s="10">
         <f>IF(C82="","",COUNTA($C$2:C82))</f>
         <v>81</v>
@@ -6573,7 +6643,7 @@
       <c r="R82" s="11"/>
       <c r="S82" s="10"/>
     </row>
-    <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B83" s="10">
         <f>IF(C83="","",COUNTA($C$2:C83))</f>
         <v>82</v>
@@ -6599,7 +6669,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6625,7 +6695,7 @@
       </c>
       <c r="S83" s="10"/>
     </row>
-    <row r="84" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="84" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B84" s="10">
         <f>IF(C84="","",COUNTA($C$2:C84))</f>
         <v>83</v>
@@ -6679,7 +6749,7 @@
       </c>
       <c r="S84" s="10"/>
     </row>
-    <row r="85" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="85" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B85" s="10">
         <f>IF(C85="","",COUNTA($C$2:C85))</f>
         <v>84</v>
@@ -6705,7 +6775,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6731,7 +6801,7 @@
       </c>
       <c r="S85" s="10"/>
     </row>
-    <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B86" s="10">
         <f>IF(C86="","",COUNTA($C$2:C86))</f>
         <v>85</v>
@@ -6757,7 +6827,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6773,7 +6843,7 @@
       <c r="R86" s="11"/>
       <c r="S86" s="10"/>
     </row>
-    <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B87" s="10">
         <f>IF(C87="","",COUNTA($C$2:C87))</f>
         <v>86</v>
@@ -6799,7 +6869,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6825,7 +6895,7 @@
       </c>
       <c r="S87" s="10"/>
     </row>
-    <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B88" s="10">
         <f>IF(C88="","",COUNTA($C$2:C88))</f>
         <v>87</v>
@@ -6869,7 +6939,7 @@
       <c r="R88" s="11"/>
       <c r="S88" s="10"/>
     </row>
-    <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B89" s="10">
         <f>IF(C89="","",COUNTA($C$2:C89))</f>
         <v>88</v>
@@ -6895,7 +6965,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6921,7 +6991,7 @@
       </c>
       <c r="S89" s="10"/>
     </row>
-    <row r="90" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="90" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B90" s="10">
         <f>IF(C90="","",COUNTA($C$2:C90))</f>
         <v>89</v>
@@ -6947,7 +7017,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6973,7 +7043,7 @@
       </c>
       <c r="S90" s="10"/>
     </row>
-    <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B91" s="10">
         <f>IF(C91="","",COUNTA($C$2:C91))</f>
         <v>90</v>
@@ -7017,7 +7087,7 @@
       <c r="R91" s="11"/>
       <c r="S91" s="10"/>
     </row>
-    <row r="92" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="92" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B92" s="10">
         <f>IF(C92="","",COUNTA($C$2:C92))</f>
         <v>91</v>
@@ -7043,7 +7113,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7059,7 +7129,7 @@
       <c r="R92" s="11"/>
       <c r="S92" s="10"/>
     </row>
-    <row r="93" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="93" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B93" s="10">
         <f>IF(C93="","",COUNTA($C$2:C93))</f>
         <v>92</v>
@@ -7103,7 +7173,7 @@
       <c r="R93" s="11"/>
       <c r="S93" s="10"/>
     </row>
-    <row r="94" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="94" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B94" s="10">
         <f>IF(C94="","",COUNTA($C$2:C94))</f>
         <v>93</v>
@@ -7147,7 +7217,7 @@
       <c r="R94" s="11"/>
       <c r="S94" s="10"/>
     </row>
-    <row r="95" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="95" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B95" s="10">
         <f>IF(C95="","",COUNTA($C$2:C95))</f>
         <v>94</v>
@@ -7191,7 +7261,7 @@
       <c r="R95" s="11"/>
       <c r="S95" s="10"/>
     </row>
-    <row r="96" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="96" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B96" s="10">
         <f>IF(C96="","",COUNTA($C$2:C96))</f>
         <v>95</v>
@@ -7217,7 +7287,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7233,7 +7303,7 @@
       <c r="R96" s="11"/>
       <c r="S96" s="10"/>
     </row>
-    <row r="97" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="97" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B97" s="10">
         <f>IF(C97="","",COUNTA($C$2:C97))</f>
         <v>96</v>
@@ -7277,7 +7347,7 @@
       <c r="R97" s="11"/>
       <c r="S97" s="10"/>
     </row>
-    <row r="98" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="98" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B98" s="10">
         <f>IF(C98="","",COUNTA($C$2:C98))</f>
         <v>97</v>
@@ -7303,7 +7373,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7319,7 +7389,7 @@
       <c r="R98" s="11"/>
       <c r="S98" s="10"/>
     </row>
-    <row r="99" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="99" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B99" s="10">
         <f>IF(C99="","",COUNTA($C$2:C99))</f>
         <v>98</v>
@@ -7345,7 +7415,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7361,7 +7431,7 @@
       <c r="R99" s="11"/>
       <c r="S99" s="10"/>
     </row>
-    <row r="100" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="100" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B100" s="10">
         <f>IF(C100="","",COUNTA($C$2:C100))</f>
         <v>99</v>
@@ -7386,7 +7456,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7402,7 +7472,7 @@
       <c r="R100" s="11"/>
       <c r="S100" s="10"/>
     </row>
-    <row r="101" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="101" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B101" s="10">
         <f>IF(C101="","",COUNTA($C$2:C101))</f>
         <v>100</v>
@@ -7445,7 +7515,7 @@
       <c r="R101" s="11"/>
       <c r="S101" s="10"/>
     </row>
-    <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B102" s="10">
         <f>IF(C102="","",COUNTA($C$2:C102))</f>
         <v>101</v>
@@ -7489,7 +7559,7 @@
       <c r="R102" s="11"/>
       <c r="S102" s="10"/>
     </row>
-    <row r="103" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="103" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B103" s="26">
         <f>IF(C103="","",COUNTA($C$2:C103))</f>
         <v>102</v>
@@ -7533,7 +7603,7 @@
       <c r="R103" s="11"/>
       <c r="S103" s="10"/>
     </row>
-    <row r="104" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="104" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B104" s="10">
         <f>IF(C104="","",COUNTA($C$2:C104))</f>
         <v>103</v>
@@ -7559,7 +7629,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7575,7 +7645,7 @@
       <c r="R104" s="11"/>
       <c r="S104" s="10"/>
     </row>
-    <row r="105" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="105" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B105" s="10">
         <f>IF(C105="","",COUNTA($C$2:C105))</f>
         <v>104</v>
@@ -7601,7 +7671,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7617,7 +7687,7 @@
       <c r="R105" s="11"/>
       <c r="S105" s="10"/>
     </row>
-    <row r="106" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="106" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B106" s="10">
         <f>IF(C106="","",COUNTA($C$2:C106))</f>
         <v>105</v>
@@ -7642,7 +7712,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7704,7 +7774,7 @@
       <c r="R107" s="11"/>
       <c r="S107" s="10"/>
     </row>
-    <row r="108" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="108" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B108" s="10">
         <f>IF(C108="","",COUNTA($C$2:C108))</f>
         <v>107</v>
@@ -7729,7 +7799,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7745,7 +7815,7 @@
       <c r="R108" s="11"/>
       <c r="S108" s="10"/>
     </row>
-    <row r="109" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="109" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B109" s="10">
         <f>IF(C109="","",COUNTA($C$2:C109))</f>
         <v>108</v>
@@ -7770,7 +7840,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7786,7 +7856,7 @@
       <c r="R109" s="11"/>
       <c r="S109" s="10"/>
     </row>
-    <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B110" s="10">
         <f>IF(C110="","",COUNTA($C$2:C110))</f>
         <v>109</v>
@@ -7811,7 +7881,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7830,7 +7900,7 @@
       <c r="R110" s="11"/>
       <c r="S110" s="10"/>
     </row>
-    <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B111" s="10">
         <f>IF(C111="","",COUNTA($C$2:C111))</f>
         <v>110</v>
@@ -7874,7 +7944,7 @@
       <c r="R111" s="11"/>
       <c r="S111" s="10"/>
     </row>
-    <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B112" s="10">
         <f>IF(C112="","",COUNTA($C$2:C112))</f>
         <v>111</v>
@@ -7900,7 +7970,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7919,7 +7989,7 @@
       <c r="R112" s="11"/>
       <c r="S112" s="10"/>
     </row>
-    <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B113" s="10">
         <f>IF(C113="","",COUNTA($C$2:C113))</f>
         <v>112</v>
@@ -7963,7 +8033,7 @@
       <c r="R113" s="11"/>
       <c r="S113" s="10"/>
     </row>
-    <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B114" s="10">
         <f>IF(C114="","",COUNTA($C$2:C114))</f>
         <v>113</v>
@@ -7989,7 +8059,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8008,7 +8078,7 @@
       <c r="R114" s="11"/>
       <c r="S114" s="10"/>
     </row>
-    <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B115" s="10">
         <f>IF(C115="","",COUNTA($C$2:C115))</f>
         <v>114</v>
@@ -8034,7 +8104,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
@@ -8061,7 +8131,7 @@
       <c r="R115" s="11"/>
       <c r="S115" s="10"/>
     </row>
-    <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B116" s="10">
         <f>IF(C116="","",COUNTA($C$2:C116))</f>
         <v>115</v>
@@ -8105,7 +8175,7 @@
       <c r="R116" s="11"/>
       <c r="S116" s="10"/>
     </row>
-    <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B117" s="10">
         <f>IF(C117="","",COUNTA($C$2:C117))</f>
         <v>116</v>
@@ -8131,7 +8201,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8147,7 +8217,7 @@
       <c r="R117" s="11"/>
       <c r="S117" s="10"/>
     </row>
-    <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B118" s="10">
         <f>IF(C118="","",COUNTA($C$2:C118))</f>
         <v>117</v>
@@ -8191,7 +8261,7 @@
       <c r="R118" s="11"/>
       <c r="S118" s="10"/>
     </row>
-    <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B119" s="10">
         <f>IF(C119="","",COUNTA($C$2:C119))</f>
         <v>118</v>
@@ -8217,7 +8287,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8236,7 +8306,7 @@
       <c r="R119" s="11"/>
       <c r="S119" s="10"/>
     </row>
-    <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B120" s="10">
         <f>IF(C120="","",COUNTA($C$2:C120))</f>
         <v>119</v>
@@ -8280,7 +8350,7 @@
       <c r="R120" s="11"/>
       <c r="S120" s="10"/>
     </row>
-    <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B121" s="10">
         <f>IF(C121="","",COUNTA($C$2:C121))</f>
         <v>120</v>
@@ -8324,7 +8394,7 @@
       <c r="R121" s="11"/>
       <c r="S121" s="10"/>
     </row>
-    <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B122" s="10">
         <f>IF(C122="","",COUNTA($C$2:C122))</f>
         <v>121</v>
@@ -8350,7 +8420,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8366,7 +8436,7 @@
       <c r="R122" s="11"/>
       <c r="S122" s="10"/>
     </row>
-    <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B123" s="10">
         <f>IF(C123="","",COUNTA($C$2:C123))</f>
         <v>122</v>
@@ -8392,7 +8462,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8408,7 +8478,7 @@
       <c r="R123" s="11"/>
       <c r="S123" s="10"/>
     </row>
-    <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B124" s="10">
         <f>IF(C124="","",COUNTA($C$2:C124))</f>
         <v>123</v>
@@ -8434,7 +8504,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8450,7 +8520,7 @@
       <c r="R124" s="11"/>
       <c r="S124" s="10"/>
     </row>
-    <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B125" s="10">
         <f>IF(C125="","",COUNTA($C$2:C125))</f>
         <v>124</v>
@@ -8476,7 +8546,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8492,7 +8562,7 @@
       <c r="R125" s="11"/>
       <c r="S125" s="10"/>
     </row>
-    <row r="126" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="126" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B126" s="10">
         <v>125</v>
       </c>
@@ -8527,7 +8597,7 @@
       <c r="R126" s="11"/>
       <c r="S126" s="10"/>
     </row>
-    <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B127" s="10">
         <f>IF(C127="","",COUNTA($C$2:C127))</f>
         <v>126</v>
@@ -8553,7 +8623,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8569,7 +8639,7 @@
       <c r="R127" s="11"/>
       <c r="S127" s="10"/>
     </row>
-    <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B128" s="10">
         <f>IF(C128="","",COUNTA($C$2:C128))</f>
         <v>127</v>
@@ -8595,7 +8665,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8637,7 +8707,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8653,7 +8723,7 @@
       <c r="R129" s="11"/>
       <c r="S129" s="10"/>
     </row>
-    <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B130" s="10">
         <f>IF(C130="","",COUNTA($C$2:C130))</f>
         <v>129</v>
@@ -8679,7 +8749,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8695,7 +8765,7 @@
       <c r="R130" s="11"/>
       <c r="S130" s="10"/>
     </row>
-    <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B131" s="10">
         <f>IF(C131="","",COUNTA($C$2:C131))</f>
         <v>130</v>
@@ -8739,7 +8809,7 @@
       <c r="R131" s="11"/>
       <c r="S131" s="10"/>
     </row>
-    <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B132" s="10">
         <f>IF(C132="","",COUNTA($C$2:C132))</f>
         <v>131</v>
@@ -8783,7 +8853,7 @@
       <c r="R132" s="11"/>
       <c r="S132" s="10"/>
     </row>
-    <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B133" s="10">
         <f>IF(C133="","",COUNTA($C$2:C133))</f>
         <v>132</v>
@@ -8827,7 +8897,7 @@
       <c r="R133" s="11"/>
       <c r="S133" s="10"/>
     </row>
-    <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B134" s="10">
         <f>IF(C134="","",COUNTA($C$2:C134))</f>
         <v>133</v>
@@ -8853,7 +8923,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8869,7 +8939,7 @@
       <c r="R134" s="11"/>
       <c r="S134" s="10"/>
     </row>
-    <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B135" s="10">
         <f>IF(C135="","",COUNTA($C$2:C135))</f>
         <v>134</v>
@@ -8895,7 +8965,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8911,7 +8981,7 @@
       <c r="R135" s="11"/>
       <c r="S135" s="10"/>
     </row>
-    <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B136" s="10">
         <f>IF(C136="","",COUNTA($C$2:C136))</f>
         <v>135</v>
@@ -8937,7 +9007,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8953,7 +9023,7 @@
       <c r="R136" s="11"/>
       <c r="S136" s="10"/>
     </row>
-    <row r="137" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="137" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B137" s="10">
         <f>IF(C137="","",COUNTA($C$2:C137))</f>
         <v>136</v>
@@ -8997,7 +9067,7 @@
       <c r="R137" s="11"/>
       <c r="S137" s="10"/>
     </row>
-    <row r="138" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="138" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B138" s="10">
         <f>IF(C138="","",COUNTA($C$2:C138))</f>
         <v>137</v>
@@ -9023,7 +9093,7 @@
       </c>
       <c r="I138" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J138" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9039,7 +9109,7 @@
       <c r="R138" s="11"/>
       <c r="S138" s="10"/>
     </row>
-    <row r="139" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="139" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B139" s="10">
         <f>IF(C139="","",COUNTA($C$2:C139))</f>
         <v>138</v>
@@ -9083,7 +9153,7 @@
       <c r="R139" s="11"/>
       <c r="S139" s="10"/>
     </row>
-    <row r="140" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="140" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B140" s="10">
         <f>IF(C140="","",COUNTA($C$2:C140))</f>
         <v>139</v>
@@ -9127,7 +9197,7 @@
       <c r="R140" s="11"/>
       <c r="S140" s="10"/>
     </row>
-    <row r="141" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="141" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B141" s="10">
         <f>IF(C141="","",COUNTA($C$2:C141))</f>
         <v>140</v>
@@ -9153,7 +9223,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9169,7 +9239,7 @@
       <c r="R141" s="11"/>
       <c r="S141" s="10"/>
     </row>
-    <row r="142" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="142" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B142" s="10">
         <f>IF(C142="","",COUNTA($C$2:C142))</f>
         <v>141</v>
@@ -9194,7 +9264,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9210,7 +9280,7 @@
       <c r="R142" s="11"/>
       <c r="S142" s="10"/>
     </row>
-    <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B143" s="10">
         <f>IF(C143="","",COUNTA($C$2:C143))</f>
         <v>142</v>
@@ -9235,7 +9305,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9251,7 +9321,7 @@
       <c r="R143" s="11"/>
       <c r="S143" s="10"/>
     </row>
-    <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B144" s="10">
         <f>IF(C144="","",COUNTA($C$2:C144))</f>
         <v>143</v>
@@ -9276,7 +9346,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9292,7 +9362,7 @@
       <c r="R144" s="11"/>
       <c r="S144" s="10"/>
     </row>
-    <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B145" s="10">
         <f>IF(C145="","",COUNTA($C$2:C145))</f>
         <v>144</v>
@@ -9317,7 +9387,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9333,7 +9403,7 @@
       <c r="R145" s="11"/>
       <c r="S145" s="10"/>
     </row>
-    <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B146" s="10">
         <f>IF(C146="","",COUNTA($C$2:C146))</f>
         <v>145</v>
@@ -9358,7 +9428,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9374,7 +9444,7 @@
       <c r="R146" s="11"/>
       <c r="S146" s="10"/>
     </row>
-    <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B147" s="10">
         <f>IF(C147="","",COUNTA($C$2:C147))</f>
         <v>146</v>
@@ -9399,7 +9469,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9415,7 +9485,7 @@
       <c r="R147" s="11"/>
       <c r="S147" s="10"/>
     </row>
-    <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B148" s="10">
         <f>IF(C148="","",COUNTA($C$2:C148))</f>
         <v>147</v>
@@ -9440,7 +9510,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9456,7 +9526,7 @@
       <c r="R148" s="11"/>
       <c r="S148" s="10"/>
     </row>
-    <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B149" s="10">
         <f>IF(C149="","",COUNTA($C$2:C149))</f>
         <v>148</v>
@@ -9481,7 +9551,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9497,7 +9567,7 @@
       <c r="R149" s="11"/>
       <c r="S149" s="10"/>
     </row>
-    <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B150" s="10">
         <f>IF(C150="","",COUNTA($C$2:C150))</f>
         <v>149</v>
@@ -9522,7 +9592,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9538,7 +9608,7 @@
       <c r="R150" s="11"/>
       <c r="S150" s="10"/>
     </row>
-    <row r="151" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="151" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B151" s="10">
         <f>IF(C151="","",COUNTA($C$2:C151))</f>
         <v>150</v>
@@ -9581,7 +9651,7 @@
       <c r="R151" s="11"/>
       <c r="S151" s="10"/>
     </row>
-    <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B152" s="10">
         <f>IF(C152="","",COUNTA($C$2:C152))</f>
         <v>151</v>
@@ -9606,7 +9676,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9622,7 +9692,7 @@
       <c r="R152" s="11"/>
       <c r="S152" s="10"/>
     </row>
-    <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B153" s="10">
         <f>IF(C153="","",COUNTA($C$2:C153))</f>
         <v>152</v>
@@ -9665,7 +9735,7 @@
       <c r="R153" s="11"/>
       <c r="S153" s="10"/>
     </row>
-    <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B154" s="10">
         <f>IF(C154="","",COUNTA($C$2:C154))</f>
         <v>153</v>
@@ -9690,7 +9760,7 @@
       </c>
       <c r="I154" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J154" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9706,7 +9776,7 @@
       <c r="R154" s="11"/>
       <c r="S154" s="10"/>
     </row>
-    <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B155" s="10">
         <f>IF(C155="","",COUNTA($C$2:C155))</f>
         <v>154</v>
@@ -9731,7 +9801,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9747,7 +9817,7 @@
       <c r="R155" s="11"/>
       <c r="S155" s="10"/>
     </row>
-    <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B156" s="10">
         <f>IF(C156="","",COUNTA($C$2:C156))</f>
         <v>155</v>
@@ -9772,7 +9842,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9788,7 +9858,7 @@
       <c r="R156" s="11"/>
       <c r="S156" s="10"/>
     </row>
-    <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B157" s="10">
         <f>IF(C157="","",COUNTA($C$2:C157))</f>
         <v>156</v>
@@ -9813,7 +9883,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9829,7 +9899,7 @@
       <c r="R157" s="11"/>
       <c r="S157" s="10"/>
     </row>
-    <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B158" s="10">
         <f>IF(C158="","",COUNTA($C$2:C158))</f>
         <v>157</v>
@@ -9855,7 +9925,7 @@
       </c>
       <c r="I158" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J158" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9871,7 +9941,7 @@
       <c r="R158" s="11"/>
       <c r="S158" s="10"/>
     </row>
-    <row r="159" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="159" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B159" s="10">
         <f>IF(C159="","",COUNTA($C$2:C159))</f>
         <v>158</v>
@@ -9897,7 +9967,7 @@
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9913,7 +9983,7 @@
       <c r="R159" s="11"/>
       <c r="S159" s="10"/>
     </row>
-    <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B160" s="10">
         <f>IF(C160="","",COUNTA($C$2:C160))</f>
         <v>159</v>
@@ -9939,7 +10009,7 @@
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J160" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9955,7 +10025,7 @@
       <c r="R160" s="11"/>
       <c r="S160" s="10"/>
     </row>
-    <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B161" s="10">
         <f>IF(C161="","",COUNTA($C$2:C161))</f>
         <v>160</v>
@@ -9981,7 +10051,7 @@
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J161" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9997,7 +10067,7 @@
       <c r="R161" s="11"/>
       <c r="S161" s="10"/>
     </row>
-    <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B162" s="10">
         <f>IF(C162="","",COUNTA($C$2:C162))</f>
         <v>161</v>
@@ -10041,7 +10111,7 @@
       <c r="R162" s="11"/>
       <c r="S162" s="10"/>
     </row>
-    <row r="163" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="163" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B163" s="10">
         <f>IF(C163="","",COUNTA($C$2:C163))</f>
         <v>162</v>
@@ -10066,7 +10136,7 @@
       </c>
       <c r="I163" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J163" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10082,7 +10152,7 @@
       <c r="R163" s="11"/>
       <c r="S163" s="10"/>
     </row>
-    <row r="164" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="164" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B164" s="10">
         <f>IF(C164="","",COUNTA($C$2:C164))</f>
         <v>163</v>
@@ -10108,7 +10178,7 @@
       </c>
       <c r="I164" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J164" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10124,7 +10194,7 @@
       <c r="R164" s="11"/>
       <c r="S164" s="10"/>
     </row>
-    <row r="165" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="165" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B165" s="10">
         <f>IF(C165="","",COUNTA($C$2:C165))</f>
         <v>164</v>
@@ -10149,7 +10219,7 @@
       </c>
       <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J165" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10165,7 +10235,7 @@
       <c r="R165" s="11"/>
       <c r="S165" s="10"/>
     </row>
-    <row r="166" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="166" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B166" s="10">
         <f>IF(C166="","",COUNTA($C$2:C166))</f>
         <v>165</v>
@@ -10191,7 +10261,7 @@
       </c>
       <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J166" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10207,7 +10277,7 @@
       <c r="R166" s="11"/>
       <c r="S166" s="10"/>
     </row>
-    <row r="167" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="167" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B167" s="10">
         <f>IF(C167="","",COUNTA($C$2:C167))</f>
         <v>166</v>
@@ -10233,7 +10303,7 @@
       </c>
       <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J167" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10249,7 +10319,7 @@
       <c r="R167" s="11"/>
       <c r="S167" s="10"/>
     </row>
-    <row r="168" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="168" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B168" s="10">
         <f>IF(C168="","",COUNTA($C$2:C168))</f>
         <v>167</v>
@@ -10293,7 +10363,7 @@
       <c r="R168" s="11"/>
       <c r="S168" s="10"/>
     </row>
-    <row r="169" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="169" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B169" s="10">
         <f>IF(C169="","",COUNTA($C$2:C169))</f>
         <v>168</v>
@@ -10319,7 +10389,7 @@
       </c>
       <c r="I169" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J169" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10335,7 +10405,7 @@
       <c r="R169" s="11"/>
       <c r="S169" s="10"/>
     </row>
-    <row r="170" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="170" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B170" s="10">
         <f>IF(C170="","",COUNTA($C$2:C170))</f>
         <v>169</v>
@@ -10361,7 +10431,7 @@
       </c>
       <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J170" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10377,7 +10447,7 @@
       <c r="R170" s="11"/>
       <c r="S170" s="10"/>
     </row>
-    <row r="171" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="171" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B171" s="10">
         <f>IF(C171="","",COUNTA($C$2:C171))</f>
         <v>170</v>
@@ -10403,7 +10473,7 @@
       </c>
       <c r="I171" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J171" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10419,7 +10489,7 @@
       <c r="R171" s="11"/>
       <c r="S171" s="10"/>
     </row>
-    <row r="172" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="172" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B172" s="10">
         <f>IF(C172="","",COUNTA($C$2:C172))</f>
         <v>171</v>
@@ -10445,7 +10515,7 @@
       </c>
       <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J172" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10461,7 +10531,7 @@
       <c r="R172" s="11"/>
       <c r="S172" s="10"/>
     </row>
-    <row r="173" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="173" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B173" s="10">
         <f>IF(C173="","",COUNTA($C$2:C173))</f>
         <v>172</v>
@@ -10487,7 +10557,7 @@
       </c>
       <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J173" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10503,7 +10573,7 @@
       <c r="R173" s="11"/>
       <c r="S173" s="10"/>
     </row>
-    <row r="174" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="174" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B174" s="10">
         <f>IF(C174="","",COUNTA($C$2:C174))</f>
         <v>173</v>
@@ -10529,7 +10599,7 @@
       </c>
       <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J174" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10545,7 +10615,7 @@
       <c r="R174" s="11"/>
       <c r="S174" s="10"/>
     </row>
-    <row r="175" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="175" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B175" s="10">
         <f>IF(C175="","",COUNTA($C$2:C175))</f>
         <v>174</v>
@@ -10571,7 +10641,7 @@
       </c>
       <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J175" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10587,7 +10657,7 @@
       <c r="R175" s="11"/>
       <c r="S175" s="10"/>
     </row>
-    <row r="176" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="176" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B176" s="10">
         <f>IF(C176="","",COUNTA($C$2:C176))</f>
         <v>175</v>
@@ -10631,7 +10701,7 @@
       <c r="R176" s="11"/>
       <c r="S176" s="10"/>
     </row>
-    <row r="177" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="177" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B177" s="10">
         <f>IF(C177="","",COUNTA($C$2:C177))</f>
         <v>176</v>
@@ -10657,7 +10727,7 @@
       </c>
       <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J177" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10673,7 +10743,7 @@
       <c r="R177" s="11"/>
       <c r="S177" s="10"/>
     </row>
-    <row r="178" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="178" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B178" s="10">
         <f>IF(C178="","",COUNTA($C$2:C178))</f>
         <v>177</v>
@@ -10717,7 +10787,7 @@
       <c r="R178" s="11"/>
       <c r="S178" s="10"/>
     </row>
-    <row r="179" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="179" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B179" s="10">
         <f>IF(C179="","",COUNTA($C$2:C179))</f>
         <v>178</v>
@@ -10743,10 +10813,10 @@
       </c>
       <c r="I179" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J179" s="13" t="str">
-        <f t="shared" ref="J179:J185" ca="1" si="14">IF(I179="","",
+        <f t="shared" ref="J179:J193" ca="1" si="14">IF(I179="","",
  IF(G179="선급금",
    IF(I179&lt;=20,"정상",IF(I179&lt;=90,"관리","장기미수")),
  IF(G179="자재",
@@ -10767,7 +10837,7 @@
       <c r="R179" s="11"/>
       <c r="S179" s="10"/>
     </row>
-    <row r="180" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="180" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B180" s="10">
         <f>IF(C180="","",COUNTA($C$2:C180))</f>
         <v>179</v>
@@ -10793,7 +10863,7 @@
       </c>
       <c r="I180" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J180" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10809,7 +10879,7 @@
       <c r="R180" s="11"/>
       <c r="S180" s="10"/>
     </row>
-    <row r="181" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="181" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B181" s="10">
         <f>IF(C181="","",COUNTA($C$2:C181))</f>
         <v>180</v>
@@ -10835,7 +10905,7 @@
       </c>
       <c r="I181" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J181" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10851,7 +10921,7 @@
       <c r="R181" s="11"/>
       <c r="S181" s="10"/>
     </row>
-    <row r="182" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="182" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B182" s="10">
         <f>IF(C182="","",COUNTA($C$2:C182))</f>
         <v>181</v>
@@ -10877,7 +10947,7 @@
       </c>
       <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J182" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10893,7 +10963,7 @@
       <c r="R182" s="11"/>
       <c r="S182" s="10"/>
     </row>
-    <row r="183" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="183" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B183" s="10">
         <f>IF(C183="","",COUNTA($C$2:C183))</f>
         <v>182</v>
@@ -10919,7 +10989,7 @@
       </c>
       <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J183" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10935,7 +11005,7 @@
       <c r="R183" s="11"/>
       <c r="S183" s="10"/>
     </row>
-    <row r="184" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="184" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B184" s="10">
         <f>IF(C184="","",COUNTA($C$2:C184))</f>
         <v>183</v>
@@ -10961,7 +11031,7 @@
       </c>
       <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J184" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10977,7 +11047,7 @@
       <c r="R184" s="11"/>
       <c r="S184" s="10"/>
     </row>
-    <row r="185" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="185" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B185" s="10">
         <f>IF(C185="","",COUNTA($C$2:C185))</f>
         <v>184</v>
@@ -11003,7 +11073,7 @@
       </c>
       <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J185" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11019,199 +11089,345 @@
       <c r="R185" s="11"/>
       <c r="S185" s="10"/>
     </row>
-    <row r="186" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="B186" s="10" t="str">
+    <row r="186" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B186" s="10">
         <f>IF(C186="","",COUNTA($C$2:C186))</f>
-        <v/>
-      </c>
-      <c r="C186" s="11"/>
+        <v>185</v>
+      </c>
+      <c r="C186" s="35">
+        <v>46093</v>
+      </c>
       <c r="D186" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H186" s="4"/>
-      <c r="I186" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E186" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="F186" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="G186" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H186" s="25">
+        <v>312000</v>
+      </c>
+      <c r="I186" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J186" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J186" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K186" s="11"/>
-      <c r="L186" s="11"/>
+      <c r="L186" s="11">
+        <v>46093</v>
+      </c>
       <c r="M186" s="10"/>
-      <c r="N186" s="10"/>
+      <c r="N186" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q186" s="11"/>
       <c r="R186" s="11"/>
       <c r="S186" s="10"/>
     </row>
-    <row r="187" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="B187" s="10" t="str">
+    <row r="187" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B187" s="10">
         <f>IF(C187="","",COUNTA($C$2:C187))</f>
-        <v/>
-      </c>
-      <c r="C187" s="11"/>
+        <v>186</v>
+      </c>
+      <c r="C187" s="35" t="s">
+        <v>319</v>
+      </c>
       <c r="D187" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H187" s="4"/>
-      <c r="I187" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E187" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="F187" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H187" s="25">
+        <v>500500</v>
+      </c>
+      <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J187" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J187" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K187" s="11"/>
       <c r="L187" s="11"/>
       <c r="M187" s="10"/>
-      <c r="N187" s="10"/>
+      <c r="N187" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q187" s="11"/>
       <c r="R187" s="11"/>
       <c r="S187" s="10"/>
     </row>
-    <row r="188" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="B188" s="10" t="str">
+    <row r="188" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B188" s="10">
         <f>IF(C188="","",COUNTA($C$2:C188))</f>
-        <v/>
-      </c>
-      <c r="C188" s="11"/>
+        <v>187</v>
+      </c>
+      <c r="C188" s="35" t="s">
+        <v>319</v>
+      </c>
       <c r="D188" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H188" s="4"/>
-      <c r="I188" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E188" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F188" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="G188" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H188" s="25">
+        <v>1000500</v>
+      </c>
+      <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J188" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J188" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K188" s="11"/>
       <c r="L188" s="11"/>
       <c r="M188" s="10"/>
-      <c r="N188" s="10"/>
+      <c r="N188" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q188" s="11"/>
       <c r="R188" s="11"/>
       <c r="S188" s="10"/>
     </row>
-    <row r="189" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="B189" s="10" t="str">
+    <row r="189" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B189" s="10">
         <f>IF(C189="","",COUNTA($C$2:C189))</f>
-        <v/>
-      </c>
-      <c r="C189" s="11"/>
+        <v>188</v>
+      </c>
+      <c r="C189" s="35" t="s">
+        <v>319</v>
+      </c>
       <c r="D189" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H189" s="4"/>
-      <c r="I189" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E189" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="F189" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H189" s="25">
+        <v>5775000</v>
+      </c>
+      <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J189" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J189" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K189" s="11"/>
       <c r="L189" s="11"/>
       <c r="M189" s="10"/>
-      <c r="N189" s="10"/>
+      <c r="N189" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q189" s="11"/>
       <c r="R189" s="11"/>
       <c r="S189" s="10"/>
     </row>
-    <row r="190" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="B190" s="10" t="str">
+    <row r="190" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B190" s="10">
         <f>IF(C190="","",COUNTA($C$2:C190))</f>
-        <v/>
-      </c>
-      <c r="C190" s="11"/>
+        <v>189</v>
+      </c>
+      <c r="C190" s="35" t="s">
+        <v>319</v>
+      </c>
       <c r="D190" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H190" s="4"/>
-      <c r="I190" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E190" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="F190" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="G190" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H190" s="25">
+        <v>1190000</v>
+      </c>
+      <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J190" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J190" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K190" s="11"/>
       <c r="L190" s="11"/>
       <c r="M190" s="10"/>
-      <c r="N190" s="10"/>
+      <c r="N190" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q190" s="11"/>
       <c r="R190" s="11"/>
       <c r="S190" s="10"/>
     </row>
-    <row r="191" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="B191" s="10" t="str">
+    <row r="191" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B191" s="10">
         <f>IF(C191="","",COUNTA($C$2:C191))</f>
-        <v/>
-      </c>
-      <c r="C191" s="11"/>
+        <v>190</v>
+      </c>
+      <c r="C191" s="35" t="s">
+        <v>319</v>
+      </c>
       <c r="D191" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H191" s="4"/>
-      <c r="I191" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E191" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F191" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H191" s="25">
+        <v>11147800</v>
+      </c>
+      <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J191" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J191" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K191" s="11"/>
       <c r="L191" s="11"/>
       <c r="M191" s="10"/>
-      <c r="N191" s="10"/>
+      <c r="N191" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q191" s="11"/>
       <c r="R191" s="11"/>
       <c r="S191" s="10"/>
     </row>
-    <row r="192" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="B192" s="10" t="str">
+    <row r="192" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B192" s="10">
         <f>IF(C192="","",COUNTA($C$2:C192))</f>
-        <v/>
-      </c>
-      <c r="C192" s="11"/>
+        <v>191</v>
+      </c>
+      <c r="C192" s="35" t="s">
+        <v>319</v>
+      </c>
       <c r="D192" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H192" s="4"/>
-      <c r="I192" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E192" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F192" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H192" s="25">
+        <v>2613000</v>
+      </c>
+      <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J192" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J192" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K192" s="11"/>
       <c r="L192" s="11"/>
       <c r="M192" s="10"/>
-      <c r="N192" s="10"/>
+      <c r="N192" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q192" s="11"/>
       <c r="R192" s="11"/>
       <c r="S192" s="10"/>
     </row>
-    <row r="193" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
-      <c r="B193" s="10" t="str">
+    <row r="193" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B193" s="10">
         <f>IF(C193="","",COUNTA($C$2:C193))</f>
-        <v/>
-      </c>
-      <c r="C193" s="11"/>
+        <v>192</v>
+      </c>
+      <c r="C193" s="35" t="s">
+        <v>319</v>
+      </c>
       <c r="D193" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H193" s="4"/>
-      <c r="I193" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E193" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="F193" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="G193" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="H193" s="25">
+        <v>7339000</v>
+      </c>
+      <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J193" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J193" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K193" s="11"/>
       <c r="L193" s="11"/>
       <c r="M193" s="10"/>
-      <c r="N193" s="10"/>
+      <c r="N193" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q193" s="11"/>
       <c r="R193" s="11"/>
       <c r="S193" s="10"/>
     </row>
-    <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B194" s="10" t="str">
         <f>IF(C194="","",COUNTA($C$2:C194))</f>
         <v/>
@@ -11235,7 +11451,7 @@
       <c r="R194" s="11"/>
       <c r="S194" s="10"/>
     </row>
-    <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B195" s="10" t="str">
         <f>IF(C195="","",COUNTA($C$2:C195))</f>
         <v/>
@@ -11259,7 +11475,7 @@
       <c r="R195" s="11"/>
       <c r="S195" s="10"/>
     </row>
-    <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B196" s="10" t="str">
         <f>IF(C196="","",COUNTA($C$2:C196))</f>
         <v/>
@@ -11283,7 +11499,7 @@
       <c r="R196" s="11"/>
       <c r="S196" s="10"/>
     </row>
-    <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B197" s="10" t="str">
         <f>IF(C197="","",COUNTA($C$2:C197))</f>
         <v/>
@@ -11307,7 +11523,7 @@
       <c r="R197" s="11"/>
       <c r="S197" s="10"/>
     </row>
-    <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B198" s="10" t="str">
         <f>IF(C198="","",COUNTA($C$2:C198))</f>
         <v/>
@@ -11331,7 +11547,7 @@
       <c r="R198" s="11"/>
       <c r="S198" s="10"/>
     </row>
-    <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B199" s="10" t="str">
         <f>IF(C199="","",COUNTA($C$2:C199))</f>
         <v/>
@@ -11355,7 +11571,7 @@
       <c r="R199" s="11"/>
       <c r="S199" s="10"/>
     </row>
-    <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B200" s="10" t="str">
         <f>IF(C200="","",COUNTA($C$2:C200))</f>
         <v/>
@@ -11379,7 +11595,7 @@
       <c r="R200" s="11"/>
       <c r="S200" s="10"/>
     </row>
-    <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B201" s="10" t="str">
         <f>IF(C201="","",COUNTA($C$2:C201))</f>
         <v/>
@@ -11403,7 +11619,7 @@
       <c r="R201" s="11"/>
       <c r="S201" s="10"/>
     </row>
-    <row r="202" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="202" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B202" s="10" t="str">
         <f>IF(C202="","",COUNTA($C$2:C202))</f>
         <v/>
@@ -11427,7 +11643,7 @@
       <c r="R202" s="11"/>
       <c r="S202" s="10"/>
     </row>
-    <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B203" s="10" t="str">
         <f>IF(C203="","",COUNTA($C$2:C203))</f>
         <v/>
@@ -11451,7 +11667,7 @@
       <c r="R203" s="11"/>
       <c r="S203" s="10"/>
     </row>
-    <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B204" s="10" t="str">
         <f>IF(C204="","",COUNTA($C$2:C204))</f>
         <v/>
@@ -11475,7 +11691,7 @@
       <c r="R204" s="11"/>
       <c r="S204" s="10"/>
     </row>
-    <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B205" s="10" t="str">
         <f>IF(C205="","",COUNTA($C$2:C205))</f>
         <v/>
@@ -11499,7 +11715,7 @@
       <c r="R205" s="11"/>
       <c r="S205" s="10"/>
     </row>
-    <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B206" s="10" t="str">
         <f>IF(C206="","",COUNTA($C$2:C206))</f>
         <v/>
@@ -11523,7 +11739,7 @@
       <c r="R206" s="11"/>
       <c r="S206" s="10"/>
     </row>
-    <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B207" s="10" t="str">
         <f>IF(C207="","",COUNTA($C$2:C207))</f>
         <v/>
@@ -11547,7 +11763,7 @@
       <c r="R207" s="11"/>
       <c r="S207" s="10"/>
     </row>
-    <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B208" s="10" t="str">
         <f>IF(C208="","",COUNTA($C$2:C208))</f>
         <v/>
@@ -11571,7 +11787,7 @@
       <c r="R208" s="11"/>
       <c r="S208" s="10"/>
     </row>
-    <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B209" s="10" t="str">
         <f>IF(C209="","",COUNTA($C$2:C209))</f>
         <v/>
@@ -11595,7 +11811,7 @@
       <c r="R209" s="11"/>
       <c r="S209" s="10"/>
     </row>
-    <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B210" s="10" t="str">
         <f>IF(C210="","",COUNTA($C$2:C210))</f>
         <v/>
@@ -11619,7 +11835,7 @@
       <c r="R210" s="11"/>
       <c r="S210" s="10"/>
     </row>
-    <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B211" s="10" t="str">
         <f>IF(C211="","",COUNTA($C$2:C211))</f>
         <v/>
@@ -11643,7 +11859,7 @@
       <c r="R211" s="11"/>
       <c r="S211" s="10"/>
     </row>
-    <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B212" s="10"/>
       <c r="C212" s="11"/>
       <c r="D212" s="10" t="str">
@@ -11664,7 +11880,7 @@
       <c r="R212" s="11"/>
       <c r="S212" s="10"/>
     </row>
-    <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B213" s="10"/>
       <c r="C213" s="11"/>
       <c r="D213" s="10" t="str">
@@ -11685,7 +11901,7 @@
       <c r="R213" s="11"/>
       <c r="S213" s="10"/>
     </row>
-    <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B214" s="10"/>
       <c r="C214" s="11"/>
       <c r="D214" s="10" t="str">
@@ -11706,7 +11922,7 @@
       <c r="R214" s="11"/>
       <c r="S214" s="10"/>
     </row>
-    <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B215" s="10"/>
       <c r="C215" s="11"/>
       <c r="D215" s="10" t="str">
@@ -11727,7 +11943,7 @@
       <c r="R215" s="11"/>
       <c r="S215" s="10"/>
     </row>
-    <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B216" s="10"/>
       <c r="C216" s="11"/>
       <c r="D216" s="10" t="str">
@@ -11748,7 +11964,7 @@
       <c r="R216" s="11"/>
       <c r="S216" s="10"/>
     </row>
-    <row r="217" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="217" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B217" s="10"/>
       <c r="C217" s="11"/>
       <c r="D217" s="10" t="str">
@@ -11769,7 +11985,7 @@
       <c r="R217" s="11"/>
       <c r="S217" s="10"/>
     </row>
-    <row r="218" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="218" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B218" s="10"/>
       <c r="C218" s="11"/>
       <c r="D218" s="10" t="str">
@@ -11790,7 +12006,7 @@
       <c r="R218" s="11"/>
       <c r="S218" s="10"/>
     </row>
-    <row r="219" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="219" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B219" s="10"/>
       <c r="C219" s="11"/>
       <c r="D219" s="10" t="str">
@@ -11811,7 +12027,7 @@
       <c r="R219" s="11"/>
       <c r="S219" s="10"/>
     </row>
-    <row r="220" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="220" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B220" s="10"/>
       <c r="C220" s="11"/>
       <c r="D220" s="10" t="str">
@@ -11832,7 +12048,7 @@
       <c r="R220" s="11"/>
       <c r="S220" s="10"/>
     </row>
-    <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B221" s="10"/>
       <c r="C221" s="11"/>
       <c r="D221" s="10" t="str">
@@ -11853,7 +12069,7 @@
       <c r="R221" s="11"/>
       <c r="S221" s="10"/>
     </row>
-    <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B222" s="10"/>
       <c r="C222" s="11"/>
       <c r="D222" s="10" t="str">
@@ -11874,7 +12090,7 @@
       <c r="R222" s="11"/>
       <c r="S222" s="10"/>
     </row>
-    <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B223" s="10"/>
       <c r="C223" s="11"/>
       <c r="D223" s="10" t="str">
@@ -11895,7 +12111,7 @@
       <c r="R223" s="11"/>
       <c r="S223" s="10"/>
     </row>
-    <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B224" s="10"/>
       <c r="C224" s="11"/>
       <c r="D224" s="10" t="str">
@@ -11916,7 +12132,7 @@
       <c r="R224" s="11"/>
       <c r="S224" s="10"/>
     </row>
-    <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B225" s="10"/>
       <c r="C225" s="11"/>
       <c r="D225" s="10" t="str">
@@ -11937,7 +12153,7 @@
       <c r="R225" s="11"/>
       <c r="S225" s="10"/>
     </row>
-    <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B226" s="10"/>
       <c r="C226" s="11"/>
       <c r="D226" s="10" t="str">
@@ -11958,7 +12174,7 @@
       <c r="R226" s="11"/>
       <c r="S226" s="10"/>
     </row>
-    <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B227" s="10"/>
       <c r="C227" s="11"/>
       <c r="D227" s="10" t="str">
@@ -11979,7 +12195,7 @@
       <c r="R227" s="11"/>
       <c r="S227" s="10"/>
     </row>
-    <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B228" s="10"/>
       <c r="C228" s="11"/>
       <c r="D228" s="10" t="str">
@@ -12000,7 +12216,7 @@
       <c r="R228" s="11"/>
       <c r="S228" s="10"/>
     </row>
-    <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B229" s="10"/>
       <c r="C229" s="11"/>
       <c r="D229" s="10" t="str">
@@ -12021,7 +12237,7 @@
       <c r="R229" s="11"/>
       <c r="S229" s="10"/>
     </row>
-    <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B230" s="10"/>
       <c r="C230" s="11"/>
       <c r="D230" s="10" t="str">
@@ -12042,7 +12258,7 @@
       <c r="R230" s="11"/>
       <c r="S230" s="10"/>
     </row>
-    <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B231" s="10"/>
       <c r="C231" s="11"/>
       <c r="D231" s="10" t="str">
@@ -12063,7 +12279,7 @@
       <c r="R231" s="11"/>
       <c r="S231" s="10"/>
     </row>
-    <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B232" s="10"/>
       <c r="C232" s="11"/>
       <c r="D232" s="10" t="str">
@@ -12084,7 +12300,7 @@
       <c r="R232" s="11"/>
       <c r="S232" s="10"/>
     </row>
-    <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B233" s="10"/>
       <c r="C233" s="11"/>
       <c r="D233" s="10" t="str">
@@ -12105,7 +12321,7 @@
       <c r="R233" s="11"/>
       <c r="S233" s="10"/>
     </row>
-    <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B234" s="10"/>
       <c r="C234" s="11"/>
       <c r="D234" s="10" t="str">
@@ -12126,7 +12342,7 @@
       <c r="R234" s="11"/>
       <c r="S234" s="10"/>
     </row>
-    <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B235" s="10"/>
       <c r="C235" s="11"/>
       <c r="D235" s="10" t="str">
@@ -12147,7 +12363,7 @@
       <c r="R235" s="11"/>
       <c r="S235" s="10"/>
     </row>
-    <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B236" s="10"/>
       <c r="C236" s="11"/>
       <c r="D236" s="10" t="str">
@@ -12168,7 +12384,7 @@
       <c r="R236" s="11"/>
       <c r="S236" s="10"/>
     </row>
-    <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B237" s="10"/>
       <c r="C237" s="11"/>
       <c r="D237" s="10" t="str">
@@ -12189,7 +12405,7 @@
       <c r="R237" s="11"/>
       <c r="S237" s="10"/>
     </row>
-    <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B238" s="10"/>
       <c r="C238" s="11"/>
       <c r="D238" s="10" t="str">
@@ -12210,7 +12426,7 @@
       <c r="R238" s="11"/>
       <c r="S238" s="10"/>
     </row>
-    <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B239" s="10"/>
       <c r="C239" s="11"/>
       <c r="D239" s="10" t="str">
@@ -12231,7 +12447,7 @@
       <c r="R239" s="11"/>
       <c r="S239" s="10"/>
     </row>
-    <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B240" s="10"/>
       <c r="C240" s="11"/>
       <c r="D240" s="10" t="str">
@@ -12252,7 +12468,7 @@
       <c r="R240" s="11"/>
       <c r="S240" s="10"/>
     </row>
-    <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B241" s="10"/>
       <c r="C241" s="11"/>
       <c r="D241" s="10" t="str">
@@ -12273,7 +12489,7 @@
       <c r="R241" s="11"/>
       <c r="S241" s="10"/>
     </row>
-    <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B242" s="10"/>
       <c r="C242" s="11"/>
       <c r="D242" s="10" t="str">
@@ -12294,7 +12510,7 @@
       <c r="R242" s="11"/>
       <c r="S242" s="10"/>
     </row>
-    <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B243" s="10"/>
       <c r="C243" s="11"/>
       <c r="D243" s="10" t="str">
@@ -12315,7 +12531,7 @@
       <c r="R243" s="11"/>
       <c r="S243" s="10"/>
     </row>
-    <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B244" s="10"/>
       <c r="C244" s="11"/>
       <c r="D244" s="10" t="str">
@@ -12336,7 +12552,7 @@
       <c r="R244" s="11"/>
       <c r="S244" s="10"/>
     </row>
-    <row r="245" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="245" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B245" s="10"/>
       <c r="C245" s="11"/>
       <c r="D245" s="10" t="str">
@@ -12357,7 +12573,7 @@
       <c r="R245" s="11"/>
       <c r="S245" s="10"/>
     </row>
-    <row r="246" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="246" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B246" s="10"/>
       <c r="C246" s="11"/>
       <c r="D246" s="10" t="str">
@@ -12378,7 +12594,7 @@
       <c r="R246" s="11"/>
       <c r="S246" s="10"/>
     </row>
-    <row r="247" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="247" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B247" s="10"/>
       <c r="C247" s="11"/>
       <c r="D247" s="10" t="str">
@@ -12399,7 +12615,7 @@
       <c r="R247" s="11"/>
       <c r="S247" s="10"/>
     </row>
-    <row r="248" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="248" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B248" s="10"/>
       <c r="C248" s="11"/>
       <c r="D248" s="10" t="str">
@@ -12420,7 +12636,7 @@
       <c r="R248" s="11"/>
       <c r="S248" s="10"/>
     </row>
-    <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B249" s="10"/>
       <c r="C249" s="11"/>
       <c r="D249" s="10" t="str">
@@ -12441,7 +12657,7 @@
       <c r="R249" s="11"/>
       <c r="S249" s="10"/>
     </row>
-    <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B250" s="10"/>
       <c r="C250" s="11"/>
       <c r="D250" s="10" t="str">
@@ -12462,7 +12678,7 @@
       <c r="R250" s="11"/>
       <c r="S250" s="10"/>
     </row>
-    <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B251" s="10"/>
       <c r="C251" s="11"/>
       <c r="D251" s="10" t="str">
@@ -12483,7 +12699,7 @@
       <c r="R251" s="11"/>
       <c r="S251" s="10"/>
     </row>
-    <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B252" s="10"/>
       <c r="C252" s="11"/>
       <c r="D252" s="10" t="str">
@@ -12504,7 +12720,7 @@
       <c r="R252" s="11"/>
       <c r="S252" s="10"/>
     </row>
-    <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B253" s="10"/>
       <c r="C253" s="11"/>
       <c r="D253" s="10" t="str">
@@ -12525,7 +12741,7 @@
       <c r="R253" s="11"/>
       <c r="S253" s="10"/>
     </row>
-    <row r="254" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="254" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B254" s="10"/>
       <c r="C254" s="11"/>
       <c r="D254" s="10" t="str">
@@ -12546,7 +12762,7 @@
       <c r="R254" s="11"/>
       <c r="S254" s="10"/>
     </row>
-    <row r="255" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="255" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B255" s="10"/>
       <c r="C255" s="11"/>
       <c r="D255" s="10" t="str">
@@ -12567,7 +12783,7 @@
       <c r="R255" s="11"/>
       <c r="S255" s="10"/>
     </row>
-    <row r="256" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="256" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B256" s="10"/>
       <c r="C256" s="11"/>
       <c r="D256" s="10" t="str">
@@ -12588,7 +12804,7 @@
       <c r="R256" s="11"/>
       <c r="S256" s="10"/>
     </row>
-    <row r="257" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="257" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B257" s="10"/>
       <c r="C257" s="11"/>
       <c r="D257" s="10" t="str">
@@ -12609,7 +12825,7 @@
       <c r="R257" s="11"/>
       <c r="S257" s="10"/>
     </row>
-    <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B258" s="10"/>
       <c r="C258" s="11"/>
       <c r="D258" s="10" t="str">
@@ -12630,7 +12846,7 @@
       <c r="R258" s="11"/>
       <c r="S258" s="10"/>
     </row>
-    <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B259" s="10"/>
       <c r="C259" s="11"/>
       <c r="D259" s="10" t="str">
@@ -12651,7 +12867,7 @@
       <c r="R259" s="11"/>
       <c r="S259" s="10"/>
     </row>
-    <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B260" s="10"/>
       <c r="C260" s="11"/>
       <c r="D260" s="10" t="str">
@@ -12672,7 +12888,7 @@
       <c r="R260" s="11"/>
       <c r="S260" s="10"/>
     </row>
-    <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B261" s="10"/>
       <c r="C261" s="11"/>
       <c r="D261" s="10" t="str">
@@ -12693,7 +12909,7 @@
       <c r="R261" s="11"/>
       <c r="S261" s="10"/>
     </row>
-    <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B262" s="10"/>
       <c r="C262" s="11"/>
       <c r="D262" s="10" t="str">
@@ -12714,7 +12930,7 @@
       <c r="R262" s="11"/>
       <c r="S262" s="10"/>
     </row>
-    <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B263" s="10"/>
       <c r="C263" s="11"/>
       <c r="D263" s="10" t="str">
@@ -12735,7 +12951,7 @@
       <c r="R263" s="11"/>
       <c r="S263" s="10"/>
     </row>
-    <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B264" s="10"/>
       <c r="C264" s="11"/>
       <c r="D264" s="10" t="str">
@@ -12756,7 +12972,7 @@
       <c r="R264" s="11"/>
       <c r="S264" s="10"/>
     </row>
-    <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B265" s="10"/>
       <c r="C265" s="11"/>
       <c r="D265" s="10" t="str">
@@ -12777,7 +12993,7 @@
       <c r="R265" s="11"/>
       <c r="S265" s="10"/>
     </row>
-    <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B266" s="10"/>
       <c r="C266" s="11"/>
       <c r="D266" s="10" t="str">
@@ -12798,7 +13014,7 @@
       <c r="R266" s="11"/>
       <c r="S266" s="10"/>
     </row>
-    <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B267" s="10"/>
       <c r="C267" s="11"/>
       <c r="D267" s="10" t="str">
@@ -12819,7 +13035,7 @@
       <c r="R267" s="11"/>
       <c r="S267" s="10"/>
     </row>
-    <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
       <c r="D268" s="10" t="str">
@@ -12840,7 +13056,7 @@
       <c r="R268" s="11"/>
       <c r="S268" s="10"/>
     </row>
-    <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B269" s="10"/>
       <c r="C269" s="11"/>
       <c r="D269" s="10" t="str">
@@ -12861,7 +13077,7 @@
       <c r="R269" s="11"/>
       <c r="S269" s="10"/>
     </row>
-    <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B270" s="10"/>
       <c r="C270" s="11"/>
       <c r="D270" s="10" t="str">
@@ -12882,7 +13098,7 @@
       <c r="R270" s="11"/>
       <c r="S270" s="10"/>
     </row>
-    <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B271" s="10"/>
       <c r="C271" s="11"/>
       <c r="D271" s="10" t="str">
@@ -12903,7 +13119,7 @@
       <c r="R271" s="11"/>
       <c r="S271" s="10"/>
     </row>
-    <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B272" s="10"/>
       <c r="C272" s="11"/>
       <c r="D272" s="10" t="str">
@@ -12924,7 +13140,7 @@
       <c r="R272" s="11"/>
       <c r="S272" s="10"/>
     </row>
-    <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B273" s="10"/>
       <c r="C273" s="11"/>
       <c r="D273" s="10" t="str">
@@ -12945,7 +13161,7 @@
       <c r="R273" s="11"/>
       <c r="S273" s="10"/>
     </row>
-    <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B274" s="10"/>
       <c r="C274" s="11"/>
       <c r="D274" s="10" t="str">
@@ -12966,7 +13182,7 @@
       <c r="R274" s="11"/>
       <c r="S274" s="10"/>
     </row>
-    <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B275" s="10"/>
       <c r="C275" s="11"/>
       <c r="D275" s="10" t="str">
@@ -12987,7 +13203,7 @@
       <c r="R275" s="11"/>
       <c r="S275" s="10"/>
     </row>
-    <row r="276" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="276" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B276" s="10"/>
       <c r="C276" s="11"/>
       <c r="D276" s="10" t="str">
@@ -13008,7 +13224,7 @@
       <c r="R276" s="11"/>
       <c r="S276" s="10"/>
     </row>
-    <row r="277" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="277" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B277" s="10"/>
       <c r="C277" s="11"/>
       <c r="D277" s="10" t="str">
@@ -13029,7 +13245,7 @@
       <c r="R277" s="11"/>
       <c r="S277" s="10"/>
     </row>
-    <row r="278" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="278" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B278" s="10"/>
       <c r="C278" s="11"/>
       <c r="D278" s="10" t="str">
@@ -13050,7 +13266,7 @@
       <c r="R278" s="11"/>
       <c r="S278" s="10"/>
     </row>
-    <row r="279" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="279" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B279" s="10"/>
       <c r="C279" s="11"/>
       <c r="D279" s="10" t="str">
@@ -13071,7 +13287,7 @@
       <c r="R279" s="11"/>
       <c r="S279" s="10"/>
     </row>
-    <row r="280" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="280" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B280" s="10"/>
       <c r="C280" s="11"/>
       <c r="D280" s="10" t="str">
@@ -13092,7 +13308,7 @@
       <c r="R280" s="11"/>
       <c r="S280" s="10"/>
     </row>
-    <row r="281" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="281" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B281" s="10"/>
       <c r="C281" s="11"/>
       <c r="D281" s="10" t="str">
@@ -13113,7 +13329,7 @@
       <c r="R281" s="11"/>
       <c r="S281" s="10"/>
     </row>
-    <row r="282" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="282" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B282" s="10"/>
       <c r="C282" s="11"/>
       <c r="D282" s="10" t="str">
@@ -13134,7 +13350,7 @@
       <c r="R282" s="11"/>
       <c r="S282" s="10"/>
     </row>
-    <row r="283" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="283" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B283" s="10"/>
       <c r="C283" s="11"/>
       <c r="D283" s="10" t="str">
@@ -13155,7 +13371,7 @@
       <c r="R283" s="11"/>
       <c r="S283" s="10"/>
     </row>
-    <row r="284" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="284" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B284" s="10"/>
       <c r="C284" s="11"/>
       <c r="D284" s="10" t="str">
@@ -13176,7 +13392,7 @@
       <c r="R284" s="11"/>
       <c r="S284" s="10"/>
     </row>
-    <row r="285" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="285" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B285" s="10"/>
       <c r="C285" s="11"/>
       <c r="D285" s="10" t="str">
@@ -13197,7 +13413,7 @@
       <c r="R285" s="11"/>
       <c r="S285" s="10"/>
     </row>
-    <row r="286" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="286" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B286" s="10"/>
       <c r="C286" s="11"/>
       <c r="D286" s="10" t="str">
@@ -13218,7 +13434,7 @@
       <c r="R286" s="11"/>
       <c r="S286" s="10"/>
     </row>
-    <row r="287" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="287" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B287" s="10"/>
       <c r="C287" s="11"/>
       <c r="D287" s="10" t="str">
@@ -13239,7 +13455,7 @@
       <c r="R287" s="11"/>
       <c r="S287" s="10"/>
     </row>
-    <row r="288" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="288" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B288" s="10"/>
       <c r="C288" s="11"/>
       <c r="D288" s="10" t="str">
@@ -13260,7 +13476,7 @@
       <c r="R288" s="11"/>
       <c r="S288" s="10"/>
     </row>
-    <row r="289" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="289" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B289" s="10"/>
       <c r="C289" s="11"/>
       <c r="D289" s="10" t="str">
@@ -13281,7 +13497,7 @@
       <c r="R289" s="11"/>
       <c r="S289" s="10"/>
     </row>
-    <row r="290" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="290" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B290" s="10"/>
       <c r="C290" s="11"/>
       <c r="D290" s="10" t="str">
@@ -13302,7 +13518,7 @@
       <c r="R290" s="11"/>
       <c r="S290" s="10"/>
     </row>
-    <row r="291" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="291" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B291" s="10"/>
       <c r="C291" s="11"/>
       <c r="D291" s="10" t="str">
@@ -13323,7 +13539,7 @@
       <c r="R291" s="11"/>
       <c r="S291" s="10"/>
     </row>
-    <row r="292" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="292" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B292" s="10"/>
       <c r="C292" s="11"/>
       <c r="D292" s="10" t="str">
@@ -13344,7 +13560,7 @@
       <c r="R292" s="11"/>
       <c r="S292" s="10"/>
     </row>
-    <row r="293" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="293" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B293" s="10"/>
       <c r="C293" s="11"/>
       <c r="D293" s="10" t="str">
@@ -13365,7 +13581,7 @@
       <c r="R293" s="11"/>
       <c r="S293" s="10"/>
     </row>
-    <row r="294" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="294" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B294" s="10"/>
       <c r="C294" s="11"/>
       <c r="D294" s="10" t="str">
@@ -13386,7 +13602,7 @@
       <c r="R294" s="11"/>
       <c r="S294" s="10"/>
     </row>
-    <row r="295" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="295" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B295" s="10"/>
       <c r="C295" s="11"/>
       <c r="D295" s="10" t="str">
@@ -13407,7 +13623,7 @@
       <c r="R295" s="11"/>
       <c r="S295" s="10"/>
     </row>
-    <row r="296" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="296" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B296" s="10"/>
       <c r="C296" s="11"/>
       <c r="D296" s="10" t="str">
@@ -13428,7 +13644,7 @@
       <c r="R296" s="11"/>
       <c r="S296" s="10"/>
     </row>
-    <row r="297" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="297" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B297" s="10"/>
       <c r="C297" s="11"/>
       <c r="D297" s="10" t="str">
@@ -13449,7 +13665,7 @@
       <c r="R297" s="11"/>
       <c r="S297" s="10"/>
     </row>
-    <row r="298" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="298" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B298" s="10"/>
       <c r="C298" s="11"/>
       <c r="D298" s="10" t="str">
@@ -13470,7 +13686,7 @@
       <c r="R298" s="11"/>
       <c r="S298" s="10"/>
     </row>
-    <row r="299" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="299" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B299" s="10"/>
       <c r="C299" s="11"/>
       <c r="D299" s="10" t="str">
@@ -13491,7 +13707,7 @@
       <c r="R299" s="11"/>
       <c r="S299" s="10"/>
     </row>
-    <row r="300" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="300" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B300" s="10"/>
       <c r="C300" s="11"/>
       <c r="D300" s="10" t="str">
@@ -13512,7 +13728,7 @@
       <c r="R300" s="11"/>
       <c r="S300" s="10"/>
     </row>
-    <row r="301" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="301" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B301" s="10"/>
       <c r="C301" s="11"/>
       <c r="D301" s="10" t="str">
@@ -13533,7 +13749,7 @@
       <c r="R301" s="11"/>
       <c r="S301" s="10"/>
     </row>
-    <row r="302" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="302" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B302" s="10"/>
       <c r="C302" s="11"/>
       <c r="D302" s="10" t="str">
@@ -13554,7 +13770,7 @@
       <c r="R302" s="11"/>
       <c r="S302" s="10"/>
     </row>
-    <row r="303" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="303" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B303" s="10"/>
       <c r="C303" s="11"/>
       <c r="D303" s="10" t="str">
@@ -13575,7 +13791,7 @@
       <c r="R303" s="11"/>
       <c r="S303" s="10"/>
     </row>
-    <row r="304" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="304" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B304" s="10"/>
       <c r="C304" s="11"/>
       <c r="D304" s="10" t="str">
@@ -13596,7 +13812,7 @@
       <c r="R304" s="11"/>
       <c r="S304" s="10"/>
     </row>
-    <row r="305" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="305" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B305" s="10"/>
       <c r="C305" s="11"/>
       <c r="D305" s="10" t="str">
@@ -13617,7 +13833,7 @@
       <c r="R305" s="11"/>
       <c r="S305" s="10"/>
     </row>
-    <row r="306" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="306" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B306" s="10"/>
       <c r="C306" s="11"/>
       <c r="D306" s="10" t="str">
@@ -13638,7 +13854,7 @@
       <c r="R306" s="11"/>
       <c r="S306" s="10"/>
     </row>
-    <row r="307" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="307" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B307" s="10"/>
       <c r="C307" s="11"/>
       <c r="D307" s="10" t="str">
@@ -13659,7 +13875,7 @@
       <c r="R307" s="11"/>
       <c r="S307" s="10"/>
     </row>
-    <row r="308" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="308" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B308" s="10"/>
       <c r="C308" s="11"/>
       <c r="D308" s="10" t="str">
@@ -13680,7 +13896,7 @@
       <c r="R308" s="11"/>
       <c r="S308" s="10"/>
     </row>
-    <row r="309" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="309" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B309" s="10"/>
       <c r="C309" s="11"/>
       <c r="D309" s="10" t="str">
@@ -13701,7 +13917,7 @@
       <c r="R309" s="11"/>
       <c r="S309" s="10"/>
     </row>
-    <row r="310" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="310" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B310" s="10"/>
       <c r="C310" s="11"/>
       <c r="D310" s="10" t="str">
@@ -13722,7 +13938,7 @@
       <c r="R310" s="11"/>
       <c r="S310" s="10"/>
     </row>
-    <row r="311" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="311" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B311" s="10"/>
       <c r="C311" s="11"/>
       <c r="D311" s="10" t="str">
@@ -13743,7 +13959,7 @@
       <c r="R311" s="11"/>
       <c r="S311" s="10"/>
     </row>
-    <row r="312" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="312" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B312" s="10"/>
       <c r="C312" s="11"/>
       <c r="D312" s="10" t="str">
@@ -13764,7 +13980,7 @@
       <c r="R312" s="11"/>
       <c r="S312" s="10"/>
     </row>
-    <row r="313" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="313" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B313" s="10"/>
       <c r="C313" s="11"/>
       <c r="D313" s="10" t="str">
@@ -13785,7 +14001,7 @@
       <c r="R313" s="11"/>
       <c r="S313" s="10"/>
     </row>
-    <row r="314" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="314" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B314" s="10"/>
       <c r="C314" s="11"/>
       <c r="D314" s="10" t="str">
@@ -13806,7 +14022,7 @@
       <c r="R314" s="11"/>
       <c r="S314" s="10"/>
     </row>
-    <row r="315" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="315" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B315" s="10"/>
       <c r="C315" s="11"/>
       <c r="D315" s="10" t="str">
@@ -13827,7 +14043,7 @@
       <c r="R315" s="11"/>
       <c r="S315" s="10"/>
     </row>
-    <row r="316" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="316" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B316" s="10"/>
       <c r="C316" s="11"/>
       <c r="D316" s="10" t="str">
@@ -13848,7 +14064,7 @@
       <c r="R316" s="11"/>
       <c r="S316" s="10"/>
     </row>
-    <row r="317" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="317" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B317" s="10"/>
       <c r="C317" s="11"/>
       <c r="D317" s="10" t="str">
@@ -13869,7 +14085,7 @@
       <c r="R317" s="11"/>
       <c r="S317" s="10"/>
     </row>
-    <row r="318" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="318" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B318" s="10"/>
       <c r="C318" s="11"/>
       <c r="D318" s="10" t="str">
@@ -13890,7 +14106,7 @@
       <c r="R318" s="11"/>
       <c r="S318" s="10"/>
     </row>
-    <row r="319" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="319" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B319" s="10"/>
       <c r="C319" s="11"/>
       <c r="D319" s="10" t="str">
@@ -13911,7 +14127,7 @@
       <c r="R319" s="11"/>
       <c r="S319" s="10"/>
     </row>
-    <row r="320" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="320" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B320" s="10"/>
       <c r="C320" s="11"/>
       <c r="D320" s="10" t="str">
@@ -13932,7 +14148,7 @@
       <c r="R320" s="11"/>
       <c r="S320" s="10"/>
     </row>
-    <row r="321" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="321" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B321" s="10"/>
       <c r="C321" s="11"/>
       <c r="D321" s="10" t="str">
@@ -13953,7 +14169,7 @@
       <c r="R321" s="11"/>
       <c r="S321" s="10"/>
     </row>
-    <row r="322" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="322" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B322" s="10"/>
       <c r="C322" s="11"/>
       <c r="D322" s="10" t="str">
@@ -13974,7 +14190,7 @@
       <c r="R322" s="11"/>
       <c r="S322" s="10"/>
     </row>
-    <row r="323" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="323" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B323" s="10"/>
       <c r="C323" s="11"/>
       <c r="D323" s="10" t="str">
@@ -13995,7 +14211,7 @@
       <c r="R323" s="11"/>
       <c r="S323" s="10"/>
     </row>
-    <row r="324" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="324" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B324" s="10"/>
       <c r="C324" s="11"/>
       <c r="D324" s="10" t="str">
@@ -14016,7 +14232,7 @@
       <c r="R324" s="11"/>
       <c r="S324" s="10"/>
     </row>
-    <row r="325" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="325" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B325" s="10"/>
       <c r="C325" s="11"/>
       <c r="D325" s="10" t="str">
@@ -14037,7 +14253,7 @@
       <c r="R325" s="11"/>
       <c r="S325" s="10"/>
     </row>
-    <row r="326" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="326" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B326" s="10"/>
       <c r="C326" s="11"/>
       <c r="D326" s="10" t="str">
@@ -14058,7 +14274,7 @@
       <c r="R326" s="11"/>
       <c r="S326" s="10"/>
     </row>
-    <row r="327" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="327" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B327" s="10"/>
       <c r="C327" s="11"/>
       <c r="D327" s="10" t="str">
@@ -14079,7 +14295,7 @@
       <c r="R327" s="11"/>
       <c r="S327" s="10"/>
     </row>
-    <row r="328" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="328" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B328" s="10"/>
       <c r="C328" s="11"/>
       <c r="D328" s="10" t="str">
@@ -14100,7 +14316,7 @@
       <c r="R328" s="11"/>
       <c r="S328" s="10"/>
     </row>
-    <row r="329" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="329" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B329" s="10"/>
       <c r="C329" s="11"/>
       <c r="D329" s="10" t="str">
@@ -14121,7 +14337,7 @@
       <c r="R329" s="11"/>
       <c r="S329" s="10"/>
     </row>
-    <row r="330" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="330" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B330" s="10"/>
       <c r="C330" s="11"/>
       <c r="D330" s="10" t="str">
@@ -14142,7 +14358,7 @@
       <c r="R330" s="11"/>
       <c r="S330" s="10"/>
     </row>
-    <row r="331" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="331" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
       <c r="D331" s="10" t="str">
@@ -14163,7 +14379,7 @@
       <c r="R331" s="11"/>
       <c r="S331" s="10"/>
     </row>
-    <row r="332" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="332" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
@@ -14184,7 +14400,7 @@
       <c r="R332" s="11"/>
       <c r="S332" s="10"/>
     </row>
-    <row r="333" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="333" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B333" s="10"/>
       <c r="C333" s="11"/>
       <c r="D333" s="10" t="str">
@@ -14205,7 +14421,7 @@
       <c r="R333" s="11"/>
       <c r="S333" s="10"/>
     </row>
-    <row r="334" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="334" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B334" s="10"/>
       <c r="C334" s="11"/>
       <c r="D334" s="10" t="str">
@@ -14226,7 +14442,7 @@
       <c r="R334" s="11"/>
       <c r="S334" s="10"/>
     </row>
-    <row r="335" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="335" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B335" s="10"/>
       <c r="C335" s="11"/>
       <c r="D335" s="10" t="str">
@@ -14247,7 +14463,7 @@
       <c r="R335" s="11"/>
       <c r="S335" s="10"/>
     </row>
-    <row r="336" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="336" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B336" s="10"/>
       <c r="C336" s="11"/>
       <c r="D336" s="10" t="str">
@@ -14268,7 +14484,7 @@
       <c r="R336" s="11"/>
       <c r="S336" s="10"/>
     </row>
-    <row r="337" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="337" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B337" s="10"/>
       <c r="C337" s="11"/>
       <c r="D337" s="10" t="str">
@@ -14289,7 +14505,7 @@
       <c r="R337" s="11"/>
       <c r="S337" s="10"/>
     </row>
-    <row r="338" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="338" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B338" s="10"/>
       <c r="C338" s="11"/>
       <c r="D338" s="10" t="str">
@@ -14310,7 +14526,7 @@
       <c r="R338" s="11"/>
       <c r="S338" s="10"/>
     </row>
-    <row r="339" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="339" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B339" s="10"/>
       <c r="C339" s="11"/>
       <c r="D339" s="10" t="str">
@@ -14331,7 +14547,7 @@
       <c r="R339" s="11"/>
       <c r="S339" s="10"/>
     </row>
-    <row r="340" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="340" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B340" s="10"/>
       <c r="C340" s="11"/>
       <c r="D340" s="10" t="str">
@@ -14352,7 +14568,7 @@
       <c r="R340" s="11"/>
       <c r="S340" s="10"/>
     </row>
-    <row r="341" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="341" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B341" s="10"/>
       <c r="C341" s="11"/>
       <c r="D341" s="10" t="str">
@@ -14373,7 +14589,7 @@
       <c r="R341" s="11"/>
       <c r="S341" s="10"/>
     </row>
-    <row r="342" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="342" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B342" s="10"/>
       <c r="C342" s="11"/>
       <c r="D342" s="10" t="str">
@@ -14394,7 +14610,7 @@
       <c r="R342" s="11"/>
       <c r="S342" s="10"/>
     </row>
-    <row r="343" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="343" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B343" s="10"/>
       <c r="C343" s="11"/>
       <c r="D343" s="10" t="str">
@@ -14415,7 +14631,7 @@
       <c r="R343" s="11"/>
       <c r="S343" s="10"/>
     </row>
-    <row r="344" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="344" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B344" s="10"/>
       <c r="C344" s="11"/>
       <c r="D344" s="10" t="str">
@@ -14436,7 +14652,7 @@
       <c r="R344" s="11"/>
       <c r="S344" s="10"/>
     </row>
-    <row r="345" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="345" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B345" s="10"/>
       <c r="C345" s="11"/>
       <c r="D345" s="10" t="str">
@@ -14457,7 +14673,7 @@
       <c r="R345" s="11"/>
       <c r="S345" s="10"/>
     </row>
-    <row r="346" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="346" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B346" s="10"/>
       <c r="C346" s="11"/>
       <c r="D346" s="10" t="str">
@@ -14478,7 +14694,7 @@
       <c r="R346" s="11"/>
       <c r="S346" s="10"/>
     </row>
-    <row r="347" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="347" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B347" s="10"/>
       <c r="C347" s="11"/>
       <c r="D347" s="10" t="str">
@@ -14499,7 +14715,7 @@
       <c r="R347" s="11"/>
       <c r="S347" s="10"/>
     </row>
-    <row r="348" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="348" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B348" s="10"/>
       <c r="C348" s="11"/>
       <c r="D348" s="10" t="str">
@@ -14520,7 +14736,7 @@
       <c r="R348" s="11"/>
       <c r="S348" s="10"/>
     </row>
-    <row r="349" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="349" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B349" s="10"/>
       <c r="C349" s="11"/>
       <c r="D349" s="10" t="str">
@@ -14541,7 +14757,7 @@
       <c r="R349" s="11"/>
       <c r="S349" s="10"/>
     </row>
-    <row r="350" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="350" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B350" s="10"/>
       <c r="C350" s="11"/>
       <c r="D350" s="10" t="str">
@@ -14562,7 +14778,7 @@
       <c r="R350" s="11"/>
       <c r="S350" s="10"/>
     </row>
-    <row r="351" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="351" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B351" s="10"/>
       <c r="C351" s="11"/>
       <c r="D351" s="10" t="str">
@@ -14583,7 +14799,7 @@
       <c r="R351" s="11"/>
       <c r="S351" s="10"/>
     </row>
-    <row r="352" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="352" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B352" s="10"/>
       <c r="C352" s="11"/>
       <c r="D352" s="10" t="str">
@@ -14604,7 +14820,7 @@
       <c r="R352" s="11"/>
       <c r="S352" s="10"/>
     </row>
-    <row r="353" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="353" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B353" s="10"/>
       <c r="C353" s="11"/>
       <c r="D353" s="10" t="str">
@@ -14625,7 +14841,7 @@
       <c r="R353" s="11"/>
       <c r="S353" s="10"/>
     </row>
-    <row r="354" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="354" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B354" s="10"/>
       <c r="C354" s="11"/>
       <c r="D354" s="10" t="str">
@@ -14646,7 +14862,7 @@
       <c r="R354" s="11"/>
       <c r="S354" s="10"/>
     </row>
-    <row r="355" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="355" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B355" s="10"/>
       <c r="C355" s="11"/>
       <c r="D355" s="10" t="str">
@@ -14667,7 +14883,7 @@
       <c r="R355" s="11"/>
       <c r="S355" s="10"/>
     </row>
-    <row r="356" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="356" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B356" s="10"/>
       <c r="C356" s="11"/>
       <c r="D356" s="10" t="str">
@@ -14688,7 +14904,7 @@
       <c r="R356" s="11"/>
       <c r="S356" s="10"/>
     </row>
-    <row r="357" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="357" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B357" s="10"/>
       <c r="C357" s="11"/>
       <c r="D357" s="10" t="str">
@@ -14709,7 +14925,7 @@
       <c r="R357" s="11"/>
       <c r="S357" s="10"/>
     </row>
-    <row r="358" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="358" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B358" s="10"/>
       <c r="C358" s="11"/>
       <c r="D358" s="10" t="str">
@@ -14730,7 +14946,7 @@
       <c r="R358" s="11"/>
       <c r="S358" s="10"/>
     </row>
-    <row r="359" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="359" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B359" s="10"/>
       <c r="C359" s="11"/>
       <c r="D359" s="10" t="str">
@@ -14751,7 +14967,7 @@
       <c r="R359" s="11"/>
       <c r="S359" s="10"/>
     </row>
-    <row r="360" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="360" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B360" s="10"/>
       <c r="C360" s="11"/>
       <c r="D360" s="10" t="str">
@@ -14772,7 +14988,7 @@
       <c r="R360" s="11"/>
       <c r="S360" s="10"/>
     </row>
-    <row r="361" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="361" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B361" s="10"/>
       <c r="C361" s="11"/>
       <c r="D361" s="10" t="str">
@@ -14793,7 +15009,7 @@
       <c r="R361" s="11"/>
       <c r="S361" s="10"/>
     </row>
-    <row r="362" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="362" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B362" s="10"/>
       <c r="C362" s="11"/>
       <c r="D362" s="10" t="str">
@@ -14814,7 +15030,7 @@
       <c r="R362" s="11"/>
       <c r="S362" s="10"/>
     </row>
-    <row r="363" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="363" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B363" s="10"/>
       <c r="C363" s="11"/>
       <c r="D363" s="10" t="str">
@@ -14835,7 +15051,7 @@
       <c r="R363" s="11"/>
       <c r="S363" s="10"/>
     </row>
-    <row r="364" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="364" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B364" s="10"/>
       <c r="C364" s="11"/>
       <c r="D364" s="10" t="str">
@@ -14856,7 +15072,7 @@
       <c r="R364" s="11"/>
       <c r="S364" s="10"/>
     </row>
-    <row r="365" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="365" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B365" s="10"/>
       <c r="C365" s="11"/>
       <c r="D365" s="10" t="str">
@@ -14877,7 +15093,7 @@
       <c r="R365" s="11"/>
       <c r="S365" s="10"/>
     </row>
-    <row r="366" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="366" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B366" s="10"/>
       <c r="C366" s="11"/>
       <c r="D366" s="10" t="str">
@@ -14898,7 +15114,7 @@
       <c r="R366" s="11"/>
       <c r="S366" s="10"/>
     </row>
-    <row r="367" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="367" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B367" s="10"/>
       <c r="C367" s="11"/>
       <c r="D367" s="10" t="str">
@@ -14919,7 +15135,7 @@
       <c r="R367" s="11"/>
       <c r="S367" s="10"/>
     </row>
-    <row r="368" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="368" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B368" s="10"/>
       <c r="C368" s="11"/>
       <c r="D368" s="10" t="str">
@@ -14940,7 +15156,7 @@
       <c r="R368" s="11"/>
       <c r="S368" s="10"/>
     </row>
-    <row r="369" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="369" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B369" s="10"/>
       <c r="C369" s="11"/>
       <c r="D369" s="10" t="str">
@@ -14961,7 +15177,7 @@
       <c r="R369" s="11"/>
       <c r="S369" s="10"/>
     </row>
-    <row r="370" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="370" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B370" s="10"/>
       <c r="C370" s="11"/>
       <c r="D370" s="10" t="str">
@@ -14982,7 +15198,7 @@
       <c r="R370" s="11"/>
       <c r="S370" s="10"/>
     </row>
-    <row r="371" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="371" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B371" s="10"/>
       <c r="C371" s="11"/>
       <c r="D371" s="10" t="str">
@@ -15003,7 +15219,7 @@
       <c r="R371" s="11"/>
       <c r="S371" s="10"/>
     </row>
-    <row r="372" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="372" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B372" s="10"/>
       <c r="C372" s="11"/>
       <c r="D372" s="10" t="str">
@@ -15024,7 +15240,7 @@
       <c r="R372" s="11"/>
       <c r="S372" s="10"/>
     </row>
-    <row r="373" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="373" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B373" s="10"/>
       <c r="C373" s="11"/>
       <c r="D373" s="10" t="str">
@@ -15045,7 +15261,7 @@
       <c r="R373" s="11"/>
       <c r="S373" s="10"/>
     </row>
-    <row r="374" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="374" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B374" s="10"/>
       <c r="C374" s="11"/>
       <c r="D374" s="10" t="str">
@@ -15066,7 +15282,7 @@
       <c r="R374" s="11"/>
       <c r="S374" s="10"/>
     </row>
-    <row r="375" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="375" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B375" s="10"/>
       <c r="C375" s="11"/>
       <c r="D375" s="10" t="str">
@@ -15087,7 +15303,7 @@
       <c r="R375" s="11"/>
       <c r="S375" s="10"/>
     </row>
-    <row r="376" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="376" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B376" s="10"/>
       <c r="C376" s="11"/>
       <c r="D376" s="10" t="str">
@@ -15108,7 +15324,7 @@
       <c r="R376" s="11"/>
       <c r="S376" s="10"/>
     </row>
-    <row r="377" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="377" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B377" s="10"/>
       <c r="C377" s="11"/>
       <c r="D377" s="10" t="str">
@@ -15129,7 +15345,7 @@
       <c r="R377" s="11"/>
       <c r="S377" s="10"/>
     </row>
-    <row r="378" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="378" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B378" s="10"/>
       <c r="C378" s="11"/>
       <c r="D378" s="10" t="str">
@@ -15150,7 +15366,7 @@
       <c r="R378" s="11"/>
       <c r="S378" s="10"/>
     </row>
-    <row r="379" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="379" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B379" s="10"/>
       <c r="C379" s="11"/>
       <c r="D379" s="10" t="str">
@@ -15171,7 +15387,7 @@
       <c r="R379" s="11"/>
       <c r="S379" s="10"/>
     </row>
-    <row r="380" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="380" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B380" s="10"/>
       <c r="C380" s="11"/>
       <c r="D380" s="10" t="str">
@@ -15192,7 +15408,7 @@
       <c r="R380" s="11"/>
       <c r="S380" s="10"/>
     </row>
-    <row r="381" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="381" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B381" s="10"/>
       <c r="C381" s="11"/>
       <c r="D381" s="10" t="str">
@@ -15213,7 +15429,7 @@
       <c r="R381" s="11"/>
       <c r="S381" s="10"/>
     </row>
-    <row r="382" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="382" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B382" s="10"/>
       <c r="C382" s="11"/>
       <c r="D382" s="10" t="str">
@@ -15234,7 +15450,7 @@
       <c r="R382" s="11"/>
       <c r="S382" s="10"/>
     </row>
-    <row r="383" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="383" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B383" s="10"/>
       <c r="C383" s="11"/>
       <c r="D383" s="10" t="str">
@@ -15255,7 +15471,7 @@
       <c r="R383" s="11"/>
       <c r="S383" s="10"/>
     </row>
-    <row r="384" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="384" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B384" s="10"/>
       <c r="C384" s="11"/>
       <c r="D384" s="10" t="str">
@@ -15276,7 +15492,7 @@
       <c r="R384" s="11"/>
       <c r="S384" s="10"/>
     </row>
-    <row r="385" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="385" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B385" s="10"/>
       <c r="C385" s="11"/>
       <c r="D385" s="10" t="str">
@@ -15297,7 +15513,7 @@
       <c r="R385" s="11"/>
       <c r="S385" s="10"/>
     </row>
-    <row r="386" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="386" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B386" s="10"/>
       <c r="C386" s="11"/>
       <c r="D386" s="10" t="str">
@@ -15318,7 +15534,7 @@
       <c r="R386" s="11"/>
       <c r="S386" s="10"/>
     </row>
-    <row r="387" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="387" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B387" s="10"/>
       <c r="C387" s="11"/>
       <c r="D387" s="10" t="str">
@@ -15339,7 +15555,7 @@
       <c r="R387" s="11"/>
       <c r="S387" s="10"/>
     </row>
-    <row r="388" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="388" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B388" s="10"/>
       <c r="C388" s="11"/>
       <c r="D388" s="10" t="str">
@@ -15360,7 +15576,7 @@
       <c r="R388" s="11"/>
       <c r="S388" s="10"/>
     </row>
-    <row r="389" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="389" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B389" s="10"/>
       <c r="C389" s="11"/>
       <c r="D389" s="10" t="str">
@@ -15381,7 +15597,7 @@
       <c r="R389" s="11"/>
       <c r="S389" s="10"/>
     </row>
-    <row r="390" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="390" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B390" s="10"/>
       <c r="C390" s="11"/>
       <c r="D390" s="10" t="str">
@@ -15402,7 +15618,7 @@
       <c r="R390" s="11"/>
       <c r="S390" s="10"/>
     </row>
-    <row r="391" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="391" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B391" s="10"/>
       <c r="C391" s="11"/>
       <c r="D391" s="10" t="str">
@@ -15423,7 +15639,7 @@
       <c r="R391" s="11"/>
       <c r="S391" s="10"/>
     </row>
-    <row r="392" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="392" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B392" s="10"/>
       <c r="C392" s="11"/>
       <c r="D392" s="10" t="str">
@@ -15444,7 +15660,7 @@
       <c r="R392" s="11"/>
       <c r="S392" s="10"/>
     </row>
-    <row r="393" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="393" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B393" s="10"/>
       <c r="C393" s="11"/>
       <c r="D393" s="10" t="str">
@@ -15465,7 +15681,7 @@
       <c r="R393" s="11"/>
       <c r="S393" s="10"/>
     </row>
-    <row r="394" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="394" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B394" s="10"/>
       <c r="C394" s="11"/>
       <c r="D394" s="10" t="str">
@@ -15486,7 +15702,7 @@
       <c r="R394" s="11"/>
       <c r="S394" s="10"/>
     </row>
-    <row r="395" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="395" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
       <c r="D395" s="10" t="str">
@@ -15507,7 +15723,7 @@
       <c r="R395" s="11"/>
       <c r="S395" s="10"/>
     </row>
-    <row r="396" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="396" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
@@ -15528,7 +15744,7 @@
       <c r="R396" s="11"/>
       <c r="S396" s="10"/>
     </row>
-    <row r="397" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="397" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B397" s="10"/>
       <c r="C397" s="11"/>
       <c r="D397" s="10" t="str">
@@ -15549,7 +15765,7 @@
       <c r="R397" s="11"/>
       <c r="S397" s="10"/>
     </row>
-    <row r="398" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="398" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B398" s="10"/>
       <c r="C398" s="11"/>
       <c r="D398" s="10" t="str">
@@ -15570,7 +15786,7 @@
       <c r="R398" s="11"/>
       <c r="S398" s="10"/>
     </row>
-    <row r="399" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="399" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B399" s="10"/>
       <c r="C399" s="11"/>
       <c r="D399" s="10" t="str">
@@ -15591,7 +15807,7 @@
       <c r="R399" s="11"/>
       <c r="S399" s="10"/>
     </row>
-    <row r="400" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="400" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B400" s="10"/>
       <c r="C400" s="11"/>
       <c r="D400" s="10" t="str">
@@ -15612,7 +15828,7 @@
       <c r="R400" s="11"/>
       <c r="S400" s="10"/>
     </row>
-    <row r="401" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="401" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B401" s="10"/>
       <c r="C401" s="11"/>
       <c r="D401" s="10" t="str">
@@ -15633,7 +15849,7 @@
       <c r="R401" s="11"/>
       <c r="S401" s="10"/>
     </row>
-    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
       <c r="D402" s="10" t="str">
@@ -15654,7 +15870,7 @@
       <c r="R402" s="11"/>
       <c r="S402" s="10"/>
     </row>
-    <row r="403" spans="2:19" hidden="1">
+    <row r="403" spans="2:19">
       <c r="B403" s="10"/>
       <c r="C403" s="11"/>
       <c r="D403" s="1" t="str">
@@ -15670,7 +15886,7 @@
       <c r="Q403" s="11"/>
       <c r="R403" s="11"/>
     </row>
-    <row r="404" spans="2:19" hidden="1">
+    <row r="404" spans="2:19">
       <c r="B404" s="10"/>
       <c r="C404" s="11"/>
       <c r="D404" s="1" t="str">
@@ -15686,7 +15902,7 @@
       <c r="Q404" s="11"/>
       <c r="R404" s="11"/>
     </row>
-    <row r="405" spans="2:19" hidden="1">
+    <row r="405" spans="2:19">
       <c r="B405" s="10"/>
       <c r="C405" s="11"/>
       <c r="D405" s="1" t="str">
@@ -15700,7 +15916,7 @@
       <c r="Q405" s="11"/>
       <c r="R405" s="11"/>
     </row>
-    <row r="406" spans="2:19" hidden="1">
+    <row r="406" spans="2:19">
       <c r="B406" s="10"/>
       <c r="C406" s="11"/>
       <c r="D406" s="1" t="str">
@@ -15714,7 +15930,7 @@
       <c r="Q406" s="11"/>
       <c r="R406" s="11"/>
     </row>
-    <row r="407" spans="2:19" hidden="1">
+    <row r="407" spans="2:19">
       <c r="B407" s="10"/>
       <c r="C407" s="11"/>
       <c r="D407" s="1" t="str">
@@ -15724,7 +15940,7 @@
       <c r="Q407" s="11"/>
       <c r="R407" s="11"/>
     </row>
-    <row r="408" spans="2:19" hidden="1">
+    <row r="408" spans="2:19">
       <c r="B408" s="10"/>
       <c r="C408" s="11"/>
       <c r="D408" s="1" t="str">
@@ -15739,224 +15955,238 @@
       <c r="F409" s="62"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S408">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="(주)다수건설"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="43" priority="56">
+    <cfRule type="expression" dxfId="45" priority="60">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="42" priority="55">
+    <cfRule type="expression" dxfId="44" priority="59">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="41" priority="54">
+    <cfRule type="expression" dxfId="43" priority="58">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="40" priority="53">
+    <cfRule type="expression" dxfId="42" priority="57">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="39" priority="48">
+    <cfRule type="expression" dxfId="41" priority="52">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="38" priority="38">
+    <cfRule type="expression" dxfId="40" priority="42">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="37" priority="37">
+    <cfRule type="expression" dxfId="39" priority="41">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="36" priority="35">
+    <cfRule type="expression" dxfId="38" priority="39">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="35" priority="34">
+    <cfRule type="expression" dxfId="37" priority="38">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="34" priority="33">
+    <cfRule type="expression" dxfId="36" priority="37">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="33" priority="32">
+    <cfRule type="expression" dxfId="35" priority="36">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="32" priority="31">
+    <cfRule type="expression" dxfId="34" priority="35">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="31" priority="30">
+    <cfRule type="expression" dxfId="33" priority="34">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="30" priority="29">
+    <cfRule type="expression" dxfId="32" priority="33">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="29" priority="28">
+    <cfRule type="expression" dxfId="31" priority="32">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="28" priority="27">
+    <cfRule type="expression" dxfId="30" priority="31">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="27" priority="26">
+    <cfRule type="expression" dxfId="29" priority="30">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="26" priority="25">
+    <cfRule type="expression" dxfId="28" priority="29">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="25" priority="24">
+    <cfRule type="expression" dxfId="27" priority="28">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="24" priority="23">
+    <cfRule type="expression" dxfId="26" priority="27">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="23" priority="22">
+    <cfRule type="expression" dxfId="25" priority="26">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="22" priority="21">
+    <cfRule type="expression" dxfId="24" priority="25">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="21" priority="20">
+    <cfRule type="expression" dxfId="23" priority="24">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="20" priority="19">
+    <cfRule type="expression" dxfId="22" priority="23">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="19" priority="17">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="17" priority="15">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="16" priority="14">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="16" priority="16">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="15" priority="15">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="12" priority="10">
+    <cfRule type="expression" dxfId="14" priority="14">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="13" priority="13">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
-    <cfRule type="expression" dxfId="10" priority="8">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179:F185">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E178">
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E179:E185">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="9" priority="9">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166:C178">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="6" priority="6">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H179:H185">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>$J179="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F186:F193">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$J186="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E186:E193">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$J186="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H186:H193">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J186="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C186:C193">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J179="잔금"</formula>
+      <formula>$J186="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N185">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N193">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D408">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1604,22 +1604,7 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="46">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <fill>
         <patternFill>
@@ -2702,7 +2687,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2827,7 +2812,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2925,7 +2910,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2981,7 +2966,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3030,7 +3015,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3081,7 +3066,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3133,7 +3118,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3272,7 +3257,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3328,7 +3313,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3377,7 +3362,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3426,7 +3411,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3473,7 +3458,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3520,7 +3505,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3567,7 +3552,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3614,7 +3599,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3661,7 +3646,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3710,7 +3695,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3759,7 +3744,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3808,7 +3793,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3857,7 +3842,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3906,7 +3891,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3955,7 +3940,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4004,7 +3989,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4053,7 +4038,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4102,7 +4087,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4151,7 +4136,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4200,7 +4185,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4249,7 +4234,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4298,7 +4283,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4347,7 +4332,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4396,7 +4381,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4441,7 +4426,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4495,7 +4480,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4551,7 +4536,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4604,7 +4589,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4651,7 +4636,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4705,7 +4690,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4810,7 +4795,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4959,7 +4944,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5006,7 +4991,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5439,7 +5424,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5486,7 +5471,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5533,7 +5518,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5580,7 +5565,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -5871,7 +5856,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5915,7 +5900,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6200,7 +6185,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6345,7 +6330,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6583,7 +6568,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6669,7 +6654,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6775,7 +6760,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6827,7 +6812,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6869,7 +6854,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6965,7 +6950,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7017,7 +7002,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7113,11 +7098,11 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K92" s="11"/>
       <c r="L92" s="11"/>
@@ -7287,7 +7272,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7373,7 +7358,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7415,7 +7400,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7456,7 +7441,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7629,7 +7614,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7671,7 +7656,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7712,7 +7697,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7799,7 +7784,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7840,11 +7825,11 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K109" s="11"/>
       <c r="L109" s="11"/>
@@ -7881,7 +7866,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7970,7 +7955,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8059,7 +8044,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8104,7 +8089,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
@@ -8201,7 +8186,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8287,7 +8272,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8420,7 +8405,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8462,7 +8447,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8504,7 +8489,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8546,7 +8531,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8623,7 +8608,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8665,7 +8650,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8707,7 +8692,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8749,7 +8734,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8923,7 +8908,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8965,7 +8950,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9007,7 +8992,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9089,11 +9074,11 @@
         <v>237</v>
       </c>
       <c r="H138" s="59">
-        <v>10474600</v>
+        <v>11171400</v>
       </c>
       <c r="I138" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J138" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9223,7 +9208,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9264,7 +9249,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9305,7 +9290,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9346,7 +9331,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9387,7 +9372,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9428,7 +9413,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9469,7 +9454,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9510,7 +9495,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9551,7 +9536,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9592,7 +9577,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9676,7 +9661,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9760,7 +9745,7 @@
       </c>
       <c r="I154" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J154" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9801,7 +9786,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9842,7 +9827,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9883,7 +9868,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9932,7 +9917,9 @@
         <v>정상</v>
       </c>
       <c r="K158" s="11"/>
-      <c r="L158" s="11"/>
+      <c r="L158" s="11">
+        <v>46094</v>
+      </c>
       <c r="M158" s="10"/>
       <c r="N158" s="10" t="s">
         <v>33</v>
@@ -9967,7 +9954,7 @@
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10009,7 +9996,7 @@
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J160" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10051,7 +10038,7 @@
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J161" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10143,7 +10130,9 @@
         <v>정상</v>
       </c>
       <c r="K163" s="11"/>
-      <c r="L163" s="11"/>
+      <c r="L163" s="11">
+        <v>46094</v>
+      </c>
       <c r="M163" s="10"/>
       <c r="N163" s="10" t="s">
         <v>33</v>
@@ -10185,7 +10174,9 @@
         <v>정상</v>
       </c>
       <c r="K164" s="11"/>
-      <c r="L164" s="11"/>
+      <c r="L164" s="11">
+        <v>46094</v>
+      </c>
       <c r="M164" s="10"/>
       <c r="N164" s="10" t="s">
         <v>33</v>
@@ -10219,7 +10210,7 @@
       </c>
       <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J165" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10261,7 +10252,7 @@
       </c>
       <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J166" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10303,7 +10294,7 @@
       </c>
       <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J167" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10396,7 +10387,9 @@
         <v>정상</v>
       </c>
       <c r="K169" s="11"/>
-      <c r="L169" s="11"/>
+      <c r="L169" s="11">
+        <v>46094</v>
+      </c>
       <c r="M169" s="10"/>
       <c r="N169" s="10" t="s">
         <v>33</v>
@@ -10431,7 +10424,7 @@
       </c>
       <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J170" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10473,7 +10466,7 @@
       </c>
       <c r="I171" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J171" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10515,7 +10508,7 @@
       </c>
       <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J172" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10557,7 +10550,7 @@
       </c>
       <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J173" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10599,7 +10592,7 @@
       </c>
       <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J174" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10641,7 +10634,7 @@
       </c>
       <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J175" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10727,7 +10720,7 @@
       </c>
       <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J177" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10813,7 +10806,7 @@
       </c>
       <c r="I179" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J179" s="13" t="str">
         <f t="shared" ref="J179:J193" ca="1" si="14">IF(I179="","",
@@ -10863,7 +10856,7 @@
       </c>
       <c r="I180" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J180" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10905,7 +10898,7 @@
       </c>
       <c r="I181" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J181" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10947,7 +10940,7 @@
       </c>
       <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J182" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10989,7 +10982,7 @@
       </c>
       <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J183" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11031,7 +11024,7 @@
       </c>
       <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J184" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11073,7 +11066,7 @@
       </c>
       <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J185" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11159,7 +11152,7 @@
       </c>
       <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J187" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11201,7 +11194,7 @@
       </c>
       <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J188" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11243,7 +11236,7 @@
       </c>
       <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J189" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11285,7 +11278,7 @@
       </c>
       <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J190" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11327,7 +11320,7 @@
       </c>
       <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J191" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11369,7 +11362,7 @@
       </c>
       <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J192" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11411,7 +11404,7 @@
       </c>
       <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J193" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -15958,207 +15951,207 @@
   <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="45" priority="60">
+    <cfRule type="expression" dxfId="44" priority="60">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="44" priority="59">
+    <cfRule type="expression" dxfId="43" priority="59">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="43" priority="58">
+    <cfRule type="expression" dxfId="42" priority="58">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="42" priority="57">
+    <cfRule type="expression" dxfId="41" priority="57">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="41" priority="52">
+    <cfRule type="expression" dxfId="40" priority="52">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="40" priority="42">
+    <cfRule type="expression" dxfId="39" priority="42">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="39" priority="41">
+    <cfRule type="expression" dxfId="38" priority="41">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="38" priority="39">
+    <cfRule type="expression" dxfId="37" priority="39">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="37" priority="38">
+    <cfRule type="expression" dxfId="36" priority="38">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="36" priority="37">
+    <cfRule type="expression" dxfId="35" priority="37">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="35" priority="36">
+    <cfRule type="expression" dxfId="34" priority="36">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="34" priority="35">
+    <cfRule type="expression" dxfId="33" priority="35">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="33" priority="34">
+    <cfRule type="expression" dxfId="32" priority="34">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="32" priority="33">
+    <cfRule type="expression" dxfId="31" priority="33">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="31" priority="32">
+    <cfRule type="expression" dxfId="30" priority="32">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="30" priority="31">
+    <cfRule type="expression" dxfId="29" priority="31">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="29" priority="30">
+    <cfRule type="expression" dxfId="28" priority="30">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="28" priority="29">
+    <cfRule type="expression" dxfId="27" priority="29">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="27" priority="28">
+    <cfRule type="expression" dxfId="26" priority="28">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="26" priority="27">
+    <cfRule type="expression" dxfId="25" priority="27">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="25" priority="26">
+    <cfRule type="expression" dxfId="24" priority="26">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="24" priority="25">
+    <cfRule type="expression" dxfId="23" priority="25">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="22" priority="24">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="22" priority="23">
+    <cfRule type="expression" dxfId="21" priority="23">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="19" priority="20">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="19" priority="19">
+    <cfRule type="expression" dxfId="18" priority="19">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="17" priority="18">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="16" priority="17">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="16" priority="16">
+    <cfRule type="expression" dxfId="15" priority="16">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="15" priority="15">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="12" priority="13">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179:F185">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E178">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E179:E185">
-    <cfRule type="expression" dxfId="9" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166:C178">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H179:H185">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9204,7 +9204,7 @@
         <v>243</v>
       </c>
       <c r="H141" s="60">
-        <v>20124400</v>
+        <v>30186600</v>
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="335">
   <si>
     <t>순번</t>
   </si>
@@ -1144,6 +1144,58 @@
   </si>
   <si>
     <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘케이개발㈜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>신당삼성아파트</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특허료</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁전빌라파트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠실리센츠에폭시</t>
+  </si>
+  <si>
+    <t>잠실리센츠</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>용현금호어울림4단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>수원로얄팰리스</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현마을경남아너스빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>기흥우방아이유쉘</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>미래산업개발</t>
+  </si>
+  <si>
+    <t>(주)두영이앤씨</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
   </si>
   <si>
     <t>자재</t>
@@ -1604,7 +1656,67 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="49">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -10809,7 +10921,7 @@
         <v>5</v>
       </c>
       <c r="J179" s="13" t="str">
-        <f t="shared" ref="J179:J193" ca="1" si="14">IF(I179="","",
+        <f t="shared" ref="J179:J201" ca="1" si="14">IF(I179="","",
  IF(G179="선급금",
    IF(I179&lt;=20,"정상",IF(I179&lt;=90,"관리","장기미수")),
  IF(G179="자재",
@@ -11421,193 +11533,337 @@
       <c r="S193" s="10"/>
     </row>
     <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B194" s="10" t="str">
+      <c r="B194" s="10">
         <f>IF(C194="","",COUNTA($C$2:C194))</f>
-        <v/>
-      </c>
-      <c r="C194" s="11"/>
+        <v>193</v>
+      </c>
+      <c r="C194" s="11">
+        <v>46094</v>
+      </c>
       <c r="D194" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H194" s="4"/>
-      <c r="I194" s="6" t="str">
+        <v>C</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G194" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="H194" s="4">
+        <v>1291250</v>
+      </c>
+      <c r="I194" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J194" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J194" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K194" s="11"/>
       <c r="L194" s="11"/>
       <c r="M194" s="10"/>
-      <c r="N194" s="10"/>
+      <c r="N194" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q194" s="11"/>
       <c r="R194" s="11"/>
       <c r="S194" s="10"/>
     </row>
     <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B195" s="10" t="str">
+      <c r="B195" s="10">
         <f>IF(C195="","",COUNTA($C$2:C195))</f>
-        <v/>
-      </c>
-      <c r="C195" s="11"/>
+        <v>194</v>
+      </c>
+      <c r="C195" s="35" t="s">
+        <v>333</v>
+      </c>
       <c r="D195" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H195" s="4"/>
-      <c r="I195" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E195" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="F195" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="G195" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H195" s="25">
+        <v>500500</v>
+      </c>
+      <c r="I195" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J195" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J195" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K195" s="11"/>
       <c r="L195" s="11"/>
       <c r="M195" s="10"/>
-      <c r="N195" s="10"/>
+      <c r="N195" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q195" s="11"/>
       <c r="R195" s="11"/>
       <c r="S195" s="10"/>
     </row>
     <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B196" s="10" t="str">
+      <c r="B196" s="10">
         <f>IF(C196="","",COUNTA($C$2:C196))</f>
-        <v/>
-      </c>
-      <c r="C196" s="11"/>
+        <v>195</v>
+      </c>
+      <c r="C196" s="35" t="s">
+        <v>333</v>
+      </c>
       <c r="D196" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H196" s="4"/>
-      <c r="I196" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E196" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F196" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="G196" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H196" s="25">
+        <v>3448000</v>
+      </c>
+      <c r="I196" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J196" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J196" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K196" s="11"/>
       <c r="L196" s="11"/>
       <c r="M196" s="10"/>
-      <c r="N196" s="10"/>
+      <c r="N196" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q196" s="11"/>
       <c r="R196" s="11"/>
       <c r="S196" s="10"/>
     </row>
     <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B197" s="10" t="str">
+      <c r="B197" s="10">
         <f>IF(C197="","",COUNTA($C$2:C197))</f>
-        <v/>
-      </c>
-      <c r="C197" s="11"/>
+        <v>196</v>
+      </c>
+      <c r="C197" s="35" t="s">
+        <v>333</v>
+      </c>
       <c r="D197" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H197" s="4"/>
-      <c r="I197" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E197" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F197" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="G197" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H197" s="25">
+        <v>28750000</v>
+      </c>
+      <c r="I197" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J197" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J197" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K197" s="11"/>
       <c r="L197" s="11"/>
       <c r="M197" s="10"/>
-      <c r="N197" s="10"/>
+      <c r="N197" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q197" s="11"/>
       <c r="R197" s="11"/>
       <c r="S197" s="10"/>
     </row>
     <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B198" s="10" t="str">
+      <c r="B198" s="10">
         <f>IF(C198="","",COUNTA($C$2:C198))</f>
-        <v/>
-      </c>
-      <c r="C198" s="11"/>
+        <v>197</v>
+      </c>
+      <c r="C198" s="35" t="s">
+        <v>333</v>
+      </c>
       <c r="D198" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H198" s="4"/>
-      <c r="I198" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E198" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="F198" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="G198" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H198" s="25">
+        <v>3430000</v>
+      </c>
+      <c r="I198" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J198" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J198" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K198" s="11"/>
       <c r="L198" s="11"/>
       <c r="M198" s="10"/>
-      <c r="N198" s="10"/>
+      <c r="N198" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q198" s="11"/>
       <c r="R198" s="11"/>
       <c r="S198" s="10"/>
     </row>
     <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B199" s="10" t="str">
+      <c r="B199" s="10">
         <f>IF(C199="","",COUNTA($C$2:C199))</f>
-        <v/>
-      </c>
-      <c r="C199" s="11"/>
+        <v>198</v>
+      </c>
+      <c r="C199" s="35" t="s">
+        <v>333</v>
+      </c>
       <c r="D199" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H199" s="4"/>
-      <c r="I199" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E199" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F199" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="G199" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H199" s="25">
+        <v>14700000</v>
+      </c>
+      <c r="I199" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J199" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J199" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K199" s="11"/>
       <c r="L199" s="11"/>
       <c r="M199" s="10"/>
-      <c r="N199" s="10"/>
+      <c r="N199" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q199" s="11"/>
       <c r="R199" s="11"/>
       <c r="S199" s="10"/>
     </row>
     <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B200" s="10" t="str">
+      <c r="B200" s="10">
         <f>IF(C200="","",COUNTA($C$2:C200))</f>
-        <v/>
-      </c>
-      <c r="C200" s="11"/>
+        <v>199</v>
+      </c>
+      <c r="C200" s="35" t="s">
+        <v>333</v>
+      </c>
       <c r="D200" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H200" s="4"/>
-      <c r="I200" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E200" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="F200" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="G200" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H200" s="25">
+        <v>780000</v>
+      </c>
+      <c r="I200" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J200" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J200" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K200" s="11"/>
       <c r="L200" s="11"/>
       <c r="M200" s="10"/>
-      <c r="N200" s="10"/>
+      <c r="N200" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q200" s="11"/>
       <c r="R200" s="11"/>
       <c r="S200" s="10"/>
     </row>
     <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B201" s="10" t="str">
+      <c r="B201" s="10">
         <f>IF(C201="","",COUNTA($C$2:C201))</f>
-        <v/>
-      </c>
-      <c r="C201" s="11"/>
+        <v>200</v>
+      </c>
+      <c r="C201" s="35" t="s">
+        <v>333</v>
+      </c>
       <c r="D201" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H201" s="4"/>
-      <c r="I201" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E201" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F201" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="G201" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H201" s="25">
+        <v>220100</v>
+      </c>
+      <c r="I201" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J201" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J201" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K201" s="11"/>
       <c r="L201" s="11"/>
       <c r="M201" s="10"/>
-      <c r="N201" s="10"/>
+      <c r="N201" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q201" s="11"/>
       <c r="R201" s="11"/>
       <c r="S201" s="10"/>
@@ -15951,235 +16207,255 @@
   <autoFilter ref="A1:S408"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="44" priority="60">
+    <cfRule type="expression" dxfId="48" priority="64">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="43" priority="59">
+    <cfRule type="expression" dxfId="47" priority="63">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="42" priority="58">
+    <cfRule type="expression" dxfId="46" priority="62">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="41" priority="57">
+    <cfRule type="expression" dxfId="45" priority="61">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="40" priority="52">
+    <cfRule type="expression" dxfId="44" priority="56">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="39" priority="42">
+    <cfRule type="expression" dxfId="43" priority="46">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="38" priority="41">
+    <cfRule type="expression" dxfId="42" priority="45">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="37" priority="39">
+    <cfRule type="expression" dxfId="41" priority="43">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="36" priority="38">
+    <cfRule type="expression" dxfId="40" priority="42">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="35" priority="37">
+    <cfRule type="expression" dxfId="39" priority="41">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="34" priority="36">
+    <cfRule type="expression" dxfId="38" priority="40">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="33" priority="35">
+    <cfRule type="expression" dxfId="37" priority="39">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="32" priority="34">
+    <cfRule type="expression" dxfId="36" priority="38">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="31" priority="33">
+    <cfRule type="expression" dxfId="35" priority="37">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
+    <cfRule type="expression" dxfId="34" priority="36">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F111 F113">
+    <cfRule type="expression" dxfId="33" priority="35">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F112">
+    <cfRule type="expression" dxfId="32" priority="34">
+      <formula>$J112="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H111:H113">
+    <cfRule type="expression" dxfId="31" priority="33">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C111:C113">
     <cfRule type="expression" dxfId="30" priority="32">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F111 F113">
+  <conditionalFormatting sqref="E117">
     <cfRule type="expression" dxfId="29" priority="31">
-      <formula>$J111="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="28" priority="30">
-      <formula>$J112="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="27" priority="29">
-      <formula>$J111="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="26" priority="28">
-      <formula>$J111="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="25" priority="27">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="24" priority="26">
+    <cfRule type="expression" dxfId="28" priority="30">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="23" priority="25">
+    <cfRule type="expression" dxfId="27" priority="29">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="22" priority="24">
+    <cfRule type="expression" dxfId="26" priority="28">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="21" priority="23">
+    <cfRule type="expression" dxfId="25" priority="27">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="20" priority="21">
+    <cfRule type="expression" dxfId="24" priority="25">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="23" priority="24">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="22" priority="23">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="21" priority="22">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="19" priority="20">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="18" priority="19">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="17" priority="18">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="16" priority="17">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>$J166="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F179:F185">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>$J179="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E166:E178">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>$J166="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E179:E185">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>$J179="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C166:C178">
     <cfRule type="expression" dxfId="11" priority="12">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F179:F185">
+  <conditionalFormatting sqref="C179:C185">
     <cfRule type="expression" dxfId="10" priority="11">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E166:E178">
+  <conditionalFormatting sqref="H166:H178">
     <cfRule type="expression" dxfId="9" priority="10">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E179:E185">
+  <conditionalFormatting sqref="H179:H185">
     <cfRule type="expression" dxfId="8" priority="9">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C166:C178">
+  <conditionalFormatting sqref="F186:F193">
     <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$J166="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>$J179="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>$J166="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H179:H185">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>$J179="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F186:F193">
-    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$J186="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E186:E193">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$J186="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H186:H193">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$J186="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C186:C193">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$J186="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F195:F201">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$J195="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E195:E201">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$J195="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C195:C201">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J195="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H195:H201">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J186="잔금"</formula>
+      <formula>$J195="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N193">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N201">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D408">

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,15 +11,15 @@
     <sheet name="프로세스현황" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$408</definedName>
-    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$408</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$407</definedName>
+    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$407</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="334">
   <si>
     <t>순번</t>
   </si>
@@ -1128,10 +1128,6 @@
   </si>
   <si>
     <t>광양금광1차</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>궁전빌라파트</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
@@ -1656,67 +1652,7 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="49">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <fill>
         <patternFill>
@@ -2690,7 +2626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S409"/>
+  <dimension ref="A1:S408"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
@@ -9259,7 +9195,7 @@
         <v>46086</v>
       </c>
       <c r="D140" s="10" t="str">
-        <f t="shared" ref="D140:D203" si="12">IF(G140="","",IF(OR(G140="선급금",G140="중도금",G140="잔금"),"A",IF(G140="자재","B",IF(G140="특허료","C",""))))</f>
+        <f t="shared" ref="D140:D202" si="12">IF(G140="","",IF(OR(G140="선급금",G140="중도금",G140="잔금"),"A",IF(G140="자재","B",IF(G140="특허료","C",""))))</f>
         <v>A</v>
       </c>
       <c r="E140" s="57" t="s">
@@ -9275,7 +9211,7 @@
         <v>19544000</v>
       </c>
       <c r="I140" s="6">
-        <f t="shared" ref="I140:I203" ca="1" si="13">IF(C140="","",IF(L140="",TODAY()-C140,L140-C140))</f>
+        <f t="shared" ref="I140:I202" ca="1" si="13">IF(C140="","",IF(L140="",TODAY()-C140,L140-C140))</f>
         <v>4</v>
       </c>
       <c r="J140" s="13" t="str">
@@ -10921,7 +10857,7 @@
         <v>5</v>
       </c>
       <c r="J179" s="13" t="str">
-        <f t="shared" ref="J179:J201" ca="1" si="14">IF(I179="","",
+        <f t="shared" ref="J179:J200" ca="1" si="14">IF(I179="","",
  IF(G179="선급금",
    IF(I179&lt;=20,"정상",IF(I179&lt;=90,"관리","장기미수")),
  IF(G179="자재",
@@ -11213,7 +11149,7 @@
         <v>311</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H186" s="25">
         <v>312000</v>
@@ -11244,23 +11180,23 @@
         <v>186</v>
       </c>
       <c r="C187" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D187" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E187" s="23" t="s">
-        <v>283</v>
+        <v>30</v>
       </c>
       <c r="F187" s="23" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G187" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H187" s="25">
-        <v>500500</v>
+        <v>1000500</v>
       </c>
       <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11286,23 +11222,23 @@
         <v>187</v>
       </c>
       <c r="C188" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D188" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>30</v>
+        <v>203</v>
       </c>
       <c r="F188" s="23" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H188" s="25">
-        <v>1000500</v>
+        <v>5775000</v>
       </c>
       <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11328,23 +11264,23 @@
         <v>188</v>
       </c>
       <c r="C189" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D189" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F189" s="23" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H189" s="25">
-        <v>5775000</v>
+        <v>1190000</v>
       </c>
       <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11370,23 +11306,23 @@
         <v>189</v>
       </c>
       <c r="C190" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D190" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="F190" s="23" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H190" s="25">
-        <v>1190000</v>
+        <v>11147800</v>
       </c>
       <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11412,23 +11348,23 @@
         <v>190</v>
       </c>
       <c r="C191" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D191" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="F191" s="23" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G191" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H191" s="25">
-        <v>11147800</v>
+        <v>2613000</v>
       </c>
       <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11454,23 +11390,23 @@
         <v>191</v>
       </c>
       <c r="C192" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D192" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>227</v>
+        <v>112</v>
       </c>
       <c r="F192" s="23" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H192" s="25">
-        <v>2613000</v>
+        <v>7339000</v>
       </c>
       <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11495,28 +11431,28 @@
         <f>IF(C193="","",COUNTA($C$2:C193))</f>
         <v>192</v>
       </c>
-      <c r="C193" s="35" t="s">
-        <v>319</v>
+      <c r="C193" s="11">
+        <v>46094</v>
       </c>
       <c r="D193" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>B</v>
-      </c>
-      <c r="E193" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="F193" s="23" t="s">
-        <v>315</v>
+        <v>C</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>321</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="H193" s="25">
-        <v>7339000</v>
+        <v>322</v>
+      </c>
+      <c r="H193" s="4">
+        <v>1291250</v>
       </c>
       <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J193" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11537,24 +11473,24 @@
         <f>IF(C194="","",COUNTA($C$2:C194))</f>
         <v>193</v>
       </c>
-      <c r="C194" s="11">
-        <v>46094</v>
+      <c r="C194" s="35" t="s">
+        <v>332</v>
       </c>
       <c r="D194" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>C</v>
-      </c>
-      <c r="E194" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="F194" s="6" t="s">
-        <v>322</v>
+        <v>B</v>
+      </c>
+      <c r="E194" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="F194" s="23" t="s">
+        <v>323</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H194" s="4">
-        <v>1291250</v>
+        <v>333</v>
+      </c>
+      <c r="H194" s="25">
+        <v>500500</v>
       </c>
       <c r="I194" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11580,23 +11516,23 @@
         <v>194</v>
       </c>
       <c r="C195" s="35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D195" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>331</v>
+        <v>24</v>
       </c>
       <c r="F195" s="23" t="s">
         <v>324</v>
       </c>
       <c r="G195" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H195" s="25">
-        <v>500500</v>
+        <v>3448000</v>
       </c>
       <c r="I195" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11622,7 +11558,7 @@
         <v>195</v>
       </c>
       <c r="C196" s="35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D196" s="10" t="str">
         <f t="shared" si="12"/>
@@ -11635,10 +11571,10 @@
         <v>325</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H196" s="25">
-        <v>3448000</v>
+        <v>28750000</v>
       </c>
       <c r="I196" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11664,23 +11600,23 @@
         <v>196</v>
       </c>
       <c r="C197" s="35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D197" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>24</v>
+        <v>229</v>
       </c>
       <c r="F197" s="23" t="s">
         <v>326</v>
       </c>
       <c r="G197" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H197" s="25">
-        <v>28750000</v>
+        <v>3430000</v>
       </c>
       <c r="I197" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11706,23 +11642,23 @@
         <v>197</v>
       </c>
       <c r="C198" s="35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D198" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F198" s="23" t="s">
         <v>327</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H198" s="25">
-        <v>3430000</v>
+        <v>14700000</v>
       </c>
       <c r="I198" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11748,23 +11684,23 @@
         <v>198</v>
       </c>
       <c r="C199" s="35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D199" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>227</v>
+        <v>331</v>
       </c>
       <c r="F199" s="23" t="s">
         <v>328</v>
       </c>
       <c r="G199" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H199" s="25">
-        <v>14700000</v>
+        <v>780000</v>
       </c>
       <c r="I199" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11790,23 +11726,23 @@
         <v>199</v>
       </c>
       <c r="C200" s="35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D200" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>332</v>
+        <v>39</v>
       </c>
       <c r="F200" s="23" t="s">
         <v>329</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H200" s="25">
-        <v>780000</v>
+        <v>220100</v>
       </c>
       <c r="I200" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11827,43 +11763,25 @@
       <c r="S200" s="10"/>
     </row>
     <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B201" s="10">
+      <c r="B201" s="10" t="str">
         <f>IF(C201="","",COUNTA($C$2:C201))</f>
-        <v>200</v>
-      </c>
-      <c r="C201" s="35" t="s">
-        <v>333</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C201" s="11"/>
       <c r="D201" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>B</v>
-      </c>
-      <c r="E201" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="F201" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="G201" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="H201" s="25">
-        <v>220100</v>
-      </c>
-      <c r="I201" s="6">
+        <v/>
+      </c>
+      <c r="H201" s="4"/>
+      <c r="I201" s="6" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="J201" s="13" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v>정상</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J201" s="13"/>
       <c r="K201" s="11"/>
       <c r="L201" s="11"/>
       <c r="M201" s="10"/>
-      <c r="N201" s="10" t="s">
-        <v>33</v>
-      </c>
+      <c r="N201" s="10"/>
       <c r="Q201" s="11"/>
       <c r="R201" s="11"/>
       <c r="S201" s="10"/>
@@ -11899,12 +11817,12 @@
       </c>
       <c r="C203" s="11"/>
       <c r="D203" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D203:D266" si="15">IF(G203="","",IF(OR(G203="선급금",G203="중도금",G203="잔금"),"A",IF(G203="자재","B",IF(G203="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H203" s="4"/>
       <c r="I203" s="6" t="str">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" ref="I203:I266" ca="1" si="16">IF(C203="","",IF(L203="",TODAY()-C203,L203-C203))</f>
         <v/>
       </c>
       <c r="J203" s="13"/>
@@ -11923,12 +11841,12 @@
       </c>
       <c r="C204" s="11"/>
       <c r="D204" s="10" t="str">
-        <f t="shared" ref="D204:D267" si="15">IF(G204="","",IF(OR(G204="선급금",G204="중도금",G204="잔금"),"A",IF(G204="자재","B",IF(G204="특허료","C",""))))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" s="6" t="str">
-        <f t="shared" ref="I204:I267" ca="1" si="16">IF(C204="","",IF(L204="",TODAY()-C204,L204-C204))</f>
+        <f t="shared" ca="1" si="16"/>
         <v/>
       </c>
       <c r="J204" s="13"/>
@@ -12085,10 +12003,7 @@
       <c r="S210" s="10"/>
     </row>
     <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B211" s="10" t="str">
-        <f>IF(C211="","",COUNTA($C$2:C211))</f>
-        <v/>
-      </c>
+      <c r="B211" s="10"/>
       <c r="C211" s="11"/>
       <c r="D211" s="10" t="str">
         <f t="shared" si="15"/>
@@ -13267,12 +13182,12 @@
       <c r="B267" s="10"/>
       <c r="C267" s="11"/>
       <c r="D267" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="D267:D330" si="17">IF(G267="","",IF(OR(G267="선급금",G267="중도금",G267="잔금"),"A",IF(G267="자재","B",IF(G267="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H267" s="4"/>
       <c r="I267" s="6" t="str">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ref="I267:I330" ca="1" si="18">IF(C267="","",IF(L267="",TODAY()-C267,L267-C267))</f>
         <v/>
       </c>
       <c r="J267" s="13"/>
@@ -13288,12 +13203,12 @@
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
       <c r="D268" s="10" t="str">
-        <f t="shared" ref="D268:D331" si="17">IF(G268="","",IF(OR(G268="선급금",G268="중도금",G268="잔금"),"A",IF(G268="자재","B",IF(G268="특허료","C",""))))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" s="6" t="str">
-        <f t="shared" ref="I268:I331" ca="1" si="18">IF(C268="","",IF(L268="",TODAY()-C268,L268-C268))</f>
+        <f t="shared" ca="1" si="18"/>
         <v/>
       </c>
       <c r="J268" s="13"/>
@@ -14611,12 +14526,12 @@
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
       <c r="D331" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="D331:D394" si="19">IF(G331="","",IF(OR(G331="선급금",G331="중도금",G331="잔금"),"A",IF(G331="자재","B",IF(G331="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H331" s="4"/>
       <c r="I331" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ref="I331:I394" ca="1" si="20">IF(C331="","",IF(L331="",TODAY()-C331,L331-C331))</f>
         <v/>
       </c>
       <c r="J331" s="13"/>
@@ -14632,12 +14547,12 @@
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
-        <f t="shared" ref="D332:D395" si="19">IF(G332="","",IF(OR(G332="선급금",G332="중도금",G332="잔금"),"A",IF(G332="자재","B",IF(G332="특허료","C",""))))</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="6" t="str">
-        <f t="shared" ref="I332:I395" ca="1" si="20">IF(C332="","",IF(L332="",TODAY()-C332,L332-C332))</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
       <c r="J332" s="13"/>
@@ -15955,12 +15870,12 @@
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
       <c r="D395" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="D395:D407" si="21">IF(G395="","",IF(OR(G395="선급금",G395="중도금",G395="잔금"),"A",IF(G395="자재","B",IF(G395="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H395" s="4"/>
       <c r="I395" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ref="I395:I405" ca="1" si="22">IF(C395="","",IF(L395="",TODAY()-C395,L395-C395))</f>
         <v/>
       </c>
       <c r="J395" s="13"/>
@@ -15976,12 +15891,12 @@
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
-        <f t="shared" ref="D396:D408" si="21">IF(G396="","",IF(OR(G396="선급금",G396="중도금",G396="잔금"),"A",IF(G396="자재","B",IF(G396="특허료","C",""))))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="H396" s="4"/>
       <c r="I396" s="6" t="str">
-        <f t="shared" ref="I396:I406" ca="1" si="22">IF(C396="","",IF(L396="",TODAY()-C396,L396-C396))</f>
+        <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
       <c r="J396" s="13"/>
@@ -16098,26 +16013,21 @@
       <c r="R401" s="11"/>
       <c r="S401" s="10"/>
     </row>
-    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="402" spans="2:19">
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
-      <c r="D402" s="10" t="str">
+      <c r="D402" s="1" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="H402" s="4"/>
-      <c r="I402" s="6" t="str">
+      <c r="I402" s="1" t="str">
         <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
-      <c r="J402" s="13"/>
       <c r="K402" s="11"/>
       <c r="L402" s="11"/>
-      <c r="M402" s="10"/>
-      <c r="N402" s="10"/>
       <c r="Q402" s="11"/>
       <c r="R402" s="11"/>
-      <c r="S402" s="10"/>
     </row>
     <row r="403" spans="2:19">
       <c r="B403" s="10"/>
@@ -16146,8 +16056,6 @@
         <f t="shared" ca="1" si="22"/>
         <v/>
       </c>
-      <c r="K404" s="11"/>
-      <c r="L404" s="11"/>
       <c r="Q404" s="11"/>
       <c r="R404" s="11"/>
     </row>
@@ -16172,10 +16080,6 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="I406" s="1" t="str">
-        <f t="shared" ca="1" si="22"/>
-        <v/>
-      </c>
       <c r="Q406" s="11"/>
       <c r="R406" s="11"/>
     </row>
@@ -16189,276 +16093,246 @@
       <c r="Q407" s="11"/>
       <c r="R407" s="11"/>
     </row>
-    <row r="408" spans="2:19">
-      <c r="B408" s="10"/>
-      <c r="C408" s="11"/>
-      <c r="D408" s="1" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Q408" s="11"/>
-      <c r="R408" s="11"/>
-    </row>
-    <row r="409" spans="2:19" ht="16.5" customHeight="1">
-      <c r="C409" s="58"/>
-      <c r="F409" s="62"/>
+    <row r="408" spans="2:19" ht="16.5" customHeight="1">
+      <c r="C408" s="58"/>
+      <c r="F408" s="62"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S408"/>
+  <autoFilter ref="A1:S407"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="48" priority="64">
+    <cfRule type="expression" dxfId="44" priority="64">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="47" priority="63">
+    <cfRule type="expression" dxfId="43" priority="63">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="46" priority="62">
+    <cfRule type="expression" dxfId="42" priority="62">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="45" priority="61">
+    <cfRule type="expression" dxfId="41" priority="61">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="44" priority="56">
+    <cfRule type="expression" dxfId="40" priority="56">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E98:E99">
-    <cfRule type="expression" dxfId="43" priority="46">
+  <conditionalFormatting sqref="E98:E99 E186:F192 H186:H192 C186:C192">
+    <cfRule type="expression" dxfId="39" priority="46">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="42" priority="45">
+    <cfRule type="expression" dxfId="38" priority="45">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="41" priority="43">
+    <cfRule type="expression" dxfId="37" priority="43">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="40" priority="42">
+    <cfRule type="expression" dxfId="36" priority="42">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="39" priority="41">
+    <cfRule type="expression" dxfId="35" priority="41">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="38" priority="40">
+    <cfRule type="expression" dxfId="34" priority="40">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="37" priority="39">
+    <cfRule type="expression" dxfId="33" priority="39">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="36" priority="38">
+    <cfRule type="expression" dxfId="32" priority="38">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="35" priority="37">
+    <cfRule type="expression" dxfId="31" priority="37">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="34" priority="36">
+    <cfRule type="expression" dxfId="30" priority="36">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="33" priority="35">
+    <cfRule type="expression" dxfId="29" priority="35">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="32" priority="34">
+    <cfRule type="expression" dxfId="28" priority="34">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="31" priority="33">
+    <cfRule type="expression" dxfId="27" priority="33">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="30" priority="32">
+    <cfRule type="expression" dxfId="26" priority="32">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="29" priority="31">
+    <cfRule type="expression" dxfId="25" priority="31">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="28" priority="30">
+    <cfRule type="expression" dxfId="24" priority="30">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="27" priority="29">
+    <cfRule type="expression" dxfId="23" priority="29">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="26" priority="28">
+    <cfRule type="expression" dxfId="22" priority="28">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="25" priority="27">
+    <cfRule type="expression" dxfId="21" priority="27">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="24" priority="25">
+    <cfRule type="expression" dxfId="20" priority="25">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="19" priority="24">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="22" priority="23">
+    <cfRule type="expression" dxfId="18" priority="23">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="17" priority="22">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="20" priority="21">
+    <cfRule type="expression" dxfId="16" priority="21">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="15" priority="20">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="14" priority="19">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="13" priority="18">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="12" priority="17">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="11" priority="16">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179:F185">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="10" priority="15">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E178">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="9" priority="14">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E179:E185">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166:C178">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="5" priority="10">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H179:H185">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F186:F193">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$J186="잔금"</formula>
+  <conditionalFormatting sqref="F194:F200">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E186:E193">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>$J186="잔금"</formula>
+  <conditionalFormatting sqref="E194:E200">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H186:H193">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>$J186="잔금"</formula>
+  <conditionalFormatting sqref="C194:C200">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C186:C193">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>$J186="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F195:F201">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$J195="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E195:E201">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>$J195="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C195:C201">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$J195="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H195:H201">
+  <conditionalFormatting sqref="H194:H200">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J195="잔금"</formula>
+      <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N201">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N200">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D408">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D407">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2735,7 +2735,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2860,7 +2860,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -5904,7 +5904,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
@@ -8234,7 +8234,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="I124" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J124" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="I138" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J138" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="I154" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J154" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J160" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J161" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J165" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J166" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J167" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J170" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="I171" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J171" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J172" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J173" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J174" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J175" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J177" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I179" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J179" s="13" t="str">
         <f t="shared" ref="J179:J200" ca="1" si="14">IF(I179="","",
@@ -10904,7 +10904,7 @@
       </c>
       <c r="I180" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J180" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="I181" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J181" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J182" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J183" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J184" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J185" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J187" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J188" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J189" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J190" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J191" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J192" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J193" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="I194" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J194" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="I195" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J195" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="I196" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J196" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11627,7 +11627,9 @@
         <v>정상</v>
       </c>
       <c r="K197" s="11"/>
-      <c r="L197" s="11"/>
+      <c r="L197" s="11">
+        <v>46097</v>
+      </c>
       <c r="M197" s="10"/>
       <c r="N197" s="10" t="s">
         <v>33</v>
@@ -11662,7 +11664,7 @@
       </c>
       <c r="I198" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J198" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11704,7 +11706,7 @@
       </c>
       <c r="I199" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J199" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11746,7 +11748,7 @@
       </c>
       <c r="I200" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J200" s="13" t="str">
         <f t="shared" ca="1" si="14"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9793,14 +9793,16 @@
       </c>
       <c r="I154" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J154" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K154" s="11"/>
-      <c r="L154" s="11"/>
+      <c r="L154" s="11">
+        <v>46097</v>
+      </c>
       <c r="M154" s="10"/>
       <c r="N154" s="10" t="s">
         <v>33</v>
@@ -10514,14 +10516,16 @@
       </c>
       <c r="I171" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J171" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K171" s="11"/>
-      <c r="L171" s="11"/>
+      <c r="L171" s="11">
+        <v>46097</v>
+      </c>
       <c r="M171" s="10"/>
       <c r="N171" s="10" t="s">
         <v>33</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="352">
   <si>
     <t>순번</t>
   </si>
@@ -1192,6 +1192,76 @@
   </si>
   <si>
     <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>색채산업개발㈜</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>토당금강KCC</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>중도금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>하계극동건영벽산</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>시흥참이슬아파트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>동탄더레이크팰리스</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>문촌마을10단지동부</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>평택비전지웰푸르지오</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>동탄역시범리슈빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>민락엘레트19아파트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼호한아름2차</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>철원산호그린빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>헬리오시티</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>무동센텀파라디아</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>가천대역두산위브</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)스타건설</t>
   </si>
   <si>
     <t>자재</t>
@@ -1450,7 +1520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1631,6 +1701,7 @@
     <xf numFmtId="14" fontId="13" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="18">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
@@ -1652,7 +1723,67 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="49">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2735,7 +2866,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2860,7 +2991,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -2958,7 +3089,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3014,7 +3145,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3063,7 +3194,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3114,7 +3245,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3166,7 +3297,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3305,7 +3436,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3361,7 +3492,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3410,7 +3541,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3459,7 +3590,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3506,7 +3637,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3553,7 +3684,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3600,7 +3731,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3647,7 +3778,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3694,7 +3825,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3743,7 +3874,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3792,7 +3923,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3841,7 +3972,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3890,7 +4021,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3939,7 +4070,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3988,7 +4119,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4037,7 +4168,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4086,7 +4217,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4135,7 +4266,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4184,7 +4315,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4233,7 +4364,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4282,7 +4413,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4331,7 +4462,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4380,7 +4511,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4429,7 +4560,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4474,7 +4605,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4528,7 +4659,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4584,7 +4715,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4637,7 +4768,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4684,7 +4815,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4738,7 +4869,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4843,7 +4974,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4992,7 +5123,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5039,7 +5170,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5472,7 +5603,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5519,7 +5650,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5566,7 +5697,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5613,7 +5744,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -5904,7 +6035,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -5948,7 +6079,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6233,7 +6364,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6378,7 +6509,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6616,7 +6747,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6702,7 +6833,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6808,7 +6939,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6860,7 +6991,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6902,7 +7033,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6998,7 +7129,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7050,7 +7181,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7146,7 +7277,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7320,7 +7451,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7406,7 +7537,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7448,7 +7579,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7489,7 +7620,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7662,7 +7793,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7704,7 +7835,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7745,7 +7876,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7832,7 +7963,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7873,7 +8004,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7914,7 +8045,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8003,7 +8134,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8092,7 +8223,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8137,7 +8268,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
@@ -8234,7 +8365,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8320,7 +8451,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8453,7 +8584,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8495,7 +8626,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8544,7 +8675,9 @@
         <v>정상</v>
       </c>
       <c r="K124" s="11"/>
-      <c r="L124" s="11"/>
+      <c r="L124" s="11">
+        <v>46098</v>
+      </c>
       <c r="M124" s="10"/>
       <c r="N124" s="10" t="s">
         <v>33</v>
@@ -8579,7 +8712,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8656,7 +8789,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8698,7 +8831,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8740,7 +8873,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8782,7 +8915,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8956,7 +9089,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8998,7 +9131,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9040,7 +9173,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9133,7 +9266,9 @@
         <v>정상</v>
       </c>
       <c r="K138" s="11"/>
-      <c r="L138" s="11"/>
+      <c r="L138" s="11">
+        <v>46098</v>
+      </c>
       <c r="M138" s="10"/>
       <c r="N138" s="10" t="s">
         <v>33</v>
@@ -9256,7 +9391,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9297,7 +9432,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9338,7 +9473,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9379,7 +9514,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9420,7 +9555,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9461,7 +9596,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9502,7 +9637,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9543,7 +9678,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9584,7 +9719,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9625,7 +9760,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9709,7 +9844,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9836,7 +9971,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9877,7 +10012,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9918,7 +10053,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10004,7 +10139,7 @@
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10046,7 +10181,7 @@
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J160" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10088,7 +10223,7 @@
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J161" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10260,7 +10395,7 @@
       </c>
       <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J165" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10302,7 +10437,7 @@
       </c>
       <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J166" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10344,7 +10479,7 @@
       </c>
       <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J167" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10474,7 +10609,7 @@
       </c>
       <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J170" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10560,7 +10695,7 @@
       </c>
       <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J172" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10602,7 +10737,7 @@
       </c>
       <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J173" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10644,7 +10779,7 @@
       </c>
       <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J174" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10686,7 +10821,7 @@
       </c>
       <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J175" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10772,7 +10907,7 @@
       </c>
       <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J177" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10858,10 +10993,10 @@
       </c>
       <c r="I179" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J179" s="13" t="str">
-        <f t="shared" ref="J179:J200" ca="1" si="14">IF(I179="","",
+        <f t="shared" ref="J179:J215" ca="1" si="14">IF(I179="","",
  IF(G179="선급금",
    IF(I179&lt;=20,"정상",IF(I179&lt;=90,"관리","장기미수")),
  IF(G179="자재",
@@ -10908,7 +11043,7 @@
       </c>
       <c r="I180" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J180" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10950,7 +11085,7 @@
       </c>
       <c r="I181" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J181" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -10992,7 +11127,7 @@
       </c>
       <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J182" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11034,7 +11169,7 @@
       </c>
       <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J183" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11076,7 +11211,7 @@
       </c>
       <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J184" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11118,7 +11253,7 @@
       </c>
       <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J185" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11204,7 +11339,7 @@
       </c>
       <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J187" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11246,7 +11381,7 @@
       </c>
       <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J188" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11288,7 +11423,7 @@
       </c>
       <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J189" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11330,7 +11465,7 @@
       </c>
       <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J190" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11372,7 +11507,7 @@
       </c>
       <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J191" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11414,7 +11549,7 @@
       </c>
       <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J192" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11456,7 +11591,7 @@
       </c>
       <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J193" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11498,7 +11633,7 @@
       </c>
       <c r="I194" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J194" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11540,7 +11675,7 @@
       </c>
       <c r="I195" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J195" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11582,7 +11717,7 @@
       </c>
       <c r="I196" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J196" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11668,7 +11803,7 @@
       </c>
       <c r="I198" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J198" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11710,7 +11845,7 @@
       </c>
       <c r="I199" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J199" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11752,7 +11887,7 @@
       </c>
       <c r="I200" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J200" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11769,346 +11904,631 @@
       <c r="S200" s="10"/>
     </row>
     <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B201" s="10" t="str">
+      <c r="B201" s="10">
         <f>IF(C201="","",COUNTA($C$2:C201))</f>
-        <v/>
-      </c>
-      <c r="C201" s="11"/>
+        <v>200</v>
+      </c>
+      <c r="C201" s="35">
+        <v>46097</v>
+      </c>
       <c r="D201" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H201" s="4"/>
-      <c r="I201" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F201" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G201" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H201" s="4">
+        <v>22342800</v>
+      </c>
+      <c r="I201" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J201" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J201" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K201" s="11"/>
       <c r="L201" s="11"/>
       <c r="M201" s="10"/>
-      <c r="N201" s="10"/>
+      <c r="N201" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q201" s="11"/>
       <c r="R201" s="11"/>
       <c r="S201" s="10"/>
     </row>
     <row r="202" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B202" s="10" t="str">
+      <c r="B202" s="10">
         <f>IF(C202="","",COUNTA($C$2:C202))</f>
-        <v/>
-      </c>
-      <c r="C202" s="11"/>
+        <v>201</v>
+      </c>
+      <c r="C202" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D202" s="10" t="str">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="H202" s="4"/>
-      <c r="I202" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E202" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F202" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="G202" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H202" s="25">
+        <v>19467400</v>
+      </c>
+      <c r="I202" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="J202" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J202" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K202" s="11"/>
       <c r="L202" s="11"/>
       <c r="M202" s="10"/>
-      <c r="N202" s="10"/>
+      <c r="N202" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q202" s="11"/>
       <c r="R202" s="11"/>
       <c r="S202" s="10"/>
     </row>
     <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B203" s="10" t="str">
+      <c r="B203" s="10">
         <f>IF(C203="","",COUNTA($C$2:C203))</f>
-        <v/>
-      </c>
-      <c r="C203" s="11"/>
+        <v>202</v>
+      </c>
+      <c r="C203" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D203" s="10" t="str">
         <f t="shared" ref="D203:D266" si="15">IF(G203="","",IF(OR(G203="선급금",G203="중도금",G203="잔금"),"A",IF(G203="자재","B",IF(G203="특허료","C",""))))</f>
-        <v/>
-      </c>
-      <c r="H203" s="4"/>
-      <c r="I203" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E203" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F203" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="G203" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H203" s="25">
+        <v>4765000</v>
+      </c>
+      <c r="I203" s="6">
         <f t="shared" ref="I203:I266" ca="1" si="16">IF(C203="","",IF(L203="",TODAY()-C203,L203-C203))</f>
-        <v/>
-      </c>
-      <c r="J203" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J203" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K203" s="11"/>
       <c r="L203" s="11"/>
       <c r="M203" s="10"/>
-      <c r="N203" s="10"/>
+      <c r="N203" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q203" s="11"/>
       <c r="R203" s="11"/>
       <c r="S203" s="10"/>
     </row>
     <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B204" s="10" t="str">
+      <c r="B204" s="10">
         <f>IF(C204="","",COUNTA($C$2:C204))</f>
-        <v/>
-      </c>
-      <c r="C204" s="11"/>
+        <v>203</v>
+      </c>
+      <c r="C204" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D204" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H204" s="4"/>
-      <c r="I204" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E204" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="F204" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="G204" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H204" s="25">
+        <v>954500</v>
+      </c>
+      <c r="I204" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J204" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J204" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K204" s="11"/>
       <c r="L204" s="11"/>
       <c r="M204" s="10"/>
-      <c r="N204" s="10"/>
+      <c r="N204" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q204" s="11"/>
       <c r="R204" s="11"/>
       <c r="S204" s="10"/>
     </row>
     <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B205" s="10" t="str">
+      <c r="B205" s="10">
         <f>IF(C205="","",COUNTA($C$2:C205))</f>
-        <v/>
-      </c>
-      <c r="C205" s="11"/>
+        <v>204</v>
+      </c>
+      <c r="C205" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D205" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H205" s="4"/>
-      <c r="I205" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E205" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F205" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="G205" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H205" s="25">
+        <v>9631000</v>
+      </c>
+      <c r="I205" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J205" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J205" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K205" s="11"/>
       <c r="L205" s="11"/>
       <c r="M205" s="10"/>
-      <c r="N205" s="10"/>
+      <c r="N205" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q205" s="11"/>
       <c r="R205" s="11"/>
       <c r="S205" s="10"/>
     </row>
     <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B206" s="10" t="str">
+      <c r="B206" s="10">
         <f>IF(C206="","",COUNTA($C$2:C206))</f>
-        <v/>
-      </c>
-      <c r="C206" s="11"/>
+        <v>205</v>
+      </c>
+      <c r="C206" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D206" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H206" s="4"/>
-      <c r="I206" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E206" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F206" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="G206" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H206" s="25">
+        <v>1745000</v>
+      </c>
+      <c r="I206" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J206" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J206" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K206" s="11"/>
       <c r="L206" s="11"/>
       <c r="M206" s="10"/>
-      <c r="N206" s="10"/>
+      <c r="N206" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q206" s="11"/>
       <c r="R206" s="11"/>
       <c r="S206" s="10"/>
     </row>
     <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B207" s="10" t="str">
+      <c r="B207" s="10">
         <f>IF(C207="","",COUNTA($C$2:C207))</f>
-        <v/>
-      </c>
-      <c r="C207" s="11"/>
+        <v>206</v>
+      </c>
+      <c r="C207" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D207" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H207" s="4"/>
-      <c r="I207" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E207" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F207" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="G207" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H207" s="25">
+        <v>493400</v>
+      </c>
+      <c r="I207" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J207" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J207" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K207" s="11"/>
       <c r="L207" s="11"/>
       <c r="M207" s="10"/>
-      <c r="N207" s="10"/>
+      <c r="N207" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q207" s="11"/>
       <c r="R207" s="11"/>
       <c r="S207" s="10"/>
     </row>
     <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B208" s="10" t="str">
+      <c r="B208" s="10">
         <f>IF(C208="","",COUNTA($C$2:C208))</f>
-        <v/>
-      </c>
-      <c r="C208" s="11"/>
+        <v>207</v>
+      </c>
+      <c r="C208" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D208" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H208" s="4"/>
-      <c r="I208" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E208" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F208" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="G208" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H208" s="25">
+        <v>3568200</v>
+      </c>
+      <c r="I208" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J208" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J208" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K208" s="11"/>
       <c r="L208" s="11"/>
       <c r="M208" s="10"/>
-      <c r="N208" s="10"/>
+      <c r="N208" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q208" s="11"/>
       <c r="R208" s="11"/>
       <c r="S208" s="10"/>
     </row>
     <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B209" s="10" t="str">
+      <c r="B209" s="10">
         <f>IF(C209="","",COUNTA($C$2:C209))</f>
-        <v/>
-      </c>
-      <c r="C209" s="11"/>
+        <v>208</v>
+      </c>
+      <c r="C209" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D209" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H209" s="4"/>
-      <c r="I209" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E209" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F209" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="G209" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H209" s="25">
+        <v>4110300</v>
+      </c>
+      <c r="I209" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J209" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J209" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K209" s="11"/>
       <c r="L209" s="11"/>
       <c r="M209" s="10"/>
-      <c r="N209" s="10"/>
+      <c r="N209" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q209" s="11"/>
       <c r="R209" s="11"/>
       <c r="S209" s="10"/>
     </row>
     <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B210" s="10" t="str">
+      <c r="B210" s="10">
         <f>IF(C210="","",COUNTA($C$2:C210))</f>
-        <v/>
-      </c>
-      <c r="C210" s="11"/>
+        <v>209</v>
+      </c>
+      <c r="C210" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D210" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H210" s="4"/>
-      <c r="I210" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E210" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="F210" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="G210" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H210" s="25">
+        <v>1318600</v>
+      </c>
+      <c r="I210" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J210" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J210" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K210" s="11"/>
       <c r="L210" s="11"/>
       <c r="M210" s="10"/>
-      <c r="N210" s="10"/>
+      <c r="N210" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q210" s="11"/>
       <c r="R210" s="11"/>
       <c r="S210" s="10"/>
     </row>
     <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B211" s="10"/>
-      <c r="C211" s="11"/>
+      <c r="B211" s="10">
+        <f>IF(C211="","",COUNTA($C$2:C211))</f>
+        <v>210</v>
+      </c>
+      <c r="C211" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D211" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H211" s="4"/>
-      <c r="I211" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E211" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="F211" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="G211" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H211" s="25">
+        <v>3541500</v>
+      </c>
+      <c r="I211" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J211" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J211" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K211" s="11"/>
       <c r="L211" s="11"/>
       <c r="M211" s="10"/>
-      <c r="N211" s="10"/>
+      <c r="N211" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q211" s="11"/>
       <c r="R211" s="11"/>
       <c r="S211" s="10"/>
     </row>
     <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B212" s="10"/>
-      <c r="C212" s="11"/>
+      <c r="B212" s="10">
+        <f>IF(C212="","",COUNTA($C$2:C212))</f>
+        <v>211</v>
+      </c>
+      <c r="C212" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D212" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H212" s="4"/>
-      <c r="I212" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E212" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="F212" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="G212" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H212" s="25">
+        <v>3512300</v>
+      </c>
+      <c r="I212" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J212" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J212" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K212" s="11"/>
       <c r="L212" s="11"/>
       <c r="M212" s="10"/>
-      <c r="N212" s="10"/>
+      <c r="N212" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q212" s="11"/>
       <c r="R212" s="11"/>
       <c r="S212" s="10"/>
     </row>
     <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B213" s="10"/>
-      <c r="C213" s="11"/>
+      <c r="B213" s="10">
+        <f>IF(C213="","",COUNTA($C$2:C213))</f>
+        <v>212</v>
+      </c>
+      <c r="C213" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D213" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H213" s="4"/>
-      <c r="I213" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E213" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="F213" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="G213" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H213" s="25">
+        <v>11000000</v>
+      </c>
+      <c r="I213" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J213" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J213" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K213" s="11"/>
       <c r="L213" s="11"/>
       <c r="M213" s="10"/>
-      <c r="N213" s="10"/>
+      <c r="N213" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q213" s="11"/>
       <c r="R213" s="11"/>
       <c r="S213" s="10"/>
     </row>
     <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B214" s="10"/>
-      <c r="C214" s="11"/>
+      <c r="B214" s="10">
+        <f>IF(C214="","",COUNTA($C$2:C214))</f>
+        <v>213</v>
+      </c>
+      <c r="C214" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D214" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H214" s="4"/>
-      <c r="I214" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E214" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F214" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="G214" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H214" s="25">
+        <v>21000000</v>
+      </c>
+      <c r="I214" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J214" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J214" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K214" s="11"/>
       <c r="L214" s="11"/>
       <c r="M214" s="10"/>
-      <c r="N214" s="10"/>
+      <c r="N214" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q214" s="11"/>
       <c r="R214" s="11"/>
       <c r="S214" s="10"/>
     </row>
     <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B215" s="10"/>
-      <c r="C215" s="11"/>
+      <c r="B215" s="10">
+        <f>IF(C215="","",COUNTA($C$2:C215))</f>
+        <v>214</v>
+      </c>
+      <c r="C215" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="D215" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H215" s="4"/>
-      <c r="I215" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E215" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F215" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="G215" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H215" s="25">
+        <v>806000</v>
+      </c>
+      <c r="I215" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J215" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J215" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K215" s="11"/>
       <c r="L215" s="11"/>
       <c r="M215" s="10"/>
-      <c r="N215" s="10"/>
+      <c r="N215" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q215" s="11"/>
       <c r="R215" s="11"/>
       <c r="S215" s="10"/>
@@ -12120,6 +12540,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
+      <c r="F216" s="64"/>
       <c r="H216" s="4"/>
       <c r="I216" s="6" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -16107,235 +16528,255 @@
   <autoFilter ref="A1:S407"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="44" priority="64">
+    <cfRule type="expression" dxfId="48" priority="68">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="43" priority="63">
+    <cfRule type="expression" dxfId="47" priority="67">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="42" priority="62">
+    <cfRule type="expression" dxfId="46" priority="66">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="41" priority="61">
+    <cfRule type="expression" dxfId="45" priority="65">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="40" priority="56">
+    <cfRule type="expression" dxfId="44" priority="60">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99 E186:F192 H186:H192 C186:C192">
-    <cfRule type="expression" dxfId="39" priority="46">
+    <cfRule type="expression" dxfId="43" priority="50">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="38" priority="45">
+    <cfRule type="expression" dxfId="42" priority="49">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="37" priority="43">
+    <cfRule type="expression" dxfId="41" priority="47">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="36" priority="42">
+    <cfRule type="expression" dxfId="40" priority="46">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="35" priority="41">
+    <cfRule type="expression" dxfId="39" priority="45">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="34" priority="40">
+    <cfRule type="expression" dxfId="38" priority="44">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="33" priority="39">
+    <cfRule type="expression" dxfId="37" priority="43">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="32" priority="38">
+    <cfRule type="expression" dxfId="36" priority="42">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="31" priority="37">
+    <cfRule type="expression" dxfId="35" priority="41">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
+    <cfRule type="expression" dxfId="34" priority="40">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F111 F113">
+    <cfRule type="expression" dxfId="33" priority="39">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F112">
+    <cfRule type="expression" dxfId="32" priority="38">
+      <formula>$J112="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H111:H113">
+    <cfRule type="expression" dxfId="31" priority="37">
+      <formula>$J111="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C111:C113">
     <cfRule type="expression" dxfId="30" priority="36">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F111 F113">
+  <conditionalFormatting sqref="E117">
     <cfRule type="expression" dxfId="29" priority="35">
-      <formula>$J111="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="28" priority="34">
-      <formula>$J112="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="27" priority="33">
-      <formula>$J111="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="26" priority="32">
-      <formula>$J111="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="25" priority="31">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="24" priority="30">
+    <cfRule type="expression" dxfId="28" priority="34">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="23" priority="29">
+    <cfRule type="expression" dxfId="27" priority="33">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="22" priority="28">
+    <cfRule type="expression" dxfId="26" priority="32">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="21" priority="27">
+    <cfRule type="expression" dxfId="25" priority="31">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="20" priority="25">
+    <cfRule type="expression" dxfId="24" priority="29">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="19" priority="24">
+    <cfRule type="expression" dxfId="23" priority="28">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="18" priority="23">
+    <cfRule type="expression" dxfId="22" priority="27">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="17" priority="22">
+    <cfRule type="expression" dxfId="21" priority="26">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="16" priority="21">
+    <cfRule type="expression" dxfId="20" priority="25">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="15" priority="20">
+    <cfRule type="expression" dxfId="19" priority="24">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="14" priority="19">
+    <cfRule type="expression" dxfId="18" priority="23">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="13" priority="18">
+    <cfRule type="expression" dxfId="17" priority="22">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="12" priority="17">
+    <cfRule type="expression" dxfId="16" priority="21">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
+    <cfRule type="expression" dxfId="15" priority="20">
+      <formula>$J166="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F179:F185">
+    <cfRule type="expression" dxfId="14" priority="19">
+      <formula>$J179="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E166:E178">
+    <cfRule type="expression" dxfId="13" priority="18">
+      <formula>$J166="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E179:E185">
+    <cfRule type="expression" dxfId="12" priority="17">
+      <formula>$J179="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C166:C178">
     <cfRule type="expression" dxfId="11" priority="16">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F179:F185">
+  <conditionalFormatting sqref="C179:C185">
     <cfRule type="expression" dxfId="10" priority="15">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E166:E178">
+  <conditionalFormatting sqref="H166:H178">
     <cfRule type="expression" dxfId="9" priority="14">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E179:E185">
+  <conditionalFormatting sqref="H179:H185">
     <cfRule type="expression" dxfId="8" priority="13">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C166:C178">
-    <cfRule type="expression" dxfId="7" priority="12">
-      <formula>$J166="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="6" priority="11">
-      <formula>$J179="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="5" priority="10">
-      <formula>$J166="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H179:H185">
-    <cfRule type="expression" dxfId="4" priority="9">
-      <formula>$J179="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F194:F200">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E194:E200">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C194:C200">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="C194:C201">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H194:H200">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$J194="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C202:C215">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$J202="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F202:F215">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$J202="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H202:H215">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J202="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E202:E215">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J194="잔금"</formula>
+      <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N200">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N215">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D407">

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="388">
   <si>
     <t>순번</t>
   </si>
@@ -1262,6 +1262,139 @@
   </si>
   <si>
     <t>(주)스타건설</t>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자양10차현대홈타운</t>
+  </si>
+  <si>
+    <t>여름건설(주)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선급금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>고척파크푸르지오</t>
+  </si>
+  <si>
+    <t>코오롱아파트</t>
+  </si>
+  <si>
+    <t>수림1차아파트</t>
+  </si>
+  <si>
+    <t>동현이앤씨㈜</t>
+  </si>
+  <si>
+    <t>주식회사 수림씨앤에스</t>
+  </si>
+  <si>
+    <t>오창2지구대원칸타빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>보령광명샤인빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>역전할머니맥주부산안락점</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>노형뜨란채</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>하계극동건영벽산</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>이편한세상태전2차</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표건설본사</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>민락동진로비치</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>불당파크푸르지오2단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울역센트럴자이</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>수원로얄팰리스</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>문수피오레</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>조치원자이</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>창원지하</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>가람마을10단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>염리상록아파트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>소촌대성베르힐써밋페인트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>소촌대성베르힐</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>공릉한보에센시티</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>불암현대</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼호한아름2차</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>중산11단지현대</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표건설(주)</t>
+  </si>
+  <si>
+    <t>(주)삼정엔지니어링</t>
+  </si>
+  <si>
+    <t>(주)정문씨앤씨</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
   </si>
   <si>
     <t>자재</t>
@@ -1520,7 +1653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1701,7 +1834,10 @@
     <xf numFmtId="14" fontId="13" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="18">
     <cellStyle name="Excel Built-in Comma [0]" xfId="8"/>
@@ -1723,7 +1859,307 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="49">
+  <dxfs count="69">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2866,7 +3302,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -2991,7 +3427,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3089,7 +3525,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3145,7 +3581,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3194,7 +3630,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3245,11 +3681,11 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>관리</v>
+        <v>장기미수</v>
       </c>
       <c r="K9" s="11">
         <v>46111</v>
@@ -3297,7 +3733,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3436,7 +3872,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3492,7 +3928,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3541,7 +3977,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3590,7 +4026,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3637,7 +4073,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3684,7 +4120,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3731,7 +4167,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3778,7 +4214,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3825,7 +4261,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3874,7 +4310,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3923,7 +4359,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3972,7 +4408,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4021,7 +4457,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4070,7 +4506,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4119,7 +4555,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4168,7 +4604,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4217,7 +4653,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4266,7 +4702,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4315,7 +4751,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4364,7 +4800,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4413,7 +4849,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4462,7 +4898,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4511,7 +4947,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4560,7 +4996,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4605,7 +5041,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4659,7 +5095,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4715,7 +5151,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4768,7 +5204,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4815,7 +5251,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4869,7 +5305,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4974,7 +5410,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5123,7 +5559,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5170,7 +5606,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5603,7 +6039,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5650,7 +6086,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5697,7 +6133,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5744,7 +6180,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -6035,11 +6471,11 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>관리</v>
+        <v>장기미수</v>
       </c>
       <c r="K66" s="11">
         <v>46052</v>
@@ -6079,7 +6515,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6364,7 +6800,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6509,7 +6945,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6747,7 +7183,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6833,7 +7269,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6939,7 +7375,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6991,7 +7427,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7033,7 +7469,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7129,7 +7565,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7181,7 +7617,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7277,7 +7713,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7451,7 +7887,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7537,7 +7973,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7579,7 +8015,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7620,7 +8056,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7793,7 +8229,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7835,7 +8271,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7876,7 +8312,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7963,7 +8399,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8004,7 +8440,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8045,7 +8481,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8134,7 +8570,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8223,7 +8659,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8268,7 +8704,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
@@ -8365,7 +8801,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8451,7 +8887,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8584,7 +9020,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8626,7 +9062,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8712,7 +9148,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8789,7 +9225,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8831,7 +9267,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8873,7 +9309,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8915,7 +9351,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9089,7 +9525,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9131,7 +9567,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9173,7 +9609,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9391,7 +9827,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9432,7 +9868,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9473,7 +9909,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9514,7 +9950,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9555,7 +9991,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9596,7 +10032,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9637,7 +10073,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9678,7 +10114,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9719,7 +10155,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9760,7 +10196,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9844,7 +10280,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9971,7 +10407,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10012,7 +10448,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10053,7 +10489,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10139,7 +10575,7 @@
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10181,7 +10617,7 @@
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J160" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10223,7 +10659,7 @@
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J161" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10395,7 +10831,7 @@
       </c>
       <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J165" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10437,7 +10873,7 @@
       </c>
       <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J166" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10479,7 +10915,7 @@
       </c>
       <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J167" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10609,7 +11045,7 @@
       </c>
       <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J170" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10695,7 +11131,7 @@
       </c>
       <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J172" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10737,7 +11173,7 @@
       </c>
       <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J173" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10779,7 +11215,7 @@
       </c>
       <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J174" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10821,7 +11257,7 @@
       </c>
       <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J175" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10907,7 +11343,7 @@
       </c>
       <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J177" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10993,10 +11429,10 @@
       </c>
       <c r="I179" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J179" s="13" t="str">
-        <f t="shared" ref="J179:J215" ca="1" si="14">IF(I179="","",
+        <f t="shared" ref="J179:J242" ca="1" si="14">IF(I179="","",
  IF(G179="선급금",
    IF(I179&lt;=20,"정상",IF(I179&lt;=90,"관리","장기미수")),
  IF(G179="자재",
@@ -11043,7 +11479,7 @@
       </c>
       <c r="I180" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J180" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11085,7 +11521,7 @@
       </c>
       <c r="I181" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J181" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11127,7 +11563,7 @@
       </c>
       <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J182" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11169,7 +11605,7 @@
       </c>
       <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J183" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11211,7 +11647,7 @@
       </c>
       <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J184" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11253,7 +11689,7 @@
       </c>
       <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J185" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11339,7 +11775,7 @@
       </c>
       <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J187" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11381,7 +11817,7 @@
       </c>
       <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J188" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11423,7 +11859,7 @@
       </c>
       <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J189" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11465,7 +11901,7 @@
       </c>
       <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J190" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11507,7 +11943,7 @@
       </c>
       <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J191" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11549,7 +11985,7 @@
       </c>
       <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J192" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11591,7 +12027,7 @@
       </c>
       <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J193" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11633,7 +12069,7 @@
       </c>
       <c r="I194" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J194" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11675,7 +12111,7 @@
       </c>
       <c r="I195" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J195" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11717,7 +12153,7 @@
       </c>
       <c r="I196" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J196" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11803,7 +12239,7 @@
       </c>
       <c r="I198" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J198" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11845,7 +12281,7 @@
       </c>
       <c r="I199" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J199" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11887,7 +12323,7 @@
       </c>
       <c r="I200" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J200" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11929,7 +12365,7 @@
       </c>
       <c r="I201" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J201" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11971,7 +12407,7 @@
       </c>
       <c r="I202" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J202" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12013,7 +12449,7 @@
       </c>
       <c r="I203" s="6">
         <f t="shared" ref="I203:I266" ca="1" si="16">IF(C203="","",IF(L203="",TODAY()-C203,L203-C203))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J203" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12055,7 +12491,7 @@
       </c>
       <c r="I204" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J204" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12097,7 +12533,7 @@
       </c>
       <c r="I205" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J205" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12139,7 +12575,7 @@
       </c>
       <c r="I206" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J206" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12181,7 +12617,7 @@
       </c>
       <c r="I207" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J207" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12223,7 +12659,7 @@
       </c>
       <c r="I208" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J208" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12265,7 +12701,7 @@
       </c>
       <c r="I209" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J209" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12307,7 +12743,7 @@
       </c>
       <c r="I210" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J210" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12349,7 +12785,7 @@
       </c>
       <c r="I211" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J211" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12391,7 +12827,7 @@
       </c>
       <c r="I212" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J212" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12433,7 +12869,7 @@
       </c>
       <c r="I213" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J213" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12475,7 +12911,7 @@
       </c>
       <c r="I214" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J214" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12517,7 +12953,7 @@
       </c>
       <c r="I215" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J215" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12534,596 +12970,1200 @@
       <c r="S215" s="10"/>
     </row>
     <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B216" s="10"/>
-      <c r="C216" s="11"/>
+      <c r="B216" s="10">
+        <f>IF(C216="","",COUNTA($C$2:C216))</f>
+        <v>215</v>
+      </c>
+      <c r="C216" s="63">
+        <v>46099</v>
+      </c>
       <c r="D216" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="F216" s="64"/>
-      <c r="H216" s="4"/>
-      <c r="I216" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E216" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="F216" s="65" t="s">
+        <v>352</v>
+      </c>
+      <c r="G216" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="H216" s="64">
+        <v>4354200</v>
+      </c>
+      <c r="I216" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J216" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J216" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K216" s="11"/>
       <c r="L216" s="11"/>
       <c r="M216" s="10"/>
-      <c r="N216" s="10"/>
+      <c r="N216" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q216" s="11"/>
       <c r="R216" s="11"/>
       <c r="S216" s="10"/>
     </row>
     <row r="217" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B217" s="10"/>
-      <c r="C217" s="11"/>
+      <c r="B217" s="10">
+        <f>IF(C217="","",COUNTA($C$2:C217))</f>
+        <v>216</v>
+      </c>
+      <c r="C217" s="63">
+        <v>46099</v>
+      </c>
       <c r="D217" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H217" s="4"/>
-      <c r="I217" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F217" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G217" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="H217" s="4">
+        <v>28530900</v>
+      </c>
+      <c r="I217" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J217" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J217" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K217" s="11"/>
       <c r="L217" s="11"/>
       <c r="M217" s="10"/>
-      <c r="N217" s="10"/>
+      <c r="N217" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q217" s="11"/>
       <c r="R217" s="11"/>
       <c r="S217" s="10"/>
     </row>
     <row r="218" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B218" s="10"/>
-      <c r="C218" s="11"/>
+      <c r="B218" s="10">
+        <f>IF(C218="","",COUNTA($C$2:C218))</f>
+        <v>217</v>
+      </c>
+      <c r="C218" s="63">
+        <v>46099</v>
+      </c>
       <c r="D218" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H218" s="4"/>
-      <c r="I218" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F218" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="G218" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="H218" s="4">
+        <v>26089600</v>
+      </c>
+      <c r="I218" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J218" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J218" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K218" s="11"/>
-      <c r="L218" s="11"/>
+      <c r="L218" s="11">
+        <v>46099</v>
+      </c>
       <c r="M218" s="10"/>
-      <c r="N218" s="10"/>
+      <c r="N218" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q218" s="11"/>
       <c r="R218" s="11"/>
       <c r="S218" s="10"/>
     </row>
     <row r="219" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B219" s="10"/>
-      <c r="C219" s="11"/>
+      <c r="B219" s="10">
+        <f>IF(C219="","",COUNTA($C$2:C219))</f>
+        <v>218</v>
+      </c>
+      <c r="C219" s="63">
+        <v>46099</v>
+      </c>
       <c r="D219" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H219" s="4"/>
-      <c r="I219" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G219" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="H219" s="4">
+        <v>27749100</v>
+      </c>
+      <c r="I219" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J219" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J219" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K219" s="11"/>
       <c r="L219" s="11"/>
       <c r="M219" s="10"/>
-      <c r="N219" s="10"/>
+      <c r="N219" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q219" s="11"/>
       <c r="R219" s="11"/>
       <c r="S219" s="10"/>
     </row>
     <row r="220" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B220" s="10"/>
-      <c r="C220" s="11"/>
+      <c r="B220" s="10">
+        <f>IF(C220="","",COUNTA($C$2:C220))</f>
+        <v>219</v>
+      </c>
+      <c r="C220" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D220" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H220" s="4"/>
-      <c r="I220" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E220" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F220" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="G220" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H220" s="25">
+        <v>1842500</v>
+      </c>
+      <c r="I220" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J220" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J220" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K220" s="11"/>
-      <c r="L220" s="11"/>
+      <c r="L220" s="11">
+        <v>46100</v>
+      </c>
       <c r="M220" s="10"/>
-      <c r="N220" s="10"/>
+      <c r="N220" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q220" s="11"/>
       <c r="R220" s="11"/>
       <c r="S220" s="10"/>
     </row>
     <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B221" s="10"/>
-      <c r="C221" s="11"/>
+      <c r="B221" s="10">
+        <f>IF(C221="","",COUNTA($C$2:C221))</f>
+        <v>220</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D221" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H221" s="4"/>
-      <c r="I221" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E221" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F221" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="G221" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H221" s="25">
+        <v>6583500</v>
+      </c>
+      <c r="I221" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J221" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J221" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K221" s="11"/>
       <c r="L221" s="11"/>
       <c r="M221" s="10"/>
-      <c r="N221" s="10"/>
+      <c r="N221" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q221" s="11"/>
       <c r="R221" s="11"/>
       <c r="S221" s="10"/>
     </row>
     <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B222" s="10"/>
-      <c r="C222" s="11"/>
+      <c r="B222" s="10">
+        <f>IF(C222="","",COUNTA($C$2:C222))</f>
+        <v>221</v>
+      </c>
+      <c r="C222" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D222" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H222" s="4"/>
-      <c r="I222" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E222" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F222" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="G222" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H222" s="25">
+        <v>2038700</v>
+      </c>
+      <c r="I222" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J222" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J222" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K222" s="11"/>
       <c r="L222" s="11"/>
       <c r="M222" s="10"/>
-      <c r="N222" s="10"/>
+      <c r="N222" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q222" s="11"/>
       <c r="R222" s="11"/>
       <c r="S222" s="10"/>
     </row>
     <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B223" s="10"/>
-      <c r="C223" s="11"/>
+      <c r="B223" s="10">
+        <f>IF(C223="","",COUNTA($C$2:C223))</f>
+        <v>222</v>
+      </c>
+      <c r="C223" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D223" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H223" s="4"/>
-      <c r="I223" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E223" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F223" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="G223" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H223" s="25">
+        <v>4750000</v>
+      </c>
+      <c r="I223" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J223" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J223" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K223" s="11"/>
       <c r="L223" s="11"/>
       <c r="M223" s="10"/>
-      <c r="N223" s="10"/>
+      <c r="N223" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q223" s="11"/>
       <c r="R223" s="11"/>
       <c r="S223" s="10"/>
     </row>
     <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B224" s="10"/>
-      <c r="C224" s="11"/>
+      <c r="B224" s="10">
+        <f>IF(C224="","",COUNTA($C$2:C224))</f>
+        <v>223</v>
+      </c>
+      <c r="C224" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D224" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H224" s="4"/>
-      <c r="I224" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E224" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F224" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="G224" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H224" s="25">
+        <v>3572000</v>
+      </c>
+      <c r="I224" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J224" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J224" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K224" s="11"/>
       <c r="L224" s="11"/>
       <c r="M224" s="10"/>
-      <c r="N224" s="10"/>
+      <c r="N224" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q224" s="11"/>
       <c r="R224" s="11"/>
       <c r="S224" s="10"/>
     </row>
     <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B225" s="10"/>
-      <c r="C225" s="11"/>
+      <c r="B225" s="10">
+        <f>IF(C225="","",COUNTA($C$2:C225))</f>
+        <v>224</v>
+      </c>
+      <c r="C225" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D225" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H225" s="4"/>
-      <c r="I225" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E225" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F225" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="G225" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H225" s="25">
+        <v>435000</v>
+      </c>
+      <c r="I225" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J225" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J225" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K225" s="11"/>
       <c r="L225" s="11"/>
       <c r="M225" s="10"/>
-      <c r="N225" s="10"/>
+      <c r="N225" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q225" s="11"/>
       <c r="R225" s="11"/>
       <c r="S225" s="10"/>
     </row>
     <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B226" s="10"/>
-      <c r="C226" s="11"/>
+      <c r="B226" s="10">
+        <f>IF(C226="","",COUNTA($C$2:C226))</f>
+        <v>225</v>
+      </c>
+      <c r="C226" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D226" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H226" s="4"/>
-      <c r="I226" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E226" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="F226" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="G226" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H226" s="25">
+        <v>637000</v>
+      </c>
+      <c r="I226" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J226" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J226" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K226" s="11"/>
       <c r="L226" s="11"/>
       <c r="M226" s="10"/>
-      <c r="N226" s="10"/>
+      <c r="N226" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q226" s="11"/>
       <c r="R226" s="11"/>
       <c r="S226" s="10"/>
     </row>
     <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B227" s="10"/>
-      <c r="C227" s="11"/>
+      <c r="B227" s="10">
+        <f>IF(C227="","",COUNTA($C$2:C227))</f>
+        <v>226</v>
+      </c>
+      <c r="C227" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D227" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H227" s="4"/>
-      <c r="I227" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E227" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="F227" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="G227" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H227" s="25">
+        <v>34583000</v>
+      </c>
+      <c r="I227" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J227" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J227" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K227" s="11"/>
       <c r="L227" s="11"/>
       <c r="M227" s="10"/>
-      <c r="N227" s="10"/>
+      <c r="N227" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q227" s="11"/>
       <c r="R227" s="11"/>
       <c r="S227" s="10"/>
     </row>
     <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B228" s="10"/>
-      <c r="C228" s="11"/>
+      <c r="B228" s="10">
+        <f>IF(C228="","",COUNTA($C$2:C228))</f>
+        <v>227</v>
+      </c>
+      <c r="C228" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D228" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H228" s="4"/>
-      <c r="I228" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E228" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="F228" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="G228" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H228" s="25">
+        <v>6600000</v>
+      </c>
+      <c r="I228" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J228" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J228" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K228" s="11"/>
       <c r="L228" s="11"/>
       <c r="M228" s="10"/>
-      <c r="N228" s="10"/>
+      <c r="N228" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q228" s="11"/>
       <c r="R228" s="11"/>
       <c r="S228" s="10"/>
     </row>
     <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B229" s="10"/>
-      <c r="C229" s="11"/>
+      <c r="B229" s="10">
+        <f>IF(C229="","",COUNTA($C$2:C229))</f>
+        <v>228</v>
+      </c>
+      <c r="C229" s="11" t="s">
+        <v>385</v>
+      </c>
       <c r="D229" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H229" s="4"/>
-      <c r="I229" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E229" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="F229" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="G229" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H229" s="25">
+        <v>15802000</v>
+      </c>
+      <c r="I229" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J229" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J229" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K229" s="11"/>
       <c r="L229" s="11"/>
       <c r="M229" s="10"/>
-      <c r="N229" s="10"/>
+      <c r="N229" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q229" s="11"/>
       <c r="R229" s="11"/>
       <c r="S229" s="10"/>
     </row>
     <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B230" s="10"/>
-      <c r="C230" s="11"/>
+      <c r="B230" s="10">
+        <f>IF(C230="","",COUNTA($C$2:C230))</f>
+        <v>229</v>
+      </c>
+      <c r="C230" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D230" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H230" s="4"/>
-      <c r="I230" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E230" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F230" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="G230" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H230" s="25">
+        <v>9450000</v>
+      </c>
+      <c r="I230" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J230" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J230" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K230" s="11"/>
       <c r="L230" s="11"/>
       <c r="M230" s="10"/>
-      <c r="N230" s="10"/>
+      <c r="N230" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q230" s="11"/>
       <c r="R230" s="11"/>
       <c r="S230" s="10"/>
     </row>
     <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B231" s="10"/>
-      <c r="C231" s="11"/>
+      <c r="B231" s="10">
+        <f>IF(C231="","",COUNTA($C$2:C231))</f>
+        <v>230</v>
+      </c>
+      <c r="C231" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D231" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H231" s="4"/>
-      <c r="I231" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E231" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F231" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="G231" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H231" s="25">
+        <v>521000</v>
+      </c>
+      <c r="I231" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J231" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J231" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K231" s="11"/>
       <c r="L231" s="11"/>
       <c r="M231" s="10"/>
-      <c r="N231" s="10"/>
+      <c r="N231" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q231" s="11"/>
       <c r="R231" s="11"/>
       <c r="S231" s="10"/>
     </row>
     <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B232" s="10"/>
-      <c r="C232" s="11"/>
+      <c r="B232" s="10">
+        <f>IF(C232="","",COUNTA($C$2:C232))</f>
+        <v>231</v>
+      </c>
+      <c r="C232" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D232" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H232" s="4"/>
-      <c r="I232" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E232" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F232" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="G232" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H232" s="25">
+        <v>333000</v>
+      </c>
+      <c r="I232" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J232" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J232" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K232" s="11"/>
       <c r="L232" s="11"/>
       <c r="M232" s="10"/>
-      <c r="N232" s="10"/>
+      <c r="N232" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q232" s="11"/>
       <c r="R232" s="11"/>
       <c r="S232" s="10"/>
     </row>
     <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B233" s="10"/>
-      <c r="C233" s="11"/>
+      <c r="B233" s="10">
+        <f>IF(C233="","",COUNTA($C$2:C233))</f>
+        <v>232</v>
+      </c>
+      <c r="C233" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D233" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H233" s="4"/>
-      <c r="I233" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E233" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F233" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="G233" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H233" s="25">
+        <v>2835000</v>
+      </c>
+      <c r="I233" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J233" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J233" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K233" s="11"/>
       <c r="L233" s="11"/>
       <c r="M233" s="10"/>
-      <c r="N233" s="10"/>
+      <c r="N233" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q233" s="11"/>
       <c r="R233" s="11"/>
       <c r="S233" s="10"/>
     </row>
     <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B234" s="10"/>
-      <c r="C234" s="11"/>
+      <c r="B234" s="10">
+        <f>IF(C234="","",COUNTA($C$2:C234))</f>
+        <v>233</v>
+      </c>
+      <c r="C234" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D234" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H234" s="4"/>
-      <c r="I234" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E234" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="F234" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="G234" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H234" s="25">
+        <v>351900</v>
+      </c>
+      <c r="I234" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J234" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J234" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K234" s="11"/>
-      <c r="L234" s="11"/>
+      <c r="L234" s="11">
+        <v>46100</v>
+      </c>
       <c r="M234" s="10"/>
-      <c r="N234" s="10"/>
+      <c r="N234" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q234" s="11"/>
       <c r="R234" s="11"/>
       <c r="S234" s="10"/>
     </row>
     <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B235" s="10"/>
-      <c r="C235" s="11"/>
+      <c r="B235" s="10">
+        <f>IF(C235="","",COUNTA($C$2:C235))</f>
+        <v>234</v>
+      </c>
+      <c r="C235" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D235" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H235" s="4"/>
-      <c r="I235" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E235" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F235" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="G235" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H235" s="25">
+        <v>839000</v>
+      </c>
+      <c r="I235" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J235" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J235" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K235" s="11"/>
       <c r="L235" s="11"/>
       <c r="M235" s="10"/>
-      <c r="N235" s="10"/>
+      <c r="N235" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q235" s="11"/>
       <c r="R235" s="11"/>
       <c r="S235" s="10"/>
     </row>
     <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B236" s="10"/>
-      <c r="C236" s="11"/>
+      <c r="B236" s="10">
+        <f>IF(C236="","",COUNTA($C$2:C236))</f>
+        <v>235</v>
+      </c>
+      <c r="C236" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D236" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H236" s="4"/>
-      <c r="I236" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E236" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="F236" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="G236" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H236" s="25">
+        <v>1507200</v>
+      </c>
+      <c r="I236" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J236" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J236" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K236" s="11"/>
       <c r="L236" s="11"/>
       <c r="M236" s="10"/>
-      <c r="N236" s="10"/>
+      <c r="N236" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q236" s="11"/>
       <c r="R236" s="11"/>
       <c r="S236" s="10"/>
     </row>
     <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B237" s="10"/>
-      <c r="C237" s="11"/>
+      <c r="B237" s="10">
+        <f>IF(C237="","",COUNTA($C$2:C237))</f>
+        <v>236</v>
+      </c>
+      <c r="C237" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D237" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H237" s="4"/>
-      <c r="I237" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E237" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="F237" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="G237" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H237" s="25">
+        <v>585000</v>
+      </c>
+      <c r="I237" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J237" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J237" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K237" s="11"/>
       <c r="L237" s="11"/>
       <c r="M237" s="10"/>
-      <c r="N237" s="10"/>
+      <c r="N237" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q237" s="11"/>
       <c r="R237" s="11"/>
       <c r="S237" s="10"/>
     </row>
     <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B238" s="10"/>
-      <c r="C238" s="11"/>
+      <c r="B238" s="10">
+        <f>IF(C238="","",COUNTA($C$2:C238))</f>
+        <v>237</v>
+      </c>
+      <c r="C238" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D238" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H238" s="4"/>
-      <c r="I238" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E238" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="F238" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="G238" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H238" s="25">
+        <v>615000</v>
+      </c>
+      <c r="I238" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J238" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J238" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K238" s="11"/>
       <c r="L238" s="11"/>
       <c r="M238" s="10"/>
-      <c r="N238" s="10"/>
+      <c r="N238" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q238" s="11"/>
       <c r="R238" s="11"/>
       <c r="S238" s="10"/>
     </row>
     <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B239" s="10"/>
-      <c r="C239" s="11"/>
+      <c r="B239" s="10">
+        <f>IF(C239="","",COUNTA($C$2:C239))</f>
+        <v>238</v>
+      </c>
+      <c r="C239" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D239" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H239" s="4"/>
-      <c r="I239" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E239" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="F239" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="G239" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H239" s="25">
+        <v>44793500</v>
+      </c>
+      <c r="I239" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J239" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J239" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K239" s="11"/>
       <c r="L239" s="11"/>
       <c r="M239" s="10"/>
-      <c r="N239" s="10"/>
+      <c r="N239" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q239" s="11"/>
       <c r="R239" s="11"/>
       <c r="S239" s="10"/>
     </row>
     <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B240" s="10"/>
-      <c r="C240" s="11"/>
+      <c r="B240" s="10">
+        <f>IF(C240="","",COUNTA($C$2:C240))</f>
+        <v>239</v>
+      </c>
+      <c r="C240" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D240" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H240" s="4"/>
-      <c r="I240" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E240" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F240" s="23" t="s">
+        <v>378</v>
+      </c>
+      <c r="G240" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H240" s="25">
+        <v>602300</v>
+      </c>
+      <c r="I240" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J240" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J240" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K240" s="11"/>
       <c r="L240" s="11"/>
       <c r="M240" s="10"/>
-      <c r="N240" s="10"/>
+      <c r="N240" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q240" s="11"/>
       <c r="R240" s="11"/>
       <c r="S240" s="10"/>
     </row>
     <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B241" s="10"/>
-      <c r="C241" s="11"/>
+      <c r="B241" s="10">
+        <f>IF(C241="","",COUNTA($C$2:C241))</f>
+        <v>240</v>
+      </c>
+      <c r="C241" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D241" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H241" s="4"/>
-      <c r="I241" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E241" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F241" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="G241" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H241" s="25">
+        <v>1180000</v>
+      </c>
+      <c r="I241" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J241" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J241" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K241" s="11"/>
       <c r="L241" s="11"/>
       <c r="M241" s="10"/>
-      <c r="N241" s="10"/>
+      <c r="N241" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q241" s="11"/>
       <c r="R241" s="11"/>
       <c r="S241" s="10"/>
     </row>
     <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B242" s="10"/>
-      <c r="C242" s="11"/>
+      <c r="B242" s="10">
+        <f>IF(C242="","",COUNTA($C$2:C242))</f>
+        <v>241</v>
+      </c>
+      <c r="C242" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D242" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H242" s="4"/>
-      <c r="I242" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E242" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="F242" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="G242" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H242" s="25">
+        <v>3300000</v>
+      </c>
+      <c r="I242" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J242" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J242" s="13" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
       <c r="K242" s="11"/>
       <c r="L242" s="11"/>
       <c r="M242" s="10"/>
-      <c r="N242" s="10"/>
+      <c r="N242" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q242" s="11"/>
       <c r="R242" s="11"/>
       <c r="S242" s="10"/>
     </row>
     <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B243" s="10"/>
-      <c r="C243" s="11"/>
+      <c r="B243" s="10">
+        <f>IF(C243="","",COUNTA($C$2:C243))</f>
+        <v>242</v>
+      </c>
+      <c r="C243" s="11" t="s">
+        <v>386</v>
+      </c>
       <c r="D243" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H243" s="4"/>
-      <c r="I243" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E243" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F243" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="G243" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H243" s="25">
+        <v>1548500</v>
+      </c>
+      <c r="I243" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J243" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J243" s="13" t="str">
+        <f t="shared" ref="J243" ca="1" si="17">IF(I243="","",
+ IF(G243="선급금",
+   IF(I243&lt;=20,"정상",IF(I243&lt;=90,"관리","장기미수")),
+ IF(G243="자재",
+   IF(I243&lt;=40,"정상",IF(I243&lt;=90,"관리","장기미수")),
+   IF(I243&lt;=30,"정상",IF(I243&lt;=90,"관리","장기미수"))
+  )
+ )
+)</f>
+        <v>정상</v>
+      </c>
       <c r="K243" s="11"/>
       <c r="L243" s="11"/>
       <c r="M243" s="10"/>
-      <c r="N243" s="10"/>
+      <c r="N243" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q243" s="11"/>
       <c r="R243" s="11"/>
       <c r="S243" s="10"/>
     </row>
     <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B244" s="10"/>
+      <c r="B244" s="10" t="str">
+        <f>IF(C244="","",COUNTA($C$2:C244))</f>
+        <v/>
+      </c>
       <c r="C244" s="11"/>
       <c r="D244" s="10" t="str">
         <f t="shared" si="15"/>
@@ -13609,12 +14649,12 @@
       <c r="B267" s="10"/>
       <c r="C267" s="11"/>
       <c r="D267" s="10" t="str">
-        <f t="shared" ref="D267:D330" si="17">IF(G267="","",IF(OR(G267="선급금",G267="중도금",G267="잔금"),"A",IF(G267="자재","B",IF(G267="특허료","C",""))))</f>
+        <f t="shared" ref="D267:D330" si="18">IF(G267="","",IF(OR(G267="선급금",G267="중도금",G267="잔금"),"A",IF(G267="자재","B",IF(G267="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H267" s="4"/>
       <c r="I267" s="6" t="str">
-        <f t="shared" ref="I267:I330" ca="1" si="18">IF(C267="","",IF(L267="",TODAY()-C267,L267-C267))</f>
+        <f t="shared" ref="I267:I330" ca="1" si="19">IF(C267="","",IF(L267="",TODAY()-C267,L267-C267))</f>
         <v/>
       </c>
       <c r="J267" s="13"/>
@@ -13630,12 +14670,12 @@
       <c r="B268" s="10"/>
       <c r="C268" s="11"/>
       <c r="D268" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H268" s="4"/>
       <c r="I268" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J268" s="13"/>
@@ -13651,12 +14691,12 @@
       <c r="B269" s="10"/>
       <c r="C269" s="11"/>
       <c r="D269" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H269" s="4"/>
       <c r="I269" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J269" s="13"/>
@@ -13672,12 +14712,12 @@
       <c r="B270" s="10"/>
       <c r="C270" s="11"/>
       <c r="D270" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H270" s="4"/>
       <c r="I270" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J270" s="13"/>
@@ -13693,12 +14733,12 @@
       <c r="B271" s="10"/>
       <c r="C271" s="11"/>
       <c r="D271" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H271" s="4"/>
       <c r="I271" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J271" s="13"/>
@@ -13714,12 +14754,12 @@
       <c r="B272" s="10"/>
       <c r="C272" s="11"/>
       <c r="D272" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H272" s="4"/>
       <c r="I272" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J272" s="13"/>
@@ -13735,12 +14775,12 @@
       <c r="B273" s="10"/>
       <c r="C273" s="11"/>
       <c r="D273" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H273" s="4"/>
       <c r="I273" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J273" s="13"/>
@@ -13756,12 +14796,12 @@
       <c r="B274" s="10"/>
       <c r="C274" s="11"/>
       <c r="D274" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H274" s="4"/>
       <c r="I274" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J274" s="13"/>
@@ -13777,12 +14817,12 @@
       <c r="B275" s="10"/>
       <c r="C275" s="11"/>
       <c r="D275" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H275" s="4"/>
       <c r="I275" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J275" s="13"/>
@@ -13798,12 +14838,12 @@
       <c r="B276" s="10"/>
       <c r="C276" s="11"/>
       <c r="D276" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H276" s="4"/>
       <c r="I276" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J276" s="13"/>
@@ -13819,12 +14859,12 @@
       <c r="B277" s="10"/>
       <c r="C277" s="11"/>
       <c r="D277" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H277" s="4"/>
       <c r="I277" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J277" s="13"/>
@@ -13840,12 +14880,12 @@
       <c r="B278" s="10"/>
       <c r="C278" s="11"/>
       <c r="D278" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H278" s="4"/>
       <c r="I278" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J278" s="13"/>
@@ -13861,12 +14901,12 @@
       <c r="B279" s="10"/>
       <c r="C279" s="11"/>
       <c r="D279" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H279" s="4"/>
       <c r="I279" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J279" s="13"/>
@@ -13882,12 +14922,12 @@
       <c r="B280" s="10"/>
       <c r="C280" s="11"/>
       <c r="D280" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H280" s="4"/>
       <c r="I280" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J280" s="13"/>
@@ -13903,12 +14943,12 @@
       <c r="B281" s="10"/>
       <c r="C281" s="11"/>
       <c r="D281" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H281" s="4"/>
       <c r="I281" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J281" s="13"/>
@@ -13924,12 +14964,12 @@
       <c r="B282" s="10"/>
       <c r="C282" s="11"/>
       <c r="D282" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H282" s="4"/>
       <c r="I282" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J282" s="13"/>
@@ -13945,12 +14985,12 @@
       <c r="B283" s="10"/>
       <c r="C283" s="11"/>
       <c r="D283" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H283" s="4"/>
       <c r="I283" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J283" s="13"/>
@@ -13966,12 +15006,12 @@
       <c r="B284" s="10"/>
       <c r="C284" s="11"/>
       <c r="D284" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H284" s="4"/>
       <c r="I284" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J284" s="13"/>
@@ -13987,12 +15027,12 @@
       <c r="B285" s="10"/>
       <c r="C285" s="11"/>
       <c r="D285" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H285" s="4"/>
       <c r="I285" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J285" s="13"/>
@@ -14008,12 +15048,12 @@
       <c r="B286" s="10"/>
       <c r="C286" s="11"/>
       <c r="D286" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H286" s="4"/>
       <c r="I286" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J286" s="13"/>
@@ -14029,12 +15069,12 @@
       <c r="B287" s="10"/>
       <c r="C287" s="11"/>
       <c r="D287" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H287" s="4"/>
       <c r="I287" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J287" s="13"/>
@@ -14050,12 +15090,12 @@
       <c r="B288" s="10"/>
       <c r="C288" s="11"/>
       <c r="D288" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H288" s="4"/>
       <c r="I288" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J288" s="13"/>
@@ -14071,12 +15111,12 @@
       <c r="B289" s="10"/>
       <c r="C289" s="11"/>
       <c r="D289" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H289" s="4"/>
       <c r="I289" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J289" s="13"/>
@@ -14092,12 +15132,12 @@
       <c r="B290" s="10"/>
       <c r="C290" s="11"/>
       <c r="D290" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H290" s="4"/>
       <c r="I290" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J290" s="13"/>
@@ -14113,12 +15153,12 @@
       <c r="B291" s="10"/>
       <c r="C291" s="11"/>
       <c r="D291" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H291" s="4"/>
       <c r="I291" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J291" s="13"/>
@@ -14134,12 +15174,12 @@
       <c r="B292" s="10"/>
       <c r="C292" s="11"/>
       <c r="D292" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H292" s="4"/>
       <c r="I292" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J292" s="13"/>
@@ -14155,12 +15195,12 @@
       <c r="B293" s="10"/>
       <c r="C293" s="11"/>
       <c r="D293" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H293" s="4"/>
       <c r="I293" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J293" s="13"/>
@@ -14176,12 +15216,12 @@
       <c r="B294" s="10"/>
       <c r="C294" s="11"/>
       <c r="D294" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H294" s="4"/>
       <c r="I294" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J294" s="13"/>
@@ -14197,12 +15237,12 @@
       <c r="B295" s="10"/>
       <c r="C295" s="11"/>
       <c r="D295" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H295" s="4"/>
       <c r="I295" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J295" s="13"/>
@@ -14218,12 +15258,12 @@
       <c r="B296" s="10"/>
       <c r="C296" s="11"/>
       <c r="D296" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H296" s="4"/>
       <c r="I296" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J296" s="13"/>
@@ -14239,12 +15279,12 @@
       <c r="B297" s="10"/>
       <c r="C297" s="11"/>
       <c r="D297" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H297" s="4"/>
       <c r="I297" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J297" s="13"/>
@@ -14260,12 +15300,12 @@
       <c r="B298" s="10"/>
       <c r="C298" s="11"/>
       <c r="D298" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H298" s="4"/>
       <c r="I298" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J298" s="13"/>
@@ -14281,12 +15321,12 @@
       <c r="B299" s="10"/>
       <c r="C299" s="11"/>
       <c r="D299" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H299" s="4"/>
       <c r="I299" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J299" s="13"/>
@@ -14302,12 +15342,12 @@
       <c r="B300" s="10"/>
       <c r="C300" s="11"/>
       <c r="D300" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H300" s="4"/>
       <c r="I300" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J300" s="13"/>
@@ -14323,12 +15363,12 @@
       <c r="B301" s="10"/>
       <c r="C301" s="11"/>
       <c r="D301" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H301" s="4"/>
       <c r="I301" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J301" s="13"/>
@@ -14344,12 +15384,12 @@
       <c r="B302" s="10"/>
       <c r="C302" s="11"/>
       <c r="D302" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H302" s="4"/>
       <c r="I302" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J302" s="13"/>
@@ -14365,12 +15405,12 @@
       <c r="B303" s="10"/>
       <c r="C303" s="11"/>
       <c r="D303" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H303" s="4"/>
       <c r="I303" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J303" s="13"/>
@@ -14386,12 +15426,12 @@
       <c r="B304" s="10"/>
       <c r="C304" s="11"/>
       <c r="D304" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H304" s="4"/>
       <c r="I304" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J304" s="13"/>
@@ -14407,12 +15447,12 @@
       <c r="B305" s="10"/>
       <c r="C305" s="11"/>
       <c r="D305" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H305" s="4"/>
       <c r="I305" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J305" s="13"/>
@@ -14428,12 +15468,12 @@
       <c r="B306" s="10"/>
       <c r="C306" s="11"/>
       <c r="D306" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H306" s="4"/>
       <c r="I306" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J306" s="13"/>
@@ -14449,12 +15489,12 @@
       <c r="B307" s="10"/>
       <c r="C307" s="11"/>
       <c r="D307" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H307" s="4"/>
       <c r="I307" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J307" s="13"/>
@@ -14470,12 +15510,12 @@
       <c r="B308" s="10"/>
       <c r="C308" s="11"/>
       <c r="D308" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H308" s="4"/>
       <c r="I308" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J308" s="13"/>
@@ -14491,12 +15531,12 @@
       <c r="B309" s="10"/>
       <c r="C309" s="11"/>
       <c r="D309" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H309" s="4"/>
       <c r="I309" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J309" s="13"/>
@@ -14512,12 +15552,12 @@
       <c r="B310" s="10"/>
       <c r="C310" s="11"/>
       <c r="D310" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H310" s="4"/>
       <c r="I310" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J310" s="13"/>
@@ -14533,12 +15573,12 @@
       <c r="B311" s="10"/>
       <c r="C311" s="11"/>
       <c r="D311" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H311" s="4"/>
       <c r="I311" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J311" s="13"/>
@@ -14554,12 +15594,12 @@
       <c r="B312" s="10"/>
       <c r="C312" s="11"/>
       <c r="D312" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H312" s="4"/>
       <c r="I312" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J312" s="13"/>
@@ -14575,12 +15615,12 @@
       <c r="B313" s="10"/>
       <c r="C313" s="11"/>
       <c r="D313" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H313" s="4"/>
       <c r="I313" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J313" s="13"/>
@@ -14596,12 +15636,12 @@
       <c r="B314" s="10"/>
       <c r="C314" s="11"/>
       <c r="D314" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H314" s="4"/>
       <c r="I314" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J314" s="13"/>
@@ -14617,12 +15657,12 @@
       <c r="B315" s="10"/>
       <c r="C315" s="11"/>
       <c r="D315" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H315" s="4"/>
       <c r="I315" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J315" s="13"/>
@@ -14638,12 +15678,12 @@
       <c r="B316" s="10"/>
       <c r="C316" s="11"/>
       <c r="D316" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H316" s="4"/>
       <c r="I316" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J316" s="13"/>
@@ -14659,12 +15699,12 @@
       <c r="B317" s="10"/>
       <c r="C317" s="11"/>
       <c r="D317" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H317" s="4"/>
       <c r="I317" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J317" s="13"/>
@@ -14680,12 +15720,12 @@
       <c r="B318" s="10"/>
       <c r="C318" s="11"/>
       <c r="D318" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H318" s="4"/>
       <c r="I318" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J318" s="13"/>
@@ -14701,12 +15741,12 @@
       <c r="B319" s="10"/>
       <c r="C319" s="11"/>
       <c r="D319" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H319" s="4"/>
       <c r="I319" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J319" s="13"/>
@@ -14722,12 +15762,12 @@
       <c r="B320" s="10"/>
       <c r="C320" s="11"/>
       <c r="D320" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H320" s="4"/>
       <c r="I320" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J320" s="13"/>
@@ -14743,12 +15783,12 @@
       <c r="B321" s="10"/>
       <c r="C321" s="11"/>
       <c r="D321" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H321" s="4"/>
       <c r="I321" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J321" s="13"/>
@@ -14764,12 +15804,12 @@
       <c r="B322" s="10"/>
       <c r="C322" s="11"/>
       <c r="D322" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H322" s="4"/>
       <c r="I322" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J322" s="13"/>
@@ -14785,12 +15825,12 @@
       <c r="B323" s="10"/>
       <c r="C323" s="11"/>
       <c r="D323" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H323" s="4"/>
       <c r="I323" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J323" s="13"/>
@@ -14806,12 +15846,12 @@
       <c r="B324" s="10"/>
       <c r="C324" s="11"/>
       <c r="D324" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H324" s="4"/>
       <c r="I324" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J324" s="13"/>
@@ -14827,12 +15867,12 @@
       <c r="B325" s="10"/>
       <c r="C325" s="11"/>
       <c r="D325" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H325" s="4"/>
       <c r="I325" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J325" s="13"/>
@@ -14848,12 +15888,12 @@
       <c r="B326" s="10"/>
       <c r="C326" s="11"/>
       <c r="D326" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H326" s="4"/>
       <c r="I326" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J326" s="13"/>
@@ -14869,12 +15909,12 @@
       <c r="B327" s="10"/>
       <c r="C327" s="11"/>
       <c r="D327" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H327" s="4"/>
       <c r="I327" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J327" s="13"/>
@@ -14890,12 +15930,12 @@
       <c r="B328" s="10"/>
       <c r="C328" s="11"/>
       <c r="D328" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H328" s="4"/>
       <c r="I328" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J328" s="13"/>
@@ -14911,12 +15951,12 @@
       <c r="B329" s="10"/>
       <c r="C329" s="11"/>
       <c r="D329" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H329" s="4"/>
       <c r="I329" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J329" s="13"/>
@@ -14932,12 +15972,12 @@
       <c r="B330" s="10"/>
       <c r="C330" s="11"/>
       <c r="D330" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H330" s="4"/>
       <c r="I330" s="6" t="str">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J330" s="13"/>
@@ -14953,12 +15993,12 @@
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
       <c r="D331" s="10" t="str">
-        <f t="shared" ref="D331:D394" si="19">IF(G331="","",IF(OR(G331="선급금",G331="중도금",G331="잔금"),"A",IF(G331="자재","B",IF(G331="특허료","C",""))))</f>
+        <f t="shared" ref="D331:D394" si="20">IF(G331="","",IF(OR(G331="선급금",G331="중도금",G331="잔금"),"A",IF(G331="자재","B",IF(G331="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H331" s="4"/>
       <c r="I331" s="6" t="str">
-        <f t="shared" ref="I331:I394" ca="1" si="20">IF(C331="","",IF(L331="",TODAY()-C331,L331-C331))</f>
+        <f t="shared" ref="I331:I394" ca="1" si="21">IF(C331="","",IF(L331="",TODAY()-C331,L331-C331))</f>
         <v/>
       </c>
       <c r="J331" s="13"/>
@@ -14974,12 +16014,12 @@
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J332" s="13"/>
@@ -14995,12 +16035,12 @@
       <c r="B333" s="10"/>
       <c r="C333" s="11"/>
       <c r="D333" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H333" s="4"/>
       <c r="I333" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J333" s="13"/>
@@ -15016,12 +16056,12 @@
       <c r="B334" s="10"/>
       <c r="C334" s="11"/>
       <c r="D334" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H334" s="4"/>
       <c r="I334" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J334" s="13"/>
@@ -15037,12 +16077,12 @@
       <c r="B335" s="10"/>
       <c r="C335" s="11"/>
       <c r="D335" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H335" s="4"/>
       <c r="I335" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J335" s="13"/>
@@ -15058,12 +16098,12 @@
       <c r="B336" s="10"/>
       <c r="C336" s="11"/>
       <c r="D336" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H336" s="4"/>
       <c r="I336" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J336" s="13"/>
@@ -15079,12 +16119,12 @@
       <c r="B337" s="10"/>
       <c r="C337" s="11"/>
       <c r="D337" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H337" s="4"/>
       <c r="I337" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J337" s="13"/>
@@ -15100,12 +16140,12 @@
       <c r="B338" s="10"/>
       <c r="C338" s="11"/>
       <c r="D338" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H338" s="4"/>
       <c r="I338" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J338" s="13"/>
@@ -15121,12 +16161,12 @@
       <c r="B339" s="10"/>
       <c r="C339" s="11"/>
       <c r="D339" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H339" s="4"/>
       <c r="I339" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J339" s="13"/>
@@ -15142,12 +16182,12 @@
       <c r="B340" s="10"/>
       <c r="C340" s="11"/>
       <c r="D340" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H340" s="4"/>
       <c r="I340" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J340" s="13"/>
@@ -15163,12 +16203,12 @@
       <c r="B341" s="10"/>
       <c r="C341" s="11"/>
       <c r="D341" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H341" s="4"/>
       <c r="I341" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J341" s="13"/>
@@ -15184,12 +16224,12 @@
       <c r="B342" s="10"/>
       <c r="C342" s="11"/>
       <c r="D342" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H342" s="4"/>
       <c r="I342" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J342" s="13"/>
@@ -15205,12 +16245,12 @@
       <c r="B343" s="10"/>
       <c r="C343" s="11"/>
       <c r="D343" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H343" s="4"/>
       <c r="I343" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J343" s="13"/>
@@ -15226,12 +16266,12 @@
       <c r="B344" s="10"/>
       <c r="C344" s="11"/>
       <c r="D344" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H344" s="4"/>
       <c r="I344" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J344" s="13"/>
@@ -15247,12 +16287,12 @@
       <c r="B345" s="10"/>
       <c r="C345" s="11"/>
       <c r="D345" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H345" s="4"/>
       <c r="I345" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J345" s="13"/>
@@ -15268,12 +16308,12 @@
       <c r="B346" s="10"/>
       <c r="C346" s="11"/>
       <c r="D346" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H346" s="4"/>
       <c r="I346" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J346" s="13"/>
@@ -15289,12 +16329,12 @@
       <c r="B347" s="10"/>
       <c r="C347" s="11"/>
       <c r="D347" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H347" s="4"/>
       <c r="I347" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J347" s="13"/>
@@ -15310,12 +16350,12 @@
       <c r="B348" s="10"/>
       <c r="C348" s="11"/>
       <c r="D348" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H348" s="4"/>
       <c r="I348" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J348" s="13"/>
@@ -15331,12 +16371,12 @@
       <c r="B349" s="10"/>
       <c r="C349" s="11"/>
       <c r="D349" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H349" s="4"/>
       <c r="I349" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J349" s="13"/>
@@ -15352,12 +16392,12 @@
       <c r="B350" s="10"/>
       <c r="C350" s="11"/>
       <c r="D350" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H350" s="4"/>
       <c r="I350" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J350" s="13"/>
@@ -15373,12 +16413,12 @@
       <c r="B351" s="10"/>
       <c r="C351" s="11"/>
       <c r="D351" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H351" s="4"/>
       <c r="I351" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J351" s="13"/>
@@ -15394,12 +16434,12 @@
       <c r="B352" s="10"/>
       <c r="C352" s="11"/>
       <c r="D352" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H352" s="4"/>
       <c r="I352" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J352" s="13"/>
@@ -15415,12 +16455,12 @@
       <c r="B353" s="10"/>
       <c r="C353" s="11"/>
       <c r="D353" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H353" s="4"/>
       <c r="I353" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J353" s="13"/>
@@ -15436,12 +16476,12 @@
       <c r="B354" s="10"/>
       <c r="C354" s="11"/>
       <c r="D354" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H354" s="4"/>
       <c r="I354" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J354" s="13"/>
@@ -15457,12 +16497,12 @@
       <c r="B355" s="10"/>
       <c r="C355" s="11"/>
       <c r="D355" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H355" s="4"/>
       <c r="I355" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J355" s="13"/>
@@ -15478,12 +16518,12 @@
       <c r="B356" s="10"/>
       <c r="C356" s="11"/>
       <c r="D356" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H356" s="4"/>
       <c r="I356" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J356" s="13"/>
@@ -15499,12 +16539,12 @@
       <c r="B357" s="10"/>
       <c r="C357" s="11"/>
       <c r="D357" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H357" s="4"/>
       <c r="I357" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J357" s="13"/>
@@ -15520,12 +16560,12 @@
       <c r="B358" s="10"/>
       <c r="C358" s="11"/>
       <c r="D358" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H358" s="4"/>
       <c r="I358" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J358" s="13"/>
@@ -15541,12 +16581,12 @@
       <c r="B359" s="10"/>
       <c r="C359" s="11"/>
       <c r="D359" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H359" s="4"/>
       <c r="I359" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J359" s="13"/>
@@ -15562,12 +16602,12 @@
       <c r="B360" s="10"/>
       <c r="C360" s="11"/>
       <c r="D360" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H360" s="4"/>
       <c r="I360" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J360" s="13"/>
@@ -15583,12 +16623,12 @@
       <c r="B361" s="10"/>
       <c r="C361" s="11"/>
       <c r="D361" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H361" s="4"/>
       <c r="I361" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J361" s="13"/>
@@ -15604,12 +16644,12 @@
       <c r="B362" s="10"/>
       <c r="C362" s="11"/>
       <c r="D362" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H362" s="4"/>
       <c r="I362" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J362" s="13"/>
@@ -15625,12 +16665,12 @@
       <c r="B363" s="10"/>
       <c r="C363" s="11"/>
       <c r="D363" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H363" s="4"/>
       <c r="I363" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J363" s="13"/>
@@ -15646,12 +16686,12 @@
       <c r="B364" s="10"/>
       <c r="C364" s="11"/>
       <c r="D364" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H364" s="4"/>
       <c r="I364" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J364" s="13"/>
@@ -15667,12 +16707,12 @@
       <c r="B365" s="10"/>
       <c r="C365" s="11"/>
       <c r="D365" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H365" s="4"/>
       <c r="I365" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J365" s="13"/>
@@ -15688,12 +16728,12 @@
       <c r="B366" s="10"/>
       <c r="C366" s="11"/>
       <c r="D366" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H366" s="4"/>
       <c r="I366" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J366" s="13"/>
@@ -15709,12 +16749,12 @@
       <c r="B367" s="10"/>
       <c r="C367" s="11"/>
       <c r="D367" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H367" s="4"/>
       <c r="I367" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J367" s="13"/>
@@ -15730,12 +16770,12 @@
       <c r="B368" s="10"/>
       <c r="C368" s="11"/>
       <c r="D368" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H368" s="4"/>
       <c r="I368" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J368" s="13"/>
@@ -15751,12 +16791,12 @@
       <c r="B369" s="10"/>
       <c r="C369" s="11"/>
       <c r="D369" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H369" s="4"/>
       <c r="I369" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J369" s="13"/>
@@ -15772,12 +16812,12 @@
       <c r="B370" s="10"/>
       <c r="C370" s="11"/>
       <c r="D370" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H370" s="4"/>
       <c r="I370" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J370" s="13"/>
@@ -15793,12 +16833,12 @@
       <c r="B371" s="10"/>
       <c r="C371" s="11"/>
       <c r="D371" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H371" s="4"/>
       <c r="I371" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J371" s="13"/>
@@ -15814,12 +16854,12 @@
       <c r="B372" s="10"/>
       <c r="C372" s="11"/>
       <c r="D372" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H372" s="4"/>
       <c r="I372" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J372" s="13"/>
@@ -15835,12 +16875,12 @@
       <c r="B373" s="10"/>
       <c r="C373" s="11"/>
       <c r="D373" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H373" s="4"/>
       <c r="I373" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J373" s="13"/>
@@ -15856,12 +16896,12 @@
       <c r="B374" s="10"/>
       <c r="C374" s="11"/>
       <c r="D374" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H374" s="4"/>
       <c r="I374" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J374" s="13"/>
@@ -15877,12 +16917,12 @@
       <c r="B375" s="10"/>
       <c r="C375" s="11"/>
       <c r="D375" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H375" s="4"/>
       <c r="I375" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J375" s="13"/>
@@ -15898,12 +16938,12 @@
       <c r="B376" s="10"/>
       <c r="C376" s="11"/>
       <c r="D376" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H376" s="4"/>
       <c r="I376" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J376" s="13"/>
@@ -15919,12 +16959,12 @@
       <c r="B377" s="10"/>
       <c r="C377" s="11"/>
       <c r="D377" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H377" s="4"/>
       <c r="I377" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J377" s="13"/>
@@ -15940,12 +16980,12 @@
       <c r="B378" s="10"/>
       <c r="C378" s="11"/>
       <c r="D378" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H378" s="4"/>
       <c r="I378" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J378" s="13"/>
@@ -15961,12 +17001,12 @@
       <c r="B379" s="10"/>
       <c r="C379" s="11"/>
       <c r="D379" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H379" s="4"/>
       <c r="I379" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J379" s="13"/>
@@ -15982,12 +17022,12 @@
       <c r="B380" s="10"/>
       <c r="C380" s="11"/>
       <c r="D380" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H380" s="4"/>
       <c r="I380" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J380" s="13"/>
@@ -16003,12 +17043,12 @@
       <c r="B381" s="10"/>
       <c r="C381" s="11"/>
       <c r="D381" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H381" s="4"/>
       <c r="I381" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J381" s="13"/>
@@ -16024,12 +17064,12 @@
       <c r="B382" s="10"/>
       <c r="C382" s="11"/>
       <c r="D382" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H382" s="4"/>
       <c r="I382" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J382" s="13"/>
@@ -16045,12 +17085,12 @@
       <c r="B383" s="10"/>
       <c r="C383" s="11"/>
       <c r="D383" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H383" s="4"/>
       <c r="I383" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J383" s="13"/>
@@ -16066,12 +17106,12 @@
       <c r="B384" s="10"/>
       <c r="C384" s="11"/>
       <c r="D384" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H384" s="4"/>
       <c r="I384" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J384" s="13"/>
@@ -16087,12 +17127,12 @@
       <c r="B385" s="10"/>
       <c r="C385" s="11"/>
       <c r="D385" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H385" s="4"/>
       <c r="I385" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J385" s="13"/>
@@ -16108,12 +17148,12 @@
       <c r="B386" s="10"/>
       <c r="C386" s="11"/>
       <c r="D386" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H386" s="4"/>
       <c r="I386" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J386" s="13"/>
@@ -16129,12 +17169,12 @@
       <c r="B387" s="10"/>
       <c r="C387" s="11"/>
       <c r="D387" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H387" s="4"/>
       <c r="I387" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J387" s="13"/>
@@ -16150,12 +17190,12 @@
       <c r="B388" s="10"/>
       <c r="C388" s="11"/>
       <c r="D388" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H388" s="4"/>
       <c r="I388" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J388" s="13"/>
@@ -16171,12 +17211,12 @@
       <c r="B389" s="10"/>
       <c r="C389" s="11"/>
       <c r="D389" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H389" s="4"/>
       <c r="I389" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J389" s="13"/>
@@ -16192,12 +17232,12 @@
       <c r="B390" s="10"/>
       <c r="C390" s="11"/>
       <c r="D390" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H390" s="4"/>
       <c r="I390" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J390" s="13"/>
@@ -16213,12 +17253,12 @@
       <c r="B391" s="10"/>
       <c r="C391" s="11"/>
       <c r="D391" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H391" s="4"/>
       <c r="I391" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J391" s="13"/>
@@ -16234,12 +17274,12 @@
       <c r="B392" s="10"/>
       <c r="C392" s="11"/>
       <c r="D392" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H392" s="4"/>
       <c r="I392" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J392" s="13"/>
@@ -16255,12 +17295,12 @@
       <c r="B393" s="10"/>
       <c r="C393" s="11"/>
       <c r="D393" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H393" s="4"/>
       <c r="I393" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J393" s="13"/>
@@ -16276,12 +17316,12 @@
       <c r="B394" s="10"/>
       <c r="C394" s="11"/>
       <c r="D394" s="10" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H394" s="4"/>
       <c r="I394" s="6" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J394" s="13"/>
@@ -16297,12 +17337,12 @@
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
       <c r="D395" s="10" t="str">
-        <f t="shared" ref="D395:D407" si="21">IF(G395="","",IF(OR(G395="선급금",G395="중도금",G395="잔금"),"A",IF(G395="자재","B",IF(G395="특허료","C",""))))</f>
+        <f t="shared" ref="D395:D407" si="22">IF(G395="","",IF(OR(G395="선급금",G395="중도금",G395="잔금"),"A",IF(G395="자재","B",IF(G395="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H395" s="4"/>
       <c r="I395" s="6" t="str">
-        <f t="shared" ref="I395:I405" ca="1" si="22">IF(C395="","",IF(L395="",TODAY()-C395,L395-C395))</f>
+        <f t="shared" ref="I395:I405" ca="1" si="23">IF(C395="","",IF(L395="",TODAY()-C395,L395-C395))</f>
         <v/>
       </c>
       <c r="J395" s="13"/>
@@ -16318,12 +17358,12 @@
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H396" s="4"/>
       <c r="I396" s="6" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="J396" s="13"/>
@@ -16339,12 +17379,12 @@
       <c r="B397" s="10"/>
       <c r="C397" s="11"/>
       <c r="D397" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H397" s="4"/>
       <c r="I397" s="6" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="J397" s="13"/>
@@ -16360,12 +17400,12 @@
       <c r="B398" s="10"/>
       <c r="C398" s="11"/>
       <c r="D398" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H398" s="4"/>
       <c r="I398" s="6" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="J398" s="13"/>
@@ -16381,12 +17421,12 @@
       <c r="B399" s="10"/>
       <c r="C399" s="11"/>
       <c r="D399" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H399" s="4"/>
       <c r="I399" s="6" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="J399" s="13"/>
@@ -16402,12 +17442,12 @@
       <c r="B400" s="10"/>
       <c r="C400" s="11"/>
       <c r="D400" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H400" s="4"/>
       <c r="I400" s="6" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="J400" s="13"/>
@@ -16423,12 +17463,12 @@
       <c r="B401" s="10"/>
       <c r="C401" s="11"/>
       <c r="D401" s="10" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="H401" s="4"/>
       <c r="I401" s="6" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="J401" s="13"/>
@@ -16444,11 +17484,11 @@
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
       <c r="D402" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I402" s="1" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="K402" s="11"/>
@@ -16460,11 +17500,11 @@
       <c r="B403" s="10"/>
       <c r="C403" s="11"/>
       <c r="D403" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I403" s="1" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="K403" s="11"/>
@@ -16476,11 +17516,11 @@
       <c r="B404" s="10"/>
       <c r="C404" s="11"/>
       <c r="D404" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I404" s="1" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="Q404" s="11"/>
@@ -16490,11 +17530,11 @@
       <c r="B405" s="10"/>
       <c r="C405" s="11"/>
       <c r="D405" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="I405" s="1" t="str">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="Q405" s="11"/>
@@ -16504,7 +17544,7 @@
       <c r="B406" s="10"/>
       <c r="C406" s="11"/>
       <c r="D406" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q406" s="11"/>
@@ -16514,7 +17554,7 @@
       <c r="B407" s="10"/>
       <c r="C407" s="11"/>
       <c r="D407" s="1" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q407" s="11"/>
@@ -16528,255 +17568,310 @@
   <autoFilter ref="A1:S407"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="48" priority="68">
+    <cfRule type="expression" dxfId="68" priority="83">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="47" priority="67">
+    <cfRule type="expression" dxfId="67" priority="82">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="46" priority="66">
+    <cfRule type="expression" dxfId="66" priority="81">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="45" priority="65">
+    <cfRule type="expression" dxfId="65" priority="80">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="44" priority="60">
+    <cfRule type="expression" dxfId="64" priority="75">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99 E186:F192 H186:H192 C186:C192">
-    <cfRule type="expression" dxfId="43" priority="50">
+    <cfRule type="expression" dxfId="63" priority="65">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="42" priority="49">
+    <cfRule type="expression" dxfId="62" priority="64">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="41" priority="47">
+    <cfRule type="expression" dxfId="61" priority="62">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="40" priority="46">
+    <cfRule type="expression" dxfId="60" priority="61">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="39" priority="45">
+    <cfRule type="expression" dxfId="59" priority="60">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="38" priority="44">
+    <cfRule type="expression" dxfId="58" priority="59">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="37" priority="43">
+    <cfRule type="expression" dxfId="57" priority="58">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="36" priority="42">
+    <cfRule type="expression" dxfId="56" priority="57">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="35" priority="41">
+    <cfRule type="expression" dxfId="55" priority="56">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="34" priority="40">
+    <cfRule type="expression" dxfId="54" priority="55">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="33" priority="39">
+    <cfRule type="expression" dxfId="53" priority="54">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="32" priority="38">
+    <cfRule type="expression" dxfId="52" priority="53">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="31" priority="37">
+    <cfRule type="expression" dxfId="51" priority="52">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="30" priority="36">
+    <cfRule type="expression" dxfId="50" priority="51">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="29" priority="35">
+    <cfRule type="expression" dxfId="49" priority="50">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="28" priority="34">
+    <cfRule type="expression" dxfId="48" priority="49">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="27" priority="33">
+    <cfRule type="expression" dxfId="47" priority="48">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="26" priority="32">
+    <cfRule type="expression" dxfId="46" priority="47">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="25" priority="31">
+    <cfRule type="expression" dxfId="45" priority="46">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="24" priority="29">
+    <cfRule type="expression" dxfId="44" priority="44">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="23" priority="28">
+    <cfRule type="expression" dxfId="43" priority="43">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="22" priority="27">
+    <cfRule type="expression" dxfId="42" priority="42">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="21" priority="26">
+    <cfRule type="expression" dxfId="41" priority="41">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="20" priority="25">
+    <cfRule type="expression" dxfId="40" priority="40">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="19" priority="24">
+    <cfRule type="expression" dxfId="39" priority="39">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="18" priority="23">
+    <cfRule type="expression" dxfId="38" priority="38">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="17" priority="22">
+    <cfRule type="expression" dxfId="37" priority="37">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="16" priority="21">
+    <cfRule type="expression" dxfId="36" priority="36">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
-    <cfRule type="expression" dxfId="15" priority="20">
+    <cfRule type="expression" dxfId="35" priority="35">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179:F185">
-    <cfRule type="expression" dxfId="14" priority="19">
+    <cfRule type="expression" dxfId="34" priority="34">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E178">
-    <cfRule type="expression" dxfId="13" priority="18">
+    <cfRule type="expression" dxfId="33" priority="33">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E179:E185">
-    <cfRule type="expression" dxfId="12" priority="17">
+    <cfRule type="expression" dxfId="32" priority="32">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166:C178">
-    <cfRule type="expression" dxfId="11" priority="16">
+    <cfRule type="expression" dxfId="31" priority="31">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="10" priority="15">
+    <cfRule type="expression" dxfId="30" priority="30">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="9" priority="14">
+    <cfRule type="expression" dxfId="29" priority="29">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H179:H185">
-    <cfRule type="expression" dxfId="8" priority="13">
+    <cfRule type="expression" dxfId="28" priority="28">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F194:F200">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="27" priority="23">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E194:E200">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="26" priority="22">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C194:C201">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="25" priority="21">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H194:H200">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="24" priority="20">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C202:C215">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="23" priority="19">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F202:F215">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="22" priority="18">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H202:H215">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="21" priority="17">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E202:E215">
+  <conditionalFormatting sqref="E202:E216">
+    <cfRule type="expression" dxfId="20" priority="16">
+      <formula>$J202="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C216">
+    <cfRule type="expression" dxfId="19" priority="15">
+      <formula>$I216="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H216">
+    <cfRule type="expression" dxfId="18" priority="10">
+      <formula>$I216="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C217">
+    <cfRule type="expression" dxfId="17" priority="9">
+      <formula>$I217="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C218">
+    <cfRule type="expression" dxfId="16" priority="8">
+      <formula>$I218="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C219">
+    <cfRule type="expression" dxfId="15" priority="7">
+      <formula>$I219="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F220:F229">
+    <cfRule type="expression" dxfId="9" priority="6">
+      <formula>$J220="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F230:F243">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>$J230="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E220:E229">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>$J220="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E230:E243">
+    <cfRule type="expression" dxfId="4" priority="3">
+      <formula>$J230="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H220:H229">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J220="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H230:H243">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J202="잔금"</formula>
+      <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N215">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N243">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D407">

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="406">
   <si>
     <t>순번</t>
   </si>
@@ -1395,6 +1395,68 @@
   </si>
   <si>
     <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>성균관대역서희스타힐스 1,2단지아파트</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜모아씨앤에스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>크로바아파트</t>
+  </si>
+  <si>
+    <t>삼일원앙아파트</t>
+  </si>
+  <si>
+    <t>산격대우아파트</t>
+  </si>
+  <si>
+    <t>주식회사 위즈페인팅</t>
+  </si>
+  <si>
+    <t>(주)도경</t>
+  </si>
+  <si>
+    <t>㈜일성기업</t>
+  </si>
+  <si>
+    <t>중도금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>경동김포감정389영업소</t>
+  </si>
+  <si>
+    <t>태전주공2단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>철산두산위브</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>장현2엔플러스빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>노형뜨란채</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)방수존건설</t>
+  </si>
+  <si>
+    <t>(주)첨단누수연구소</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
   </si>
   <si>
     <t>자재</t>
@@ -1859,7 +1921,7 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="69">
+  <dxfs count="74">
     <dxf>
       <fill>
         <patternFill>
@@ -1934,6 +1996,51 @@
           <color auto="1"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -3302,7 +3409,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -3427,7 +3534,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3525,7 +3632,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3581,7 +3688,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3630,7 +3737,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3681,7 +3788,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3733,7 +3840,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3872,7 +3979,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3928,7 +4035,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3977,7 +4084,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4026,7 +4133,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4073,7 +4180,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4120,7 +4227,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4167,7 +4274,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4214,7 +4321,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4261,7 +4368,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4310,7 +4417,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4359,7 +4466,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4408,7 +4515,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4457,7 +4564,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4506,7 +4613,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4555,7 +4662,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4604,7 +4711,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4653,7 +4760,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4702,7 +4809,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4751,7 +4858,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4800,7 +4907,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4849,7 +4956,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4898,7 +5005,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4947,7 +5054,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4996,7 +5103,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5041,7 +5148,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5095,7 +5202,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5151,7 +5258,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5204,7 +5311,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5251,7 +5358,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5305,7 +5412,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5410,7 +5517,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5559,7 +5666,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5606,7 +5713,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6039,7 +6146,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6086,7 +6193,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6133,7 +6240,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6180,7 +6287,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -6471,7 +6578,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6515,7 +6622,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6800,7 +6907,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6945,7 +7052,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7183,7 +7290,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7269,7 +7376,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7375,7 +7482,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7427,7 +7534,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7469,7 +7576,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7565,7 +7672,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7617,7 +7724,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7713,7 +7820,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7887,11 +7994,11 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K96" s="11"/>
       <c r="L96" s="11"/>
@@ -7973,11 +8080,11 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K98" s="11"/>
       <c r="L98" s="11"/>
@@ -8015,11 +8122,11 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K99" s="11"/>
       <c r="L99" s="11"/>
@@ -8056,7 +8163,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8229,7 +8336,7 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8271,7 +8378,7 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8312,7 +8419,7 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8399,7 +8506,7 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8440,7 +8547,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8481,7 +8588,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8570,7 +8677,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8659,7 +8766,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8704,7 +8811,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
@@ -8801,7 +8908,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8887,7 +8994,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9020,7 +9127,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9062,7 +9169,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9148,7 +9255,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9225,7 +9332,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9267,7 +9374,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9309,7 +9416,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9351,7 +9458,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9525,7 +9632,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9567,7 +9674,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9609,7 +9716,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9827,7 +9934,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9868,7 +9975,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9909,7 +10016,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9950,7 +10057,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9991,7 +10098,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10032,7 +10139,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10073,7 +10180,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10114,7 +10221,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10155,7 +10262,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10196,7 +10303,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10280,7 +10387,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10407,7 +10514,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10448,7 +10555,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10489,7 +10596,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10575,7 +10682,7 @@
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10617,7 +10724,7 @@
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J160" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10659,7 +10766,7 @@
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J161" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10831,7 +10938,7 @@
       </c>
       <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J165" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10873,7 +10980,7 @@
       </c>
       <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J166" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10915,7 +11022,7 @@
       </c>
       <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J167" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11045,7 +11152,7 @@
       </c>
       <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J170" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11131,7 +11238,7 @@
       </c>
       <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J172" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11173,7 +11280,7 @@
       </c>
       <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J173" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11215,7 +11322,7 @@
       </c>
       <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J174" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11257,7 +11364,7 @@
       </c>
       <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J175" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11343,7 +11450,7 @@
       </c>
       <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J177" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11444,7 +11551,9 @@
         <v>정상</v>
       </c>
       <c r="K179" s="11"/>
-      <c r="L179" s="11"/>
+      <c r="L179" s="11">
+        <v>46101</v>
+      </c>
       <c r="M179" s="10"/>
       <c r="N179" s="10" t="s">
         <v>33</v>
@@ -11479,7 +11588,7 @@
       </c>
       <c r="I180" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J180" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11528,7 +11637,9 @@
         <v>정상</v>
       </c>
       <c r="K181" s="11"/>
-      <c r="L181" s="11"/>
+      <c r="L181" s="11">
+        <v>46101</v>
+      </c>
       <c r="M181" s="10"/>
       <c r="N181" s="10" t="s">
         <v>33</v>
@@ -11563,7 +11674,7 @@
       </c>
       <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J182" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11605,7 +11716,7 @@
       </c>
       <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J183" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11647,7 +11758,7 @@
       </c>
       <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J184" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11689,7 +11800,7 @@
       </c>
       <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J185" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11775,7 +11886,7 @@
       </c>
       <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J187" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11817,7 +11928,7 @@
       </c>
       <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J188" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11859,7 +11970,7 @@
       </c>
       <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J189" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11901,7 +12012,7 @@
       </c>
       <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J190" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11943,7 +12054,7 @@
       </c>
       <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J191" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11985,7 +12096,7 @@
       </c>
       <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J192" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12027,7 +12138,7 @@
       </c>
       <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J193" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12069,7 +12180,7 @@
       </c>
       <c r="I194" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J194" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12111,7 +12222,7 @@
       </c>
       <c r="I195" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J195" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12153,7 +12264,7 @@
       </c>
       <c r="I196" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J196" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12239,7 +12350,7 @@
       </c>
       <c r="I198" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J198" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12281,7 +12392,7 @@
       </c>
       <c r="I199" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J199" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12323,7 +12434,7 @@
       </c>
       <c r="I200" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J200" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12365,7 +12476,7 @@
       </c>
       <c r="I201" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J201" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12407,7 +12518,7 @@
       </c>
       <c r="I202" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J202" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12449,7 +12560,7 @@
       </c>
       <c r="I203" s="6">
         <f t="shared" ref="I203:I266" ca="1" si="16">IF(C203="","",IF(L203="",TODAY()-C203,L203-C203))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J203" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12491,7 +12602,7 @@
       </c>
       <c r="I204" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J204" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12533,7 +12644,7 @@
       </c>
       <c r="I205" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J205" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12575,7 +12686,7 @@
       </c>
       <c r="I206" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J206" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12617,7 +12728,7 @@
       </c>
       <c r="I207" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J207" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12659,7 +12770,7 @@
       </c>
       <c r="I208" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J208" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12701,7 +12812,7 @@
       </c>
       <c r="I209" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J209" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12743,7 +12854,7 @@
       </c>
       <c r="I210" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J210" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12785,7 +12896,7 @@
       </c>
       <c r="I211" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J211" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12827,7 +12938,7 @@
       </c>
       <c r="I212" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J212" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12869,7 +12980,7 @@
       </c>
       <c r="I213" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J213" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12911,7 +13022,7 @@
       </c>
       <c r="I214" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J214" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12953,7 +13064,7 @@
       </c>
       <c r="I215" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J215" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12995,7 +13106,7 @@
       </c>
       <c r="I216" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J216" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13037,7 +13148,7 @@
       </c>
       <c r="I217" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J217" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13123,7 +13234,7 @@
       </c>
       <c r="I219" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J219" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13209,7 +13320,7 @@
       </c>
       <c r="I221" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J221" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13251,7 +13362,7 @@
       </c>
       <c r="I222" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J222" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13293,7 +13404,7 @@
       </c>
       <c r="I223" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J223" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13335,7 +13446,7 @@
       </c>
       <c r="I224" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J224" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13377,7 +13488,7 @@
       </c>
       <c r="I225" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J225" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13419,7 +13530,7 @@
       </c>
       <c r="I226" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J226" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13461,7 +13572,7 @@
       </c>
       <c r="I227" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J227" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13503,7 +13614,7 @@
       </c>
       <c r="I228" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J228" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13545,7 +13656,7 @@
       </c>
       <c r="I229" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J229" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13587,7 +13698,7 @@
       </c>
       <c r="I230" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J230" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13629,7 +13740,7 @@
       </c>
       <c r="I231" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J231" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13671,7 +13782,7 @@
       </c>
       <c r="I232" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J232" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13713,7 +13824,7 @@
       </c>
       <c r="I233" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J233" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13799,7 +13910,7 @@
       </c>
       <c r="I235" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J235" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13841,7 +13952,7 @@
       </c>
       <c r="I236" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J236" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13883,7 +13994,7 @@
       </c>
       <c r="I237" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J237" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13925,7 +14036,7 @@
       </c>
       <c r="I238" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J238" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13967,7 +14078,7 @@
       </c>
       <c r="I239" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J239" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14009,7 +14120,7 @@
       </c>
       <c r="I240" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J240" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14051,7 +14162,7 @@
       </c>
       <c r="I241" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J241" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14093,7 +14204,7 @@
       </c>
       <c r="I242" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J242" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14135,10 +14246,10 @@
       </c>
       <c r="I243" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J243" s="13" t="str">
-        <f t="shared" ref="J243" ca="1" si="17">IF(I243="","",
+        <f t="shared" ref="J243:J252" ca="1" si="17">IF(I243="","",
  IF(G243="선급금",
    IF(I243&lt;=20,"정상",IF(I243&lt;=90,"관리","장기미수")),
  IF(G243="자재",
@@ -14160,193 +14271,372 @@
       <c r="S243" s="10"/>
     </row>
     <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B244" s="10" t="str">
+      <c r="B244" s="10">
         <f>IF(C244="","",COUNTA($C$2:C244))</f>
-        <v/>
-      </c>
-      <c r="C244" s="11"/>
-      <c r="D244" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H244" s="4"/>
-      <c r="I244" s="6" t="str">
+        <v>243</v>
+      </c>
+      <c r="C244" s="11">
+        <v>46101</v>
+      </c>
+      <c r="D244" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="F244" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="G244" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H244" s="4">
+        <v>10716800</v>
+      </c>
+      <c r="I244" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J244" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J244" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K244" s="11"/>
       <c r="L244" s="11"/>
       <c r="M244" s="10"/>
-      <c r="N244" s="10"/>
+      <c r="N244" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q244" s="11"/>
       <c r="R244" s="11"/>
       <c r="S244" s="10"/>
     </row>
     <row r="245" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B245" s="10"/>
-      <c r="C245" s="11"/>
-      <c r="D245" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H245" s="4"/>
-      <c r="I245" s="6" t="str">
+      <c r="B245" s="10">
+        <f>IF(C245="","",COUNTA($C$2:C245))</f>
+        <v>244</v>
+      </c>
+      <c r="C245" s="63">
+        <v>46101</v>
+      </c>
+      <c r="D245" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E245" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F245" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="G245" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="H245" s="4">
+        <v>9029600</v>
+      </c>
+      <c r="I245" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J245" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J245" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K245" s="11"/>
       <c r="L245" s="11"/>
       <c r="M245" s="10"/>
-      <c r="N245" s="10"/>
+      <c r="N245" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q245" s="11"/>
       <c r="R245" s="11"/>
       <c r="S245" s="10"/>
     </row>
     <row r="246" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B246" s="10"/>
-      <c r="C246" s="11"/>
-      <c r="D246" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H246" s="4"/>
-      <c r="I246" s="6" t="str">
+      <c r="B246" s="10">
+        <f>IF(C246="","",COUNTA($C$2:C246))</f>
+        <v>245</v>
+      </c>
+      <c r="C246" s="63">
+        <v>46101</v>
+      </c>
+      <c r="D246" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E246" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F246" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="G246" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="H246" s="4">
+        <v>6484400</v>
+      </c>
+      <c r="I246" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J246" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J246" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K246" s="11"/>
       <c r="L246" s="11"/>
       <c r="M246" s="10"/>
-      <c r="N246" s="10"/>
+      <c r="N246" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q246" s="11"/>
       <c r="R246" s="11"/>
       <c r="S246" s="10"/>
     </row>
     <row r="247" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B247" s="10"/>
-      <c r="C247" s="11"/>
-      <c r="D247" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H247" s="4"/>
-      <c r="I247" s="6" t="str">
+      <c r="B247" s="10">
+        <f>IF(C247="","",COUNTA($C$2:C247))</f>
+        <v>246</v>
+      </c>
+      <c r="C247" s="63">
+        <v>46101</v>
+      </c>
+      <c r="D247" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E247" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="F247" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="G247" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="H247" s="4">
+        <v>52857300</v>
+      </c>
+      <c r="I247" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J247" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J247" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K247" s="11"/>
       <c r="L247" s="11"/>
       <c r="M247" s="10"/>
-      <c r="N247" s="10"/>
+      <c r="N247" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q247" s="11"/>
       <c r="R247" s="11"/>
       <c r="S247" s="10"/>
     </row>
     <row r="248" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B248" s="10"/>
-      <c r="C248" s="11"/>
-      <c r="D248" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H248" s="4"/>
-      <c r="I248" s="6" t="str">
+      <c r="B248" s="10">
+        <f>IF(C248="","",COUNTA($C$2:C248))</f>
+        <v>247</v>
+      </c>
+      <c r="C248" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="D248" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E248" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="F248" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="G248" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="H248" s="25">
+        <v>114000</v>
+      </c>
+      <c r="I248" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J248" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J248" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K248" s="11"/>
       <c r="L248" s="11"/>
       <c r="M248" s="10"/>
-      <c r="N248" s="10"/>
+      <c r="N248" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q248" s="11"/>
       <c r="R248" s="11"/>
       <c r="S248" s="10"/>
     </row>
     <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B249" s="10"/>
-      <c r="C249" s="11"/>
-      <c r="D249" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H249" s="4"/>
-      <c r="I249" s="6" t="str">
+      <c r="B249" s="10">
+        <f>IF(C249="","",COUNTA($C$2:C249))</f>
+        <v>248</v>
+      </c>
+      <c r="C249" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="D249" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E249" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F249" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="G249" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="H249" s="25">
+        <v>9563000</v>
+      </c>
+      <c r="I249" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J249" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J249" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K249" s="11"/>
       <c r="L249" s="11"/>
       <c r="M249" s="10"/>
-      <c r="N249" s="10"/>
+      <c r="N249" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q249" s="11"/>
       <c r="R249" s="11"/>
       <c r="S249" s="10"/>
     </row>
     <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B250" s="10"/>
-      <c r="C250" s="11"/>
-      <c r="D250" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H250" s="4"/>
-      <c r="I250" s="6" t="str">
+      <c r="B250" s="10">
+        <f>IF(C250="","",COUNTA($C$2:C250))</f>
+        <v>249</v>
+      </c>
+      <c r="C250" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="D250" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E250" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F250" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="G250" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="H250" s="25">
+        <v>2270000</v>
+      </c>
+      <c r="I250" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J250" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J250" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K250" s="11"/>
       <c r="L250" s="11"/>
       <c r="M250" s="10"/>
-      <c r="N250" s="10"/>
+      <c r="N250" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q250" s="11"/>
       <c r="R250" s="11"/>
       <c r="S250" s="10"/>
     </row>
     <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B251" s="10"/>
-      <c r="C251" s="11"/>
-      <c r="D251" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H251" s="4"/>
-      <c r="I251" s="6" t="str">
+      <c r="B251" s="10">
+        <f>IF(C251="","",COUNTA($C$2:C251))</f>
+        <v>250</v>
+      </c>
+      <c r="C251" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E251" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="F251" s="23" t="s">
+        <v>400</v>
+      </c>
+      <c r="G251" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="H251" s="25">
+        <v>121500</v>
+      </c>
+      <c r="I251" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J251" s="13"/>
+        <v>0</v>
+      </c>
+      <c r="J251" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K251" s="11"/>
-      <c r="L251" s="11"/>
+      <c r="L251" s="11">
+        <v>46101</v>
+      </c>
       <c r="M251" s="10"/>
-      <c r="N251" s="10"/>
+      <c r="N251" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q251" s="11"/>
       <c r="R251" s="11"/>
       <c r="S251" s="10"/>
     </row>
     <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B252" s="10"/>
-      <c r="C252" s="11"/>
-      <c r="D252" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H252" s="4"/>
-      <c r="I252" s="6" t="str">
+      <c r="B252" s="10">
+        <f>IF(C252="","",COUNTA($C$2:C252))</f>
+        <v>251</v>
+      </c>
+      <c r="C252" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E252" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F252" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="G252" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="H252" s="25">
+        <v>658000</v>
+      </c>
+      <c r="I252" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J252" s="13"/>
+        <v>3</v>
+      </c>
+      <c r="J252" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K252" s="11"/>
       <c r="L252" s="11"/>
       <c r="M252" s="10"/>
-      <c r="N252" s="10"/>
+      <c r="N252" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q252" s="11"/>
       <c r="R252" s="11"/>
       <c r="S252" s="10"/>
@@ -17568,310 +17858,345 @@
   <autoFilter ref="A1:S407"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="68" priority="83">
+    <cfRule type="expression" dxfId="73" priority="90">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="67" priority="82">
+    <cfRule type="expression" dxfId="72" priority="89">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="66" priority="81">
+    <cfRule type="expression" dxfId="71" priority="88">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="65" priority="80">
+    <cfRule type="expression" dxfId="70" priority="87">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="64" priority="75">
+    <cfRule type="expression" dxfId="69" priority="82">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99 E186:F192 H186:H192 C186:C192">
-    <cfRule type="expression" dxfId="63" priority="65">
+    <cfRule type="expression" dxfId="68" priority="72">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="62" priority="64">
+    <cfRule type="expression" dxfId="67" priority="71">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="61" priority="62">
+    <cfRule type="expression" dxfId="66" priority="69">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="60" priority="61">
+    <cfRule type="expression" dxfId="65" priority="68">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="59" priority="60">
+    <cfRule type="expression" dxfId="64" priority="67">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="58" priority="59">
+    <cfRule type="expression" dxfId="63" priority="66">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="57" priority="58">
+    <cfRule type="expression" dxfId="62" priority="65">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="56" priority="57">
+    <cfRule type="expression" dxfId="61" priority="64">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="55" priority="56">
+    <cfRule type="expression" dxfId="60" priority="63">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="54" priority="55">
+    <cfRule type="expression" dxfId="59" priority="62">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="53" priority="54">
+    <cfRule type="expression" dxfId="58" priority="61">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="52" priority="53">
+    <cfRule type="expression" dxfId="57" priority="60">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="51" priority="52">
+    <cfRule type="expression" dxfId="56" priority="59">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="50" priority="51">
+    <cfRule type="expression" dxfId="55" priority="58">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="49" priority="50">
+    <cfRule type="expression" dxfId="54" priority="57">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="48" priority="49">
+    <cfRule type="expression" dxfId="53" priority="56">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="47" priority="48">
+    <cfRule type="expression" dxfId="52" priority="55">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="46" priority="47">
+    <cfRule type="expression" dxfId="51" priority="54">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="45" priority="46">
+    <cfRule type="expression" dxfId="50" priority="53">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="44" priority="44">
+    <cfRule type="expression" dxfId="49" priority="51">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="43" priority="43">
+    <cfRule type="expression" dxfId="48" priority="50">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="42" priority="42">
+    <cfRule type="expression" dxfId="47" priority="49">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="41" priority="41">
+    <cfRule type="expression" dxfId="46" priority="48">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="40" priority="40">
+    <cfRule type="expression" dxfId="45" priority="47">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="39" priority="39">
+    <cfRule type="expression" dxfId="44" priority="46">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="38" priority="38">
+    <cfRule type="expression" dxfId="43" priority="45">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="37" priority="37">
+    <cfRule type="expression" dxfId="42" priority="44">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="36" priority="36">
+    <cfRule type="expression" dxfId="41" priority="43">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
-    <cfRule type="expression" dxfId="35" priority="35">
+    <cfRule type="expression" dxfId="40" priority="42">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179:F185">
-    <cfRule type="expression" dxfId="34" priority="34">
+    <cfRule type="expression" dxfId="39" priority="41">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E178">
-    <cfRule type="expression" dxfId="33" priority="33">
+    <cfRule type="expression" dxfId="38" priority="40">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E179:E185">
-    <cfRule type="expression" dxfId="32" priority="32">
+    <cfRule type="expression" dxfId="37" priority="39">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166:C178">
-    <cfRule type="expression" dxfId="31" priority="31">
+    <cfRule type="expression" dxfId="36" priority="38">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="30" priority="30">
+    <cfRule type="expression" dxfId="35" priority="37">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="29" priority="29">
+    <cfRule type="expression" dxfId="34" priority="36">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H179:H185">
-    <cfRule type="expression" dxfId="28" priority="28">
+    <cfRule type="expression" dxfId="33" priority="35">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F194:F200">
-    <cfRule type="expression" dxfId="27" priority="23">
+    <cfRule type="expression" dxfId="32" priority="30">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E194:E200">
-    <cfRule type="expression" dxfId="26" priority="22">
+    <cfRule type="expression" dxfId="31" priority="29">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C194:C201">
-    <cfRule type="expression" dxfId="25" priority="21">
+    <cfRule type="expression" dxfId="30" priority="28">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H194:H200">
-    <cfRule type="expression" dxfId="24" priority="20">
+    <cfRule type="expression" dxfId="29" priority="27">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C202:C215">
-    <cfRule type="expression" dxfId="23" priority="19">
+    <cfRule type="expression" dxfId="28" priority="26">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F202:F215">
-    <cfRule type="expression" dxfId="22" priority="18">
+    <cfRule type="expression" dxfId="27" priority="25">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H202:H215">
-    <cfRule type="expression" dxfId="21" priority="17">
+    <cfRule type="expression" dxfId="26" priority="24">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E202:E216">
-    <cfRule type="expression" dxfId="20" priority="16">
+    <cfRule type="expression" dxfId="25" priority="23">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C216">
-    <cfRule type="expression" dxfId="19" priority="15">
+    <cfRule type="expression" dxfId="24" priority="22">
       <formula>$I216="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H216">
-    <cfRule type="expression" dxfId="18" priority="10">
+    <cfRule type="expression" dxfId="23" priority="17">
       <formula>$I216="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C217">
-    <cfRule type="expression" dxfId="17" priority="9">
+    <cfRule type="expression" dxfId="22" priority="16">
       <formula>$I217="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="21" priority="15">
       <formula>$I218="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C219">
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="20" priority="14">
       <formula>$I219="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F220:F229">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="19" priority="13">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F230:F243">
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="18" priority="12">
       <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E220:E229">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="17" priority="11">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E230:E243">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="16" priority="10">
       <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H220:H229">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H230:H243">
+    <cfRule type="expression" dxfId="14" priority="8">
+      <formula>$J230="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C245">
+    <cfRule type="expression" dxfId="13" priority="7">
+      <formula>$I245="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C246">
+    <cfRule type="expression" dxfId="12" priority="6">
+      <formula>$I246="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C247">
+    <cfRule type="expression" dxfId="11" priority="5">
+      <formula>$I247="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F248:F252">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>$J248="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E248:E252">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$J248="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C248:C252">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$J248="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H248:H252">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J230="잔금"</formula>
+      <formula>$J248="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N243">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N252">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D407">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1921,7 +1921,7 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="74">
+  <dxfs count="67">
     <dxf>
       <fill>
         <patternFill>
@@ -1966,81 +1966,6 @@
           <color auto="1"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -3409,7 +3334,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I56" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J2" s="13" t="str">
         <f ca="1">IF(I2="","",
@@ -3534,7 +3459,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3632,7 +3557,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3688,7 +3613,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3737,7 +3662,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3788,7 +3713,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -3840,11 +3765,11 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>관리</v>
+        <v>장기미수</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -3979,7 +3904,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4035,7 +3960,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4084,7 +4009,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4133,7 +4058,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4180,7 +4105,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4227,7 +4152,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4274,7 +4199,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4321,7 +4246,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4368,7 +4293,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4417,7 +4342,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4466,7 +4391,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4515,7 +4440,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4564,7 +4489,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4613,7 +4538,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4662,7 +4587,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4711,7 +4636,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4760,7 +4685,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4809,7 +4734,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4858,7 +4783,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4907,7 +4832,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4956,7 +4881,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5005,7 +4930,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5054,7 +4979,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5103,7 +5028,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5148,7 +5073,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5202,7 +5127,7 @@
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5258,7 +5183,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5311,7 +5236,7 @@
       </c>
       <c r="I40" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5320,7 +5245,9 @@
       <c r="K40" s="11">
         <v>46063</v>
       </c>
-      <c r="L40" s="11"/>
+      <c r="L40" s="11">
+        <v>46105</v>
+      </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10" t="s">
         <v>20</v>
@@ -5358,7 +5285,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5412,7 +5339,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5517,7 +5444,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5666,7 +5593,7 @@
       </c>
       <c r="I47" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J47" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5675,7 +5602,9 @@
       <c r="K47" s="11">
         <v>46063</v>
       </c>
-      <c r="L47" s="11"/>
+      <c r="L47" s="11">
+        <v>46105</v>
+      </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10" t="s">
         <v>20</v>
@@ -5713,7 +5642,7 @@
       </c>
       <c r="I48" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J48" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5722,7 +5651,9 @@
       <c r="K48" s="11">
         <v>46063</v>
       </c>
-      <c r="L48" s="11"/>
+      <c r="L48" s="11">
+        <v>46105</v>
+      </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10" t="s">
         <v>20</v>
@@ -6146,7 +6077,7 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57:I66" ca="1" si="4">IF(C57="","",IF(L57="",TODAY()-C57,L57-C57))</f>
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J57" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6193,7 +6124,7 @@
       </c>
       <c r="I58" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J58" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6240,7 +6171,7 @@
       </c>
       <c r="I59" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J59" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -6287,7 +6218,7 @@
       </c>
       <c r="I60" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J60" s="13" t="str">
         <f t="shared" ref="J60:J114" ca="1" si="5">IF(I60="","",
@@ -6578,7 +6509,7 @@
       </c>
       <c r="I66" s="12">
         <f t="shared" ca="1" si="4"/>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J66" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6622,7 +6553,7 @@
       </c>
       <c r="I67" s="6">
         <f t="shared" ref="I67:I72" ca="1" si="7">IF(C67="","",IF(L67="",TODAY()-C67,L67-C67))</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J67" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -6907,7 +6838,7 @@
       </c>
       <c r="I73" s="6">
         <f t="shared" ref="I73:I76" ca="1" si="8">IF(C73="","",IF(L73="",TODAY()-C73,L73-C73))</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J73" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7052,7 +6983,7 @@
       </c>
       <c r="I76" s="6">
         <f t="shared" ca="1" si="8"/>
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J76" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7290,7 +7221,7 @@
       </c>
       <c r="I81" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J81" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7376,7 +7307,7 @@
       </c>
       <c r="I83" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J83" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7482,7 +7413,7 @@
       </c>
       <c r="I85" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J85" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7534,7 +7465,7 @@
       </c>
       <c r="I86" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J86" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7576,7 +7507,7 @@
       </c>
       <c r="I87" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J87" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7672,7 +7603,7 @@
       </c>
       <c r="I89" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J89" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7724,7 +7655,7 @@
       </c>
       <c r="I90" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J90" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7820,7 +7751,7 @@
       </c>
       <c r="I92" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J92" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -7994,7 +7925,7 @@
       </c>
       <c r="I96" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J96" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8080,7 +8011,7 @@
       </c>
       <c r="I98" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J98" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8122,7 +8053,7 @@
       </c>
       <c r="I99" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J99" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8163,7 +8094,7 @@
       </c>
       <c r="I100" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J100" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8336,11 +8267,11 @@
       </c>
       <c r="I104" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J104" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K104" s="11"/>
       <c r="L104" s="11"/>
@@ -8378,11 +8309,11 @@
       </c>
       <c r="I105" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J105" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K105" s="11"/>
       <c r="L105" s="11"/>
@@ -8419,11 +8350,11 @@
       </c>
       <c r="I106" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J106" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K106" s="11"/>
       <c r="L106" s="11"/>
@@ -8506,11 +8437,11 @@
       </c>
       <c r="I108" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J108" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K108" s="11"/>
       <c r="L108" s="11"/>
@@ -8547,7 +8478,7 @@
       </c>
       <c r="I109" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J109" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8588,7 +8519,7 @@
       </c>
       <c r="I110" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J110" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8677,7 +8608,7 @@
       </c>
       <c r="I112" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J112" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8766,7 +8697,7 @@
       </c>
       <c r="I114" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J114" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8811,7 +8742,7 @@
       </c>
       <c r="I115" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J115" s="13" t="str">
         <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
@@ -8908,7 +8839,7 @@
       </c>
       <c r="I117" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J117" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -8994,7 +8925,7 @@
       </c>
       <c r="I119" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J119" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9127,7 +9058,7 @@
       </c>
       <c r="I122" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J122" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9169,7 +9100,7 @@
       </c>
       <c r="I123" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J123" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9255,7 +9186,7 @@
       </c>
       <c r="I125" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J125" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9332,7 +9263,7 @@
       </c>
       <c r="I127" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J127" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9374,7 +9305,7 @@
       </c>
       <c r="I128" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J128" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9416,7 +9347,7 @@
       </c>
       <c r="I129" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J129" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9458,7 +9389,7 @@
       </c>
       <c r="I130" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J130" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9632,7 +9563,7 @@
       </c>
       <c r="I134" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J134" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9674,7 +9605,7 @@
       </c>
       <c r="I135" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J135" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9716,7 +9647,7 @@
       </c>
       <c r="I136" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J136" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9934,7 +9865,7 @@
       </c>
       <c r="I141" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9975,7 +9906,7 @@
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J142" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10016,7 +9947,7 @@
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J143" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10057,7 +9988,7 @@
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J144" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10098,7 +10029,7 @@
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J145" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10139,7 +10070,7 @@
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J146" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10180,7 +10111,7 @@
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J147" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10221,7 +10152,7 @@
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J148" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10262,7 +10193,7 @@
       </c>
       <c r="I149" s="6">
         <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J149" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10303,7 +10234,7 @@
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10387,7 +10318,7 @@
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10514,7 +10445,7 @@
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10555,7 +10486,7 @@
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J156" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10596,7 +10527,7 @@
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J157" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10682,7 +10613,7 @@
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10724,7 +10655,7 @@
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J160" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10766,7 +10697,7 @@
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J161" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10938,7 +10869,7 @@
       </c>
       <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J165" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10980,7 +10911,7 @@
       </c>
       <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J166" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11022,7 +10953,7 @@
       </c>
       <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J167" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11152,7 +11083,7 @@
       </c>
       <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J170" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11238,7 +11169,7 @@
       </c>
       <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J172" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11280,7 +11211,7 @@
       </c>
       <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J173" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11322,7 +11253,7 @@
       </c>
       <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J174" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11364,7 +11295,7 @@
       </c>
       <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J175" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11450,7 +11381,7 @@
       </c>
       <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J177" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11588,7 +11519,7 @@
       </c>
       <c r="I180" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J180" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11674,7 +11605,7 @@
       </c>
       <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J182" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11716,7 +11647,7 @@
       </c>
       <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J183" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11758,7 +11689,7 @@
       </c>
       <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J184" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11800,7 +11731,7 @@
       </c>
       <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J185" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11886,7 +11817,7 @@
       </c>
       <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J187" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11928,7 +11859,7 @@
       </c>
       <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J188" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -11970,7 +11901,7 @@
       </c>
       <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J189" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12012,7 +11943,7 @@
       </c>
       <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J190" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12054,7 +11985,7 @@
       </c>
       <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J191" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12096,7 +12027,7 @@
       </c>
       <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J192" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12138,7 +12069,7 @@
       </c>
       <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J193" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12180,7 +12111,7 @@
       </c>
       <c r="I194" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J194" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12222,7 +12153,7 @@
       </c>
       <c r="I195" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J195" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12264,7 +12195,7 @@
       </c>
       <c r="I196" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J196" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12350,7 +12281,7 @@
       </c>
       <c r="I198" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J198" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12392,7 +12323,7 @@
       </c>
       <c r="I199" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J199" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12434,7 +12365,7 @@
       </c>
       <c r="I200" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J200" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12476,7 +12407,7 @@
       </c>
       <c r="I201" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J201" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12518,7 +12449,7 @@
       </c>
       <c r="I202" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J202" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12560,7 +12491,7 @@
       </c>
       <c r="I203" s="6">
         <f t="shared" ref="I203:I266" ca="1" si="16">IF(C203="","",IF(L203="",TODAY()-C203,L203-C203))</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J203" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12602,7 +12533,7 @@
       </c>
       <c r="I204" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J204" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12644,7 +12575,7 @@
       </c>
       <c r="I205" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J205" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12686,7 +12617,7 @@
       </c>
       <c r="I206" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J206" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12728,7 +12659,7 @@
       </c>
       <c r="I207" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J207" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12770,7 +12701,7 @@
       </c>
       <c r="I208" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J208" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12812,7 +12743,7 @@
       </c>
       <c r="I209" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J209" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12854,14 +12785,16 @@
       </c>
       <c r="I210" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J210" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K210" s="11"/>
-      <c r="L210" s="11"/>
+      <c r="L210" s="11">
+        <v>46105</v>
+      </c>
       <c r="M210" s="10"/>
       <c r="N210" s="10" t="s">
         <v>33</v>
@@ -12896,7 +12829,7 @@
       </c>
       <c r="I211" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J211" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12938,7 +12871,7 @@
       </c>
       <c r="I212" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J212" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12980,7 +12913,7 @@
       </c>
       <c r="I213" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J213" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13022,7 +12955,7 @@
       </c>
       <c r="I214" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J214" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13064,7 +12997,7 @@
       </c>
       <c r="I215" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J215" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13106,7 +13039,7 @@
       </c>
       <c r="I216" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J216" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13148,7 +13081,7 @@
       </c>
       <c r="I217" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J217" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13234,7 +13167,7 @@
       </c>
       <c r="I219" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J219" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13320,7 +13253,7 @@
       </c>
       <c r="I221" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J221" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13362,7 +13295,7 @@
       </c>
       <c r="I222" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J222" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13404,7 +13337,7 @@
       </c>
       <c r="I223" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J223" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13446,7 +13379,7 @@
       </c>
       <c r="I224" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J224" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13488,7 +13421,7 @@
       </c>
       <c r="I225" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J225" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13530,7 +13463,7 @@
       </c>
       <c r="I226" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J226" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13572,7 +13505,7 @@
       </c>
       <c r="I227" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J227" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13614,7 +13547,7 @@
       </c>
       <c r="I228" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J228" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13656,7 +13589,7 @@
       </c>
       <c r="I229" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J229" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13698,7 +13631,7 @@
       </c>
       <c r="I230" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J230" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13740,7 +13673,7 @@
       </c>
       <c r="I231" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J231" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13782,7 +13715,7 @@
       </c>
       <c r="I232" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J232" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13824,7 +13757,7 @@
       </c>
       <c r="I233" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J233" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13910,7 +13843,7 @@
       </c>
       <c r="I235" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J235" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13952,7 +13885,7 @@
       </c>
       <c r="I236" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J236" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13994,7 +13927,7 @@
       </c>
       <c r="I237" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J237" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14036,7 +13969,7 @@
       </c>
       <c r="I238" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J238" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14078,7 +14011,7 @@
       </c>
       <c r="I239" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J239" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14120,7 +14053,7 @@
       </c>
       <c r="I240" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J240" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14162,7 +14095,7 @@
       </c>
       <c r="I241" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J241" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14204,7 +14137,7 @@
       </c>
       <c r="I242" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J242" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14246,7 +14179,7 @@
       </c>
       <c r="I243" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J243" s="13" t="str">
         <f t="shared" ref="J243:J252" ca="1" si="17">IF(I243="","",
@@ -14295,7 +14228,7 @@
       </c>
       <c r="I244" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J244" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14336,7 +14269,7 @@
       </c>
       <c r="I245" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J245" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14377,7 +14310,7 @@
       </c>
       <c r="I246" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J246" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14418,7 +14351,7 @@
       </c>
       <c r="I247" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J247" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14459,7 +14392,7 @@
       </c>
       <c r="I248" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J248" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14500,7 +14433,7 @@
       </c>
       <c r="I249" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J249" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14541,7 +14474,7 @@
       </c>
       <c r="I250" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J250" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14625,7 +14558,7 @@
       </c>
       <c r="I252" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J252" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -17858,332 +17791,332 @@
   <autoFilter ref="A1:S407"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="73" priority="90">
+    <cfRule type="expression" dxfId="66" priority="90">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="72" priority="89">
+    <cfRule type="expression" dxfId="65" priority="89">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="71" priority="88">
+    <cfRule type="expression" dxfId="64" priority="88">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="70" priority="87">
+    <cfRule type="expression" dxfId="63" priority="87">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="69" priority="82">
+    <cfRule type="expression" dxfId="62" priority="82">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99 E186:F192 H186:H192 C186:C192">
-    <cfRule type="expression" dxfId="68" priority="72">
+    <cfRule type="expression" dxfId="61" priority="72">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="67" priority="71">
+    <cfRule type="expression" dxfId="60" priority="71">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="66" priority="69">
+    <cfRule type="expression" dxfId="59" priority="69">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="65" priority="68">
+    <cfRule type="expression" dxfId="58" priority="68">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="64" priority="67">
+    <cfRule type="expression" dxfId="57" priority="67">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="63" priority="66">
+    <cfRule type="expression" dxfId="56" priority="66">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="62" priority="65">
+    <cfRule type="expression" dxfId="55" priority="65">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="61" priority="64">
+    <cfRule type="expression" dxfId="54" priority="64">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="60" priority="63">
+    <cfRule type="expression" dxfId="53" priority="63">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="59" priority="62">
+    <cfRule type="expression" dxfId="52" priority="62">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="58" priority="61">
+    <cfRule type="expression" dxfId="51" priority="61">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="57" priority="60">
+    <cfRule type="expression" dxfId="50" priority="60">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="56" priority="59">
+    <cfRule type="expression" dxfId="49" priority="59">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="55" priority="58">
+    <cfRule type="expression" dxfId="48" priority="58">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="54" priority="57">
+    <cfRule type="expression" dxfId="47" priority="57">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="53" priority="56">
+    <cfRule type="expression" dxfId="46" priority="56">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="52" priority="55">
+    <cfRule type="expression" dxfId="45" priority="55">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="51" priority="54">
+    <cfRule type="expression" dxfId="44" priority="54">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="50" priority="53">
+    <cfRule type="expression" dxfId="43" priority="53">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="49" priority="51">
+    <cfRule type="expression" dxfId="42" priority="51">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="48" priority="50">
+    <cfRule type="expression" dxfId="41" priority="50">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="47" priority="49">
+    <cfRule type="expression" dxfId="40" priority="49">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="46" priority="48">
+    <cfRule type="expression" dxfId="39" priority="48">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="45" priority="47">
+    <cfRule type="expression" dxfId="38" priority="47">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="44" priority="46">
+    <cfRule type="expression" dxfId="37" priority="46">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="43" priority="45">
+    <cfRule type="expression" dxfId="36" priority="45">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="42" priority="44">
+    <cfRule type="expression" dxfId="35" priority="44">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="41" priority="43">
+    <cfRule type="expression" dxfId="34" priority="43">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
-    <cfRule type="expression" dxfId="40" priority="42">
+    <cfRule type="expression" dxfId="33" priority="42">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179:F185">
-    <cfRule type="expression" dxfId="39" priority="41">
+    <cfRule type="expression" dxfId="32" priority="41">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E178">
-    <cfRule type="expression" dxfId="38" priority="40">
+    <cfRule type="expression" dxfId="31" priority="40">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E179:E185">
-    <cfRule type="expression" dxfId="37" priority="39">
+    <cfRule type="expression" dxfId="30" priority="39">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166:C178">
-    <cfRule type="expression" dxfId="36" priority="38">
+    <cfRule type="expression" dxfId="29" priority="38">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="35" priority="37">
+    <cfRule type="expression" dxfId="28" priority="37">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="34" priority="36">
+    <cfRule type="expression" dxfId="27" priority="36">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H179:H185">
-    <cfRule type="expression" dxfId="33" priority="35">
+    <cfRule type="expression" dxfId="26" priority="35">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F194:F200">
-    <cfRule type="expression" dxfId="32" priority="30">
+    <cfRule type="expression" dxfId="25" priority="30">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E194:E200">
-    <cfRule type="expression" dxfId="31" priority="29">
+    <cfRule type="expression" dxfId="24" priority="29">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C194:C201">
-    <cfRule type="expression" dxfId="30" priority="28">
+    <cfRule type="expression" dxfId="23" priority="28">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H194:H200">
-    <cfRule type="expression" dxfId="29" priority="27">
+    <cfRule type="expression" dxfId="22" priority="27">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C202:C215">
-    <cfRule type="expression" dxfId="28" priority="26">
+    <cfRule type="expression" dxfId="21" priority="26">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F202:F215">
-    <cfRule type="expression" dxfId="27" priority="25">
+    <cfRule type="expression" dxfId="20" priority="25">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H202:H215">
-    <cfRule type="expression" dxfId="26" priority="24">
+    <cfRule type="expression" dxfId="19" priority="24">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E202:E216">
-    <cfRule type="expression" dxfId="25" priority="23">
+    <cfRule type="expression" dxfId="18" priority="23">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C216">
-    <cfRule type="expression" dxfId="24" priority="22">
+    <cfRule type="expression" dxfId="17" priority="22">
       <formula>$I216="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H216">
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="16" priority="17">
       <formula>$I216="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C217">
-    <cfRule type="expression" dxfId="22" priority="16">
+    <cfRule type="expression" dxfId="15" priority="16">
       <formula>$I217="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218">
-    <cfRule type="expression" dxfId="21" priority="15">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>$I218="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C219">
-    <cfRule type="expression" dxfId="20" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>$I219="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F220:F229">
-    <cfRule type="expression" dxfId="19" priority="13">
+    <cfRule type="expression" dxfId="12" priority="13">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F230:F243">
-    <cfRule type="expression" dxfId="18" priority="12">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E220:E229">
-    <cfRule type="expression" dxfId="17" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E230:E243">
-    <cfRule type="expression" dxfId="16" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H220:H229">
-    <cfRule type="expression" dxfId="15" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H230:H243">
-    <cfRule type="expression" dxfId="14" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C245">
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$I245="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C246">
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$I246="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C247">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$I247="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F248:F252">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$J248="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E248:E252">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$J248="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C248:C252">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$J248="잔금"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="440">
   <si>
     <t>순번</t>
   </si>
@@ -1457,6 +1457,133 @@
   </si>
   <si>
     <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>강서힐스테이트</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜석민이앤씨</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자양10차현대홈타운</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>여름건설(주)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>한보구암마을아파트</t>
+  </si>
+  <si>
+    <t>암사동한솔아파트</t>
+  </si>
+  <si>
+    <t>선급금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜케이탑건설</t>
+  </si>
+  <si>
+    <t>㈜적산건설</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>호연상사</t>
+  </si>
+  <si>
+    <t>(주)조광피엔텍</t>
+  </si>
+  <si>
+    <t>(주)미사건설</t>
+  </si>
+  <si>
+    <t>수원로얄팰리스</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>광교자연앤힐스테이트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>경남여성가족재단</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>인성마을신갈현대</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>효천1중흥s크래스</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>수지동보1차</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>에듀타운자이1단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>동부산아이존빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>불당지웰시티푸르지오1단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>하안주공7단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>해운대센텀트루엘2단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>보령광명샤인빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>동탄역시범리슈빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>속초청초대우</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>상계주공14단지</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>불암현대</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>천안역우방아이유쉘</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>호매실경남아너스빌</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>시흥참이슬아파트</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>자재</t>
@@ -1921,7 +2048,92 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="74">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -14182,7 +14394,7 @@
         <v>6</v>
       </c>
       <c r="J243" s="13" t="str">
-        <f t="shared" ref="J243:J252" ca="1" si="17">IF(I243="","",
+        <f t="shared" ref="J243:J275" ca="1" si="17">IF(I243="","",
  IF(G243="선급금",
    IF(I243&lt;=20,"정상",IF(I243&lt;=90,"관리","장기미수")),
  IF(G243="자재",
@@ -14575,484 +14787,965 @@
       <c r="S252" s="10"/>
     </row>
     <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B253" s="10"/>
-      <c r="C253" s="11"/>
-      <c r="D253" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H253" s="4"/>
-      <c r="I253" s="6" t="str">
+      <c r="B253" s="10">
+        <f>IF(C253="","",COUNTA($C$2:C253))</f>
+        <v>252</v>
+      </c>
+      <c r="C253" s="63">
+        <v>46104</v>
+      </c>
+      <c r="D253" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E253" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="F253" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="G253" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H253" s="4">
+        <v>23835400</v>
+      </c>
+      <c r="I253" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J253" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J253" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K253" s="11"/>
       <c r="L253" s="11"/>
       <c r="M253" s="10"/>
-      <c r="N253" s="10"/>
+      <c r="N253" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q253" s="11"/>
       <c r="R253" s="11"/>
       <c r="S253" s="10"/>
     </row>
     <row r="254" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B254" s="10"/>
-      <c r="C254" s="11"/>
-      <c r="D254" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H254" s="4"/>
-      <c r="I254" s="6" t="str">
+      <c r="B254" s="10">
+        <f>IF(C254="","",COUNTA($C$2:C254))</f>
+        <v>253</v>
+      </c>
+      <c r="C254" s="63">
+        <v>46104</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E254" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="F254" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G254" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H254" s="4">
+        <v>8708400</v>
+      </c>
+      <c r="I254" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J254" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J254" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K254" s="11"/>
       <c r="L254" s="11"/>
       <c r="M254" s="10"/>
-      <c r="N254" s="10"/>
+      <c r="N254" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q254" s="11"/>
       <c r="R254" s="11"/>
       <c r="S254" s="10"/>
     </row>
     <row r="255" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B255" s="10"/>
-      <c r="C255" s="11"/>
+      <c r="B255" s="10">
+        <f>IF(C255="","",COUNTA($C$2:C255))</f>
+        <v>254</v>
+      </c>
+      <c r="C255" s="63">
+        <v>46105</v>
+      </c>
       <c r="D255" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H255" s="4"/>
-      <c r="I255" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E255" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="F255" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="G255" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H255" s="4">
+        <v>8559000</v>
+      </c>
+      <c r="I255" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J255" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J255" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K255" s="11"/>
       <c r="L255" s="11"/>
       <c r="M255" s="10"/>
-      <c r="N255" s="10"/>
+      <c r="N255" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q255" s="11"/>
       <c r="R255" s="11"/>
       <c r="S255" s="10"/>
     </row>
     <row r="256" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B256" s="10"/>
-      <c r="C256" s="11"/>
+      <c r="B256" s="10">
+        <f>IF(C256="","",COUNTA($C$2:C256))</f>
+        <v>255</v>
+      </c>
+      <c r="C256" s="63">
+        <v>46105</v>
+      </c>
       <c r="D256" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H256" s="4"/>
-      <c r="I256" s="6" t="str">
+        <v>A</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="F256" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="G256" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="H256" s="4">
+        <v>3281000</v>
+      </c>
+      <c r="I256" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J256" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J256" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K256" s="11"/>
       <c r="L256" s="11"/>
       <c r="M256" s="10"/>
-      <c r="N256" s="10"/>
+      <c r="N256" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q256" s="11"/>
       <c r="R256" s="11"/>
       <c r="S256" s="10"/>
     </row>
     <row r="257" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B257" s="10"/>
-      <c r="C257" s="11"/>
+      <c r="B257" s="10">
+        <f>IF(C257="","",COUNTA($C$2:C257))</f>
+        <v>256</v>
+      </c>
+      <c r="C257" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D257" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H257" s="4"/>
-      <c r="I257" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E257" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F257" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="G257" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H257" s="4">
+        <v>4290000</v>
+      </c>
+      <c r="I257" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J257" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J257" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K257" s="11"/>
       <c r="L257" s="11"/>
       <c r="M257" s="10"/>
-      <c r="N257" s="10"/>
+      <c r="N257" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q257" s="11"/>
       <c r="R257" s="11"/>
       <c r="S257" s="10"/>
     </row>
     <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B258" s="10"/>
-      <c r="C258" s="11"/>
+      <c r="B258" s="10">
+        <f>IF(C258="","",COUNTA($C$2:C258))</f>
+        <v>257</v>
+      </c>
+      <c r="C258" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D258" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H258" s="4"/>
-      <c r="I258" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="F258" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="G258" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H258" s="4">
+        <v>8800000</v>
+      </c>
+      <c r="I258" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J258" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J258" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K258" s="11"/>
       <c r="L258" s="11"/>
       <c r="M258" s="10"/>
-      <c r="N258" s="10"/>
+      <c r="N258" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q258" s="11"/>
       <c r="R258" s="11"/>
       <c r="S258" s="10"/>
     </row>
     <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B259" s="10"/>
-      <c r="C259" s="11"/>
+      <c r="B259" s="10">
+        <f>IF(C259="","",COUNTA($C$2:C259))</f>
+        <v>258</v>
+      </c>
+      <c r="C259" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D259" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H259" s="4"/>
-      <c r="I259" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F259" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="G259" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H259" s="4">
+        <v>465000</v>
+      </c>
+      <c r="I259" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J259" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J259" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K259" s="11"/>
       <c r="L259" s="11"/>
       <c r="M259" s="10"/>
-      <c r="N259" s="10"/>
+      <c r="N259" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q259" s="11"/>
       <c r="R259" s="11"/>
       <c r="S259" s="10"/>
     </row>
     <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B260" s="10"/>
-      <c r="C260" s="11"/>
+      <c r="B260" s="10">
+        <f>IF(C260="","",COUNTA($C$2:C260))</f>
+        <v>259</v>
+      </c>
+      <c r="C260" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D260" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H260" s="4"/>
-      <c r="I260" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F260" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="G260" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H260" s="4">
+        <v>5765500</v>
+      </c>
+      <c r="I260" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J260" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J260" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K260" s="11"/>
       <c r="L260" s="11"/>
       <c r="M260" s="10"/>
-      <c r="N260" s="10"/>
+      <c r="N260" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q260" s="11"/>
       <c r="R260" s="11"/>
       <c r="S260" s="10"/>
     </row>
     <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B261" s="10"/>
-      <c r="C261" s="11"/>
+      <c r="B261" s="10">
+        <f>IF(C261="","",COUNTA($C$2:C261))</f>
+        <v>260</v>
+      </c>
+      <c r="C261" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D261" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H261" s="4"/>
-      <c r="I261" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F261" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="G261" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H261" s="4">
+        <v>222000</v>
+      </c>
+      <c r="I261" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J261" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J261" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K261" s="11"/>
       <c r="L261" s="11"/>
       <c r="M261" s="10"/>
-      <c r="N261" s="10"/>
+      <c r="N261" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q261" s="11"/>
       <c r="R261" s="11"/>
       <c r="S261" s="10"/>
     </row>
     <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B262" s="10"/>
-      <c r="C262" s="11"/>
+      <c r="B262" s="10">
+        <f>IF(C262="","",COUNTA($C$2:C262))</f>
+        <v>261</v>
+      </c>
+      <c r="C262" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D262" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H262" s="4"/>
-      <c r="I262" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F262" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="G262" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H262" s="4">
+        <v>1866000</v>
+      </c>
+      <c r="I262" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J262" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J262" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K262" s="11"/>
       <c r="L262" s="11"/>
       <c r="M262" s="10"/>
-      <c r="N262" s="10"/>
+      <c r="N262" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q262" s="11"/>
       <c r="R262" s="11"/>
       <c r="S262" s="10"/>
     </row>
     <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B263" s="10"/>
-      <c r="C263" s="11"/>
+      <c r="B263" s="10">
+        <f>IF(C263="","",COUNTA($C$2:C263))</f>
+        <v>262</v>
+      </c>
+      <c r="C263" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D263" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H263" s="4"/>
-      <c r="I263" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F263" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="G263" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H263" s="4">
+        <v>798500</v>
+      </c>
+      <c r="I263" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J263" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J263" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K263" s="11"/>
       <c r="L263" s="11"/>
       <c r="M263" s="10"/>
-      <c r="N263" s="10"/>
+      <c r="N263" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q263" s="11"/>
       <c r="R263" s="11"/>
       <c r="S263" s="10"/>
     </row>
     <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B264" s="10"/>
-      <c r="C264" s="11"/>
+      <c r="B264" s="10">
+        <f>IF(C264="","",COUNTA($C$2:C264))</f>
+        <v>263</v>
+      </c>
+      <c r="C264" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D264" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H264" s="4"/>
-      <c r="I264" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E264" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="F264" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="G264" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H264" s="4">
+        <v>5442500</v>
+      </c>
+      <c r="I264" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J264" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J264" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K264" s="11"/>
       <c r="L264" s="11"/>
       <c r="M264" s="10"/>
-      <c r="N264" s="10"/>
+      <c r="N264" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q264" s="11"/>
       <c r="R264" s="11"/>
       <c r="S264" s="10"/>
     </row>
     <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B265" s="10"/>
-      <c r="C265" s="11"/>
+      <c r="B265" s="10">
+        <f>IF(C265="","",COUNTA($C$2:C265))</f>
+        <v>264</v>
+      </c>
+      <c r="C265" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D265" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H265" s="4"/>
-      <c r="I265" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E265" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F265" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="G265" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H265" s="4">
+        <v>2969500</v>
+      </c>
+      <c r="I265" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J265" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J265" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K265" s="11"/>
       <c r="L265" s="11"/>
       <c r="M265" s="10"/>
-      <c r="N265" s="10"/>
+      <c r="N265" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q265" s="11"/>
       <c r="R265" s="11"/>
       <c r="S265" s="10"/>
     </row>
     <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B266" s="10"/>
-      <c r="C266" s="11"/>
+      <c r="B266" s="10">
+        <f>IF(C266="","",COUNTA($C$2:C266))</f>
+        <v>265</v>
+      </c>
+      <c r="C266" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D266" s="10" t="str">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="H266" s="4"/>
-      <c r="I266" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F266" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="G266" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H266" s="4">
+        <v>10451300</v>
+      </c>
+      <c r="I266" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-      <c r="J266" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J266" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K266" s="11"/>
       <c r="L266" s="11"/>
       <c r="M266" s="10"/>
-      <c r="N266" s="10"/>
+      <c r="N266" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q266" s="11"/>
       <c r="R266" s="11"/>
       <c r="S266" s="10"/>
     </row>
     <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B267" s="10"/>
-      <c r="C267" s="11"/>
+      <c r="B267" s="10">
+        <f>IF(C267="","",COUNTA($C$2:C267))</f>
+        <v>266</v>
+      </c>
+      <c r="C267" s="11" t="s">
+        <v>415</v>
+      </c>
       <c r="D267" s="10" t="str">
         <f t="shared" ref="D267:D330" si="18">IF(G267="","",IF(OR(G267="선급금",G267="중도금",G267="잔금"),"A",IF(G267="자재","B",IF(G267="특허료","C",""))))</f>
-        <v/>
-      </c>
-      <c r="H267" s="4"/>
-      <c r="I267" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E267" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F267" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="G267" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H267" s="4">
+        <v>2250000</v>
+      </c>
+      <c r="I267" s="6">
         <f t="shared" ref="I267:I330" ca="1" si="19">IF(C267="","",IF(L267="",TODAY()-C267,L267-C267))</f>
-        <v/>
-      </c>
-      <c r="J267" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="J267" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K267" s="11"/>
       <c r="L267" s="11"/>
       <c r="M267" s="10"/>
-      <c r="N267" s="10"/>
+      <c r="N267" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q267" s="11"/>
       <c r="R267" s="11"/>
       <c r="S267" s="10"/>
     </row>
     <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B268" s="10"/>
-      <c r="C268" s="11"/>
+      <c r="B268" s="10">
+        <f>IF(C268="","",COUNTA($C$2:C268))</f>
+        <v>267</v>
+      </c>
+      <c r="C268" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D268" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H268" s="4"/>
-      <c r="I268" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E268" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F268" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="G268" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H268" s="4">
+        <v>2711000</v>
+      </c>
+      <c r="I268" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J268" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J268" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K268" s="11"/>
       <c r="L268" s="11"/>
       <c r="M268" s="10"/>
-      <c r="N268" s="10"/>
+      <c r="N268" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q268" s="11"/>
       <c r="R268" s="11"/>
       <c r="S268" s="10"/>
     </row>
     <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B269" s="10"/>
-      <c r="C269" s="11"/>
+      <c r="B269" s="10">
+        <f>IF(C269="","",COUNTA($C$2:C269))</f>
+        <v>268</v>
+      </c>
+      <c r="C269" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D269" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H269" s="4"/>
-      <c r="I269" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E269" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F269" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="G269" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H269" s="4">
+        <v>10539000</v>
+      </c>
+      <c r="I269" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J269" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J269" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K269" s="11"/>
       <c r="L269" s="11"/>
       <c r="M269" s="10"/>
-      <c r="N269" s="10"/>
+      <c r="N269" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q269" s="11"/>
       <c r="R269" s="11"/>
       <c r="S269" s="10"/>
     </row>
     <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B270" s="10"/>
-      <c r="C270" s="11"/>
+      <c r="B270" s="10">
+        <f>IF(C270="","",COUNTA($C$2:C270))</f>
+        <v>269</v>
+      </c>
+      <c r="C270" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D270" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H270" s="4"/>
-      <c r="I270" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E270" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="F270" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="G270" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H270" s="4">
+        <v>1021000</v>
+      </c>
+      <c r="I270" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J270" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J270" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K270" s="11"/>
       <c r="L270" s="11"/>
       <c r="M270" s="10"/>
-      <c r="N270" s="10"/>
+      <c r="N270" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q270" s="11"/>
       <c r="R270" s="11"/>
       <c r="S270" s="10"/>
     </row>
     <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B271" s="10"/>
-      <c r="C271" s="11"/>
+      <c r="B271" s="10">
+        <f>IF(C271="","",COUNTA($C$2:C271))</f>
+        <v>270</v>
+      </c>
+      <c r="C271" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D271" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H271" s="4"/>
-      <c r="I271" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E271" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F271" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="G271" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H271" s="4">
+        <v>427800</v>
+      </c>
+      <c r="I271" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J271" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J271" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K271" s="11"/>
       <c r="L271" s="11"/>
       <c r="M271" s="10"/>
-      <c r="N271" s="10"/>
+      <c r="N271" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q271" s="11"/>
       <c r="R271" s="11"/>
       <c r="S271" s="10"/>
     </row>
     <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B272" s="10"/>
-      <c r="C272" s="11"/>
+      <c r="B272" s="10">
+        <f>IF(C272="","",COUNTA($C$2:C272))</f>
+        <v>271</v>
+      </c>
+      <c r="C272" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D272" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H272" s="4"/>
-      <c r="I272" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F272" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="G272" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H272" s="4">
+        <v>1180000</v>
+      </c>
+      <c r="I272" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J272" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J272" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K272" s="11"/>
       <c r="L272" s="11"/>
       <c r="M272" s="10"/>
-      <c r="N272" s="10"/>
+      <c r="N272" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q272" s="11"/>
       <c r="R272" s="11"/>
       <c r="S272" s="10"/>
     </row>
     <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B273" s="10"/>
-      <c r="C273" s="11"/>
+      <c r="B273" s="10">
+        <f>IF(C273="","",COUNTA($C$2:C273))</f>
+        <v>272</v>
+      </c>
+      <c r="C273" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D273" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H273" s="4"/>
-      <c r="I273" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E273" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F273" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="G273" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H273" s="4">
+        <v>4520000</v>
+      </c>
+      <c r="I273" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J273" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J273" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K273" s="11"/>
       <c r="L273" s="11"/>
       <c r="M273" s="10"/>
-      <c r="N273" s="10"/>
+      <c r="N273" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q273" s="11"/>
       <c r="R273" s="11"/>
       <c r="S273" s="10"/>
     </row>
     <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B274" s="10"/>
-      <c r="C274" s="11"/>
+      <c r="B274" s="10">
+        <f>IF(C274="","",COUNTA($C$2:C274))</f>
+        <v>273</v>
+      </c>
+      <c r="C274" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D274" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H274" s="4"/>
-      <c r="I274" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F274" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="G274" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H274" s="4">
+        <v>157000</v>
+      </c>
+      <c r="I274" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J274" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J274" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K274" s="11"/>
       <c r="L274" s="11"/>
       <c r="M274" s="10"/>
-      <c r="N274" s="10"/>
+      <c r="N274" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q274" s="11"/>
       <c r="R274" s="11"/>
       <c r="S274" s="10"/>
     </row>
     <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B275" s="10"/>
-      <c r="C275" s="11"/>
+      <c r="B275" s="10">
+        <f>IF(C275="","",COUNTA($C$2:C275))</f>
+        <v>274</v>
+      </c>
+      <c r="C275" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D275" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H275" s="4"/>
-      <c r="I275" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E275" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F275" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="G275" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H275" s="4">
+        <v>2380000</v>
+      </c>
+      <c r="I275" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J275" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J275" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K275" s="11"/>
       <c r="L275" s="11"/>
       <c r="M275" s="10"/>
-      <c r="N275" s="10"/>
+      <c r="N275" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q275" s="11"/>
       <c r="R275" s="11"/>
       <c r="S275" s="10"/>
@@ -17791,345 +18484,360 @@
   <autoFilter ref="A1:S407"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
-    <cfRule type="expression" dxfId="66" priority="90">
+    <cfRule type="expression" dxfId="73" priority="93">
       <formula>$J3="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" dxfId="65" priority="89">
+    <cfRule type="expression" dxfId="72" priority="92">
       <formula>$J8="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="expression" dxfId="64" priority="88">
+    <cfRule type="expression" dxfId="71" priority="91">
       <formula>$J4="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="expression" dxfId="63" priority="87">
+    <cfRule type="expression" dxfId="70" priority="90">
       <formula>$J9="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41 E37">
-    <cfRule type="expression" dxfId="62" priority="82">
+    <cfRule type="expression" dxfId="69" priority="85">
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E98:E99 E186:F192 H186:H192 C186:C192">
-    <cfRule type="expression" dxfId="61" priority="72">
+    <cfRule type="expression" dxfId="68" priority="75">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="expression" dxfId="60" priority="71">
+    <cfRule type="expression" dxfId="67" priority="74">
       <formula>$J98="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104:F105">
-    <cfRule type="expression" dxfId="59" priority="69">
+    <cfRule type="expression" dxfId="66" priority="72">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H105">
-    <cfRule type="expression" dxfId="58" priority="68">
+    <cfRule type="expression" dxfId="65" priority="71">
       <formula>$J104="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E106:E108">
-    <cfRule type="expression" dxfId="57" priority="67">
+    <cfRule type="expression" dxfId="64" priority="70">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F106:F108">
-    <cfRule type="expression" dxfId="56" priority="66">
+    <cfRule type="expression" dxfId="63" priority="69">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H106:H108">
-    <cfRule type="expression" dxfId="55" priority="65">
+    <cfRule type="expression" dxfId="62" priority="68">
       <formula>$J106="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E110">
-    <cfRule type="expression" dxfId="54" priority="64">
+    <cfRule type="expression" dxfId="61" priority="67">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F110">
-    <cfRule type="expression" dxfId="53" priority="63">
+    <cfRule type="expression" dxfId="60" priority="66">
       <formula>$J110="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111:E113">
-    <cfRule type="expression" dxfId="52" priority="62">
+    <cfRule type="expression" dxfId="59" priority="65">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F111 F113">
-    <cfRule type="expression" dxfId="51" priority="61">
+    <cfRule type="expression" dxfId="58" priority="64">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F112">
-    <cfRule type="expression" dxfId="50" priority="60">
+    <cfRule type="expression" dxfId="57" priority="63">
       <formula>$J112="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H111:H113">
-    <cfRule type="expression" dxfId="49" priority="59">
+    <cfRule type="expression" dxfId="56" priority="62">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C111:C113">
-    <cfRule type="expression" dxfId="48" priority="58">
+    <cfRule type="expression" dxfId="55" priority="61">
       <formula>$J111="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E117">
-    <cfRule type="expression" dxfId="47" priority="57">
+    <cfRule type="expression" dxfId="54" priority="60">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117">
-    <cfRule type="expression" dxfId="46" priority="56">
+    <cfRule type="expression" dxfId="53" priority="59">
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142:F149">
-    <cfRule type="expression" dxfId="45" priority="55">
+    <cfRule type="expression" dxfId="52" priority="58">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E142:E149">
-    <cfRule type="expression" dxfId="44" priority="54">
+    <cfRule type="expression" dxfId="51" priority="57">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H142:H149">
-    <cfRule type="expression" dxfId="43" priority="53">
+    <cfRule type="expression" dxfId="50" priority="56">
       <formula>$J142="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E151:E157">
-    <cfRule type="expression" dxfId="42" priority="51">
+    <cfRule type="expression" dxfId="49" priority="54">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151:F157">
-    <cfRule type="expression" dxfId="41" priority="50">
+    <cfRule type="expression" dxfId="48" priority="53">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C151:C157">
-    <cfRule type="expression" dxfId="40" priority="49">
+    <cfRule type="expression" dxfId="47" priority="52">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H151:H157">
-    <cfRule type="expression" dxfId="39" priority="48">
+    <cfRule type="expression" dxfId="46" priority="51">
       <formula>$J151="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C158">
-    <cfRule type="expression" dxfId="38" priority="47">
+    <cfRule type="expression" dxfId="45" priority="50">
       <formula>$I158="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F159:F162">
-    <cfRule type="expression" dxfId="37" priority="46">
+    <cfRule type="expression" dxfId="44" priority="49">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E159:E162">
-    <cfRule type="expression" dxfId="36" priority="45">
+    <cfRule type="expression" dxfId="43" priority="48">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C159:C165">
-    <cfRule type="expression" dxfId="35" priority="44">
+    <cfRule type="expression" dxfId="42" priority="47">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H159:H162">
-    <cfRule type="expression" dxfId="34" priority="43">
+    <cfRule type="expression" dxfId="41" priority="46">
       <formula>$J159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F166:F178">
-    <cfRule type="expression" dxfId="33" priority="42">
+    <cfRule type="expression" dxfId="40" priority="45">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F179:F185">
-    <cfRule type="expression" dxfId="32" priority="41">
+    <cfRule type="expression" dxfId="39" priority="44">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E178">
-    <cfRule type="expression" dxfId="31" priority="40">
+    <cfRule type="expression" dxfId="38" priority="43">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E179:E185">
-    <cfRule type="expression" dxfId="30" priority="39">
+    <cfRule type="expression" dxfId="37" priority="42">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C166:C178">
-    <cfRule type="expression" dxfId="29" priority="38">
+    <cfRule type="expression" dxfId="36" priority="41">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C179:C185">
-    <cfRule type="expression" dxfId="28" priority="37">
+    <cfRule type="expression" dxfId="35" priority="40">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H166:H178">
-    <cfRule type="expression" dxfId="27" priority="36">
+    <cfRule type="expression" dxfId="34" priority="39">
       <formula>$J166="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H179:H185">
-    <cfRule type="expression" dxfId="26" priority="35">
+    <cfRule type="expression" dxfId="33" priority="38">
       <formula>$J179="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F194:F200">
-    <cfRule type="expression" dxfId="25" priority="30">
+    <cfRule type="expression" dxfId="32" priority="33">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E194:E200">
-    <cfRule type="expression" dxfId="24" priority="29">
+    <cfRule type="expression" dxfId="31" priority="32">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C194:C201">
-    <cfRule type="expression" dxfId="23" priority="28">
+    <cfRule type="expression" dxfId="30" priority="31">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H194:H200">
-    <cfRule type="expression" dxfId="22" priority="27">
+    <cfRule type="expression" dxfId="29" priority="30">
       <formula>$J194="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C202:C215">
-    <cfRule type="expression" dxfId="21" priority="26">
+    <cfRule type="expression" dxfId="28" priority="29">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F202:F215">
-    <cfRule type="expression" dxfId="20" priority="25">
+    <cfRule type="expression" dxfId="27" priority="28">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H202:H215">
-    <cfRule type="expression" dxfId="19" priority="24">
+    <cfRule type="expression" dxfId="26" priority="27">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E202:E216">
-    <cfRule type="expression" dxfId="18" priority="23">
+    <cfRule type="expression" dxfId="25" priority="26">
       <formula>$J202="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C216">
-    <cfRule type="expression" dxfId="17" priority="22">
+    <cfRule type="expression" dxfId="24" priority="25">
       <formula>$I216="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H216">
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="23" priority="20">
       <formula>$I216="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C217">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>$I217="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="21" priority="18">
       <formula>$I218="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C219">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="20" priority="17">
       <formula>$I219="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F220:F229">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="19" priority="16">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F230:F243">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="18" priority="15">
       <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E220:E229">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="17" priority="14">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E230:E243">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="16" priority="13">
       <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H220:H229">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="15" priority="12">
       <formula>$J220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H230:H243">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="14" priority="11">
       <formula>$J230="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C245">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="13" priority="10">
       <formula>$I245="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C246">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>$I246="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C247">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>$I247="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F248:F252">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="10" priority="7">
       <formula>$J248="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E248:E252">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>$J248="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C248:C252">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>$J248="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H248:H252">
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>$J248="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C253:C256">
+    <cfRule type="expression" dxfId="6" priority="3">
+      <formula>$I253="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F257:F266">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$J257="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F267:F275">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J248="잔금"</formula>
+      <formula>$J267="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N252">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N275">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D407">

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,15 +11,15 @@
     <sheet name="프로세스현황" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$407</definedName>
-    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$S$408</definedName>
+    <definedName name="_xlnm._FilterDatabase">data!$A$1:$S$408</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="443">
   <si>
     <t>순번</t>
   </si>
@@ -1587,6 +1587,17 @@
   </si>
   <si>
     <t>자재</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>해운대센텀트루엘</t>
+  </si>
+  <si>
+    <t>㈜에이치제이건설</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선급금</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2050,19 +2061,9 @@
   </cellStyles>
   <dxfs count="74">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -2100,9 +2101,19 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE6F3FF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -3437,7 +3448,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S408"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S409"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
@@ -4195,7 +4207,7 @@
       </c>
       <c r="S14" s="10"/>
     </row>
-    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B15" s="10">
         <f>IF(C15="","",COUNTA($C$2:C15))</f>
         <v>14</v>
@@ -4244,7 +4256,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B16" s="10">
         <f>IF(C16="","",COUNTA($C$2:C16))</f>
         <v>15</v>
@@ -4291,7 +4303,7 @@
       <c r="R16" s="14"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B17" s="10">
         <f>IF(C17="","",COUNTA($C$2:C17))</f>
         <v>16</v>
@@ -4338,7 +4350,7 @@
       <c r="R17" s="14"/>
       <c r="S17" s="10"/>
     </row>
-    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B18" s="10">
         <f>IF(C18="","",COUNTA($C$2:C18))</f>
         <v>17</v>
@@ -4385,7 +4397,7 @@
       <c r="R18" s="14"/>
       <c r="S18" s="10"/>
     </row>
-    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B19" s="10">
         <f>IF(C19="","",COUNTA($C$2:C19))</f>
         <v>18</v>
@@ -4432,7 +4444,7 @@
       <c r="R19" s="14"/>
       <c r="S19" s="10"/>
     </row>
-    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B20" s="10">
         <f>IF(C20="","",COUNTA($C$2:C20))</f>
         <v>19</v>
@@ -4479,7 +4491,7 @@
       <c r="R20" s="14"/>
       <c r="S20" s="10"/>
     </row>
-    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B21" s="10">
         <f>IF(C21="","",COUNTA($C$2:C21))</f>
         <v>20</v>
@@ -4528,7 +4540,7 @@
       </c>
       <c r="S21" s="10"/>
     </row>
-    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B22" s="10">
         <f>IF(C22="","",COUNTA($C$2:C22))</f>
         <v>21</v>
@@ -4577,7 +4589,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B23" s="10">
         <f>IF(C23="","",COUNTA($C$2:C23))</f>
         <v>22</v>
@@ -4626,7 +4638,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B24" s="10">
         <f>IF(C24="","",COUNTA($C$2:C24))</f>
         <v>23</v>
@@ -4675,7 +4687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B25" s="10">
         <f>IF(C25="","",COUNTA($C$2:C25))</f>
         <v>24</v>
@@ -4724,7 +4736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B26" s="10">
         <f>IF(C26="","",COUNTA($C$2:C26))</f>
         <v>25</v>
@@ -4773,7 +4785,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B27" s="10">
         <f>IF(C27="","",COUNTA($C$2:C27))</f>
         <v>26</v>
@@ -4822,7 +4834,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B28" s="10">
         <f>IF(C28="","",COUNTA($C$2:C28))</f>
         <v>27</v>
@@ -4871,7 +4883,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B29" s="10">
         <f>IF(C29="","",COUNTA($C$2:C29))</f>
         <v>28</v>
@@ -4920,7 +4932,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B30" s="10">
         <f>IF(C30="","",COUNTA($C$2:C30))</f>
         <v>29</v>
@@ -4969,7 +4981,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B31" s="10">
         <f>IF(C31="","",COUNTA($C$2:C31))</f>
         <v>30</v>
@@ -5018,7 +5030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B32" s="10">
         <f>IF(C32="","",COUNTA($C$2:C32))</f>
         <v>31</v>
@@ -5067,7 +5079,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B33" s="10">
         <f>IF(C33="","",COUNTA($C$2:C33))</f>
         <v>32</v>
@@ -5116,7 +5128,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B34" s="10">
         <f>IF(C34="","",COUNTA($C$2:C34))</f>
         <v>33</v>
@@ -5165,7 +5177,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B35" s="10">
         <f>IF(C35="","",COUNTA($C$2:C35))</f>
         <v>34</v>
@@ -5214,7 +5226,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B36" s="10">
         <f>IF(C36="","",COUNTA($C$2:C36))</f>
         <v>35</v>
@@ -5259,7 +5271,7 @@
       <c r="R36" s="14"/>
       <c r="S36" s="10"/>
     </row>
-    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B37" s="10">
         <f>IF(C37="","",COUNTA($C$2:C37))</f>
         <v>36</v>
@@ -5313,7 +5325,7 @@
       </c>
       <c r="S37" s="10"/>
     </row>
-    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B38" s="10">
         <f>IF(C38="","",COUNTA($C$2:C38))</f>
         <v>37</v>
@@ -5369,7 +5381,7 @@
       </c>
       <c r="S38" s="10"/>
     </row>
-    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B39" s="10">
         <f>IF(C39="","",COUNTA($C$2:C39))</f>
         <v>38</v>
@@ -5422,7 +5434,7 @@
       </c>
       <c r="S39" s="10"/>
     </row>
-    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B40" s="10">
         <f>IF(C40="","",COUNTA($C$2:C40))</f>
         <v>39</v>
@@ -5471,7 +5483,7 @@
       <c r="R40" s="11"/>
       <c r="S40" s="10"/>
     </row>
-    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B41" s="10">
         <f>IF(C41="","",COUNTA($C$2:C41))</f>
         <v>40</v>
@@ -5525,7 +5537,7 @@
       </c>
       <c r="S41" s="10"/>
     </row>
-    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B42" s="10">
         <f>IF(C42="","",COUNTA($C$2:C42))</f>
         <v>41</v>
@@ -5578,7 +5590,7 @@
       </c>
       <c r="S42" s="10"/>
     </row>
-    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B43" s="10">
         <f>IF(C43="","",COUNTA($C$2:C43))</f>
         <v>42</v>
@@ -5630,7 +5642,7 @@
       <c r="R43" s="11"/>
       <c r="S43" s="10"/>
     </row>
-    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B44" s="10">
         <f>IF(C44="","",COUNTA($C$2:C44))</f>
         <v>43</v>
@@ -5681,7 +5693,7 @@
       </c>
       <c r="S44" s="10"/>
     </row>
-    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B45" s="10">
         <f>IF(C45="","",COUNTA($C$2:C45))</f>
         <v>44</v>
@@ -5730,7 +5742,7 @@
       <c r="R45" s="11"/>
       <c r="S45" s="10"/>
     </row>
-    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B46" s="10">
         <f>IF(C46="","",COUNTA($C$2:C46))</f>
         <v>45</v>
@@ -5779,7 +5791,7 @@
       <c r="R46" s="11"/>
       <c r="S46" s="10"/>
     </row>
-    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B47" s="10">
         <f>IF(C47="","",COUNTA($C$2:C47))</f>
         <v>46</v>
@@ -5828,7 +5840,7 @@
       <c r="R47" s="11"/>
       <c r="S47" s="10"/>
     </row>
-    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B48" s="10">
         <f>IF(C48="","",COUNTA($C$2:C48))</f>
         <v>47</v>
@@ -5877,7 +5889,7 @@
       <c r="R48" s="11"/>
       <c r="S48" s="10"/>
     </row>
-    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B49" s="10">
         <f>IF(C49="","",COUNTA($C$2:C49))</f>
         <v>48</v>
@@ -5926,7 +5938,7 @@
       <c r="R49" s="11"/>
       <c r="S49" s="10"/>
     </row>
-    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B50" s="10">
         <f>IF(C50="","",COUNTA($C$2:C50))</f>
         <v>49</v>
@@ -5975,7 +5987,7 @@
       <c r="R50" s="11"/>
       <c r="S50" s="10"/>
     </row>
-    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B51" s="10">
         <f>IF(C51="","",COUNTA($C$2:C51))</f>
         <v>50</v>
@@ -6021,7 +6033,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="10"/>
     </row>
-    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B52" s="10">
         <f>IF(C52="","",COUNTA($C$2:C52))</f>
         <v>51</v>
@@ -6067,7 +6079,7 @@
       <c r="R52" s="11"/>
       <c r="S52" s="10"/>
     </row>
-    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B53" s="10">
         <f>IF(C53="","",COUNTA($C$2:C53))</f>
         <v>52</v>
@@ -6116,7 +6128,7 @@
       <c r="R53" s="11"/>
       <c r="S53" s="10"/>
     </row>
-    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B54" s="10">
         <f>IF(C54="","",COUNTA($C$2:C54))</f>
         <v>53</v>
@@ -6170,7 +6182,7 @@
       </c>
       <c r="S54" s="10"/>
     </row>
-    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B55" s="10">
         <f>IF(C55="","",COUNTA($C$2:C55))</f>
         <v>54</v>
@@ -6214,7 +6226,7 @@
       <c r="R55" s="11"/>
       <c r="S55" s="10"/>
     </row>
-    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B56" s="10">
         <f>IF(C56="","",COUNTA($C$2:C56))</f>
         <v>55</v>
@@ -6263,7 +6275,7 @@
       <c r="R56" s="11"/>
       <c r="S56" s="10"/>
     </row>
-    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B57" s="10">
         <f>IF(C57="","",COUNTA($C$2:C57))</f>
         <v>56</v>
@@ -6310,7 +6322,7 @@
       <c r="R57" s="14"/>
       <c r="S57" s="10"/>
     </row>
-    <row r="58" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="58" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B58" s="10">
         <f>IF(C58="","",COUNTA($C$2:C58))</f>
         <v>57</v>
@@ -6357,7 +6369,7 @@
       <c r="R58" s="14"/>
       <c r="S58" s="10"/>
     </row>
-    <row r="59" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="59" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B59" s="10">
         <f>IF(C59="","",COUNTA($C$2:C59))</f>
         <v>58</v>
@@ -6404,7 +6416,7 @@
       <c r="R59" s="14"/>
       <c r="S59" s="10"/>
     </row>
-    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="60" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B60" s="10">
         <f>IF(C60="","",COUNTA($C$2:C60))</f>
         <v>59</v>
@@ -6459,7 +6471,7 @@
       <c r="R60" s="14"/>
       <c r="S60" s="10"/>
     </row>
-    <row r="61" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="61" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B61" s="10">
         <f>IF(C61="","",COUNTA($C$2:C61))</f>
         <v>60</v>
@@ -6505,7 +6517,7 @@
       <c r="R61" s="14"/>
       <c r="S61" s="10"/>
     </row>
-    <row r="62" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="62" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B62" s="10">
         <f>IF(C62="","",COUNTA($C$2:C62))</f>
         <v>61</v>
@@ -6551,7 +6563,7 @@
       <c r="R62" s="14"/>
       <c r="S62" s="10"/>
     </row>
-    <row r="63" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="63" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B63" s="10">
         <f>IF(C63="","",COUNTA($C$2:C63))</f>
         <v>62</v>
@@ -6600,7 +6612,7 @@
       <c r="R63" s="14"/>
       <c r="S63" s="10"/>
     </row>
-    <row r="64" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="64" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B64" s="10">
         <f>IF(C64="","",COUNTA($C$2:C64))</f>
         <v>63</v>
@@ -6649,7 +6661,7 @@
       <c r="R64" s="14"/>
       <c r="S64" s="10"/>
     </row>
-    <row r="65" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="65" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B65" s="10">
         <f>IF(C65="","",COUNTA($C$2:C65))</f>
         <v>64</v>
@@ -6695,7 +6707,7 @@
       <c r="R65" s="14"/>
       <c r="S65" s="10"/>
     </row>
-    <row r="66" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="66" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B66" s="10">
         <f>IF(C66="","",COUNTA($C$2:C66))</f>
         <v>65</v>
@@ -6739,7 +6751,7 @@
       <c r="R66" s="14"/>
       <c r="S66" s="10"/>
     </row>
-    <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="67" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B67" s="10">
         <f>IF(C67="","",COUNTA($C$2:C67))</f>
         <v>66</v>
@@ -6783,7 +6795,7 @@
       <c r="R67" s="11"/>
       <c r="S67" s="10"/>
     </row>
-    <row r="68" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="68" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B68" s="10">
         <f>IF(C68="","",COUNTA($C$2:C68))</f>
         <v>67</v>
@@ -6827,7 +6839,7 @@
       <c r="R68" s="11"/>
       <c r="S68" s="10"/>
     </row>
-    <row r="69" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="69" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B69" s="10">
         <f>IF(C69="","",COUNTA($C$2:C69))</f>
         <v>68</v>
@@ -6871,7 +6883,7 @@
       <c r="R69" s="11"/>
       <c r="S69" s="10"/>
     </row>
-    <row r="70" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="70" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B70" s="10">
         <f>IF(C70="","",COUNTA($C$2:C70))</f>
         <v>69</v>
@@ -6918,7 +6930,7 @@
       <c r="R70" s="11"/>
       <c r="S70" s="10"/>
     </row>
-    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="71" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B71" s="10">
         <f>IF(C71="","",COUNTA($C$2:C71))</f>
         <v>70</v>
@@ -6970,7 +6982,7 @@
       <c r="R71" s="11"/>
       <c r="S71" s="10"/>
     </row>
-    <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="72" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B72" s="10">
         <f>IF(C72="","",COUNTA($C$2:C72))</f>
         <v>71</v>
@@ -7024,7 +7036,7 @@
       </c>
       <c r="S72" s="10"/>
     </row>
-    <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="73" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B73" s="10">
         <f>IF(C73="","",COUNTA($C$2:C73))</f>
         <v>72</v>
@@ -7071,7 +7083,7 @@
       <c r="R73" s="11"/>
       <c r="S73" s="10"/>
     </row>
-    <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="74" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B74" s="10">
         <f>IF(C74="","",COUNTA($C$2:C74))</f>
         <v>73</v>
@@ -7125,7 +7137,7 @@
       </c>
       <c r="S74" s="10"/>
     </row>
-    <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="75" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B75" s="10">
         <f>IF(C75="","",COUNTA($C$2:C75))</f>
         <v>74</v>
@@ -7169,7 +7181,7 @@
       <c r="R75" s="11"/>
       <c r="S75" s="10"/>
     </row>
-    <row r="76" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="76" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B76" s="10">
         <f>IF(C76="","",COUNTA($C$2:C76))</f>
         <v>75</v>
@@ -7211,7 +7223,7 @@
       <c r="R76" s="11"/>
       <c r="S76" s="10"/>
     </row>
-    <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="77" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B77" s="10">
         <f>IF(C77="","",COUNTA($C$2:C77))</f>
         <v>76</v>
@@ -7220,7 +7232,7 @@
         <v>46034</v>
       </c>
       <c r="D77" s="10" t="str">
-        <f t="shared" ref="D77:D139" si="9">IF(G77="","",IF(OR(G77="선급금",G77="중도금",G77="잔금"),"A",IF(G77="자재","B",IF(G77="특허료","C",""))))</f>
+        <f t="shared" ref="D77:D140" si="9">IF(G77="","",IF(OR(G77="선급금",G77="중도금",G77="잔금"),"A",IF(G77="자재","B",IF(G77="특허료","C",""))))</f>
         <v>B</v>
       </c>
       <c r="E77" s="6" t="s">
@@ -7236,7 +7248,7 @@
         <v>2200000</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" ref="I77:I139" ca="1" si="10">IF(C77="","",IF(L77="",TODAY()-C77,L77-C77))</f>
+        <f t="shared" ref="I77:I140" ca="1" si="10">IF(C77="","",IF(L77="",TODAY()-C77,L77-C77))</f>
         <v>11</v>
       </c>
       <c r="J77" s="13" t="str">
@@ -7265,7 +7277,7 @@
       </c>
       <c r="S77" s="10"/>
     </row>
-    <row r="78" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="78" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B78" s="10">
         <f>IF(C78="","",COUNTA($C$2:C78))</f>
         <v>77</v>
@@ -7319,7 +7331,7 @@
       </c>
       <c r="S78" s="10"/>
     </row>
-    <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="79" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B79" s="10">
         <f>IF(C79="","",COUNTA($C$2:C79))</f>
         <v>78</v>
@@ -7363,7 +7375,7 @@
       <c r="R79" s="11"/>
       <c r="S79" s="10"/>
     </row>
-    <row r="80" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="80" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B80" s="10">
         <f>IF(C80="","",COUNTA($C$2:C80))</f>
         <v>79</v>
@@ -7407,7 +7419,7 @@
       <c r="R80" s="11"/>
       <c r="S80" s="10"/>
     </row>
-    <row r="81" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="81" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B81" s="10">
         <f>IF(C81="","",COUNTA($C$2:C81))</f>
         <v>80</v>
@@ -7449,7 +7461,7 @@
       <c r="R81" s="11"/>
       <c r="S81" s="10"/>
     </row>
-    <row r="82" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="82" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B82" s="10">
         <f>IF(C82="","",COUNTA($C$2:C82))</f>
         <v>81</v>
@@ -7493,7 +7505,7 @@
       <c r="R82" s="11"/>
       <c r="S82" s="10"/>
     </row>
-    <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="83" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B83" s="10">
         <f>IF(C83="","",COUNTA($C$2:C83))</f>
         <v>82</v>
@@ -7545,7 +7557,7 @@
       </c>
       <c r="S83" s="10"/>
     </row>
-    <row r="84" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="84" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B84" s="10">
         <f>IF(C84="","",COUNTA($C$2:C84))</f>
         <v>83</v>
@@ -7599,7 +7611,7 @@
       </c>
       <c r="S84" s="10"/>
     </row>
-    <row r="85" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="85" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B85" s="10">
         <f>IF(C85="","",COUNTA($C$2:C85))</f>
         <v>84</v>
@@ -7651,7 +7663,7 @@
       </c>
       <c r="S85" s="10"/>
     </row>
-    <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="86" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B86" s="10">
         <f>IF(C86="","",COUNTA($C$2:C86))</f>
         <v>85</v>
@@ -7693,7 +7705,7 @@
       <c r="R86" s="11"/>
       <c r="S86" s="10"/>
     </row>
-    <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="87" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B87" s="10">
         <f>IF(C87="","",COUNTA($C$2:C87))</f>
         <v>86</v>
@@ -7745,7 +7757,7 @@
       </c>
       <c r="S87" s="10"/>
     </row>
-    <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="88" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B88" s="10">
         <f>IF(C88="","",COUNTA($C$2:C88))</f>
         <v>87</v>
@@ -7789,7 +7801,7 @@
       <c r="R88" s="11"/>
       <c r="S88" s="10"/>
     </row>
-    <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="89" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B89" s="10">
         <f>IF(C89="","",COUNTA($C$2:C89))</f>
         <v>88</v>
@@ -7841,7 +7853,7 @@
       </c>
       <c r="S89" s="10"/>
     </row>
-    <row r="90" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="90" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B90" s="10">
         <f>IF(C90="","",COUNTA($C$2:C90))</f>
         <v>89</v>
@@ -7893,7 +7905,7 @@
       </c>
       <c r="S90" s="10"/>
     </row>
-    <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="91" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B91" s="10">
         <f>IF(C91="","",COUNTA($C$2:C91))</f>
         <v>90</v>
@@ -7937,7 +7949,7 @@
       <c r="R91" s="11"/>
       <c r="S91" s="10"/>
     </row>
-    <row r="92" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="92" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B92" s="10">
         <f>IF(C92="","",COUNTA($C$2:C92))</f>
         <v>91</v>
@@ -7979,7 +7991,7 @@
       <c r="R92" s="11"/>
       <c r="S92" s="10"/>
     </row>
-    <row r="93" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="93" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B93" s="10">
         <f>IF(C93="","",COUNTA($C$2:C93))</f>
         <v>92</v>
@@ -8023,7 +8035,7 @@
       <c r="R93" s="11"/>
       <c r="S93" s="10"/>
     </row>
-    <row r="94" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="94" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B94" s="10">
         <f>IF(C94="","",COUNTA($C$2:C94))</f>
         <v>93</v>
@@ -8067,7 +8079,7 @@
       <c r="R94" s="11"/>
       <c r="S94" s="10"/>
     </row>
-    <row r="95" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="95" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B95" s="10">
         <f>IF(C95="","",COUNTA($C$2:C95))</f>
         <v>94</v>
@@ -8111,7 +8123,7 @@
       <c r="R95" s="11"/>
       <c r="S95" s="10"/>
     </row>
-    <row r="96" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="96" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B96" s="10">
         <f>IF(C96="","",COUNTA($C$2:C96))</f>
         <v>95</v>
@@ -8153,7 +8165,7 @@
       <c r="R96" s="11"/>
       <c r="S96" s="10"/>
     </row>
-    <row r="97" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="97" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B97" s="10">
         <f>IF(C97="","",COUNTA($C$2:C97))</f>
         <v>96</v>
@@ -8197,7 +8209,7 @@
       <c r="R97" s="11"/>
       <c r="S97" s="10"/>
     </row>
-    <row r="98" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="98" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B98" s="10">
         <f>IF(C98="","",COUNTA($C$2:C98))</f>
         <v>97</v>
@@ -8239,7 +8251,7 @@
       <c r="R98" s="11"/>
       <c r="S98" s="10"/>
     </row>
-    <row r="99" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="99" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B99" s="10">
         <f>IF(C99="","",COUNTA($C$2:C99))</f>
         <v>98</v>
@@ -8281,7 +8293,7 @@
       <c r="R99" s="11"/>
       <c r="S99" s="10"/>
     </row>
-    <row r="100" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="100" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B100" s="10">
         <f>IF(C100="","",COUNTA($C$2:C100))</f>
         <v>99</v>
@@ -8322,7 +8334,7 @@
       <c r="R100" s="11"/>
       <c r="S100" s="10"/>
     </row>
-    <row r="101" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="101" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B101" s="10">
         <f>IF(C101="","",COUNTA($C$2:C101))</f>
         <v>100</v>
@@ -8365,7 +8377,7 @@
       <c r="R101" s="11"/>
       <c r="S101" s="10"/>
     </row>
-    <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="102" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B102" s="10">
         <f>IF(C102="","",COUNTA($C$2:C102))</f>
         <v>101</v>
@@ -8453,7 +8465,7 @@
       <c r="R103" s="11"/>
       <c r="S103" s="10"/>
     </row>
-    <row r="104" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="104" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B104" s="10">
         <f>IF(C104="","",COUNTA($C$2:C104))</f>
         <v>103</v>
@@ -8495,7 +8507,7 @@
       <c r="R104" s="11"/>
       <c r="S104" s="10"/>
     </row>
-    <row r="105" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="105" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B105" s="10">
         <f>IF(C105="","",COUNTA($C$2:C105))</f>
         <v>104</v>
@@ -8537,7 +8549,7 @@
       <c r="R105" s="11"/>
       <c r="S105" s="10"/>
     </row>
-    <row r="106" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="106" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B106" s="10">
         <f>IF(C106="","",COUNTA($C$2:C106))</f>
         <v>105</v>
@@ -8581,7 +8593,7 @@
       <c r="R106" s="11"/>
       <c r="S106" s="10"/>
     </row>
-    <row r="107" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="107" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B107" s="10">
         <f>IF(C107="","",COUNTA($C$2:C107))</f>
         <v>106</v>
@@ -8624,7 +8636,7 @@
       <c r="R107" s="11"/>
       <c r="S107" s="10"/>
     </row>
-    <row r="108" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="108" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B108" s="10">
         <f>IF(C108="","",COUNTA($C$2:C108))</f>
         <v>107</v>
@@ -8665,7 +8677,7 @@
       <c r="R108" s="11"/>
       <c r="S108" s="10"/>
     </row>
-    <row r="109" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="109" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B109" s="10">
         <f>IF(C109="","",COUNTA($C$2:C109))</f>
         <v>108</v>
@@ -8706,7 +8718,7 @@
       <c r="R109" s="11"/>
       <c r="S109" s="10"/>
     </row>
-    <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="110" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B110" s="10">
         <f>IF(C110="","",COUNTA($C$2:C110))</f>
         <v>109</v>
@@ -8750,7 +8762,7 @@
       <c r="R110" s="11"/>
       <c r="S110" s="10"/>
     </row>
-    <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="111" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B111" s="10">
         <f>IF(C111="","",COUNTA($C$2:C111))</f>
         <v>110</v>
@@ -8794,7 +8806,7 @@
       <c r="R111" s="11"/>
       <c r="S111" s="10"/>
     </row>
-    <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="112" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B112" s="10">
         <f>IF(C112="","",COUNTA($C$2:C112))</f>
         <v>111</v>
@@ -8839,7 +8851,7 @@
       <c r="R112" s="11"/>
       <c r="S112" s="10"/>
     </row>
-    <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="113" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B113" s="10">
         <f>IF(C113="","",COUNTA($C$2:C113))</f>
         <v>112</v>
@@ -8883,7 +8895,7 @@
       <c r="R113" s="11"/>
       <c r="S113" s="10"/>
     </row>
-    <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="114" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B114" s="10">
         <f>IF(C114="","",COUNTA($C$2:C114))</f>
         <v>113</v>
@@ -8928,7 +8940,7 @@
       <c r="R114" s="11"/>
       <c r="S114" s="10"/>
     </row>
-    <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="115" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B115" s="10">
         <f>IF(C115="","",COUNTA($C$2:C115))</f>
         <v>114</v>
@@ -8957,7 +8969,7 @@
         <v>30</v>
       </c>
       <c r="J115" s="13" t="str">
-        <f t="shared" ref="J115:J178" ca="1" si="11">IF(I115="","",
+        <f t="shared" ref="J115:J179" ca="1" si="11">IF(I115="","",
  IF(G115="선급금",
    IF(I115&lt;=20,"정상",IF(I115&lt;=90,"관리","장기미수")),
  IF(G115="자재",
@@ -8981,7 +8993,7 @@
       <c r="R115" s="11"/>
       <c r="S115" s="10"/>
     </row>
-    <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="116" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B116" s="10">
         <f>IF(C116="","",COUNTA($C$2:C116))</f>
         <v>115</v>
@@ -9025,7 +9037,7 @@
       <c r="R116" s="11"/>
       <c r="S116" s="10"/>
     </row>
-    <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="117" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B117" s="10">
         <f>IF(C117="","",COUNTA($C$2:C117))</f>
         <v>116</v>
@@ -9067,7 +9079,7 @@
       <c r="R117" s="11"/>
       <c r="S117" s="10"/>
     </row>
-    <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="118" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B118" s="10">
         <f>IF(C118="","",COUNTA($C$2:C118))</f>
         <v>117</v>
@@ -9111,7 +9123,7 @@
       <c r="R118" s="11"/>
       <c r="S118" s="10"/>
     </row>
-    <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="119" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B119" s="10">
         <f>IF(C119="","",COUNTA($C$2:C119))</f>
         <v>118</v>
@@ -9156,7 +9168,7 @@
       <c r="R119" s="11"/>
       <c r="S119" s="10"/>
     </row>
-    <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="120" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B120" s="10">
         <f>IF(C120="","",COUNTA($C$2:C120))</f>
         <v>119</v>
@@ -9200,7 +9212,7 @@
       <c r="R120" s="11"/>
       <c r="S120" s="10"/>
     </row>
-    <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="121" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B121" s="10">
         <f>IF(C121="","",COUNTA($C$2:C121))</f>
         <v>120</v>
@@ -9244,7 +9256,7 @@
       <c r="R121" s="11"/>
       <c r="S121" s="10"/>
     </row>
-    <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="122" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B122" s="10">
         <f>IF(C122="","",COUNTA($C$2:C122))</f>
         <v>121</v>
@@ -9286,7 +9298,7 @@
       <c r="R122" s="11"/>
       <c r="S122" s="10"/>
     </row>
-    <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="123" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B123" s="10">
         <f>IF(C123="","",COUNTA($C$2:C123))</f>
         <v>122</v>
@@ -9328,7 +9340,7 @@
       <c r="R123" s="11"/>
       <c r="S123" s="10"/>
     </row>
-    <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="124" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B124" s="10">
         <f>IF(C124="","",COUNTA($C$2:C124))</f>
         <v>123</v>
@@ -9372,7 +9384,7 @@
       <c r="R124" s="11"/>
       <c r="S124" s="10"/>
     </row>
-    <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="125" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B125" s="10">
         <f>IF(C125="","",COUNTA($C$2:C125))</f>
         <v>124</v>
@@ -9449,7 +9461,7 @@
       <c r="R126" s="11"/>
       <c r="S126" s="10"/>
     </row>
-    <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="127" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B127" s="10">
         <f>IF(C127="","",COUNTA($C$2:C127))</f>
         <v>126</v>
@@ -9491,7 +9503,7 @@
       <c r="R127" s="11"/>
       <c r="S127" s="10"/>
     </row>
-    <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="128" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B128" s="10">
         <f>IF(C128="","",COUNTA($C$2:C128))</f>
         <v>127</v>
@@ -9533,7 +9545,7 @@
       <c r="R128" s="11"/>
       <c r="S128" s="10"/>
     </row>
-    <row r="129" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="129" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B129" s="10">
         <f>IF(C129="","",COUNTA($C$2:C129))</f>
         <v>128</v>
@@ -9575,7 +9587,7 @@
       <c r="R129" s="11"/>
       <c r="S129" s="10"/>
     </row>
-    <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="130" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B130" s="10">
         <f>IF(C130="","",COUNTA($C$2:C130))</f>
         <v>129</v>
@@ -9617,7 +9629,7 @@
       <c r="R130" s="11"/>
       <c r="S130" s="10"/>
     </row>
-    <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="131" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B131" s="10">
         <f>IF(C131="","",COUNTA($C$2:C131))</f>
         <v>130</v>
@@ -9661,7 +9673,7 @@
       <c r="R131" s="11"/>
       <c r="S131" s="10"/>
     </row>
-    <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="132" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B132" s="10">
         <f>IF(C132="","",COUNTA($C$2:C132))</f>
         <v>131</v>
@@ -9705,7 +9717,7 @@
       <c r="R132" s="11"/>
       <c r="S132" s="10"/>
     </row>
-    <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="133" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B133" s="10">
         <f>IF(C133="","",COUNTA($C$2:C133))</f>
         <v>132</v>
@@ -9749,7 +9761,7 @@
       <c r="R133" s="11"/>
       <c r="S133" s="10"/>
     </row>
-    <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="134" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B134" s="10">
         <f>IF(C134="","",COUNTA($C$2:C134))</f>
         <v>133</v>
@@ -9791,7 +9803,7 @@
       <c r="R134" s="11"/>
       <c r="S134" s="10"/>
     </row>
-    <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="135" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B135" s="10">
         <f>IF(C135="","",COUNTA($C$2:C135))</f>
         <v>134</v>
@@ -9833,7 +9845,7 @@
       <c r="R135" s="11"/>
       <c r="S135" s="10"/>
     </row>
-    <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="136" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B136" s="10">
         <f>IF(C136="","",COUNTA($C$2:C136))</f>
         <v>135</v>
@@ -9976,29 +9988,27 @@
         <v>A</v>
       </c>
       <c r="E139" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>241</v>
+        <v>441</v>
+      </c>
+      <c r="F139" s="62" t="s">
+        <v>440</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="H139" s="59">
-        <v>9772000</v>
+        <v>442</v>
+      </c>
+      <c r="H139" s="61">
+        <v>11115400</v>
       </c>
       <c r="I139" s="6">
         <f t="shared" ca="1" si="10"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J139" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
-        <v>정상</v>
+        <v>관리</v>
       </c>
       <c r="K139" s="11"/>
-      <c r="L139" s="11">
-        <v>46085</v>
-      </c>
+      <c r="L139" s="11"/>
       <c r="M139" s="10"/>
       <c r="N139" s="10" t="s">
         <v>33</v>
@@ -10013,27 +10023,27 @@
         <v>139</v>
       </c>
       <c r="C140" s="58">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="D140" s="10" t="str">
-        <f t="shared" ref="D140:D202" si="12">IF(G140="","",IF(OR(G140="선급금",G140="중도금",G140="잔금"),"A",IF(G140="자재","B",IF(G140="특허료","C",""))))</f>
+        <f t="shared" si="9"/>
         <v>A</v>
       </c>
       <c r="E140" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="F140" s="57" t="s">
-        <v>236</v>
+      <c r="F140" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="H140" s="61">
-        <v>19544000</v>
+        <v>237</v>
+      </c>
+      <c r="H140" s="59">
+        <v>9772000</v>
       </c>
       <c r="I140" s="6">
-        <f t="shared" ref="I140:I202" ca="1" si="13">IF(C140="","",IF(L140="",TODAY()-C140,L140-C140))</f>
-        <v>4</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>0</v>
       </c>
       <c r="J140" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10041,7 +10051,7 @@
       </c>
       <c r="K140" s="11"/>
       <c r="L140" s="11">
-        <v>46090</v>
+        <v>46085</v>
       </c>
       <c r="M140" s="10"/>
       <c r="N140" s="10" t="s">
@@ -10060,31 +10070,33 @@
         <v>46086</v>
       </c>
       <c r="D141" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D141:D203" si="12">IF(G141="","",IF(OR(G141="선급금",G141="중도금",G141="잔금"),"A",IF(G141="자재","B",IF(G141="특허료","C",""))))</f>
         <v>A</v>
       </c>
-      <c r="E141" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>242</v>
+      <c r="E141" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="F141" s="57" t="s">
+        <v>236</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="H141" s="60">
-        <v>30186600</v>
+        <v>240</v>
+      </c>
+      <c r="H141" s="61">
+        <v>19544000</v>
       </c>
       <c r="I141" s="6">
-        <f t="shared" ca="1" si="13"/>
-        <v>20</v>
+        <f t="shared" ref="I141:I203" ca="1" si="13">IF(C141="","",IF(L141="",TODAY()-C141,L141-C141))</f>
+        <v>4</v>
       </c>
       <c r="J141" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K141" s="11"/>
-      <c r="L141" s="11"/>
+      <c r="L141" s="11">
+        <v>46090</v>
+      </c>
       <c r="M141" s="10"/>
       <c r="N141" s="10" t="s">
         <v>33</v>
@@ -10101,20 +10113,21 @@
       <c r="C142" s="58">
         <v>46086</v>
       </c>
-      <c r="D142" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="E142" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="F142" s="23" t="s">
-        <v>204</v>
+      <c r="D142" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v>A</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="H142" s="25">
-        <v>577500</v>
+        <v>243</v>
+      </c>
+      <c r="H142" s="60">
+        <v>30186600</v>
       </c>
       <c r="I142" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10134,7 +10147,7 @@
       <c r="R142" s="11"/>
       <c r="S142" s="10"/>
     </row>
-    <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="143" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B143" s="10">
         <f>IF(C143="","",COUNTA($C$2:C143))</f>
         <v>142</v>
@@ -10146,16 +10159,16 @@
         <v>249</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F143" s="23" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G143" s="6" t="s">
         <v>250</v>
       </c>
       <c r="H143" s="25">
-        <v>226000</v>
+        <v>577500</v>
       </c>
       <c r="I143" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10175,7 +10188,7 @@
       <c r="R143" s="11"/>
       <c r="S143" s="10"/>
     </row>
-    <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="144" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B144" s="10">
         <f>IF(C144="","",COUNTA($C$2:C144))</f>
         <v>143</v>
@@ -10187,16 +10200,16 @@
         <v>249</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c r="F144" s="23" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="G144" s="6" t="s">
         <v>250</v>
       </c>
       <c r="H144" s="25">
-        <v>237000</v>
+        <v>226000</v>
       </c>
       <c r="I144" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10216,7 +10229,7 @@
       <c r="R144" s="11"/>
       <c r="S144" s="10"/>
     </row>
-    <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="145" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B145" s="10">
         <f>IF(C145="","",COUNTA($C$2:C145))</f>
         <v>144</v>
@@ -10228,16 +10241,16 @@
         <v>249</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>248</v>
+        <v>26</v>
       </c>
       <c r="F145" s="23" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G145" s="6" t="s">
         <v>250</v>
       </c>
       <c r="H145" s="25">
-        <v>167500</v>
+        <v>237000</v>
       </c>
       <c r="I145" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10257,7 +10270,7 @@
       <c r="R145" s="11"/>
       <c r="S145" s="10"/>
     </row>
-    <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="146" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B146" s="10">
         <f>IF(C146="","",COUNTA($C$2:C146))</f>
         <v>145</v>
@@ -10269,16 +10282,16 @@
         <v>249</v>
       </c>
       <c r="E146" s="23" t="s">
-        <v>128</v>
+        <v>248</v>
       </c>
       <c r="F146" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G146" s="6" t="s">
         <v>250</v>
       </c>
       <c r="H146" s="25">
-        <v>3179600</v>
+        <v>167500</v>
       </c>
       <c r="I146" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10298,7 +10311,7 @@
       <c r="R146" s="11"/>
       <c r="S146" s="10"/>
     </row>
-    <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="147" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B147" s="10">
         <f>IF(C147="","",COUNTA($C$2:C147))</f>
         <v>146</v>
@@ -10310,16 +10323,16 @@
         <v>249</v>
       </c>
       <c r="E147" s="23" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="F147" s="23" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="G147" s="6" t="s">
         <v>250</v>
       </c>
       <c r="H147" s="25">
-        <v>5500000</v>
+        <v>3179600</v>
       </c>
       <c r="I147" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10339,7 +10352,7 @@
       <c r="R147" s="11"/>
       <c r="S147" s="10"/>
     </row>
-    <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="148" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B148" s="10">
         <f>IF(C148="","",COUNTA($C$2:C148))</f>
         <v>147</v>
@@ -10360,7 +10373,7 @@
         <v>250</v>
       </c>
       <c r="H148" s="25">
-        <v>1801000</v>
+        <v>5500000</v>
       </c>
       <c r="I148" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10380,7 +10393,7 @@
       <c r="R148" s="11"/>
       <c r="S148" s="10"/>
     </row>
-    <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="149" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B149" s="10">
         <f>IF(C149="","",COUNTA($C$2:C149))</f>
         <v>148</v>
@@ -10395,16 +10408,16 @@
         <v>227</v>
       </c>
       <c r="F149" s="23" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="G149" s="6" t="s">
         <v>250</v>
       </c>
       <c r="H149" s="25">
-        <v>6400500</v>
+        <v>1801000</v>
       </c>
       <c r="I149" s="6">
-        <f ca="1">IF(C149="","",IF(L149="",TODAY()-C149,L149-C149))</f>
+        <f t="shared" ca="1" si="13"/>
         <v>20</v>
       </c>
       <c r="J149" s="13" t="str">
@@ -10421,32 +10434,32 @@
       <c r="R149" s="11"/>
       <c r="S149" s="10"/>
     </row>
-    <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="150" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B150" s="10">
         <f>IF(C150="","",COUNTA($C$2:C150))</f>
         <v>149</v>
       </c>
       <c r="C150" s="58">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>256</v>
+        <v>249</v>
+      </c>
+      <c r="E150" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F150" s="23" t="s">
+        <v>247</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="H150" s="4">
-        <v>5358400</v>
+        <v>250</v>
+      </c>
+      <c r="H150" s="25">
+        <v>6400500</v>
       </c>
       <c r="I150" s="6">
         <f ca="1">IF(C150="","",IF(L150="",TODAY()-C150,L150-C150))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J150" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10467,36 +10480,34 @@
         <f>IF(C151="","",COUNTA($C$2:C151))</f>
         <v>150</v>
       </c>
-      <c r="C151" s="35" t="s">
-        <v>265</v>
+      <c r="C151" s="58">
+        <v>46087</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E151" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F151" s="23" t="s">
-        <v>260</v>
+        <v>253</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="H151" s="25">
-        <v>753000</v>
+        <v>237</v>
+      </c>
+      <c r="H151" s="4">
+        <v>5358400</v>
       </c>
       <c r="I151" s="6">
-        <f t="shared" ca="1" si="13"/>
-        <v>0</v>
+        <f ca="1">IF(C151="","",IF(L151="",TODAY()-C151,L151-C151))</f>
+        <v>19</v>
       </c>
       <c r="J151" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K151" s="11"/>
-      <c r="L151" s="11">
-        <v>46087</v>
-      </c>
+      <c r="L151" s="11"/>
       <c r="M151" s="10"/>
       <c r="N151" s="10" t="s">
         <v>33</v>
@@ -10505,7 +10516,7 @@
       <c r="R151" s="11"/>
       <c r="S151" s="10"/>
     </row>
-    <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="152" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B152" s="10">
         <f>IF(C152="","",COUNTA($C$2:C152))</f>
         <v>151</v>
@@ -10517,27 +10528,29 @@
         <v>182</v>
       </c>
       <c r="E152" s="23" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="F152" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G152" s="6" t="s">
         <v>266</v>
       </c>
       <c r="H152" s="25">
-        <v>3230000</v>
+        <v>753000</v>
       </c>
       <c r="I152" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J152" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K152" s="11"/>
-      <c r="L152" s="11"/>
+      <c r="L152" s="11">
+        <v>46087</v>
+      </c>
       <c r="M152" s="10"/>
       <c r="N152" s="10" t="s">
         <v>33</v>
@@ -10546,7 +10559,7 @@
       <c r="R152" s="11"/>
       <c r="S152" s="10"/>
     </row>
-    <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="153" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B153" s="10">
         <f>IF(C153="","",COUNTA($C$2:C153))</f>
         <v>152</v>
@@ -10558,29 +10571,27 @@
         <v>182</v>
       </c>
       <c r="E153" s="23" t="s">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="F153" s="23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G153" s="6" t="s">
         <v>266</v>
       </c>
       <c r="H153" s="25">
-        <v>5030650</v>
+        <v>3230000</v>
       </c>
       <c r="I153" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J153" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K153" s="11"/>
-      <c r="L153" s="11">
-        <v>46087</v>
-      </c>
+      <c r="L153" s="11"/>
       <c r="M153" s="10"/>
       <c r="N153" s="10" t="s">
         <v>33</v>
@@ -10589,7 +10600,7 @@
       <c r="R153" s="11"/>
       <c r="S153" s="10"/>
     </row>
-    <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="154" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B154" s="10">
         <f>IF(C154="","",COUNTA($C$2:C154))</f>
         <v>153</v>
@@ -10601,20 +10612,20 @@
         <v>182</v>
       </c>
       <c r="E154" s="23" t="s">
-        <v>259</v>
+        <v>130</v>
       </c>
       <c r="F154" s="23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>266</v>
       </c>
       <c r="H154" s="25">
-        <v>9140500</v>
+        <v>5030650</v>
       </c>
       <c r="I154" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J154" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10622,7 +10633,7 @@
       </c>
       <c r="K154" s="11"/>
       <c r="L154" s="11">
-        <v>46097</v>
+        <v>46087</v>
       </c>
       <c r="M154" s="10"/>
       <c r="N154" s="10" t="s">
@@ -10632,7 +10643,7 @@
       <c r="R154" s="11"/>
       <c r="S154" s="10"/>
     </row>
-    <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="155" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B155" s="10">
         <f>IF(C155="","",COUNTA($C$2:C155))</f>
         <v>154</v>
@@ -10644,27 +10655,29 @@
         <v>182</v>
       </c>
       <c r="E155" s="23" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="F155" s="23" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>266</v>
       </c>
       <c r="H155" s="25">
-        <v>16695000</v>
+        <v>9140500</v>
       </c>
       <c r="I155" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J155" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K155" s="11"/>
-      <c r="L155" s="11"/>
+      <c r="L155" s="11">
+        <v>46097</v>
+      </c>
       <c r="M155" s="10"/>
       <c r="N155" s="10" t="s">
         <v>33</v>
@@ -10673,7 +10686,7 @@
       <c r="R155" s="11"/>
       <c r="S155" s="10"/>
     </row>
-    <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="156" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B156" s="10">
         <f>IF(C156="","",COUNTA($C$2:C156))</f>
         <v>155</v>
@@ -10694,7 +10707,7 @@
         <v>266</v>
       </c>
       <c r="H156" s="25">
-        <v>1870000</v>
+        <v>16695000</v>
       </c>
       <c r="I156" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10714,7 +10727,7 @@
       <c r="R156" s="11"/>
       <c r="S156" s="10"/>
     </row>
-    <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="157" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B157" s="10">
         <f>IF(C157="","",COUNTA($C$2:C157))</f>
         <v>156</v>
@@ -10726,16 +10739,16 @@
         <v>182</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="F157" s="23" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G157" s="6" t="s">
         <v>266</v>
       </c>
       <c r="H157" s="25">
-        <v>12478000</v>
+        <v>1870000</v>
       </c>
       <c r="I157" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10755,42 +10768,39 @@
       <c r="R157" s="11"/>
       <c r="S157" s="10"/>
     </row>
-    <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="158" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B158" s="10">
         <f>IF(C158="","",COUNTA($C$2:C158))</f>
         <v>157</v>
       </c>
-      <c r="C158" s="63">
-        <v>46090</v>
-      </c>
-      <c r="D158" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v>A</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>270</v>
+      <c r="C158" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E158" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F158" s="23" t="s">
+        <v>264</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="H158" s="4">
-        <v>29070400</v>
+        <v>266</v>
+      </c>
+      <c r="H158" s="25">
+        <v>12478000</v>
       </c>
       <c r="I158" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J158" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K158" s="11"/>
-      <c r="L158" s="11">
-        <v>46094</v>
-      </c>
+      <c r="L158" s="11"/>
       <c r="M158" s="10"/>
       <c r="N158" s="10" t="s">
         <v>33</v>
@@ -10804,35 +10814,37 @@
         <f>IF(C159="","",COUNTA($C$2:C159))</f>
         <v>158</v>
       </c>
-      <c r="C159" s="35" t="s">
-        <v>279</v>
+      <c r="C159" s="63">
+        <v>46090</v>
       </c>
       <c r="D159" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>B</v>
-      </c>
-      <c r="E159" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="F159" s="23" t="s">
-        <v>273</v>
+        <v>A</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H159" s="25">
-        <v>3390000</v>
+        <v>272</v>
+      </c>
+      <c r="H159" s="4">
+        <v>29070400</v>
       </c>
       <c r="I159" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J159" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K159" s="11"/>
-      <c r="L159" s="11"/>
+      <c r="L159" s="11">
+        <v>46094</v>
+      </c>
       <c r="M159" s="10"/>
       <c r="N159" s="10" t="s">
         <v>33</v>
@@ -10841,7 +10853,7 @@
       <c r="R159" s="11"/>
       <c r="S159" s="10"/>
     </row>
-    <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="160" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B160" s="10">
         <f>IF(C160="","",COUNTA($C$2:C160))</f>
         <v>159</v>
@@ -10854,16 +10866,16 @@
         <v>B</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>277</v>
+        <v>207</v>
       </c>
       <c r="F160" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G160" s="6" t="s">
         <v>280</v>
       </c>
       <c r="H160" s="25">
-        <v>9140500</v>
+        <v>3390000</v>
       </c>
       <c r="I160" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10883,7 +10895,7 @@
       <c r="R160" s="11"/>
       <c r="S160" s="10"/>
     </row>
-    <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="161" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B161" s="10">
         <f>IF(C161="","",COUNTA($C$2:C161))</f>
         <v>160</v>
@@ -10896,16 +10908,16 @@
         <v>B</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
       <c r="F161" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G161" s="6" t="s">
         <v>280</v>
       </c>
       <c r="H161" s="25">
-        <v>4719500</v>
+        <v>9140500</v>
       </c>
       <c r="I161" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -10925,7 +10937,7 @@
       <c r="R161" s="11"/>
       <c r="S161" s="10"/>
     </row>
-    <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="162" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B162" s="10">
         <f>IF(C162="","",COUNTA($C$2:C162))</f>
         <v>161</v>
@@ -10938,29 +10950,27 @@
         <v>B</v>
       </c>
       <c r="E162" s="23" t="s">
-        <v>278</v>
+        <v>215</v>
       </c>
       <c r="F162" s="23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G162" s="6" t="s">
         <v>280</v>
       </c>
       <c r="H162" s="25">
-        <v>38534600</v>
+        <v>4719500</v>
       </c>
       <c r="I162" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J162" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K162" s="11"/>
-      <c r="L162" s="11">
-        <v>46091</v>
-      </c>
+      <c r="L162" s="11"/>
       <c r="M162" s="10"/>
       <c r="N162" s="10" t="s">
         <v>33</v>
@@ -10969,32 +10979,33 @@
       <c r="R162" s="11"/>
       <c r="S162" s="10"/>
     </row>
-    <row r="163" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="163" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B163" s="10">
         <f>IF(C163="","",COUNTA($C$2:C163))</f>
         <v>162</v>
       </c>
       <c r="C163" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="D163" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="E163" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="F163" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
+      </c>
+      <c r="D163" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v>B</v>
+      </c>
+      <c r="E163" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="F163" s="23" t="s">
+        <v>276</v>
       </c>
       <c r="G163" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="H163" s="4">
-        <v>13694000</v>
+        <v>280</v>
+      </c>
+      <c r="H163" s="25">
+        <v>38534600</v>
       </c>
       <c r="I163" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J163" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11002,7 +11013,7 @@
       </c>
       <c r="K163" s="11"/>
       <c r="L163" s="11">
-        <v>46094</v>
+        <v>46091</v>
       </c>
       <c r="M163" s="10"/>
       <c r="N163" s="10" t="s">
@@ -11017,24 +11028,23 @@
         <f>IF(C164="","",COUNTA($C$2:C164))</f>
         <v>163</v>
       </c>
-      <c r="C164" s="35">
-        <v>46091</v>
-      </c>
-      <c r="D164" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v>A</v>
+      <c r="C164" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="D164" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="H164" s="4">
-        <v>59166000</v>
+        <v>13694000</v>
       </c>
       <c r="I164" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11062,33 +11072,36 @@
         <v>164</v>
       </c>
       <c r="C165" s="35">
-        <v>46092</v>
-      </c>
-      <c r="D165" s="10" t="s">
-        <v>185</v>
+        <v>46091</v>
+      </c>
+      <c r="D165" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v>A</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>173</v>
+        <v>288</v>
       </c>
       <c r="H165" s="4">
-        <v>4500000</v>
+        <v>59166000</v>
       </c>
       <c r="I165" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J165" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K165" s="11"/>
-      <c r="L165" s="11"/>
+      <c r="L165" s="11">
+        <v>46094</v>
+      </c>
       <c r="M165" s="10"/>
       <c r="N165" s="10" t="s">
         <v>33</v>
@@ -11097,33 +11110,32 @@
       <c r="R165" s="11"/>
       <c r="S165" s="10"/>
     </row>
-    <row r="166" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="166" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B166" s="10">
         <f>IF(C166="","",COUNTA($C$2:C166))</f>
         <v>165</v>
       </c>
-      <c r="C166" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="D166" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v>B</v>
-      </c>
-      <c r="E166" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="F166" s="23" t="s">
-        <v>291</v>
+      <c r="C166" s="35">
+        <v>46092</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="H166" s="25">
-        <v>8400000</v>
+        <v>173</v>
+      </c>
+      <c r="H166" s="4">
+        <v>4500000</v>
       </c>
       <c r="I166" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J166" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11139,7 +11151,7 @@
       <c r="R166" s="11"/>
       <c r="S166" s="10"/>
     </row>
-    <row r="167" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="167" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B167" s="10">
         <f>IF(C167="","",COUNTA($C$2:C167))</f>
         <v>166</v>
@@ -11152,16 +11164,16 @@
         <v>B</v>
       </c>
       <c r="E167" s="23" t="s">
-        <v>24</v>
+        <v>227</v>
       </c>
       <c r="F167" s="23" t="s">
-        <v>193</v>
+        <v>291</v>
       </c>
       <c r="G167" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H167" s="25">
-        <v>46282000</v>
+        <v>8400000</v>
       </c>
       <c r="I167" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11181,7 +11193,7 @@
       <c r="R167" s="11"/>
       <c r="S167" s="10"/>
     </row>
-    <row r="168" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="168" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B168" s="10">
         <f>IF(C168="","",COUNTA($C$2:C168))</f>
         <v>167</v>
@@ -11194,29 +11206,27 @@
         <v>B</v>
       </c>
       <c r="E168" s="23" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="F168" s="23" t="s">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="G168" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H168" s="25">
-        <v>1832500</v>
+        <v>46282000</v>
       </c>
       <c r="I168" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J168" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K168" s="11"/>
-      <c r="L168" s="11">
-        <v>46091</v>
-      </c>
+      <c r="L168" s="11"/>
       <c r="M168" s="10"/>
       <c r="N168" s="10" t="s">
         <v>33</v>
@@ -11225,7 +11235,7 @@
       <c r="R168" s="11"/>
       <c r="S168" s="10"/>
     </row>
-    <row r="169" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="169" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B169" s="10">
         <f>IF(C169="","",COUNTA($C$2:C169))</f>
         <v>168</v>
@@ -11238,20 +11248,20 @@
         <v>B</v>
       </c>
       <c r="E169" s="23" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="F169" s="23" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G169" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H169" s="25">
-        <v>222000</v>
+        <v>1832500</v>
       </c>
       <c r="I169" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J169" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11259,7 +11269,7 @@
       </c>
       <c r="K169" s="11"/>
       <c r="L169" s="11">
-        <v>46094</v>
+        <v>46091</v>
       </c>
       <c r="M169" s="10"/>
       <c r="N169" s="10" t="s">
@@ -11269,7 +11279,7 @@
       <c r="R169" s="11"/>
       <c r="S169" s="10"/>
     </row>
-    <row r="170" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="170" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B170" s="10">
         <f>IF(C170="","",COUNTA($C$2:C170))</f>
         <v>169</v>
@@ -11282,27 +11292,29 @@
         <v>B</v>
       </c>
       <c r="E170" s="23" t="s">
-        <v>277</v>
+        <v>122</v>
       </c>
       <c r="F170" s="23" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G170" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H170" s="25">
-        <v>14080000</v>
+        <v>222000</v>
       </c>
       <c r="I170" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J170" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K170" s="11"/>
-      <c r="L170" s="11"/>
+      <c r="L170" s="11">
+        <v>46094</v>
+      </c>
       <c r="M170" s="10"/>
       <c r="N170" s="10" t="s">
         <v>33</v>
@@ -11311,7 +11323,7 @@
       <c r="R170" s="11"/>
       <c r="S170" s="10"/>
     </row>
-    <row r="171" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="171" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B171" s="10">
         <f>IF(C171="","",COUNTA($C$2:C171))</f>
         <v>170</v>
@@ -11324,7 +11336,7 @@
         <v>B</v>
       </c>
       <c r="E171" s="23" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="F171" s="23" t="s">
         <v>294</v>
@@ -11337,16 +11349,14 @@
       </c>
       <c r="I171" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J171" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K171" s="11"/>
-      <c r="L171" s="11">
-        <v>46097</v>
-      </c>
+      <c r="L171" s="11"/>
       <c r="M171" s="10"/>
       <c r="N171" s="10" t="s">
         <v>33</v>
@@ -11355,7 +11365,7 @@
       <c r="R171" s="11"/>
       <c r="S171" s="10"/>
     </row>
-    <row r="172" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="172" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B172" s="10">
         <f>IF(C172="","",COUNTA($C$2:C172))</f>
         <v>171</v>
@@ -11368,27 +11378,29 @@
         <v>B</v>
       </c>
       <c r="E172" s="23" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="F172" s="23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G172" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H172" s="25">
-        <v>1186600</v>
+        <v>14080000</v>
       </c>
       <c r="I172" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J172" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K172" s="11"/>
-      <c r="L172" s="11"/>
+      <c r="L172" s="11">
+        <v>46097</v>
+      </c>
       <c r="M172" s="10"/>
       <c r="N172" s="10" t="s">
         <v>33</v>
@@ -11397,7 +11409,7 @@
       <c r="R172" s="11"/>
       <c r="S172" s="10"/>
     </row>
-    <row r="173" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="173" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B173" s="10">
         <f>IF(C173="","",COUNTA($C$2:C173))</f>
         <v>172</v>
@@ -11410,16 +11422,16 @@
         <v>B</v>
       </c>
       <c r="E173" s="23" t="s">
-        <v>62</v>
+        <v>231</v>
       </c>
       <c r="F173" s="23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G173" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H173" s="25">
-        <v>270000</v>
+        <v>1186600</v>
       </c>
       <c r="I173" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11439,7 +11451,7 @@
       <c r="R173" s="11"/>
       <c r="S173" s="10"/>
     </row>
-    <row r="174" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="174" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B174" s="10">
         <f>IF(C174="","",COUNTA($C$2:C174))</f>
         <v>173</v>
@@ -11452,16 +11464,16 @@
         <v>B</v>
       </c>
       <c r="E174" s="23" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F174" s="23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G174" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H174" s="25">
-        <v>5912000</v>
+        <v>270000</v>
       </c>
       <c r="I174" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11481,7 +11493,7 @@
       <c r="R174" s="11"/>
       <c r="S174" s="10"/>
     </row>
-    <row r="175" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="175" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B175" s="10">
         <f>IF(C175="","",COUNTA($C$2:C175))</f>
         <v>174</v>
@@ -11497,13 +11509,13 @@
         <v>24</v>
       </c>
       <c r="F175" s="23" t="s">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="G175" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H175" s="25">
-        <v>4992000</v>
+        <v>5912000</v>
       </c>
       <c r="I175" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11523,7 +11535,7 @@
       <c r="R175" s="11"/>
       <c r="S175" s="10"/>
     </row>
-    <row r="176" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="176" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B176" s="10">
         <f>IF(C176="","",COUNTA($C$2:C176))</f>
         <v>175</v>
@@ -11536,29 +11548,27 @@
         <v>B</v>
       </c>
       <c r="E176" s="23" t="s">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="F176" s="23" t="s">
-        <v>298</v>
+        <v>193</v>
       </c>
       <c r="G176" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H176" s="25">
-        <v>950350</v>
+        <v>4992000</v>
       </c>
       <c r="I176" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J176" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K176" s="11"/>
-      <c r="L176" s="11">
-        <v>46091</v>
-      </c>
+      <c r="L176" s="11"/>
       <c r="M176" s="10"/>
       <c r="N176" s="10" t="s">
         <v>33</v>
@@ -11567,7 +11577,7 @@
       <c r="R176" s="11"/>
       <c r="S176" s="10"/>
     </row>
-    <row r="177" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="177" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B177" s="10">
         <f>IF(C177="","",COUNTA($C$2:C177))</f>
         <v>176</v>
@@ -11580,27 +11590,29 @@
         <v>B</v>
       </c>
       <c r="E177" s="23" t="s">
-        <v>215</v>
+        <v>130</v>
       </c>
       <c r="F177" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G177" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H177" s="25">
-        <v>770400</v>
+        <v>950350</v>
       </c>
       <c r="I177" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J177" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K177" s="11"/>
-      <c r="L177" s="11"/>
+      <c r="L177" s="11">
+        <v>46091</v>
+      </c>
       <c r="M177" s="10"/>
       <c r="N177" s="10" t="s">
         <v>33</v>
@@ -11609,7 +11621,7 @@
       <c r="R177" s="11"/>
       <c r="S177" s="10"/>
     </row>
-    <row r="178" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="178" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B178" s="10">
         <f>IF(C178="","",COUNTA($C$2:C178))</f>
         <v>177</v>
@@ -11622,29 +11634,27 @@
         <v>B</v>
       </c>
       <c r="E178" s="23" t="s">
-        <v>307</v>
+        <v>215</v>
       </c>
       <c r="F178" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G178" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H178" s="25">
-        <v>473600</v>
+        <v>770400</v>
       </c>
       <c r="I178" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J178" s="13" t="str">
         <f t="shared" ca="1" si="11"/>
         <v>정상</v>
       </c>
       <c r="K178" s="11"/>
-      <c r="L178" s="11">
-        <v>46091</v>
-      </c>
+      <c r="L178" s="11"/>
       <c r="M178" s="10"/>
       <c r="N178" s="10" t="s">
         <v>33</v>
@@ -11653,92 +11663,94 @@
       <c r="R178" s="11"/>
       <c r="S178" s="10"/>
     </row>
-    <row r="179" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="179" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B179" s="10">
         <f>IF(C179="","",COUNTA($C$2:C179))</f>
         <v>178</v>
       </c>
       <c r="C179" s="35" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D179" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E179" s="23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F179" s="23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G179" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H179" s="25">
-        <v>121500</v>
+        <v>473600</v>
       </c>
       <c r="I179" s="6">
         <f t="shared" ca="1" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J179" s="13" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v>정상</v>
+      </c>
+      <c r="K179" s="11"/>
+      <c r="L179" s="11">
+        <v>46091</v>
+      </c>
+      <c r="M179" s="10"/>
+      <c r="N179" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q179" s="11"/>
+      <c r="R179" s="11"/>
+      <c r="S179" s="10"/>
+    </row>
+    <row r="180" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B180" s="10">
+        <f>IF(C180="","",COUNTA($C$2:C180))</f>
+        <v>179</v>
+      </c>
+      <c r="C180" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="D180" s="10" t="str">
+        <f t="shared" si="12"/>
+        <v>B</v>
+      </c>
+      <c r="E180" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="F180" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="G180" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="H180" s="25">
+        <v>121500</v>
+      </c>
+      <c r="I180" s="6">
+        <f t="shared" ca="1" si="13"/>
         <v>9</v>
       </c>
-      <c r="J179" s="13" t="str">
-        <f t="shared" ref="J179:J242" ca="1" si="14">IF(I179="","",
- IF(G179="선급금",
-   IF(I179&lt;=20,"정상",IF(I179&lt;=90,"관리","장기미수")),
- IF(G179="자재",
-   IF(I179&lt;=40,"정상",IF(I179&lt;=90,"관리","장기미수")),
-   IF(I179&lt;=30,"정상",IF(I179&lt;=90,"관리","장기미수"))
+      <c r="J180" s="13" t="str">
+        <f t="shared" ref="J180:J243" ca="1" si="14">IF(I180="","",
+ IF(G180="선급금",
+   IF(I180&lt;=20,"정상",IF(I180&lt;=90,"관리","장기미수")),
+ IF(G180="자재",
+   IF(I180&lt;=40,"정상",IF(I180&lt;=90,"관리","장기미수")),
+   IF(I180&lt;=30,"정상",IF(I180&lt;=90,"관리","장기미수"))
   )
  )
 )</f>
         <v>정상</v>
       </c>
-      <c r="K179" s="11"/>
-      <c r="L179" s="11">
+      <c r="K180" s="11"/>
+      <c r="L180" s="11">
         <v>46101</v>
       </c>
-      <c r="M179" s="10"/>
-      <c r="N179" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q179" s="11"/>
-      <c r="R179" s="11"/>
-      <c r="S179" s="10"/>
-    </row>
-    <row r="180" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B180" s="10">
-        <f>IF(C180="","",COUNTA($C$2:C180))</f>
-        <v>179</v>
-      </c>
-      <c r="C180" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="D180" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v>B</v>
-      </c>
-      <c r="E180" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="F180" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="G180" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="H180" s="25">
-        <v>16818900</v>
-      </c>
-      <c r="I180" s="6">
-        <f t="shared" ca="1" si="13"/>
-        <v>14</v>
-      </c>
-      <c r="J180" s="13" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v>정상</v>
-      </c>
-      <c r="K180" s="11"/>
-      <c r="L180" s="11"/>
       <c r="M180" s="10"/>
       <c r="N180" s="10" t="s">
         <v>33</v>
@@ -11747,7 +11759,7 @@
       <c r="R180" s="11"/>
       <c r="S180" s="10"/>
     </row>
-    <row r="181" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="181" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B181" s="10">
         <f>IF(C181="","",COUNTA($C$2:C181))</f>
         <v>180</v>
@@ -11760,29 +11772,27 @@
         <v>B</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F181" s="23" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G181" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H181" s="25">
-        <v>294800</v>
+        <v>16818900</v>
       </c>
       <c r="I181" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J181" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K181" s="11"/>
-      <c r="L181" s="11">
-        <v>46101</v>
-      </c>
+      <c r="L181" s="11"/>
       <c r="M181" s="10"/>
       <c r="N181" s="10" t="s">
         <v>33</v>
@@ -11791,7 +11801,7 @@
       <c r="R181" s="11"/>
       <c r="S181" s="10"/>
     </row>
-    <row r="182" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="182" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B182" s="10">
         <f>IF(C182="","",COUNTA($C$2:C182))</f>
         <v>181</v>
@@ -11804,27 +11814,29 @@
         <v>B</v>
       </c>
       <c r="E182" s="23" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="F182" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G182" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H182" s="25">
-        <v>321000</v>
+        <v>294800</v>
       </c>
       <c r="I182" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J182" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K182" s="11"/>
-      <c r="L182" s="11"/>
+      <c r="L182" s="11">
+        <v>46101</v>
+      </c>
       <c r="M182" s="10"/>
       <c r="N182" s="10" t="s">
         <v>33</v>
@@ -11833,7 +11845,7 @@
       <c r="R182" s="11"/>
       <c r="S182" s="10"/>
     </row>
-    <row r="183" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="183" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B183" s="10">
         <f>IF(C183="","",COUNTA($C$2:C183))</f>
         <v>182</v>
@@ -11846,16 +11858,16 @@
         <v>B</v>
       </c>
       <c r="E183" s="23" t="s">
-        <v>309</v>
+        <v>118</v>
       </c>
       <c r="F183" s="23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G183" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H183" s="25">
-        <v>1275400</v>
+        <v>321000</v>
       </c>
       <c r="I183" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11875,7 +11887,7 @@
       <c r="R183" s="11"/>
       <c r="S183" s="10"/>
     </row>
-    <row r="184" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="184" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B184" s="10">
         <f>IF(C184="","",COUNTA($C$2:C184))</f>
         <v>183</v>
@@ -11888,16 +11900,16 @@
         <v>B</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>24</v>
+        <v>309</v>
       </c>
       <c r="F184" s="23" t="s">
-        <v>193</v>
+        <v>305</v>
       </c>
       <c r="G184" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H184" s="25">
-        <v>11000000</v>
+        <v>1275400</v>
       </c>
       <c r="I184" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11917,7 +11929,7 @@
       <c r="R184" s="11"/>
       <c r="S184" s="10"/>
     </row>
-    <row r="185" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="185" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B185" s="10">
         <f>IF(C185="","",COUNTA($C$2:C185))</f>
         <v>184</v>
@@ -11930,16 +11942,16 @@
         <v>B</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F185" s="23" t="s">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="G185" s="6" t="s">
         <v>310</v>
       </c>
       <c r="H185" s="25">
-        <v>5475500</v>
+        <v>11000000</v>
       </c>
       <c r="I185" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -11959,42 +11971,40 @@
       <c r="R185" s="11"/>
       <c r="S185" s="10"/>
     </row>
-    <row r="186" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="186" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B186" s="10">
         <f>IF(C186="","",COUNTA($C$2:C186))</f>
         <v>185</v>
       </c>
-      <c r="C186" s="35">
-        <v>46093</v>
+      <c r="C186" s="35" t="s">
+        <v>287</v>
       </c>
       <c r="D186" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
       <c r="F186" s="23" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="H186" s="25">
-        <v>312000</v>
+        <v>5475500</v>
       </c>
       <c r="I186" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J186" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K186" s="11"/>
-      <c r="L186" s="11">
-        <v>46093</v>
-      </c>
+      <c r="L186" s="11"/>
       <c r="M186" s="10"/>
       <c r="N186" s="10" t="s">
         <v>33</v>
@@ -12003,40 +12013,42 @@
       <c r="R186" s="11"/>
       <c r="S186" s="10"/>
     </row>
-    <row r="187" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="187" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B187" s="10">
         <f>IF(C187="","",COUNTA($C$2:C187))</f>
         <v>186</v>
       </c>
-      <c r="C187" s="35" t="s">
-        <v>318</v>
+      <c r="C187" s="35">
+        <v>46093</v>
       </c>
       <c r="D187" s="10" t="str">
         <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E187" s="23" t="s">
-        <v>30</v>
+        <v>307</v>
       </c>
       <c r="F187" s="23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G187" s="6" t="s">
         <v>319</v>
       </c>
       <c r="H187" s="25">
-        <v>1000500</v>
+        <v>312000</v>
       </c>
       <c r="I187" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J187" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K187" s="11"/>
-      <c r="L187" s="11"/>
+      <c r="L187" s="11">
+        <v>46093</v>
+      </c>
       <c r="M187" s="10"/>
       <c r="N187" s="10" t="s">
         <v>33</v>
@@ -12045,7 +12057,7 @@
       <c r="R187" s="11"/>
       <c r="S187" s="10"/>
     </row>
-    <row r="188" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="188" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B188" s="10">
         <f>IF(C188="","",COUNTA($C$2:C188))</f>
         <v>187</v>
@@ -12058,16 +12070,16 @@
         <v>B</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>203</v>
+        <v>30</v>
       </c>
       <c r="F188" s="23" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G188" s="6" t="s">
         <v>319</v>
       </c>
       <c r="H188" s="25">
-        <v>5775000</v>
+        <v>1000500</v>
       </c>
       <c r="I188" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12087,7 +12099,7 @@
       <c r="R188" s="11"/>
       <c r="S188" s="10"/>
     </row>
-    <row r="189" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="189" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B189" s="10">
         <f>IF(C189="","",COUNTA($C$2:C189))</f>
         <v>188</v>
@@ -12100,16 +12112,16 @@
         <v>B</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F189" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G189" s="6" t="s">
         <v>319</v>
       </c>
       <c r="H189" s="25">
-        <v>1190000</v>
+        <v>5775000</v>
       </c>
       <c r="I189" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12129,7 +12141,7 @@
       <c r="R189" s="11"/>
       <c r="S189" s="10"/>
     </row>
-    <row r="190" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="190" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B190" s="10">
         <f>IF(C190="","",COUNTA($C$2:C190))</f>
         <v>189</v>
@@ -12142,16 +12154,16 @@
         <v>B</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="F190" s="23" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G190" s="6" t="s">
         <v>319</v>
       </c>
       <c r="H190" s="25">
-        <v>11147800</v>
+        <v>1190000</v>
       </c>
       <c r="I190" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12171,7 +12183,7 @@
       <c r="R190" s="11"/>
       <c r="S190" s="10"/>
     </row>
-    <row r="191" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="191" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B191" s="10">
         <f>IF(C191="","",COUNTA($C$2:C191))</f>
         <v>190</v>
@@ -12184,16 +12196,16 @@
         <v>B</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>227</v>
+        <v>101</v>
       </c>
       <c r="F191" s="23" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G191" s="6" t="s">
         <v>319</v>
       </c>
       <c r="H191" s="25">
-        <v>2613000</v>
+        <v>11147800</v>
       </c>
       <c r="I191" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12213,7 +12225,7 @@
       <c r="R191" s="11"/>
       <c r="S191" s="10"/>
     </row>
-    <row r="192" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="192" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B192" s="10">
         <f>IF(C192="","",COUNTA($C$2:C192))</f>
         <v>191</v>
@@ -12226,16 +12238,16 @@
         <v>B</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>112</v>
+        <v>227</v>
       </c>
       <c r="F192" s="23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G192" s="6" t="s">
         <v>319</v>
       </c>
       <c r="H192" s="25">
-        <v>7339000</v>
+        <v>2613000</v>
       </c>
       <c r="I192" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12255,33 +12267,33 @@
       <c r="R192" s="11"/>
       <c r="S192" s="10"/>
     </row>
-    <row r="193" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="193" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B193" s="10">
         <f>IF(C193="","",COUNTA($C$2:C193))</f>
         <v>192</v>
       </c>
-      <c r="C193" s="11">
-        <v>46094</v>
+      <c r="C193" s="35" t="s">
+        <v>318</v>
       </c>
       <c r="D193" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>C</v>
-      </c>
-      <c r="E193" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="F193" s="6" t="s">
-        <v>321</v>
+        <v>B</v>
+      </c>
+      <c r="E193" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="F193" s="23" t="s">
+        <v>315</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="H193" s="4">
-        <v>1291250</v>
+        <v>319</v>
+      </c>
+      <c r="H193" s="25">
+        <v>7339000</v>
       </c>
       <c r="I193" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J193" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12297,29 +12309,29 @@
       <c r="R193" s="11"/>
       <c r="S193" s="10"/>
     </row>
-    <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="194" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B194" s="10">
         <f>IF(C194="","",COUNTA($C$2:C194))</f>
         <v>193</v>
       </c>
-      <c r="C194" s="35" t="s">
-        <v>332</v>
+      <c r="C194" s="11">
+        <v>46094</v>
       </c>
       <c r="D194" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>B</v>
-      </c>
-      <c r="E194" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="F194" s="23" t="s">
-        <v>323</v>
+        <v>C</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>321</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="H194" s="25">
-        <v>500500</v>
+        <v>322</v>
+      </c>
+      <c r="H194" s="4">
+        <v>1291250</v>
       </c>
       <c r="I194" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12339,7 +12351,7 @@
       <c r="R194" s="11"/>
       <c r="S194" s="10"/>
     </row>
-    <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="195" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B195" s="10">
         <f>IF(C195="","",COUNTA($C$2:C195))</f>
         <v>194</v>
@@ -12352,16 +12364,16 @@
         <v>B</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>24</v>
+        <v>330</v>
       </c>
       <c r="F195" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G195" s="6" t="s">
         <v>333</v>
       </c>
       <c r="H195" s="25">
-        <v>3448000</v>
+        <v>500500</v>
       </c>
       <c r="I195" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12381,7 +12393,7 @@
       <c r="R195" s="11"/>
       <c r="S195" s="10"/>
     </row>
-    <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="196" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B196" s="10">
         <f>IF(C196="","",COUNTA($C$2:C196))</f>
         <v>195</v>
@@ -12397,13 +12409,13 @@
         <v>24</v>
       </c>
       <c r="F196" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G196" s="6" t="s">
         <v>333</v>
       </c>
       <c r="H196" s="25">
-        <v>28750000</v>
+        <v>3448000</v>
       </c>
       <c r="I196" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12423,7 +12435,7 @@
       <c r="R196" s="11"/>
       <c r="S196" s="10"/>
     </row>
-    <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="197" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B197" s="10">
         <f>IF(C197="","",COUNTA($C$2:C197))</f>
         <v>196</v>
@@ -12436,29 +12448,27 @@
         <v>B</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>229</v>
+        <v>24</v>
       </c>
       <c r="F197" s="23" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G197" s="6" t="s">
         <v>333</v>
       </c>
       <c r="H197" s="25">
-        <v>3430000</v>
+        <v>28750000</v>
       </c>
       <c r="I197" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J197" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K197" s="11"/>
-      <c r="L197" s="11">
-        <v>46097</v>
-      </c>
+      <c r="L197" s="11"/>
       <c r="M197" s="10"/>
       <c r="N197" s="10" t="s">
         <v>33</v>
@@ -12467,7 +12477,7 @@
       <c r="R197" s="11"/>
       <c r="S197" s="10"/>
     </row>
-    <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="198" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B198" s="10">
         <f>IF(C198="","",COUNTA($C$2:C198))</f>
         <v>197</v>
@@ -12480,27 +12490,29 @@
         <v>B</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F198" s="23" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G198" s="6" t="s">
         <v>333</v>
       </c>
       <c r="H198" s="25">
-        <v>14700000</v>
+        <v>3430000</v>
       </c>
       <c r="I198" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J198" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K198" s="11"/>
-      <c r="L198" s="11"/>
+      <c r="L198" s="11">
+        <v>46097</v>
+      </c>
       <c r="M198" s="10"/>
       <c r="N198" s="10" t="s">
         <v>33</v>
@@ -12509,7 +12521,7 @@
       <c r="R198" s="11"/>
       <c r="S198" s="10"/>
     </row>
-    <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="199" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B199" s="10">
         <f>IF(C199="","",COUNTA($C$2:C199))</f>
         <v>198</v>
@@ -12522,16 +12534,16 @@
         <v>B</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>331</v>
+        <v>227</v>
       </c>
       <c r="F199" s="23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G199" s="6" t="s">
         <v>333</v>
       </c>
       <c r="H199" s="25">
-        <v>780000</v>
+        <v>14700000</v>
       </c>
       <c r="I199" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12551,7 +12563,7 @@
       <c r="R199" s="11"/>
       <c r="S199" s="10"/>
     </row>
-    <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="200" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B200" s="10">
         <f>IF(C200="","",COUNTA($C$2:C200))</f>
         <v>199</v>
@@ -12564,16 +12576,16 @@
         <v>B</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>39</v>
+        <v>331</v>
       </c>
       <c r="F200" s="23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G200" s="6" t="s">
         <v>333</v>
       </c>
       <c r="H200" s="25">
-        <v>220100</v>
+        <v>780000</v>
       </c>
       <c r="I200" s="6">
         <f t="shared" ca="1" si="13"/>
@@ -12593,33 +12605,33 @@
       <c r="R200" s="11"/>
       <c r="S200" s="10"/>
     </row>
-    <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="201" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B201" s="10">
         <f>IF(C201="","",COUNTA($C$2:C201))</f>
         <v>200</v>
       </c>
-      <c r="C201" s="35">
-        <v>46097</v>
+      <c r="C201" s="35" t="s">
+        <v>332</v>
       </c>
       <c r="D201" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>A</v>
-      </c>
-      <c r="E201" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="F201" s="6" t="s">
-        <v>335</v>
+        <v>B</v>
+      </c>
+      <c r="E201" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="F201" s="23" t="s">
+        <v>329</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="H201" s="4">
-        <v>22342800</v>
+        <v>333</v>
+      </c>
+      <c r="H201" s="25">
+        <v>220100</v>
       </c>
       <c r="I201" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J201" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12640,28 +12652,28 @@
         <f>IF(C202="","",COUNTA($C$2:C202))</f>
         <v>201</v>
       </c>
-      <c r="C202" s="35" t="s">
-        <v>337</v>
+      <c r="C202" s="35">
+        <v>46097</v>
       </c>
       <c r="D202" s="10" t="str">
         <f t="shared" si="12"/>
-        <v>B</v>
-      </c>
-      <c r="E202" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="F202" s="23" t="s">
-        <v>338</v>
+        <v>A</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>335</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="H202" s="25">
-        <v>19467400</v>
+        <v>336</v>
+      </c>
+      <c r="H202" s="4">
+        <v>22342800</v>
       </c>
       <c r="I202" s="6">
         <f t="shared" ca="1" si="13"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J202" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -12677,7 +12689,7 @@
       <c r="R202" s="11"/>
       <c r="S202" s="10"/>
     </row>
-    <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="203" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B203" s="10">
         <f>IF(C203="","",COUNTA($C$2:C203))</f>
         <v>202</v>
@@ -12686,7 +12698,7 @@
         <v>337</v>
       </c>
       <c r="D203" s="10" t="str">
-        <f t="shared" ref="D203:D266" si="15">IF(G203="","",IF(OR(G203="선급금",G203="중도금",G203="잔금"),"A",IF(G203="자재","B",IF(G203="특허료","C",""))))</f>
+        <f t="shared" si="12"/>
         <v>B</v>
       </c>
       <c r="E203" s="23" t="s">
@@ -12699,10 +12711,10 @@
         <v>351</v>
       </c>
       <c r="H203" s="25">
-        <v>4765000</v>
+        <v>19467400</v>
       </c>
       <c r="I203" s="6">
-        <f t="shared" ref="I203:I266" ca="1" si="16">IF(C203="","",IF(L203="",TODAY()-C203,L203-C203))</f>
+        <f t="shared" ca="1" si="13"/>
         <v>8</v>
       </c>
       <c r="J203" s="13" t="str">
@@ -12719,7 +12731,7 @@
       <c r="R203" s="11"/>
       <c r="S203" s="10"/>
     </row>
-    <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="204" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B204" s="10">
         <f>IF(C204="","",COUNTA($C$2:C204))</f>
         <v>203</v>
@@ -12728,23 +12740,23 @@
         <v>337</v>
       </c>
       <c r="D204" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="D204:D267" si="15">IF(G204="","",IF(OR(G204="선급금",G204="중도금",G204="잔금"),"A",IF(G204="자재","B",IF(G204="특허료","C",""))))</f>
         <v>B</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="F204" s="23" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G204" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H204" s="25">
-        <v>954500</v>
+        <v>4765000</v>
       </c>
       <c r="I204" s="6">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" ref="I204:I267" ca="1" si="16">IF(C204="","",IF(L204="",TODAY()-C204,L204-C204))</f>
         <v>8</v>
       </c>
       <c r="J204" s="13" t="str">
@@ -12761,7 +12773,7 @@
       <c r="R204" s="11"/>
       <c r="S204" s="10"/>
     </row>
-    <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="205" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B205" s="10">
         <f>IF(C205="","",COUNTA($C$2:C205))</f>
         <v>204</v>
@@ -12774,16 +12786,16 @@
         <v>B</v>
       </c>
       <c r="E205" s="23" t="s">
-        <v>101</v>
+        <v>231</v>
       </c>
       <c r="F205" s="23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G205" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H205" s="25">
-        <v>9631000</v>
+        <v>954500</v>
       </c>
       <c r="I205" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -12803,7 +12815,7 @@
       <c r="R205" s="11"/>
       <c r="S205" s="10"/>
     </row>
-    <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="206" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B206" s="10">
         <f>IF(C206="","",COUNTA($C$2:C206))</f>
         <v>205</v>
@@ -12816,16 +12828,16 @@
         <v>B</v>
       </c>
       <c r="E206" s="23" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="F206" s="23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G206" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H206" s="25">
-        <v>1745000</v>
+        <v>9631000</v>
       </c>
       <c r="I206" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -12845,7 +12857,7 @@
       <c r="R206" s="11"/>
       <c r="S206" s="10"/>
     </row>
-    <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="207" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B207" s="10">
         <f>IF(C207="","",COUNTA($C$2:C207))</f>
         <v>206</v>
@@ -12858,16 +12870,16 @@
         <v>B</v>
       </c>
       <c r="E207" s="23" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="F207" s="23" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G207" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H207" s="25">
-        <v>493400</v>
+        <v>1745000</v>
       </c>
       <c r="I207" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -12887,7 +12899,7 @@
       <c r="R207" s="11"/>
       <c r="S207" s="10"/>
     </row>
-    <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="208" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B208" s="10">
         <f>IF(C208="","",COUNTA($C$2:C208))</f>
         <v>207</v>
@@ -12903,13 +12915,13 @@
         <v>128</v>
       </c>
       <c r="F208" s="23" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G208" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H208" s="25">
-        <v>3568200</v>
+        <v>493400</v>
       </c>
       <c r="I208" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -12929,7 +12941,7 @@
       <c r="R208" s="11"/>
       <c r="S208" s="10"/>
     </row>
-    <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="209" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B209" s="10">
         <f>IF(C209="","",COUNTA($C$2:C209))</f>
         <v>208</v>
@@ -12951,7 +12963,7 @@
         <v>351</v>
       </c>
       <c r="H209" s="25">
-        <v>4110300</v>
+        <v>3568200</v>
       </c>
       <c r="I209" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -12971,7 +12983,7 @@
       <c r="R209" s="11"/>
       <c r="S209" s="10"/>
     </row>
-    <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="210" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B210" s="10">
         <f>IF(C210="","",COUNTA($C$2:C210))</f>
         <v>209</v>
@@ -12984,29 +12996,27 @@
         <v>B</v>
       </c>
       <c r="E210" s="23" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="F210" s="23" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G210" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H210" s="25">
-        <v>1318600</v>
+        <v>4110300</v>
       </c>
       <c r="I210" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J210" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K210" s="11"/>
-      <c r="L210" s="11">
-        <v>46105</v>
-      </c>
+      <c r="L210" s="11"/>
       <c r="M210" s="10"/>
       <c r="N210" s="10" t="s">
         <v>33</v>
@@ -13015,7 +13025,7 @@
       <c r="R210" s="11"/>
       <c r="S210" s="10"/>
     </row>
-    <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="211" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B211" s="10">
         <f>IF(C211="","",COUNTA($C$2:C211))</f>
         <v>210</v>
@@ -13028,27 +13038,29 @@
         <v>B</v>
       </c>
       <c r="E211" s="23" t="s">
-        <v>350</v>
+        <v>166</v>
       </c>
       <c r="F211" s="23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G211" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H211" s="25">
-        <v>3541500</v>
+        <v>1318600</v>
       </c>
       <c r="I211" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J211" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K211" s="11"/>
-      <c r="L211" s="11"/>
+      <c r="L211" s="11">
+        <v>46105</v>
+      </c>
       <c r="M211" s="10"/>
       <c r="N211" s="10" t="s">
         <v>33</v>
@@ -13057,7 +13069,7 @@
       <c r="R211" s="11"/>
       <c r="S211" s="10"/>
     </row>
-    <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="212" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B212" s="10">
         <f>IF(C212="","",COUNTA($C$2:C212))</f>
         <v>211</v>
@@ -13070,16 +13082,16 @@
         <v>B</v>
       </c>
       <c r="E212" s="23" t="s">
-        <v>215</v>
+        <v>350</v>
       </c>
       <c r="F212" s="23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G212" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H212" s="25">
-        <v>3512300</v>
+        <v>3541500</v>
       </c>
       <c r="I212" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13099,7 +13111,7 @@
       <c r="R212" s="11"/>
       <c r="S212" s="10"/>
     </row>
-    <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="213" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B213" s="10">
         <f>IF(C213="","",COUNTA($C$2:C213))</f>
         <v>212</v>
@@ -13112,16 +13124,16 @@
         <v>B</v>
       </c>
       <c r="E213" s="23" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="F213" s="23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G213" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H213" s="25">
-        <v>11000000</v>
+        <v>3512300</v>
       </c>
       <c r="I213" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13141,7 +13153,7 @@
       <c r="R213" s="11"/>
       <c r="S213" s="10"/>
     </row>
-    <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="214" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B214" s="10">
         <f>IF(C214="","",COUNTA($C$2:C214))</f>
         <v>213</v>
@@ -13154,16 +13166,16 @@
         <v>B</v>
       </c>
       <c r="E214" s="23" t="s">
-        <v>110</v>
+        <v>259</v>
       </c>
       <c r="F214" s="23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G214" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H214" s="25">
-        <v>21000000</v>
+        <v>11000000</v>
       </c>
       <c r="I214" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13183,7 +13195,7 @@
       <c r="R214" s="11"/>
       <c r="S214" s="10"/>
     </row>
-    <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="215" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B215" s="10">
         <f>IF(C215="","",COUNTA($C$2:C215))</f>
         <v>214</v>
@@ -13196,16 +13208,16 @@
         <v>B</v>
       </c>
       <c r="E215" s="23" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F215" s="23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G215" s="6" t="s">
         <v>351</v>
       </c>
       <c r="H215" s="25">
-        <v>806000</v>
+        <v>21000000</v>
       </c>
       <c r="I215" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13225,33 +13237,33 @@
       <c r="R215" s="11"/>
       <c r="S215" s="10"/>
     </row>
-    <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="216" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B216" s="10">
         <f>IF(C216="","",COUNTA($C$2:C216))</f>
         <v>215</v>
       </c>
-      <c r="C216" s="63">
-        <v>46099</v>
+      <c r="C216" s="35" t="s">
+        <v>337</v>
       </c>
       <c r="D216" s="10" t="str">
         <f t="shared" si="15"/>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E216" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="F216" s="65" t="s">
-        <v>352</v>
+        <v>118</v>
+      </c>
+      <c r="F216" s="23" t="s">
+        <v>349</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="H216" s="64">
-        <v>4354200</v>
+        <v>351</v>
+      </c>
+      <c r="H216" s="25">
+        <v>806000</v>
       </c>
       <c r="I216" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J216" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13279,17 +13291,17 @@
         <f t="shared" si="15"/>
         <v>A</v>
       </c>
-      <c r="E217" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F217" s="6" t="s">
-        <v>355</v>
+      <c r="E217" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="F217" s="65" t="s">
+        <v>352</v>
       </c>
       <c r="G217" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="H217" s="4">
-        <v>28530900</v>
+      <c r="H217" s="64">
+        <v>4354200</v>
       </c>
       <c r="I217" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13322,29 +13334,27 @@
         <v>A</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>358</v>
+        <v>118</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G218" s="6" t="s">
         <v>354</v>
       </c>
       <c r="H218" s="4">
-        <v>26089600</v>
+        <v>28530900</v>
       </c>
       <c r="I218" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J218" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K218" s="11"/>
-      <c r="L218" s="11">
-        <v>46099</v>
-      </c>
+      <c r="L218" s="11"/>
       <c r="M218" s="10"/>
       <c r="N218" s="10" t="s">
         <v>33</v>
@@ -13366,27 +13376,29 @@
         <v>A</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G219" s="6" t="s">
         <v>354</v>
       </c>
       <c r="H219" s="4">
-        <v>27749100</v>
+        <v>26089600</v>
       </c>
       <c r="I219" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J219" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K219" s="11"/>
-      <c r="L219" s="11"/>
+      <c r="L219" s="11">
+        <v>46099</v>
+      </c>
       <c r="M219" s="10"/>
       <c r="N219" s="10" t="s">
         <v>33</v>
@@ -13400,37 +13412,35 @@
         <f>IF(C220="","",COUNTA($C$2:C220))</f>
         <v>219</v>
       </c>
-      <c r="C220" s="11" t="s">
-        <v>385</v>
+      <c r="C220" s="63">
+        <v>46099</v>
       </c>
       <c r="D220" s="10" t="str">
         <f t="shared" si="15"/>
-        <v>B</v>
-      </c>
-      <c r="E220" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="F220" s="23" t="s">
-        <v>360</v>
+        <v>A</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>357</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="H220" s="25">
-        <v>1842500</v>
+        <v>354</v>
+      </c>
+      <c r="H220" s="4">
+        <v>27749100</v>
       </c>
       <c r="I220" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J220" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K220" s="11"/>
-      <c r="L220" s="11">
-        <v>46100</v>
-      </c>
+      <c r="L220" s="11"/>
       <c r="M220" s="10"/>
       <c r="N220" s="10" t="s">
         <v>33</v>
@@ -13439,7 +13449,7 @@
       <c r="R220" s="11"/>
       <c r="S220" s="10"/>
     </row>
-    <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="221" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B221" s="10">
         <f>IF(C221="","",COUNTA($C$2:C221))</f>
         <v>220</v>
@@ -13452,27 +13462,29 @@
         <v>B</v>
       </c>
       <c r="E221" s="23" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="F221" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G221" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H221" s="25">
-        <v>6583500</v>
+        <v>1842500</v>
       </c>
       <c r="I221" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J221" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K221" s="11"/>
-      <c r="L221" s="11"/>
+      <c r="L221" s="11">
+        <v>46100</v>
+      </c>
       <c r="M221" s="10"/>
       <c r="N221" s="10" t="s">
         <v>33</v>
@@ -13481,7 +13493,7 @@
       <c r="R221" s="11"/>
       <c r="S221" s="10"/>
     </row>
-    <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="222" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B222" s="10">
         <f>IF(C222="","",COUNTA($C$2:C222))</f>
         <v>221</v>
@@ -13494,16 +13506,16 @@
         <v>B</v>
       </c>
       <c r="E222" s="23" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="F222" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G222" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H222" s="25">
-        <v>2038700</v>
+        <v>6583500</v>
       </c>
       <c r="I222" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13523,7 +13535,7 @@
       <c r="R222" s="11"/>
       <c r="S222" s="10"/>
     </row>
-    <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="223" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B223" s="10">
         <f>IF(C223="","",COUNTA($C$2:C223))</f>
         <v>222</v>
@@ -13536,16 +13548,16 @@
         <v>B</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="F223" s="23" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G223" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H223" s="25">
-        <v>4750000</v>
+        <v>2038700</v>
       </c>
       <c r="I223" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13565,7 +13577,7 @@
       <c r="R223" s="11"/>
       <c r="S223" s="10"/>
     </row>
-    <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="224" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B224" s="10">
         <f>IF(C224="","",COUNTA($C$2:C224))</f>
         <v>223</v>
@@ -13578,16 +13590,16 @@
         <v>B</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F224" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G224" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H224" s="25">
-        <v>3572000</v>
+        <v>4750000</v>
       </c>
       <c r="I224" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13607,7 +13619,7 @@
       <c r="R224" s="11"/>
       <c r="S224" s="10"/>
     </row>
-    <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="225" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B225" s="10">
         <f>IF(C225="","",COUNTA($C$2:C225))</f>
         <v>224</v>
@@ -13620,16 +13632,16 @@
         <v>B</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="F225" s="23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G225" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H225" s="25">
-        <v>435000</v>
+        <v>3572000</v>
       </c>
       <c r="I225" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13649,7 +13661,7 @@
       <c r="R225" s="11"/>
       <c r="S225" s="10"/>
     </row>
-    <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="226" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B226" s="10">
         <f>IF(C226="","",COUNTA($C$2:C226))</f>
         <v>225</v>
@@ -13662,16 +13674,16 @@
         <v>B</v>
       </c>
       <c r="E226" s="23" t="s">
-        <v>382</v>
+        <v>24</v>
       </c>
       <c r="F226" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G226" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H226" s="25">
-        <v>637000</v>
+        <v>435000</v>
       </c>
       <c r="I226" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13691,7 +13703,7 @@
       <c r="R226" s="11"/>
       <c r="S226" s="10"/>
     </row>
-    <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="227" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B227" s="10">
         <f>IF(C227="","",COUNTA($C$2:C227))</f>
         <v>226</v>
@@ -13704,16 +13716,16 @@
         <v>B</v>
       </c>
       <c r="E227" s="23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F227" s="23" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G227" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H227" s="25">
-        <v>34583000</v>
+        <v>637000</v>
       </c>
       <c r="I227" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13733,7 +13745,7 @@
       <c r="R227" s="11"/>
       <c r="S227" s="10"/>
     </row>
-    <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="228" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B228" s="10">
         <f>IF(C228="","",COUNTA($C$2:C228))</f>
         <v>227</v>
@@ -13746,16 +13758,16 @@
         <v>B</v>
       </c>
       <c r="E228" s="23" t="s">
-        <v>216</v>
+        <v>383</v>
       </c>
       <c r="F228" s="23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G228" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H228" s="25">
-        <v>6600000</v>
+        <v>34583000</v>
       </c>
       <c r="I228" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13775,7 +13787,7 @@
       <c r="R228" s="11"/>
       <c r="S228" s="10"/>
     </row>
-    <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="229" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B229" s="10">
         <f>IF(C229="","",COUNTA($C$2:C229))</f>
         <v>228</v>
@@ -13788,16 +13800,16 @@
         <v>B</v>
       </c>
       <c r="E229" s="23" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F229" s="23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G229" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H229" s="25">
-        <v>15802000</v>
+        <v>6600000</v>
       </c>
       <c r="I229" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13817,33 +13829,33 @@
       <c r="R229" s="11"/>
       <c r="S229" s="10"/>
     </row>
-    <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="230" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B230" s="10">
         <f>IF(C230="","",COUNTA($C$2:C230))</f>
         <v>229</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D230" s="10" t="str">
         <f t="shared" si="15"/>
         <v>B</v>
       </c>
       <c r="E230" s="23" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F230" s="23" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G230" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H230" s="25">
-        <v>9450000</v>
+        <v>15802000</v>
       </c>
       <c r="I230" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J230" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13859,7 +13871,7 @@
       <c r="R230" s="11"/>
       <c r="S230" s="10"/>
     </row>
-    <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="231" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B231" s="10">
         <f>IF(C231="","",COUNTA($C$2:C231))</f>
         <v>230</v>
@@ -13872,16 +13884,16 @@
         <v>B</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="F231" s="23" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="G231" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H231" s="25">
-        <v>521000</v>
+        <v>9450000</v>
       </c>
       <c r="I231" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13901,7 +13913,7 @@
       <c r="R231" s="11"/>
       <c r="S231" s="10"/>
     </row>
-    <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="232" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B232" s="10">
         <f>IF(C232="","",COUNTA($C$2:C232))</f>
         <v>231</v>
@@ -13914,16 +13926,16 @@
         <v>B</v>
       </c>
       <c r="E232" s="23" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="F232" s="23" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="G232" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H232" s="25">
-        <v>333000</v>
+        <v>521000</v>
       </c>
       <c r="I232" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13943,7 +13955,7 @@
       <c r="R232" s="11"/>
       <c r="S232" s="10"/>
     </row>
-    <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="233" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B233" s="10">
         <f>IF(C233="","",COUNTA($C$2:C233))</f>
         <v>232</v>
@@ -13956,16 +13968,16 @@
         <v>B</v>
       </c>
       <c r="E233" s="23" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="F233" s="23" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G233" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H233" s="25">
-        <v>2835000</v>
+        <v>333000</v>
       </c>
       <c r="I233" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -13985,7 +13997,7 @@
       <c r="R233" s="11"/>
       <c r="S233" s="10"/>
     </row>
-    <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="234" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B234" s="10">
         <f>IF(C234="","",COUNTA($C$2:C234))</f>
         <v>233</v>
@@ -13998,29 +14010,27 @@
         <v>B</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="F234" s="23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G234" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H234" s="25">
-        <v>351900</v>
+        <v>2835000</v>
       </c>
       <c r="I234" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J234" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K234" s="11"/>
-      <c r="L234" s="11">
-        <v>46100</v>
-      </c>
+      <c r="L234" s="11"/>
       <c r="M234" s="10"/>
       <c r="N234" s="10" t="s">
         <v>33</v>
@@ -14029,7 +14039,7 @@
       <c r="R234" s="11"/>
       <c r="S234" s="10"/>
     </row>
-    <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="235" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B235" s="10">
         <f>IF(C235="","",COUNTA($C$2:C235))</f>
         <v>234</v>
@@ -14042,27 +14052,29 @@
         <v>B</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="F235" s="23" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G235" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H235" s="25">
-        <v>839000</v>
+        <v>351900</v>
       </c>
       <c r="I235" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J235" s="13" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>정상</v>
       </c>
       <c r="K235" s="11"/>
-      <c r="L235" s="11"/>
+      <c r="L235" s="11">
+        <v>46100</v>
+      </c>
       <c r="M235" s="10"/>
       <c r="N235" s="10" t="s">
         <v>33</v>
@@ -14071,7 +14083,7 @@
       <c r="R235" s="11"/>
       <c r="S235" s="10"/>
     </row>
-    <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="236" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B236" s="10">
         <f>IF(C236="","",COUNTA($C$2:C236))</f>
         <v>235</v>
@@ -14084,16 +14096,16 @@
         <v>B</v>
       </c>
       <c r="E236" s="23" t="s">
-        <v>384</v>
+        <v>17</v>
       </c>
       <c r="F236" s="23" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G236" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H236" s="25">
-        <v>1507200</v>
+        <v>839000</v>
       </c>
       <c r="I236" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14113,7 +14125,7 @@
       <c r="R236" s="11"/>
       <c r="S236" s="10"/>
     </row>
-    <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="237" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B237" s="10">
         <f>IF(C237="","",COUNTA($C$2:C237))</f>
         <v>236</v>
@@ -14126,16 +14138,16 @@
         <v>B</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>228</v>
+        <v>384</v>
       </c>
       <c r="F237" s="23" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G237" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H237" s="25">
-        <v>585000</v>
+        <v>1507200</v>
       </c>
       <c r="I237" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14155,7 +14167,7 @@
       <c r="R237" s="11"/>
       <c r="S237" s="10"/>
     </row>
-    <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="238" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B238" s="10">
         <f>IF(C238="","",COUNTA($C$2:C238))</f>
         <v>237</v>
@@ -14168,16 +14180,16 @@
         <v>B</v>
       </c>
       <c r="E238" s="23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F238" s="23" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="G238" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H238" s="25">
-        <v>615000</v>
+        <v>585000</v>
       </c>
       <c r="I238" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14197,7 +14209,7 @@
       <c r="R238" s="11"/>
       <c r="S238" s="10"/>
     </row>
-    <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="239" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B239" s="10">
         <f>IF(C239="","",COUNTA($C$2:C239))</f>
         <v>238</v>
@@ -14210,16 +14222,16 @@
         <v>B</v>
       </c>
       <c r="E239" s="23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F239" s="23" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="G239" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H239" s="25">
-        <v>44793500</v>
+        <v>615000</v>
       </c>
       <c r="I239" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14239,7 +14251,7 @@
       <c r="R239" s="11"/>
       <c r="S239" s="10"/>
     </row>
-    <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="240" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B240" s="10">
         <f>IF(C240="","",COUNTA($C$2:C240))</f>
         <v>239</v>
@@ -14252,16 +14264,16 @@
         <v>B</v>
       </c>
       <c r="E240" s="23" t="s">
-        <v>39</v>
+        <v>228</v>
       </c>
       <c r="F240" s="23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G240" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H240" s="25">
-        <v>602300</v>
+        <v>44793500</v>
       </c>
       <c r="I240" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14281,7 +14293,7 @@
       <c r="R240" s="11"/>
       <c r="S240" s="10"/>
     </row>
-    <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="241" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B241" s="10">
         <f>IF(C241="","",COUNTA($C$2:C241))</f>
         <v>240</v>
@@ -14294,16 +14306,16 @@
         <v>B</v>
       </c>
       <c r="E241" s="23" t="s">
-        <v>227</v>
+        <v>39</v>
       </c>
       <c r="F241" s="23" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G241" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H241" s="25">
-        <v>1180000</v>
+        <v>602300</v>
       </c>
       <c r="I241" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14323,7 +14335,7 @@
       <c r="R241" s="11"/>
       <c r="S241" s="10"/>
     </row>
-    <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="242" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B242" s="10">
         <f>IF(C242="","",COUNTA($C$2:C242))</f>
         <v>241</v>
@@ -14336,16 +14348,16 @@
         <v>B</v>
       </c>
       <c r="E242" s="23" t="s">
-        <v>350</v>
+        <v>227</v>
       </c>
       <c r="F242" s="23" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G242" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H242" s="25">
-        <v>3300000</v>
+        <v>1180000</v>
       </c>
       <c r="I242" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14365,7 +14377,7 @@
       <c r="R242" s="11"/>
       <c r="S242" s="10"/>
     </row>
-    <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="243" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B243" s="10">
         <f>IF(C243="","",COUNTA($C$2:C243))</f>
         <v>242</v>
@@ -14378,74 +14390,75 @@
         <v>B</v>
       </c>
       <c r="E243" s="23" t="s">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="F243" s="23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G243" s="6" t="s">
         <v>387</v>
       </c>
       <c r="H243" s="25">
-        <v>1548500</v>
+        <v>3300000</v>
       </c>
       <c r="I243" s="6">
         <f t="shared" ca="1" si="16"/>
         <v>6</v>
       </c>
       <c r="J243" s="13" t="str">
-        <f t="shared" ref="J243:J275" ca="1" si="17">IF(I243="","",
- IF(G243="선급금",
-   IF(I243&lt;=20,"정상",IF(I243&lt;=90,"관리","장기미수")),
- IF(G243="자재",
-   IF(I243&lt;=40,"정상",IF(I243&lt;=90,"관리","장기미수")),
-   IF(I243&lt;=30,"정상",IF(I243&lt;=90,"관리","장기미수"))
+        <f t="shared" ca="1" si="14"/>
+        <v>정상</v>
+      </c>
+      <c r="K243" s="11"/>
+      <c r="L243" s="11"/>
+      <c r="M243" s="10"/>
+      <c r="N243" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q243" s="11"/>
+      <c r="R243" s="11"/>
+      <c r="S243" s="10"/>
+    </row>
+    <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B244" s="10">
+        <f>IF(C244="","",COUNTA($C$2:C244))</f>
+        <v>243</v>
+      </c>
+      <c r="C244" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D244" s="10" t="str">
+        <f t="shared" si="15"/>
+        <v>B</v>
+      </c>
+      <c r="E244" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F244" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="G244" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H244" s="25">
+        <v>1548500</v>
+      </c>
+      <c r="I244" s="6">
+        <f t="shared" ca="1" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="J244" s="13" t="str">
+        <f t="shared" ref="J244:J276" ca="1" si="17">IF(I244="","",
+ IF(G244="선급금",
+   IF(I244&lt;=20,"정상",IF(I244&lt;=90,"관리","장기미수")),
+ IF(G244="자재",
+   IF(I244&lt;=40,"정상",IF(I244&lt;=90,"관리","장기미수")),
+   IF(I244&lt;=30,"정상",IF(I244&lt;=90,"관리","장기미수"))
   )
  )
 )</f>
         <v>정상</v>
       </c>
-      <c r="K243" s="11"/>
-      <c r="L243" s="11"/>
-      <c r="M243" s="10"/>
-      <c r="N243" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q243" s="11"/>
-      <c r="R243" s="11"/>
-      <c r="S243" s="10"/>
-    </row>
-    <row r="244" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B244" s="10">
-        <f>IF(C244="","",COUNTA($C$2:C244))</f>
-        <v>243</v>
-      </c>
-      <c r="C244" s="11">
-        <v>46101</v>
-      </c>
-      <c r="D244" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="E244" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="F244" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="G244" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="H244" s="4">
-        <v>10716800</v>
-      </c>
-      <c r="I244" s="6">
-        <f t="shared" ca="1" si="16"/>
-        <v>5</v>
-      </c>
-      <c r="J244" s="13" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>정상</v>
-      </c>
       <c r="K244" s="11"/>
       <c r="L244" s="11"/>
       <c r="M244" s="10"/>
@@ -14461,23 +14474,23 @@
         <f>IF(C245="","",COUNTA($C$2:C245))</f>
         <v>244</v>
       </c>
-      <c r="C245" s="63">
+      <c r="C245" s="11">
         <v>46101</v>
       </c>
       <c r="D245" s="10" t="s">
         <v>253</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F245" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G245" s="6" t="s">
-        <v>243</v>
+        <v>396</v>
       </c>
       <c r="H245" s="4">
-        <v>9029600</v>
+        <v>10716800</v>
       </c>
       <c r="I245" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14509,16 +14522,16 @@
         <v>253</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F246" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G246" s="6" t="s">
         <v>243</v>
       </c>
       <c r="H246" s="4">
-        <v>6484400</v>
+        <v>9029600</v>
       </c>
       <c r="I246" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14550,16 +14563,16 @@
         <v>253</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G247" s="6" t="s">
         <v>243</v>
       </c>
       <c r="H247" s="4">
-        <v>52857300</v>
+        <v>6484400</v>
       </c>
       <c r="I247" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14584,23 +14597,23 @@
         <f>IF(C248="","",COUNTA($C$2:C248))</f>
         <v>247</v>
       </c>
-      <c r="C248" s="35" t="s">
-        <v>404</v>
+      <c r="C248" s="63">
+        <v>46101</v>
       </c>
       <c r="D248" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E248" s="23" t="s">
-        <v>402</v>
-      </c>
-      <c r="F248" s="23" t="s">
-        <v>397</v>
+        <v>253</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="F248" s="6" t="s">
+        <v>392</v>
       </c>
       <c r="G248" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="H248" s="25">
-        <v>114000</v>
+        <v>243</v>
+      </c>
+      <c r="H248" s="4">
+        <v>52857300</v>
       </c>
       <c r="I248" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14620,7 +14633,7 @@
       <c r="R248" s="11"/>
       <c r="S248" s="10"/>
     </row>
-    <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="249" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B249" s="10">
         <f>IF(C249="","",COUNTA($C$2:C249))</f>
         <v>248</v>
@@ -14632,16 +14645,16 @@
         <v>182</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>24</v>
+        <v>402</v>
       </c>
       <c r="F249" s="23" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G249" s="6" t="s">
         <v>405</v>
       </c>
       <c r="H249" s="25">
-        <v>9563000</v>
+        <v>114000</v>
       </c>
       <c r="I249" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14661,7 +14674,7 @@
       <c r="R249" s="11"/>
       <c r="S249" s="10"/>
     </row>
-    <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="250" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B250" s="10">
         <f>IF(C250="","",COUNTA($C$2:C250))</f>
         <v>249</v>
@@ -14673,16 +14686,16 @@
         <v>182</v>
       </c>
       <c r="E250" s="23" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="F250" s="23" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G250" s="6" t="s">
         <v>405</v>
       </c>
       <c r="H250" s="25">
-        <v>2270000</v>
+        <v>9563000</v>
       </c>
       <c r="I250" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14702,7 +14715,7 @@
       <c r="R250" s="11"/>
       <c r="S250" s="10"/>
     </row>
-    <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="251" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B251" s="10">
         <f>IF(C251="","",COUNTA($C$2:C251))</f>
         <v>250</v>
@@ -14714,29 +14727,27 @@
         <v>182</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>403</v>
+        <v>101</v>
       </c>
       <c r="F251" s="23" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G251" s="6" t="s">
         <v>405</v>
       </c>
       <c r="H251" s="25">
-        <v>121500</v>
+        <v>2270000</v>
       </c>
       <c r="I251" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J251" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
         <v>정상</v>
       </c>
       <c r="K251" s="11"/>
-      <c r="L251" s="11">
-        <v>46101</v>
-      </c>
+      <c r="L251" s="11"/>
       <c r="M251" s="10"/>
       <c r="N251" s="10" t="s">
         <v>33</v>
@@ -14745,7 +14756,7 @@
       <c r="R251" s="11"/>
       <c r="S251" s="10"/>
     </row>
-    <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="252" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B252" s="10">
         <f>IF(C252="","",COUNTA($C$2:C252))</f>
         <v>251</v>
@@ -14757,27 +14768,29 @@
         <v>182</v>
       </c>
       <c r="E252" s="23" t="s">
-        <v>124</v>
+        <v>403</v>
       </c>
       <c r="F252" s="23" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G252" s="6" t="s">
         <v>405</v>
       </c>
       <c r="H252" s="25">
-        <v>658000</v>
+        <v>121500</v>
       </c>
       <c r="I252" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J252" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
         <v>정상</v>
       </c>
       <c r="K252" s="11"/>
-      <c r="L252" s="11"/>
+      <c r="L252" s="11">
+        <v>46101</v>
+      </c>
       <c r="M252" s="10"/>
       <c r="N252" s="10" t="s">
         <v>33</v>
@@ -14786,32 +14799,32 @@
       <c r="R252" s="11"/>
       <c r="S252" s="10"/>
     </row>
-    <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="253" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B253" s="10">
         <f>IF(C253="","",COUNTA($C$2:C253))</f>
         <v>252</v>
       </c>
-      <c r="C253" s="63">
-        <v>46104</v>
+      <c r="C253" s="35" t="s">
+        <v>404</v>
       </c>
       <c r="D253" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="E253" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="F253" s="6" t="s">
-        <v>406</v>
+        <v>182</v>
+      </c>
+      <c r="E253" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F253" s="23" t="s">
+        <v>401</v>
       </c>
       <c r="G253" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="H253" s="4">
-        <v>23835400</v>
+        <v>405</v>
+      </c>
+      <c r="H253" s="25">
+        <v>658000</v>
       </c>
       <c r="I253" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J253" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14839,16 +14852,16 @@
         <v>253</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F254" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G254" s="6" t="s">
         <v>240</v>
       </c>
       <c r="H254" s="4">
-        <v>8708400</v>
+        <v>23835400</v>
       </c>
       <c r="I254" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14874,27 +14887,26 @@
         <v>254</v>
       </c>
       <c r="C255" s="63">
-        <v>46105</v>
-      </c>
-      <c r="D255" s="10" t="str">
-        <f t="shared" si="15"/>
-        <v>A</v>
+        <v>46104</v>
+      </c>
+      <c r="D255" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F255" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G255" s="6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H255" s="4">
-        <v>8559000</v>
+        <v>8708400</v>
       </c>
       <c r="I255" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J255" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14923,16 +14935,16 @@
         <v>A</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F256" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G256" s="6" t="s">
-        <v>412</v>
+        <v>237</v>
       </c>
       <c r="H256" s="4">
-        <v>3281000</v>
+        <v>8559000</v>
       </c>
       <c r="I256" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -14957,28 +14969,28 @@
         <f>IF(C257="","",COUNTA($C$2:C257))</f>
         <v>256</v>
       </c>
-      <c r="C257" s="11" t="s">
-        <v>415</v>
+      <c r="C257" s="63">
+        <v>46105</v>
       </c>
       <c r="D257" s="10" t="str">
         <f t="shared" si="15"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E257" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F257" s="23" t="s">
-        <v>420</v>
+        <v>414</v>
+      </c>
+      <c r="F257" s="6" t="s">
+        <v>411</v>
       </c>
       <c r="G257" s="6" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="H257" s="4">
-        <v>4290000</v>
+        <v>3281000</v>
       </c>
       <c r="I257" s="6">
         <f t="shared" ca="1" si="16"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J257" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -14994,7 +15006,7 @@
       <c r="R257" s="11"/>
       <c r="S257" s="10"/>
     </row>
-    <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="258" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B258" s="10">
         <f>IF(C258="","",COUNTA($C$2:C258))</f>
         <v>257</v>
@@ -15007,16 +15019,16 @@
         <v>B</v>
       </c>
       <c r="E258" s="6" t="s">
-        <v>417</v>
+        <v>227</v>
       </c>
       <c r="F258" s="23" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G258" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H258" s="4">
-        <v>8800000</v>
+        <v>4290000</v>
       </c>
       <c r="I258" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15036,7 +15048,7 @@
       <c r="R258" s="11"/>
       <c r="S258" s="10"/>
     </row>
-    <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="259" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B259" s="10">
         <f>IF(C259="","",COUNTA($C$2:C259))</f>
         <v>258</v>
@@ -15049,16 +15061,16 @@
         <v>B</v>
       </c>
       <c r="E259" s="6" t="s">
-        <v>26</v>
+        <v>417</v>
       </c>
       <c r="F259" s="23" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G259" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H259" s="4">
-        <v>465000</v>
+        <v>8800000</v>
       </c>
       <c r="I259" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15078,7 +15090,7 @@
       <c r="R259" s="11"/>
       <c r="S259" s="10"/>
     </row>
-    <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="260" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B260" s="10">
         <f>IF(C260="","",COUNTA($C$2:C260))</f>
         <v>259</v>
@@ -15091,16 +15103,16 @@
         <v>B</v>
       </c>
       <c r="E260" s="6" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="F260" s="23" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G260" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H260" s="4">
-        <v>5765500</v>
+        <v>465000</v>
       </c>
       <c r="I260" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15120,7 +15132,7 @@
       <c r="R260" s="11"/>
       <c r="S260" s="10"/>
     </row>
-    <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="261" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B261" s="10">
         <f>IF(C261="","",COUNTA($C$2:C261))</f>
         <v>260</v>
@@ -15133,16 +15145,16 @@
         <v>B</v>
       </c>
       <c r="E261" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F261" s="23" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G261" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H261" s="4">
-        <v>222000</v>
+        <v>5765500</v>
       </c>
       <c r="I261" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15162,7 +15174,7 @@
       <c r="R261" s="11"/>
       <c r="S261" s="10"/>
     </row>
-    <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="262" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B262" s="10">
         <f>IF(C262="","",COUNTA($C$2:C262))</f>
         <v>261</v>
@@ -15175,16 +15187,16 @@
         <v>B</v>
       </c>
       <c r="E262" s="6" t="s">
-        <v>215</v>
+        <v>122</v>
       </c>
       <c r="F262" s="23" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G262" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H262" s="4">
-        <v>1866000</v>
+        <v>222000</v>
       </c>
       <c r="I262" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15204,7 +15216,7 @@
       <c r="R262" s="11"/>
       <c r="S262" s="10"/>
     </row>
-    <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="263" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B263" s="10">
         <f>IF(C263="","",COUNTA($C$2:C263))</f>
         <v>262</v>
@@ -15217,16 +15229,16 @@
         <v>B</v>
       </c>
       <c r="E263" s="6" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="F263" s="23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G263" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H263" s="4">
-        <v>798500</v>
+        <v>1866000</v>
       </c>
       <c r="I263" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15246,7 +15258,7 @@
       <c r="R263" s="11"/>
       <c r="S263" s="10"/>
     </row>
-    <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="264" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B264" s="10">
         <f>IF(C264="","",COUNTA($C$2:C264))</f>
         <v>263</v>
@@ -15259,16 +15271,16 @@
         <v>B</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>418</v>
+        <v>183</v>
       </c>
       <c r="F264" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G264" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H264" s="4">
-        <v>5442500</v>
+        <v>798500</v>
       </c>
       <c r="I264" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15288,7 +15300,7 @@
       <c r="R264" s="11"/>
       <c r="S264" s="10"/>
     </row>
-    <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="265" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B265" s="10">
         <f>IF(C265="","",COUNTA($C$2:C265))</f>
         <v>264</v>
@@ -15301,16 +15313,16 @@
         <v>B</v>
       </c>
       <c r="E265" s="6" t="s">
-        <v>216</v>
+        <v>418</v>
       </c>
       <c r="F265" s="23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G265" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H265" s="4">
-        <v>2969500</v>
+        <v>5442500</v>
       </c>
       <c r="I265" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15330,7 +15342,7 @@
       <c r="R265" s="11"/>
       <c r="S265" s="10"/>
     </row>
-    <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="266" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B266" s="10">
         <f>IF(C266="","",COUNTA($C$2:C266))</f>
         <v>265</v>
@@ -15343,16 +15355,16 @@
         <v>B</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="F266" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G266" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H266" s="4">
-        <v>10451300</v>
+        <v>2969500</v>
       </c>
       <c r="I266" s="6">
         <f t="shared" ca="1" si="16"/>
@@ -15372,7 +15384,7 @@
       <c r="R266" s="11"/>
       <c r="S266" s="10"/>
     </row>
-    <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="267" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B267" s="10">
         <f>IF(C267="","",COUNTA($C$2:C267))</f>
         <v>266</v>
@@ -15381,23 +15393,23 @@
         <v>415</v>
       </c>
       <c r="D267" s="10" t="str">
-        <f t="shared" ref="D267:D330" si="18">IF(G267="","",IF(OR(G267="선급금",G267="중도금",G267="잔금"),"A",IF(G267="자재","B",IF(G267="특허료","C",""))))</f>
+        <f t="shared" si="15"/>
         <v>B</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="F267" s="23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G267" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H267" s="4">
-        <v>2250000</v>
+        <v>10451300</v>
       </c>
       <c r="I267" s="6">
-        <f t="shared" ref="I267:I330" ca="1" si="19">IF(C267="","",IF(L267="",TODAY()-C267,L267-C267))</f>
+        <f t="shared" ca="1" si="16"/>
         <v>2</v>
       </c>
       <c r="J267" s="13" t="str">
@@ -15414,33 +15426,33 @@
       <c r="R267" s="11"/>
       <c r="S267" s="10"/>
     </row>
-    <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="268" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B268" s="10">
         <f>IF(C268="","",COUNTA($C$2:C268))</f>
         <v>267</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D268" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="D268:D331" si="18">IF(G268="","",IF(OR(G268="선급금",G268="중도금",G268="잔금"),"A",IF(G268="자재","B",IF(G268="특허료","C",""))))</f>
         <v>B</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F268" s="23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G268" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H268" s="4">
-        <v>2711000</v>
+        <v>2250000</v>
       </c>
       <c r="I268" s="6">
-        <f t="shared" ca="1" si="19"/>
-        <v>1</v>
+        <f t="shared" ref="I268:I331" ca="1" si="19">IF(C268="","",IF(L268="",TODAY()-C268,L268-C268))</f>
+        <v>2</v>
       </c>
       <c r="J268" s="13" t="str">
         <f t="shared" ca="1" si="17"/>
@@ -15456,7 +15468,7 @@
       <c r="R268" s="11"/>
       <c r="S268" s="10"/>
     </row>
-    <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="269" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B269" s="10">
         <f>IF(C269="","",COUNTA($C$2:C269))</f>
         <v>268</v>
@@ -15472,13 +15484,13 @@
         <v>128</v>
       </c>
       <c r="F269" s="23" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G269" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H269" s="4">
-        <v>10539000</v>
+        <v>2711000</v>
       </c>
       <c r="I269" s="6">
         <f t="shared" ca="1" si="19"/>
@@ -15498,7 +15510,7 @@
       <c r="R269" s="11"/>
       <c r="S269" s="10"/>
     </row>
-    <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="270" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B270" s="10">
         <f>IF(C270="","",COUNTA($C$2:C270))</f>
         <v>269</v>
@@ -15511,16 +15523,16 @@
         <v>B</v>
       </c>
       <c r="E270" s="6" t="s">
-        <v>419</v>
+        <v>128</v>
       </c>
       <c r="F270" s="23" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G270" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H270" s="4">
-        <v>1021000</v>
+        <v>10539000</v>
       </c>
       <c r="I270" s="6">
         <f t="shared" ca="1" si="19"/>
@@ -15540,7 +15552,7 @@
       <c r="R270" s="11"/>
       <c r="S270" s="10"/>
     </row>
-    <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="271" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B271" s="10">
         <f>IF(C271="","",COUNTA($C$2:C271))</f>
         <v>270</v>
@@ -15553,16 +15565,16 @@
         <v>B</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>99</v>
+        <v>419</v>
       </c>
       <c r="F271" s="23" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G271" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H271" s="4">
-        <v>427800</v>
+        <v>1021000</v>
       </c>
       <c r="I271" s="6">
         <f t="shared" ca="1" si="19"/>
@@ -15582,7 +15594,7 @@
       <c r="R271" s="11"/>
       <c r="S271" s="10"/>
     </row>
-    <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="272" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B272" s="10">
         <f>IF(C272="","",COUNTA($C$2:C272))</f>
         <v>271</v>
@@ -15595,16 +15607,16 @@
         <v>B</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="F272" s="23" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G272" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H272" s="4">
-        <v>1180000</v>
+        <v>427800</v>
       </c>
       <c r="I272" s="6">
         <f t="shared" ca="1" si="19"/>
@@ -15624,7 +15636,7 @@
       <c r="R272" s="11"/>
       <c r="S272" s="10"/>
     </row>
-    <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="273" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B273" s="10">
         <f>IF(C273="","",COUNTA($C$2:C273))</f>
         <v>272</v>
@@ -15637,16 +15649,16 @@
         <v>B</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="F273" s="23" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G273" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H273" s="4">
-        <v>4520000</v>
+        <v>1180000</v>
       </c>
       <c r="I273" s="6">
         <f t="shared" ca="1" si="19"/>
@@ -15666,7 +15678,7 @@
       <c r="R273" s="11"/>
       <c r="S273" s="10"/>
     </row>
-    <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="274" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B274" s="10">
         <f>IF(C274="","",COUNTA($C$2:C274))</f>
         <v>273</v>
@@ -15679,16 +15691,16 @@
         <v>B</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>128</v>
+        <v>216</v>
       </c>
       <c r="F274" s="23" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G274" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H274" s="4">
-        <v>157000</v>
+        <v>4520000</v>
       </c>
       <c r="I274" s="6">
         <f t="shared" ca="1" si="19"/>
@@ -15708,7 +15720,7 @@
       <c r="R274" s="11"/>
       <c r="S274" s="10"/>
     </row>
-    <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="275" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B275" s="10">
         <f>IF(C275="","",COUNTA($C$2:C275))</f>
         <v>274</v>
@@ -15721,16 +15733,16 @@
         <v>B</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>231</v>
+        <v>128</v>
       </c>
       <c r="F275" s="23" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G275" s="6" t="s">
         <v>439</v>
       </c>
       <c r="H275" s="4">
-        <v>2380000</v>
+        <v>157000</v>
       </c>
       <c r="I275" s="6">
         <f t="shared" ca="1" si="19"/>
@@ -15750,28 +15762,49 @@
       <c r="R275" s="11"/>
       <c r="S275" s="10"/>
     </row>
-    <row r="276" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B276" s="10"/>
-      <c r="C276" s="11"/>
+    <row r="276" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
+      <c r="B276" s="10">
+        <f>IF(C276="","",COUNTA($C$2:C276))</f>
+        <v>275</v>
+      </c>
+      <c r="C276" s="11" t="s">
+        <v>416</v>
+      </c>
       <c r="D276" s="10" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="H276" s="4"/>
-      <c r="I276" s="6" t="str">
+        <v>B</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F276" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="G276" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H276" s="4">
+        <v>2380000</v>
+      </c>
+      <c r="I276" s="6">
         <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-      <c r="J276" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="J276" s="13" t="str">
+        <f t="shared" ca="1" si="17"/>
+        <v>정상</v>
+      </c>
       <c r="K276" s="11"/>
       <c r="L276" s="11"/>
       <c r="M276" s="10"/>
-      <c r="N276" s="10"/>
+      <c r="N276" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="Q276" s="11"/>
       <c r="R276" s="11"/>
       <c r="S276" s="10"/>
     </row>
-    <row r="277" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="277" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B277" s="10"/>
       <c r="C277" s="11"/>
       <c r="D277" s="10" t="str">
@@ -15792,7 +15825,7 @@
       <c r="R277" s="11"/>
       <c r="S277" s="10"/>
     </row>
-    <row r="278" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="278" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B278" s="10"/>
       <c r="C278" s="11"/>
       <c r="D278" s="10" t="str">
@@ -15813,7 +15846,7 @@
       <c r="R278" s="11"/>
       <c r="S278" s="10"/>
     </row>
-    <row r="279" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="279" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B279" s="10"/>
       <c r="C279" s="11"/>
       <c r="D279" s="10" t="str">
@@ -15834,7 +15867,7 @@
       <c r="R279" s="11"/>
       <c r="S279" s="10"/>
     </row>
-    <row r="280" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="280" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B280" s="10"/>
       <c r="C280" s="11"/>
       <c r="D280" s="10" t="str">
@@ -15855,7 +15888,7 @@
       <c r="R280" s="11"/>
       <c r="S280" s="10"/>
     </row>
-    <row r="281" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="281" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B281" s="10"/>
       <c r="C281" s="11"/>
       <c r="D281" s="10" t="str">
@@ -15876,7 +15909,7 @@
       <c r="R281" s="11"/>
       <c r="S281" s="10"/>
     </row>
-    <row r="282" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="282" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B282" s="10"/>
       <c r="C282" s="11"/>
       <c r="D282" s="10" t="str">
@@ -15897,7 +15930,7 @@
       <c r="R282" s="11"/>
       <c r="S282" s="10"/>
     </row>
-    <row r="283" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="283" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B283" s="10"/>
       <c r="C283" s="11"/>
       <c r="D283" s="10" t="str">
@@ -15918,7 +15951,7 @@
       <c r="R283" s="11"/>
       <c r="S283" s="10"/>
     </row>
-    <row r="284" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="284" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B284" s="10"/>
       <c r="C284" s="11"/>
       <c r="D284" s="10" t="str">
@@ -15939,7 +15972,7 @@
       <c r="R284" s="11"/>
       <c r="S284" s="10"/>
     </row>
-    <row r="285" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="285" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B285" s="10"/>
       <c r="C285" s="11"/>
       <c r="D285" s="10" t="str">
@@ -15960,7 +15993,7 @@
       <c r="R285" s="11"/>
       <c r="S285" s="10"/>
     </row>
-    <row r="286" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="286" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B286" s="10"/>
       <c r="C286" s="11"/>
       <c r="D286" s="10" t="str">
@@ -15981,7 +16014,7 @@
       <c r="R286" s="11"/>
       <c r="S286" s="10"/>
     </row>
-    <row r="287" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="287" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B287" s="10"/>
       <c r="C287" s="11"/>
       <c r="D287" s="10" t="str">
@@ -16002,7 +16035,7 @@
       <c r="R287" s="11"/>
       <c r="S287" s="10"/>
     </row>
-    <row r="288" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="288" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B288" s="10"/>
       <c r="C288" s="11"/>
       <c r="D288" s="10" t="str">
@@ -16023,7 +16056,7 @@
       <c r="R288" s="11"/>
       <c r="S288" s="10"/>
     </row>
-    <row r="289" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="289" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B289" s="10"/>
       <c r="C289" s="11"/>
       <c r="D289" s="10" t="str">
@@ -16044,7 +16077,7 @@
       <c r="R289" s="11"/>
       <c r="S289" s="10"/>
     </row>
-    <row r="290" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="290" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B290" s="10"/>
       <c r="C290" s="11"/>
       <c r="D290" s="10" t="str">
@@ -16065,7 +16098,7 @@
       <c r="R290" s="11"/>
       <c r="S290" s="10"/>
     </row>
-    <row r="291" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="291" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B291" s="10"/>
       <c r="C291" s="11"/>
       <c r="D291" s="10" t="str">
@@ -16086,7 +16119,7 @@
       <c r="R291" s="11"/>
       <c r="S291" s="10"/>
     </row>
-    <row r="292" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="292" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B292" s="10"/>
       <c r="C292" s="11"/>
       <c r="D292" s="10" t="str">
@@ -16107,7 +16140,7 @@
       <c r="R292" s="11"/>
       <c r="S292" s="10"/>
     </row>
-    <row r="293" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="293" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B293" s="10"/>
       <c r="C293" s="11"/>
       <c r="D293" s="10" t="str">
@@ -16128,7 +16161,7 @@
       <c r="R293" s="11"/>
       <c r="S293" s="10"/>
     </row>
-    <row r="294" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="294" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B294" s="10"/>
       <c r="C294" s="11"/>
       <c r="D294" s="10" t="str">
@@ -16149,7 +16182,7 @@
       <c r="R294" s="11"/>
       <c r="S294" s="10"/>
     </row>
-    <row r="295" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="295" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B295" s="10"/>
       <c r="C295" s="11"/>
       <c r="D295" s="10" t="str">
@@ -16170,7 +16203,7 @@
       <c r="R295" s="11"/>
       <c r="S295" s="10"/>
     </row>
-    <row r="296" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="296" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B296" s="10"/>
       <c r="C296" s="11"/>
       <c r="D296" s="10" t="str">
@@ -16191,7 +16224,7 @@
       <c r="R296" s="11"/>
       <c r="S296" s="10"/>
     </row>
-    <row r="297" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="297" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B297" s="10"/>
       <c r="C297" s="11"/>
       <c r="D297" s="10" t="str">
@@ -16212,7 +16245,7 @@
       <c r="R297" s="11"/>
       <c r="S297" s="10"/>
     </row>
-    <row r="298" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="298" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B298" s="10"/>
       <c r="C298" s="11"/>
       <c r="D298" s="10" t="str">
@@ -16233,7 +16266,7 @@
       <c r="R298" s="11"/>
       <c r="S298" s="10"/>
     </row>
-    <row r="299" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="299" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B299" s="10"/>
       <c r="C299" s="11"/>
       <c r="D299" s="10" t="str">
@@ -16254,7 +16287,7 @@
       <c r="R299" s="11"/>
       <c r="S299" s="10"/>
     </row>
-    <row r="300" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="300" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B300" s="10"/>
       <c r="C300" s="11"/>
       <c r="D300" s="10" t="str">
@@ -16275,7 +16308,7 @@
       <c r="R300" s="11"/>
       <c r="S300" s="10"/>
     </row>
-    <row r="301" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="301" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B301" s="10"/>
       <c r="C301" s="11"/>
       <c r="D301" s="10" t="str">
@@ -16296,7 +16329,7 @@
       <c r="R301" s="11"/>
       <c r="S301" s="10"/>
     </row>
-    <row r="302" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="302" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B302" s="10"/>
       <c r="C302" s="11"/>
       <c r="D302" s="10" t="str">
@@ -16317,7 +16350,7 @@
       <c r="R302" s="11"/>
       <c r="S302" s="10"/>
     </row>
-    <row r="303" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="303" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B303" s="10"/>
       <c r="C303" s="11"/>
       <c r="D303" s="10" t="str">
@@ -16338,7 +16371,7 @@
       <c r="R303" s="11"/>
       <c r="S303" s="10"/>
     </row>
-    <row r="304" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="304" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B304" s="10"/>
       <c r="C304" s="11"/>
       <c r="D304" s="10" t="str">
@@ -16359,7 +16392,7 @@
       <c r="R304" s="11"/>
       <c r="S304" s="10"/>
     </row>
-    <row r="305" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="305" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B305" s="10"/>
       <c r="C305" s="11"/>
       <c r="D305" s="10" t="str">
@@ -16380,7 +16413,7 @@
       <c r="R305" s="11"/>
       <c r="S305" s="10"/>
     </row>
-    <row r="306" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="306" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B306" s="10"/>
       <c r="C306" s="11"/>
       <c r="D306" s="10" t="str">
@@ -16401,7 +16434,7 @@
       <c r="R306" s="11"/>
       <c r="S306" s="10"/>
     </row>
-    <row r="307" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="307" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B307" s="10"/>
       <c r="C307" s="11"/>
       <c r="D307" s="10" t="str">
@@ -16422,7 +16455,7 @@
       <c r="R307" s="11"/>
       <c r="S307" s="10"/>
     </row>
-    <row r="308" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="308" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B308" s="10"/>
       <c r="C308" s="11"/>
       <c r="D308" s="10" t="str">
@@ -16443,7 +16476,7 @@
       <c r="R308" s="11"/>
       <c r="S308" s="10"/>
     </row>
-    <row r="309" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="309" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B309" s="10"/>
       <c r="C309" s="11"/>
       <c r="D309" s="10" t="str">
@@ -16464,7 +16497,7 @@
       <c r="R309" s="11"/>
       <c r="S309" s="10"/>
     </row>
-    <row r="310" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="310" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B310" s="10"/>
       <c r="C310" s="11"/>
       <c r="D310" s="10" t="str">
@@ -16485,7 +16518,7 @@
       <c r="R310" s="11"/>
       <c r="S310" s="10"/>
     </row>
-    <row r="311" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="311" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B311" s="10"/>
       <c r="C311" s="11"/>
       <c r="D311" s="10" t="str">
@@ -16506,7 +16539,7 @@
       <c r="R311" s="11"/>
       <c r="S311" s="10"/>
     </row>
-    <row r="312" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="312" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B312" s="10"/>
       <c r="C312" s="11"/>
       <c r="D312" s="10" t="str">
@@ -16527,7 +16560,7 @@
       <c r="R312" s="11"/>
       <c r="S312" s="10"/>
     </row>
-    <row r="313" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="313" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B313" s="10"/>
       <c r="C313" s="11"/>
       <c r="D313" s="10" t="str">
@@ -16548,7 +16581,7 @@
       <c r="R313" s="11"/>
       <c r="S313" s="10"/>
     </row>
-    <row r="314" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="314" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B314" s="10"/>
       <c r="C314" s="11"/>
       <c r="D314" s="10" t="str">
@@ -16569,7 +16602,7 @@
       <c r="R314" s="11"/>
       <c r="S314" s="10"/>
     </row>
-    <row r="315" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="315" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B315" s="10"/>
       <c r="C315" s="11"/>
       <c r="D315" s="10" t="str">
@@ -16590,7 +16623,7 @@
       <c r="R315" s="11"/>
       <c r="S315" s="10"/>
     </row>
-    <row r="316" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="316" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B316" s="10"/>
       <c r="C316" s="11"/>
       <c r="D316" s="10" t="str">
@@ -16611,7 +16644,7 @@
       <c r="R316" s="11"/>
       <c r="S316" s="10"/>
     </row>
-    <row r="317" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="317" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B317" s="10"/>
       <c r="C317" s="11"/>
       <c r="D317" s="10" t="str">
@@ -16632,7 +16665,7 @@
       <c r="R317" s="11"/>
       <c r="S317" s="10"/>
     </row>
-    <row r="318" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="318" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B318" s="10"/>
       <c r="C318" s="11"/>
       <c r="D318" s="10" t="str">
@@ -16653,7 +16686,7 @@
       <c r="R318" s="11"/>
       <c r="S318" s="10"/>
     </row>
-    <row r="319" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="319" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B319" s="10"/>
       <c r="C319" s="11"/>
       <c r="D319" s="10" t="str">
@@ -16674,7 +16707,7 @@
       <c r="R319" s="11"/>
       <c r="S319" s="10"/>
     </row>
-    <row r="320" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="320" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B320" s="10"/>
       <c r="C320" s="11"/>
       <c r="D320" s="10" t="str">
@@ -16695,7 +16728,7 @@
       <c r="R320" s="11"/>
       <c r="S320" s="10"/>
     </row>
-    <row r="321" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="321" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B321" s="10"/>
       <c r="C321" s="11"/>
       <c r="D321" s="10" t="str">
@@ -16716,7 +16749,7 @@
       <c r="R321" s="11"/>
       <c r="S321" s="10"/>
     </row>
-    <row r="322" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="322" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B322" s="10"/>
       <c r="C322" s="11"/>
       <c r="D322" s="10" t="str">
@@ -16737,7 +16770,7 @@
       <c r="R322" s="11"/>
       <c r="S322" s="10"/>
     </row>
-    <row r="323" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="323" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B323" s="10"/>
       <c r="C323" s="11"/>
       <c r="D323" s="10" t="str">
@@ -16758,7 +16791,7 @@
       <c r="R323" s="11"/>
       <c r="S323" s="10"/>
     </row>
-    <row r="324" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="324" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B324" s="10"/>
       <c r="C324" s="11"/>
       <c r="D324" s="10" t="str">
@@ -16779,7 +16812,7 @@
       <c r="R324" s="11"/>
       <c r="S324" s="10"/>
     </row>
-    <row r="325" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="325" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B325" s="10"/>
       <c r="C325" s="11"/>
       <c r="D325" s="10" t="str">
@@ -16800,7 +16833,7 @@
       <c r="R325" s="11"/>
       <c r="S325" s="10"/>
     </row>
-    <row r="326" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="326" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B326" s="10"/>
       <c r="C326" s="11"/>
       <c r="D326" s="10" t="str">
@@ -16821,7 +16854,7 @@
       <c r="R326" s="11"/>
       <c r="S326" s="10"/>
     </row>
-    <row r="327" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="327" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B327" s="10"/>
       <c r="C327" s="11"/>
       <c r="D327" s="10" t="str">
@@ -16842,7 +16875,7 @@
       <c r="R327" s="11"/>
       <c r="S327" s="10"/>
     </row>
-    <row r="328" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="328" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B328" s="10"/>
       <c r="C328" s="11"/>
       <c r="D328" s="10" t="str">
@@ -16863,7 +16896,7 @@
       <c r="R328" s="11"/>
       <c r="S328" s="10"/>
     </row>
-    <row r="329" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="329" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B329" s="10"/>
       <c r="C329" s="11"/>
       <c r="D329" s="10" t="str">
@@ -16884,7 +16917,7 @@
       <c r="R329" s="11"/>
       <c r="S329" s="10"/>
     </row>
-    <row r="330" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="330" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B330" s="10"/>
       <c r="C330" s="11"/>
       <c r="D330" s="10" t="str">
@@ -16905,16 +16938,16 @@
       <c r="R330" s="11"/>
       <c r="S330" s="10"/>
     </row>
-    <row r="331" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="331" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B331" s="10"/>
       <c r="C331" s="11"/>
       <c r="D331" s="10" t="str">
-        <f t="shared" ref="D331:D394" si="20">IF(G331="","",IF(OR(G331="선급금",G331="중도금",G331="잔금"),"A",IF(G331="자재","B",IF(G331="특허료","C",""))))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H331" s="4"/>
       <c r="I331" s="6" t="str">
-        <f t="shared" ref="I331:I394" ca="1" si="21">IF(C331="","",IF(L331="",TODAY()-C331,L331-C331))</f>
+        <f t="shared" ca="1" si="19"/>
         <v/>
       </c>
       <c r="J331" s="13"/>
@@ -16926,16 +16959,16 @@
       <c r="R331" s="11"/>
       <c r="S331" s="10"/>
     </row>
-    <row r="332" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="332" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B332" s="10"/>
       <c r="C332" s="11"/>
       <c r="D332" s="10" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D332:D395" si="20">IF(G332="","",IF(OR(G332="선급금",G332="중도금",G332="잔금"),"A",IF(G332="자재","B",IF(G332="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="6" t="str">
-        <f t="shared" ca="1" si="21"/>
+        <f t="shared" ref="I332:I395" ca="1" si="21">IF(C332="","",IF(L332="",TODAY()-C332,L332-C332))</f>
         <v/>
       </c>
       <c r="J332" s="13"/>
@@ -16947,7 +16980,7 @@
       <c r="R332" s="11"/>
       <c r="S332" s="10"/>
     </row>
-    <row r="333" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="333" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B333" s="10"/>
       <c r="C333" s="11"/>
       <c r="D333" s="10" t="str">
@@ -16968,7 +17001,7 @@
       <c r="R333" s="11"/>
       <c r="S333" s="10"/>
     </row>
-    <row r="334" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="334" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B334" s="10"/>
       <c r="C334" s="11"/>
       <c r="D334" s="10" t="str">
@@ -16989,7 +17022,7 @@
       <c r="R334" s="11"/>
       <c r="S334" s="10"/>
     </row>
-    <row r="335" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="335" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B335" s="10"/>
       <c r="C335" s="11"/>
       <c r="D335" s="10" t="str">
@@ -17010,7 +17043,7 @@
       <c r="R335" s="11"/>
       <c r="S335" s="10"/>
     </row>
-    <row r="336" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="336" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B336" s="10"/>
       <c r="C336" s="11"/>
       <c r="D336" s="10" t="str">
@@ -17031,7 +17064,7 @@
       <c r="R336" s="11"/>
       <c r="S336" s="10"/>
     </row>
-    <row r="337" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="337" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B337" s="10"/>
       <c r="C337" s="11"/>
       <c r="D337" s="10" t="str">
@@ -17052,7 +17085,7 @@
       <c r="R337" s="11"/>
       <c r="S337" s="10"/>
     </row>
-    <row r="338" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="338" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B338" s="10"/>
       <c r="C338" s="11"/>
       <c r="D338" s="10" t="str">
@@ -17073,7 +17106,7 @@
       <c r="R338" s="11"/>
       <c r="S338" s="10"/>
     </row>
-    <row r="339" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="339" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B339" s="10"/>
       <c r="C339" s="11"/>
       <c r="D339" s="10" t="str">
@@ -17094,7 +17127,7 @@
       <c r="R339" s="11"/>
       <c r="S339" s="10"/>
     </row>
-    <row r="340" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="340" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B340" s="10"/>
       <c r="C340" s="11"/>
       <c r="D340" s="10" t="str">
@@ -17115,7 +17148,7 @@
       <c r="R340" s="11"/>
       <c r="S340" s="10"/>
     </row>
-    <row r="341" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="341" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B341" s="10"/>
       <c r="C341" s="11"/>
       <c r="D341" s="10" t="str">
@@ -17136,7 +17169,7 @@
       <c r="R341" s="11"/>
       <c r="S341" s="10"/>
     </row>
-    <row r="342" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="342" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B342" s="10"/>
       <c r="C342" s="11"/>
       <c r="D342" s="10" t="str">
@@ -17157,7 +17190,7 @@
       <c r="R342" s="11"/>
       <c r="S342" s="10"/>
     </row>
-    <row r="343" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="343" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B343" s="10"/>
       <c r="C343" s="11"/>
       <c r="D343" s="10" t="str">
@@ -17178,7 +17211,7 @@
       <c r="R343" s="11"/>
       <c r="S343" s="10"/>
     </row>
-    <row r="344" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="344" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B344" s="10"/>
       <c r="C344" s="11"/>
       <c r="D344" s="10" t="str">
@@ -17199,7 +17232,7 @@
       <c r="R344" s="11"/>
       <c r="S344" s="10"/>
     </row>
-    <row r="345" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="345" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B345" s="10"/>
       <c r="C345" s="11"/>
       <c r="D345" s="10" t="str">
@@ -17220,7 +17253,7 @@
       <c r="R345" s="11"/>
       <c r="S345" s="10"/>
     </row>
-    <row r="346" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="346" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B346" s="10"/>
       <c r="C346" s="11"/>
       <c r="D346" s="10" t="str">
@@ -17241,7 +17274,7 @@
       <c r="R346" s="11"/>
       <c r="S346" s="10"/>
     </row>
-    <row r="347" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="347" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B347" s="10"/>
       <c r="C347" s="11"/>
       <c r="D347" s="10" t="str">
@@ -17262,7 +17295,7 @@
       <c r="R347" s="11"/>
       <c r="S347" s="10"/>
     </row>
-    <row r="348" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="348" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B348" s="10"/>
       <c r="C348" s="11"/>
       <c r="D348" s="10" t="str">
@@ -17283,7 +17316,7 @@
       <c r="R348" s="11"/>
       <c r="S348" s="10"/>
     </row>
-    <row r="349" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="349" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B349" s="10"/>
       <c r="C349" s="11"/>
       <c r="D349" s="10" t="str">
@@ -17304,7 +17337,7 @@
       <c r="R349" s="11"/>
       <c r="S349" s="10"/>
     </row>
-    <row r="350" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="350" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B350" s="10"/>
       <c r="C350" s="11"/>
       <c r="D350" s="10" t="str">
@@ -17325,7 +17358,7 @@
       <c r="R350" s="11"/>
       <c r="S350" s="10"/>
     </row>
-    <row r="351" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="351" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B351" s="10"/>
       <c r="C351" s="11"/>
       <c r="D351" s="10" t="str">
@@ -17346,7 +17379,7 @@
       <c r="R351" s="11"/>
       <c r="S351" s="10"/>
     </row>
-    <row r="352" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="352" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B352" s="10"/>
       <c r="C352" s="11"/>
       <c r="D352" s="10" t="str">
@@ -17367,7 +17400,7 @@
       <c r="R352" s="11"/>
       <c r="S352" s="10"/>
     </row>
-    <row r="353" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="353" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B353" s="10"/>
       <c r="C353" s="11"/>
       <c r="D353" s="10" t="str">
@@ -17388,7 +17421,7 @@
       <c r="R353" s="11"/>
       <c r="S353" s="10"/>
     </row>
-    <row r="354" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="354" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B354" s="10"/>
       <c r="C354" s="11"/>
       <c r="D354" s="10" t="str">
@@ -17409,7 +17442,7 @@
       <c r="R354" s="11"/>
       <c r="S354" s="10"/>
     </row>
-    <row r="355" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="355" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B355" s="10"/>
       <c r="C355" s="11"/>
       <c r="D355" s="10" t="str">
@@ -17430,7 +17463,7 @@
       <c r="R355" s="11"/>
       <c r="S355" s="10"/>
     </row>
-    <row r="356" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="356" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B356" s="10"/>
       <c r="C356" s="11"/>
       <c r="D356" s="10" t="str">
@@ -17451,7 +17484,7 @@
       <c r="R356" s="11"/>
       <c r="S356" s="10"/>
     </row>
-    <row r="357" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="357" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B357" s="10"/>
       <c r="C357" s="11"/>
       <c r="D357" s="10" t="str">
@@ -17472,7 +17505,7 @@
       <c r="R357" s="11"/>
       <c r="S357" s="10"/>
     </row>
-    <row r="358" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="358" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B358" s="10"/>
       <c r="C358" s="11"/>
       <c r="D358" s="10" t="str">
@@ -17493,7 +17526,7 @@
       <c r="R358" s="11"/>
       <c r="S358" s="10"/>
     </row>
-    <row r="359" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="359" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B359" s="10"/>
       <c r="C359" s="11"/>
       <c r="D359" s="10" t="str">
@@ -17514,7 +17547,7 @@
       <c r="R359" s="11"/>
       <c r="S359" s="10"/>
     </row>
-    <row r="360" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="360" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B360" s="10"/>
       <c r="C360" s="11"/>
       <c r="D360" s="10" t="str">
@@ -17535,7 +17568,7 @@
       <c r="R360" s="11"/>
       <c r="S360" s="10"/>
     </row>
-    <row r="361" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="361" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B361" s="10"/>
       <c r="C361" s="11"/>
       <c r="D361" s="10" t="str">
@@ -17556,7 +17589,7 @@
       <c r="R361" s="11"/>
       <c r="S361" s="10"/>
     </row>
-    <row r="362" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="362" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B362" s="10"/>
       <c r="C362" s="11"/>
       <c r="D362" s="10" t="str">
@@ -17577,7 +17610,7 @@
       <c r="R362" s="11"/>
       <c r="S362" s="10"/>
     </row>
-    <row r="363" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="363" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B363" s="10"/>
       <c r="C363" s="11"/>
       <c r="D363" s="10" t="str">
@@ -17598,7 +17631,7 @@
       <c r="R363" s="11"/>
       <c r="S363" s="10"/>
     </row>
-    <row r="364" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="364" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B364" s="10"/>
       <c r="C364" s="11"/>
       <c r="D364" s="10" t="str">
@@ -17619,7 +17652,7 @@
       <c r="R364" s="11"/>
       <c r="S364" s="10"/>
     </row>
-    <row r="365" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="365" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B365" s="10"/>
       <c r="C365" s="11"/>
       <c r="D365" s="10" t="str">
@@ -17640,7 +17673,7 @@
       <c r="R365" s="11"/>
       <c r="S365" s="10"/>
     </row>
-    <row r="366" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="366" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B366" s="10"/>
       <c r="C366" s="11"/>
       <c r="D366" s="10" t="str">
@@ -17661,7 +17694,7 @@
       <c r="R366" s="11"/>
       <c r="S366" s="10"/>
     </row>
-    <row r="367" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="367" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B367" s="10"/>
       <c r="C367" s="11"/>
       <c r="D367" s="10" t="str">
@@ -17682,7 +17715,7 @@
       <c r="R367" s="11"/>
       <c r="S367" s="10"/>
     </row>
-    <row r="368" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="368" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B368" s="10"/>
       <c r="C368" s="11"/>
       <c r="D368" s="10" t="str">
@@ -17703,7 +17736,7 @@
       <c r="R368" s="11"/>
       <c r="S368" s="10"/>
     </row>
-    <row r="369" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="369" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B369" s="10"/>
       <c r="C369" s="11"/>
       <c r="D369" s="10" t="str">
@@ -17724,7 +17757,7 @@
       <c r="R369" s="11"/>
       <c r="S369" s="10"/>
     </row>
-    <row r="370" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="370" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B370" s="10"/>
       <c r="C370" s="11"/>
       <c r="D370" s="10" t="str">
@@ -17745,7 +17778,7 @@
       <c r="R370" s="11"/>
       <c r="S370" s="10"/>
     </row>
-    <row r="371" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="371" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B371" s="10"/>
       <c r="C371" s="11"/>
       <c r="D371" s="10" t="str">
@@ -17766,7 +17799,7 @@
       <c r="R371" s="11"/>
       <c r="S371" s="10"/>
     </row>
-    <row r="372" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="372" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B372" s="10"/>
       <c r="C372" s="11"/>
       <c r="D372" s="10" t="str">
@@ -17787,7 +17820,7 @@
       <c r="R372" s="11"/>
       <c r="S372" s="10"/>
     </row>
-    <row r="373" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="373" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B373" s="10"/>
       <c r="C373" s="11"/>
       <c r="D373" s="10" t="str">
@@ -17808,7 +17841,7 @@
       <c r="R373" s="11"/>
       <c r="S373" s="10"/>
     </row>
-    <row r="374" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="374" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B374" s="10"/>
       <c r="C374" s="11"/>
       <c r="D374" s="10" t="str">
@@ -17829,7 +17862,7 @@
       <c r="R374" s="11"/>
       <c r="S374" s="10"/>
     </row>
-    <row r="375" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="375" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B375" s="10"/>
       <c r="C375" s="11"/>
       <c r="D375" s="10" t="str">
@@ -17850,7 +17883,7 @@
       <c r="R375" s="11"/>
       <c r="S375" s="10"/>
     </row>
-    <row r="376" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="376" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B376" s="10"/>
       <c r="C376" s="11"/>
       <c r="D376" s="10" t="str">
@@ -17871,7 +17904,7 @@
       <c r="R376" s="11"/>
       <c r="S376" s="10"/>
     </row>
-    <row r="377" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="377" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B377" s="10"/>
       <c r="C377" s="11"/>
       <c r="D377" s="10" t="str">
@@ -17892,7 +17925,7 @@
       <c r="R377" s="11"/>
       <c r="S377" s="10"/>
     </row>
-    <row r="378" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="378" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B378" s="10"/>
       <c r="C378" s="11"/>
       <c r="D378" s="10" t="str">
@@ -17913,7 +17946,7 @@
       <c r="R378" s="11"/>
       <c r="S378" s="10"/>
     </row>
-    <row r="379" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="379" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B379" s="10"/>
       <c r="C379" s="11"/>
       <c r="D379" s="10" t="str">
@@ -17934,7 +17967,7 @@
       <c r="R379" s="11"/>
       <c r="S379" s="10"/>
     </row>
-    <row r="380" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="380" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B380" s="10"/>
       <c r="C380" s="11"/>
       <c r="D380" s="10" t="str">
@@ -17955,7 +17988,7 @@
       <c r="R380" s="11"/>
       <c r="S380" s="10"/>
     </row>
-    <row r="381" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="381" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B381" s="10"/>
       <c r="C381" s="11"/>
       <c r="D381" s="10" t="str">
@@ -17976,7 +18009,7 @@
       <c r="R381" s="11"/>
       <c r="S381" s="10"/>
     </row>
-    <row r="382" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="382" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B382" s="10"/>
       <c r="C382" s="11"/>
       <c r="D382" s="10" t="str">
@@ -17997,7 +18030,7 @@
       <c r="R382" s="11"/>
       <c r="S382" s="10"/>
     </row>
-    <row r="383" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="383" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B383" s="10"/>
       <c r="C383" s="11"/>
       <c r="D383" s="10" t="str">
@@ -18018,7 +18051,7 @@
       <c r="R383" s="11"/>
       <c r="S383" s="10"/>
     </row>
-    <row r="384" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="384" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B384" s="10"/>
       <c r="C384" s="11"/>
       <c r="D384" s="10" t="str">
@@ -18039,7 +18072,7 @@
       <c r="R384" s="11"/>
       <c r="S384" s="10"/>
     </row>
-    <row r="385" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="385" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B385" s="10"/>
       <c r="C385" s="11"/>
       <c r="D385" s="10" t="str">
@@ -18060,7 +18093,7 @@
       <c r="R385" s="11"/>
       <c r="S385" s="10"/>
     </row>
-    <row r="386" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="386" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B386" s="10"/>
       <c r="C386" s="11"/>
       <c r="D386" s="10" t="str">
@@ -18081,7 +18114,7 @@
       <c r="R386" s="11"/>
       <c r="S386" s="10"/>
     </row>
-    <row r="387" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="387" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B387" s="10"/>
       <c r="C387" s="11"/>
       <c r="D387" s="10" t="str">
@@ -18102,7 +18135,7 @@
       <c r="R387" s="11"/>
       <c r="S387" s="10"/>
     </row>
-    <row r="388" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="388" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B388" s="10"/>
       <c r="C388" s="11"/>
       <c r="D388" s="10" t="str">
@@ -18123,7 +18156,7 @@
       <c r="R388" s="11"/>
       <c r="S388" s="10"/>
     </row>
-    <row r="389" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="389" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B389" s="10"/>
       <c r="C389" s="11"/>
       <c r="D389" s="10" t="str">
@@ -18144,7 +18177,7 @@
       <c r="R389" s="11"/>
       <c r="S389" s="10"/>
     </row>
-    <row r="390" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="390" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B390" s="10"/>
       <c r="C390" s="11"/>
       <c r="D390" s="10" t="str">
@@ -18165,7 +18198,7 @@
       <c r="R390" s="11"/>
       <c r="S390" s="10"/>
     </row>
-    <row r="391" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="391" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B391" s="10"/>
       <c r="C391" s="11"/>
       <c r="D391" s="10" t="str">
@@ -18186,7 +18219,7 @@
       <c r="R391" s="11"/>
       <c r="S391" s="10"/>
     </row>
-    <row r="392" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="392" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B392" s="10"/>
       <c r="C392" s="11"/>
       <c r="D392" s="10" t="str">
@@ -18207,7 +18240,7 @@
       <c r="R392" s="11"/>
       <c r="S392" s="10"/>
     </row>
-    <row r="393" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="393" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B393" s="10"/>
       <c r="C393" s="11"/>
       <c r="D393" s="10" t="str">
@@ -18228,7 +18261,7 @@
       <c r="R393" s="11"/>
       <c r="S393" s="10"/>
     </row>
-    <row r="394" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="394" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B394" s="10"/>
       <c r="C394" s="11"/>
       <c r="D394" s="10" t="str">
@@ -18249,16 +18282,16 @@
       <c r="R394" s="11"/>
       <c r="S394" s="10"/>
     </row>
-    <row r="395" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="395" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B395" s="10"/>
       <c r="C395" s="11"/>
       <c r="D395" s="10" t="str">
-        <f t="shared" ref="D395:D407" si="22">IF(G395="","",IF(OR(G395="선급금",G395="중도금",G395="잔금"),"A",IF(G395="자재","B",IF(G395="특허료","C",""))))</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H395" s="4"/>
       <c r="I395" s="6" t="str">
-        <f t="shared" ref="I395:I405" ca="1" si="23">IF(C395="","",IF(L395="",TODAY()-C395,L395-C395))</f>
+        <f t="shared" ca="1" si="21"/>
         <v/>
       </c>
       <c r="J395" s="13"/>
@@ -18270,16 +18303,16 @@
       <c r="R395" s="11"/>
       <c r="S395" s="10"/>
     </row>
-    <row r="396" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="396" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B396" s="10"/>
       <c r="C396" s="11"/>
       <c r="D396" s="10" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="D396:D408" si="22">IF(G396="","",IF(OR(G396="선급금",G396="중도금",G396="잔금"),"A",IF(G396="자재","B",IF(G396="특허료","C",""))))</f>
         <v/>
       </c>
       <c r="H396" s="4"/>
       <c r="I396" s="6" t="str">
-        <f t="shared" ca="1" si="23"/>
+        <f t="shared" ref="I396:I406" ca="1" si="23">IF(C396="","",IF(L396="",TODAY()-C396,L396-C396))</f>
         <v/>
       </c>
       <c r="J396" s="13"/>
@@ -18291,7 +18324,7 @@
       <c r="R396" s="11"/>
       <c r="S396" s="10"/>
     </row>
-    <row r="397" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="397" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B397" s="10"/>
       <c r="C397" s="11"/>
       <c r="D397" s="10" t="str">
@@ -18312,7 +18345,7 @@
       <c r="R397" s="11"/>
       <c r="S397" s="10"/>
     </row>
-    <row r="398" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="398" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B398" s="10"/>
       <c r="C398" s="11"/>
       <c r="D398" s="10" t="str">
@@ -18333,7 +18366,7 @@
       <c r="R398" s="11"/>
       <c r="S398" s="10"/>
     </row>
-    <row r="399" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="399" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B399" s="10"/>
       <c r="C399" s="11"/>
       <c r="D399" s="10" t="str">
@@ -18354,7 +18387,7 @@
       <c r="R399" s="11"/>
       <c r="S399" s="10"/>
     </row>
-    <row r="400" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="400" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B400" s="10"/>
       <c r="C400" s="11"/>
       <c r="D400" s="10" t="str">
@@ -18375,7 +18408,7 @@
       <c r="R400" s="11"/>
       <c r="S400" s="10"/>
     </row>
-    <row r="401" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="401" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B401" s="10"/>
       <c r="C401" s="11"/>
       <c r="D401" s="10" t="str">
@@ -18396,23 +18429,28 @@
       <c r="R401" s="11"/>
       <c r="S401" s="10"/>
     </row>
-    <row r="402" spans="2:19">
+    <row r="402" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B402" s="10"/>
       <c r="C402" s="11"/>
-      <c r="D402" s="1" t="str">
+      <c r="D402" s="10" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="I402" s="1" t="str">
+      <c r="H402" s="4"/>
+      <c r="I402" s="6" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
+      <c r="J402" s="13"/>
       <c r="K402" s="11"/>
       <c r="L402" s="11"/>
+      <c r="M402" s="10"/>
+      <c r="N402" s="10"/>
       <c r="Q402" s="11"/>
       <c r="R402" s="11"/>
-    </row>
-    <row r="403" spans="2:19">
+      <c r="S402" s="10"/>
+    </row>
+    <row r="403" spans="2:19" hidden="1">
       <c r="B403" s="10"/>
       <c r="C403" s="11"/>
       <c r="D403" s="1" t="str">
@@ -18428,7 +18466,7 @@
       <c r="Q403" s="11"/>
       <c r="R403" s="11"/>
     </row>
-    <row r="404" spans="2:19">
+    <row r="404" spans="2:19" hidden="1">
       <c r="B404" s="10"/>
       <c r="C404" s="11"/>
       <c r="D404" s="1" t="str">
@@ -18439,10 +18477,12 @@
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
+      <c r="K404" s="11"/>
+      <c r="L404" s="11"/>
       <c r="Q404" s="11"/>
       <c r="R404" s="11"/>
     </row>
-    <row r="405" spans="2:19">
+    <row r="405" spans="2:19" hidden="1">
       <c r="B405" s="10"/>
       <c r="C405" s="11"/>
       <c r="D405" s="1" t="str">
@@ -18456,17 +18496,21 @@
       <c r="Q405" s="11"/>
       <c r="R405" s="11"/>
     </row>
-    <row r="406" spans="2:19">
+    <row r="406" spans="2:19" hidden="1">
       <c r="B406" s="10"/>
       <c r="C406" s="11"/>
       <c r="D406" s="1" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
+      <c r="I406" s="1" t="str">
+        <f t="shared" ca="1" si="23"/>
+        <v/>
+      </c>
       <c r="Q406" s="11"/>
       <c r="R406" s="11"/>
     </row>
-    <row r="407" spans="2:19">
+    <row r="407" spans="2:19" hidden="1">
       <c r="B407" s="10"/>
       <c r="C407" s="11"/>
       <c r="D407" s="1" t="str">
@@ -18476,12 +18520,28 @@
       <c r="Q407" s="11"/>
       <c r="R407" s="11"/>
     </row>
-    <row r="408" spans="2:19" ht="16.5" customHeight="1">
-      <c r="C408" s="58"/>
-      <c r="F408" s="62"/>
+    <row r="408" spans="2:19" hidden="1">
+      <c r="B408" s="10"/>
+      <c r="C408" s="11"/>
+      <c r="D408" s="1" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Q408" s="11"/>
+      <c r="R408" s="11"/>
+    </row>
+    <row r="409" spans="2:19" ht="16.5" customHeight="1">
+      <c r="C409" s="58"/>
+      <c r="F409" s="62"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S407"/>
+  <autoFilter ref="A1:S408">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="A"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E3 F57:F60">
     <cfRule type="expression" dxfId="73" priority="93">
@@ -18508,7 +18568,7 @@
       <formula>$J37="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E98:E99 E186:F192 H186:H192 C186:C192">
+  <conditionalFormatting sqref="E98:E99 E187:F193 H187:H193 C187:C193">
     <cfRule type="expression" dxfId="68" priority="75">
       <formula>$J98="잔금"</formula>
     </cfRule>
@@ -18588,259 +18648,259 @@
       <formula>$J117="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F142:F149">
+  <conditionalFormatting sqref="F143:F150">
     <cfRule type="expression" dxfId="52" priority="58">
-      <formula>$J142="잔금"</formula>
+      <formula>$J143="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E142:E149">
+  <conditionalFormatting sqref="E143:E150">
     <cfRule type="expression" dxfId="51" priority="57">
-      <formula>$J142="잔금"</formula>
+      <formula>$J143="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H142:H149">
+  <conditionalFormatting sqref="H143:H150">
     <cfRule type="expression" dxfId="50" priority="56">
-      <formula>$J142="잔금"</formula>
+      <formula>$J143="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E151:E157">
+  <conditionalFormatting sqref="E152:E158">
     <cfRule type="expression" dxfId="49" priority="54">
-      <formula>$J151="잔금"</formula>
+      <formula>$J152="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F151:F157">
+  <conditionalFormatting sqref="F152:F158">
     <cfRule type="expression" dxfId="48" priority="53">
-      <formula>$J151="잔금"</formula>
+      <formula>$J152="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C151:C157">
+  <conditionalFormatting sqref="C152:C158">
     <cfRule type="expression" dxfId="47" priority="52">
-      <formula>$J151="잔금"</formula>
+      <formula>$J152="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H151:H157">
+  <conditionalFormatting sqref="H152:H158">
     <cfRule type="expression" dxfId="46" priority="51">
-      <formula>$J151="잔금"</formula>
+      <formula>$J152="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C158">
+  <conditionalFormatting sqref="C159">
     <cfRule type="expression" dxfId="45" priority="50">
-      <formula>$I158="잔금"</formula>
+      <formula>$I159="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F159:F162">
+  <conditionalFormatting sqref="F160:F163">
     <cfRule type="expression" dxfId="44" priority="49">
-      <formula>$J159="잔금"</formula>
+      <formula>$J160="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E159:E162">
+  <conditionalFormatting sqref="E160:E163">
     <cfRule type="expression" dxfId="43" priority="48">
-      <formula>$J159="잔금"</formula>
+      <formula>$J160="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C159:C165">
+  <conditionalFormatting sqref="C160:C166">
     <cfRule type="expression" dxfId="42" priority="47">
-      <formula>$J159="잔금"</formula>
+      <formula>$J160="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H159:H162">
+  <conditionalFormatting sqref="H160:H163">
     <cfRule type="expression" dxfId="41" priority="46">
-      <formula>$J159="잔금"</formula>
+      <formula>$J160="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F166:F178">
+  <conditionalFormatting sqref="F167:F179">
     <cfRule type="expression" dxfId="40" priority="45">
-      <formula>$J166="잔금"</formula>
+      <formula>$J167="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F179:F185">
+  <conditionalFormatting sqref="F180:F186">
     <cfRule type="expression" dxfId="39" priority="44">
-      <formula>$J179="잔금"</formula>
+      <formula>$J180="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E166:E178">
+  <conditionalFormatting sqref="E167:E179">
     <cfRule type="expression" dxfId="38" priority="43">
-      <formula>$J166="잔금"</formula>
+      <formula>$J167="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E179:E185">
+  <conditionalFormatting sqref="E180:E186">
     <cfRule type="expression" dxfId="37" priority="42">
-      <formula>$J179="잔금"</formula>
+      <formula>$J180="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C166:C178">
+  <conditionalFormatting sqref="C167:C179">
     <cfRule type="expression" dxfId="36" priority="41">
-      <formula>$J166="잔금"</formula>
+      <formula>$J167="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C179:C185">
+  <conditionalFormatting sqref="C180:C186">
     <cfRule type="expression" dxfId="35" priority="40">
-      <formula>$J179="잔금"</formula>
+      <formula>$J180="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H166:H178">
+  <conditionalFormatting sqref="H167:H179">
     <cfRule type="expression" dxfId="34" priority="39">
-      <formula>$J166="잔금"</formula>
+      <formula>$J167="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H179:H185">
+  <conditionalFormatting sqref="H180:H186">
     <cfRule type="expression" dxfId="33" priority="38">
-      <formula>$J179="잔금"</formula>
+      <formula>$J180="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F194:F200">
+  <conditionalFormatting sqref="F195:F201">
     <cfRule type="expression" dxfId="32" priority="33">
-      <formula>$J194="잔금"</formula>
+      <formula>$J195="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E194:E200">
+  <conditionalFormatting sqref="E195:E201">
     <cfRule type="expression" dxfId="31" priority="32">
-      <formula>$J194="잔금"</formula>
+      <formula>$J195="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C194:C201">
+  <conditionalFormatting sqref="C195:C202">
     <cfRule type="expression" dxfId="30" priority="31">
-      <formula>$J194="잔금"</formula>
+      <formula>$J195="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H194:H200">
+  <conditionalFormatting sqref="H195:H201">
     <cfRule type="expression" dxfId="29" priority="30">
-      <formula>$J194="잔금"</formula>
+      <formula>$J195="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C202:C215">
+  <conditionalFormatting sqref="C203:C216">
     <cfRule type="expression" dxfId="28" priority="29">
-      <formula>$J202="잔금"</formula>
+      <formula>$J203="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F202:F215">
+  <conditionalFormatting sqref="F203:F216">
     <cfRule type="expression" dxfId="27" priority="28">
-      <formula>$J202="잔금"</formula>
+      <formula>$J203="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H202:H215">
+  <conditionalFormatting sqref="H203:H216">
     <cfRule type="expression" dxfId="26" priority="27">
-      <formula>$J202="잔금"</formula>
+      <formula>$J203="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E202:E216">
+  <conditionalFormatting sqref="E203:E217">
     <cfRule type="expression" dxfId="25" priority="26">
-      <formula>$J202="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C216">
-    <cfRule type="expression" dxfId="24" priority="25">
-      <formula>$I216="잔금"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H216">
-    <cfRule type="expression" dxfId="23" priority="20">
-      <formula>$I216="잔금"</formula>
+      <formula>$J203="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C217">
-    <cfRule type="expression" dxfId="22" priority="19">
+    <cfRule type="expression" dxfId="24" priority="25">
+      <formula>$I217="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H217">
+    <cfRule type="expression" dxfId="23" priority="20">
       <formula>$I217="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C218">
-    <cfRule type="expression" dxfId="21" priority="18">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>$I218="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C219">
-    <cfRule type="expression" dxfId="20" priority="17">
+    <cfRule type="expression" dxfId="21" priority="18">
       <formula>$I219="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F220:F229">
-    <cfRule type="expression" dxfId="19" priority="16">
-      <formula>$J220="잔금"</formula>
+  <conditionalFormatting sqref="C220">
+    <cfRule type="expression" dxfId="20" priority="17">
+      <formula>$I220="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F230:F243">
-    <cfRule type="expression" dxfId="18" priority="15">
-      <formula>$J230="잔금"</formula>
+  <conditionalFormatting sqref="F221:F230">
+    <cfRule type="expression" dxfId="19" priority="16">
+      <formula>$J221="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E220:E229">
-    <cfRule type="expression" dxfId="17" priority="14">
-      <formula>$J220="잔금"</formula>
+  <conditionalFormatting sqref="F231:F244">
+    <cfRule type="expression" dxfId="18" priority="15">
+      <formula>$J231="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E230:E243">
-    <cfRule type="expression" dxfId="16" priority="13">
-      <formula>$J230="잔금"</formula>
+  <conditionalFormatting sqref="E221:E230">
+    <cfRule type="expression" dxfId="17" priority="14">
+      <formula>$J221="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H220:H229">
-    <cfRule type="expression" dxfId="15" priority="12">
-      <formula>$J220="잔금"</formula>
+  <conditionalFormatting sqref="E231:E244">
+    <cfRule type="expression" dxfId="16" priority="13">
+      <formula>$J231="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H230:H243">
-    <cfRule type="expression" dxfId="14" priority="11">
-      <formula>$J230="잔금"</formula>
+  <conditionalFormatting sqref="H221:H230">
+    <cfRule type="expression" dxfId="15" priority="12">
+      <formula>$J221="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C245">
-    <cfRule type="expression" dxfId="13" priority="10">
-      <formula>$I245="잔금"</formula>
+  <conditionalFormatting sqref="H231:H244">
+    <cfRule type="expression" dxfId="14" priority="11">
+      <formula>$J231="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C246">
-    <cfRule type="expression" dxfId="12" priority="9">
+    <cfRule type="expression" dxfId="13" priority="10">
       <formula>$I246="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C247">
-    <cfRule type="expression" dxfId="11" priority="8">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>$I247="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F248:F252">
-    <cfRule type="expression" dxfId="10" priority="7">
-      <formula>$J248="잔금"</formula>
+  <conditionalFormatting sqref="C248">
+    <cfRule type="expression" dxfId="11" priority="8">
+      <formula>$I248="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E248:E252">
-    <cfRule type="expression" dxfId="9" priority="6">
-      <formula>$J248="잔금"</formula>
+  <conditionalFormatting sqref="F249:F253">
+    <cfRule type="expression" dxfId="10" priority="7">
+      <formula>$J249="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C248:C252">
-    <cfRule type="expression" dxfId="8" priority="5">
-      <formula>$J248="잔금"</formula>
+  <conditionalFormatting sqref="E249:E253">
+    <cfRule type="expression" dxfId="9" priority="6">
+      <formula>$J249="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H248:H252">
-    <cfRule type="expression" dxfId="7" priority="4">
-      <formula>$J248="잔금"</formula>
+  <conditionalFormatting sqref="C249:C253">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>$J249="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C253:C256">
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>$I253="잔금"</formula>
+  <conditionalFormatting sqref="H249:H253">
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>$J249="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F257:F266">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$J257="잔금"</formula>
+  <conditionalFormatting sqref="C254:C257">
+    <cfRule type="expression" dxfId="6" priority="3">
+      <formula>$I254="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F267:F275">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$J267="잔금"</formula>
+  <conditionalFormatting sqref="F258:F267">
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>$J258="잔금"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F268:F276">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>$J268="잔금"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="G2:G71">
       <formula1>"선급금,중도금,잔금,자재,특허료"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N275">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N118 N120:N276">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D407">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D408">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1519" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="470">
   <si>
     <t>순번</t>
   </si>
@@ -1603,68 +1603,92 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>선급금</t>
+    <t>소촌대성베르힐</t>
+  </si>
+  <si>
+    <t>부천소사엠제이펠리스</t>
+  </si>
+  <si>
+    <t>도경오벨리스</t>
+  </si>
+  <si>
+    <t>부천위브더스테이트</t>
+  </si>
+  <si>
+    <t>자재대금</t>
+  </si>
+  <si>
+    <t>신사한신휴플러스</t>
+  </si>
+  <si>
+    <t>아인스빌</t>
+  </si>
+  <si>
+    <t>동탄역시범리슈빌</t>
+  </si>
+  <si>
+    <t>파크푸르지오2단지</t>
+  </si>
+  <si>
+    <t>경동아산음봉산동850영업소</t>
+  </si>
+  <si>
+    <t>구영2차푸르지오</t>
+  </si>
+  <si>
+    <t>해운대센텀트루엘2단지</t>
+  </si>
+  <si>
+    <t>일광자이푸르지오1단지</t>
+  </si>
+  <si>
+    <t>남가좌현대</t>
+  </si>
+  <si>
+    <t>푸른뫼아파트</t>
+  </si>
+  <si>
+    <t>(주)다원건설</t>
+  </si>
+  <si>
+    <t>(주)덕일산업</t>
+  </si>
+  <si>
+    <t>(주)청명이앤디</t>
+  </si>
+  <si>
+    <t>태원건설(주)</t>
+  </si>
+  <si>
+    <t>덕수건설(주)</t>
+  </si>
+  <si>
+    <t>자재</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>소촌대성베르힐</t>
-  </si>
-  <si>
-    <t>부천소사엠제이펠리스</t>
-  </si>
-  <si>
-    <t>도경오벨리스</t>
-  </si>
-  <si>
-    <t>부천위브더스테이트</t>
-  </si>
-  <si>
-    <t>자재대금</t>
-  </si>
-  <si>
-    <t>신사한신휴플러스</t>
-  </si>
-  <si>
-    <t>아인스빌</t>
-  </si>
-  <si>
-    <t>동탄역시범리슈빌</t>
-  </si>
-  <si>
-    <t>파크푸르지오2단지</t>
-  </si>
-  <si>
-    <t>경동아산음봉산동850영업소</t>
-  </si>
-  <si>
-    <t>구영2차푸르지오</t>
-  </si>
-  <si>
-    <t>해운대센텀트루엘2단지</t>
-  </si>
-  <si>
-    <t>해운대센텀트루엘2단지(에폭시)</t>
-  </si>
-  <si>
-    <t>일광자이푸르지오1단지</t>
-  </si>
-  <si>
-    <t>(주)다원건설</t>
-  </si>
-  <si>
-    <t>(주)덕일산업</t>
-  </si>
-  <si>
-    <t>(주)청명이앤디</t>
-  </si>
-  <si>
     <t>2026-03-26</t>
   </si>
   <si>
     <t>2026-03-27</t>
   </si>
   <si>
-    <t>자재</t>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>동탄역시범한화꿈에그린프레스티지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)석민이앤씨</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>행원마을동아솔레시티</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)이음건설</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2054,107 +2078,7 @@
     <cellStyle name="표준 2" xfId="7"/>
     <cellStyle name="표준 3" xfId="1"/>
   </cellStyles>
-  <dxfs count="94">
-    <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFA6A6A6"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE6F3FF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="84">
     <dxf>
       <fill>
         <patternFill>
@@ -3713,7 +3637,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S409"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S410"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.125" style="1" customWidth="1"/>
@@ -3822,7 +3747,7 @@
       </c>
       <c r="I2" s="12">
         <f t="shared" ref="I2:I33" ca="1" si="1">IF(C2="","",IF(L2="",TODAY()-C2,L2-C2))</f>
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J2" s="13" t="str">
         <f t="shared" ref="J2:J33" ca="1" si="2">IF(I2="","",
@@ -3939,7 +3864,7 @@
       </c>
       <c r="I4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4037,7 +3962,7 @@
       </c>
       <c r="I6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4093,7 +4018,7 @@
       </c>
       <c r="I7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J7" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4142,7 +4067,7 @@
       </c>
       <c r="I8" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4193,7 +4118,7 @@
       </c>
       <c r="I9" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4245,7 +4170,7 @@
       </c>
       <c r="I10" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4384,7 +4309,7 @@
       </c>
       <c r="I13" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4440,7 +4365,7 @@
       </c>
       <c r="I14" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4463,7 +4388,7 @@
       </c>
       <c r="S14" s="10"/>
     </row>
-    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="15" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B15" s="10">
         <f>IF(C15="","",COUNTA($C$2:C15))</f>
         <v>14</v>
@@ -4489,7 +4414,7 @@
       </c>
       <c r="I15" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4512,7 +4437,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="16" spans="1:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B16" s="10">
         <f>IF(C16="","",COUNTA($C$2:C16))</f>
         <v>15</v>
@@ -4538,7 +4463,7 @@
       </c>
       <c r="I16" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4559,7 +4484,7 @@
       <c r="R16" s="14"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="17" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B17" s="10">
         <f>IF(C17="","",COUNTA($C$2:C17))</f>
         <v>16</v>
@@ -4585,7 +4510,7 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4606,7 +4531,7 @@
       <c r="R17" s="14"/>
       <c r="S17" s="10"/>
     </row>
-    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="18" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B18" s="10">
         <f>IF(C18="","",COUNTA($C$2:C18))</f>
         <v>17</v>
@@ -4632,7 +4557,7 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4653,7 +4578,7 @@
       <c r="R18" s="14"/>
       <c r="S18" s="10"/>
     </row>
-    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="19" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B19" s="10">
         <f>IF(C19="","",COUNTA($C$2:C19))</f>
         <v>18</v>
@@ -4679,7 +4604,7 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4700,7 +4625,7 @@
       <c r="R19" s="14"/>
       <c r="S19" s="10"/>
     </row>
-    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="20" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B20" s="10">
         <f>IF(C20="","",COUNTA($C$2:C20))</f>
         <v>19</v>
@@ -4726,7 +4651,7 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4747,7 +4672,7 @@
       <c r="R20" s="14"/>
       <c r="S20" s="10"/>
     </row>
-    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="21" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B21" s="10">
         <f>IF(C21="","",COUNTA($C$2:C21))</f>
         <v>20</v>
@@ -4773,7 +4698,7 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4796,7 +4721,7 @@
       </c>
       <c r="S21" s="10"/>
     </row>
-    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="22" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B22" s="10">
         <f>IF(C22="","",COUNTA($C$2:C22))</f>
         <v>21</v>
@@ -4822,7 +4747,7 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4845,7 +4770,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="23" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B23" s="10">
         <f>IF(C23="","",COUNTA($C$2:C23))</f>
         <v>22</v>
@@ -4871,7 +4796,7 @@
       </c>
       <c r="I23" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4894,7 +4819,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="24" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B24" s="10">
         <f>IF(C24="","",COUNTA($C$2:C24))</f>
         <v>23</v>
@@ -4920,7 +4845,7 @@
       </c>
       <c r="I24" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4943,7 +4868,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="25" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B25" s="10">
         <f>IF(C25="","",COUNTA($C$2:C25))</f>
         <v>24</v>
@@ -4969,7 +4894,7 @@
       </c>
       <c r="I25" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -4992,7 +4917,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="26" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B26" s="10">
         <f>IF(C26="","",COUNTA($C$2:C26))</f>
         <v>25</v>
@@ -5018,7 +4943,7 @@
       </c>
       <c r="I26" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5041,7 +4966,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="27" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B27" s="10">
         <f>IF(C27="","",COUNTA($C$2:C27))</f>
         <v>26</v>
@@ -5067,7 +4992,7 @@
       </c>
       <c r="I27" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5090,7 +5015,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="28" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B28" s="10">
         <f>IF(C28="","",COUNTA($C$2:C28))</f>
         <v>27</v>
@@ -5116,7 +5041,7 @@
       </c>
       <c r="I28" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5139,7 +5064,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="29" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B29" s="10">
         <f>IF(C29="","",COUNTA($C$2:C29))</f>
         <v>28</v>
@@ -5165,7 +5090,7 @@
       </c>
       <c r="I29" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5188,7 +5113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="30" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B30" s="10">
         <f>IF(C30="","",COUNTA($C$2:C30))</f>
         <v>29</v>
@@ -5214,7 +5139,7 @@
       </c>
       <c r="I30" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5237,7 +5162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="31" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B31" s="10">
         <f>IF(C31="","",COUNTA($C$2:C31))</f>
         <v>30</v>
@@ -5263,7 +5188,7 @@
       </c>
       <c r="I31" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5286,7 +5211,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="32" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B32" s="10">
         <f>IF(C32="","",COUNTA($C$2:C32))</f>
         <v>31</v>
@@ -5312,7 +5237,7 @@
       </c>
       <c r="I32" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5335,7 +5260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="33" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B33" s="10">
         <f>IF(C33="","",COUNTA($C$2:C33))</f>
         <v>32</v>
@@ -5361,7 +5286,7 @@
       </c>
       <c r="I33" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -5384,7 +5309,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="34" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B34" s="10">
         <f>IF(C34="","",COUNTA($C$2:C34))</f>
         <v>33</v>
@@ -5410,7 +5335,7 @@
       </c>
       <c r="I34" s="12">
         <f t="shared" ref="I34:I65" ca="1" si="3">IF(C34="","",IF(L34="",TODAY()-C34,L34-C34))</f>
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ref="J34:J65" ca="1" si="4">IF(I34="","",
@@ -5441,7 +5366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="35" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B35" s="10">
         <f>IF(C35="","",COUNTA($C$2:C35))</f>
         <v>34</v>
@@ -5467,7 +5392,7 @@
       </c>
       <c r="I35" s="12">
         <f t="shared" ca="1" si="3"/>
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5490,7 +5415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="36" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B36" s="10">
         <f>IF(C36="","",COUNTA($C$2:C36))</f>
         <v>35</v>
@@ -5516,7 +5441,7 @@
       </c>
       <c r="I36" s="12">
         <f t="shared" ca="1" si="3"/>
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5535,7 +5460,7 @@
       <c r="R36" s="14"/>
       <c r="S36" s="10"/>
     </row>
-    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="37" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B37" s="10">
         <f>IF(C37="","",COUNTA($C$2:C37))</f>
         <v>36</v>
@@ -5561,7 +5486,7 @@
       </c>
       <c r="I37" s="12">
         <f t="shared" ca="1" si="3"/>
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5591,7 +5516,7 @@
       </c>
       <c r="S37" s="10"/>
     </row>
-    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="38" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B38" s="10">
         <f>IF(C38="","",COUNTA($C$2:C38))</f>
         <v>37</v>
@@ -5613,11 +5538,11 @@
         <v>48</v>
       </c>
       <c r="H38" s="4">
-        <v>44129345</v>
+        <v>46151936</v>
       </c>
       <c r="I38" s="12">
         <f t="shared" ca="1" si="3"/>
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5647,7 +5572,7 @@
       </c>
       <c r="S38" s="10"/>
     </row>
-    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="39" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B39" s="10">
         <f>IF(C39="","",COUNTA($C$2:C39))</f>
         <v>38</v>
@@ -5673,7 +5598,7 @@
       </c>
       <c r="I39" s="12">
         <f t="shared" ca="1" si="3"/>
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5700,7 +5625,7 @@
       </c>
       <c r="S39" s="10"/>
     </row>
-    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="40" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B40" s="10">
         <f>IF(C40="","",COUNTA($C$2:C40))</f>
         <v>39</v>
@@ -5749,7 +5674,7 @@
       <c r="R40" s="11"/>
       <c r="S40" s="10"/>
     </row>
-    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="41" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B41" s="10">
         <f>IF(C41="","",COUNTA($C$2:C41))</f>
         <v>40</v>
@@ -5775,7 +5700,7 @@
       </c>
       <c r="I41" s="12">
         <f t="shared" ca="1" si="3"/>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5805,7 +5730,7 @@
       </c>
       <c r="S41" s="10"/>
     </row>
-    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="42" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B42" s="10">
         <f>IF(C42="","",COUNTA($C$2:C42))</f>
         <v>41</v>
@@ -5831,7 +5756,7 @@
       </c>
       <c r="I42" s="12">
         <f t="shared" ca="1" si="3"/>
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5858,7 +5783,7 @@
       </c>
       <c r="S42" s="10"/>
     </row>
-    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="43" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B43" s="10">
         <f>IF(C43="","",COUNTA($C$2:C43))</f>
         <v>42</v>
@@ -5910,7 +5835,7 @@
       <c r="R43" s="11"/>
       <c r="S43" s="10"/>
     </row>
-    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="44" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B44" s="10">
         <f>IF(C44="","",COUNTA($C$2:C44))</f>
         <v>43</v>
@@ -5936,7 +5861,7 @@
       </c>
       <c r="I44" s="12">
         <f t="shared" ca="1" si="3"/>
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J44" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5961,7 +5886,7 @@
       </c>
       <c r="S44" s="10"/>
     </row>
-    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="45" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B45" s="10">
         <f>IF(C45="","",COUNTA($C$2:C45))</f>
         <v>44</v>
@@ -6010,7 +5935,7 @@
       <c r="R45" s="11"/>
       <c r="S45" s="10"/>
     </row>
-    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="46" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B46" s="10">
         <f>IF(C46="","",COUNTA($C$2:C46))</f>
         <v>45</v>
@@ -6059,7 +5984,7 @@
       <c r="R46" s="11"/>
       <c r="S46" s="10"/>
     </row>
-    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="47" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B47" s="10">
         <f>IF(C47="","",COUNTA($C$2:C47))</f>
         <v>46</v>
@@ -6108,7 +6033,7 @@
       <c r="R47" s="11"/>
       <c r="S47" s="10"/>
     </row>
-    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="48" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B48" s="10">
         <f>IF(C48="","",COUNTA($C$2:C48))</f>
         <v>47</v>
@@ -6157,7 +6082,7 @@
       <c r="R48" s="11"/>
       <c r="S48" s="10"/>
     </row>
-    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="49" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B49" s="10">
         <f>IF(C49="","",COUNTA($C$2:C49))</f>
         <v>48</v>
@@ -6206,7 +6131,7 @@
       <c r="R49" s="11"/>
       <c r="S49" s="10"/>
     </row>
-    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="50" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B50" s="10">
         <f>IF(C50="","",COUNTA($C$2:C50))</f>
         <v>49</v>
@@ -6255,7 +6180,7 @@
       <c r="R50" s="11"/>
       <c r="S50" s="10"/>
     </row>
-    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="51" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B51" s="10">
         <f>IF(C51="","",COUNTA($C$2:C51))</f>
         <v>50</v>
@@ -6301,7 +6226,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="10"/>
     </row>
-    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="52" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B52" s="10">
         <f>IF(C52="","",COUNTA($C$2:C52))</f>
         <v>51</v>
@@ -6347,7 +6272,7 @@
       <c r="R52" s="11"/>
       <c r="S52" s="10"/>
     </row>
-    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="53" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B53" s="10">
         <f>IF(C53="","",COUNTA($C$2:C53))</f>
         <v>52</v>
@@ -6396,7 +6321,7 @@
       <c r="R53" s="11"/>
       <c r="S53" s="10"/>
     </row>
-    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="54" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B54" s="10">
         <f>IF(C54="","",COUNTA($C$2:C54))</f>
         <v>53</v>
@@ -6450,7 +6375,7 @@
       </c>
       <c r="S54" s="10"/>
     </row>
-    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="55" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B55" s="10">
         <f>IF(C55="","",COUNTA($C$2:C55))</f>
         <v>54</v>
@@ -6494,7 +6419,7 @@
       <c r="R55" s="11"/>
       <c r="S55" s="10"/>
     </row>
-    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="56" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B56" s="10">
         <f>IF(C56="","",COUNTA($C$2:C56))</f>
         <v>55</v>
@@ -6543,7 +6468,7 @@
       <c r="R56" s="11"/>
       <c r="S56" s="10"/>
     </row>
-    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" customHeight="1">
+    <row r="57" spans="2:19" s="6" customFormat="1" ht="16.5" hidden="1" customHeight="1">
       <c r="B57" s="10">
         <f>IF(C57="","",COUNTA($C$2:C57))</f>
         <v>56</v>
@@ -6569,7 +6494,7 @@
       </c>
       <c r="I57" s